--- a/cables.xlsx
+++ b/cables.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/SystemDocumentation/github/uactechdoc/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BE20EA-1D71-4144-91A6-6796A5FA9626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C533099-6638-234B-8899-0C0135B5933B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5780" yWindow="1640" windowWidth="24460" windowHeight="16580" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="5" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -8230,7 +8230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8445,7 +8445,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8746,19 +8745,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8802,6 +8788,19 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
     </dxf>
     <dxf>
       <border outline="0">
@@ -17329,70 +17328,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17648,13 +17584,76 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M950" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="A1:M949" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="17" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{B4B079C1-C2FD-4543-BF85-C40BEF0990F3}" name="SrcPort" dataDxfId="16" totalsRowDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B4B079C1-C2FD-4543-BF85-C40BEF0990F3}" name="SrcPort" dataDxfId="15" totalsRowDxfId="3"/>
     <tableColumn id="4" xr3:uid="{AC3F24B7-C4B3-CC4C-A7E3-6BB3319549AD}" name="DstTag" dataDxfId="14" totalsRowDxfId="2"/>
     <tableColumn id="5" xr3:uid="{723F3509-3335-1241-A5F2-61206DF5595A}" name="DstPort" dataDxfId="13"/>
     <tableColumn id="6" xr3:uid="{7D4B1BBD-F461-7E4D-A272-8B68F8EE10FB}" name="Type" dataDxfId="12"/>
@@ -46215,7 +46214,7 @@
         <v>1151</v>
       </c>
       <c r="C894" s="83" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D894" s="83" t="s">
         <v>1151</v>
@@ -48008,7 +48007,7 @@
       </c>
       <c r="J949" s="29"/>
       <c r="K949" s="29"/>
-      <c r="L949" s="120"/>
+      <c r="L949" s="31"/>
       <c r="M949" s="29"/>
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.2">

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C533099-6638-234B-8899-0C0135B5933B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16C4A81-4394-4A45-99B7-356591C72AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5780" yWindow="1640" windowWidth="24460" windowHeight="16580" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="9" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7722" uniqueCount="2589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7722" uniqueCount="2590">
   <si>
     <t>Tag</t>
   </si>
@@ -7808,6 +7808,9 @@
   </si>
   <si>
     <t>ZAIU-B002</t>
+  </si>
+  <si>
+    <t>PP SW hdmi</t>
   </si>
 </sst>
 </file>
@@ -17328,7 +17331,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17585,7 +17588,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17649,7 +17652,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M950" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M949" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
+  <autoFilter ref="A1:M949" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="out_04"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
@@ -18024,7 +18033,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>25</v>
       </c>
@@ -18059,7 +18068,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
@@ -18094,7 +18103,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
@@ -18129,7 +18138,7 @@
       <c r="L4" s="19"/>
       <c r="M4" s="20"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>6</v>
       </c>
@@ -18164,7 +18173,7 @@
       <c r="L5" s="23"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>7</v>
       </c>
@@ -18199,7 +18208,7 @@
       <c r="L6" s="19"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
@@ -18234,7 +18243,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
@@ -18263,7 +18272,7 @@
       </c>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>10</v>
       </c>
@@ -18298,7 +18307,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="24"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>11</v>
       </c>
@@ -18323,7 +18332,7 @@
       <c r="L10" s="19"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
@@ -18358,7 +18367,7 @@
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
@@ -18391,7 +18400,7 @@
       <c r="L12" s="19"/>
       <c r="M12" s="20"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
@@ -18424,7 +18433,7 @@
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>15</v>
       </c>
@@ -18455,7 +18464,7 @@
       <c r="L14" s="19"/>
       <c r="M14" s="20"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
         <v>16</v>
       </c>
@@ -18480,7 +18489,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -18505,7 +18514,7 @@
       <c r="L16" s="19"/>
       <c r="M16" s="20"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
         <v>18</v>
       </c>
@@ -18536,7 +18545,7 @@
       <c r="L17" s="23"/>
       <c r="M17" s="24"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>19</v>
       </c>
@@ -18555,7 +18564,7 @@
       <c r="L18" s="19"/>
       <c r="M18" s="20"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>20</v>
       </c>
@@ -18574,7 +18583,7 @@
       <c r="L19" s="23"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>21</v>
       </c>
@@ -18593,7 +18602,7 @@
       <c r="L20" s="19"/>
       <c r="M20" s="20"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
@@ -18620,7 +18629,7 @@
       <c r="L21" s="19"/>
       <c r="M21" s="20"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
         <v>24</v>
       </c>
@@ -18647,7 +18656,7 @@
       <c r="L22" s="23"/>
       <c r="M22" s="24"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
         <v>30</v>
       </c>
@@ -18676,7 +18685,7 @@
       <c r="L23" s="19"/>
       <c r="M23" s="20"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="21" t="s">
         <v>48</v>
       </c>
@@ -18703,7 +18712,7 @@
       <c r="L24" s="23"/>
       <c r="M24" s="24"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>43</v>
       </c>
@@ -18734,7 +18743,7 @@
       <c r="L25" s="19"/>
       <c r="M25" s="20"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="28" t="s">
         <v>45</v>
       </c>
@@ -18761,7 +18770,7 @@
       <c r="L26" s="27"/>
       <c r="M26" s="24"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>46</v>
       </c>
@@ -18788,7 +18797,7 @@
       <c r="L27" s="19"/>
       <c r="M27" s="20"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>57</v>
       </c>
@@ -18819,7 +18828,7 @@
       <c r="L28" s="23"/>
       <c r="M28" s="24"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>58</v>
       </c>
@@ -18852,7 +18861,7 @@
       <c r="L29" s="19"/>
       <c r="M29" s="20"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21" t="s">
         <v>59</v>
       </c>
@@ -18887,7 +18896,7 @@
       <c r="L30" s="23"/>
       <c r="M30" s="24"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>60</v>
       </c>
@@ -18922,7 +18931,7 @@
       <c r="L31" s="19"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21" t="s">
         <v>61</v>
       </c>
@@ -18957,7 +18966,7 @@
       <c r="L32" s="23"/>
       <c r="M32" s="24"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>69</v>
       </c>
@@ -18984,7 +18993,7 @@
       <c r="L33" s="23"/>
       <c r="M33" s="24"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="17" t="s">
         <v>73</v>
       </c>
@@ -19013,7 +19022,7 @@
       <c r="L34" s="19"/>
       <c r="M34" s="20"/>
     </row>
-    <row r="35" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21" t="s">
         <v>76</v>
       </c>
@@ -19048,7 +19057,7 @@
       <c r="L35" s="23"/>
       <c r="M35" s="24"/>
     </row>
-    <row r="36" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21" t="s">
         <v>75</v>
       </c>
@@ -19075,7 +19084,7 @@
       <c r="L36" s="19"/>
       <c r="M36" s="20"/>
     </row>
-    <row r="37" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>74</v>
       </c>
@@ -19110,7 +19119,7 @@
       <c r="L37" s="23"/>
       <c r="M37" s="24"/>
     </row>
-    <row r="38" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>80</v>
       </c>
@@ -19147,7 +19156,7 @@
       <c r="L38" s="19"/>
       <c r="M38" s="20"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="21" t="s">
         <v>81</v>
       </c>
@@ -19182,7 +19191,7 @@
       <c r="L39" s="23"/>
       <c r="M39" s="24"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21" t="s">
         <v>82</v>
       </c>
@@ -19209,7 +19218,7 @@
       <c r="L40" s="19"/>
       <c r="M40" s="20"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
         <v>84</v>
       </c>
@@ -19244,7 +19253,7 @@
       <c r="L41" s="23"/>
       <c r="M41" s="24"/>
     </row>
-    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
         <v>85</v>
       </c>
@@ -19279,7 +19288,7 @@
       <c r="L42" s="19"/>
       <c r="M42" s="30"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="21" t="s">
         <v>86</v>
       </c>
@@ -19314,7 +19323,7 @@
       <c r="L43" s="23"/>
       <c r="M43" s="24"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
         <v>89</v>
       </c>
@@ -19331,7 +19340,7 @@
       <c r="L44" s="19"/>
       <c r="M44" s="20"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21" t="s">
         <v>92</v>
       </c>
@@ -19348,7 +19357,7 @@
       <c r="L45" s="23"/>
       <c r="M45" s="24"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
         <v>93</v>
       </c>
@@ -19365,7 +19374,7 @@
       <c r="L46" s="19"/>
       <c r="M46" s="20"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="21" t="s">
         <v>94</v>
       </c>
@@ -19400,7 +19409,7 @@
       <c r="L47" s="23"/>
       <c r="M47" s="24"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="17" t="s">
         <v>103</v>
       </c>
@@ -19435,7 +19444,7 @@
       <c r="L48" s="19"/>
       <c r="M48" s="20"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="21" t="s">
         <v>104</v>
       </c>
@@ -19470,7 +19479,7 @@
       <c r="L49" s="23"/>
       <c r="M49" s="24"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>105</v>
       </c>
@@ -19497,7 +19506,7 @@
       <c r="L50" s="19"/>
       <c r="M50" s="20"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="21" t="s">
         <v>109</v>
       </c>
@@ -19532,7 +19541,7 @@
       <c r="L51" s="23"/>
       <c r="M51" s="24"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="17" t="s">
         <v>358</v>
       </c>
@@ -19563,7 +19572,7 @@
       <c r="L52" s="19"/>
       <c r="M52" s="20"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="21" t="s">
         <v>111</v>
       </c>
@@ -19590,7 +19599,7 @@
       <c r="L53" s="23"/>
       <c r="M53" s="24"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
         <v>116</v>
       </c>
@@ -19621,7 +19630,7 @@
       <c r="L54" s="19"/>
       <c r="M54" s="20"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
         <v>118</v>
       </c>
@@ -19654,7 +19663,7 @@
       <c r="L55" s="23"/>
       <c r="M55" s="24"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="21" t="s">
         <v>120</v>
       </c>
@@ -19683,7 +19692,7 @@
       <c r="L56" s="19"/>
       <c r="M56" s="20"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="21" t="s">
         <v>122</v>
       </c>
@@ -19710,7 +19719,7 @@
       <c r="L57" s="23"/>
       <c r="M57" s="24"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
         <v>123</v>
       </c>
@@ -19727,7 +19736,7 @@
       <c r="L58" s="19"/>
       <c r="M58" s="20"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="21" t="s">
         <v>124</v>
       </c>
@@ -19756,7 +19765,7 @@
       <c r="L59" s="23"/>
       <c r="M59" s="24"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="21" t="s">
         <v>125</v>
       </c>
@@ -19785,7 +19794,7 @@
       <c r="L60" s="19"/>
       <c r="M60" s="20"/>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="21" t="s">
         <v>128</v>
       </c>
@@ -19818,7 +19827,7 @@
       <c r="L61" s="23"/>
       <c r="M61" s="24"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="17" t="s">
         <v>138</v>
       </c>
@@ -19845,7 +19854,7 @@
       <c r="L62" s="19"/>
       <c r="M62" s="20"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="21" t="s">
         <v>176</v>
       </c>
@@ -19878,7 +19887,7 @@
       </c>
       <c r="M63" s="24"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>177</v>
       </c>
@@ -19911,7 +19920,7 @@
       <c r="L64" s="19"/>
       <c r="M64" s="20"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="21" t="s">
         <v>178</v>
       </c>
@@ -19946,7 +19955,7 @@
       <c r="L65" s="23"/>
       <c r="M65" s="24"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="17" t="s">
         <v>179</v>
       </c>
@@ -19979,7 +19988,7 @@
       <c r="L66" s="19"/>
       <c r="M66" s="20"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="21" t="s">
         <v>180</v>
       </c>
@@ -20012,7 +20021,7 @@
       <c r="L67" s="23"/>
       <c r="M67" s="24"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="21" t="s">
         <v>181</v>
       </c>
@@ -20043,7 +20052,7 @@
       <c r="L68" s="19"/>
       <c r="M68" s="20"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="21" t="s">
         <v>158</v>
       </c>
@@ -20076,7 +20085,7 @@
       <c r="L69" s="19"/>
       <c r="M69" s="20"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="21" t="s">
         <v>159</v>
       </c>
@@ -20109,7 +20118,7 @@
       <c r="L70" s="23"/>
       <c r="M70" s="24"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="21" t="s">
         <v>160</v>
       </c>
@@ -20142,7 +20151,7 @@
       <c r="L71" s="19"/>
       <c r="M71" s="20"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="21" t="s">
         <v>161</v>
       </c>
@@ -20179,7 +20188,7 @@
       <c r="L72" s="23"/>
       <c r="M72" s="24"/>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="21" t="s">
         <v>167</v>
       </c>
@@ -20212,7 +20221,7 @@
       <c r="L73" s="19"/>
       <c r="M73" s="20"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="21" t="s">
         <v>168</v>
       </c>
@@ -20245,7 +20254,7 @@
       <c r="L74" s="23"/>
       <c r="M74" s="24"/>
     </row>
-    <row r="75" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="21" t="s">
         <v>169</v>
       </c>
@@ -20278,7 +20287,7 @@
       <c r="L75" s="19"/>
       <c r="M75" s="20"/>
     </row>
-    <row r="76" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A76" s="21" t="s">
         <v>2446</v>
       </c>
@@ -20313,7 +20322,7 @@
       <c r="L76" s="22"/>
       <c r="M76" s="20"/>
     </row>
-    <row r="77" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A77" s="21" t="s">
         <v>2447</v>
       </c>
@@ -20348,7 +20357,7 @@
       <c r="L77" s="22"/>
       <c r="M77" s="20"/>
     </row>
-    <row r="78" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
         <v>2448</v>
       </c>
@@ -20383,7 +20392,7 @@
       <c r="L78" s="22"/>
       <c r="M78" s="20"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
         <v>167</v>
       </c>
@@ -20416,7 +20425,7 @@
       <c r="L79" s="22"/>
       <c r="M79" s="20"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>168</v>
       </c>
@@ -20449,7 +20458,7 @@
       <c r="L80" s="22"/>
       <c r="M80" s="20"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>169</v>
       </c>
@@ -20482,7 +20491,7 @@
       <c r="L81" s="22"/>
       <c r="M81" s="20"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
         <v>174</v>
       </c>
@@ -20509,7 +20518,7 @@
       <c r="L82" s="23"/>
       <c r="M82" s="24"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>187</v>
       </c>
@@ -20540,7 +20549,7 @@
       <c r="L83" s="19"/>
       <c r="M83" s="20"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
         <v>202</v>
       </c>
@@ -20571,7 +20580,7 @@
       <c r="L84" s="23"/>
       <c r="M84" s="24"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="21" t="s">
         <v>203</v>
       </c>
@@ -20602,7 +20611,7 @@
       <c r="L85" s="19"/>
       <c r="M85" s="20"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="21" t="s">
         <v>204</v>
       </c>
@@ -20637,7 +20646,7 @@
       <c r="L86" s="23"/>
       <c r="M86" s="24"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>205</v>
       </c>
@@ -20672,7 +20681,7 @@
       <c r="L87" s="19"/>
       <c r="M87" s="20"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="21" t="s">
         <v>206</v>
       </c>
@@ -20703,7 +20712,7 @@
       <c r="L88" s="23"/>
       <c r="M88" s="24"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="21" t="s">
         <v>207</v>
       </c>
@@ -20736,7 +20745,7 @@
       <c r="L89" s="19"/>
       <c r="M89" s="20"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="21" t="s">
         <v>208</v>
       </c>
@@ -20769,7 +20778,7 @@
       <c r="L90" s="23"/>
       <c r="M90" s="24"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
         <v>209</v>
       </c>
@@ -20802,7 +20811,7 @@
       <c r="L91" s="19"/>
       <c r="M91" s="20"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
         <v>210</v>
       </c>
@@ -20837,7 +20846,7 @@
       <c r="L92" s="23"/>
       <c r="M92" s="24"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
         <v>211</v>
       </c>
@@ -20868,7 +20877,7 @@
       <c r="L93" s="19"/>
       <c r="M93" s="20"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
         <v>212</v>
       </c>
@@ -20903,7 +20912,7 @@
       <c r="L94" s="23"/>
       <c r="M94" s="24"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
         <v>216</v>
       </c>
@@ -20934,7 +20943,7 @@
       <c r="L95" s="19"/>
       <c r="M95" s="20"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
         <v>220</v>
       </c>
@@ -20965,7 +20974,7 @@
       <c r="L96" s="23"/>
       <c r="M96" s="24"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
         <v>539</v>
       </c>
@@ -20982,7 +20991,7 @@
       <c r="L97" s="19"/>
       <c r="M97" s="20"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
         <v>540</v>
       </c>
@@ -20999,7 +21008,7 @@
       <c r="L98" s="23"/>
       <c r="M98" s="24"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>518</v>
       </c>
@@ -21022,7 +21031,7 @@
       <c r="L99" s="19"/>
       <c r="M99" s="20"/>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="21"/>
       <c r="B100" s="22" t="s">
         <v>64</v>
@@ -21053,7 +21062,7 @@
       <c r="L100" s="19"/>
       <c r="M100" s="20"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
         <v>1912</v>
       </c>
@@ -21086,7 +21095,7 @@
       <c r="L101" s="23"/>
       <c r="M101" s="24"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
         <v>231</v>
       </c>
@@ -21119,7 +21128,7 @@
       <c r="L102" s="19"/>
       <c r="M102" s="20"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>230</v>
       </c>
@@ -21152,7 +21161,7 @@
       <c r="L103" s="23"/>
       <c r="M103" s="24"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
         <v>293</v>
       </c>
@@ -21187,7 +21196,7 @@
       <c r="L104" s="19"/>
       <c r="M104" s="20"/>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
         <v>294</v>
       </c>
@@ -21222,7 +21231,7 @@
       <c r="L105" s="23"/>
       <c r="M105" s="24"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
         <v>47</v>
       </c>
@@ -21249,7 +21258,7 @@
       <c r="L106" s="19"/>
       <c r="M106" s="20"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="21"/>
       <c r="B107" s="22" t="s">
         <v>244</v>
@@ -21280,7 +21289,7 @@
       <c r="L107" s="23"/>
       <c r="M107" s="24"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
         <v>246</v>
       </c>
@@ -21307,7 +21316,7 @@
       <c r="L108" s="19"/>
       <c r="M108" s="20"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
         <v>256</v>
       </c>
@@ -21338,7 +21347,7 @@
       <c r="L109" s="23"/>
       <c r="M109" s="24"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
         <v>852</v>
       </c>
@@ -21369,7 +21378,7 @@
       <c r="L110" s="19"/>
       <c r="M110" s="20"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
         <v>849</v>
       </c>
@@ -21402,7 +21411,7 @@
       <c r="L111" s="23"/>
       <c r="M111" s="24"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
         <v>850</v>
       </c>
@@ -21435,7 +21444,7 @@
       <c r="L112" s="19"/>
       <c r="M112" s="20"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
         <v>851</v>
       </c>
@@ -21468,7 +21477,7 @@
       <c r="L113" s="23"/>
       <c r="M113" s="24"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
         <v>845</v>
       </c>
@@ -21497,7 +21506,7 @@
       <c r="L114" s="19"/>
       <c r="M114" s="20"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
         <v>846</v>
       </c>
@@ -21526,7 +21535,7 @@
       <c r="L115" s="23"/>
       <c r="M115" s="24"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
         <v>847</v>
       </c>
@@ -21553,7 +21562,7 @@
       <c r="L116" s="19"/>
       <c r="M116" s="20"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
         <v>848</v>
       </c>
@@ -21584,7 +21593,7 @@
       <c r="L117" s="23"/>
       <c r="M117" s="24"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="21"/>
       <c r="B118" s="22"/>
       <c r="C118" s="23"/>
@@ -21599,7 +21608,7 @@
       <c r="L118" s="19"/>
       <c r="M118" s="20"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
         <v>322</v>
       </c>
@@ -21630,7 +21639,7 @@
       <c r="L119" s="23"/>
       <c r="M119" s="24"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="21" t="s">
         <v>325</v>
       </c>
@@ -21655,7 +21664,7 @@
       <c r="L120" s="23"/>
       <c r="M120" s="24"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="21" t="s">
         <v>328</v>
       </c>
@@ -21682,7 +21691,7 @@
       <c r="L121" s="23"/>
       <c r="M121" s="24"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="21" t="s">
         <v>331</v>
       </c>
@@ -21709,7 +21718,7 @@
       <c r="L122" s="19"/>
       <c r="M122" s="20"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>338</v>
       </c>
@@ -21734,7 +21743,7 @@
       <c r="L123" s="23"/>
       <c r="M123" s="24"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>339</v>
       </c>
@@ -21769,7 +21778,7 @@
       <c r="L124" s="19"/>
       <c r="M124" s="20"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="21" t="s">
         <v>340</v>
       </c>
@@ -21792,7 +21801,7 @@
       <c r="L125" s="23"/>
       <c r="M125" s="24"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
         <v>341</v>
       </c>
@@ -21815,7 +21824,7 @@
       <c r="L126" s="19"/>
       <c r="M126" s="20"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="21" t="s">
         <v>342</v>
       </c>
@@ -21838,7 +21847,7 @@
       <c r="L127" s="23"/>
       <c r="M127" s="24"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="21" t="s">
         <v>349</v>
       </c>
@@ -21867,7 +21876,7 @@
       <c r="L128" s="19"/>
       <c r="M128" s="20"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="21" t="s">
         <v>22</v>
       </c>
@@ -21892,7 +21901,7 @@
       <c r="L129" s="23"/>
       <c r="M129" s="24"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="21" t="s">
         <v>357</v>
       </c>
@@ -21925,7 +21934,7 @@
       <c r="L130" s="19"/>
       <c r="M130" s="20"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="21" t="s">
         <v>2377</v>
       </c>
@@ -21960,7 +21969,7 @@
       <c r="L131" s="23"/>
       <c r="M131" s="24"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="21"/>
       <c r="B132" s="22"/>
       <c r="C132" s="23"/>
@@ -21977,7 +21986,7 @@
       <c r="L132" s="19"/>
       <c r="M132" s="20"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="21" t="s">
         <v>361</v>
       </c>
@@ -22012,7 +22021,7 @@
       <c r="L133" s="23"/>
       <c r="M133" s="24"/>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="21" t="s">
         <v>408</v>
       </c>
@@ -22047,7 +22056,7 @@
       <c r="L134" s="19"/>
       <c r="M134" s="20"/>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="21" t="s">
         <v>409</v>
       </c>
@@ -22082,7 +22091,7 @@
       <c r="L135" s="23"/>
       <c r="M135" s="24"/>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="21" t="s">
         <v>410</v>
       </c>
@@ -22117,7 +22126,7 @@
       <c r="L136" s="19"/>
       <c r="M136" s="20"/>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="21" t="s">
         <v>411</v>
       </c>
@@ -22152,7 +22161,7 @@
       <c r="L137" s="23"/>
       <c r="M137" s="24"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="21" t="s">
         <v>412</v>
       </c>
@@ -22187,7 +22196,7 @@
       <c r="L138" s="19"/>
       <c r="M138" s="20"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="21" t="s">
         <v>413</v>
       </c>
@@ -22222,7 +22231,7 @@
       <c r="L139" s="23"/>
       <c r="M139" s="24"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="21" t="s">
         <v>414</v>
       </c>
@@ -22257,7 +22266,7 @@
       <c r="L140" s="19"/>
       <c r="M140" s="20"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="21" t="s">
         <v>415</v>
       </c>
@@ -22292,7 +22301,7 @@
       <c r="L141" s="23"/>
       <c r="M141" s="24"/>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="21" t="s">
         <v>416</v>
       </c>
@@ -22327,7 +22336,7 @@
       <c r="L142" s="19"/>
       <c r="M142" s="20"/>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="21" t="s">
         <v>417</v>
       </c>
@@ -22362,7 +22371,7 @@
       <c r="L143" s="23"/>
       <c r="M143" s="24"/>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="21" t="s">
         <v>418</v>
       </c>
@@ -22397,7 +22406,7 @@
       <c r="L144" s="19"/>
       <c r="M144" s="20"/>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="21" t="s">
         <v>419</v>
       </c>
@@ -22432,7 +22441,7 @@
       <c r="L145" s="23"/>
       <c r="M145" s="24"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="21" t="s">
         <v>420</v>
       </c>
@@ -22467,7 +22476,7 @@
       <c r="L146" s="19"/>
       <c r="M146" s="20"/>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="75" t="s">
         <v>421</v>
       </c>
@@ -22502,7 +22511,7 @@
       <c r="L147" s="33"/>
       <c r="M147" s="34"/>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="29" t="s">
         <v>422</v>
       </c>
@@ -22537,7 +22546,7 @@
       <c r="L148" s="29"/>
       <c r="M148" s="29"/>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="76" t="s">
         <v>423</v>
       </c>
@@ -22570,7 +22579,7 @@
       <c r="L149" s="29"/>
       <c r="M149" s="29"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="29" t="s">
         <v>424</v>
       </c>
@@ -22603,7 +22612,7 @@
       <c r="L150" s="29"/>
       <c r="M150" s="29"/>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="29" t="s">
         <v>425</v>
       </c>
@@ -22636,7 +22645,7 @@
       <c r="L151" s="29"/>
       <c r="M151" s="29"/>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="29" t="s">
         <v>426</v>
       </c>
@@ -22669,7 +22678,7 @@
       <c r="L152" s="29"/>
       <c r="M152" s="29"/>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="29" t="s">
         <v>427</v>
       </c>
@@ -22704,7 +22713,7 @@
       <c r="L153" s="29"/>
       <c r="M153" s="29"/>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="29" t="s">
         <v>428</v>
       </c>
@@ -22739,7 +22748,7 @@
       <c r="L154" s="29"/>
       <c r="M154" s="29"/>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="29" t="s">
         <v>429</v>
       </c>
@@ -22774,7 +22783,7 @@
       <c r="L155" s="29"/>
       <c r="M155" s="29"/>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="29" t="s">
         <v>430</v>
       </c>
@@ -22809,7 +22818,7 @@
       <c r="L156" s="29"/>
       <c r="M156" s="29"/>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="29" t="s">
         <v>431</v>
       </c>
@@ -22844,7 +22853,7 @@
       <c r="L157" s="29"/>
       <c r="M157" s="29"/>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="29" t="s">
         <v>432</v>
       </c>
@@ -22879,7 +22888,7 @@
       <c r="L158" s="29"/>
       <c r="M158" s="29"/>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="29" t="s">
         <v>433</v>
       </c>
@@ -22914,7 +22923,7 @@
       <c r="L159" s="29"/>
       <c r="M159" s="29"/>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="29" t="s">
         <v>434</v>
       </c>
@@ -22949,7 +22958,7 @@
       <c r="L160" s="29"/>
       <c r="M160" s="29"/>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="29" t="s">
         <v>435</v>
       </c>
@@ -22984,7 +22993,7 @@
       <c r="L161" s="29"/>
       <c r="M161" s="29"/>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="29" t="s">
         <v>436</v>
       </c>
@@ -23019,7 +23028,7 @@
       <c r="L162" s="29"/>
       <c r="M162" s="29"/>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="29" t="s">
         <v>437</v>
       </c>
@@ -23054,7 +23063,7 @@
       <c r="L163" s="29"/>
       <c r="M163" s="29"/>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="29" t="s">
         <v>438</v>
       </c>
@@ -23089,7 +23098,7 @@
       <c r="L164" s="29"/>
       <c r="M164" s="29"/>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="29" t="s">
         <v>439</v>
       </c>
@@ -23124,7 +23133,7 @@
       <c r="L165" s="29"/>
       <c r="M165" s="29"/>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="29" t="s">
         <v>440</v>
       </c>
@@ -23159,7 +23168,7 @@
       <c r="L166" s="29"/>
       <c r="M166" s="29"/>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="29" t="s">
         <v>441</v>
       </c>
@@ -23194,7 +23203,7 @@
       <c r="L167" s="29"/>
       <c r="M167" s="29"/>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="29" t="s">
         <v>442</v>
       </c>
@@ -23229,7 +23238,7 @@
       <c r="L168" s="29"/>
       <c r="M168" s="29"/>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="29" t="s">
         <v>443</v>
       </c>
@@ -23264,7 +23273,7 @@
       <c r="L169" s="29"/>
       <c r="M169" s="29"/>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="29" t="s">
         <v>444</v>
       </c>
@@ -23299,7 +23308,7 @@
       <c r="L170" s="29"/>
       <c r="M170" s="29"/>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="29" t="s">
         <v>445</v>
       </c>
@@ -23334,7 +23343,7 @@
       <c r="L171" s="29"/>
       <c r="M171" s="29"/>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="29" t="s">
         <v>446</v>
       </c>
@@ -23369,7 +23378,7 @@
       <c r="L172" s="29"/>
       <c r="M172" s="29"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="29" t="s">
         <v>447</v>
       </c>
@@ -23404,7 +23413,7 @@
       <c r="L173" s="29"/>
       <c r="M173" s="29"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="29" t="s">
         <v>448</v>
       </c>
@@ -23439,7 +23448,7 @@
       <c r="L174" s="29"/>
       <c r="M174" s="29"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="29" t="s">
         <v>449</v>
       </c>
@@ -23474,7 +23483,7 @@
       <c r="L175" s="29"/>
       <c r="M175" s="29"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="29" t="s">
         <v>450</v>
       </c>
@@ -23509,7 +23518,7 @@
       <c r="L176" s="29"/>
       <c r="M176" s="29"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="29" t="s">
         <v>451</v>
       </c>
@@ -23544,7 +23553,7 @@
       <c r="L177" s="29"/>
       <c r="M177" s="29"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="29" t="s">
         <v>452</v>
       </c>
@@ -23579,7 +23588,7 @@
       <c r="L178" s="29"/>
       <c r="M178" s="29"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="29" t="s">
         <v>453</v>
       </c>
@@ -23614,7 +23623,7 @@
       <c r="L179" s="29"/>
       <c r="M179" s="29"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="29" t="s">
         <v>454</v>
       </c>
@@ -23649,7 +23658,7 @@
       <c r="L180" s="29"/>
       <c r="M180" s="29"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="29" t="s">
         <v>455</v>
       </c>
@@ -23684,7 +23693,7 @@
       <c r="L181" s="29"/>
       <c r="M181" s="29"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="29" t="s">
         <v>456</v>
       </c>
@@ -23719,7 +23728,7 @@
       <c r="L182" s="29"/>
       <c r="M182" s="29"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="29" t="s">
         <v>457</v>
       </c>
@@ -23754,7 +23763,7 @@
       <c r="L183" s="29"/>
       <c r="M183" s="29"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="29" t="s">
         <v>458</v>
       </c>
@@ -23789,7 +23798,7 @@
       <c r="L184" s="29"/>
       <c r="M184" s="29"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="29" t="s">
         <v>459</v>
       </c>
@@ -23824,7 +23833,7 @@
       <c r="L185" s="29"/>
       <c r="M185" s="29"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="29" t="s">
         <v>460</v>
       </c>
@@ -23859,7 +23868,7 @@
       <c r="L186" s="29"/>
       <c r="M186" s="29"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="29" t="s">
         <v>461</v>
       </c>
@@ -23894,7 +23903,7 @@
       <c r="L187" s="29"/>
       <c r="M187" s="29"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="29" t="s">
         <v>462</v>
       </c>
@@ -23929,7 +23938,7 @@
       <c r="L188" s="29"/>
       <c r="M188" s="29"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="29" t="s">
         <v>463</v>
       </c>
@@ -23964,7 +23973,7 @@
       <c r="L189" s="29"/>
       <c r="M189" s="29"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="29" t="s">
         <v>464</v>
       </c>
@@ -23999,7 +24008,7 @@
       <c r="L190" s="29"/>
       <c r="M190" s="29"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="29" t="s">
         <v>465</v>
       </c>
@@ -24034,7 +24043,7 @@
       <c r="L191" s="29"/>
       <c r="M191" s="29"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="29" t="s">
         <v>466</v>
       </c>
@@ -24067,7 +24076,7 @@
       <c r="L192" s="29"/>
       <c r="M192" s="29"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="29" t="s">
         <v>467</v>
       </c>
@@ -24100,7 +24109,7 @@
       <c r="L193" s="29"/>
       <c r="M193" s="29"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="29" t="s">
         <v>468</v>
       </c>
@@ -24133,7 +24142,7 @@
       <c r="L194" s="29"/>
       <c r="M194" s="29"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="29" t="s">
         <v>469</v>
       </c>
@@ -24166,7 +24175,7 @@
       <c r="L195" s="29"/>
       <c r="M195" s="29"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="29" t="s">
         <v>470</v>
       </c>
@@ -24201,7 +24210,7 @@
       <c r="L196" s="29"/>
       <c r="M196" s="29"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="29" t="s">
         <v>471</v>
       </c>
@@ -24236,7 +24245,7 @@
       <c r="L197" s="29"/>
       <c r="M197" s="29"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="29" t="s">
         <v>472</v>
       </c>
@@ -24269,7 +24278,7 @@
       <c r="L198" s="29"/>
       <c r="M198" s="29"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="29" t="s">
         <v>473</v>
       </c>
@@ -24302,7 +24311,7 @@
       <c r="L199" s="29"/>
       <c r="M199" s="29"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="29" t="s">
         <v>474</v>
       </c>
@@ -24335,7 +24344,7 @@
       <c r="L200" s="29"/>
       <c r="M200" s="29"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="29" t="s">
         <v>1708</v>
       </c>
@@ -24368,7 +24377,7 @@
       <c r="L201" s="31"/>
       <c r="M201" s="29"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
         <v>1709</v>
       </c>
@@ -24403,7 +24412,7 @@
       <c r="L202" s="31"/>
       <c r="M202" s="29"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
         <v>1710</v>
       </c>
@@ -24438,7 +24447,7 @@
       <c r="L203" s="31"/>
       <c r="M203" s="29"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
         <v>1711</v>
       </c>
@@ -24473,7 +24482,7 @@
       <c r="L204" s="31"/>
       <c r="M204" s="29"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
         <v>1712</v>
       </c>
@@ -24506,7 +24515,7 @@
       <c r="L205" s="31"/>
       <c r="M205" s="29"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
         <v>1713</v>
       </c>
@@ -24539,7 +24548,7 @@
       <c r="L206" s="31"/>
       <c r="M206" s="29"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
         <v>1714</v>
       </c>
@@ -24572,7 +24581,7 @@
       <c r="L207" s="31"/>
       <c r="M207" s="29"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
         <v>1715</v>
       </c>
@@ -24605,7 +24614,7 @@
       <c r="L208" s="31"/>
       <c r="M208" s="29"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
         <v>1716</v>
       </c>
@@ -24638,7 +24647,7 @@
       <c r="L209" s="31"/>
       <c r="M209" s="29"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="29" t="s">
         <v>1717</v>
       </c>
@@ -24671,7 +24680,7 @@
       <c r="L210" s="31"/>
       <c r="M210" s="29"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="29" t="s">
         <v>1718</v>
       </c>
@@ -24704,7 +24713,7 @@
       <c r="L211" s="31"/>
       <c r="M211" s="29"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="29" t="s">
         <v>1719</v>
       </c>
@@ -24737,7 +24746,7 @@
       <c r="L212" s="31"/>
       <c r="M212" s="29"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="29" t="s">
         <v>1720</v>
       </c>
@@ -24770,7 +24779,7 @@
       <c r="L213" s="31"/>
       <c r="M213" s="29"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="29" t="s">
         <v>1721</v>
       </c>
@@ -24803,7 +24812,7 @@
       <c r="L214" s="31"/>
       <c r="M214" s="29"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="29" t="s">
         <v>1722</v>
       </c>
@@ -24836,7 +24845,7 @@
       <c r="L215" s="31"/>
       <c r="M215" s="29"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="29" t="s">
         <v>1723</v>
       </c>
@@ -24869,7 +24878,7 @@
       <c r="L216" s="31"/>
       <c r="M216" s="29"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="29" t="s">
         <v>475</v>
       </c>
@@ -24904,7 +24913,7 @@
       <c r="L217" s="29"/>
       <c r="M217" s="29"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="29" t="s">
         <v>476</v>
       </c>
@@ -24939,7 +24948,7 @@
       <c r="L218" s="29"/>
       <c r="M218" s="29"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="29"/>
       <c r="B219" s="31"/>
       <c r="C219" s="29"/>
@@ -24954,7 +24963,7 @@
       <c r="L219" s="29"/>
       <c r="M219" s="29"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="29"/>
       <c r="B220" s="31"/>
       <c r="C220" s="29"/>
@@ -24969,7 +24978,7 @@
       <c r="L220" s="29"/>
       <c r="M220" s="29"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="29" t="s">
         <v>482</v>
       </c>
@@ -25006,7 +25015,7 @@
       </c>
       <c r="M221" s="29"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="29" t="s">
         <v>483</v>
       </c>
@@ -25039,7 +25048,7 @@
       <c r="L222" s="31"/>
       <c r="M222" s="29"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
         <v>487</v>
       </c>
@@ -25074,7 +25083,7 @@
       </c>
       <c r="M223" s="29"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
         <v>492</v>
       </c>
@@ -25109,7 +25118,7 @@
       <c r="L224" s="31"/>
       <c r="M224" s="29"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
         <v>493</v>
       </c>
@@ -25144,7 +25153,7 @@
       <c r="L225" s="31"/>
       <c r="M225" s="29"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="29"/>
       <c r="B226" s="31" t="s">
         <v>496</v>
@@ -25179,7 +25188,7 @@
       <c r="L226" s="31"/>
       <c r="M226" s="29"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="29"/>
       <c r="B227" s="38" t="s">
         <v>498</v>
@@ -25212,7 +25221,7 @@
       <c r="L227" s="31"/>
       <c r="M227" s="29"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="29"/>
       <c r="B228" s="31"/>
       <c r="C228" s="29"/>
@@ -25227,7 +25236,7 @@
       <c r="L228" s="31"/>
       <c r="M228" s="29"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="29" t="s">
         <v>2292</v>
       </c>
@@ -25264,7 +25273,7 @@
       </c>
       <c r="M229" s="29"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="29" t="s">
         <v>509</v>
       </c>
@@ -25299,7 +25308,7 @@
       <c r="L230" s="31"/>
       <c r="M230" s="29"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="29" t="s">
         <v>515</v>
       </c>
@@ -25334,7 +25343,7 @@
       <c r="L231" s="31"/>
       <c r="M231" s="29"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="29" t="s">
         <v>520</v>
       </c>
@@ -25359,7 +25368,7 @@
       <c r="L232" s="31"/>
       <c r="M232" s="29"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="29" t="s">
         <v>521</v>
       </c>
@@ -25384,7 +25393,7 @@
       <c r="L233" s="31"/>
       <c r="M233" s="29"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="39" t="s">
         <v>525</v>
       </c>
@@ -25411,7 +25420,7 @@
       <c r="L234" s="31"/>
       <c r="M234" s="29"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="29" t="s">
         <v>526</v>
       </c>
@@ -25438,7 +25447,7 @@
       <c r="L235" s="31"/>
       <c r="M235" s="29"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="29" t="s">
         <v>529</v>
       </c>
@@ -25469,7 +25478,7 @@
       <c r="L236" s="31"/>
       <c r="M236" s="29"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="29" t="s">
         <v>530</v>
       </c>
@@ -25500,7 +25509,7 @@
       <c r="L237" s="31"/>
       <c r="M237" s="29"/>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="29" t="s">
         <v>531</v>
       </c>
@@ -25531,7 +25540,7 @@
       <c r="L238" s="31"/>
       <c r="M238" s="29"/>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="29" t="s">
         <v>728</v>
       </c>
@@ -25556,7 +25565,7 @@
       <c r="L239" s="31"/>
       <c r="M239" s="29"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="29" t="s">
         <v>729</v>
       </c>
@@ -25581,7 +25590,7 @@
       <c r="L240" s="31"/>
       <c r="M240" s="29"/>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="29" t="s">
         <v>543</v>
       </c>
@@ -25608,7 +25617,7 @@
       <c r="L241" s="31"/>
       <c r="M241" s="29"/>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="29" t="s">
         <v>622</v>
       </c>
@@ -25641,7 +25650,7 @@
       <c r="L242" s="31"/>
       <c r="M242" s="29"/>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="29" t="s">
         <v>557</v>
       </c>
@@ -25666,7 +25675,7 @@
       <c r="L243" s="31"/>
       <c r="M243" s="29"/>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="29" t="s">
         <v>558</v>
       </c>
@@ -25695,7 +25704,7 @@
       <c r="L244" s="31"/>
       <c r="M244" s="29"/>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="29" t="s">
         <v>559</v>
       </c>
@@ -25724,7 +25733,7 @@
       <c r="L245" s="31"/>
       <c r="M245" s="29"/>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="29" t="s">
         <v>560</v>
       </c>
@@ -25753,7 +25762,7 @@
       <c r="L246" s="31"/>
       <c r="M246" s="29"/>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="29" t="s">
         <v>623</v>
       </c>
@@ -25784,7 +25793,7 @@
       <c r="L247" s="31"/>
       <c r="M247" s="29"/>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="29" t="s">
         <v>640</v>
       </c>
@@ -25815,7 +25824,7 @@
       <c r="L248" s="31"/>
       <c r="M248" s="29"/>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="31" t="s">
         <v>642</v>
       </c>
@@ -25850,7 +25859,7 @@
       <c r="L249" s="31"/>
       <c r="M249" s="29"/>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="29" t="s">
         <v>637</v>
       </c>
@@ -25883,7 +25892,7 @@
       <c r="L250" s="31"/>
       <c r="M250" s="29"/>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="29" t="s">
         <v>624</v>
       </c>
@@ -25914,7 +25923,7 @@
       <c r="L251" s="31"/>
       <c r="M251" s="29"/>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="29" t="s">
         <v>625</v>
       </c>
@@ -25949,7 +25958,7 @@
       <c r="L252" s="31"/>
       <c r="M252" s="29"/>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="29" t="s">
         <v>627</v>
       </c>
@@ -25982,7 +25991,7 @@
       <c r="L253" s="31"/>
       <c r="M253" s="29"/>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="29" t="s">
         <v>563</v>
       </c>
@@ -26011,7 +26020,7 @@
       <c r="L254" s="31"/>
       <c r="M254" s="29"/>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="29" t="s">
         <v>564</v>
       </c>
@@ -26038,7 +26047,7 @@
       <c r="L255" s="31"/>
       <c r="M255" s="29"/>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="29" t="s">
         <v>565</v>
       </c>
@@ -26065,7 +26074,7 @@
       <c r="L256" s="31"/>
       <c r="M256" s="29"/>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="29" t="s">
         <v>650</v>
       </c>
@@ -26092,7 +26101,7 @@
       <c r="L257" s="31"/>
       <c r="M257" s="29"/>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="29" t="s">
         <v>590</v>
       </c>
@@ -26117,7 +26126,7 @@
       <c r="L258" s="31"/>
       <c r="M258" s="29"/>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="29" t="s">
         <v>596</v>
       </c>
@@ -26150,7 +26159,7 @@
       <c r="L259" s="31"/>
       <c r="M259" s="29"/>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="29" t="s">
         <v>589</v>
       </c>
@@ -26177,7 +26186,7 @@
       <c r="L260" s="31"/>
       <c r="M260" s="29"/>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="29" t="s">
         <v>588</v>
       </c>
@@ -26204,7 +26213,7 @@
       <c r="L261" s="31"/>
       <c r="M261" s="29"/>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="29" t="s">
         <v>587</v>
       </c>
@@ -26231,7 +26240,7 @@
       <c r="L262" s="31"/>
       <c r="M262" s="29"/>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="29" t="s">
         <v>593</v>
       </c>
@@ -26264,7 +26273,7 @@
       <c r="L263" s="31"/>
       <c r="M263" s="29"/>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="29" t="s">
         <v>594</v>
       </c>
@@ -26297,7 +26306,7 @@
       <c r="L264" s="31"/>
       <c r="M264" s="29"/>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="29" t="s">
         <v>595</v>
       </c>
@@ -26330,7 +26339,7 @@
       <c r="L265" s="31"/>
       <c r="M265" s="29"/>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="29" t="s">
         <v>586</v>
       </c>
@@ -26355,7 +26364,7 @@
       <c r="L266" s="31"/>
       <c r="M266" s="29"/>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="29" t="s">
         <v>585</v>
       </c>
@@ -26380,7 +26389,7 @@
       <c r="L267" s="31"/>
       <c r="M267" s="29"/>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="29" t="s">
         <v>598</v>
       </c>
@@ -26415,7 +26424,7 @@
       <c r="L268" s="31"/>
       <c r="M268" s="29"/>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="29" t="s">
         <v>599</v>
       </c>
@@ -26446,7 +26455,7 @@
       <c r="L269" s="31"/>
       <c r="M269" s="29"/>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="29" t="s">
         <v>602</v>
       </c>
@@ -26475,7 +26484,7 @@
       <c r="L270" s="31"/>
       <c r="M270" s="29"/>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="29" t="s">
         <v>616</v>
       </c>
@@ -26504,7 +26513,7 @@
       <c r="L271" s="31"/>
       <c r="M271" s="29"/>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="29" t="s">
         <v>617</v>
       </c>
@@ -26533,7 +26542,7 @@
       <c r="L272" s="31"/>
       <c r="M272" s="29"/>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="29" t="s">
         <v>618</v>
       </c>
@@ -26562,7 +26571,7 @@
       <c r="L273" s="31"/>
       <c r="M273" s="29"/>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="29" t="s">
         <v>619</v>
       </c>
@@ -26591,7 +26600,7 @@
       <c r="L274" s="31"/>
       <c r="M274" s="29"/>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="29" t="s">
         <v>620</v>
       </c>
@@ -26620,7 +26629,7 @@
       <c r="L275" s="31"/>
       <c r="M275" s="29"/>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="29" t="s">
         <v>621</v>
       </c>
@@ -26649,7 +26658,7 @@
       <c r="L276" s="31"/>
       <c r="M276" s="29"/>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="29" t="s">
         <v>632</v>
       </c>
@@ -26680,7 +26689,7 @@
       <c r="L277" s="31"/>
       <c r="M277" s="29"/>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="29" t="s">
         <v>633</v>
       </c>
@@ -26709,7 +26718,7 @@
       <c r="L278" s="31"/>
       <c r="M278" s="29"/>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="29" t="s">
         <v>651</v>
       </c>
@@ -26736,7 +26745,7 @@
       <c r="L279" s="31"/>
       <c r="M279" s="29"/>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="29" t="s">
         <v>653</v>
       </c>
@@ -26761,7 +26770,7 @@
       <c r="L280" s="31"/>
       <c r="M280" s="29"/>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="29" t="s">
         <v>655</v>
       </c>
@@ -26786,7 +26795,7 @@
       <c r="L281" s="31"/>
       <c r="M281" s="29"/>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="29" t="s">
         <v>657</v>
       </c>
@@ -26811,7 +26820,7 @@
       <c r="L282" s="31"/>
       <c r="M282" s="29"/>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="29" t="s">
         <v>658</v>
       </c>
@@ -26838,7 +26847,7 @@
       <c r="L283" s="31"/>
       <c r="M283" s="29"/>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="29" t="s">
         <v>662</v>
       </c>
@@ -26865,7 +26874,7 @@
       <c r="L284" s="31"/>
       <c r="M284" s="29"/>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="29" t="s">
         <v>663</v>
       </c>
@@ -26892,7 +26901,7 @@
       <c r="L285" s="31"/>
       <c r="M285" s="29"/>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="29" t="s">
         <v>677</v>
       </c>
@@ -26925,7 +26934,7 @@
       <c r="L286" s="31"/>
       <c r="M286" s="29"/>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="29" t="s">
         <v>664</v>
       </c>
@@ -26952,7 +26961,7 @@
       <c r="L287" s="31"/>
       <c r="M287" s="29"/>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="29" t="s">
         <v>667</v>
       </c>
@@ -26979,7 +26988,7 @@
       <c r="L288" s="31"/>
       <c r="M288" s="29"/>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="29" t="s">
         <v>670</v>
       </c>
@@ -27004,7 +27013,7 @@
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="29" t="s">
         <v>671</v>
       </c>
@@ -27031,7 +27040,7 @@
       <c r="L290" s="31"/>
       <c r="M290" s="29"/>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="29" t="s">
         <v>673</v>
       </c>
@@ -27058,7 +27067,7 @@
       <c r="L291" s="31"/>
       <c r="M291" s="29"/>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="29" t="s">
         <v>674</v>
       </c>
@@ -27087,7 +27096,7 @@
       <c r="L292" s="31"/>
       <c r="M292" s="29"/>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="29" t="s">
         <v>676</v>
       </c>
@@ -27126,7 +27135,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="29" t="s">
         <v>682</v>
       </c>
@@ -27153,7 +27162,7 @@
       <c r="L294" s="31"/>
       <c r="M294" s="29"/>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="29" t="s">
         <v>684</v>
       </c>
@@ -27186,7 +27195,7 @@
       <c r="L295" s="31"/>
       <c r="M295" s="29"/>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="31" t="s">
         <v>689</v>
       </c>
@@ -27219,7 +27228,7 @@
       <c r="L296" s="31"/>
       <c r="M296" s="29"/>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="29" t="s">
         <v>690</v>
       </c>
@@ -27250,7 +27259,7 @@
       <c r="L297" s="31"/>
       <c r="M297" s="29"/>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="29" t="s">
         <v>697</v>
       </c>
@@ -27275,7 +27284,7 @@
       <c r="L298" s="31"/>
       <c r="M298" s="29"/>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="45" t="s">
         <v>699</v>
       </c>
@@ -27302,7 +27311,7 @@
       <c r="L299" s="31"/>
       <c r="M299" s="29"/>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="46" t="s">
         <v>700</v>
       </c>
@@ -27337,7 +27346,7 @@
       <c r="L300" s="31"/>
       <c r="M300" s="29"/>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="48" t="s">
         <v>701</v>
       </c>
@@ -27372,7 +27381,7 @@
       <c r="L301" s="31"/>
       <c r="M301" s="29"/>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="39" t="s">
         <v>702</v>
       </c>
@@ -27399,7 +27408,7 @@
       <c r="L302" s="31"/>
       <c r="M302" s="29"/>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="29" t="s">
         <v>713</v>
       </c>
@@ -27430,7 +27439,7 @@
       <c r="L303" s="31"/>
       <c r="M303" s="29"/>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="29" t="s">
         <v>714</v>
       </c>
@@ -27463,7 +27472,7 @@
       <c r="L304" s="31"/>
       <c r="M304" s="29"/>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="29" t="s">
         <v>716</v>
       </c>
@@ -27494,7 +27503,7 @@
       <c r="L305" s="31"/>
       <c r="M305" s="29"/>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="39" t="s">
         <v>718</v>
       </c>
@@ -27521,7 +27530,7 @@
       <c r="L306" s="31"/>
       <c r="M306" s="29"/>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="46" t="s">
         <v>756</v>
       </c>
@@ -27546,7 +27555,7 @@
       <c r="L307" s="31"/>
       <c r="M307" s="29"/>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="45" t="s">
         <v>755</v>
       </c>
@@ -27571,7 +27580,7 @@
       <c r="L308" s="31"/>
       <c r="M308" s="29"/>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="48" t="s">
         <v>757</v>
       </c>
@@ -27596,7 +27605,7 @@
       <c r="L309" s="31"/>
       <c r="M309" s="29"/>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="29" t="s">
         <v>721</v>
       </c>
@@ -27623,7 +27632,7 @@
       <c r="L310" s="31"/>
       <c r="M310" s="29"/>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="29" t="s">
         <v>722</v>
       </c>
@@ -27650,7 +27659,7 @@
       <c r="L311" s="31"/>
       <c r="M311" s="29"/>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="29" t="s">
         <v>724</v>
       </c>
@@ -27677,7 +27686,7 @@
       <c r="L312" s="31"/>
       <c r="M312" s="29"/>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="29" t="s">
         <v>733</v>
       </c>
@@ -27716,7 +27725,7 @@
       </c>
       <c r="M313" s="29"/>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="29" t="s">
         <v>736</v>
       </c>
@@ -27755,7 +27764,7 @@
       </c>
       <c r="M314" s="29"/>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="29" t="s">
         <v>741</v>
       </c>
@@ -27790,7 +27799,7 @@
       <c r="L315" s="31"/>
       <c r="M315" s="29"/>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="29" t="s">
         <v>743</v>
       </c>
@@ -27825,7 +27834,7 @@
       <c r="L316" s="31"/>
       <c r="M316" s="29"/>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="29" t="s">
         <v>745</v>
       </c>
@@ -27858,7 +27867,7 @@
       <c r="L317" s="31"/>
       <c r="M317" s="29"/>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="29" t="s">
         <v>747</v>
       </c>
@@ -27885,7 +27894,7 @@
       <c r="L318" s="31"/>
       <c r="M318" s="29"/>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="29" t="s">
         <v>750</v>
       </c>
@@ -27912,7 +27921,7 @@
       <c r="L319" s="31"/>
       <c r="M319" s="29"/>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="29" t="s">
         <v>767</v>
       </c>
@@ -27945,7 +27954,7 @@
       <c r="L320" s="31"/>
       <c r="M320" s="29"/>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="29" t="s">
         <v>773</v>
       </c>
@@ -27970,7 +27979,7 @@
       <c r="L321" s="31"/>
       <c r="M321" s="29"/>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="29" t="s">
         <v>774</v>
       </c>
@@ -28003,7 +28012,7 @@
       <c r="L322" s="31"/>
       <c r="M322" s="29"/>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="29" t="s">
         <v>780</v>
       </c>
@@ -28038,7 +28047,7 @@
       <c r="L323" s="31"/>
       <c r="M323" s="29"/>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="29" t="s">
         <v>782</v>
       </c>
@@ -28065,7 +28074,7 @@
       <c r="L324" s="31"/>
       <c r="M324" s="29"/>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="29" t="s">
         <v>785</v>
       </c>
@@ -28100,7 +28109,7 @@
       </c>
       <c r="M325" s="29"/>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="29" t="s">
         <v>788</v>
       </c>
@@ -28129,7 +28138,7 @@
       </c>
       <c r="M326" s="29"/>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="29" t="s">
         <v>789</v>
       </c>
@@ -28166,7 +28175,7 @@
       </c>
       <c r="M327" s="29"/>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="29" t="s">
         <v>790</v>
       </c>
@@ -28195,7 +28204,7 @@
       <c r="L328" s="31"/>
       <c r="M328" s="29"/>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="29" t="s">
         <v>794</v>
       </c>
@@ -28232,7 +28241,7 @@
       <c r="L329" s="31"/>
       <c r="M329" s="29"/>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="29" t="s">
         <v>799</v>
       </c>
@@ -28261,7 +28270,7 @@
       <c r="L330" s="31"/>
       <c r="M330" s="29"/>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="29" t="s">
         <v>808</v>
       </c>
@@ -28294,7 +28303,7 @@
       <c r="L331" s="31"/>
       <c r="M331" s="29"/>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="29" t="s">
         <v>809</v>
       </c>
@@ -28327,7 +28336,7 @@
       <c r="L332" s="31"/>
       <c r="M332" s="29"/>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="29" t="s">
         <v>823</v>
       </c>
@@ -28362,7 +28371,7 @@
       <c r="L333" s="31"/>
       <c r="M333" s="29"/>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="29" t="s">
         <v>812</v>
       </c>
@@ -28403,7 +28412,7 @@
       <c r="V334" s="4"/>
       <c r="W334" s="5"/>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="29" t="s">
         <v>816</v>
       </c>
@@ -28430,7 +28439,7 @@
       <c r="L335" s="31"/>
       <c r="M335" s="29"/>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="29" t="s">
         <v>817</v>
       </c>
@@ -28453,7 +28462,7 @@
       <c r="L336" s="31"/>
       <c r="M336" s="29"/>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="29" t="s">
         <v>819</v>
       </c>
@@ -28486,7 +28495,7 @@
       <c r="L337" s="31"/>
       <c r="M337" s="29"/>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="29" t="s">
         <v>811</v>
       </c>
@@ -28517,7 +28526,7 @@
       <c r="L338" s="31"/>
       <c r="M338" s="29"/>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="29" t="s">
         <v>826</v>
       </c>
@@ -28544,7 +28553,7 @@
       <c r="L339" s="31"/>
       <c r="M339" s="29"/>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="29" t="s">
         <v>862</v>
       </c>
@@ -28583,7 +28592,7 @@
       </c>
       <c r="M340" s="29"/>
     </row>
-    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="45" t="s">
         <v>842</v>
       </c>
@@ -28614,7 +28623,7 @@
       <c r="L341" s="41"/>
       <c r="M341" s="45"/>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="29" t="s">
         <v>843</v>
       </c>
@@ -28645,7 +28654,7 @@
       <c r="L342" s="31"/>
       <c r="M342" s="29"/>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="29" t="s">
         <v>822</v>
       </c>
@@ -28678,7 +28687,7 @@
       <c r="L343" s="31"/>
       <c r="M343" s="29"/>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="29" t="s">
         <v>841</v>
       </c>
@@ -28711,7 +28720,7 @@
       <c r="L344" s="31"/>
       <c r="M344" s="29"/>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="29" t="s">
         <v>837</v>
       </c>
@@ -28750,7 +28759,7 @@
       </c>
       <c r="M345" s="29"/>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="29" t="s">
         <v>853</v>
       </c>
@@ -28783,7 +28792,7 @@
       <c r="L346" s="31"/>
       <c r="M346" s="29"/>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="29" t="s">
         <v>863</v>
       </c>
@@ -28808,7 +28817,7 @@
       <c r="L347" s="31"/>
       <c r="M347" s="29"/>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="29" t="s">
         <v>864</v>
       </c>
@@ -28833,7 +28842,7 @@
       <c r="L348" s="31"/>
       <c r="M348" s="29"/>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="29" t="s">
         <v>870</v>
       </c>
@@ -28864,7 +28873,7 @@
       <c r="L349" s="31"/>
       <c r="M349" s="29"/>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="29" t="s">
         <v>871</v>
       </c>
@@ -28895,7 +28904,7 @@
       <c r="L350" s="31"/>
       <c r="M350" s="29"/>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="29" t="s">
         <v>872</v>
       </c>
@@ -28926,7 +28935,7 @@
       <c r="L351" s="31"/>
       <c r="M351" s="29"/>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="29" t="s">
         <v>875</v>
       </c>
@@ -28957,7 +28966,7 @@
       <c r="L352" s="31"/>
       <c r="M352" s="29"/>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="29" t="s">
         <v>877</v>
       </c>
@@ -28988,7 +28997,7 @@
       <c r="L353" s="31"/>
       <c r="M353" s="29"/>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="29" t="s">
         <v>879</v>
       </c>
@@ -29019,7 +29028,7 @@
       <c r="L354" s="31"/>
       <c r="M354" s="29"/>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="29"/>
       <c r="B355" s="29" t="s">
         <v>867</v>
@@ -29048,7 +29057,7 @@
       <c r="L355" s="31"/>
       <c r="M355" s="29"/>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="29"/>
       <c r="B356" s="29" t="s">
         <v>867</v>
@@ -29077,7 +29086,7 @@
       <c r="L356" s="31"/>
       <c r="M356" s="29"/>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="29"/>
       <c r="B357" s="29" t="s">
         <v>867</v>
@@ -29106,7 +29115,7 @@
       <c r="L357" s="31"/>
       <c r="M357" s="29"/>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="29"/>
       <c r="B358" s="29" t="s">
         <v>867</v>
@@ -29135,7 +29144,7 @@
       <c r="L358" s="31"/>
       <c r="M358" s="29"/>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="29" t="s">
         <v>1016</v>
       </c>
@@ -29166,7 +29175,7 @@
       <c r="L359" s="31"/>
       <c r="M359" s="29"/>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="29" t="s">
         <v>1017</v>
       </c>
@@ -29197,7 +29206,7 @@
       <c r="L360" s="31"/>
       <c r="M360" s="29"/>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="29" t="s">
         <v>1018</v>
       </c>
@@ -29228,7 +29237,7 @@
       <c r="L361" s="31"/>
       <c r="M361" s="29"/>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="29" t="s">
         <v>1019</v>
       </c>
@@ -29259,7 +29268,7 @@
       <c r="L362" s="31"/>
       <c r="M362" s="29"/>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="29" t="s">
         <v>894</v>
       </c>
@@ -29290,7 +29299,7 @@
       <c r="L363" s="31"/>
       <c r="M363" s="29"/>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="29" t="s">
         <v>895</v>
       </c>
@@ -29321,7 +29330,7 @@
       <c r="L364" s="31"/>
       <c r="M364" s="29"/>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="29" t="s">
         <v>896</v>
       </c>
@@ -29352,7 +29361,7 @@
       <c r="L365" s="31"/>
       <c r="M365" s="29"/>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="29" t="s">
         <v>897</v>
       </c>
@@ -29383,7 +29392,7 @@
       <c r="L366" s="31"/>
       <c r="M366" s="29"/>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="29" t="s">
         <v>911</v>
       </c>
@@ -29408,7 +29417,7 @@
       <c r="L367" s="31"/>
       <c r="M367" s="29"/>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="29" t="s">
         <v>913</v>
       </c>
@@ -29435,7 +29444,7 @@
       <c r="L368" s="31"/>
       <c r="M368" s="29"/>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="29" t="s">
         <v>915</v>
       </c>
@@ -29460,7 +29469,7 @@
       <c r="L369" s="31"/>
       <c r="M369" s="29"/>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="29" t="s">
         <v>916</v>
       </c>
@@ -29487,7 +29496,7 @@
       <c r="L370" s="31"/>
       <c r="M370" s="29"/>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="29" t="s">
         <v>917</v>
       </c>
@@ -29512,7 +29521,7 @@
       <c r="L371" s="31"/>
       <c r="M371" s="29"/>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="29" t="s">
         <v>918</v>
       </c>
@@ -29537,7 +29546,7 @@
       <c r="L372" s="31"/>
       <c r="M372" s="29"/>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="29" t="s">
         <v>919</v>
       </c>
@@ -29572,7 +29581,7 @@
       <c r="L373" s="31"/>
       <c r="M373" s="29"/>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="29" t="s">
         <v>920</v>
       </c>
@@ -29605,7 +29614,7 @@
       <c r="L374" s="31"/>
       <c r="M374" s="29"/>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
         <v>921</v>
       </c>
@@ -29636,7 +29645,7 @@
       <c r="L375" s="31"/>
       <c r="M375" s="29"/>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
         <v>930</v>
       </c>
@@ -29667,7 +29676,7 @@
       <c r="L376" s="31"/>
       <c r="M376" s="29"/>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
         <v>933</v>
       </c>
@@ -29698,7 +29707,7 @@
       <c r="L377" s="31"/>
       <c r="M377" s="29"/>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
         <v>934</v>
       </c>
@@ -29729,7 +29738,7 @@
       <c r="L378" s="31"/>
       <c r="M378" s="29"/>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
         <v>935</v>
       </c>
@@ -29760,7 +29769,7 @@
       <c r="L379" s="31"/>
       <c r="M379" s="29"/>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
         <v>937</v>
       </c>
@@ -29791,7 +29800,7 @@
       <c r="L380" s="31"/>
       <c r="M380" s="29"/>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="29" t="s">
         <v>940</v>
       </c>
@@ -29822,7 +29831,7 @@
       <c r="L381" s="31"/>
       <c r="M381" s="29"/>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="29" t="s">
         <v>948</v>
       </c>
@@ -29853,7 +29862,7 @@
       <c r="L382" s="31"/>
       <c r="M382" s="29"/>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="29" t="s">
         <v>950</v>
       </c>
@@ -29886,7 +29895,7 @@
       <c r="L383" s="31"/>
       <c r="M383" s="29"/>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="29" t="s">
         <v>951</v>
       </c>
@@ -29919,7 +29928,7 @@
       <c r="L384" s="31"/>
       <c r="M384" s="29"/>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="29" t="s">
         <v>952</v>
       </c>
@@ -29952,7 +29961,7 @@
       <c r="L385" s="31"/>
       <c r="M385" s="29"/>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="29" t="s">
         <v>955</v>
       </c>
@@ -29983,7 +29992,7 @@
       <c r="L386" s="31"/>
       <c r="M386" s="29"/>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="29" t="s">
         <v>956</v>
       </c>
@@ -30014,7 +30023,7 @@
       <c r="L387" s="31"/>
       <c r="M387" s="29"/>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="29" t="s">
         <v>957</v>
       </c>
@@ -30045,7 +30054,7 @@
       <c r="L388" s="31"/>
       <c r="M388" s="29"/>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="29" t="s">
         <v>1006</v>
       </c>
@@ -30072,7 +30081,7 @@
       <c r="L389" s="31"/>
       <c r="M389" s="29"/>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="29" t="s">
         <v>1002</v>
       </c>
@@ -30099,7 +30108,7 @@
       <c r="L390" s="31"/>
       <c r="M390" s="29"/>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="29" t="s">
         <v>1003</v>
       </c>
@@ -30126,7 +30135,7 @@
       <c r="L391" s="31"/>
       <c r="M391" s="29"/>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="29" t="s">
         <v>1004</v>
       </c>
@@ -30153,7 +30162,7 @@
       <c r="L392" s="31"/>
       <c r="M392" s="29"/>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
         <v>1005</v>
       </c>
@@ -30180,7 +30189,7 @@
       <c r="L393" s="31"/>
       <c r="M393" s="29"/>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
         <v>965</v>
       </c>
@@ -30207,7 +30216,7 @@
       <c r="L394" s="31"/>
       <c r="M394" s="29"/>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
         <v>966</v>
       </c>
@@ -30234,7 +30243,7 @@
       <c r="L395" s="31"/>
       <c r="M395" s="29"/>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
         <v>971</v>
       </c>
@@ -30257,7 +30266,7 @@
       <c r="L396" s="31"/>
       <c r="M396" s="29"/>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
         <v>972</v>
       </c>
@@ -30280,7 +30289,7 @@
       <c r="L397" s="31"/>
       <c r="M397" s="29"/>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
         <v>973</v>
       </c>
@@ -30303,7 +30312,7 @@
       <c r="L398" s="31"/>
       <c r="M398" s="29"/>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
         <v>982</v>
       </c>
@@ -30326,7 +30335,7 @@
       <c r="L399" s="31"/>
       <c r="M399" s="29"/>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
         <v>983</v>
       </c>
@@ -30349,7 +30358,7 @@
       <c r="L400" s="31"/>
       <c r="M400" s="29"/>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
         <v>984</v>
       </c>
@@ -30372,7 +30381,7 @@
       <c r="L401" s="31"/>
       <c r="M401" s="29"/>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
         <v>985</v>
       </c>
@@ -30395,7 +30404,7 @@
       <c r="L402" s="31"/>
       <c r="M402" s="29"/>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
         <v>986</v>
       </c>
@@ -30418,7 +30427,7 @@
       <c r="L403" s="31"/>
       <c r="M403" s="29"/>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
         <v>987</v>
       </c>
@@ -30441,7 +30450,7 @@
       <c r="L404" s="31"/>
       <c r="M404" s="29"/>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
         <v>988</v>
       </c>
@@ -30464,7 +30473,7 @@
       <c r="L405" s="31"/>
       <c r="M405" s="29"/>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
         <v>989</v>
       </c>
@@ -30487,7 +30496,7 @@
       <c r="L406" s="31"/>
       <c r="M406" s="29"/>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="29" t="s">
         <v>990</v>
       </c>
@@ -30510,7 +30519,7 @@
       <c r="L407" s="31"/>
       <c r="M407" s="29"/>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="29" t="s">
         <v>996</v>
       </c>
@@ -30539,7 +30548,7 @@
       <c r="L408" s="31"/>
       <c r="M408" s="29"/>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="29" t="s">
         <v>1000</v>
       </c>
@@ -30574,7 +30583,7 @@
       <c r="L409" s="31"/>
       <c r="M409" s="29"/>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="29" t="s">
         <v>999</v>
       </c>
@@ -30607,7 +30616,7 @@
       <c r="L410" s="31"/>
       <c r="M410" s="29"/>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
         <v>997</v>
       </c>
@@ -30636,7 +30645,7 @@
       <c r="L411" s="31"/>
       <c r="M411" s="29"/>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
         <v>994</v>
       </c>
@@ -30661,7 +30670,7 @@
       <c r="L412" s="31"/>
       <c r="M412" s="29"/>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
         <v>1013</v>
       </c>
@@ -30686,7 +30695,7 @@
       <c r="L413" s="31"/>
       <c r="M413" s="29"/>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
         <v>1014</v>
       </c>
@@ -30711,7 +30720,7 @@
       <c r="L414" s="31"/>
       <c r="M414" s="29"/>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="29" t="s">
         <v>1015</v>
       </c>
@@ -30736,7 +30745,7 @@
       <c r="L415" s="31"/>
       <c r="M415" s="29"/>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="29" t="s">
         <v>1020</v>
       </c>
@@ -30765,7 +30774,7 @@
       </c>
       <c r="M416" s="29"/>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="29" t="s">
         <v>1021</v>
       </c>
@@ -30792,7 +30801,7 @@
       <c r="L417" s="31"/>
       <c r="M417" s="29"/>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="29" t="s">
         <v>1022</v>
       </c>
@@ -30819,7 +30828,7 @@
       <c r="L418" s="31"/>
       <c r="M418" s="29"/>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="29" t="s">
         <v>1023</v>
       </c>
@@ -30846,7 +30855,7 @@
       <c r="L419" s="31"/>
       <c r="M419" s="29"/>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="29" t="s">
         <v>1024</v>
       </c>
@@ -30873,7 +30882,7 @@
       <c r="L420" s="31"/>
       <c r="M420" s="29"/>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="29" t="s">
         <v>1028</v>
       </c>
@@ -30908,7 +30917,7 @@
       <c r="L421" s="31"/>
       <c r="M421" s="29"/>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="29" t="s">
         <v>1037</v>
       </c>
@@ -30945,7 +30954,7 @@
       <c r="L422" s="31"/>
       <c r="M422" s="29"/>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="29" t="s">
         <v>1040</v>
       </c>
@@ -30976,7 +30985,7 @@
       <c r="L423" s="31"/>
       <c r="M423" s="29"/>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="29" t="s">
         <v>1041</v>
       </c>
@@ -31013,7 +31022,7 @@
       <c r="L424" s="31"/>
       <c r="M424" s="29"/>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="29" t="s">
         <v>1045</v>
       </c>
@@ -31038,7 +31047,7 @@
       <c r="L425" s="31"/>
       <c r="M425" s="29"/>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="29" t="s">
         <v>1046</v>
       </c>
@@ -31069,7 +31078,7 @@
       <c r="L426" s="31"/>
       <c r="M426" s="29"/>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="29" t="s">
         <v>1047</v>
       </c>
@@ -31098,7 +31107,7 @@
       <c r="L427" s="31"/>
       <c r="M427" s="29"/>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="29" t="s">
         <v>1049</v>
       </c>
@@ -31129,7 +31138,7 @@
       <c r="L428" s="31"/>
       <c r="M428" s="29"/>
     </row>
-    <row r="429" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="29" t="s">
         <v>1050</v>
       </c>
@@ -31160,7 +31169,7 @@
       <c r="L429" s="31"/>
       <c r="M429" s="29"/>
     </row>
-    <row r="430" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A430" s="29" t="s">
         <v>1053</v>
       </c>
@@ -31197,7 +31206,7 @@
       </c>
       <c r="M430" s="29"/>
     </row>
-    <row r="431" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A431" s="29" t="s">
         <v>1363</v>
       </c>
@@ -31230,7 +31239,7 @@
       <c r="L431" s="31"/>
       <c r="M431" s="29"/>
     </row>
-    <row r="432" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A432" s="29" t="s">
         <v>1055</v>
       </c>
@@ -31259,7 +31268,7 @@
       </c>
       <c r="M432" s="29"/>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="29" t="s">
         <v>1058</v>
       </c>
@@ -31288,7 +31297,7 @@
       <c r="L433" s="31"/>
       <c r="M433" s="29"/>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="29" t="s">
         <v>1061</v>
       </c>
@@ -31317,7 +31326,7 @@
       <c r="L434" s="31"/>
       <c r="M434" s="29"/>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="29" t="s">
         <v>1064</v>
       </c>
@@ -31356,7 +31365,7 @@
       </c>
       <c r="M435" s="29"/>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="29" t="s">
         <v>1065</v>
       </c>
@@ -31395,7 +31404,7 @@
       </c>
       <c r="M436" s="29"/>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="29" t="s">
         <v>1066</v>
       </c>
@@ -31434,7 +31443,7 @@
       </c>
       <c r="M437" s="29"/>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
         <v>1072</v>
       </c>
@@ -31469,7 +31478,7 @@
       <c r="L438" s="31"/>
       <c r="M438" s="29"/>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
         <v>1073</v>
       </c>
@@ -31504,7 +31513,7 @@
       <c r="L439" s="31"/>
       <c r="M439" s="29"/>
     </row>
-    <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="29" t="s">
         <v>1074</v>
       </c>
@@ -31539,7 +31548,7 @@
       <c r="L440" s="31"/>
       <c r="M440" s="29"/>
     </row>
-    <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A441" s="29" t="s">
         <v>1356</v>
       </c>
@@ -31572,7 +31581,7 @@
       <c r="L441" s="31"/>
       <c r="M441" s="29"/>
     </row>
-    <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
         <v>1357</v>
       </c>
@@ -31603,7 +31612,7 @@
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
-    <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="29" t="s">
         <v>1358</v>
       </c>
@@ -31632,7 +31641,7 @@
       <c r="L443" s="31"/>
       <c r="M443" s="29"/>
     </row>
-    <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
         <v>1359</v>
       </c>
@@ -31665,7 +31674,7 @@
       <c r="L444" s="31"/>
       <c r="M444" s="29"/>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
         <v>1360</v>
       </c>
@@ -31696,7 +31705,7 @@
       <c r="L445" s="31"/>
       <c r="M445" s="29"/>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
         <v>1361</v>
       </c>
@@ -31727,7 +31736,7 @@
       <c r="L446" s="31"/>
       <c r="M446" s="29"/>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
         <v>1362</v>
       </c>
@@ -31758,7 +31767,7 @@
       <c r="L447" s="31"/>
       <c r="M447" s="29"/>
     </row>
-    <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="29" t="s">
         <v>1363</v>
       </c>
@@ -31789,7 +31798,7 @@
       <c r="L448" s="31"/>
       <c r="M448" s="29"/>
     </row>
-    <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A449" s="29" t="s">
         <v>1364</v>
       </c>
@@ -31822,7 +31831,7 @@
       <c r="L449" s="31"/>
       <c r="M449" s="29"/>
     </row>
-    <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A450" s="29" t="s">
         <v>1365</v>
       </c>
@@ -31853,7 +31862,7 @@
       <c r="L450" s="31"/>
       <c r="M450" s="29"/>
     </row>
-    <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
         <v>1366</v>
       </c>
@@ -31884,7 +31893,7 @@
       <c r="L451" s="31"/>
       <c r="M451" s="29"/>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
         <v>1369</v>
       </c>
@@ -31915,7 +31924,7 @@
       <c r="L452" s="31"/>
       <c r="M452" s="29"/>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="29" t="s">
         <v>1076</v>
       </c>
@@ -31952,7 +31961,7 @@
       <c r="L453" s="31"/>
       <c r="M453" s="29"/>
     </row>
-    <row r="454" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="29" t="s">
         <v>1078</v>
       </c>
@@ -31989,7 +31998,7 @@
       <c r="L454" s="31"/>
       <c r="M454" s="29"/>
     </row>
-    <row r="455" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A455" s="29" t="s">
         <v>2392</v>
       </c>
@@ -32012,7 +32021,7 @@
       <c r="L455" s="31"/>
       <c r="M455" s="29"/>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="29" t="s">
         <v>1083</v>
       </c>
@@ -32037,7 +32046,7 @@
       <c r="L456" s="31"/>
       <c r="M456" s="29"/>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="34" t="s">
         <v>1186</v>
       </c>
@@ -32074,7 +32083,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="34" t="s">
         <v>1187</v>
       </c>
@@ -32111,7 +32120,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="34" t="s">
         <v>1188</v>
       </c>
@@ -32148,7 +32157,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="34" t="s">
         <v>1189</v>
       </c>
@@ -32185,7 +32194,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="34" t="s">
         <v>1190</v>
       </c>
@@ -32222,7 +32231,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="57" t="s">
         <v>1234</v>
       </c>
@@ -32259,7 +32268,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="57" t="s">
         <v>1195</v>
       </c>
@@ -32296,7 +32305,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="57" t="s">
         <v>1194</v>
       </c>
@@ -32333,7 +32342,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="29" t="s">
         <v>1191</v>
       </c>
@@ -32370,7 +32379,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="29" t="s">
         <v>1192</v>
       </c>
@@ -32407,7 +32416,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="29" t="s">
         <v>1193</v>
       </c>
@@ -32444,7 +32453,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="21" t="s">
         <v>13</v>
       </c>
@@ -32475,7 +32484,7 @@
       <c r="L468" s="31"/>
       <c r="M468" s="29"/>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="21" t="s">
         <v>14</v>
       </c>
@@ -32506,7 +32515,7 @@
       <c r="L469" s="31"/>
       <c r="M469" s="29"/>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="21" t="s">
         <v>18</v>
       </c>
@@ -32537,7 +32546,7 @@
       <c r="L470" s="31"/>
       <c r="M470" s="29"/>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="21" t="s">
         <v>15</v>
       </c>
@@ -32568,7 +32577,7 @@
       <c r="L471" s="31"/>
       <c r="M471" s="29"/>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
         <v>1111</v>
       </c>
@@ -32599,7 +32608,7 @@
       <c r="L472" s="31"/>
       <c r="M472" s="29"/>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="21" t="s">
         <v>16</v>
       </c>
@@ -32630,7 +32639,7 @@
       <c r="L473" s="31"/>
       <c r="M473" s="29"/>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
         <v>1112</v>
       </c>
@@ -32657,7 +32666,7 @@
       <c r="L474" s="31"/>
       <c r="M474" s="29"/>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="21" t="s">
         <v>17</v>
       </c>
@@ -32694,7 +32703,7 @@
       <c r="L475" s="31"/>
       <c r="M475" s="29"/>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="29"/>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -32709,7 +32718,7 @@
       <c r="L476" s="31"/>
       <c r="M476" s="29"/>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="29" t="s">
         <v>1176</v>
       </c>
@@ -32746,7 +32755,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="29" t="s">
         <v>1177</v>
       </c>
@@ -32783,7 +32792,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="29" t="s">
         <v>1178</v>
       </c>
@@ -32820,7 +32829,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="29" t="s">
         <v>1179</v>
       </c>
@@ -32857,7 +32866,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="29" t="s">
         <v>1180</v>
       </c>
@@ -32894,7 +32903,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="29" t="s">
         <v>1181</v>
       </c>
@@ -32931,7 +32940,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="29" t="s">
         <v>1182</v>
       </c>
@@ -32968,7 +32977,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="29" t="s">
         <v>1183</v>
       </c>
@@ -33005,7 +33014,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="29" t="s">
         <v>1184</v>
       </c>
@@ -33042,7 +33051,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="29" t="s">
         <v>1185</v>
       </c>
@@ -33079,7 +33088,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="29" t="s">
         <v>2238</v>
       </c>
@@ -33110,7 +33119,7 @@
       <c r="L487" s="31"/>
       <c r="M487" s="29"/>
     </row>
-    <row r="488" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="29"/>
       <c r="B488" s="29"/>
       <c r="C488" s="53"/>
@@ -33125,7 +33134,7 @@
       <c r="L488" s="31"/>
       <c r="M488" s="29"/>
     </row>
-    <row r="489" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A489" s="105"/>
       <c r="B489" s="105"/>
       <c r="C489" s="73"/>
@@ -33140,7 +33149,7 @@
       <c r="L489" s="31"/>
       <c r="M489" s="29"/>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="29" t="s">
         <v>2239</v>
       </c>
@@ -33171,7 +33180,7 @@
       <c r="L490" s="31"/>
       <c r="M490" s="29"/>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
         <v>1113</v>
       </c>
@@ -33200,7 +33209,7 @@
       <c r="L491" s="31"/>
       <c r="M491" s="29"/>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="29" t="s">
         <v>1114</v>
       </c>
@@ -33227,7 +33236,7 @@
       <c r="L492" s="31"/>
       <c r="M492" s="29"/>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="29" t="s">
         <v>1233</v>
       </c>
@@ -33262,7 +33271,7 @@
       <c r="L493" s="31"/>
       <c r="M493" s="29"/>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="29" t="s">
         <v>1231</v>
       </c>
@@ -33299,7 +33308,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="29" t="s">
         <v>1235</v>
       </c>
@@ -33336,7 +33345,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="29" t="s">
         <v>1232</v>
       </c>
@@ -33373,7 +33382,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="497" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="57" t="s">
         <v>1236</v>
       </c>
@@ -33410,7 +33419,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A498" s="57" t="s">
         <v>1237</v>
       </c>
@@ -33447,7 +33456,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="499" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A499" s="34" t="s">
         <v>1212</v>
       </c>
@@ -33476,7 +33485,7 @@
       <c r="L499" s="31"/>
       <c r="M499" s="29"/>
     </row>
-    <row r="500" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A500" s="34" t="s">
         <v>1215</v>
       </c>
@@ -33501,7 +33510,7 @@
       <c r="L500" s="31"/>
       <c r="M500" s="29"/>
     </row>
-    <row r="501" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A501" s="60" t="s">
         <v>1238</v>
       </c>
@@ -33536,7 +33545,7 @@
       <c r="L501" s="31"/>
       <c r="M501" s="29"/>
     </row>
-    <row r="502" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A502" s="29" t="s">
         <v>1239</v>
       </c>
@@ -33565,7 +33574,7 @@
       <c r="L502" s="31"/>
       <c r="M502" s="29"/>
     </row>
-    <row r="503" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A503" s="29" t="s">
         <v>1247</v>
       </c>
@@ -33594,7 +33603,7 @@
       <c r="L503" s="31"/>
       <c r="M503" s="29"/>
     </row>
-    <row r="504" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A504" s="34" t="s">
         <v>1246</v>
       </c>
@@ -33631,7 +33640,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="505" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A505" s="29" t="s">
         <v>327</v>
       </c>
@@ -33666,7 +33675,7 @@
       <c r="L505" s="31"/>
       <c r="M505" s="29"/>
     </row>
-    <row r="506" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A506" s="34" t="s">
         <v>1248</v>
       </c>
@@ -33705,7 +33714,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="507" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A507" s="34" t="s">
         <v>1252</v>
       </c>
@@ -33742,7 +33751,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="508" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
         <v>1254</v>
       </c>
@@ -33779,7 +33788,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="509" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A509" s="34" t="s">
         <v>1258</v>
       </c>
@@ -33818,7 +33827,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="34" t="s">
         <v>1117</v>
       </c>
@@ -33845,7 +33854,7 @@
       <c r="L510" s="31"/>
       <c r="M510" s="29"/>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="24" t="s">
         <v>1118</v>
       </c>
@@ -33872,7 +33881,7 @@
       <c r="L511" s="31"/>
       <c r="M511" s="29"/>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="29" t="s">
         <v>1119</v>
       </c>
@@ -33899,7 +33908,7 @@
       </c>
       <c r="M512" s="29"/>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="29" t="s">
         <v>1120</v>
       </c>
@@ -33926,7 +33935,7 @@
       </c>
       <c r="M513" s="29"/>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="29" t="s">
         <v>1121</v>
       </c>
@@ -33953,7 +33962,7 @@
       </c>
       <c r="M514" s="29"/>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="29" t="s">
         <v>1122</v>
       </c>
@@ -33982,7 +33991,7 @@
       </c>
       <c r="M515" s="29"/>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="29" t="s">
         <v>1127</v>
       </c>
@@ -34019,7 +34028,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="29" t="s">
         <v>1128</v>
       </c>
@@ -34054,7 +34063,7 @@
       </c>
       <c r="M517" s="29"/>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="29" t="s">
         <v>1132</v>
       </c>
@@ -34089,7 +34098,7 @@
       <c r="L518" s="31"/>
       <c r="M518" s="29"/>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="29" t="s">
         <v>1133</v>
       </c>
@@ -34124,7 +34133,7 @@
       <c r="L519" s="31"/>
       <c r="M519" s="29"/>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="29" t="s">
         <v>1134</v>
       </c>
@@ -34159,7 +34168,7 @@
       <c r="L520" s="31"/>
       <c r="M520" s="29"/>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="31" t="s">
         <v>1140</v>
       </c>
@@ -34194,7 +34203,7 @@
       <c r="L521" s="31"/>
       <c r="M521" s="29"/>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="31" t="s">
         <v>1141</v>
       </c>
@@ -34229,7 +34238,7 @@
       <c r="L522" s="31"/>
       <c r="M522" s="29"/>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="31" t="s">
         <v>1142</v>
       </c>
@@ -34264,7 +34273,7 @@
       <c r="L523" s="31"/>
       <c r="M523" s="29"/>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="29" t="s">
         <v>1144</v>
       </c>
@@ -34299,7 +34308,7 @@
       <c r="L524" s="31"/>
       <c r="M524" s="29"/>
     </row>
-    <row r="525" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="29" t="s">
         <v>1147</v>
       </c>
@@ -34334,7 +34343,7 @@
       <c r="L525" s="31"/>
       <c r="M525" s="29"/>
     </row>
-    <row r="526" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A526" s="29" t="s">
         <v>1845</v>
       </c>
@@ -34371,7 +34380,7 @@
       <c r="L526" s="31"/>
       <c r="M526" s="29"/>
     </row>
-    <row r="527" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A527" s="29" t="s">
         <v>1846</v>
       </c>
@@ -34408,7 +34417,7 @@
       <c r="L527" s="31"/>
       <c r="M527" s="29"/>
     </row>
-    <row r="528" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A528" s="29" t="s">
         <v>1847</v>
       </c>
@@ -34445,7 +34454,7 @@
       <c r="L528" s="31"/>
       <c r="M528" s="29"/>
     </row>
-    <row r="529" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A529" s="29" t="s">
         <v>1848</v>
       </c>
@@ -34482,7 +34491,7 @@
       <c r="L529" s="31"/>
       <c r="M529" s="29"/>
     </row>
-    <row r="530" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A530" s="29" t="s">
         <v>1849</v>
       </c>
@@ -34519,7 +34528,7 @@
       <c r="L530" s="31"/>
       <c r="M530" s="29"/>
     </row>
-    <row r="531" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A531" s="29" t="s">
         <v>1850</v>
       </c>
@@ -34556,7 +34565,7 @@
       <c r="L531" s="31"/>
       <c r="M531" s="29"/>
     </row>
-    <row r="532" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A532" s="29" t="s">
         <v>1851</v>
       </c>
@@ -34593,7 +34602,7 @@
       <c r="L532" s="31"/>
       <c r="M532" s="29"/>
     </row>
-    <row r="533" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A533" s="29" t="s">
         <v>1852</v>
       </c>
@@ -34630,7 +34639,7 @@
       <c r="L533" s="31"/>
       <c r="M533" s="29"/>
     </row>
-    <row r="534" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A534" s="29" t="s">
         <v>1853</v>
       </c>
@@ -34667,7 +34676,7 @@
       <c r="L534" s="31"/>
       <c r="M534" s="29"/>
     </row>
-    <row r="535" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A535" s="29" t="s">
         <v>1854</v>
       </c>
@@ -34704,7 +34713,7 @@
       <c r="L535" s="31"/>
       <c r="M535" s="29"/>
     </row>
-    <row r="536" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A536" s="29" t="s">
         <v>1855</v>
       </c>
@@ -34741,7 +34750,7 @@
       <c r="L536" s="31"/>
       <c r="M536" s="29"/>
     </row>
-    <row r="537" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A537" s="29" t="s">
         <v>1856</v>
       </c>
@@ -34778,7 +34787,7 @@
       <c r="L537" s="31"/>
       <c r="M537" s="29"/>
     </row>
-    <row r="538" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A538" s="29" t="s">
         <v>1857</v>
       </c>
@@ -34815,7 +34824,7 @@
       <c r="L538" s="31"/>
       <c r="M538" s="29"/>
     </row>
-    <row r="539" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A539" s="29" t="s">
         <v>1208</v>
       </c>
@@ -34846,7 +34855,7 @@
       <c r="L539" s="31"/>
       <c r="M539" s="29"/>
     </row>
-    <row r="540" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A540" s="29" t="s">
         <v>1260</v>
       </c>
@@ -34869,7 +34878,7 @@
       <c r="L540" s="31"/>
       <c r="M540" s="29"/>
     </row>
-    <row r="541" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A541" s="29" t="s">
         <v>1219</v>
       </c>
@@ -34904,7 +34913,7 @@
       <c r="L541" s="31"/>
       <c r="M541" s="29"/>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="34" t="s">
         <v>1196</v>
       </c>
@@ -34939,7 +34948,7 @@
       <c r="L542" s="31"/>
       <c r="M542" s="29"/>
     </row>
-    <row r="543" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="29" t="s">
         <v>1206</v>
       </c>
@@ -34970,7 +34979,7 @@
       <c r="L543" s="31"/>
       <c r="M543" s="29"/>
     </row>
-    <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A544" s="29" t="s">
         <v>1268</v>
       </c>
@@ -34999,7 +35008,7 @@
       <c r="L544" s="31"/>
       <c r="M544" s="29"/>
     </row>
-    <row r="545" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A545" s="29" t="s">
         <v>1269</v>
       </c>
@@ -35028,7 +35037,7 @@
       <c r="L545" s="31"/>
       <c r="M545" s="29"/>
     </row>
-    <row r="546" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A546" s="29" t="s">
         <v>1273</v>
       </c>
@@ -35057,7 +35066,7 @@
       <c r="L546" s="31"/>
       <c r="M546" s="29"/>
     </row>
-    <row r="547" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A547" s="29" t="s">
         <v>1728</v>
       </c>
@@ -35086,7 +35095,7 @@
       <c r="L547" s="31"/>
       <c r="M547" s="29"/>
     </row>
-    <row r="548" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A548" s="29" t="s">
         <v>1729</v>
       </c>
@@ -35115,7 +35124,7 @@
       <c r="L548" s="31"/>
       <c r="M548" s="29"/>
     </row>
-    <row r="549" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A549" s="29" t="s">
         <v>1730</v>
       </c>
@@ -35144,7 +35153,7 @@
       <c r="L549" s="31"/>
       <c r="M549" s="29"/>
     </row>
-    <row r="550" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A550" s="29" t="s">
         <v>1731</v>
       </c>
@@ -35173,7 +35182,7 @@
       <c r="L550" s="31"/>
       <c r="M550" s="29"/>
     </row>
-    <row r="551" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A551" s="29" t="s">
         <v>1732</v>
       </c>
@@ -35202,7 +35211,7 @@
       <c r="L551" s="31"/>
       <c r="M551" s="29"/>
     </row>
-    <row r="552" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A552" s="29" t="s">
         <v>1733</v>
       </c>
@@ -35231,7 +35240,7 @@
       <c r="L552" s="31"/>
       <c r="M552" s="29"/>
     </row>
-    <row r="553" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A553" s="29" t="s">
         <v>1734</v>
       </c>
@@ -35260,7 +35269,7 @@
       <c r="L553" s="31"/>
       <c r="M553" s="29"/>
     </row>
-    <row r="554" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A554" s="29" t="s">
         <v>1735</v>
       </c>
@@ -35289,7 +35298,7 @@
       <c r="L554" s="31"/>
       <c r="M554" s="29"/>
     </row>
-    <row r="555" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A555" s="29" t="s">
         <v>1736</v>
       </c>
@@ -35318,7 +35327,7 @@
       <c r="L555" s="31"/>
       <c r="M555" s="29"/>
     </row>
-    <row r="556" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A556" s="29" t="s">
         <v>1737</v>
       </c>
@@ -35347,7 +35356,7 @@
       <c r="L556" s="31"/>
       <c r="M556" s="29"/>
     </row>
-    <row r="557" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A557" s="29" t="s">
         <v>1398</v>
       </c>
@@ -35376,7 +35385,7 @@
       <c r="L557" s="31"/>
       <c r="M557" s="29"/>
     </row>
-    <row r="558" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A558" s="29" t="s">
         <v>1399</v>
       </c>
@@ -35405,7 +35414,7 @@
       <c r="L558" s="31"/>
       <c r="M558" s="29"/>
     </row>
-    <row r="559" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A559" s="29" t="s">
         <v>1400</v>
       </c>
@@ -35434,7 +35443,7 @@
       <c r="L559" s="31"/>
       <c r="M559" s="29"/>
     </row>
-    <row r="560" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A560" s="29" t="s">
         <v>1401</v>
       </c>
@@ -35463,7 +35472,7 @@
       <c r="L560" s="31"/>
       <c r="M560" s="29"/>
     </row>
-    <row r="561" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A561" s="29" t="s">
         <v>1402</v>
       </c>
@@ -35492,7 +35501,7 @@
       <c r="L561" s="31"/>
       <c r="M561" s="29"/>
     </row>
-    <row r="562" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A562" s="29" t="s">
         <v>1403</v>
       </c>
@@ -35521,7 +35530,7 @@
       <c r="L562" s="31"/>
       <c r="M562" s="29"/>
     </row>
-    <row r="563" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A563" s="29" t="s">
         <v>1404</v>
       </c>
@@ -35550,7 +35559,7 @@
       <c r="L563" s="31"/>
       <c r="M563" s="29"/>
     </row>
-    <row r="564" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A564" s="29" t="s">
         <v>1405</v>
       </c>
@@ -35579,7 +35588,7 @@
       <c r="L564" s="31"/>
       <c r="M564" s="29"/>
     </row>
-    <row r="565" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A565" s="29" t="s">
         <v>1406</v>
       </c>
@@ -35608,7 +35617,7 @@
       <c r="L565" s="31"/>
       <c r="M565" s="29"/>
     </row>
-    <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A566" s="29" t="s">
         <v>1407</v>
       </c>
@@ -35637,7 +35646,7 @@
       <c r="L566" s="31"/>
       <c r="M566" s="29"/>
     </row>
-    <row r="567" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A567" s="29" t="s">
         <v>1408</v>
       </c>
@@ -35666,7 +35675,7 @@
       <c r="L567" s="31"/>
       <c r="M567" s="29"/>
     </row>
-    <row r="568" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A568" s="29" t="s">
         <v>1762</v>
       </c>
@@ -35695,7 +35704,7 @@
       <c r="L568" s="31"/>
       <c r="M568" s="29"/>
     </row>
-    <row r="569" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A569" s="73" t="s">
         <v>1326</v>
       </c>
@@ -35728,7 +35737,7 @@
       <c r="L569" s="31"/>
       <c r="M569" s="29"/>
     </row>
-    <row r="570" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A570" s="73" t="s">
         <v>1327</v>
       </c>
@@ -35761,7 +35770,7 @@
       <c r="L570" s="31"/>
       <c r="M570" s="29"/>
     </row>
-    <row r="571" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A571" s="73" t="s">
         <v>1328</v>
       </c>
@@ -35794,7 +35803,7 @@
       <c r="L571" s="31"/>
       <c r="M571" s="29"/>
     </row>
-    <row r="572" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A572" s="73" t="s">
         <v>1329</v>
       </c>
@@ -35827,7 +35836,7 @@
       <c r="L572" s="31"/>
       <c r="M572" s="29"/>
     </row>
-    <row r="573" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A573" s="73" t="s">
         <v>1330</v>
       </c>
@@ -35860,7 +35869,7 @@
       <c r="L573" s="31"/>
       <c r="M573" s="29"/>
     </row>
-    <row r="574" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A574" s="73" t="s">
         <v>1331</v>
       </c>
@@ -35893,7 +35902,7 @@
       <c r="L574" s="31"/>
       <c r="M574" s="29"/>
     </row>
-    <row r="575" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A575" s="73" t="s">
         <v>1332</v>
       </c>
@@ -35926,7 +35935,7 @@
       <c r="L575" s="31"/>
       <c r="M575" s="29"/>
     </row>
-    <row r="576" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A576" s="73" t="s">
         <v>1333</v>
       </c>
@@ -35959,7 +35968,7 @@
       <c r="L576" s="31"/>
       <c r="M576" s="29"/>
     </row>
-    <row r="577" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A577" s="73" t="s">
         <v>1334</v>
       </c>
@@ -35992,7 +36001,7 @@
       <c r="L577" s="31"/>
       <c r="M577" s="29"/>
     </row>
-    <row r="578" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A578" s="73" t="s">
         <v>1335</v>
       </c>
@@ -36025,7 +36034,7 @@
       <c r="L578" s="31"/>
       <c r="M578" s="29"/>
     </row>
-    <row r="579" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A579" s="73" t="s">
         <v>1336</v>
       </c>
@@ -36058,7 +36067,7 @@
       <c r="L579" s="31"/>
       <c r="M579" s="29"/>
     </row>
-    <row r="580" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A580" s="29" t="s">
         <v>1381</v>
       </c>
@@ -36093,7 +36102,7 @@
       <c r="L580" s="31"/>
       <c r="M580" s="29"/>
     </row>
-    <row r="581" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A581" s="29" t="s">
         <v>1394</v>
       </c>
@@ -36126,7 +36135,7 @@
       <c r="L581" s="31"/>
       <c r="M581" s="29"/>
     </row>
-    <row r="582" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A582" s="29" t="s">
         <v>1395</v>
       </c>
@@ -36159,7 +36168,7 @@
       <c r="L582" s="31"/>
       <c r="M582" s="29"/>
     </row>
-    <row r="583" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A583" s="29" t="s">
         <v>1396</v>
       </c>
@@ -36190,7 +36199,7 @@
       <c r="L583" s="31"/>
       <c r="M583" s="29"/>
     </row>
-    <row r="584" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A584" s="29" t="s">
         <v>1397</v>
       </c>
@@ -36221,7 +36230,7 @@
       <c r="L584" s="31"/>
       <c r="M584" s="29"/>
     </row>
-    <row r="585" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A585" s="29" t="s">
         <v>1398</v>
       </c>
@@ -36252,7 +36261,7 @@
       <c r="L585" s="31"/>
       <c r="M585" s="29"/>
     </row>
-    <row r="586" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A586" s="29" t="s">
         <v>1399</v>
       </c>
@@ -36283,7 +36292,7 @@
       <c r="L586" s="31"/>
       <c r="M586" s="29"/>
     </row>
-    <row r="587" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A587" s="29" t="s">
         <v>1400</v>
       </c>
@@ -36314,7 +36323,7 @@
       <c r="L587" s="31"/>
       <c r="M587" s="29"/>
     </row>
-    <row r="588" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A588" s="29" t="s">
         <v>1401</v>
       </c>
@@ -36345,7 +36354,7 @@
       <c r="L588" s="31"/>
       <c r="M588" s="29"/>
     </row>
-    <row r="589" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A589" s="29" t="s">
         <v>1402</v>
       </c>
@@ -36376,7 +36385,7 @@
       <c r="L589" s="31"/>
       <c r="M589" s="29"/>
     </row>
-    <row r="590" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A590" s="29" t="s">
         <v>1403</v>
       </c>
@@ -36407,7 +36416,7 @@
       <c r="L590" s="31"/>
       <c r="M590" s="29"/>
     </row>
-    <row r="591" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A591" s="29" t="s">
         <v>1404</v>
       </c>
@@ -36438,7 +36447,7 @@
       <c r="L591" s="31"/>
       <c r="M591" s="29"/>
     </row>
-    <row r="592" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A592" s="29" t="s">
         <v>1405</v>
       </c>
@@ -36469,7 +36478,7 @@
       <c r="L592" s="31"/>
       <c r="M592" s="29"/>
     </row>
-    <row r="593" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A593" s="29" t="s">
         <v>1406</v>
       </c>
@@ -36500,7 +36509,7 @@
       <c r="L593" s="31"/>
       <c r="M593" s="29"/>
     </row>
-    <row r="594" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A594" s="29" t="s">
         <v>1407</v>
       </c>
@@ -36531,7 +36540,7 @@
       <c r="L594" s="31"/>
       <c r="M594" s="29"/>
     </row>
-    <row r="595" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A595" s="29" t="s">
         <v>1408</v>
       </c>
@@ -36562,7 +36571,7 @@
       <c r="L595" s="31"/>
       <c r="M595" s="29"/>
     </row>
-    <row r="596" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A596" s="29" t="s">
         <v>1409</v>
       </c>
@@ -36593,7 +36602,7 @@
       <c r="L596" s="31"/>
       <c r="M596" s="29"/>
     </row>
-    <row r="597" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A597" s="29" t="s">
         <v>1410</v>
       </c>
@@ -36624,7 +36633,7 @@
       <c r="L597" s="31"/>
       <c r="M597" s="29"/>
     </row>
-    <row r="598" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A598" s="29" t="s">
         <v>1411</v>
       </c>
@@ -36655,7 +36664,7 @@
       <c r="L598" s="31"/>
       <c r="M598" s="29"/>
     </row>
-    <row r="599" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A599" s="29" t="s">
         <v>1412</v>
       </c>
@@ -36686,7 +36695,7 @@
       <c r="L599" s="31"/>
       <c r="M599" s="29"/>
     </row>
-    <row r="600" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A600" s="29" t="s">
         <v>1413</v>
       </c>
@@ -36717,7 +36726,7 @@
       <c r="L600" s="31"/>
       <c r="M600" s="29"/>
     </row>
-    <row r="601" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A601" s="29" t="s">
         <v>1414</v>
       </c>
@@ -36748,7 +36757,7 @@
       <c r="L601" s="31"/>
       <c r="M601" s="29"/>
     </row>
-    <row r="602" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A602" s="29" t="s">
         <v>1415</v>
       </c>
@@ -36779,7 +36788,7 @@
       <c r="L602" s="31"/>
       <c r="M602" s="29"/>
     </row>
-    <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A603" s="29" t="s">
         <v>1416</v>
       </c>
@@ -36810,7 +36819,7 @@
       <c r="L603" s="31"/>
       <c r="M603" s="29"/>
     </row>
-    <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A604" s="29" t="s">
         <v>1417</v>
       </c>
@@ -36841,7 +36850,7 @@
       <c r="L604" s="31"/>
       <c r="M604" s="29"/>
     </row>
-    <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A605" s="29" t="s">
         <v>1446</v>
       </c>
@@ -36874,7 +36883,7 @@
       <c r="L605" s="31"/>
       <c r="M605" s="29"/>
     </row>
-    <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A606" s="29" t="s">
         <v>1447</v>
       </c>
@@ -36907,7 +36916,7 @@
       <c r="L606" s="31"/>
       <c r="M606" s="29"/>
     </row>
-    <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A607" s="29" t="s">
         <v>1448</v>
       </c>
@@ -36940,7 +36949,7 @@
       <c r="L607" s="31"/>
       <c r="M607" s="29"/>
     </row>
-    <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A608" s="29" t="s">
         <v>1449</v>
       </c>
@@ -36973,7 +36982,7 @@
       <c r="L608" s="31"/>
       <c r="M608" s="29"/>
     </row>
-    <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A609" s="29" t="s">
         <v>1450</v>
       </c>
@@ -37004,7 +37013,7 @@
       <c r="L609" s="31"/>
       <c r="M609" s="29"/>
     </row>
-    <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A610" s="29" t="s">
         <v>1451</v>
       </c>
@@ -37035,7 +37044,7 @@
       <c r="L610" s="31"/>
       <c r="M610" s="29"/>
     </row>
-    <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A611" s="29" t="s">
         <v>1452</v>
       </c>
@@ -37066,7 +37075,7 @@
       <c r="L611" s="31"/>
       <c r="M611" s="29"/>
     </row>
-    <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A612" s="29" t="s">
         <v>1453</v>
       </c>
@@ -37097,7 +37106,7 @@
       <c r="L612" s="31"/>
       <c r="M612" s="29"/>
     </row>
-    <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A613" s="29" t="s">
         <v>1454</v>
       </c>
@@ -37128,7 +37137,7 @@
       <c r="L613" s="31"/>
       <c r="M613" s="29"/>
     </row>
-    <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A614" s="29" t="s">
         <v>1455</v>
       </c>
@@ -37159,7 +37168,7 @@
       <c r="L614" s="31"/>
       <c r="M614" s="29"/>
     </row>
-    <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A615" s="29" t="s">
         <v>1456</v>
       </c>
@@ -37190,7 +37199,7 @@
       <c r="L615" s="31"/>
       <c r="M615" s="29"/>
     </row>
-    <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A616" s="29" t="s">
         <v>1457</v>
       </c>
@@ -37221,7 +37230,7 @@
       <c r="L616" s="31"/>
       <c r="M616" s="29"/>
     </row>
-    <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A617" s="29" t="s">
         <v>1458</v>
       </c>
@@ -37252,7 +37261,7 @@
       <c r="L617" s="31"/>
       <c r="M617" s="29"/>
     </row>
-    <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A618" s="29" t="s">
         <v>1459</v>
       </c>
@@ -37283,7 +37292,7 @@
       <c r="L618" s="31"/>
       <c r="M618" s="29"/>
     </row>
-    <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A619" s="29" t="s">
         <v>1460</v>
       </c>
@@ -37316,7 +37325,7 @@
       <c r="L619" s="31"/>
       <c r="M619" s="29"/>
     </row>
-    <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A620" s="29" t="s">
         <v>1461</v>
       </c>
@@ -37349,7 +37358,7 @@
       <c r="L620" s="31"/>
       <c r="M620" s="29"/>
     </row>
-    <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A621" s="29" t="s">
         <v>1462</v>
       </c>
@@ -37380,7 +37389,7 @@
       <c r="L621" s="31"/>
       <c r="M621" s="29"/>
     </row>
-    <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A622" s="29" t="s">
         <v>1463</v>
       </c>
@@ -37411,7 +37420,7 @@
       <c r="L622" s="31"/>
       <c r="M622" s="29"/>
     </row>
-    <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A623" s="29" t="s">
         <v>1464</v>
       </c>
@@ -37442,7 +37451,7 @@
       <c r="L623" s="31"/>
       <c r="M623" s="29"/>
     </row>
-    <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A624" s="29" t="s">
         <v>1465</v>
       </c>
@@ -37475,7 +37484,7 @@
       <c r="L624" s="31"/>
       <c r="M624" s="29"/>
     </row>
-    <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A625" s="29" t="s">
         <v>1466</v>
       </c>
@@ -37508,7 +37517,7 @@
       <c r="L625" s="31"/>
       <c r="M625" s="29"/>
     </row>
-    <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A626" s="29" t="s">
         <v>1467</v>
       </c>
@@ -37539,7 +37548,7 @@
       <c r="L626" s="31"/>
       <c r="M626" s="29"/>
     </row>
-    <row r="627" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A627" s="29" t="s">
         <v>1468</v>
       </c>
@@ -37570,7 +37579,7 @@
       <c r="L627" s="31"/>
       <c r="M627" s="29"/>
     </row>
-    <row r="628" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A628" s="29" t="s">
         <v>1469</v>
       </c>
@@ -37601,7 +37610,7 @@
       <c r="L628" s="31"/>
       <c r="M628" s="29"/>
     </row>
-    <row r="629" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A629" s="29" t="s">
         <v>1681</v>
       </c>
@@ -37634,7 +37643,7 @@
       <c r="L629" s="31"/>
       <c r="M629" s="29"/>
     </row>
-    <row r="630" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
         <v>1682</v>
       </c>
@@ -37667,7 +37676,7 @@
       <c r="L630" s="31"/>
       <c r="M630" s="29"/>
     </row>
-    <row r="631" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A631" s="29" t="s">
         <v>1479</v>
       </c>
@@ -37694,7 +37703,7 @@
       <c r="L631" s="31"/>
       <c r="M631" s="29"/>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="29" t="s">
         <v>1480</v>
       </c>
@@ -37721,7 +37730,7 @@
       <c r="L632" s="31"/>
       <c r="M632" s="29"/>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="29" t="s">
         <v>1492</v>
       </c>
@@ -37756,7 +37765,7 @@
       <c r="L633" s="31"/>
       <c r="M633" s="29"/>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="29" t="s">
         <v>1493</v>
       </c>
@@ -37791,7 +37800,7 @@
       <c r="L634" s="31"/>
       <c r="M634" s="29"/>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="29" t="s">
         <v>1494</v>
       </c>
@@ -37826,7 +37835,7 @@
       <c r="L635" s="31"/>
       <c r="M635" s="29"/>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="29" t="s">
         <v>1495</v>
       </c>
@@ -37861,7 +37870,7 @@
       <c r="L636" s="31"/>
       <c r="M636" s="29"/>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="29" t="s">
         <v>1496</v>
       </c>
@@ -37896,7 +37905,7 @@
       <c r="L637" s="31"/>
       <c r="M637" s="29"/>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="29" t="s">
         <v>1497</v>
       </c>
@@ -37931,7 +37940,7 @@
       <c r="L638" s="31"/>
       <c r="M638" s="29"/>
     </row>
-    <row r="639" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="29" t="s">
         <v>1498</v>
       </c>
@@ -37966,7 +37975,7 @@
       <c r="L639" s="31"/>
       <c r="M639" s="29"/>
     </row>
-    <row r="640" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A640" s="29" t="s">
         <v>1507</v>
       </c>
@@ -38001,7 +38010,7 @@
       <c r="L640" s="31"/>
       <c r="M640" s="29"/>
     </row>
-    <row r="641" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A641" s="29" t="s">
         <v>1508</v>
       </c>
@@ -38036,7 +38045,7 @@
       <c r="L641" s="31"/>
       <c r="M641" s="29"/>
     </row>
-    <row r="642" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A642" s="29" t="s">
         <v>1509</v>
       </c>
@@ -38071,7 +38080,7 @@
       <c r="L642" s="31"/>
       <c r="M642" s="29"/>
     </row>
-    <row r="643" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A643" s="29" t="s">
         <v>1510</v>
       </c>
@@ -38106,7 +38115,7 @@
       <c r="L643" s="31"/>
       <c r="M643" s="29"/>
     </row>
-    <row r="644" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A644" s="29" t="s">
         <v>1511</v>
       </c>
@@ -38141,7 +38150,7 @@
       <c r="L644" s="31"/>
       <c r="M644" s="29"/>
     </row>
-    <row r="645" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A645" s="29" t="s">
         <v>1512</v>
       </c>
@@ -38176,7 +38185,7 @@
       <c r="L645" s="31"/>
       <c r="M645" s="29"/>
     </row>
-    <row r="646" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A646" s="29" t="s">
         <v>1516</v>
       </c>
@@ -38211,7 +38220,7 @@
       <c r="L646" s="31"/>
       <c r="M646" s="29"/>
     </row>
-    <row r="647" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A647" s="29" t="s">
         <v>1530</v>
       </c>
@@ -38246,7 +38255,7 @@
       <c r="L647" s="31"/>
       <c r="M647" s="29"/>
     </row>
-    <row r="648" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A648" s="29" t="s">
         <v>1531</v>
       </c>
@@ -38281,7 +38290,7 @@
       <c r="L648" s="31"/>
       <c r="M648" s="29"/>
     </row>
-    <row r="649" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A649" s="29" t="s">
         <v>1532</v>
       </c>
@@ -38316,7 +38325,7 @@
       <c r="L649" s="31"/>
       <c r="M649" s="29"/>
     </row>
-    <row r="650" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A650" s="29" t="s">
         <v>1517</v>
       </c>
@@ -38351,7 +38360,7 @@
       <c r="L650" s="31"/>
       <c r="M650" s="29"/>
     </row>
-    <row r="651" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A651" s="29" t="s">
         <v>1518</v>
       </c>
@@ -38386,7 +38395,7 @@
       <c r="L651" s="31"/>
       <c r="M651" s="29"/>
     </row>
-    <row r="652" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A652" s="29" t="s">
         <v>1533</v>
       </c>
@@ -38421,7 +38430,7 @@
       <c r="L652" s="31"/>
       <c r="M652" s="29"/>
     </row>
-    <row r="653" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A653" s="29" t="s">
         <v>1534</v>
       </c>
@@ -38456,7 +38465,7 @@
       <c r="L653" s="31"/>
       <c r="M653" s="29"/>
     </row>
-    <row r="654" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A654" s="29" t="s">
         <v>1535</v>
       </c>
@@ -38491,7 +38500,7 @@
       <c r="L654" s="31"/>
       <c r="M654" s="29"/>
     </row>
-    <row r="655" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A655" s="29" t="s">
         <v>1536</v>
       </c>
@@ -38526,7 +38535,7 @@
       <c r="L655" s="31"/>
       <c r="M655" s="29"/>
     </row>
-    <row r="656" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A656" s="29" t="s">
         <v>1537</v>
       </c>
@@ -38561,7 +38570,7 @@
       <c r="L656" s="31"/>
       <c r="M656" s="29"/>
     </row>
-    <row r="657" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A657" s="29" t="s">
         <v>1538</v>
       </c>
@@ -38596,7 +38605,7 @@
       <c r="L657" s="31"/>
       <c r="M657" s="29"/>
     </row>
-    <row r="658" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A658" s="29" t="s">
         <v>1539</v>
       </c>
@@ -38631,7 +38640,7 @@
       <c r="L658" s="31"/>
       <c r="M658" s="29"/>
     </row>
-    <row r="659" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A659" s="29" t="s">
         <v>1540</v>
       </c>
@@ -38666,7 +38675,7 @@
       <c r="L659" s="31"/>
       <c r="M659" s="29"/>
     </row>
-    <row r="660" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A660" s="29" t="s">
         <v>1541</v>
       </c>
@@ -38701,7 +38710,7 @@
       <c r="L660" s="31"/>
       <c r="M660" s="29"/>
     </row>
-    <row r="661" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A661" s="29" t="s">
         <v>1542</v>
       </c>
@@ -38736,7 +38745,7 @@
       <c r="L661" s="31"/>
       <c r="M661" s="29"/>
     </row>
-    <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A662" s="29" t="s">
         <v>1543</v>
       </c>
@@ -38771,7 +38780,7 @@
       <c r="L662" s="31"/>
       <c r="M662" s="29"/>
     </row>
-    <row r="663" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
         <v>1544</v>
       </c>
@@ -38792,7 +38801,7 @@
       <c r="L663" s="31"/>
       <c r="M663" s="29"/>
     </row>
-    <row r="664" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A664" s="29" t="s">
         <v>1545</v>
       </c>
@@ -38813,7 +38822,7 @@
       <c r="L664" s="31"/>
       <c r="M664" s="29"/>
     </row>
-    <row r="665" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A665" s="29" t="s">
         <v>1546</v>
       </c>
@@ -38834,7 +38843,7 @@
       <c r="L665" s="31"/>
       <c r="M665" s="29"/>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="29" t="s">
         <v>2451</v>
       </c>
@@ -38869,7 +38878,7 @@
       <c r="L666" s="31"/>
       <c r="M666" s="29"/>
     </row>
-    <row r="667" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="29" t="s">
         <v>2452</v>
       </c>
@@ -38904,7 +38913,7 @@
       <c r="L667" s="31"/>
       <c r="M667" s="29"/>
     </row>
-    <row r="668" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A668" s="29" t="s">
         <v>2453</v>
       </c>
@@ -38935,7 +38944,7 @@
       <c r="L668" s="31"/>
       <c r="M668" s="29"/>
     </row>
-    <row r="669" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A669" s="29" t="s">
         <v>2454</v>
       </c>
@@ -38966,7 +38975,7 @@
       <c r="L669" s="31"/>
       <c r="M669" s="29"/>
     </row>
-    <row r="670" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A670" s="29" t="s">
         <v>2455</v>
       </c>
@@ -38997,7 +39006,7 @@
       <c r="L670" s="31"/>
       <c r="M670" s="29"/>
     </row>
-    <row r="671" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A671" s="29" t="s">
         <v>2456</v>
       </c>
@@ -39028,7 +39037,7 @@
       <c r="L671" s="31"/>
       <c r="M671" s="29"/>
     </row>
-    <row r="672" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A672" s="29" t="s">
         <v>2457</v>
       </c>
@@ -39059,7 +39068,7 @@
       <c r="L672" s="31"/>
       <c r="M672" s="29"/>
     </row>
-    <row r="673" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A673" s="29" t="s">
         <v>2458</v>
       </c>
@@ -39090,7 +39099,7 @@
       <c r="L673" s="31"/>
       <c r="M673" s="29"/>
     </row>
-    <row r="674" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A674" s="29" t="s">
         <v>2459</v>
       </c>
@@ -39121,7 +39130,7 @@
       <c r="L674" s="31"/>
       <c r="M674" s="29"/>
     </row>
-    <row r="675" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A675" s="29" t="s">
         <v>2460</v>
       </c>
@@ -39152,7 +39161,7 @@
       <c r="L675" s="31"/>
       <c r="M675" s="29"/>
     </row>
-    <row r="676" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A676" s="29" t="s">
         <v>2461</v>
       </c>
@@ -39183,7 +39192,7 @@
       <c r="L676" s="31"/>
       <c r="M676" s="29"/>
     </row>
-    <row r="677" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A677" s="29" t="s">
         <v>2462</v>
       </c>
@@ -39214,7 +39223,7 @@
       <c r="L677" s="31"/>
       <c r="M677" s="29"/>
     </row>
-    <row r="678" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A678" s="29" t="s">
         <v>2463</v>
       </c>
@@ -39245,7 +39254,7 @@
       <c r="L678" s="31"/>
       <c r="M678" s="29"/>
     </row>
-    <row r="679" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A679" s="29" t="s">
         <v>2464</v>
       </c>
@@ -39276,7 +39285,7 @@
       <c r="L679" s="31"/>
       <c r="M679" s="29"/>
     </row>
-    <row r="680" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A680" s="29" t="s">
         <v>2465</v>
       </c>
@@ -39307,7 +39316,7 @@
       <c r="L680" s="31"/>
       <c r="M680" s="29"/>
     </row>
-    <row r="681" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A681" s="29" t="s">
         <v>2466</v>
       </c>
@@ -39338,7 +39347,7 @@
       <c r="L681" s="31"/>
       <c r="M681" s="29"/>
     </row>
-    <row r="682" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A682" s="29" t="s">
         <v>2467</v>
       </c>
@@ -39369,7 +39378,7 @@
       <c r="L682" s="31"/>
       <c r="M682" s="29"/>
     </row>
-    <row r="683" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A683" s="29" t="s">
         <v>2468</v>
       </c>
@@ -39400,7 +39409,7 @@
       <c r="L683" s="31"/>
       <c r="M683" s="29"/>
     </row>
-    <row r="684" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A684" s="29" t="s">
         <v>2469</v>
       </c>
@@ -39431,7 +39440,7 @@
       <c r="L684" s="31"/>
       <c r="M684" s="29"/>
     </row>
-    <row r="685" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A685" s="29" t="s">
         <v>2470</v>
       </c>
@@ -39462,7 +39471,7 @@
       <c r="L685" s="31"/>
       <c r="M685" s="29"/>
     </row>
-    <row r="686" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A686" s="29" t="s">
         <v>2471</v>
       </c>
@@ -39493,7 +39502,7 @@
       <c r="L686" s="31"/>
       <c r="M686" s="29"/>
     </row>
-    <row r="687" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A687" s="29" t="s">
         <v>2472</v>
       </c>
@@ -39524,7 +39533,7 @@
       <c r="L687" s="31"/>
       <c r="M687" s="29"/>
     </row>
-    <row r="688" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A688" s="29" t="s">
         <v>2473</v>
       </c>
@@ -39555,7 +39564,7 @@
       <c r="L688" s="31"/>
       <c r="M688" s="29"/>
     </row>
-    <row r="689" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A689" s="29" t="s">
         <v>2474</v>
       </c>
@@ -39586,7 +39595,7 @@
       <c r="L689" s="31"/>
       <c r="M689" s="29"/>
     </row>
-    <row r="690" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A690" s="29" t="s">
         <v>2475</v>
       </c>
@@ -39621,7 +39630,7 @@
       <c r="L690" s="31"/>
       <c r="M690" s="29"/>
     </row>
-    <row r="691" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A691" s="29" t="s">
         <v>2476</v>
       </c>
@@ -39656,7 +39665,7 @@
       <c r="L691" s="31"/>
       <c r="M691" s="29"/>
     </row>
-    <row r="692" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A692" s="29" t="s">
         <v>2477</v>
       </c>
@@ -39691,7 +39700,7 @@
       <c r="L692" s="31"/>
       <c r="M692" s="29"/>
     </row>
-    <row r="693" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A693" s="29" t="s">
         <v>2478</v>
       </c>
@@ -39726,7 +39735,7 @@
       <c r="L693" s="31"/>
       <c r="M693" s="29"/>
     </row>
-    <row r="694" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A694" s="29" t="s">
         <v>2479</v>
       </c>
@@ -39761,7 +39770,7 @@
       <c r="L694" s="31"/>
       <c r="M694" s="29"/>
     </row>
-    <row r="695" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A695" s="29" t="s">
         <v>2480</v>
       </c>
@@ -39796,7 +39805,7 @@
       <c r="L695" s="31"/>
       <c r="M695" s="29"/>
     </row>
-    <row r="696" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A696" s="29" t="s">
         <v>2481</v>
       </c>
@@ -39831,7 +39840,7 @@
       <c r="L696" s="31"/>
       <c r="M696" s="29"/>
     </row>
-    <row r="697" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A697" s="29" t="s">
         <v>2482</v>
       </c>
@@ -39866,7 +39875,7 @@
       <c r="L697" s="31"/>
       <c r="M697" s="29"/>
     </row>
-    <row r="698" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
         <v>2483</v>
       </c>
@@ -39901,7 +39910,7 @@
       <c r="L698" s="31"/>
       <c r="M698" s="29"/>
     </row>
-    <row r="699" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
         <v>2484</v>
       </c>
@@ -39936,7 +39945,7 @@
       <c r="L699" s="31"/>
       <c r="M699" s="29"/>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
         <v>1559</v>
       </c>
@@ -39965,7 +39974,7 @@
       <c r="L700" s="31"/>
       <c r="M700" s="29"/>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
         <v>1560</v>
       </c>
@@ -39994,7 +40003,7 @@
       <c r="L701" s="31"/>
       <c r="M701" s="29"/>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
         <v>1561</v>
       </c>
@@ -40023,7 +40032,7 @@
       <c r="L702" s="31"/>
       <c r="M702" s="29"/>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
         <v>1562</v>
       </c>
@@ -40052,7 +40061,7 @@
       <c r="L703" s="31"/>
       <c r="M703" s="29"/>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
         <v>1563</v>
       </c>
@@ -40081,7 +40090,7 @@
       <c r="L704" s="31"/>
       <c r="M704" s="29"/>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
         <v>1564</v>
       </c>
@@ -40110,7 +40119,7 @@
       <c r="L705" s="31"/>
       <c r="M705" s="29"/>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
         <v>1565</v>
       </c>
@@ -40139,7 +40148,7 @@
       <c r="L706" s="31"/>
       <c r="M706" s="29"/>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
         <v>1566</v>
       </c>
@@ -40168,7 +40177,7 @@
       <c r="L707" s="31"/>
       <c r="M707" s="29"/>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
         <v>1569</v>
       </c>
@@ -40197,7 +40206,7 @@
       <c r="L708" s="31"/>
       <c r="M708" s="29"/>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
         <v>1570</v>
       </c>
@@ -40226,7 +40235,7 @@
       <c r="L709" s="31"/>
       <c r="M709" s="29"/>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
         <v>1571</v>
       </c>
@@ -40255,7 +40264,7 @@
       <c r="L710" s="31"/>
       <c r="M710" s="29"/>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
         <v>1572</v>
       </c>
@@ -40284,7 +40293,7 @@
       <c r="L711" s="31"/>
       <c r="M711" s="29"/>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
         <v>1573</v>
       </c>
@@ -40313,7 +40322,7 @@
       <c r="L712" s="31"/>
       <c r="M712" s="29"/>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="29" t="s">
         <v>1574</v>
       </c>
@@ -40342,7 +40351,7 @@
       <c r="L713" s="31"/>
       <c r="M713" s="29"/>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="29" t="s">
         <v>1575</v>
       </c>
@@ -40371,7 +40380,7 @@
       <c r="L714" s="31"/>
       <c r="M714" s="29"/>
     </row>
-    <row r="715" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="29" t="s">
         <v>1576</v>
       </c>
@@ -40400,7 +40409,7 @@
       <c r="L715" s="31"/>
       <c r="M715" s="29"/>
     </row>
-    <row r="716" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A716" s="29" t="s">
         <v>1577</v>
       </c>
@@ -40429,7 +40438,7 @@
       <c r="L716" s="31"/>
       <c r="M716" s="29"/>
     </row>
-    <row r="717" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" s="29" t="s">
         <v>1578</v>
       </c>
@@ -40458,7 +40467,7 @@
       <c r="L717" s="31"/>
       <c r="M717" s="29"/>
     </row>
-    <row r="718" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A718" s="29" t="s">
         <v>1579</v>
       </c>
@@ -40487,7 +40496,7 @@
       <c r="L718" s="31"/>
       <c r="M718" s="29"/>
     </row>
-    <row r="719" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" s="29" t="s">
         <v>1580</v>
       </c>
@@ -40516,7 +40525,7 @@
       <c r="L719" s="31"/>
       <c r="M719" s="29"/>
     </row>
-    <row r="720" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A720" s="29" t="s">
         <v>1581</v>
       </c>
@@ -40545,7 +40554,7 @@
       <c r="L720" s="31"/>
       <c r="M720" s="29"/>
     </row>
-    <row r="721" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" s="29" t="s">
         <v>1582</v>
       </c>
@@ -40574,7 +40583,7 @@
       <c r="L721" s="31"/>
       <c r="M721" s="29"/>
     </row>
-    <row r="722" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A722" s="29" t="s">
         <v>1583</v>
       </c>
@@ -40603,7 +40612,7 @@
       <c r="L722" s="31"/>
       <c r="M722" s="29"/>
     </row>
-    <row r="723" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" s="29" t="s">
         <v>1584</v>
       </c>
@@ -40632,7 +40641,7 @@
       <c r="L723" s="31"/>
       <c r="M723" s="29"/>
     </row>
-    <row r="724" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A724" s="29" t="s">
         <v>2485</v>
       </c>
@@ -40665,7 +40674,7 @@
       <c r="L724" s="31"/>
       <c r="M724" s="29"/>
     </row>
-    <row r="725" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A725" s="29" t="s">
         <v>2486</v>
       </c>
@@ -40698,7 +40707,7 @@
       <c r="L725" s="31"/>
       <c r="M725" s="29"/>
     </row>
-    <row r="726" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A726" s="29" t="s">
         <v>2487</v>
       </c>
@@ -40731,7 +40740,7 @@
       <c r="L726" s="31"/>
       <c r="M726" s="29"/>
     </row>
-    <row r="727" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A727" s="29" t="s">
         <v>2488</v>
       </c>
@@ -40764,7 +40773,7 @@
       <c r="L727" s="31"/>
       <c r="M727" s="29"/>
     </row>
-    <row r="728" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A728" s="29" t="s">
         <v>2489</v>
       </c>
@@ -40797,7 +40806,7 @@
       <c r="L728" s="31"/>
       <c r="M728" s="29"/>
     </row>
-    <row r="729" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A729" s="29" t="s">
         <v>2490</v>
       </c>
@@ -40830,7 +40839,7 @@
       <c r="L729" s="31"/>
       <c r="M729" s="29"/>
     </row>
-    <row r="730" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A730" s="29" t="s">
         <v>2491</v>
       </c>
@@ -40863,7 +40872,7 @@
       <c r="L730" s="31"/>
       <c r="M730" s="29"/>
     </row>
-    <row r="731" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A731" s="29" t="s">
         <v>2492</v>
       </c>
@@ -40896,7 +40905,7 @@
       <c r="L731" s="31"/>
       <c r="M731" s="29"/>
     </row>
-    <row r="732" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A732" s="29" t="s">
         <v>2493</v>
       </c>
@@ -40929,7 +40938,7 @@
       <c r="L732" s="31"/>
       <c r="M732" s="29"/>
     </row>
-    <row r="733" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A733" s="29" t="s">
         <v>2494</v>
       </c>
@@ -40962,7 +40971,7 @@
       <c r="L733" s="31"/>
       <c r="M733" s="29"/>
     </row>
-    <row r="734" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A734" s="29" t="s">
         <v>2495</v>
       </c>
@@ -40995,7 +41004,7 @@
       <c r="L734" s="31"/>
       <c r="M734" s="29"/>
     </row>
-    <row r="735" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A735" s="29" t="s">
         <v>2496</v>
       </c>
@@ -41028,7 +41037,7 @@
       <c r="L735" s="31"/>
       <c r="M735" s="29"/>
     </row>
-    <row r="736" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A736" s="29" t="s">
         <v>2497</v>
       </c>
@@ -41061,7 +41070,7 @@
       <c r="L736" s="31"/>
       <c r="M736" s="29"/>
     </row>
-    <row r="737" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A737" s="29" t="s">
         <v>2498</v>
       </c>
@@ -41094,7 +41103,7 @@
       <c r="L737" s="31"/>
       <c r="M737" s="29"/>
     </row>
-    <row r="738" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A738" s="29" t="s">
         <v>2499</v>
       </c>
@@ -41127,7 +41136,7 @@
       <c r="L738" s="31"/>
       <c r="M738" s="29"/>
     </row>
-    <row r="739" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A739" s="29" t="s">
         <v>2500</v>
       </c>
@@ -41160,7 +41169,7 @@
       <c r="L739" s="31"/>
       <c r="M739" s="29"/>
     </row>
-    <row r="740" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A740" s="29" t="s">
         <v>2501</v>
       </c>
@@ -41193,7 +41202,7 @@
       <c r="L740" s="31"/>
       <c r="M740" s="29"/>
     </row>
-    <row r="741" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A741" s="29" t="s">
         <v>2502</v>
       </c>
@@ -41226,7 +41235,7 @@
       <c r="L741" s="31"/>
       <c r="M741" s="29"/>
     </row>
-    <row r="742" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A742" s="29" t="s">
         <v>2503</v>
       </c>
@@ -41259,7 +41268,7 @@
       <c r="L742" s="31"/>
       <c r="M742" s="29"/>
     </row>
-    <row r="743" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A743" s="29" t="s">
         <v>2504</v>
       </c>
@@ -41292,7 +41301,7 @@
       <c r="L743" s="31"/>
       <c r="M743" s="29"/>
     </row>
-    <row r="744" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A744" s="29" t="s">
         <v>2505</v>
       </c>
@@ -41325,7 +41334,7 @@
       <c r="L744" s="31"/>
       <c r="M744" s="29"/>
     </row>
-    <row r="745" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A745" s="29" t="s">
         <v>2506</v>
       </c>
@@ -41358,7 +41367,7 @@
       <c r="L745" s="31"/>
       <c r="M745" s="29"/>
     </row>
-    <row r="746" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A746" s="29" t="s">
         <v>2507</v>
       </c>
@@ -41391,7 +41400,7 @@
       <c r="L746" s="31"/>
       <c r="M746" s="29"/>
     </row>
-    <row r="747" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A747" s="29" t="s">
         <v>2508</v>
       </c>
@@ -41424,7 +41433,7 @@
       <c r="L747" s="31"/>
       <c r="M747" s="29"/>
     </row>
-    <row r="748" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A748" s="29" t="s">
         <v>2509</v>
       </c>
@@ -41457,7 +41466,7 @@
       <c r="L748" s="31"/>
       <c r="M748" s="29"/>
     </row>
-    <row r="749" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A749" s="29" t="s">
         <v>2510</v>
       </c>
@@ -41490,7 +41499,7 @@
       <c r="L749" s="31"/>
       <c r="M749" s="29"/>
     </row>
-    <row r="750" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A750" s="29" t="s">
         <v>2511</v>
       </c>
@@ -41523,7 +41532,7 @@
       <c r="L750" s="31"/>
       <c r="M750" s="29"/>
     </row>
-    <row r="751" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A751" s="29" t="s">
         <v>2512</v>
       </c>
@@ -41556,7 +41565,7 @@
       <c r="L751" s="31"/>
       <c r="M751" s="29"/>
     </row>
-    <row r="752" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A752" s="29" t="s">
         <v>2513</v>
       </c>
@@ -41589,7 +41598,7 @@
       <c r="L752" s="31"/>
       <c r="M752" s="29"/>
     </row>
-    <row r="753" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A753" s="29" t="s">
         <v>2514</v>
       </c>
@@ -41622,7 +41631,7 @@
       <c r="L753" s="31"/>
       <c r="M753" s="29"/>
     </row>
-    <row r="754" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A754" s="29" t="s">
         <v>2515</v>
       </c>
@@ -41655,7 +41664,7 @@
       <c r="L754" s="31"/>
       <c r="M754" s="29"/>
     </row>
-    <row r="755" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A755" s="29" t="s">
         <v>2516</v>
       </c>
@@ -41688,7 +41697,7 @@
       <c r="L755" s="31"/>
       <c r="M755" s="29"/>
     </row>
-    <row r="756" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A756" s="29" t="s">
         <v>2517</v>
       </c>
@@ -41721,7 +41730,7 @@
       <c r="L756" s="31"/>
       <c r="M756" s="29"/>
     </row>
-    <row r="757" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A757" s="29" t="s">
         <v>2518</v>
       </c>
@@ -41754,7 +41763,7 @@
       <c r="L757" s="31"/>
       <c r="M757" s="29"/>
     </row>
-    <row r="758" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A758" s="29" t="s">
         <v>2519</v>
       </c>
@@ -41787,7 +41796,7 @@
       <c r="L758" s="31"/>
       <c r="M758" s="29"/>
     </row>
-    <row r="759" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A759" s="29" t="s">
         <v>2520</v>
       </c>
@@ -41820,7 +41829,7 @@
       <c r="L759" s="31"/>
       <c r="M759" s="29"/>
     </row>
-    <row r="760" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A760" s="29" t="s">
         <v>2521</v>
       </c>
@@ -41853,7 +41862,7 @@
       <c r="L760" s="31"/>
       <c r="M760" s="29"/>
     </row>
-    <row r="761" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A761" s="29" t="s">
         <v>2522</v>
       </c>
@@ -41886,7 +41895,7 @@
       <c r="L761" s="31"/>
       <c r="M761" s="29"/>
     </row>
-    <row r="762" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A762" s="29" t="s">
         <v>2523</v>
       </c>
@@ -41919,7 +41928,7 @@
       <c r="L762" s="31"/>
       <c r="M762" s="29"/>
     </row>
-    <row r="763" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A763" s="29" t="s">
         <v>2524</v>
       </c>
@@ -41952,7 +41961,7 @@
       <c r="L763" s="31"/>
       <c r="M763" s="29"/>
     </row>
-    <row r="764" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A764" s="29" t="s">
         <v>2525</v>
       </c>
@@ -41985,7 +41994,7 @@
       <c r="L764" s="31"/>
       <c r="M764" s="29"/>
     </row>
-    <row r="765" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A765" s="29" t="s">
         <v>2526</v>
       </c>
@@ -42018,7 +42027,7 @@
       <c r="L765" s="31"/>
       <c r="M765" s="29"/>
     </row>
-    <row r="766" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A766" s="29" t="s">
         <v>2527</v>
       </c>
@@ -42051,7 +42060,7 @@
       <c r="L766" s="31"/>
       <c r="M766" s="29"/>
     </row>
-    <row r="767" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A767" s="29" t="s">
         <v>2528</v>
       </c>
@@ -42084,7 +42093,7 @@
       <c r="L767" s="31"/>
       <c r="M767" s="29"/>
     </row>
-    <row r="768" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A768" s="29" t="s">
         <v>2529</v>
       </c>
@@ -42117,7 +42126,7 @@
       <c r="L768" s="31"/>
       <c r="M768" s="29"/>
     </row>
-    <row r="769" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A769" s="29" t="s">
         <v>2530</v>
       </c>
@@ -42150,7 +42159,7 @@
       <c r="L769" s="31"/>
       <c r="M769" s="29"/>
     </row>
-    <row r="770" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A770" s="29" t="s">
         <v>2531</v>
       </c>
@@ -42183,7 +42192,7 @@
       <c r="L770" s="31"/>
       <c r="M770" s="29"/>
     </row>
-    <row r="771" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A771" s="29" t="s">
         <v>2532</v>
       </c>
@@ -42216,7 +42225,7 @@
       <c r="L771" s="31"/>
       <c r="M771" s="29"/>
     </row>
-    <row r="772" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A772" s="29" t="s">
         <v>2533</v>
       </c>
@@ -42249,7 +42258,7 @@
       <c r="L772" s="31"/>
       <c r="M772" s="29"/>
     </row>
-    <row r="773" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A773" s="29" t="s">
         <v>2534</v>
       </c>
@@ -42282,7 +42291,7 @@
       <c r="L773" s="31"/>
       <c r="M773" s="29"/>
     </row>
-    <row r="774" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A774" s="29" t="s">
         <v>2535</v>
       </c>
@@ -42315,7 +42324,7 @@
       <c r="L774" s="31"/>
       <c r="M774" s="29"/>
     </row>
-    <row r="775" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A775" s="29" t="s">
         <v>2536</v>
       </c>
@@ -42348,7 +42357,7 @@
       <c r="L775" s="31"/>
       <c r="M775" s="29"/>
     </row>
-    <row r="776" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A776" s="29" t="s">
         <v>2537</v>
       </c>
@@ -42381,7 +42390,7 @@
       <c r="L776" s="31"/>
       <c r="M776" s="29"/>
     </row>
-    <row r="777" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A777" s="29" t="s">
         <v>2538</v>
       </c>
@@ -42414,7 +42423,7 @@
       <c r="L777" s="31"/>
       <c r="M777" s="29"/>
     </row>
-    <row r="778" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A778" s="29" t="s">
         <v>2539</v>
       </c>
@@ -42447,7 +42456,7 @@
       <c r="L778" s="31"/>
       <c r="M778" s="29"/>
     </row>
-    <row r="779" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A779" s="29" t="s">
         <v>2540</v>
       </c>
@@ -42480,7 +42489,7 @@
       <c r="L779" s="31"/>
       <c r="M779" s="29"/>
     </row>
-    <row r="780" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A780" s="29" t="s">
         <v>2541</v>
       </c>
@@ -42513,7 +42522,7 @@
       <c r="L780" s="31"/>
       <c r="M780" s="29"/>
     </row>
-    <row r="781" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A781" s="29" t="s">
         <v>2542</v>
       </c>
@@ -42546,7 +42555,7 @@
       <c r="L781" s="31"/>
       <c r="M781" s="29"/>
     </row>
-    <row r="782" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A782" s="29" t="s">
         <v>2543</v>
       </c>
@@ -42579,7 +42588,7 @@
       <c r="L782" s="31"/>
       <c r="M782" s="29"/>
     </row>
-    <row r="783" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A783" s="29" t="s">
         <v>2544</v>
       </c>
@@ -42612,7 +42621,7 @@
       <c r="L783" s="31"/>
       <c r="M783" s="29"/>
     </row>
-    <row r="784" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A784" s="29" t="s">
         <v>2545</v>
       </c>
@@ -42645,7 +42654,7 @@
       <c r="L784" s="31"/>
       <c r="M784" s="29"/>
     </row>
-    <row r="785" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A785" s="29" t="s">
         <v>2546</v>
       </c>
@@ -42678,7 +42687,7 @@
       <c r="L785" s="31"/>
       <c r="M785" s="29"/>
     </row>
-    <row r="786" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A786" s="29" t="s">
         <v>2547</v>
       </c>
@@ -42711,7 +42720,7 @@
       <c r="L786" s="31"/>
       <c r="M786" s="29"/>
     </row>
-    <row r="787" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A787" s="29" t="s">
         <v>2548</v>
       </c>
@@ -42744,7 +42753,7 @@
       <c r="L787" s="31"/>
       <c r="M787" s="29"/>
     </row>
-    <row r="788" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A788" s="29" t="s">
         <v>2549</v>
       </c>
@@ -42777,7 +42786,7 @@
       <c r="L788" s="31"/>
       <c r="M788" s="29"/>
     </row>
-    <row r="789" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A789" s="29" t="s">
         <v>2550</v>
       </c>
@@ -42810,7 +42819,7 @@
       <c r="L789" s="31"/>
       <c r="M789" s="29"/>
     </row>
-    <row r="790" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" s="29" t="s">
         <v>2551</v>
       </c>
@@ -42847,7 +42856,7 @@
       <c r="L790" s="31"/>
       <c r="M790" s="29"/>
     </row>
-    <row r="791" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" s="29" t="s">
         <v>2552</v>
       </c>
@@ -42884,7 +42893,7 @@
       <c r="L791" s="31"/>
       <c r="M791" s="29"/>
     </row>
-    <row r="792" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" s="29" t="s">
         <v>2553</v>
       </c>
@@ -42921,7 +42930,7 @@
       <c r="L792" s="31"/>
       <c r="M792" s="29"/>
     </row>
-    <row r="793" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" s="29" t="s">
         <v>2554</v>
       </c>
@@ -42958,7 +42967,7 @@
       <c r="L793" s="31"/>
       <c r="M793" s="29"/>
     </row>
-    <row r="794" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="29" t="s">
         <v>2555</v>
       </c>
@@ -42995,7 +43004,7 @@
       <c r="L794" s="31"/>
       <c r="M794" s="29"/>
     </row>
-    <row r="795" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" s="29" t="s">
         <v>2556</v>
       </c>
@@ -43032,7 +43041,7 @@
       <c r="L795" s="31"/>
       <c r="M795" s="29"/>
     </row>
-    <row r="796" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="29" t="s">
         <v>2557</v>
       </c>
@@ -43069,7 +43078,7 @@
       <c r="L796" s="31"/>
       <c r="M796" s="29"/>
     </row>
-    <row r="797" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="29" t="s">
         <v>2558</v>
       </c>
@@ -43106,7 +43115,7 @@
       <c r="L797" s="31"/>
       <c r="M797" s="29"/>
     </row>
-    <row r="798" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A798" s="29" t="s">
         <v>1858</v>
       </c>
@@ -43139,7 +43148,7 @@
       <c r="L798" s="31"/>
       <c r="M798" s="29"/>
     </row>
-    <row r="799" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A799" s="29" t="s">
         <v>1859</v>
       </c>
@@ -43172,7 +43181,7 @@
       <c r="L799" s="31"/>
       <c r="M799" s="29"/>
     </row>
-    <row r="800" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" s="29" t="s">
         <v>1664</v>
       </c>
@@ -43203,7 +43212,7 @@
       <c r="L800" s="31"/>
       <c r="M800" s="29"/>
     </row>
-    <row r="801" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
         <v>1665</v>
       </c>
@@ -43234,7 +43243,7 @@
       <c r="L801" s="31"/>
       <c r="M801" s="29"/>
     </row>
-    <row r="802" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
         <v>1666</v>
       </c>
@@ -43265,7 +43274,7 @@
       <c r="L802" s="31"/>
       <c r="M802" s="29"/>
     </row>
-    <row r="803" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
         <v>1667</v>
       </c>
@@ -43296,7 +43305,7 @@
       <c r="L803" s="31"/>
       <c r="M803" s="29"/>
     </row>
-    <row r="804" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
         <v>1668</v>
       </c>
@@ -43327,7 +43336,7 @@
       <c r="L804" s="31"/>
       <c r="M804" s="29"/>
     </row>
-    <row r="805" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
         <v>1669</v>
       </c>
@@ -43358,7 +43367,7 @@
       <c r="L805" s="31"/>
       <c r="M805" s="29"/>
     </row>
-    <row r="806" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" s="29" t="s">
         <v>1670</v>
       </c>
@@ -43389,7 +43398,7 @@
       <c r="L806" s="31"/>
       <c r="M806" s="29"/>
     </row>
-    <row r="807" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" s="29" t="s">
         <v>1671</v>
       </c>
@@ -43420,7 +43429,7 @@
       <c r="L807" s="31"/>
       <c r="M807" s="29"/>
     </row>
-    <row r="808" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
         <v>1702</v>
       </c>
@@ -43449,7 +43458,7 @@
       <c r="L808" s="31"/>
       <c r="M808" s="29"/>
     </row>
-    <row r="809" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
         <v>1703</v>
       </c>
@@ -43478,7 +43487,7 @@
       <c r="L809" s="31"/>
       <c r="M809" s="29"/>
     </row>
-    <row r="810" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
         <v>1704</v>
       </c>
@@ -43507,7 +43516,7 @@
       <c r="L810" s="31"/>
       <c r="M810" s="29"/>
     </row>
-    <row r="811" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
         <v>1705</v>
       </c>
@@ -43536,7 +43545,7 @@
       <c r="L811" s="31"/>
       <c r="M811" s="29"/>
     </row>
-    <row r="812" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
         <v>1706</v>
       </c>
@@ -43565,7 +43574,7 @@
       <c r="L812" s="31"/>
       <c r="M812" s="29"/>
     </row>
-    <row r="813" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
         <v>1769</v>
       </c>
@@ -43594,7 +43603,7 @@
       <c r="L813" s="31"/>
       <c r="M813" s="29"/>
     </row>
-    <row r="814" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" s="29" t="s">
         <v>1770</v>
       </c>
@@ -43623,7 +43632,7 @@
       <c r="L814" s="31"/>
       <c r="M814" s="29"/>
     </row>
-    <row r="815" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" s="29" t="s">
         <v>1771</v>
       </c>
@@ -43654,7 +43663,7 @@
       <c r="L815" s="31"/>
       <c r="M815" s="29"/>
     </row>
-    <row r="816" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" s="29" t="s">
         <v>1772</v>
       </c>
@@ -43685,7 +43694,7 @@
       <c r="L816" s="31"/>
       <c r="M816" s="29"/>
     </row>
-    <row r="817" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
         <v>1773</v>
       </c>
@@ -43716,7 +43725,7 @@
       <c r="L817" s="31"/>
       <c r="M817" s="29"/>
     </row>
-    <row r="818" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
         <v>1781</v>
       </c>
@@ -43747,7 +43756,7 @@
       <c r="L818" s="31"/>
       <c r="M818" s="29"/>
     </row>
-    <row r="819" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A819" s="29" t="s">
         <v>1782</v>
       </c>
@@ -43778,7 +43787,7 @@
       <c r="L819" s="31"/>
       <c r="M819" s="29"/>
     </row>
-    <row r="820" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" s="29" t="s">
         <v>1783</v>
       </c>
@@ -43809,7 +43818,7 @@
       <c r="L820" s="31"/>
       <c r="M820" s="29"/>
     </row>
-    <row r="821" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" s="29" t="s">
         <v>1784</v>
       </c>
@@ -43840,7 +43849,7 @@
       <c r="L821" s="31"/>
       <c r="M821" s="29"/>
     </row>
-    <row r="822" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" s="29" t="s">
         <v>1785</v>
       </c>
@@ -43871,7 +43880,7 @@
       <c r="L822" s="31"/>
       <c r="M822" s="29"/>
     </row>
-    <row r="823" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A823" s="29" t="s">
         <v>1805</v>
       </c>
@@ -43902,7 +43911,7 @@
       <c r="L823" s="31"/>
       <c r="M823" s="29"/>
     </row>
-    <row r="824" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
         <v>1806</v>
       </c>
@@ -43933,7 +43942,7 @@
       <c r="L824" s="31"/>
       <c r="M824" s="29"/>
     </row>
-    <row r="825" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
         <v>1810</v>
       </c>
@@ -43964,7 +43973,7 @@
       <c r="L825" s="31"/>
       <c r="M825" s="29"/>
     </row>
-    <row r="826" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
         <v>1811</v>
       </c>
@@ -43995,7 +44004,7 @@
       <c r="L826" s="31"/>
       <c r="M826" s="29"/>
     </row>
-    <row r="827" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
         <v>1819</v>
       </c>
@@ -44026,7 +44035,7 @@
       <c r="L827" s="31"/>
       <c r="M827" s="29"/>
     </row>
-    <row r="828" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
         <v>1820</v>
       </c>
@@ -44057,7 +44066,7 @@
       <c r="L828" s="31"/>
       <c r="M828" s="29"/>
     </row>
-    <row r="829" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
         <v>1826</v>
       </c>
@@ -44088,7 +44097,7 @@
       <c r="L829" s="31"/>
       <c r="M829" s="29"/>
     </row>
-    <row r="830" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" s="29" t="s">
         <v>1827</v>
       </c>
@@ -44119,7 +44128,7 @@
       <c r="L830" s="31"/>
       <c r="M830" s="29"/>
     </row>
-    <row r="831" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" s="29" t="s">
         <v>1830</v>
       </c>
@@ -44148,7 +44157,7 @@
       <c r="L831" s="31"/>
       <c r="M831" s="29"/>
     </row>
-    <row r="832" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" s="29" t="s">
         <v>1831</v>
       </c>
@@ -44177,7 +44186,7 @@
       <c r="L832" s="31"/>
       <c r="M832" s="29"/>
     </row>
-    <row r="833" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" s="29" t="s">
         <v>2559</v>
       </c>
@@ -44210,7 +44219,7 @@
       <c r="L833" s="31"/>
       <c r="M833" s="29"/>
     </row>
-    <row r="834" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" s="29" t="s">
         <v>2560</v>
       </c>
@@ -44243,7 +44252,7 @@
       <c r="L834" s="31"/>
       <c r="M834" s="29"/>
     </row>
-    <row r="835" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" s="29" t="s">
         <v>2561</v>
       </c>
@@ -44276,7 +44285,7 @@
       <c r="L835" s="31"/>
       <c r="M835" s="29"/>
     </row>
-    <row r="836" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" s="29" t="s">
         <v>2562</v>
       </c>
@@ -44309,7 +44318,7 @@
       <c r="L836" s="31"/>
       <c r="M836" s="29"/>
     </row>
-    <row r="837" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" s="29" t="s">
         <v>2563</v>
       </c>
@@ -44342,7 +44351,7 @@
       <c r="L837" s="31"/>
       <c r="M837" s="29"/>
     </row>
-    <row r="838" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A838" s="29" t="s">
         <v>2564</v>
       </c>
@@ -44375,7 +44384,7 @@
       <c r="L838" s="31"/>
       <c r="M838" s="29"/>
     </row>
-    <row r="839" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" s="29" t="s">
         <v>2565</v>
       </c>
@@ -44408,7 +44417,7 @@
       <c r="L839" s="31"/>
       <c r="M839" s="29"/>
     </row>
-    <row r="840" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" s="29" t="s">
         <v>2566</v>
       </c>
@@ -44441,7 +44450,7 @@
       <c r="L840" s="31"/>
       <c r="M840" s="29"/>
     </row>
-    <row r="841" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" s="29" t="s">
         <v>2567</v>
       </c>
@@ -44474,7 +44483,7 @@
       <c r="L841" s="31"/>
       <c r="M841" s="29"/>
     </row>
-    <row r="842" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A842" s="29" t="s">
         <v>2568</v>
       </c>
@@ -44507,7 +44516,7 @@
       <c r="L842" s="31"/>
       <c r="M842" s="29"/>
     </row>
-    <row r="843" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A843" s="29" t="s">
         <v>2569</v>
       </c>
@@ -44540,7 +44549,7 @@
       <c r="L843" s="31"/>
       <c r="M843" s="29"/>
     </row>
-    <row r="844" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" s="29" t="s">
         <v>2570</v>
       </c>
@@ -44573,7 +44582,7 @@
       <c r="L844" s="31"/>
       <c r="M844" s="29"/>
     </row>
-    <row r="845" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" s="29" t="s">
         <v>2571</v>
       </c>
@@ -44606,7 +44615,7 @@
       <c r="L845" s="31"/>
       <c r="M845" s="29"/>
     </row>
-    <row r="846" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" s="29" t="s">
         <v>2572</v>
       </c>
@@ -44639,7 +44648,7 @@
       <c r="L846" s="31"/>
       <c r="M846" s="29"/>
     </row>
-    <row r="847" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A847" s="29" t="s">
         <v>2573</v>
       </c>
@@ -44672,7 +44681,7 @@
       <c r="L847" s="31"/>
       <c r="M847" s="29"/>
     </row>
-    <row r="848" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" s="29" t="s">
         <v>2574</v>
       </c>
@@ -44705,7 +44714,7 @@
       <c r="L848" s="31"/>
       <c r="M848" s="29"/>
     </row>
-    <row r="849" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A849" s="29" t="s">
         <v>2575</v>
       </c>
@@ -44738,7 +44747,7 @@
       <c r="L849" s="31"/>
       <c r="M849" s="29"/>
     </row>
-    <row r="850" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A850" s="29" t="s">
         <v>2576</v>
       </c>
@@ -44771,7 +44780,7 @@
       <c r="L850" s="31"/>
       <c r="M850" s="29"/>
     </row>
-    <row r="851" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" s="29" t="s">
         <v>2577</v>
       </c>
@@ -44804,7 +44813,7 @@
       <c r="L851" s="31"/>
       <c r="M851" s="29"/>
     </row>
-    <row r="852" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A852" s="29" t="s">
         <v>2578</v>
       </c>
@@ -44837,7 +44846,7 @@
       <c r="L852" s="31"/>
       <c r="M852" s="29"/>
     </row>
-    <row r="853" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" s="29" t="s">
         <v>1978</v>
       </c>
@@ -44870,7 +44879,7 @@
       <c r="L853" s="31"/>
       <c r="M853" s="29"/>
     </row>
-    <row r="854" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A854" s="29" t="s">
         <v>1979</v>
       </c>
@@ -44903,7 +44912,7 @@
       <c r="L854" s="31"/>
       <c r="M854" s="29"/>
     </row>
-    <row r="855" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A855" s="29" t="s">
         <v>1884</v>
       </c>
@@ -44940,7 +44949,7 @@
       <c r="L855" s="31"/>
       <c r="M855" s="29"/>
     </row>
-    <row r="856" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" s="29" t="s">
         <v>1888</v>
       </c>
@@ -44965,7 +44974,7 @@
       <c r="L856" s="31"/>
       <c r="M856" s="29"/>
     </row>
-    <row r="857" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A857" s="29" t="s">
         <v>1887</v>
       </c>
@@ -44998,7 +45007,7 @@
       <c r="L857" s="31"/>
       <c r="M857" s="29"/>
     </row>
-    <row r="858" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" s="29" t="s">
         <v>1894</v>
       </c>
@@ -45031,7 +45040,7 @@
       <c r="L858" s="31"/>
       <c r="M858" s="29"/>
     </row>
-    <row r="859" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A859" s="29" t="s">
         <v>1895</v>
       </c>
@@ -45064,7 +45073,7 @@
       <c r="L859" s="31"/>
       <c r="M859" s="29"/>
     </row>
-    <row r="860" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A860" s="29" t="s">
         <v>1899</v>
       </c>
@@ -45097,7 +45106,7 @@
       <c r="L860" s="31"/>
       <c r="M860" s="29"/>
     </row>
-    <row r="861" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>2267</v>
       </c>
@@ -45128,7 +45137,7 @@
       <c r="L861" s="31"/>
       <c r="M861" s="29"/>
     </row>
-    <row r="862" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A862" s="29" t="s">
         <v>2288</v>
       </c>
@@ -45159,7 +45168,7 @@
       <c r="L862" s="31"/>
       <c r="M862" s="29"/>
     </row>
-    <row r="863" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A863" s="80" t="s">
         <v>2296</v>
       </c>
@@ -45190,7 +45199,7 @@
       <c r="L863" s="31"/>
       <c r="M863" s="29"/>
     </row>
-    <row r="864" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" s="29" t="s">
         <v>2291</v>
       </c>
@@ -45221,7 +45230,7 @@
       <c r="L864" s="31"/>
       <c r="M864" s="29"/>
     </row>
-    <row r="865" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A865" s="29" t="s">
         <v>1923</v>
       </c>
@@ -45256,7 +45265,7 @@
       <c r="L865" s="31"/>
       <c r="M865" s="29"/>
     </row>
-    <row r="866" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A866" s="29" t="s">
         <v>1917</v>
       </c>
@@ -45291,7 +45300,7 @@
       <c r="L866" s="31"/>
       <c r="M866" s="29"/>
     </row>
-    <row r="867" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A867" s="29" t="s">
         <v>1924</v>
       </c>
@@ -45328,7 +45337,7 @@
       <c r="L867" s="31"/>
       <c r="M867" s="29"/>
     </row>
-    <row r="868" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A868" s="29" t="s">
         <v>1925</v>
       </c>
@@ -45359,7 +45368,7 @@
       <c r="L868" s="31"/>
       <c r="M868" s="29"/>
     </row>
-    <row r="869" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A869" s="29" t="s">
         <v>1926</v>
       </c>
@@ -45394,7 +45403,7 @@
       <c r="L869" s="31"/>
       <c r="M869" s="29"/>
     </row>
-    <row r="870" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A870" s="29" t="s">
         <v>1927</v>
       </c>
@@ -45429,7 +45438,7 @@
       <c r="L870" s="31"/>
       <c r="M870" s="29"/>
     </row>
-    <row r="871" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A871" s="29" t="s">
         <v>1928</v>
       </c>
@@ -45462,7 +45471,7 @@
       <c r="L871" s="31"/>
       <c r="M871" s="29"/>
     </row>
-    <row r="872" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A872" s="29" t="s">
         <v>1929</v>
       </c>
@@ -45497,7 +45506,7 @@
       <c r="L872" s="31"/>
       <c r="M872" s="29"/>
     </row>
-    <row r="873" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A873" s="29" t="s">
         <v>1930</v>
       </c>
@@ -45526,7 +45535,7 @@
       <c r="L873" s="31"/>
       <c r="M873" s="29"/>
     </row>
-    <row r="874" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A874" s="29" t="s">
         <v>1931</v>
       </c>
@@ -45555,7 +45564,7 @@
       <c r="L874" s="31"/>
       <c r="M874" s="29"/>
     </row>
-    <row r="875" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A875" s="29" t="s">
         <v>1932</v>
       </c>
@@ -45592,7 +45601,7 @@
       <c r="L875" s="31"/>
       <c r="M875" s="29"/>
     </row>
-    <row r="876" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A876" s="29" t="s">
         <v>1933</v>
       </c>
@@ -45627,7 +45636,7 @@
       <c r="L876" s="31"/>
       <c r="M876" s="29"/>
     </row>
-    <row r="877" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A877" s="29" t="s">
         <v>2253</v>
       </c>
@@ -45660,7 +45669,7 @@
       <c r="L877" s="31"/>
       <c r="M877" s="29"/>
     </row>
-    <row r="878" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A878" s="29" t="s">
         <v>1975</v>
       </c>
@@ -45695,7 +45704,7 @@
       <c r="L878" s="31"/>
       <c r="M878" s="29"/>
     </row>
-    <row r="879" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A879" s="29" t="s">
         <v>1980</v>
       </c>
@@ -45730,7 +45739,7 @@
       <c r="L879" s="31"/>
       <c r="M879" s="29"/>
     </row>
-    <row r="880" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A880" s="29" t="s">
         <v>2252</v>
       </c>
@@ -45765,7 +45774,7 @@
       <c r="L880" s="31"/>
       <c r="M880" s="29"/>
     </row>
-    <row r="881" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A881" s="29" t="s">
         <v>2251</v>
       </c>
@@ -45800,7 +45809,7 @@
       <c r="L881" s="31"/>
       <c r="M881" s="29"/>
     </row>
-    <row r="882" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A882" s="29" t="s">
         <v>2250</v>
       </c>
@@ -45833,7 +45842,7 @@
       <c r="L882" s="31"/>
       <c r="M882" s="29"/>
     </row>
-    <row r="883" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A883" s="29" t="s">
         <v>1907</v>
       </c>
@@ -45866,7 +45875,7 @@
       <c r="L883" s="31"/>
       <c r="M883" s="29"/>
     </row>
-    <row r="884" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A884" s="29" t="s">
         <v>1908</v>
       </c>
@@ -45893,7 +45902,7 @@
       <c r="L884" s="31"/>
       <c r="M884" s="29"/>
     </row>
-    <row r="885" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A885" s="29" t="s">
         <v>1909</v>
       </c>
@@ -45928,7 +45937,7 @@
       <c r="L885" s="31"/>
       <c r="M885" s="29"/>
     </row>
-    <row r="886" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A886" s="29" t="s">
         <v>2268</v>
       </c>
@@ -45959,7 +45968,7 @@
       <c r="L886" s="31"/>
       <c r="M886" s="29"/>
     </row>
-    <row r="887" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A887" s="29" t="s">
         <v>2282</v>
       </c>
@@ -45994,7 +46003,7 @@
       <c r="L887" s="31"/>
       <c r="M887" s="29"/>
     </row>
-    <row r="888" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A888" s="29" t="s">
         <v>2283</v>
       </c>
@@ -46029,7 +46038,7 @@
       <c r="L888" s="31"/>
       <c r="M888" s="29"/>
     </row>
-    <row r="889" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A889" s="29" t="s">
         <v>2285</v>
       </c>
@@ -46064,7 +46073,7 @@
       <c r="L889" s="31"/>
       <c r="M889" s="29"/>
     </row>
-    <row r="890" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
         <v>2295</v>
       </c>
@@ -46101,7 +46110,7 @@
       <c r="L890" s="31"/>
       <c r="M890" s="29"/>
     </row>
-    <row r="891" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A891" s="29" t="s">
         <v>2330</v>
       </c>
@@ -46136,7 +46145,7 @@
       <c r="L891" s="31"/>
       <c r="M891" s="29"/>
     </row>
-    <row r="892" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A892" s="29" t="s">
         <v>2331</v>
       </c>
@@ -46171,7 +46180,7 @@
       <c r="L892" s="31"/>
       <c r="M892" s="29"/>
     </row>
-    <row r="893" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A893" s="29" t="s">
         <v>2332</v>
       </c>
@@ -46235,13 +46244,13 @@
         <v>72</v>
       </c>
       <c r="J894" s="83" t="s">
-        <v>1095</v>
+        <v>2589</v>
       </c>
       <c r="K894" s="29"/>
       <c r="L894" s="31"/>
       <c r="M894" s="29"/>
     </row>
-    <row r="895" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A895" s="29" t="s">
         <v>2334</v>
       </c>
@@ -46276,7 +46285,7 @@
       <c r="L895" s="31"/>
       <c r="M895" s="29"/>
     </row>
-    <row r="896" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A896" s="29" t="s">
         <v>2335</v>
       </c>
@@ -46311,7 +46320,7 @@
       <c r="L896" s="31"/>
       <c r="M896" s="29"/>
     </row>
-    <row r="897" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A897" s="29" t="s">
         <v>2336</v>
       </c>
@@ -46346,7 +46355,7 @@
       <c r="L897" s="31"/>
       <c r="M897" s="29"/>
     </row>
-    <row r="898" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A898" s="29" t="s">
         <v>2337</v>
       </c>
@@ -46381,7 +46390,7 @@
       <c r="L898" s="31"/>
       <c r="M898" s="29"/>
     </row>
-    <row r="899" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A899" s="29" t="s">
         <v>2338</v>
       </c>
@@ -46416,7 +46425,7 @@
       <c r="L899" s="31"/>
       <c r="M899" s="29"/>
     </row>
-    <row r="900" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A900" s="29" t="s">
         <v>2339</v>
       </c>
@@ -46451,7 +46460,7 @@
       <c r="L900" s="31"/>
       <c r="M900" s="29"/>
     </row>
-    <row r="901" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A901" s="29" t="s">
         <v>2340</v>
       </c>
@@ -46486,7 +46495,7 @@
       <c r="L901" s="31"/>
       <c r="M901" s="29"/>
     </row>
-    <row r="902" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A902" s="29" t="s">
         <v>2341</v>
       </c>
@@ -46521,7 +46530,7 @@
       <c r="L902" s="31"/>
       <c r="M902" s="29"/>
     </row>
-    <row r="903" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A903" s="29" t="s">
         <v>2342</v>
       </c>
@@ -46556,7 +46565,7 @@
       <c r="L903" s="31"/>
       <c r="M903" s="29"/>
     </row>
-    <row r="904" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A904" s="29" t="s">
         <v>2343</v>
       </c>
@@ -46591,7 +46600,7 @@
       <c r="L904" s="31"/>
       <c r="M904" s="29"/>
     </row>
-    <row r="905" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A905" s="29" t="s">
         <v>2344</v>
       </c>
@@ -46626,7 +46635,7 @@
       <c r="L905" s="31"/>
       <c r="M905" s="29"/>
     </row>
-    <row r="906" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A906" s="29" t="s">
         <v>2345</v>
       </c>
@@ -46661,7 +46670,7 @@
       <c r="L906" s="31"/>
       <c r="M906" s="29"/>
     </row>
-    <row r="907" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A907" s="29" t="s">
         <v>2346</v>
       </c>
@@ -46696,7 +46705,7 @@
       <c r="L907" s="31"/>
       <c r="M907" s="29"/>
     </row>
-    <row r="908" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A908" s="29" t="s">
         <v>2347</v>
       </c>
@@ -46731,7 +46740,7 @@
       <c r="L908" s="31"/>
       <c r="M908" s="29"/>
     </row>
-    <row r="909" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A909" s="29" t="s">
         <v>2348</v>
       </c>
@@ -46766,7 +46775,7 @@
       <c r="L909" s="31"/>
       <c r="M909" s="29"/>
     </row>
-    <row r="910" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A910" s="29" t="s">
         <v>2349</v>
       </c>
@@ -46801,7 +46810,7 @@
       <c r="L910" s="31"/>
       <c r="M910" s="29"/>
     </row>
-    <row r="911" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A911" s="29" t="s">
         <v>2350</v>
       </c>
@@ -46836,7 +46845,7 @@
       <c r="L911" s="31"/>
       <c r="M911" s="29"/>
     </row>
-    <row r="912" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A912" s="29" t="s">
         <v>2351</v>
       </c>
@@ -46871,7 +46880,7 @@
       <c r="L912" s="31"/>
       <c r="M912" s="29"/>
     </row>
-    <row r="913" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A913" s="29" t="s">
         <v>2352</v>
       </c>
@@ -46906,7 +46915,7 @@
       <c r="L913" s="31"/>
       <c r="M913" s="29"/>
     </row>
-    <row r="914" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A914" s="29" t="s">
         <v>2353</v>
       </c>
@@ -46941,7 +46950,7 @@
       <c r="L914" s="31"/>
       <c r="M914" s="29"/>
     </row>
-    <row r="915" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A915" s="29" t="s">
         <v>2354</v>
       </c>
@@ -46976,7 +46985,7 @@
       <c r="L915" s="31"/>
       <c r="M915" s="29"/>
     </row>
-    <row r="916" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A916" s="29" t="s">
         <v>2355</v>
       </c>
@@ -47011,7 +47020,7 @@
       <c r="L916" s="31"/>
       <c r="M916" s="29"/>
     </row>
-    <row r="917" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A917" s="29" t="s">
         <v>2356</v>
       </c>
@@ -47046,7 +47055,7 @@
       <c r="L917" s="31"/>
       <c r="M917" s="29"/>
     </row>
-    <row r="918" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A918" s="29" t="s">
         <v>2357</v>
       </c>
@@ -47081,7 +47090,7 @@
       <c r="L918" s="31"/>
       <c r="M918" s="29"/>
     </row>
-    <row r="919" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A919" s="29" t="s">
         <v>2358</v>
       </c>
@@ -47116,7 +47125,7 @@
       <c r="L919" s="31"/>
       <c r="M919" s="29"/>
     </row>
-    <row r="920" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A920" s="29" t="s">
         <v>2359</v>
       </c>
@@ -47151,7 +47160,7 @@
       <c r="L920" s="31"/>
       <c r="M920" s="29"/>
     </row>
-    <row r="921" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A921" s="29" t="s">
         <v>2360</v>
       </c>
@@ -47186,7 +47195,7 @@
       <c r="L921" s="31"/>
       <c r="M921" s="29"/>
     </row>
-    <row r="922" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A922" s="29" t="s">
         <v>2361</v>
       </c>
@@ -47221,7 +47230,7 @@
       <c r="L922" s="31"/>
       <c r="M922" s="29"/>
     </row>
-    <row r="923" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A923" s="29" t="s">
         <v>2362</v>
       </c>
@@ -47256,7 +47265,7 @@
       <c r="L923" s="31"/>
       <c r="M923" s="29"/>
     </row>
-    <row r="924" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A924" s="29" t="s">
         <v>2363</v>
       </c>
@@ -47291,7 +47300,7 @@
       <c r="L924" s="31"/>
       <c r="M924" s="29"/>
     </row>
-    <row r="925" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A925" s="29" t="s">
         <v>2364</v>
       </c>
@@ -47326,7 +47335,7 @@
       <c r="L925" s="31"/>
       <c r="M925" s="29"/>
     </row>
-    <row r="926" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A926" s="29" t="s">
         <v>2365</v>
       </c>
@@ -47361,7 +47370,7 @@
       <c r="L926" s="31"/>
       <c r="M926" s="29"/>
     </row>
-    <row r="927" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A927" s="29" t="s">
         <v>2366</v>
       </c>
@@ -47396,7 +47405,7 @@
       <c r="L927" s="31"/>
       <c r="M927" s="29"/>
     </row>
-    <row r="928" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A928" s="29" t="s">
         <v>2579</v>
       </c>
@@ -47431,7 +47440,7 @@
       <c r="L928" s="31"/>
       <c r="M928" s="29"/>
     </row>
-    <row r="929" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A929" s="29" t="s">
         <v>2580</v>
       </c>
@@ -47466,7 +47475,7 @@
       <c r="L929" s="31"/>
       <c r="M929" s="29"/>
     </row>
-    <row r="930" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A930" s="29" t="s">
         <v>2581</v>
       </c>
@@ -47501,7 +47510,7 @@
       <c r="L930" s="31"/>
       <c r="M930" s="29"/>
     </row>
-    <row r="931" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A931" s="29" t="s">
         <v>2371</v>
       </c>
@@ -47536,7 +47545,7 @@
       <c r="L931" s="31"/>
       <c r="M931" s="29"/>
     </row>
-    <row r="932" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A932" s="29" t="s">
         <v>2379</v>
       </c>
@@ -47561,7 +47570,7 @@
       <c r="L932" s="31"/>
       <c r="M932" s="29"/>
     </row>
-    <row r="933" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A933" s="29" t="s">
         <v>2381</v>
       </c>
@@ -47586,7 +47595,7 @@
       <c r="L933" s="31"/>
       <c r="M933" s="29"/>
     </row>
-    <row r="934" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A934" s="29" t="s">
         <v>2384</v>
       </c>
@@ -47613,7 +47622,7 @@
       <c r="L934" s="31"/>
       <c r="M934" s="29"/>
     </row>
-    <row r="935" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A935" s="29" t="s">
         <v>2387</v>
       </c>
@@ -47640,7 +47649,7 @@
       <c r="L935" s="31"/>
       <c r="M935" s="29"/>
     </row>
-    <row r="936" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A936" s="29" t="s">
         <v>2390</v>
       </c>
@@ -47665,7 +47674,7 @@
       <c r="L936" s="31"/>
       <c r="M936" s="29"/>
     </row>
-    <row r="937" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A937" s="29" t="s">
         <v>2394</v>
       </c>
@@ -47690,7 +47699,7 @@
       <c r="L937" s="31"/>
       <c r="M937" s="29"/>
     </row>
-    <row r="938" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A938" s="29" t="s">
         <v>2395</v>
       </c>
@@ -47715,7 +47724,7 @@
       <c r="L938" s="31"/>
       <c r="M938" s="29"/>
     </row>
-    <row r="939" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A939" s="29" t="s">
         <v>2396</v>
       </c>
@@ -47740,7 +47749,7 @@
       <c r="L939" s="31"/>
       <c r="M939" s="29"/>
     </row>
-    <row r="940" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A940" s="29" t="s">
         <v>2402</v>
       </c>
@@ -47767,7 +47776,7 @@
       <c r="L940" s="31"/>
       <c r="M940" s="29"/>
     </row>
-    <row r="941" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A941" s="29" t="s">
         <v>2403</v>
       </c>
@@ -47792,7 +47801,7 @@
       <c r="L941" s="31"/>
       <c r="M941" s="29"/>
     </row>
-    <row r="942" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A942" s="29" t="s">
         <v>2405</v>
       </c>
@@ -47817,7 +47826,7 @@
       <c r="L942" s="31"/>
       <c r="M942" s="29"/>
     </row>
-    <row r="943" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A943" s="29" t="s">
         <v>2406</v>
       </c>
@@ -47842,7 +47851,7 @@
       <c r="L943" s="31"/>
       <c r="M943" s="29"/>
     </row>
-    <row r="944" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A944" s="29" t="s">
         <v>2407</v>
       </c>
@@ -47867,7 +47876,7 @@
       <c r="L944" s="31"/>
       <c r="M944" s="29"/>
     </row>
-    <row r="945" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A945" s="29" t="s">
         <v>2408</v>
       </c>
@@ -47892,7 +47901,7 @@
       <c r="L945" s="31"/>
       <c r="M945" s="29"/>
     </row>
-    <row r="946" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A946" s="29" t="s">
         <v>2410</v>
       </c>
@@ -47917,7 +47926,7 @@
       <c r="L946" s="31"/>
       <c r="M946" s="29"/>
     </row>
-    <row r="947" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A947" t="s">
         <v>2378</v>
       </c>
@@ -47944,7 +47953,7 @@
       <c r="L947" s="31"/>
       <c r="M947" s="29"/>
     </row>
-    <row r="948" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A948" s="29" t="s">
         <v>2583</v>
       </c>
@@ -47977,7 +47986,7 @@
       <c r="L948" s="31"/>
       <c r="M948" s="29"/>
     </row>
-    <row r="949" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A949" s="29" t="s">
         <v>2587</v>
       </c>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC9F225-309A-264C-89DA-BB91266D3458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD25743-B5FF-B14D-8BD5-C35440FD73A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6900" yWindow="1760" windowWidth="23340" windowHeight="14260" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -17655,13 +17655,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M949" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M948" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="input_c"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M948" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
@@ -18036,7 +18030,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>25</v>
       </c>
@@ -18071,7 +18065,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
@@ -18106,7 +18100,7 @@
       <c r="L3" s="23"/>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>5</v>
       </c>
@@ -18141,7 +18135,7 @@
       <c r="L4" s="19"/>
       <c r="M4" s="20"/>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>6</v>
       </c>
@@ -18176,7 +18170,7 @@
       <c r="L5" s="23"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>7</v>
       </c>
@@ -18211,7 +18205,7 @@
       <c r="L6" s="19"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>8</v>
       </c>
@@ -18246,7 +18240,7 @@
       <c r="L7" s="23"/>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
@@ -18275,7 +18269,7 @@
       </c>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>10</v>
       </c>
@@ -18310,7 +18304,7 @@
       <c r="L9" s="23"/>
       <c r="M9" s="24"/>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>11</v>
       </c>
@@ -18335,7 +18329,7 @@
       <c r="L10" s="19"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
         <v>12</v>
       </c>
@@ -18370,7 +18364,7 @@
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>13</v>
       </c>
@@ -18403,7 +18397,7 @@
       <c r="L12" s="19"/>
       <c r="M12" s="20"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>14</v>
       </c>
@@ -18436,7 +18430,7 @@
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>15</v>
       </c>
@@ -18467,7 +18461,7 @@
       <c r="L14" s="19"/>
       <c r="M14" s="20"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
         <v>16</v>
       </c>
@@ -18492,7 +18486,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -18517,7 +18511,7 @@
       <c r="L16" s="19"/>
       <c r="M16" s="20"/>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
         <v>18</v>
       </c>
@@ -18548,7 +18542,7 @@
       <c r="L17" s="23"/>
       <c r="M17" s="24"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>19</v>
       </c>
@@ -18567,7 +18561,7 @@
       <c r="L18" s="19"/>
       <c r="M18" s="20"/>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>20</v>
       </c>
@@ -18586,7 +18580,7 @@
       <c r="L19" s="23"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>21</v>
       </c>
@@ -18605,7 +18599,7 @@
       <c r="L20" s="19"/>
       <c r="M20" s="20"/>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
@@ -18632,7 +18626,7 @@
       <c r="L21" s="19"/>
       <c r="M21" s="20"/>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
         <v>24</v>
       </c>
@@ -18659,7 +18653,7 @@
       <c r="L22" s="23"/>
       <c r="M22" s="24"/>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
         <v>30</v>
       </c>
@@ -18688,7 +18682,7 @@
       <c r="L23" s="19"/>
       <c r="M23" s="20"/>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="21" t="s">
         <v>48</v>
       </c>
@@ -18715,7 +18709,7 @@
       <c r="L24" s="23"/>
       <c r="M24" s="24"/>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>43</v>
       </c>
@@ -18746,7 +18740,7 @@
       <c r="L25" s="19"/>
       <c r="M25" s="20"/>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="28" t="s">
         <v>45</v>
       </c>
@@ -18773,7 +18767,7 @@
       <c r="L26" s="27"/>
       <c r="M26" s="24"/>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
         <v>46</v>
       </c>
@@ -18800,7 +18794,7 @@
       <c r="L27" s="19"/>
       <c r="M27" s="20"/>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>57</v>
       </c>
@@ -18831,7 +18825,7 @@
       <c r="L28" s="23"/>
       <c r="M28" s="24"/>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
         <v>58</v>
       </c>
@@ -18864,7 +18858,7 @@
       <c r="L29" s="19"/>
       <c r="M29" s="20"/>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="21" t="s">
         <v>59</v>
       </c>
@@ -18899,7 +18893,7 @@
       <c r="L30" s="23"/>
       <c r="M30" s="24"/>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="17" t="s">
         <v>60</v>
       </c>
@@ -18934,7 +18928,7 @@
       <c r="L31" s="19"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="21" t="s">
         <v>61</v>
       </c>
@@ -18969,7 +18963,7 @@
       <c r="L32" s="23"/>
       <c r="M32" s="24"/>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>69</v>
       </c>
@@ -18996,7 +18990,7 @@
       <c r="L33" s="23"/>
       <c r="M33" s="24"/>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="17" t="s">
         <v>72</v>
       </c>
@@ -19025,7 +19019,7 @@
       <c r="L34" s="19"/>
       <c r="M34" s="20"/>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>75</v>
       </c>
@@ -19060,7 +19054,7 @@
       <c r="L35" s="23"/>
       <c r="M35" s="24"/>
     </row>
-    <row r="36" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21" t="s">
         <v>74</v>
       </c>
@@ -19087,7 +19081,7 @@
       <c r="L36" s="19"/>
       <c r="M36" s="20"/>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>73</v>
       </c>
@@ -19122,7 +19116,7 @@
       <c r="L37" s="23"/>
       <c r="M37" s="24"/>
     </row>
-    <row r="38" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>79</v>
       </c>
@@ -19159,7 +19153,7 @@
       <c r="L38" s="19"/>
       <c r="M38" s="20"/>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="21" t="s">
         <v>80</v>
       </c>
@@ -19194,7 +19188,7 @@
       <c r="L39" s="23"/>
       <c r="M39" s="24"/>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="21" t="s">
         <v>81</v>
       </c>
@@ -19221,7 +19215,7 @@
       <c r="L40" s="19"/>
       <c r="M40" s="20"/>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
         <v>83</v>
       </c>
@@ -19256,7 +19250,7 @@
       <c r="L41" s="23"/>
       <c r="M41" s="24"/>
     </row>
-    <row r="42" spans="1:13" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
         <v>84</v>
       </c>
@@ -19291,7 +19285,7 @@
       <c r="L42" s="19"/>
       <c r="M42" s="30"/>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="21" t="s">
         <v>85</v>
       </c>
@@ -19326,7 +19320,7 @@
       <c r="L43" s="23"/>
       <c r="M43" s="24"/>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
         <v>88</v>
       </c>
@@ -19343,7 +19337,7 @@
       <c r="L44" s="19"/>
       <c r="M44" s="20"/>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="21" t="s">
         <v>90</v>
       </c>
@@ -19360,7 +19354,7 @@
       <c r="L45" s="23"/>
       <c r="M45" s="24"/>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
         <v>91</v>
       </c>
@@ -19377,7 +19371,7 @@
       <c r="L46" s="19"/>
       <c r="M46" s="20"/>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="21" t="s">
         <v>92</v>
       </c>
@@ -19412,7 +19406,7 @@
       <c r="L47" s="23"/>
       <c r="M47" s="24"/>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="17" t="s">
         <v>99</v>
       </c>
@@ -19447,7 +19441,7 @@
       <c r="L48" s="19"/>
       <c r="M48" s="20"/>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="21" t="s">
         <v>100</v>
       </c>
@@ -19482,7 +19476,7 @@
       <c r="L49" s="23"/>
       <c r="M49" s="24"/>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>101</v>
       </c>
@@ -19509,7 +19503,7 @@
       <c r="L50" s="19"/>
       <c r="M50" s="20"/>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="21" t="s">
         <v>105</v>
       </c>
@@ -19544,7 +19538,7 @@
       <c r="L51" s="23"/>
       <c r="M51" s="24"/>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="17" t="s">
         <v>351</v>
       </c>
@@ -19575,7 +19569,7 @@
       <c r="L52" s="19"/>
       <c r="M52" s="20"/>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="21" t="s">
         <v>107</v>
       </c>
@@ -19602,7 +19596,7 @@
       <c r="L53" s="23"/>
       <c r="M53" s="24"/>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
         <v>112</v>
       </c>
@@ -19633,7 +19627,7 @@
       <c r="L54" s="19"/>
       <c r="M54" s="20"/>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
         <v>114</v>
       </c>
@@ -19666,7 +19660,7 @@
       <c r="L55" s="23"/>
       <c r="M55" s="24"/>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="21" t="s">
         <v>116</v>
       </c>
@@ -19695,7 +19689,7 @@
       <c r="L56" s="19"/>
       <c r="M56" s="20"/>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="21" t="s">
         <v>118</v>
       </c>
@@ -19722,7 +19716,7 @@
       <c r="L57" s="23"/>
       <c r="M57" s="24"/>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="17" t="s">
         <v>119</v>
       </c>
@@ -19739,7 +19733,7 @@
       <c r="L58" s="19"/>
       <c r="M58" s="20"/>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="21" t="s">
         <v>120</v>
       </c>
@@ -19768,7 +19762,7 @@
       <c r="L59" s="23"/>
       <c r="M59" s="24"/>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="21" t="s">
         <v>121</v>
       </c>
@@ -19797,7 +19791,7 @@
       <c r="L60" s="19"/>
       <c r="M60" s="20"/>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="21" t="s">
         <v>124</v>
       </c>
@@ -19822,7 +19816,7 @@
       <c r="L61" s="23"/>
       <c r="M61" s="24"/>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="17" t="s">
         <v>134</v>
       </c>
@@ -19849,7 +19843,7 @@
       <c r="L62" s="19"/>
       <c r="M62" s="20"/>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="21" t="s">
         <v>172</v>
       </c>
@@ -19882,7 +19876,7 @@
       </c>
       <c r="M63" s="24"/>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="17" t="s">
         <v>173</v>
       </c>
@@ -19915,7 +19909,7 @@
       <c r="L64" s="19"/>
       <c r="M64" s="20"/>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="21" t="s">
         <v>174</v>
       </c>
@@ -19950,7 +19944,7 @@
       <c r="L65" s="23"/>
       <c r="M65" s="24"/>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="17" t="s">
         <v>175</v>
       </c>
@@ -19983,7 +19977,7 @@
       <c r="L66" s="19"/>
       <c r="M66" s="20"/>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="21" t="s">
         <v>176</v>
       </c>
@@ -20016,7 +20010,7 @@
       <c r="L67" s="23"/>
       <c r="M67" s="24"/>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="21" t="s">
         <v>177</v>
       </c>
@@ -20047,7 +20041,7 @@
       <c r="L68" s="19"/>
       <c r="M68" s="20"/>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="21" t="s">
         <v>154</v>
       </c>
@@ -20080,7 +20074,7 @@
       <c r="L69" s="19"/>
       <c r="M69" s="20"/>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="21" t="s">
         <v>155</v>
       </c>
@@ -20113,7 +20107,7 @@
       <c r="L70" s="23"/>
       <c r="M70" s="24"/>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="21" t="s">
         <v>156</v>
       </c>
@@ -20146,7 +20140,7 @@
       <c r="L71" s="19"/>
       <c r="M71" s="20"/>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="21" t="s">
         <v>157</v>
       </c>
@@ -20183,7 +20177,7 @@
       <c r="L72" s="23"/>
       <c r="M72" s="24"/>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="21" t="s">
         <v>163</v>
       </c>
@@ -20216,7 +20210,7 @@
       <c r="L73" s="19"/>
       <c r="M73" s="20"/>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="21" t="s">
         <v>164</v>
       </c>
@@ -20249,7 +20243,7 @@
       <c r="L74" s="23"/>
       <c r="M74" s="24"/>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="21" t="s">
         <v>165</v>
       </c>
@@ -20282,7 +20276,7 @@
       <c r="L75" s="19"/>
       <c r="M75" s="20"/>
     </row>
-    <row r="76" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
         <v>2433</v>
       </c>
@@ -20317,7 +20311,7 @@
       <c r="L76" s="22"/>
       <c r="M76" s="20"/>
     </row>
-    <row r="77" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
         <v>2434</v>
       </c>
@@ -20352,7 +20346,7 @@
       <c r="L77" s="22"/>
       <c r="M77" s="20"/>
     </row>
-    <row r="78" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
         <v>2435</v>
       </c>
@@ -20387,7 +20381,7 @@
       <c r="L78" s="22"/>
       <c r="M78" s="20"/>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
         <v>2587</v>
       </c>
@@ -20420,7 +20414,7 @@
       <c r="L79" s="22"/>
       <c r="M79" s="20"/>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>2588</v>
       </c>
@@ -20453,7 +20447,7 @@
       <c r="L80" s="22"/>
       <c r="M80" s="20"/>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>2589</v>
       </c>
@@ -20486,7 +20480,7 @@
       <c r="L81" s="22"/>
       <c r="M81" s="20"/>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
         <v>170</v>
       </c>
@@ -20513,7 +20507,7 @@
       <c r="L82" s="23"/>
       <c r="M82" s="24"/>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>183</v>
       </c>
@@ -20544,7 +20538,7 @@
       <c r="L83" s="19"/>
       <c r="M83" s="20"/>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
         <v>198</v>
       </c>
@@ -20575,7 +20569,7 @@
       <c r="L84" s="23"/>
       <c r="M84" s="24"/>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="21" t="s">
         <v>199</v>
       </c>
@@ -20606,7 +20600,7 @@
       <c r="L85" s="19"/>
       <c r="M85" s="20"/>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="21" t="s">
         <v>200</v>
       </c>
@@ -20641,7 +20635,7 @@
       <c r="L86" s="23"/>
       <c r="M86" s="24"/>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>201</v>
       </c>
@@ -20676,7 +20670,7 @@
       <c r="L87" s="19"/>
       <c r="M87" s="20"/>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="21" t="s">
         <v>202</v>
       </c>
@@ -20707,7 +20701,7 @@
       <c r="L88" s="23"/>
       <c r="M88" s="24"/>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="21" t="s">
         <v>203</v>
       </c>
@@ -20740,7 +20734,7 @@
       <c r="L89" s="19"/>
       <c r="M89" s="20"/>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="21" t="s">
         <v>204</v>
       </c>
@@ -20773,7 +20767,7 @@
       <c r="L90" s="23"/>
       <c r="M90" s="24"/>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
         <v>205</v>
       </c>
@@ -20806,7 +20800,7 @@
       <c r="L91" s="19"/>
       <c r="M91" s="20"/>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
         <v>206</v>
       </c>
@@ -20841,7 +20835,7 @@
       <c r="L92" s="23"/>
       <c r="M92" s="24"/>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
         <v>207</v>
       </c>
@@ -20872,7 +20866,7 @@
       <c r="L93" s="19"/>
       <c r="M93" s="20"/>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
         <v>208</v>
       </c>
@@ -20907,7 +20901,7 @@
       <c r="L94" s="23"/>
       <c r="M94" s="24"/>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
         <v>212</v>
       </c>
@@ -20938,7 +20932,7 @@
       <c r="L95" s="19"/>
       <c r="M95" s="20"/>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
         <v>216</v>
       </c>
@@ -20969,7 +20963,7 @@
       <c r="L96" s="23"/>
       <c r="M96" s="24"/>
     </row>
-    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
         <v>532</v>
       </c>
@@ -20986,7 +20980,7 @@
       <c r="L97" s="19"/>
       <c r="M97" s="20"/>
     </row>
-    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
         <v>533</v>
       </c>
@@ -21003,7 +20997,7 @@
       <c r="L98" s="23"/>
       <c r="M98" s="24"/>
     </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>511</v>
       </c>
@@ -21026,7 +21020,7 @@
       <c r="L99" s="19"/>
       <c r="M99" s="20"/>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="21"/>
       <c r="B100" s="22" t="s">
         <v>64</v>
@@ -21057,7 +21051,7 @@
       <c r="L100" s="19"/>
       <c r="M100" s="20"/>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
         <v>2579</v>
       </c>
@@ -21090,7 +21084,7 @@
       <c r="L101" s="23"/>
       <c r="M101" s="24"/>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
         <v>2578</v>
       </c>
@@ -21123,7 +21117,7 @@
       <c r="L102" s="19"/>
       <c r="M102" s="20"/>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>2580</v>
       </c>
@@ -21156,7 +21150,7 @@
       <c r="L103" s="23"/>
       <c r="M103" s="24"/>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
         <v>289</v>
       </c>
@@ -21191,7 +21185,7 @@
       <c r="L104" s="19"/>
       <c r="M104" s="20"/>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
         <v>290</v>
       </c>
@@ -21226,7 +21220,7 @@
       <c r="L105" s="23"/>
       <c r="M105" s="24"/>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
         <v>47</v>
       </c>
@@ -21253,7 +21247,7 @@
       <c r="L106" s="19"/>
       <c r="M106" s="20"/>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="21"/>
       <c r="B107" s="22" t="s">
         <v>240</v>
@@ -21284,7 +21278,7 @@
       <c r="L107" s="23"/>
       <c r="M107" s="24"/>
     </row>
-    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
         <v>242</v>
       </c>
@@ -21311,7 +21305,7 @@
       <c r="L108" s="19"/>
       <c r="M108" s="20"/>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
         <v>252</v>
       </c>
@@ -21342,7 +21336,7 @@
       <c r="L109" s="23"/>
       <c r="M109" s="24"/>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
         <v>845</v>
       </c>
@@ -21373,7 +21367,7 @@
       <c r="L110" s="19"/>
       <c r="M110" s="20"/>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
         <v>842</v>
       </c>
@@ -21406,7 +21400,7 @@
       <c r="L111" s="23"/>
       <c r="M111" s="24"/>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
         <v>843</v>
       </c>
@@ -21439,7 +21433,7 @@
       <c r="L112" s="19"/>
       <c r="M112" s="20"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
         <v>844</v>
       </c>
@@ -21472,7 +21466,7 @@
       <c r="L113" s="23"/>
       <c r="M113" s="24"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
         <v>838</v>
       </c>
@@ -21501,7 +21495,7 @@
       <c r="L114" s="19"/>
       <c r="M114" s="20"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
         <v>839</v>
       </c>
@@ -21530,7 +21524,7 @@
       <c r="L115" s="23"/>
       <c r="M115" s="24"/>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
         <v>840</v>
       </c>
@@ -21557,7 +21551,7 @@
       <c r="L116" s="19"/>
       <c r="M116" s="20"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
         <v>841</v>
       </c>
@@ -21588,7 +21582,7 @@
       <c r="L117" s="23"/>
       <c r="M117" s="24"/>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21"/>
       <c r="B118" s="22"/>
       <c r="C118" s="23"/>
@@ -21603,7 +21597,7 @@
       <c r="L118" s="19"/>
       <c r="M118" s="20"/>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
         <v>315</v>
       </c>
@@ -21634,7 +21628,7 @@
       <c r="L119" s="23"/>
       <c r="M119" s="24"/>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="21" t="s">
         <v>318</v>
       </c>
@@ -21659,7 +21653,7 @@
       <c r="L120" s="23"/>
       <c r="M120" s="24"/>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="21" t="s">
         <v>321</v>
       </c>
@@ -21686,7 +21680,7 @@
       <c r="L121" s="23"/>
       <c r="M121" s="24"/>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="21" t="s">
         <v>324</v>
       </c>
@@ -21713,7 +21707,7 @@
       <c r="L122" s="19"/>
       <c r="M122" s="20"/>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>331</v>
       </c>
@@ -21738,7 +21732,7 @@
       <c r="L123" s="23"/>
       <c r="M123" s="24"/>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>332</v>
       </c>
@@ -21773,7 +21767,7 @@
       <c r="L124" s="19"/>
       <c r="M124" s="20"/>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="21" t="s">
         <v>333</v>
       </c>
@@ -21796,7 +21790,7 @@
       <c r="L125" s="23"/>
       <c r="M125" s="24"/>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
         <v>334</v>
       </c>
@@ -21819,7 +21813,7 @@
       <c r="L126" s="19"/>
       <c r="M126" s="20"/>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="21" t="s">
         <v>335</v>
       </c>
@@ -21842,7 +21836,7 @@
       <c r="L127" s="23"/>
       <c r="M127" s="24"/>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="21" t="s">
         <v>342</v>
       </c>
@@ -21871,7 +21865,7 @@
       <c r="L128" s="19"/>
       <c r="M128" s="20"/>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="21" t="s">
         <v>22</v>
       </c>
@@ -21896,7 +21890,7 @@
       <c r="L129" s="23"/>
       <c r="M129" s="24"/>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="21" t="s">
         <v>350</v>
       </c>
@@ -21929,7 +21923,7 @@
       <c r="L130" s="19"/>
       <c r="M130" s="20"/>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="21" t="s">
         <v>2364</v>
       </c>
@@ -21964,7 +21958,7 @@
       <c r="L131" s="23"/>
       <c r="M131" s="24"/>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="21" t="s">
         <v>2590</v>
       </c>
@@ -21999,7 +21993,7 @@
       <c r="L132" s="19"/>
       <c r="M132" s="20"/>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="21" t="s">
         <v>354</v>
       </c>
@@ -22034,7 +22028,7 @@
       <c r="L133" s="23"/>
       <c r="M133" s="24"/>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="21" t="s">
         <v>401</v>
       </c>
@@ -22069,7 +22063,7 @@
       <c r="L134" s="19"/>
       <c r="M134" s="20"/>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="21" t="s">
         <v>402</v>
       </c>
@@ -22104,7 +22098,7 @@
       <c r="L135" s="23"/>
       <c r="M135" s="24"/>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="21" t="s">
         <v>403</v>
       </c>
@@ -22139,7 +22133,7 @@
       <c r="L136" s="19"/>
       <c r="M136" s="20"/>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="21" t="s">
         <v>404</v>
       </c>
@@ -22174,7 +22168,7 @@
       <c r="L137" s="23"/>
       <c r="M137" s="24"/>
     </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="21" t="s">
         <v>405</v>
       </c>
@@ -22209,7 +22203,7 @@
       <c r="L138" s="19"/>
       <c r="M138" s="20"/>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="21" t="s">
         <v>406</v>
       </c>
@@ -22244,7 +22238,7 @@
       <c r="L139" s="23"/>
       <c r="M139" s="24"/>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="21" t="s">
         <v>407</v>
       </c>
@@ -22279,7 +22273,7 @@
       <c r="L140" s="19"/>
       <c r="M140" s="20"/>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="21" t="s">
         <v>408</v>
       </c>
@@ -22314,7 +22308,7 @@
       <c r="L141" s="23"/>
       <c r="M141" s="24"/>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="21" t="s">
         <v>409</v>
       </c>
@@ -22349,7 +22343,7 @@
       <c r="L142" s="19"/>
       <c r="M142" s="20"/>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="21" t="s">
         <v>410</v>
       </c>
@@ -22384,7 +22378,7 @@
       <c r="L143" s="23"/>
       <c r="M143" s="24"/>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="21" t="s">
         <v>411</v>
       </c>
@@ -22419,7 +22413,7 @@
       <c r="L144" s="19"/>
       <c r="M144" s="20"/>
     </row>
-    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="21" t="s">
         <v>412</v>
       </c>
@@ -22454,7 +22448,7 @@
       <c r="L145" s="23"/>
       <c r="M145" s="24"/>
     </row>
-    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="21" t="s">
         <v>413</v>
       </c>
@@ -22489,7 +22483,7 @@
       <c r="L146" s="19"/>
       <c r="M146" s="20"/>
     </row>
-    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="75" t="s">
         <v>414</v>
       </c>
@@ -22524,7 +22518,7 @@
       <c r="L147" s="33"/>
       <c r="M147" s="34"/>
     </row>
-    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="29" t="s">
         <v>415</v>
       </c>
@@ -22559,7 +22553,7 @@
       <c r="L148" s="29"/>
       <c r="M148" s="29"/>
     </row>
-    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="76" t="s">
         <v>416</v>
       </c>
@@ -22592,7 +22586,7 @@
       <c r="L149" s="29"/>
       <c r="M149" s="29"/>
     </row>
-    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="29" t="s">
         <v>417</v>
       </c>
@@ -22625,7 +22619,7 @@
       <c r="L150" s="29"/>
       <c r="M150" s="29"/>
     </row>
-    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="29" t="s">
         <v>418</v>
       </c>
@@ -22658,7 +22652,7 @@
       <c r="L151" s="29"/>
       <c r="M151" s="29"/>
     </row>
-    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="29" t="s">
         <v>419</v>
       </c>
@@ -22691,7 +22685,7 @@
       <c r="L152" s="29"/>
       <c r="M152" s="29"/>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="29" t="s">
         <v>420</v>
       </c>
@@ -22726,7 +22720,7 @@
       <c r="L153" s="29"/>
       <c r="M153" s="29"/>
     </row>
-    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="29" t="s">
         <v>421</v>
       </c>
@@ -22761,7 +22755,7 @@
       <c r="L154" s="29"/>
       <c r="M154" s="29"/>
     </row>
-    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="29" t="s">
         <v>422</v>
       </c>
@@ -22796,7 +22790,7 @@
       <c r="L155" s="29"/>
       <c r="M155" s="29"/>
     </row>
-    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="29" t="s">
         <v>423</v>
       </c>
@@ -22831,7 +22825,7 @@
       <c r="L156" s="29"/>
       <c r="M156" s="29"/>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="29" t="s">
         <v>424</v>
       </c>
@@ -22866,7 +22860,7 @@
       <c r="L157" s="29"/>
       <c r="M157" s="29"/>
     </row>
-    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="29" t="s">
         <v>425</v>
       </c>
@@ -22901,7 +22895,7 @@
       <c r="L158" s="29"/>
       <c r="M158" s="29"/>
     </row>
-    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="29" t="s">
         <v>426</v>
       </c>
@@ -22936,7 +22930,7 @@
       <c r="L159" s="29"/>
       <c r="M159" s="29"/>
     </row>
-    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="29" t="s">
         <v>427</v>
       </c>
@@ -22971,7 +22965,7 @@
       <c r="L160" s="29"/>
       <c r="M160" s="29"/>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="29" t="s">
         <v>428</v>
       </c>
@@ -23006,7 +23000,7 @@
       <c r="L161" s="29"/>
       <c r="M161" s="29"/>
     </row>
-    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="29" t="s">
         <v>429</v>
       </c>
@@ -23041,7 +23035,7 @@
       <c r="L162" s="29"/>
       <c r="M162" s="29"/>
     </row>
-    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="29" t="s">
         <v>430</v>
       </c>
@@ -23076,7 +23070,7 @@
       <c r="L163" s="29"/>
       <c r="M163" s="29"/>
     </row>
-    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="29" t="s">
         <v>431</v>
       </c>
@@ -23111,7 +23105,7 @@
       <c r="L164" s="29"/>
       <c r="M164" s="29"/>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="29" t="s">
         <v>432</v>
       </c>
@@ -23146,7 +23140,7 @@
       <c r="L165" s="29"/>
       <c r="M165" s="29"/>
     </row>
-    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="29" t="s">
         <v>433</v>
       </c>
@@ -23181,7 +23175,7 @@
       <c r="L166" s="29"/>
       <c r="M166" s="29"/>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="29" t="s">
         <v>434</v>
       </c>
@@ -23216,7 +23210,7 @@
       <c r="L167" s="29"/>
       <c r="M167" s="29"/>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="29" t="s">
         <v>435</v>
       </c>
@@ -23251,7 +23245,7 @@
       <c r="L168" s="29"/>
       <c r="M168" s="29"/>
     </row>
-    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="29" t="s">
         <v>436</v>
       </c>
@@ -23286,7 +23280,7 @@
       <c r="L169" s="29"/>
       <c r="M169" s="29"/>
     </row>
-    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="29" t="s">
         <v>437</v>
       </c>
@@ -23321,7 +23315,7 @@
       <c r="L170" s="29"/>
       <c r="M170" s="29"/>
     </row>
-    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="29" t="s">
         <v>438</v>
       </c>
@@ -23356,7 +23350,7 @@
       <c r="L171" s="29"/>
       <c r="M171" s="29"/>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="29" t="s">
         <v>439</v>
       </c>
@@ -23391,7 +23385,7 @@
       <c r="L172" s="29"/>
       <c r="M172" s="29"/>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="29" t="s">
         <v>440</v>
       </c>
@@ -23426,7 +23420,7 @@
       <c r="L173" s="29"/>
       <c r="M173" s="29"/>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="29" t="s">
         <v>441</v>
       </c>
@@ -23461,7 +23455,7 @@
       <c r="L174" s="29"/>
       <c r="M174" s="29"/>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="29" t="s">
         <v>442</v>
       </c>
@@ -23496,7 +23490,7 @@
       <c r="L175" s="29"/>
       <c r="M175" s="29"/>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="29" t="s">
         <v>443</v>
       </c>
@@ -23531,7 +23525,7 @@
       <c r="L176" s="29"/>
       <c r="M176" s="29"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="29" t="s">
         <v>444</v>
       </c>
@@ -23566,7 +23560,7 @@
       <c r="L177" s="29"/>
       <c r="M177" s="29"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="29" t="s">
         <v>445</v>
       </c>
@@ -23601,7 +23595,7 @@
       <c r="L178" s="29"/>
       <c r="M178" s="29"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="29" t="s">
         <v>446</v>
       </c>
@@ -23636,7 +23630,7 @@
       <c r="L179" s="29"/>
       <c r="M179" s="29"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="29" t="s">
         <v>447</v>
       </c>
@@ -23671,7 +23665,7 @@
       <c r="L180" s="29"/>
       <c r="M180" s="29"/>
     </row>
-    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="29" t="s">
         <v>448</v>
       </c>
@@ -23706,7 +23700,7 @@
       <c r="L181" s="29"/>
       <c r="M181" s="29"/>
     </row>
-    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="29" t="s">
         <v>449</v>
       </c>
@@ -23741,7 +23735,7 @@
       <c r="L182" s="29"/>
       <c r="M182" s="29"/>
     </row>
-    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="29" t="s">
         <v>450</v>
       </c>
@@ -23776,7 +23770,7 @@
       <c r="L183" s="29"/>
       <c r="M183" s="29"/>
     </row>
-    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="29" t="s">
         <v>451</v>
       </c>
@@ -23811,7 +23805,7 @@
       <c r="L184" s="29"/>
       <c r="M184" s="29"/>
     </row>
-    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="29" t="s">
         <v>452</v>
       </c>
@@ -23846,7 +23840,7 @@
       <c r="L185" s="29"/>
       <c r="M185" s="29"/>
     </row>
-    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="29" t="s">
         <v>453</v>
       </c>
@@ -23881,7 +23875,7 @@
       <c r="L186" s="29"/>
       <c r="M186" s="29"/>
     </row>
-    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="29" t="s">
         <v>454</v>
       </c>
@@ -23916,7 +23910,7 @@
       <c r="L187" s="29"/>
       <c r="M187" s="29"/>
     </row>
-    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="29" t="s">
         <v>455</v>
       </c>
@@ -23951,7 +23945,7 @@
       <c r="L188" s="29"/>
       <c r="M188" s="29"/>
     </row>
-    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="29" t="s">
         <v>456</v>
       </c>
@@ -23986,7 +23980,7 @@
       <c r="L189" s="29"/>
       <c r="M189" s="29"/>
     </row>
-    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="29" t="s">
         <v>457</v>
       </c>
@@ -24021,7 +24015,7 @@
       <c r="L190" s="29"/>
       <c r="M190" s="29"/>
     </row>
-    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="29" t="s">
         <v>458</v>
       </c>
@@ -24056,7 +24050,7 @@
       <c r="L191" s="29"/>
       <c r="M191" s="29"/>
     </row>
-    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="29" t="s">
         <v>459</v>
       </c>
@@ -24089,7 +24083,7 @@
       <c r="L192" s="29"/>
       <c r="M192" s="29"/>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="29" t="s">
         <v>460</v>
       </c>
@@ -24122,7 +24116,7 @@
       <c r="L193" s="29"/>
       <c r="M193" s="29"/>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="29" t="s">
         <v>461</v>
       </c>
@@ -24155,7 +24149,7 @@
       <c r="L194" s="29"/>
       <c r="M194" s="29"/>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="29" t="s">
         <v>462</v>
       </c>
@@ -24188,7 +24182,7 @@
       <c r="L195" s="29"/>
       <c r="M195" s="29"/>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="29" t="s">
         <v>463</v>
       </c>
@@ -24223,7 +24217,7 @@
       <c r="L196" s="29"/>
       <c r="M196" s="29"/>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="29" t="s">
         <v>464</v>
       </c>
@@ -24258,7 +24252,7 @@
       <c r="L197" s="29"/>
       <c r="M197" s="29"/>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="29" t="s">
         <v>465</v>
       </c>
@@ -24291,7 +24285,7 @@
       <c r="L198" s="29"/>
       <c r="M198" s="29"/>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="29" t="s">
         <v>466</v>
       </c>
@@ -24324,7 +24318,7 @@
       <c r="L199" s="29"/>
       <c r="M199" s="29"/>
     </row>
-    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="29" t="s">
         <v>467</v>
       </c>
@@ -24357,7 +24351,7 @@
       <c r="L200" s="29"/>
       <c r="M200" s="29"/>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="29" t="s">
         <v>1695</v>
       </c>
@@ -24390,7 +24384,7 @@
       <c r="L201" s="31"/>
       <c r="M201" s="29"/>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="29" t="s">
         <v>1696</v>
       </c>
@@ -24425,7 +24419,7 @@
       <c r="L202" s="31"/>
       <c r="M202" s="29"/>
     </row>
-    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="29" t="s">
         <v>1697</v>
       </c>
@@ -24460,7 +24454,7 @@
       <c r="L203" s="31"/>
       <c r="M203" s="29"/>
     </row>
-    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="29" t="s">
         <v>1698</v>
       </c>
@@ -24495,7 +24489,7 @@
       <c r="L204" s="31"/>
       <c r="M204" s="29"/>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="29" t="s">
         <v>1699</v>
       </c>
@@ -24528,7 +24522,7 @@
       <c r="L205" s="31"/>
       <c r="M205" s="29"/>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="29" t="s">
         <v>1700</v>
       </c>
@@ -24561,7 +24555,7 @@
       <c r="L206" s="31"/>
       <c r="M206" s="29"/>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="29" t="s">
         <v>1701</v>
       </c>
@@ -24594,7 +24588,7 @@
       <c r="L207" s="31"/>
       <c r="M207" s="29"/>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="29" t="s">
         <v>1702</v>
       </c>
@@ -24627,7 +24621,7 @@
       <c r="L208" s="31"/>
       <c r="M208" s="29"/>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="29" t="s">
         <v>1703</v>
       </c>
@@ -24660,7 +24654,7 @@
       <c r="L209" s="31"/>
       <c r="M209" s="29"/>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="29" t="s">
         <v>1704</v>
       </c>
@@ -24693,7 +24687,7 @@
       <c r="L210" s="31"/>
       <c r="M210" s="29"/>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="29" t="s">
         <v>1705</v>
       </c>
@@ -24726,7 +24720,7 @@
       <c r="L211" s="31"/>
       <c r="M211" s="29"/>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="29" t="s">
         <v>1706</v>
       </c>
@@ -24759,7 +24753,7 @@
       <c r="L212" s="31"/>
       <c r="M212" s="29"/>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="29" t="s">
         <v>1707</v>
       </c>
@@ -24792,7 +24786,7 @@
       <c r="L213" s="31"/>
       <c r="M213" s="29"/>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="29" t="s">
         <v>1708</v>
       </c>
@@ -24825,7 +24819,7 @@
       <c r="L214" s="31"/>
       <c r="M214" s="29"/>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="29" t="s">
         <v>1709</v>
       </c>
@@ -24858,7 +24852,7 @@
       <c r="L215" s="31"/>
       <c r="M215" s="29"/>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="29" t="s">
         <v>1710</v>
       </c>
@@ -24891,7 +24885,7 @@
       <c r="L216" s="31"/>
       <c r="M216" s="29"/>
     </row>
-    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="29" t="s">
         <v>468</v>
       </c>
@@ -24926,7 +24920,7 @@
       <c r="L217" s="29"/>
       <c r="M217" s="29"/>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="29" t="s">
         <v>469</v>
       </c>
@@ -24961,7 +24955,7 @@
       <c r="L218" s="29"/>
       <c r="M218" s="29"/>
     </row>
-    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="29"/>
       <c r="B219" s="31"/>
       <c r="C219" s="29"/>
@@ -24976,7 +24970,7 @@
       <c r="L219" s="29"/>
       <c r="M219" s="29"/>
     </row>
-    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="29"/>
       <c r="B220" s="31"/>
       <c r="C220" s="29"/>
@@ -24991,7 +24985,7 @@
       <c r="L220" s="29"/>
       <c r="M220" s="29"/>
     </row>
-    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="29" t="s">
         <v>475</v>
       </c>
@@ -25028,7 +25022,7 @@
       </c>
       <c r="M221" s="29"/>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="29" t="s">
         <v>476</v>
       </c>
@@ -25061,7 +25055,7 @@
       <c r="L222" s="31"/>
       <c r="M222" s="29"/>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
         <v>480</v>
       </c>
@@ -25096,7 +25090,7 @@
       </c>
       <c r="M223" s="29"/>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
         <v>485</v>
       </c>
@@ -25131,7 +25125,7 @@
       <c r="L224" s="31"/>
       <c r="M224" s="29"/>
     </row>
-    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
         <v>486</v>
       </c>
@@ -25166,7 +25160,7 @@
       <c r="L225" s="31"/>
       <c r="M225" s="29"/>
     </row>
-    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="29"/>
       <c r="B226" s="31" t="s">
         <v>489</v>
@@ -25201,7 +25195,7 @@
       <c r="L226" s="31"/>
       <c r="M226" s="29"/>
     </row>
-    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="29"/>
       <c r="B227" s="38" t="s">
         <v>491</v>
@@ -25234,7 +25228,7 @@
       <c r="L227" s="31"/>
       <c r="M227" s="29"/>
     </row>
-    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="29"/>
       <c r="B228" s="31"/>
       <c r="C228" s="29"/>
@@ -25249,7 +25243,7 @@
       <c r="L228" s="31"/>
       <c r="M228" s="29"/>
     </row>
-    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="29" t="s">
         <v>2279</v>
       </c>
@@ -25286,7 +25280,7 @@
       </c>
       <c r="M229" s="29"/>
     </row>
-    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="29" t="s">
         <v>502</v>
       </c>
@@ -25321,7 +25315,7 @@
       <c r="L230" s="31"/>
       <c r="M230" s="29"/>
     </row>
-    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="29" t="s">
         <v>508</v>
       </c>
@@ -25356,7 +25350,7 @@
       <c r="L231" s="31"/>
       <c r="M231" s="29"/>
     </row>
-    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="29" t="s">
         <v>513</v>
       </c>
@@ -25381,7 +25375,7 @@
       <c r="L232" s="31"/>
       <c r="M232" s="29"/>
     </row>
-    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="29" t="s">
         <v>514</v>
       </c>
@@ -25406,7 +25400,7 @@
       <c r="L233" s="31"/>
       <c r="M233" s="29"/>
     </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="39" t="s">
         <v>518</v>
       </c>
@@ -25433,7 +25427,7 @@
       <c r="L234" s="31"/>
       <c r="M234" s="29"/>
     </row>
-    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="29" t="s">
         <v>519</v>
       </c>
@@ -25460,7 +25454,7 @@
       <c r="L235" s="31"/>
       <c r="M235" s="29"/>
     </row>
-    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="29" t="s">
         <v>522</v>
       </c>
@@ -25491,7 +25485,7 @@
       <c r="L236" s="31"/>
       <c r="M236" s="29"/>
     </row>
-    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="29" t="s">
         <v>523</v>
       </c>
@@ -25522,7 +25516,7 @@
       <c r="L237" s="31"/>
       <c r="M237" s="29"/>
     </row>
-    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="29" t="s">
         <v>524</v>
       </c>
@@ -25553,7 +25547,7 @@
       <c r="L238" s="31"/>
       <c r="M238" s="29"/>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="29" t="s">
         <v>721</v>
       </c>
@@ -25578,7 +25572,7 @@
       <c r="L239" s="31"/>
       <c r="M239" s="29"/>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="29" t="s">
         <v>722</v>
       </c>
@@ -25603,7 +25597,7 @@
       <c r="L240" s="31"/>
       <c r="M240" s="29"/>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="29" t="s">
         <v>536</v>
       </c>
@@ -25630,7 +25624,7 @@
       <c r="L241" s="31"/>
       <c r="M241" s="29"/>
     </row>
-    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="29" t="s">
         <v>615</v>
       </c>
@@ -25663,7 +25657,7 @@
       <c r="L242" s="31"/>
       <c r="M242" s="29"/>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="29" t="s">
         <v>550</v>
       </c>
@@ -25688,7 +25682,7 @@
       <c r="L243" s="31"/>
       <c r="M243" s="29"/>
     </row>
-    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="29" t="s">
         <v>551</v>
       </c>
@@ -25717,7 +25711,7 @@
       <c r="L244" s="31"/>
       <c r="M244" s="29"/>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="29" t="s">
         <v>552</v>
       </c>
@@ -25746,7 +25740,7 @@
       <c r="L245" s="31"/>
       <c r="M245" s="29"/>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="29" t="s">
         <v>553</v>
       </c>
@@ -25775,7 +25769,7 @@
       <c r="L246" s="31"/>
       <c r="M246" s="29"/>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="29" t="s">
         <v>616</v>
       </c>
@@ -25806,7 +25800,7 @@
       <c r="L247" s="31"/>
       <c r="M247" s="29"/>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="29" t="s">
         <v>633</v>
       </c>
@@ -25837,7 +25831,7 @@
       <c r="L248" s="31"/>
       <c r="M248" s="29"/>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="31" t="s">
         <v>635</v>
       </c>
@@ -25872,7 +25866,7 @@
       <c r="L249" s="31"/>
       <c r="M249" s="29"/>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="29" t="s">
         <v>630</v>
       </c>
@@ -25905,7 +25899,7 @@
       <c r="L250" s="31"/>
       <c r="M250" s="29"/>
     </row>
-    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="29" t="s">
         <v>617</v>
       </c>
@@ -25936,7 +25930,7 @@
       <c r="L251" s="31"/>
       <c r="M251" s="29"/>
     </row>
-    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="29" t="s">
         <v>618</v>
       </c>
@@ -25971,7 +25965,7 @@
       <c r="L252" s="31"/>
       <c r="M252" s="29"/>
     </row>
-    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="29" t="s">
         <v>620</v>
       </c>
@@ -26004,7 +25998,7 @@
       <c r="L253" s="31"/>
       <c r="M253" s="29"/>
     </row>
-    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="29" t="s">
         <v>556</v>
       </c>
@@ -26033,7 +26027,7 @@
       <c r="L254" s="31"/>
       <c r="M254" s="29"/>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="29" t="s">
         <v>557</v>
       </c>
@@ -26060,7 +26054,7 @@
       <c r="L255" s="31"/>
       <c r="M255" s="29"/>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="29" t="s">
         <v>558</v>
       </c>
@@ -26087,7 +26081,7 @@
       <c r="L256" s="31"/>
       <c r="M256" s="29"/>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="29" t="s">
         <v>643</v>
       </c>
@@ -26114,7 +26108,7 @@
       <c r="L257" s="31"/>
       <c r="M257" s="29"/>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="29" t="s">
         <v>583</v>
       </c>
@@ -26139,7 +26133,7 @@
       <c r="L258" s="31"/>
       <c r="M258" s="29"/>
     </row>
-    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="29" t="s">
         <v>589</v>
       </c>
@@ -26172,7 +26166,7 @@
       <c r="L259" s="31"/>
       <c r="M259" s="29"/>
     </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="29" t="s">
         <v>582</v>
       </c>
@@ -26199,7 +26193,7 @@
       <c r="L260" s="31"/>
       <c r="M260" s="29"/>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="29" t="s">
         <v>581</v>
       </c>
@@ -26226,7 +26220,7 @@
       <c r="L261" s="31"/>
       <c r="M261" s="29"/>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="29" t="s">
         <v>580</v>
       </c>
@@ -26253,7 +26247,7 @@
       <c r="L262" s="31"/>
       <c r="M262" s="29"/>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="29" t="s">
         <v>586</v>
       </c>
@@ -26286,7 +26280,7 @@
       <c r="L263" s="31"/>
       <c r="M263" s="29"/>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="29" t="s">
         <v>587</v>
       </c>
@@ -26319,7 +26313,7 @@
       <c r="L264" s="31"/>
       <c r="M264" s="29"/>
     </row>
-    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="29" t="s">
         <v>588</v>
       </c>
@@ -26352,7 +26346,7 @@
       <c r="L265" s="31"/>
       <c r="M265" s="29"/>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="29" t="s">
         <v>579</v>
       </c>
@@ -26377,7 +26371,7 @@
       <c r="L266" s="31"/>
       <c r="M266" s="29"/>
     </row>
-    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="29" t="s">
         <v>578</v>
       </c>
@@ -26402,7 +26396,7 @@
       <c r="L267" s="31"/>
       <c r="M267" s="29"/>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="29" t="s">
         <v>591</v>
       </c>
@@ -26437,7 +26431,7 @@
       <c r="L268" s="31"/>
       <c r="M268" s="29"/>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="29" t="s">
         <v>592</v>
       </c>
@@ -26468,7 +26462,7 @@
       <c r="L269" s="31"/>
       <c r="M269" s="29"/>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="29" t="s">
         <v>595</v>
       </c>
@@ -26497,7 +26491,7 @@
       <c r="L270" s="31"/>
       <c r="M270" s="29"/>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="29" t="s">
         <v>609</v>
       </c>
@@ -26526,7 +26520,7 @@
       <c r="L271" s="31"/>
       <c r="M271" s="29"/>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="29" t="s">
         <v>610</v>
       </c>
@@ -26555,7 +26549,7 @@
       <c r="L272" s="31"/>
       <c r="M272" s="29"/>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="29" t="s">
         <v>611</v>
       </c>
@@ -26584,7 +26578,7 @@
       <c r="L273" s="31"/>
       <c r="M273" s="29"/>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="29" t="s">
         <v>612</v>
       </c>
@@ -26613,7 +26607,7 @@
       <c r="L274" s="31"/>
       <c r="M274" s="29"/>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="29" t="s">
         <v>613</v>
       </c>
@@ -26642,7 +26636,7 @@
       <c r="L275" s="31"/>
       <c r="M275" s="29"/>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="29" t="s">
         <v>614</v>
       </c>
@@ -26671,7 +26665,7 @@
       <c r="L276" s="31"/>
       <c r="M276" s="29"/>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="29" t="s">
         <v>625</v>
       </c>
@@ -26702,7 +26696,7 @@
       <c r="L277" s="31"/>
       <c r="M277" s="29"/>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="29" t="s">
         <v>626</v>
       </c>
@@ -26731,7 +26725,7 @@
       <c r="L278" s="31"/>
       <c r="M278" s="29"/>
     </row>
-    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="29" t="s">
         <v>644</v>
       </c>
@@ -26758,7 +26752,7 @@
       <c r="L279" s="31"/>
       <c r="M279" s="29"/>
     </row>
-    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="29" t="s">
         <v>646</v>
       </c>
@@ -26783,7 +26777,7 @@
       <c r="L280" s="31"/>
       <c r="M280" s="29"/>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="29" t="s">
         <v>648</v>
       </c>
@@ -26808,7 +26802,7 @@
       <c r="L281" s="31"/>
       <c r="M281" s="29"/>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="29" t="s">
         <v>650</v>
       </c>
@@ -26833,7 +26827,7 @@
       <c r="L282" s="31"/>
       <c r="M282" s="29"/>
     </row>
-    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="29" t="s">
         <v>651</v>
       </c>
@@ -26860,7 +26854,7 @@
       <c r="L283" s="31"/>
       <c r="M283" s="29"/>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="29" t="s">
         <v>655</v>
       </c>
@@ -26887,7 +26881,7 @@
       <c r="L284" s="31"/>
       <c r="M284" s="29"/>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="29" t="s">
         <v>656</v>
       </c>
@@ -26914,7 +26908,7 @@
       <c r="L285" s="31"/>
       <c r="M285" s="29"/>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="29" t="s">
         <v>670</v>
       </c>
@@ -26947,7 +26941,7 @@
       <c r="L286" s="31"/>
       <c r="M286" s="29"/>
     </row>
-    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="29" t="s">
         <v>657</v>
       </c>
@@ -26974,7 +26968,7 @@
       <c r="L287" s="31"/>
       <c r="M287" s="29"/>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="29" t="s">
         <v>660</v>
       </c>
@@ -27001,7 +26995,7 @@
       <c r="L288" s="31"/>
       <c r="M288" s="29"/>
     </row>
-    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="29" t="s">
         <v>663</v>
       </c>
@@ -27026,7 +27020,7 @@
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="29" t="s">
         <v>664</v>
       </c>
@@ -27053,7 +27047,7 @@
       <c r="L290" s="31"/>
       <c r="M290" s="29"/>
     </row>
-    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="29" t="s">
         <v>666</v>
       </c>
@@ -27080,7 +27074,7 @@
       <c r="L291" s="31"/>
       <c r="M291" s="29"/>
     </row>
-    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="29" t="s">
         <v>667</v>
       </c>
@@ -27109,7 +27103,7 @@
       <c r="L292" s="31"/>
       <c r="M292" s="29"/>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="29" t="s">
         <v>669</v>
       </c>
@@ -27148,7 +27142,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="29" t="s">
         <v>675</v>
       </c>
@@ -27175,7 +27169,7 @@
       <c r="L294" s="31"/>
       <c r="M294" s="29"/>
     </row>
-    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="29" t="s">
         <v>677</v>
       </c>
@@ -27208,7 +27202,7 @@
       <c r="L295" s="31"/>
       <c r="M295" s="29"/>
     </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="31" t="s">
         <v>682</v>
       </c>
@@ -27241,7 +27235,7 @@
       <c r="L296" s="31"/>
       <c r="M296" s="29"/>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="29" t="s">
         <v>683</v>
       </c>
@@ -27272,7 +27266,7 @@
       <c r="L297" s="31"/>
       <c r="M297" s="29"/>
     </row>
-    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="29" t="s">
         <v>690</v>
       </c>
@@ -27297,7 +27291,7 @@
       <c r="L298" s="31"/>
       <c r="M298" s="29"/>
     </row>
-    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="45" t="s">
         <v>692</v>
       </c>
@@ -27324,7 +27318,7 @@
       <c r="L299" s="31"/>
       <c r="M299" s="29"/>
     </row>
-    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="46" t="s">
         <v>693</v>
       </c>
@@ -27359,7 +27353,7 @@
       <c r="L300" s="31"/>
       <c r="M300" s="29"/>
     </row>
-    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="48" t="s">
         <v>694</v>
       </c>
@@ -27394,7 +27388,7 @@
       <c r="L301" s="31"/>
       <c r="M301" s="29"/>
     </row>
-    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="39" t="s">
         <v>695</v>
       </c>
@@ -27421,7 +27415,7 @@
       <c r="L302" s="31"/>
       <c r="M302" s="29"/>
     </row>
-    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="29" t="s">
         <v>706</v>
       </c>
@@ -27452,7 +27446,7 @@
       <c r="L303" s="31"/>
       <c r="M303" s="29"/>
     </row>
-    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="29" t="s">
         <v>707</v>
       </c>
@@ -27485,7 +27479,7 @@
       <c r="L304" s="31"/>
       <c r="M304" s="29"/>
     </row>
-    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="29" t="s">
         <v>709</v>
       </c>
@@ -27516,7 +27510,7 @@
       <c r="L305" s="31"/>
       <c r="M305" s="29"/>
     </row>
-    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="39" t="s">
         <v>711</v>
       </c>
@@ -27543,7 +27537,7 @@
       <c r="L306" s="31"/>
       <c r="M306" s="29"/>
     </row>
-    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="46" t="s">
         <v>749</v>
       </c>
@@ -27568,7 +27562,7 @@
       <c r="L307" s="31"/>
       <c r="M307" s="29"/>
     </row>
-    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="45" t="s">
         <v>748</v>
       </c>
@@ -27593,7 +27587,7 @@
       <c r="L308" s="31"/>
       <c r="M308" s="29"/>
     </row>
-    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="48" t="s">
         <v>750</v>
       </c>
@@ -27618,7 +27612,7 @@
       <c r="L309" s="31"/>
       <c r="M309" s="29"/>
     </row>
-    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="29" t="s">
         <v>714</v>
       </c>
@@ -27645,7 +27639,7 @@
       <c r="L310" s="31"/>
       <c r="M310" s="29"/>
     </row>
-    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="29" t="s">
         <v>715</v>
       </c>
@@ -27672,7 +27666,7 @@
       <c r="L311" s="31"/>
       <c r="M311" s="29"/>
     </row>
-    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="29" t="s">
         <v>717</v>
       </c>
@@ -27699,7 +27693,7 @@
       <c r="L312" s="31"/>
       <c r="M312" s="29"/>
     </row>
-    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="29" t="s">
         <v>726</v>
       </c>
@@ -27738,7 +27732,7 @@
       </c>
       <c r="M313" s="29"/>
     </row>
-    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="29" t="s">
         <v>729</v>
       </c>
@@ -27777,7 +27771,7 @@
       </c>
       <c r="M314" s="29"/>
     </row>
-    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="29" t="s">
         <v>734</v>
       </c>
@@ -27812,7 +27806,7 @@
       <c r="L315" s="31"/>
       <c r="M315" s="29"/>
     </row>
-    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="29" t="s">
         <v>736</v>
       </c>
@@ -27847,7 +27841,7 @@
       <c r="L316" s="31"/>
       <c r="M316" s="29"/>
     </row>
-    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="29" t="s">
         <v>738</v>
       </c>
@@ -27880,7 +27874,7 @@
       <c r="L317" s="31"/>
       <c r="M317" s="29"/>
     </row>
-    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="29" t="s">
         <v>740</v>
       </c>
@@ -27907,7 +27901,7 @@
       <c r="L318" s="31"/>
       <c r="M318" s="29"/>
     </row>
-    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="29" t="s">
         <v>743</v>
       </c>
@@ -27934,7 +27928,7 @@
       <c r="L319" s="31"/>
       <c r="M319" s="29"/>
     </row>
-    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="29" t="s">
         <v>760</v>
       </c>
@@ -27967,7 +27961,7 @@
       <c r="L320" s="31"/>
       <c r="M320" s="29"/>
     </row>
-    <row r="321" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A321" s="29" t="s">
         <v>766</v>
       </c>
@@ -27992,7 +27986,7 @@
       <c r="L321" s="31"/>
       <c r="M321" s="29"/>
     </row>
-    <row r="322" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A322" s="29" t="s">
         <v>767</v>
       </c>
@@ -28025,7 +28019,7 @@
       <c r="L322" s="31"/>
       <c r="M322" s="29"/>
     </row>
-    <row r="323" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A323" s="29" t="s">
         <v>773</v>
       </c>
@@ -28060,7 +28054,7 @@
       <c r="L323" s="31"/>
       <c r="M323" s="29"/>
     </row>
-    <row r="324" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A324" s="29" t="s">
         <v>775</v>
       </c>
@@ -28087,7 +28081,7 @@
       <c r="L324" s="31"/>
       <c r="M324" s="29"/>
     </row>
-    <row r="325" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A325" s="29" t="s">
         <v>778</v>
       </c>
@@ -28122,7 +28116,7 @@
       </c>
       <c r="M325" s="29"/>
     </row>
-    <row r="326" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A326" s="29" t="s">
         <v>781</v>
       </c>
@@ -28151,7 +28145,7 @@
       </c>
       <c r="M326" s="29"/>
     </row>
-    <row r="327" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A327" s="29" t="s">
         <v>782</v>
       </c>
@@ -28188,7 +28182,7 @@
       </c>
       <c r="M327" s="29"/>
     </row>
-    <row r="328" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A328" s="29" t="s">
         <v>783</v>
       </c>
@@ -28217,7 +28211,7 @@
       <c r="L328" s="31"/>
       <c r="M328" s="29"/>
     </row>
-    <row r="329" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A329" s="29" t="s">
         <v>787</v>
       </c>
@@ -28254,7 +28248,7 @@
       <c r="L329" s="31"/>
       <c r="M329" s="29"/>
     </row>
-    <row r="330" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A330" s="29" t="s">
         <v>792</v>
       </c>
@@ -28283,7 +28277,7 @@
       <c r="L330" s="31"/>
       <c r="M330" s="29"/>
     </row>
-    <row r="331" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A331" s="29" t="s">
         <v>801</v>
       </c>
@@ -28316,7 +28310,7 @@
       <c r="L331" s="31"/>
       <c r="M331" s="29"/>
     </row>
-    <row r="332" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A332" s="29" t="s">
         <v>802</v>
       </c>
@@ -28349,7 +28343,7 @@
       <c r="L332" s="31"/>
       <c r="M332" s="29"/>
     </row>
-    <row r="333" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A333" s="29" t="s">
         <v>816</v>
       </c>
@@ -28384,7 +28378,7 @@
       <c r="L333" s="31"/>
       <c r="M333" s="29"/>
     </row>
-    <row r="334" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A334" s="29" t="s">
         <v>805</v>
       </c>
@@ -28425,7 +28419,7 @@
       <c r="V334" s="4"/>
       <c r="W334" s="5"/>
     </row>
-    <row r="335" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A335" s="29" t="s">
         <v>809</v>
       </c>
@@ -28452,7 +28446,7 @@
       <c r="L335" s="31"/>
       <c r="M335" s="29"/>
     </row>
-    <row r="336" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A336" s="29" t="s">
         <v>810</v>
       </c>
@@ -28475,7 +28469,7 @@
       <c r="L336" s="31"/>
       <c r="M336" s="29"/>
     </row>
-    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="29" t="s">
         <v>812</v>
       </c>
@@ -28508,7 +28502,7 @@
       <c r="L337" s="31"/>
       <c r="M337" s="29"/>
     </row>
-    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="29" t="s">
         <v>804</v>
       </c>
@@ -28539,7 +28533,7 @@
       <c r="L338" s="31"/>
       <c r="M338" s="29"/>
     </row>
-    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="29" t="s">
         <v>819</v>
       </c>
@@ -28566,7 +28560,7 @@
       <c r="L339" s="31"/>
       <c r="M339" s="29"/>
     </row>
-    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="29" t="s">
         <v>855</v>
       </c>
@@ -28605,7 +28599,7 @@
       </c>
       <c r="M340" s="29"/>
     </row>
-    <row r="341" spans="1:13" s="9" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A341" s="45" t="s">
         <v>835</v>
       </c>
@@ -28636,7 +28630,7 @@
       <c r="L341" s="41"/>
       <c r="M341" s="45"/>
     </row>
-    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="29" t="s">
         <v>836</v>
       </c>
@@ -28667,7 +28661,7 @@
       <c r="L342" s="31"/>
       <c r="M342" s="29"/>
     </row>
-    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="29" t="s">
         <v>815</v>
       </c>
@@ -28700,7 +28694,7 @@
       <c r="L343" s="31"/>
       <c r="M343" s="29"/>
     </row>
-    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="29" t="s">
         <v>834</v>
       </c>
@@ -28733,7 +28727,7 @@
       <c r="L344" s="31"/>
       <c r="M344" s="29"/>
     </row>
-    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="29" t="s">
         <v>830</v>
       </c>
@@ -28772,7 +28766,7 @@
       </c>
       <c r="M345" s="29"/>
     </row>
-    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="29" t="s">
         <v>846</v>
       </c>
@@ -28805,7 +28799,7 @@
       <c r="L346" s="31"/>
       <c r="M346" s="29"/>
     </row>
-    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="29" t="s">
         <v>856</v>
       </c>
@@ -28830,7 +28824,7 @@
       <c r="L347" s="31"/>
       <c r="M347" s="29"/>
     </row>
-    <row r="348" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="29" t="s">
         <v>857</v>
       </c>
@@ -28855,7 +28849,7 @@
       <c r="L348" s="31"/>
       <c r="M348" s="29"/>
     </row>
-    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="29" t="s">
         <v>863</v>
       </c>
@@ -28886,7 +28880,7 @@
       <c r="L349" s="31"/>
       <c r="M349" s="29"/>
     </row>
-    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="29" t="s">
         <v>864</v>
       </c>
@@ -28917,7 +28911,7 @@
       <c r="L350" s="31"/>
       <c r="M350" s="29"/>
     </row>
-    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="29" t="s">
         <v>865</v>
       </c>
@@ -28948,7 +28942,7 @@
       <c r="L351" s="31"/>
       <c r="M351" s="29"/>
     </row>
-    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="29" t="s">
         <v>868</v>
       </c>
@@ -28979,7 +28973,7 @@
       <c r="L352" s="31"/>
       <c r="M352" s="29"/>
     </row>
-    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="29" t="s">
         <v>870</v>
       </c>
@@ -29010,7 +29004,7 @@
       <c r="L353" s="31"/>
       <c r="M353" s="29"/>
     </row>
-    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="29" t="s">
         <v>872</v>
       </c>
@@ -29041,7 +29035,7 @@
       <c r="L354" s="31"/>
       <c r="M354" s="29"/>
     </row>
-    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="29"/>
       <c r="B355" s="29" t="s">
         <v>860</v>
@@ -29070,7 +29064,7 @@
       <c r="L355" s="31"/>
       <c r="M355" s="29"/>
     </row>
-    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="29"/>
       <c r="B356" s="29" t="s">
         <v>860</v>
@@ -29099,7 +29093,7 @@
       <c r="L356" s="31"/>
       <c r="M356" s="29"/>
     </row>
-    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="29"/>
       <c r="B357" s="29" t="s">
         <v>860</v>
@@ -29128,7 +29122,7 @@
       <c r="L357" s="31"/>
       <c r="M357" s="29"/>
     </row>
-    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="29"/>
       <c r="B358" s="29" t="s">
         <v>860</v>
@@ -29157,7 +29151,7 @@
       <c r="L358" s="31"/>
       <c r="M358" s="29"/>
     </row>
-    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="29" t="s">
         <v>1009</v>
       </c>
@@ -29188,7 +29182,7 @@
       <c r="L359" s="31"/>
       <c r="M359" s="29"/>
     </row>
-    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="29" t="s">
         <v>1010</v>
       </c>
@@ -29219,7 +29213,7 @@
       <c r="L360" s="31"/>
       <c r="M360" s="29"/>
     </row>
-    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="29" t="s">
         <v>1011</v>
       </c>
@@ -29250,7 +29244,7 @@
       <c r="L361" s="31"/>
       <c r="M361" s="29"/>
     </row>
-    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="29" t="s">
         <v>1012</v>
       </c>
@@ -29281,7 +29275,7 @@
       <c r="L362" s="31"/>
       <c r="M362" s="29"/>
     </row>
-    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="29" t="s">
         <v>887</v>
       </c>
@@ -29312,7 +29306,7 @@
       <c r="L363" s="31"/>
       <c r="M363" s="29"/>
     </row>
-    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="29" t="s">
         <v>888</v>
       </c>
@@ -29343,7 +29337,7 @@
       <c r="L364" s="31"/>
       <c r="M364" s="29"/>
     </row>
-    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="29" t="s">
         <v>889</v>
       </c>
@@ -29374,7 +29368,7 @@
       <c r="L365" s="31"/>
       <c r="M365" s="29"/>
     </row>
-    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="29" t="s">
         <v>890</v>
       </c>
@@ -29405,7 +29399,7 @@
       <c r="L366" s="31"/>
       <c r="M366" s="29"/>
     </row>
-    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="29" t="s">
         <v>904</v>
       </c>
@@ -29430,7 +29424,7 @@
       <c r="L367" s="31"/>
       <c r="M367" s="29"/>
     </row>
-    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="29" t="s">
         <v>906</v>
       </c>
@@ -29457,7 +29451,7 @@
       <c r="L368" s="31"/>
       <c r="M368" s="29"/>
     </row>
-    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="29" t="s">
         <v>908</v>
       </c>
@@ -29482,7 +29476,7 @@
       <c r="L369" s="31"/>
       <c r="M369" s="29"/>
     </row>
-    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="29" t="s">
         <v>909</v>
       </c>
@@ -29509,7 +29503,7 @@
       <c r="L370" s="31"/>
       <c r="M370" s="29"/>
     </row>
-    <row r="371" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="29" t="s">
         <v>910</v>
       </c>
@@ -29534,7 +29528,7 @@
       <c r="L371" s="31"/>
       <c r="M371" s="29"/>
     </row>
-    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="29" t="s">
         <v>911</v>
       </c>
@@ -29559,7 +29553,7 @@
       <c r="L372" s="31"/>
       <c r="M372" s="29"/>
     </row>
-    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="29" t="s">
         <v>912</v>
       </c>
@@ -29594,7 +29588,7 @@
       <c r="L373" s="31"/>
       <c r="M373" s="29"/>
     </row>
-    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="29" t="s">
         <v>913</v>
       </c>
@@ -29627,7 +29621,7 @@
       <c r="L374" s="31"/>
       <c r="M374" s="29"/>
     </row>
-    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
         <v>914</v>
       </c>
@@ -29658,7 +29652,7 @@
       <c r="L375" s="31"/>
       <c r="M375" s="29"/>
     </row>
-    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
         <v>923</v>
       </c>
@@ -29689,7 +29683,7 @@
       <c r="L376" s="31"/>
       <c r="M376" s="29"/>
     </row>
-    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
         <v>926</v>
       </c>
@@ -29720,7 +29714,7 @@
       <c r="L377" s="31"/>
       <c r="M377" s="29"/>
     </row>
-    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
         <v>927</v>
       </c>
@@ -29751,7 +29745,7 @@
       <c r="L378" s="31"/>
       <c r="M378" s="29"/>
     </row>
-    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
         <v>928</v>
       </c>
@@ -29782,7 +29776,7 @@
       <c r="L379" s="31"/>
       <c r="M379" s="29"/>
     </row>
-    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
         <v>930</v>
       </c>
@@ -29813,7 +29807,7 @@
       <c r="L380" s="31"/>
       <c r="M380" s="29"/>
     </row>
-    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="29" t="s">
         <v>933</v>
       </c>
@@ -29844,7 +29838,7 @@
       <c r="L381" s="31"/>
       <c r="M381" s="29"/>
     </row>
-    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="29" t="s">
         <v>941</v>
       </c>
@@ -29875,7 +29869,7 @@
       <c r="L382" s="31"/>
       <c r="M382" s="29"/>
     </row>
-    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="29" t="s">
         <v>943</v>
       </c>
@@ -29908,7 +29902,7 @@
       <c r="L383" s="31"/>
       <c r="M383" s="29"/>
     </row>
-    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="29" t="s">
         <v>944</v>
       </c>
@@ -29941,7 +29935,7 @@
       <c r="L384" s="31"/>
       <c r="M384" s="29"/>
     </row>
-    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="29" t="s">
         <v>945</v>
       </c>
@@ -29974,7 +29968,7 @@
       <c r="L385" s="31"/>
       <c r="M385" s="29"/>
     </row>
-    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="29" t="s">
         <v>948</v>
       </c>
@@ -30005,7 +29999,7 @@
       <c r="L386" s="31"/>
       <c r="M386" s="29"/>
     </row>
-    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="29" t="s">
         <v>949</v>
       </c>
@@ -30036,7 +30030,7 @@
       <c r="L387" s="31"/>
       <c r="M387" s="29"/>
     </row>
-    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="29" t="s">
         <v>950</v>
       </c>
@@ -30067,7 +30061,7 @@
       <c r="L388" s="31"/>
       <c r="M388" s="29"/>
     </row>
-    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="29" t="s">
         <v>999</v>
       </c>
@@ -30094,7 +30088,7 @@
       <c r="L389" s="31"/>
       <c r="M389" s="29"/>
     </row>
-    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="29" t="s">
         <v>995</v>
       </c>
@@ -30121,7 +30115,7 @@
       <c r="L390" s="31"/>
       <c r="M390" s="29"/>
     </row>
-    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="29" t="s">
         <v>996</v>
       </c>
@@ -30148,7 +30142,7 @@
       <c r="L391" s="31"/>
       <c r="M391" s="29"/>
     </row>
-    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="29" t="s">
         <v>997</v>
       </c>
@@ -30175,7 +30169,7 @@
       <c r="L392" s="31"/>
       <c r="M392" s="29"/>
     </row>
-    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
         <v>998</v>
       </c>
@@ -30202,7 +30196,7 @@
       <c r="L393" s="31"/>
       <c r="M393" s="29"/>
     </row>
-    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
         <v>958</v>
       </c>
@@ -30229,7 +30223,7 @@
       <c r="L394" s="31"/>
       <c r="M394" s="29"/>
     </row>
-    <row r="395" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
         <v>959</v>
       </c>
@@ -30256,7 +30250,7 @@
       <c r="L395" s="31"/>
       <c r="M395" s="29"/>
     </row>
-    <row r="396" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
         <v>964</v>
       </c>
@@ -30279,7 +30273,7 @@
       <c r="L396" s="31"/>
       <c r="M396" s="29"/>
     </row>
-    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
         <v>965</v>
       </c>
@@ -30302,7 +30296,7 @@
       <c r="L397" s="31"/>
       <c r="M397" s="29"/>
     </row>
-    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
         <v>966</v>
       </c>
@@ -30325,7 +30319,7 @@
       <c r="L398" s="31"/>
       <c r="M398" s="29"/>
     </row>
-    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
         <v>975</v>
       </c>
@@ -30348,7 +30342,7 @@
       <c r="L399" s="31"/>
       <c r="M399" s="29"/>
     </row>
-    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
         <v>976</v>
       </c>
@@ -30371,7 +30365,7 @@
       <c r="L400" s="31"/>
       <c r="M400" s="29"/>
     </row>
-    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
         <v>977</v>
       </c>
@@ -30394,7 +30388,7 @@
       <c r="L401" s="31"/>
       <c r="M401" s="29"/>
     </row>
-    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
         <v>978</v>
       </c>
@@ -30417,7 +30411,7 @@
       <c r="L402" s="31"/>
       <c r="M402" s="29"/>
     </row>
-    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
         <v>979</v>
       </c>
@@ -30440,7 +30434,7 @@
       <c r="L403" s="31"/>
       <c r="M403" s="29"/>
     </row>
-    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
         <v>980</v>
       </c>
@@ -30463,7 +30457,7 @@
       <c r="L404" s="31"/>
       <c r="M404" s="29"/>
     </row>
-    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
         <v>981</v>
       </c>
@@ -30486,7 +30480,7 @@
       <c r="L405" s="31"/>
       <c r="M405" s="29"/>
     </row>
-    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
         <v>982</v>
       </c>
@@ -30509,7 +30503,7 @@
       <c r="L406" s="31"/>
       <c r="M406" s="29"/>
     </row>
-    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="29" t="s">
         <v>983</v>
       </c>
@@ -30532,7 +30526,7 @@
       <c r="L407" s="31"/>
       <c r="M407" s="29"/>
     </row>
-    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="29" t="s">
         <v>989</v>
       </c>
@@ -30561,7 +30555,7 @@
       <c r="L408" s="31"/>
       <c r="M408" s="29"/>
     </row>
-    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="29" t="s">
         <v>993</v>
       </c>
@@ -30596,7 +30590,7 @@
       <c r="L409" s="31"/>
       <c r="M409" s="29"/>
     </row>
-    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="29" t="s">
         <v>992</v>
       </c>
@@ -30629,7 +30623,7 @@
       <c r="L410" s="31"/>
       <c r="M410" s="29"/>
     </row>
-    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
         <v>990</v>
       </c>
@@ -30658,7 +30652,7 @@
       <c r="L411" s="31"/>
       <c r="M411" s="29"/>
     </row>
-    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
         <v>987</v>
       </c>
@@ -30683,7 +30677,7 @@
       <c r="L412" s="31"/>
       <c r="M412" s="29"/>
     </row>
-    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
         <v>1006</v>
       </c>
@@ -30708,7 +30702,7 @@
       <c r="L413" s="31"/>
       <c r="M413" s="29"/>
     </row>
-    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
         <v>1007</v>
       </c>
@@ -30733,7 +30727,7 @@
       <c r="L414" s="31"/>
       <c r="M414" s="29"/>
     </row>
-    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="29" t="s">
         <v>1008</v>
       </c>
@@ -30758,7 +30752,7 @@
       <c r="L415" s="31"/>
       <c r="M415" s="29"/>
     </row>
-    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="29" t="s">
         <v>1013</v>
       </c>
@@ -30787,7 +30781,7 @@
       </c>
       <c r="M416" s="29"/>
     </row>
-    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="29" t="s">
         <v>1014</v>
       </c>
@@ -30814,7 +30808,7 @@
       <c r="L417" s="31"/>
       <c r="M417" s="29"/>
     </row>
-    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="29" t="s">
         <v>1015</v>
       </c>
@@ -30841,7 +30835,7 @@
       <c r="L418" s="31"/>
       <c r="M418" s="29"/>
     </row>
-    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="29" t="s">
         <v>1016</v>
       </c>
@@ -30868,7 +30862,7 @@
       <c r="L419" s="31"/>
       <c r="M419" s="29"/>
     </row>
-    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="29" t="s">
         <v>1017</v>
       </c>
@@ -30895,7 +30889,7 @@
       <c r="L420" s="31"/>
       <c r="M420" s="29"/>
     </row>
-    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="29" t="s">
         <v>1021</v>
       </c>
@@ -30930,7 +30924,7 @@
       <c r="L421" s="31"/>
       <c r="M421" s="29"/>
     </row>
-    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="29" t="s">
         <v>1030</v>
       </c>
@@ -30967,7 +30961,7 @@
       <c r="L422" s="31"/>
       <c r="M422" s="29"/>
     </row>
-    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="29" t="s">
         <v>1033</v>
       </c>
@@ -30998,7 +30992,7 @@
       <c r="L423" s="31"/>
       <c r="M423" s="29"/>
     </row>
-    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="29" t="s">
         <v>1034</v>
       </c>
@@ -31035,7 +31029,7 @@
       <c r="L424" s="31"/>
       <c r="M424" s="29"/>
     </row>
-    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="29" t="s">
         <v>1038</v>
       </c>
@@ -31060,7 +31054,7 @@
       <c r="L425" s="31"/>
       <c r="M425" s="29"/>
     </row>
-    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="29" t="s">
         <v>1039</v>
       </c>
@@ -31091,7 +31085,7 @@
       <c r="L426" s="31"/>
       <c r="M426" s="29"/>
     </row>
-    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="29" t="s">
         <v>1040</v>
       </c>
@@ -31120,7 +31114,7 @@
       <c r="L427" s="31"/>
       <c r="M427" s="29"/>
     </row>
-    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="29" t="s">
         <v>1042</v>
       </c>
@@ -31151,7 +31145,7 @@
       <c r="L428" s="31"/>
       <c r="M428" s="29"/>
     </row>
-    <row r="429" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A429" s="29" t="s">
         <v>1043</v>
       </c>
@@ -31182,7 +31176,7 @@
       <c r="L429" s="31"/>
       <c r="M429" s="29"/>
     </row>
-    <row r="430" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A430" s="29" t="s">
         <v>1046</v>
       </c>
@@ -31219,7 +31213,7 @@
       </c>
       <c r="M430" s="29"/>
     </row>
-    <row r="431" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A431" s="29" t="s">
         <v>1350</v>
       </c>
@@ -31252,7 +31246,7 @@
       <c r="L431" s="31"/>
       <c r="M431" s="29"/>
     </row>
-    <row r="432" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A432" s="29" t="s">
         <v>1048</v>
       </c>
@@ -31281,7 +31275,7 @@
       </c>
       <c r="M432" s="29"/>
     </row>
-    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="29" t="s">
         <v>1051</v>
       </c>
@@ -31310,7 +31304,7 @@
       <c r="L433" s="31"/>
       <c r="M433" s="29"/>
     </row>
-    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="29" t="s">
         <v>1054</v>
       </c>
@@ -31339,7 +31333,7 @@
       <c r="L434" s="31"/>
       <c r="M434" s="29"/>
     </row>
-    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="29" t="s">
         <v>1057</v>
       </c>
@@ -31378,7 +31372,7 @@
       </c>
       <c r="M435" s="29"/>
     </row>
-    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="29" t="s">
         <v>1058</v>
       </c>
@@ -31417,7 +31411,7 @@
       </c>
       <c r="M436" s="29"/>
     </row>
-    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="29" t="s">
         <v>1059</v>
       </c>
@@ -31456,7 +31450,7 @@
       </c>
       <c r="M437" s="29"/>
     </row>
-    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
         <v>1065</v>
       </c>
@@ -31491,7 +31485,7 @@
       <c r="L438" s="31"/>
       <c r="M438" s="29"/>
     </row>
-    <row r="439" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
         <v>1066</v>
       </c>
@@ -31526,7 +31520,7 @@
       <c r="L439" s="31"/>
       <c r="M439" s="29"/>
     </row>
-    <row r="440" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="29" t="s">
         <v>1067</v>
       </c>
@@ -31561,7 +31555,7 @@
       <c r="L440" s="31"/>
       <c r="M440" s="29"/>
     </row>
-    <row r="441" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="29" t="s">
         <v>1343</v>
       </c>
@@ -31594,7 +31588,7 @@
       <c r="L441" s="31"/>
       <c r="M441" s="29"/>
     </row>
-    <row r="442" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
         <v>1344</v>
       </c>
@@ -31625,7 +31619,7 @@
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
-    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="29" t="s">
         <v>1345</v>
       </c>
@@ -31654,7 +31648,7 @@
       <c r="L443" s="31"/>
       <c r="M443" s="29"/>
     </row>
-    <row r="444" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
         <v>1346</v>
       </c>
@@ -31687,7 +31681,7 @@
       <c r="L444" s="31"/>
       <c r="M444" s="29"/>
     </row>
-    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
         <v>1347</v>
       </c>
@@ -31718,7 +31712,7 @@
       <c r="L445" s="31"/>
       <c r="M445" s="29"/>
     </row>
-    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
         <v>1348</v>
       </c>
@@ -31749,7 +31743,7 @@
       <c r="L446" s="31"/>
       <c r="M446" s="29"/>
     </row>
-    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
         <v>1349</v>
       </c>
@@ -31780,7 +31774,7 @@
       <c r="L447" s="31"/>
       <c r="M447" s="29"/>
     </row>
-    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="29" t="s">
         <v>1350</v>
       </c>
@@ -31811,7 +31805,7 @@
       <c r="L448" s="31"/>
       <c r="M448" s="29"/>
     </row>
-    <row r="449" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="29" t="s">
         <v>1351</v>
       </c>
@@ -31844,7 +31838,7 @@
       <c r="L449" s="31"/>
       <c r="M449" s="29"/>
     </row>
-    <row r="450" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="29" t="s">
         <v>1352</v>
       </c>
@@ -31875,7 +31869,7 @@
       <c r="L450" s="31"/>
       <c r="M450" s="29"/>
     </row>
-    <row r="451" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
         <v>1353</v>
       </c>
@@ -31906,7 +31900,7 @@
       <c r="L451" s="31"/>
       <c r="M451" s="29"/>
     </row>
-    <row r="452" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
         <v>1356</v>
       </c>
@@ -31937,7 +31931,7 @@
       <c r="L452" s="31"/>
       <c r="M452" s="29"/>
     </row>
-    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="29" t="s">
         <v>1069</v>
       </c>
@@ -31974,7 +31968,7 @@
       <c r="L453" s="31"/>
       <c r="M453" s="29"/>
     </row>
-    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A454" s="29" t="s">
         <v>1071</v>
       </c>
@@ -32011,7 +32005,7 @@
       <c r="L454" s="31"/>
       <c r="M454" s="29"/>
     </row>
-    <row r="455" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A455" s="29" t="s">
         <v>2379</v>
       </c>
@@ -32034,7 +32028,7 @@
       <c r="L455" s="31"/>
       <c r="M455" s="29"/>
     </row>
-    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="29" t="s">
         <v>1076</v>
       </c>
@@ -32059,7 +32053,7 @@
       <c r="L456" s="31"/>
       <c r="M456" s="29"/>
     </row>
-    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="34" t="s">
         <v>1177</v>
       </c>
@@ -32096,7 +32090,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="458" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="34" t="s">
         <v>1178</v>
       </c>
@@ -32133,7 +32127,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="459" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="34" t="s">
         <v>1179</v>
       </c>
@@ -32170,7 +32164,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="34" t="s">
         <v>1180</v>
       </c>
@@ -32207,7 +32201,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="461" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="34" t="s">
         <v>1181</v>
       </c>
@@ -32244,7 +32238,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="57" t="s">
         <v>1224</v>
       </c>
@@ -32281,7 +32275,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="463" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="57" t="s">
         <v>1186</v>
       </c>
@@ -32318,7 +32312,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="464" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="57" t="s">
         <v>1185</v>
       </c>
@@ -32355,7 +32349,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="29" t="s">
         <v>1182</v>
       </c>
@@ -32392,7 +32386,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="29" t="s">
         <v>1183</v>
       </c>
@@ -32429,7 +32423,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="29" t="s">
         <v>1184</v>
       </c>
@@ -32466,7 +32460,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="468" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="21" t="s">
         <v>13</v>
       </c>
@@ -32497,7 +32491,7 @@
       <c r="L468" s="31"/>
       <c r="M468" s="29"/>
     </row>
-    <row r="469" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="21" t="s">
         <v>14</v>
       </c>
@@ -32528,7 +32522,7 @@
       <c r="L469" s="31"/>
       <c r="M469" s="29"/>
     </row>
-    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="21" t="s">
         <v>18</v>
       </c>
@@ -32559,7 +32553,7 @@
       <c r="L470" s="31"/>
       <c r="M470" s="29"/>
     </row>
-    <row r="471" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="21" t="s">
         <v>15</v>
       </c>
@@ -32590,7 +32584,7 @@
       <c r="L471" s="31"/>
       <c r="M471" s="29"/>
     </row>
-    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
         <v>1104</v>
       </c>
@@ -32621,7 +32615,7 @@
       <c r="L472" s="31"/>
       <c r="M472" s="29"/>
     </row>
-    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="21" t="s">
         <v>16</v>
       </c>
@@ -32652,7 +32646,7 @@
       <c r="L473" s="31"/>
       <c r="M473" s="29"/>
     </row>
-    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
         <v>1105</v>
       </c>
@@ -32679,7 +32673,7 @@
       <c r="L474" s="31"/>
       <c r="M474" s="29"/>
     </row>
-    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="21" t="s">
         <v>17</v>
       </c>
@@ -32716,7 +32710,7 @@
       <c r="L475" s="31"/>
       <c r="M475" s="29"/>
     </row>
-    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29"/>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -32731,7 +32725,7 @@
       <c r="L476" s="31"/>
       <c r="M476" s="29"/>
     </row>
-    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="29" t="s">
         <v>1167</v>
       </c>
@@ -32768,7 +32762,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="478" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="29" t="s">
         <v>1168</v>
       </c>
@@ -32805,7 +32799,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="29" t="s">
         <v>1169</v>
       </c>
@@ -32842,7 +32836,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="29" t="s">
         <v>1170</v>
       </c>
@@ -32879,7 +32873,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="29" t="s">
         <v>1171</v>
       </c>
@@ -32916,7 +32910,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="29" t="s">
         <v>1172</v>
       </c>
@@ -32953,7 +32947,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="483" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="29" t="s">
         <v>1173</v>
       </c>
@@ -32990,7 +32984,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="484" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="29" t="s">
         <v>1174</v>
       </c>
@@ -33027,7 +33021,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="485" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="29" t="s">
         <v>1175</v>
       </c>
@@ -33064,7 +33058,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="486" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="29" t="s">
         <v>1176</v>
       </c>
@@ -33101,7 +33095,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="29" t="s">
         <v>2225</v>
       </c>
@@ -33132,7 +33126,7 @@
       <c r="L487" s="31"/>
       <c r="M487" s="29"/>
     </row>
-    <row r="488" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A488" s="29"/>
       <c r="B488" s="29"/>
       <c r="C488" s="53"/>
@@ -33147,7 +33141,7 @@
       <c r="L488" s="31"/>
       <c r="M488" s="29"/>
     </row>
-    <row r="489" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A489" s="105"/>
       <c r="B489" s="105"/>
       <c r="C489" s="73"/>
@@ -33162,7 +33156,7 @@
       <c r="L489" s="31"/>
       <c r="M489" s="29"/>
     </row>
-    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="29" t="s">
         <v>2226</v>
       </c>
@@ -33193,7 +33187,7 @@
       <c r="L490" s="31"/>
       <c r="M490" s="29"/>
     </row>
-    <row r="491" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
         <v>1106</v>
       </c>
@@ -33222,7 +33216,7 @@
       <c r="L491" s="31"/>
       <c r="M491" s="29"/>
     </row>
-    <row r="492" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="29" t="s">
         <v>1107</v>
       </c>
@@ -33249,7 +33243,7 @@
       <c r="L492" s="31"/>
       <c r="M492" s="29"/>
     </row>
-    <row r="493" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="29" t="s">
         <v>1223</v>
       </c>
@@ -33284,7 +33278,7 @@
       <c r="L493" s="31"/>
       <c r="M493" s="29"/>
     </row>
-    <row r="494" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="29" t="s">
         <v>1221</v>
       </c>
@@ -33321,7 +33315,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="29" t="s">
         <v>1225</v>
       </c>
@@ -33358,7 +33352,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="496" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="29" t="s">
         <v>1222</v>
       </c>
@@ -33395,7 +33389,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="497" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A497" s="57" t="s">
         <v>1226</v>
       </c>
@@ -33432,7 +33426,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="498" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="57" t="s">
         <v>1227</v>
       </c>
@@ -33469,7 +33463,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="499" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A499" s="34" t="s">
         <v>1205</v>
       </c>
@@ -33494,7 +33488,7 @@
       <c r="L499" s="31"/>
       <c r="M499" s="29"/>
     </row>
-    <row r="500" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A500" s="60" t="s">
         <v>1228</v>
       </c>
@@ -33529,7 +33523,7 @@
       <c r="L500" s="31"/>
       <c r="M500" s="29"/>
     </row>
-    <row r="501" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A501" s="29" t="s">
         <v>1229</v>
       </c>
@@ -33558,7 +33552,7 @@
       <c r="L501" s="31"/>
       <c r="M501" s="29"/>
     </row>
-    <row r="502" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A502" s="29" t="s">
         <v>1237</v>
       </c>
@@ -33587,7 +33581,7 @@
       <c r="L502" s="31"/>
       <c r="M502" s="29"/>
     </row>
-    <row r="503" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A503" s="34" t="s">
         <v>1236</v>
       </c>
@@ -33624,7 +33618,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="504" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A504" s="29" t="s">
         <v>320</v>
       </c>
@@ -33659,7 +33653,7 @@
       <c r="L504" s="31"/>
       <c r="M504" s="29"/>
     </row>
-    <row r="505" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A505" s="34" t="s">
         <v>1238</v>
       </c>
@@ -33698,7 +33692,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="506" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A506" s="34" t="s">
         <v>1242</v>
       </c>
@@ -33735,7 +33729,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="507" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A507" s="34" t="s">
         <v>1244</v>
       </c>
@@ -33772,7 +33766,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="508" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
         <v>1248</v>
       </c>
@@ -33811,7 +33805,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="509" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="34" t="s">
         <v>1110</v>
       </c>
@@ -33838,7 +33832,7 @@
       <c r="L509" s="31"/>
       <c r="M509" s="29"/>
     </row>
-    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="24" t="s">
         <v>1111</v>
       </c>
@@ -33865,7 +33859,7 @@
       <c r="L510" s="31"/>
       <c r="M510" s="29"/>
     </row>
-    <row r="511" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="29" t="s">
         <v>1112</v>
       </c>
@@ -33902,7 +33896,7 @@
       </c>
       <c r="M511" s="29"/>
     </row>
-    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="29" t="s">
         <v>1113</v>
       </c>
@@ -33929,7 +33923,7 @@
       </c>
       <c r="M512" s="29"/>
     </row>
-    <row r="513" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="29" t="s">
         <v>1114</v>
       </c>
@@ -33956,7 +33950,7 @@
       </c>
       <c r="M513" s="29"/>
     </row>
-    <row r="514" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="29" t="s">
         <v>1115</v>
       </c>
@@ -33985,7 +33979,7 @@
       </c>
       <c r="M514" s="29"/>
     </row>
-    <row r="515" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="29" t="s">
         <v>1120</v>
       </c>
@@ -34022,7 +34016,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="516" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="29" t="s">
         <v>1121</v>
       </c>
@@ -34162,7 +34156,7 @@
       <c r="L519" s="31"/>
       <c r="M519" s="29"/>
     </row>
-    <row r="520" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="31" t="s">
         <v>1131</v>
       </c>
@@ -34197,7 +34191,7 @@
       <c r="L520" s="31"/>
       <c r="M520" s="29"/>
     </row>
-    <row r="521" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="31" t="s">
         <v>1132</v>
       </c>
@@ -34232,7 +34226,7 @@
       <c r="L521" s="31"/>
       <c r="M521" s="29"/>
     </row>
-    <row r="522" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="31" t="s">
         <v>1133</v>
       </c>
@@ -34267,7 +34261,7 @@
       <c r="L522" s="31"/>
       <c r="M522" s="29"/>
     </row>
-    <row r="523" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="29" t="s">
         <v>1135</v>
       </c>
@@ -34302,7 +34296,7 @@
       <c r="L523" s="31"/>
       <c r="M523" s="29"/>
     </row>
-    <row r="524" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A524" s="29" t="s">
         <v>1138</v>
       </c>
@@ -34337,7 +34331,7 @@
       <c r="L524" s="31"/>
       <c r="M524" s="29"/>
     </row>
-    <row r="525" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A525" s="29" t="s">
         <v>1832</v>
       </c>
@@ -34374,7 +34368,7 @@
       <c r="L525" s="31"/>
       <c r="M525" s="29"/>
     </row>
-    <row r="526" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A526" s="29" t="s">
         <v>1833</v>
       </c>
@@ -34411,7 +34405,7 @@
       <c r="L526" s="31"/>
       <c r="M526" s="29"/>
     </row>
-    <row r="527" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A527" s="29" t="s">
         <v>1834</v>
       </c>
@@ -34448,7 +34442,7 @@
       <c r="L527" s="31"/>
       <c r="M527" s="29"/>
     </row>
-    <row r="528" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A528" s="29" t="s">
         <v>1835</v>
       </c>
@@ -34485,7 +34479,7 @@
       <c r="L528" s="31"/>
       <c r="M528" s="29"/>
     </row>
-    <row r="529" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A529" s="29" t="s">
         <v>1836</v>
       </c>
@@ -34522,7 +34516,7 @@
       <c r="L529" s="31"/>
       <c r="M529" s="29"/>
     </row>
-    <row r="530" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A530" s="29" t="s">
         <v>1837</v>
       </c>
@@ -34559,7 +34553,7 @@
       <c r="L530" s="31"/>
       <c r="M530" s="29"/>
     </row>
-    <row r="531" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A531" s="29" t="s">
         <v>1838</v>
       </c>
@@ -34596,7 +34590,7 @@
       <c r="L531" s="31"/>
       <c r="M531" s="29"/>
     </row>
-    <row r="532" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A532" s="29" t="s">
         <v>1839</v>
       </c>
@@ -34633,7 +34627,7 @@
       <c r="L532" s="31"/>
       <c r="M532" s="29"/>
     </row>
-    <row r="533" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A533" s="29" t="s">
         <v>1840</v>
       </c>
@@ -34670,7 +34664,7 @@
       <c r="L533" s="31"/>
       <c r="M533" s="29"/>
     </row>
-    <row r="534" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A534" s="29" t="s">
         <v>1841</v>
       </c>
@@ -34707,7 +34701,7 @@
       <c r="L534" s="31"/>
       <c r="M534" s="29"/>
     </row>
-    <row r="535" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A535" s="29" t="s">
         <v>1842</v>
       </c>
@@ -34744,7 +34738,7 @@
       <c r="L535" s="31"/>
       <c r="M535" s="29"/>
     </row>
-    <row r="536" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A536" s="29" t="s">
         <v>1843</v>
       </c>
@@ -34781,7 +34775,7 @@
       <c r="L536" s="31"/>
       <c r="M536" s="29"/>
     </row>
-    <row r="537" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A537" s="29" t="s">
         <v>1844</v>
       </c>
@@ -34818,7 +34812,7 @@
       <c r="L537" s="31"/>
       <c r="M537" s="29"/>
     </row>
-    <row r="538" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A538" s="29" t="s">
         <v>1199</v>
       </c>
@@ -34849,7 +34843,7 @@
       <c r="L538" s="31"/>
       <c r="M538" s="29"/>
     </row>
-    <row r="539" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A539" s="29" t="s">
         <v>1250</v>
       </c>
@@ -34872,7 +34866,7 @@
       <c r="L539" s="31"/>
       <c r="M539" s="29"/>
     </row>
-    <row r="540" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A540" s="29" t="s">
         <v>1209</v>
       </c>
@@ -34907,7 +34901,7 @@
       <c r="L540" s="31"/>
       <c r="M540" s="29"/>
     </row>
-    <row r="541" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="34" t="s">
         <v>1187</v>
       </c>
@@ -34942,7 +34936,7 @@
       <c r="L541" s="31"/>
       <c r="M541" s="29"/>
     </row>
-    <row r="542" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="29" t="s">
         <v>1197</v>
       </c>
@@ -34973,7 +34967,7 @@
       <c r="L542" s="31"/>
       <c r="M542" s="29"/>
     </row>
-    <row r="543" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="29" t="s">
         <v>1258</v>
       </c>
@@ -35002,7 +34996,7 @@
       <c r="L543" s="31"/>
       <c r="M543" s="29"/>
     </row>
-    <row r="544" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="29" t="s">
         <v>1259</v>
       </c>
@@ -35031,7 +35025,7 @@
       <c r="L544" s="31"/>
       <c r="M544" s="29"/>
     </row>
-    <row r="545" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A545" s="29" t="s">
         <v>1263</v>
       </c>
@@ -35060,7 +35054,7 @@
       <c r="L545" s="31"/>
       <c r="M545" s="29"/>
     </row>
-    <row r="546" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A546" s="29" t="s">
         <v>1715</v>
       </c>
@@ -35089,7 +35083,7 @@
       <c r="L546" s="31"/>
       <c r="M546" s="29"/>
     </row>
-    <row r="547" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A547" s="29" t="s">
         <v>1716</v>
       </c>
@@ -35118,7 +35112,7 @@
       <c r="L547" s="31"/>
       <c r="M547" s="29"/>
     </row>
-    <row r="548" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A548" s="29" t="s">
         <v>1717</v>
       </c>
@@ -35147,7 +35141,7 @@
       <c r="L548" s="31"/>
       <c r="M548" s="29"/>
     </row>
-    <row r="549" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A549" s="29" t="s">
         <v>1718</v>
       </c>
@@ -35176,7 +35170,7 @@
       <c r="L549" s="31"/>
       <c r="M549" s="29"/>
     </row>
-    <row r="550" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A550" s="29" t="s">
         <v>1719</v>
       </c>
@@ -35205,7 +35199,7 @@
       <c r="L550" s="31"/>
       <c r="M550" s="29"/>
     </row>
-    <row r="551" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A551" s="29" t="s">
         <v>1720</v>
       </c>
@@ -35234,7 +35228,7 @@
       <c r="L551" s="31"/>
       <c r="M551" s="29"/>
     </row>
-    <row r="552" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A552" s="29" t="s">
         <v>1721</v>
       </c>
@@ -35263,7 +35257,7 @@
       <c r="L552" s="31"/>
       <c r="M552" s="29"/>
     </row>
-    <row r="553" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A553" s="29" t="s">
         <v>1722</v>
       </c>
@@ -35292,7 +35286,7 @@
       <c r="L553" s="31"/>
       <c r="M553" s="29"/>
     </row>
-    <row r="554" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A554" s="29" t="s">
         <v>1723</v>
       </c>
@@ -35321,7 +35315,7 @@
       <c r="L554" s="31"/>
       <c r="M554" s="29"/>
     </row>
-    <row r="555" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A555" s="29" t="s">
         <v>1724</v>
       </c>
@@ -35350,7 +35344,7 @@
       <c r="L555" s="31"/>
       <c r="M555" s="29"/>
     </row>
-    <row r="556" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A556" s="29" t="s">
         <v>1385</v>
       </c>
@@ -35379,7 +35373,7 @@
       <c r="L556" s="31"/>
       <c r="M556" s="29"/>
     </row>
-    <row r="557" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A557" s="29" t="s">
         <v>1386</v>
       </c>
@@ -35408,7 +35402,7 @@
       <c r="L557" s="31"/>
       <c r="M557" s="29"/>
     </row>
-    <row r="558" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A558" s="29" t="s">
         <v>1387</v>
       </c>
@@ -35437,7 +35431,7 @@
       <c r="L558" s="31"/>
       <c r="M558" s="29"/>
     </row>
-    <row r="559" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A559" s="29" t="s">
         <v>1388</v>
       </c>
@@ -35466,7 +35460,7 @@
       <c r="L559" s="31"/>
       <c r="M559" s="29"/>
     </row>
-    <row r="560" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A560" s="29" t="s">
         <v>1389</v>
       </c>
@@ -35495,7 +35489,7 @@
       <c r="L560" s="31"/>
       <c r="M560" s="29"/>
     </row>
-    <row r="561" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A561" s="29" t="s">
         <v>1390</v>
       </c>
@@ -35524,7 +35518,7 @@
       <c r="L561" s="31"/>
       <c r="M561" s="29"/>
     </row>
-    <row r="562" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A562" s="29" t="s">
         <v>1391</v>
       </c>
@@ -35553,7 +35547,7 @@
       <c r="L562" s="31"/>
       <c r="M562" s="29"/>
     </row>
-    <row r="563" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A563" s="29" t="s">
         <v>1392</v>
       </c>
@@ -35582,7 +35576,7 @@
       <c r="L563" s="31"/>
       <c r="M563" s="29"/>
     </row>
-    <row r="564" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A564" s="29" t="s">
         <v>1393</v>
       </c>
@@ -35611,7 +35605,7 @@
       <c r="L564" s="31"/>
       <c r="M564" s="29"/>
     </row>
-    <row r="565" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A565" s="29" t="s">
         <v>1394</v>
       </c>
@@ -35640,7 +35634,7 @@
       <c r="L565" s="31"/>
       <c r="M565" s="29"/>
     </row>
-    <row r="566" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
         <v>1395</v>
       </c>
@@ -35669,7 +35663,7 @@
       <c r="L566" s="31"/>
       <c r="M566" s="29"/>
     </row>
-    <row r="567" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A567" s="29" t="s">
         <v>1749</v>
       </c>
@@ -35698,7 +35692,7 @@
       <c r="L567" s="31"/>
       <c r="M567" s="29"/>
     </row>
-    <row r="568" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A568" s="73" t="s">
         <v>1313</v>
       </c>
@@ -35731,7 +35725,7 @@
       <c r="L568" s="31"/>
       <c r="M568" s="29"/>
     </row>
-    <row r="569" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A569" s="73" t="s">
         <v>1314</v>
       </c>
@@ -35764,7 +35758,7 @@
       <c r="L569" s="31"/>
       <c r="M569" s="29"/>
     </row>
-    <row r="570" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A570" s="73" t="s">
         <v>1315</v>
       </c>
@@ -35797,7 +35791,7 @@
       <c r="L570" s="31"/>
       <c r="M570" s="29"/>
     </row>
-    <row r="571" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A571" s="73" t="s">
         <v>1316</v>
       </c>
@@ -35830,7 +35824,7 @@
       <c r="L571" s="31"/>
       <c r="M571" s="29"/>
     </row>
-    <row r="572" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A572" s="73" t="s">
         <v>1317</v>
       </c>
@@ -35863,7 +35857,7 @@
       <c r="L572" s="31"/>
       <c r="M572" s="29"/>
     </row>
-    <row r="573" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A573" s="73" t="s">
         <v>1318</v>
       </c>
@@ -35896,7 +35890,7 @@
       <c r="L573" s="31"/>
       <c r="M573" s="29"/>
     </row>
-    <row r="574" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A574" s="73" t="s">
         <v>1319</v>
       </c>
@@ -35929,7 +35923,7 @@
       <c r="L574" s="31"/>
       <c r="M574" s="29"/>
     </row>
-    <row r="575" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A575" s="73" t="s">
         <v>1320</v>
       </c>
@@ -35962,7 +35956,7 @@
       <c r="L575" s="31"/>
       <c r="M575" s="29"/>
     </row>
-    <row r="576" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A576" s="73" t="s">
         <v>1321</v>
       </c>
@@ -35995,7 +35989,7 @@
       <c r="L576" s="31"/>
       <c r="M576" s="29"/>
     </row>
-    <row r="577" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A577" s="73" t="s">
         <v>1322</v>
       </c>
@@ -36028,7 +36022,7 @@
       <c r="L577" s="31"/>
       <c r="M577" s="29"/>
     </row>
-    <row r="578" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A578" s="73" t="s">
         <v>1323</v>
       </c>
@@ -36061,7 +36055,7 @@
       <c r="L578" s="31"/>
       <c r="M578" s="29"/>
     </row>
-    <row r="579" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A579" s="29" t="s">
         <v>1368</v>
       </c>
@@ -36096,7 +36090,7 @@
       <c r="L579" s="31"/>
       <c r="M579" s="29"/>
     </row>
-    <row r="580" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A580" s="29" t="s">
         <v>1381</v>
       </c>
@@ -36129,7 +36123,7 @@
       <c r="L580" s="31"/>
       <c r="M580" s="29"/>
     </row>
-    <row r="581" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A581" s="29" t="s">
         <v>1382</v>
       </c>
@@ -36162,7 +36156,7 @@
       <c r="L581" s="31"/>
       <c r="M581" s="29"/>
     </row>
-    <row r="582" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A582" s="29" t="s">
         <v>1383</v>
       </c>
@@ -36193,7 +36187,7 @@
       <c r="L582" s="31"/>
       <c r="M582" s="29"/>
     </row>
-    <row r="583" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A583" s="29" t="s">
         <v>1384</v>
       </c>
@@ -36224,7 +36218,7 @@
       <c r="L583" s="31"/>
       <c r="M583" s="29"/>
     </row>
-    <row r="584" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A584" s="29" t="s">
         <v>1385</v>
       </c>
@@ -36255,7 +36249,7 @@
       <c r="L584" s="31"/>
       <c r="M584" s="29"/>
     </row>
-    <row r="585" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A585" s="29" t="s">
         <v>1386</v>
       </c>
@@ -36286,7 +36280,7 @@
       <c r="L585" s="31"/>
       <c r="M585" s="29"/>
     </row>
-    <row r="586" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A586" s="29" t="s">
         <v>1387</v>
       </c>
@@ -36317,7 +36311,7 @@
       <c r="L586" s="31"/>
       <c r="M586" s="29"/>
     </row>
-    <row r="587" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A587" s="29" t="s">
         <v>1388</v>
       </c>
@@ -36348,7 +36342,7 @@
       <c r="L587" s="31"/>
       <c r="M587" s="29"/>
     </row>
-    <row r="588" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A588" s="29" t="s">
         <v>1389</v>
       </c>
@@ -36379,7 +36373,7 @@
       <c r="L588" s="31"/>
       <c r="M588" s="29"/>
     </row>
-    <row r="589" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A589" s="29" t="s">
         <v>1390</v>
       </c>
@@ -36410,7 +36404,7 @@
       <c r="L589" s="31"/>
       <c r="M589" s="29"/>
     </row>
-    <row r="590" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A590" s="29" t="s">
         <v>1391</v>
       </c>
@@ -36441,7 +36435,7 @@
       <c r="L590" s="31"/>
       <c r="M590" s="29"/>
     </row>
-    <row r="591" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A591" s="29" t="s">
         <v>1392</v>
       </c>
@@ -36472,7 +36466,7 @@
       <c r="L591" s="31"/>
       <c r="M591" s="29"/>
     </row>
-    <row r="592" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A592" s="29" t="s">
         <v>1393</v>
       </c>
@@ -36503,7 +36497,7 @@
       <c r="L592" s="31"/>
       <c r="M592" s="29"/>
     </row>
-    <row r="593" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A593" s="29" t="s">
         <v>1394</v>
       </c>
@@ -36534,7 +36528,7 @@
       <c r="L593" s="31"/>
       <c r="M593" s="29"/>
     </row>
-    <row r="594" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A594" s="29" t="s">
         <v>1395</v>
       </c>
@@ -36565,7 +36559,7 @@
       <c r="L594" s="31"/>
       <c r="M594" s="29"/>
     </row>
-    <row r="595" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A595" s="29" t="s">
         <v>1396</v>
       </c>
@@ -36596,7 +36590,7 @@
       <c r="L595" s="31"/>
       <c r="M595" s="29"/>
     </row>
-    <row r="596" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A596" s="29" t="s">
         <v>1397</v>
       </c>
@@ -36627,7 +36621,7 @@
       <c r="L596" s="31"/>
       <c r="M596" s="29"/>
     </row>
-    <row r="597" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A597" s="29" t="s">
         <v>1398</v>
       </c>
@@ -36658,7 +36652,7 @@
       <c r="L597" s="31"/>
       <c r="M597" s="29"/>
     </row>
-    <row r="598" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A598" s="29" t="s">
         <v>1399</v>
       </c>
@@ -36689,7 +36683,7 @@
       <c r="L598" s="31"/>
       <c r="M598" s="29"/>
     </row>
-    <row r="599" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A599" s="29" t="s">
         <v>1400</v>
       </c>
@@ -36720,7 +36714,7 @@
       <c r="L599" s="31"/>
       <c r="M599" s="29"/>
     </row>
-    <row r="600" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A600" s="29" t="s">
         <v>1401</v>
       </c>
@@ -36751,7 +36745,7 @@
       <c r="L600" s="31"/>
       <c r="M600" s="29"/>
     </row>
-    <row r="601" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A601" s="29" t="s">
         <v>1402</v>
       </c>
@@ -36782,7 +36776,7 @@
       <c r="L601" s="31"/>
       <c r="M601" s="29"/>
     </row>
-    <row r="602" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A602" s="29" t="s">
         <v>1403</v>
       </c>
@@ -36813,7 +36807,7 @@
       <c r="L602" s="31"/>
       <c r="M602" s="29"/>
     </row>
-    <row r="603" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="29" t="s">
         <v>1404</v>
       </c>
@@ -36844,7 +36838,7 @@
       <c r="L603" s="31"/>
       <c r="M603" s="29"/>
     </row>
-    <row r="604" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="29" t="s">
         <v>1433</v>
       </c>
@@ -36877,7 +36871,7 @@
       <c r="L604" s="31"/>
       <c r="M604" s="29"/>
     </row>
-    <row r="605" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="29" t="s">
         <v>1434</v>
       </c>
@@ -36910,7 +36904,7 @@
       <c r="L605" s="31"/>
       <c r="M605" s="29"/>
     </row>
-    <row r="606" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="29" t="s">
         <v>1435</v>
       </c>
@@ -36943,7 +36937,7 @@
       <c r="L606" s="31"/>
       <c r="M606" s="29"/>
     </row>
-    <row r="607" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="29" t="s">
         <v>1436</v>
       </c>
@@ -36976,7 +36970,7 @@
       <c r="L607" s="31"/>
       <c r="M607" s="29"/>
     </row>
-    <row r="608" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="29" t="s">
         <v>1437</v>
       </c>
@@ -37007,7 +37001,7 @@
       <c r="L608" s="31"/>
       <c r="M608" s="29"/>
     </row>
-    <row r="609" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="29" t="s">
         <v>1438</v>
       </c>
@@ -37038,7 +37032,7 @@
       <c r="L609" s="31"/>
       <c r="M609" s="29"/>
     </row>
-    <row r="610" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="29" t="s">
         <v>1439</v>
       </c>
@@ -37069,7 +37063,7 @@
       <c r="L610" s="31"/>
       <c r="M610" s="29"/>
     </row>
-    <row r="611" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="29" t="s">
         <v>1440</v>
       </c>
@@ -37100,7 +37094,7 @@
       <c r="L611" s="31"/>
       <c r="M611" s="29"/>
     </row>
-    <row r="612" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="29" t="s">
         <v>1441</v>
       </c>
@@ -37131,7 +37125,7 @@
       <c r="L612" s="31"/>
       <c r="M612" s="29"/>
     </row>
-    <row r="613" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="29" t="s">
         <v>1442</v>
       </c>
@@ -37162,7 +37156,7 @@
       <c r="L613" s="31"/>
       <c r="M613" s="29"/>
     </row>
-    <row r="614" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="29" t="s">
         <v>1443</v>
       </c>
@@ -37193,7 +37187,7 @@
       <c r="L614" s="31"/>
       <c r="M614" s="29"/>
     </row>
-    <row r="615" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="29" t="s">
         <v>1444</v>
       </c>
@@ -37224,7 +37218,7 @@
       <c r="L615" s="31"/>
       <c r="M615" s="29"/>
     </row>
-    <row r="616" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="29" t="s">
         <v>1445</v>
       </c>
@@ -37255,7 +37249,7 @@
       <c r="L616" s="31"/>
       <c r="M616" s="29"/>
     </row>
-    <row r="617" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="29" t="s">
         <v>1446</v>
       </c>
@@ -37286,7 +37280,7 @@
       <c r="L617" s="31"/>
       <c r="M617" s="29"/>
     </row>
-    <row r="618" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="29" t="s">
         <v>1447</v>
       </c>
@@ -37319,7 +37313,7 @@
       <c r="L618" s="31"/>
       <c r="M618" s="29"/>
     </row>
-    <row r="619" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="29" t="s">
         <v>1448</v>
       </c>
@@ -37352,7 +37346,7 @@
       <c r="L619" s="31"/>
       <c r="M619" s="29"/>
     </row>
-    <row r="620" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="29" t="s">
         <v>1449</v>
       </c>
@@ -37383,7 +37377,7 @@
       <c r="L620" s="31"/>
       <c r="M620" s="29"/>
     </row>
-    <row r="621" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="29" t="s">
         <v>1450</v>
       </c>
@@ -37414,7 +37408,7 @@
       <c r="L621" s="31"/>
       <c r="M621" s="29"/>
     </row>
-    <row r="622" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="29" t="s">
         <v>1451</v>
       </c>
@@ -37445,7 +37439,7 @@
       <c r="L622" s="31"/>
       <c r="M622" s="29"/>
     </row>
-    <row r="623" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="29" t="s">
         <v>1452</v>
       </c>
@@ -37478,7 +37472,7 @@
       <c r="L623" s="31"/>
       <c r="M623" s="29"/>
     </row>
-    <row r="624" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="29" t="s">
         <v>1453</v>
       </c>
@@ -37511,7 +37505,7 @@
       <c r="L624" s="31"/>
       <c r="M624" s="29"/>
     </row>
-    <row r="625" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="29" t="s">
         <v>1454</v>
       </c>
@@ -37542,7 +37536,7 @@
       <c r="L625" s="31"/>
       <c r="M625" s="29"/>
     </row>
-    <row r="626" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="29" t="s">
         <v>1455</v>
       </c>
@@ -37573,7 +37567,7 @@
       <c r="L626" s="31"/>
       <c r="M626" s="29"/>
     </row>
-    <row r="627" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A627" s="29" t="s">
         <v>1456</v>
       </c>
@@ -37604,7 +37598,7 @@
       <c r="L627" s="31"/>
       <c r="M627" s="29"/>
     </row>
-    <row r="628" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A628" s="29" t="s">
         <v>1668</v>
       </c>
@@ -37637,7 +37631,7 @@
       <c r="L628" s="31"/>
       <c r="M628" s="29"/>
     </row>
-    <row r="629" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A629" s="29" t="s">
         <v>1669</v>
       </c>
@@ -37670,7 +37664,7 @@
       <c r="L629" s="31"/>
       <c r="M629" s="29"/>
     </row>
-    <row r="630" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
         <v>1466</v>
       </c>
@@ -37697,7 +37691,7 @@
       <c r="L630" s="31"/>
       <c r="M630" s="29"/>
     </row>
-    <row r="631" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="29" t="s">
         <v>1467</v>
       </c>
@@ -37724,7 +37718,7 @@
       <c r="L631" s="31"/>
       <c r="M631" s="29"/>
     </row>
-    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="29" t="s">
         <v>1479</v>
       </c>
@@ -37759,7 +37753,7 @@
       <c r="L632" s="31"/>
       <c r="M632" s="29"/>
     </row>
-    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="29" t="s">
         <v>1480</v>
       </c>
@@ -37794,7 +37788,7 @@
       <c r="L633" s="31"/>
       <c r="M633" s="29"/>
     </row>
-    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="29" t="s">
         <v>1481</v>
       </c>
@@ -37829,7 +37823,7 @@
       <c r="L634" s="31"/>
       <c r="M634" s="29"/>
     </row>
-    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="29" t="s">
         <v>1482</v>
       </c>
@@ -37864,7 +37858,7 @@
       <c r="L635" s="31"/>
       <c r="M635" s="29"/>
     </row>
-    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="29" t="s">
         <v>1483</v>
       </c>
@@ -37899,7 +37893,7 @@
       <c r="L636" s="31"/>
       <c r="M636" s="29"/>
     </row>
-    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="29" t="s">
         <v>1484</v>
       </c>
@@ -37934,7 +37928,7 @@
       <c r="L637" s="31"/>
       <c r="M637" s="29"/>
     </row>
-    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A638" s="29" t="s">
         <v>1485</v>
       </c>
@@ -37969,7 +37963,7 @@
       <c r="L638" s="31"/>
       <c r="M638" s="29"/>
     </row>
-    <row r="639" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A639" s="29" t="s">
         <v>1494</v>
       </c>
@@ -38004,7 +37998,7 @@
       <c r="L639" s="31"/>
       <c r="M639" s="29"/>
     </row>
-    <row r="640" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A640" s="29" t="s">
         <v>1495</v>
       </c>
@@ -38039,7 +38033,7 @@
       <c r="L640" s="31"/>
       <c r="M640" s="29"/>
     </row>
-    <row r="641" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A641" s="29" t="s">
         <v>1496</v>
       </c>
@@ -38074,7 +38068,7 @@
       <c r="L641" s="31"/>
       <c r="M641" s="29"/>
     </row>
-    <row r="642" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A642" s="29" t="s">
         <v>1497</v>
       </c>
@@ -38109,7 +38103,7 @@
       <c r="L642" s="31"/>
       <c r="M642" s="29"/>
     </row>
-    <row r="643" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A643" s="29" t="s">
         <v>1498</v>
       </c>
@@ -38144,7 +38138,7 @@
       <c r="L643" s="31"/>
       <c r="M643" s="29"/>
     </row>
-    <row r="644" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A644" s="29" t="s">
         <v>1499</v>
       </c>
@@ -38179,7 +38173,7 @@
       <c r="L644" s="31"/>
       <c r="M644" s="29"/>
     </row>
-    <row r="645" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A645" s="29" t="s">
         <v>1503</v>
       </c>
@@ -38214,7 +38208,7 @@
       <c r="L645" s="31"/>
       <c r="M645" s="29"/>
     </row>
-    <row r="646" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A646" s="29" t="s">
         <v>1517</v>
       </c>
@@ -38249,7 +38243,7 @@
       <c r="L646" s="31"/>
       <c r="M646" s="29"/>
     </row>
-    <row r="647" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A647" s="29" t="s">
         <v>1518</v>
       </c>
@@ -38284,7 +38278,7 @@
       <c r="L647" s="31"/>
       <c r="M647" s="29"/>
     </row>
-    <row r="648" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A648" s="29" t="s">
         <v>1519</v>
       </c>
@@ -38319,7 +38313,7 @@
       <c r="L648" s="31"/>
       <c r="M648" s="29"/>
     </row>
-    <row r="649" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A649" s="29" t="s">
         <v>1504</v>
       </c>
@@ -38354,7 +38348,7 @@
       <c r="L649" s="31"/>
       <c r="M649" s="29"/>
     </row>
-    <row r="650" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A650" s="29" t="s">
         <v>1505</v>
       </c>
@@ -38389,7 +38383,7 @@
       <c r="L650" s="31"/>
       <c r="M650" s="29"/>
     </row>
-    <row r="651" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A651" s="29" t="s">
         <v>1520</v>
       </c>
@@ -38424,7 +38418,7 @@
       <c r="L651" s="31"/>
       <c r="M651" s="29"/>
     </row>
-    <row r="652" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A652" s="29" t="s">
         <v>1521</v>
       </c>
@@ -38459,7 +38453,7 @@
       <c r="L652" s="31"/>
       <c r="M652" s="29"/>
     </row>
-    <row r="653" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A653" s="29" t="s">
         <v>1522</v>
       </c>
@@ -38494,7 +38488,7 @@
       <c r="L653" s="31"/>
       <c r="M653" s="29"/>
     </row>
-    <row r="654" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A654" s="29" t="s">
         <v>1523</v>
       </c>
@@ -38529,7 +38523,7 @@
       <c r="L654" s="31"/>
       <c r="M654" s="29"/>
     </row>
-    <row r="655" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A655" s="29" t="s">
         <v>1524</v>
       </c>
@@ -38564,7 +38558,7 @@
       <c r="L655" s="31"/>
       <c r="M655" s="29"/>
     </row>
-    <row r="656" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A656" s="29" t="s">
         <v>1525</v>
       </c>
@@ -38599,7 +38593,7 @@
       <c r="L656" s="31"/>
       <c r="M656" s="29"/>
     </row>
-    <row r="657" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A657" s="29" t="s">
         <v>1526</v>
       </c>
@@ -38634,7 +38628,7 @@
       <c r="L657" s="31"/>
       <c r="M657" s="29"/>
     </row>
-    <row r="658" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A658" s="29" t="s">
         <v>1527</v>
       </c>
@@ -38669,7 +38663,7 @@
       <c r="L658" s="31"/>
       <c r="M658" s="29"/>
     </row>
-    <row r="659" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A659" s="29" t="s">
         <v>1528</v>
       </c>
@@ -38704,7 +38698,7 @@
       <c r="L659" s="31"/>
       <c r="M659" s="29"/>
     </row>
-    <row r="660" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A660" s="29" t="s">
         <v>1529</v>
       </c>
@@ -38739,7 +38733,7 @@
       <c r="L660" s="31"/>
       <c r="M660" s="29"/>
     </row>
-    <row r="661" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="29" t="s">
         <v>1530</v>
       </c>
@@ -38774,7 +38768,7 @@
       <c r="L661" s="31"/>
       <c r="M661" s="29"/>
     </row>
-    <row r="662" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="29" t="s">
         <v>1531</v>
       </c>
@@ -38795,7 +38789,7 @@
       <c r="L662" s="31"/>
       <c r="M662" s="29"/>
     </row>
-    <row r="663" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A663" s="29" t="s">
         <v>1532</v>
       </c>
@@ -38816,7 +38810,7 @@
       <c r="L663" s="31"/>
       <c r="M663" s="29"/>
     </row>
-    <row r="664" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A664" s="29" t="s">
         <v>1533</v>
       </c>
@@ -38837,7 +38831,7 @@
       <c r="L664" s="31"/>
       <c r="M664" s="29"/>
     </row>
-    <row r="665" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="29" t="s">
         <v>2438</v>
       </c>
@@ -38872,7 +38866,7 @@
       <c r="L665" s="31"/>
       <c r="M665" s="29"/>
     </row>
-    <row r="666" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A666" s="29" t="s">
         <v>2439</v>
       </c>
@@ -38907,7 +38901,7 @@
       <c r="L666" s="31"/>
       <c r="M666" s="29"/>
     </row>
-    <row r="667" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A667" s="29" t="s">
         <v>2440</v>
       </c>
@@ -38938,7 +38932,7 @@
       <c r="L667" s="31"/>
       <c r="M667" s="29"/>
     </row>
-    <row r="668" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A668" s="29" t="s">
         <v>2441</v>
       </c>
@@ -38969,7 +38963,7 @@
       <c r="L668" s="31"/>
       <c r="M668" s="29"/>
     </row>
-    <row r="669" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A669" s="29" t="s">
         <v>2442</v>
       </c>
@@ -39000,7 +38994,7 @@
       <c r="L669" s="31"/>
       <c r="M669" s="29"/>
     </row>
-    <row r="670" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A670" s="29" t="s">
         <v>2443</v>
       </c>
@@ -39031,7 +39025,7 @@
       <c r="L670" s="31"/>
       <c r="M670" s="29"/>
     </row>
-    <row r="671" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A671" s="29" t="s">
         <v>2444</v>
       </c>
@@ -39062,7 +39056,7 @@
       <c r="L671" s="31"/>
       <c r="M671" s="29"/>
     </row>
-    <row r="672" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A672" s="29" t="s">
         <v>2445</v>
       </c>
@@ -39093,7 +39087,7 @@
       <c r="L672" s="31"/>
       <c r="M672" s="29"/>
     </row>
-    <row r="673" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A673" s="29" t="s">
         <v>2446</v>
       </c>
@@ -39124,7 +39118,7 @@
       <c r="L673" s="31"/>
       <c r="M673" s="29"/>
     </row>
-    <row r="674" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A674" s="29" t="s">
         <v>2447</v>
       </c>
@@ -39155,7 +39149,7 @@
       <c r="L674" s="31"/>
       <c r="M674" s="29"/>
     </row>
-    <row r="675" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A675" s="29" t="s">
         <v>2448</v>
       </c>
@@ -39186,7 +39180,7 @@
       <c r="L675" s="31"/>
       <c r="M675" s="29"/>
     </row>
-    <row r="676" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A676" s="29" t="s">
         <v>2449</v>
       </c>
@@ -39217,7 +39211,7 @@
       <c r="L676" s="31"/>
       <c r="M676" s="29"/>
     </row>
-    <row r="677" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A677" s="29" t="s">
         <v>2450</v>
       </c>
@@ -39248,7 +39242,7 @@
       <c r="L677" s="31"/>
       <c r="M677" s="29"/>
     </row>
-    <row r="678" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A678" s="29" t="s">
         <v>2451</v>
       </c>
@@ -39279,7 +39273,7 @@
       <c r="L678" s="31"/>
       <c r="M678" s="29"/>
     </row>
-    <row r="679" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A679" s="29" t="s">
         <v>2452</v>
       </c>
@@ -39310,7 +39304,7 @@
       <c r="L679" s="31"/>
       <c r="M679" s="29"/>
     </row>
-    <row r="680" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A680" s="29" t="s">
         <v>2453</v>
       </c>
@@ -39341,7 +39335,7 @@
       <c r="L680" s="31"/>
       <c r="M680" s="29"/>
     </row>
-    <row r="681" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A681" s="29" t="s">
         <v>2454</v>
       </c>
@@ -39372,7 +39366,7 @@
       <c r="L681" s="31"/>
       <c r="M681" s="29"/>
     </row>
-    <row r="682" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A682" s="29" t="s">
         <v>2455</v>
       </c>
@@ -39403,7 +39397,7 @@
       <c r="L682" s="31"/>
       <c r="M682" s="29"/>
     </row>
-    <row r="683" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A683" s="29" t="s">
         <v>2456</v>
       </c>
@@ -39434,7 +39428,7 @@
       <c r="L683" s="31"/>
       <c r="M683" s="29"/>
     </row>
-    <row r="684" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A684" s="29" t="s">
         <v>2457</v>
       </c>
@@ -39465,7 +39459,7 @@
       <c r="L684" s="31"/>
       <c r="M684" s="29"/>
     </row>
-    <row r="685" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A685" s="29" t="s">
         <v>2458</v>
       </c>
@@ -39496,7 +39490,7 @@
       <c r="L685" s="31"/>
       <c r="M685" s="29"/>
     </row>
-    <row r="686" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A686" s="29" t="s">
         <v>2459</v>
       </c>
@@ -39527,7 +39521,7 @@
       <c r="L686" s="31"/>
       <c r="M686" s="29"/>
     </row>
-    <row r="687" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A687" s="29" t="s">
         <v>2460</v>
       </c>
@@ -39558,7 +39552,7 @@
       <c r="L687" s="31"/>
       <c r="M687" s="29"/>
     </row>
-    <row r="688" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A688" s="29" t="s">
         <v>2461</v>
       </c>
@@ -39589,7 +39583,7 @@
       <c r="L688" s="31"/>
       <c r="M688" s="29"/>
     </row>
-    <row r="689" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A689" s="29" t="s">
         <v>2462</v>
       </c>
@@ -39624,7 +39618,7 @@
       <c r="L689" s="31"/>
       <c r="M689" s="29"/>
     </row>
-    <row r="690" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A690" s="29" t="s">
         <v>2463</v>
       </c>
@@ -39659,7 +39653,7 @@
       <c r="L690" s="31"/>
       <c r="M690" s="29"/>
     </row>
-    <row r="691" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A691" s="29" t="s">
         <v>2464</v>
       </c>
@@ -39694,7 +39688,7 @@
       <c r="L691" s="31"/>
       <c r="M691" s="29"/>
     </row>
-    <row r="692" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A692" s="29" t="s">
         <v>2465</v>
       </c>
@@ -39729,7 +39723,7 @@
       <c r="L692" s="31"/>
       <c r="M692" s="29"/>
     </row>
-    <row r="693" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A693" s="29" t="s">
         <v>2466</v>
       </c>
@@ -39764,7 +39758,7 @@
       <c r="L693" s="31"/>
       <c r="M693" s="29"/>
     </row>
-    <row r="694" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A694" s="29" t="s">
         <v>2467</v>
       </c>
@@ -39799,7 +39793,7 @@
       <c r="L694" s="31"/>
       <c r="M694" s="29"/>
     </row>
-    <row r="695" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A695" s="29" t="s">
         <v>2468</v>
       </c>
@@ -39834,7 +39828,7 @@
       <c r="L695" s="31"/>
       <c r="M695" s="29"/>
     </row>
-    <row r="696" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A696" s="29" t="s">
         <v>2469</v>
       </c>
@@ -39869,7 +39863,7 @@
       <c r="L696" s="31"/>
       <c r="M696" s="29"/>
     </row>
-    <row r="697" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A697" s="29" t="s">
         <v>2470</v>
       </c>
@@ -39904,7 +39898,7 @@
       <c r="L697" s="31"/>
       <c r="M697" s="29"/>
     </row>
-    <row r="698" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
         <v>2471</v>
       </c>
@@ -39939,7 +39933,7 @@
       <c r="L698" s="31"/>
       <c r="M698" s="29"/>
     </row>
-    <row r="699" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
         <v>1546</v>
       </c>
@@ -39968,7 +39962,7 @@
       <c r="L699" s="31"/>
       <c r="M699" s="29"/>
     </row>
-    <row r="700" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
         <v>1547</v>
       </c>
@@ -39997,7 +39991,7 @@
       <c r="L700" s="31"/>
       <c r="M700" s="29"/>
     </row>
-    <row r="701" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
         <v>1548</v>
       </c>
@@ -40026,7 +40020,7 @@
       <c r="L701" s="31"/>
       <c r="M701" s="29"/>
     </row>
-    <row r="702" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
         <v>1549</v>
       </c>
@@ -40055,7 +40049,7 @@
       <c r="L702" s="31"/>
       <c r="M702" s="29"/>
     </row>
-    <row r="703" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
         <v>1550</v>
       </c>
@@ -40084,7 +40078,7 @@
       <c r="L703" s="31"/>
       <c r="M703" s="29"/>
     </row>
-    <row r="704" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
         <v>1551</v>
       </c>
@@ -40113,7 +40107,7 @@
       <c r="L704" s="31"/>
       <c r="M704" s="29"/>
     </row>
-    <row r="705" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
         <v>1552</v>
       </c>
@@ -40142,7 +40136,7 @@
       <c r="L705" s="31"/>
       <c r="M705" s="29"/>
     </row>
-    <row r="706" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
         <v>1553</v>
       </c>
@@ -40171,7 +40165,7 @@
       <c r="L706" s="31"/>
       <c r="M706" s="29"/>
     </row>
-    <row r="707" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
         <v>1556</v>
       </c>
@@ -40200,7 +40194,7 @@
       <c r="L707" s="31"/>
       <c r="M707" s="29"/>
     </row>
-    <row r="708" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
         <v>1557</v>
       </c>
@@ -40229,7 +40223,7 @@
       <c r="L708" s="31"/>
       <c r="M708" s="29"/>
     </row>
-    <row r="709" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
         <v>1558</v>
       </c>
@@ -40258,7 +40252,7 @@
       <c r="L709" s="31"/>
       <c r="M709" s="29"/>
     </row>
-    <row r="710" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
         <v>1559</v>
       </c>
@@ -40287,7 +40281,7 @@
       <c r="L710" s="31"/>
       <c r="M710" s="29"/>
     </row>
-    <row r="711" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
         <v>1560</v>
       </c>
@@ -40316,7 +40310,7 @@
       <c r="L711" s="31"/>
       <c r="M711" s="29"/>
     </row>
-    <row r="712" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
         <v>1561</v>
       </c>
@@ -40345,7 +40339,7 @@
       <c r="L712" s="31"/>
       <c r="M712" s="29"/>
     </row>
-    <row r="713" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="29" t="s">
         <v>1562</v>
       </c>
@@ -40374,7 +40368,7 @@
       <c r="L713" s="31"/>
       <c r="M713" s="29"/>
     </row>
-    <row r="714" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A714" s="29" t="s">
         <v>1563</v>
       </c>
@@ -40403,7 +40397,7 @@
       <c r="L714" s="31"/>
       <c r="M714" s="29"/>
     </row>
-    <row r="715" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A715" s="29" t="s">
         <v>1564</v>
       </c>
@@ -40432,7 +40426,7 @@
       <c r="L715" s="31"/>
       <c r="M715" s="29"/>
     </row>
-    <row r="716" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A716" s="29" t="s">
         <v>1565</v>
       </c>
@@ -40461,7 +40455,7 @@
       <c r="L716" s="31"/>
       <c r="M716" s="29"/>
     </row>
-    <row r="717" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A717" s="29" t="s">
         <v>1566</v>
       </c>
@@ -40490,7 +40484,7 @@
       <c r="L717" s="31"/>
       <c r="M717" s="29"/>
     </row>
-    <row r="718" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A718" s="29" t="s">
         <v>1567</v>
       </c>
@@ -40519,7 +40513,7 @@
       <c r="L718" s="31"/>
       <c r="M718" s="29"/>
     </row>
-    <row r="719" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A719" s="29" t="s">
         <v>1568</v>
       </c>
@@ -40548,7 +40542,7 @@
       <c r="L719" s="31"/>
       <c r="M719" s="29"/>
     </row>
-    <row r="720" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A720" s="29" t="s">
         <v>1569</v>
       </c>
@@ -40577,7 +40571,7 @@
       <c r="L720" s="31"/>
       <c r="M720" s="29"/>
     </row>
-    <row r="721" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A721" s="29" t="s">
         <v>1570</v>
       </c>
@@ -40606,7 +40600,7 @@
       <c r="L721" s="31"/>
       <c r="M721" s="29"/>
     </row>
-    <row r="722" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A722" s="29" t="s">
         <v>1571</v>
       </c>
@@ -40635,7 +40629,7 @@
       <c r="L722" s="31"/>
       <c r="M722" s="29"/>
     </row>
-    <row r="723" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A723" s="29" t="s">
         <v>2472</v>
       </c>
@@ -40668,7 +40662,7 @@
       <c r="L723" s="31"/>
       <c r="M723" s="29"/>
     </row>
-    <row r="724" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A724" s="29" t="s">
         <v>2473</v>
       </c>
@@ -40701,7 +40695,7 @@
       <c r="L724" s="31"/>
       <c r="M724" s="29"/>
     </row>
-    <row r="725" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A725" s="29" t="s">
         <v>2474</v>
       </c>
@@ -40734,7 +40728,7 @@
       <c r="L725" s="31"/>
       <c r="M725" s="29"/>
     </row>
-    <row r="726" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A726" s="29" t="s">
         <v>2475</v>
       </c>
@@ -40767,7 +40761,7 @@
       <c r="L726" s="31"/>
       <c r="M726" s="29"/>
     </row>
-    <row r="727" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A727" s="29" t="s">
         <v>2476</v>
       </c>
@@ -40800,7 +40794,7 @@
       <c r="L727" s="31"/>
       <c r="M727" s="29"/>
     </row>
-    <row r="728" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A728" s="29" t="s">
         <v>2477</v>
       </c>
@@ -40833,7 +40827,7 @@
       <c r="L728" s="31"/>
       <c r="M728" s="29"/>
     </row>
-    <row r="729" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A729" s="29" t="s">
         <v>2478</v>
       </c>
@@ -40866,7 +40860,7 @@
       <c r="L729" s="31"/>
       <c r="M729" s="29"/>
     </row>
-    <row r="730" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A730" s="29" t="s">
         <v>2479</v>
       </c>
@@ -40899,7 +40893,7 @@
       <c r="L730" s="31"/>
       <c r="M730" s="29"/>
     </row>
-    <row r="731" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A731" s="29" t="s">
         <v>2480</v>
       </c>
@@ -40932,7 +40926,7 @@
       <c r="L731" s="31"/>
       <c r="M731" s="29"/>
     </row>
-    <row r="732" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A732" s="29" t="s">
         <v>2481</v>
       </c>
@@ -40965,7 +40959,7 @@
       <c r="L732" s="31"/>
       <c r="M732" s="29"/>
     </row>
-    <row r="733" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A733" s="29" t="s">
         <v>2482</v>
       </c>
@@ -40998,7 +40992,7 @@
       <c r="L733" s="31"/>
       <c r="M733" s="29"/>
     </row>
-    <row r="734" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A734" s="29" t="s">
         <v>2483</v>
       </c>
@@ -41031,7 +41025,7 @@
       <c r="L734" s="31"/>
       <c r="M734" s="29"/>
     </row>
-    <row r="735" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A735" s="29" t="s">
         <v>2484</v>
       </c>
@@ -41064,7 +41058,7 @@
       <c r="L735" s="31"/>
       <c r="M735" s="29"/>
     </row>
-    <row r="736" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A736" s="29" t="s">
         <v>2485</v>
       </c>
@@ -41097,7 +41091,7 @@
       <c r="L736" s="31"/>
       <c r="M736" s="29"/>
     </row>
-    <row r="737" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A737" s="29" t="s">
         <v>2486</v>
       </c>
@@ -41130,7 +41124,7 @@
       <c r="L737" s="31"/>
       <c r="M737" s="29"/>
     </row>
-    <row r="738" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A738" s="29" t="s">
         <v>2487</v>
       </c>
@@ -41163,7 +41157,7 @@
       <c r="L738" s="31"/>
       <c r="M738" s="29"/>
     </row>
-    <row r="739" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A739" s="29" t="s">
         <v>2488</v>
       </c>
@@ -41196,7 +41190,7 @@
       <c r="L739" s="31"/>
       <c r="M739" s="29"/>
     </row>
-    <row r="740" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A740" s="29" t="s">
         <v>2489</v>
       </c>
@@ -41229,7 +41223,7 @@
       <c r="L740" s="31"/>
       <c r="M740" s="29"/>
     </row>
-    <row r="741" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A741" s="29" t="s">
         <v>2490</v>
       </c>
@@ -41262,7 +41256,7 @@
       <c r="L741" s="31"/>
       <c r="M741" s="29"/>
     </row>
-    <row r="742" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A742" s="29" t="s">
         <v>2491</v>
       </c>
@@ -41295,7 +41289,7 @@
       <c r="L742" s="31"/>
       <c r="M742" s="29"/>
     </row>
-    <row r="743" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A743" s="29" t="s">
         <v>2492</v>
       </c>
@@ -41328,7 +41322,7 @@
       <c r="L743" s="31"/>
       <c r="M743" s="29"/>
     </row>
-    <row r="744" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A744" s="29" t="s">
         <v>2493</v>
       </c>
@@ -41361,7 +41355,7 @@
       <c r="L744" s="31"/>
       <c r="M744" s="29"/>
     </row>
-    <row r="745" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A745" s="29" t="s">
         <v>2494</v>
       </c>
@@ -41394,7 +41388,7 @@
       <c r="L745" s="31"/>
       <c r="M745" s="29"/>
     </row>
-    <row r="746" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A746" s="29" t="s">
         <v>2495</v>
       </c>
@@ -41427,7 +41421,7 @@
       <c r="L746" s="31"/>
       <c r="M746" s="29"/>
     </row>
-    <row r="747" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A747" s="29" t="s">
         <v>2496</v>
       </c>
@@ -41460,7 +41454,7 @@
       <c r="L747" s="31"/>
       <c r="M747" s="29"/>
     </row>
-    <row r="748" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A748" s="29" t="s">
         <v>2497</v>
       </c>
@@ -41493,7 +41487,7 @@
       <c r="L748" s="31"/>
       <c r="M748" s="29"/>
     </row>
-    <row r="749" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A749" s="29" t="s">
         <v>2498</v>
       </c>
@@ -41526,7 +41520,7 @@
       <c r="L749" s="31"/>
       <c r="M749" s="29"/>
     </row>
-    <row r="750" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A750" s="29" t="s">
         <v>2499</v>
       </c>
@@ -41559,7 +41553,7 @@
       <c r="L750" s="31"/>
       <c r="M750" s="29"/>
     </row>
-    <row r="751" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A751" s="29" t="s">
         <v>2500</v>
       </c>
@@ -41592,7 +41586,7 @@
       <c r="L751" s="31"/>
       <c r="M751" s="29"/>
     </row>
-    <row r="752" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A752" s="29" t="s">
         <v>2501</v>
       </c>
@@ -41625,7 +41619,7 @@
       <c r="L752" s="31"/>
       <c r="M752" s="29"/>
     </row>
-    <row r="753" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A753" s="29" t="s">
         <v>2502</v>
       </c>
@@ -41658,7 +41652,7 @@
       <c r="L753" s="31"/>
       <c r="M753" s="29"/>
     </row>
-    <row r="754" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A754" s="29" t="s">
         <v>2503</v>
       </c>
@@ -41691,7 +41685,7 @@
       <c r="L754" s="31"/>
       <c r="M754" s="29"/>
     </row>
-    <row r="755" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A755" s="29" t="s">
         <v>2504</v>
       </c>
@@ -41724,7 +41718,7 @@
       <c r="L755" s="31"/>
       <c r="M755" s="29"/>
     </row>
-    <row r="756" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A756" s="29" t="s">
         <v>2505</v>
       </c>
@@ -41757,7 +41751,7 @@
       <c r="L756" s="31"/>
       <c r="M756" s="29"/>
     </row>
-    <row r="757" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A757" s="29" t="s">
         <v>2506</v>
       </c>
@@ -41790,7 +41784,7 @@
       <c r="L757" s="31"/>
       <c r="M757" s="29"/>
     </row>
-    <row r="758" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A758" s="29" t="s">
         <v>2507</v>
       </c>
@@ -41823,7 +41817,7 @@
       <c r="L758" s="31"/>
       <c r="M758" s="29"/>
     </row>
-    <row r="759" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A759" s="29" t="s">
         <v>2508</v>
       </c>
@@ -41856,7 +41850,7 @@
       <c r="L759" s="31"/>
       <c r="M759" s="29"/>
     </row>
-    <row r="760" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A760" s="29" t="s">
         <v>2509</v>
       </c>
@@ -41889,7 +41883,7 @@
       <c r="L760" s="31"/>
       <c r="M760" s="29"/>
     </row>
-    <row r="761" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A761" s="29" t="s">
         <v>2510</v>
       </c>
@@ -41922,7 +41916,7 @@
       <c r="L761" s="31"/>
       <c r="M761" s="29"/>
     </row>
-    <row r="762" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A762" s="29" t="s">
         <v>2511</v>
       </c>
@@ -41955,7 +41949,7 @@
       <c r="L762" s="31"/>
       <c r="M762" s="29"/>
     </row>
-    <row r="763" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A763" s="29" t="s">
         <v>2512</v>
       </c>
@@ -41988,7 +41982,7 @@
       <c r="L763" s="31"/>
       <c r="M763" s="29"/>
     </row>
-    <row r="764" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A764" s="29" t="s">
         <v>2513</v>
       </c>
@@ -42021,7 +42015,7 @@
       <c r="L764" s="31"/>
       <c r="M764" s="29"/>
     </row>
-    <row r="765" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A765" s="29" t="s">
         <v>2514</v>
       </c>
@@ -42054,7 +42048,7 @@
       <c r="L765" s="31"/>
       <c r="M765" s="29"/>
     </row>
-    <row r="766" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A766" s="29" t="s">
         <v>2515</v>
       </c>
@@ -42087,7 +42081,7 @@
       <c r="L766" s="31"/>
       <c r="M766" s="29"/>
     </row>
-    <row r="767" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A767" s="29" t="s">
         <v>2516</v>
       </c>
@@ -42120,7 +42114,7 @@
       <c r="L767" s="31"/>
       <c r="M767" s="29"/>
     </row>
-    <row r="768" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A768" s="29" t="s">
         <v>2517</v>
       </c>
@@ -42153,7 +42147,7 @@
       <c r="L768" s="31"/>
       <c r="M768" s="29"/>
     </row>
-    <row r="769" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A769" s="29" t="s">
         <v>2518</v>
       </c>
@@ -42186,7 +42180,7 @@
       <c r="L769" s="31"/>
       <c r="M769" s="29"/>
     </row>
-    <row r="770" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A770" s="29" t="s">
         <v>2519</v>
       </c>
@@ -42219,7 +42213,7 @@
       <c r="L770" s="31"/>
       <c r="M770" s="29"/>
     </row>
-    <row r="771" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A771" s="29" t="s">
         <v>2520</v>
       </c>
@@ -42252,7 +42246,7 @@
       <c r="L771" s="31"/>
       <c r="M771" s="29"/>
     </row>
-    <row r="772" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A772" s="29" t="s">
         <v>2521</v>
       </c>
@@ -42285,7 +42279,7 @@
       <c r="L772" s="31"/>
       <c r="M772" s="29"/>
     </row>
-    <row r="773" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A773" s="29" t="s">
         <v>2522</v>
       </c>
@@ -42318,7 +42312,7 @@
       <c r="L773" s="31"/>
       <c r="M773" s="29"/>
     </row>
-    <row r="774" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A774" s="29" t="s">
         <v>2523</v>
       </c>
@@ -42351,7 +42345,7 @@
       <c r="L774" s="31"/>
       <c r="M774" s="29"/>
     </row>
-    <row r="775" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A775" s="29" t="s">
         <v>2524</v>
       </c>
@@ -42384,7 +42378,7 @@
       <c r="L775" s="31"/>
       <c r="M775" s="29"/>
     </row>
-    <row r="776" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A776" s="29" t="s">
         <v>2525</v>
       </c>
@@ -42417,7 +42411,7 @@
       <c r="L776" s="31"/>
       <c r="M776" s="29"/>
     </row>
-    <row r="777" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A777" s="29" t="s">
         <v>2526</v>
       </c>
@@ -42450,7 +42444,7 @@
       <c r="L777" s="31"/>
       <c r="M777" s="29"/>
     </row>
-    <row r="778" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A778" s="29" t="s">
         <v>2527</v>
       </c>
@@ -42483,7 +42477,7 @@
       <c r="L778" s="31"/>
       <c r="M778" s="29"/>
     </row>
-    <row r="779" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A779" s="29" t="s">
         <v>2528</v>
       </c>
@@ -42516,7 +42510,7 @@
       <c r="L779" s="31"/>
       <c r="M779" s="29"/>
     </row>
-    <row r="780" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A780" s="29" t="s">
         <v>2529</v>
       </c>
@@ -42549,7 +42543,7 @@
       <c r="L780" s="31"/>
       <c r="M780" s="29"/>
     </row>
-    <row r="781" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A781" s="29" t="s">
         <v>2530</v>
       </c>
@@ -42582,7 +42576,7 @@
       <c r="L781" s="31"/>
       <c r="M781" s="29"/>
     </row>
-    <row r="782" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A782" s="29" t="s">
         <v>2531</v>
       </c>
@@ -42615,7 +42609,7 @@
       <c r="L782" s="31"/>
       <c r="M782" s="29"/>
     </row>
-    <row r="783" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A783" s="29" t="s">
         <v>2532</v>
       </c>
@@ -42648,7 +42642,7 @@
       <c r="L783" s="31"/>
       <c r="M783" s="29"/>
     </row>
-    <row r="784" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A784" s="29" t="s">
         <v>2533</v>
       </c>
@@ -42681,7 +42675,7 @@
       <c r="L784" s="31"/>
       <c r="M784" s="29"/>
     </row>
-    <row r="785" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A785" s="29" t="s">
         <v>2534</v>
       </c>
@@ -42714,7 +42708,7 @@
       <c r="L785" s="31"/>
       <c r="M785" s="29"/>
     </row>
-    <row r="786" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A786" s="29" t="s">
         <v>2535</v>
       </c>
@@ -42747,7 +42741,7 @@
       <c r="L786" s="31"/>
       <c r="M786" s="29"/>
     </row>
-    <row r="787" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A787" s="29" t="s">
         <v>2536</v>
       </c>
@@ -42780,7 +42774,7 @@
       <c r="L787" s="31"/>
       <c r="M787" s="29"/>
     </row>
-    <row r="788" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A788" s="29" t="s">
         <v>2537</v>
       </c>
@@ -42813,7 +42807,7 @@
       <c r="L788" s="31"/>
       <c r="M788" s="29"/>
     </row>
-    <row r="789" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A789" s="29" t="s">
         <v>2538</v>
       </c>
@@ -42850,7 +42844,7 @@
       <c r="L789" s="31"/>
       <c r="M789" s="29"/>
     </row>
-    <row r="790" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A790" s="29" t="s">
         <v>2539</v>
       </c>
@@ -42887,7 +42881,7 @@
       <c r="L790" s="31"/>
       <c r="M790" s="29"/>
     </row>
-    <row r="791" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A791" s="29" t="s">
         <v>2540</v>
       </c>
@@ -42924,7 +42918,7 @@
       <c r="L791" s="31"/>
       <c r="M791" s="29"/>
     </row>
-    <row r="792" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A792" s="29" t="s">
         <v>2541</v>
       </c>
@@ -42961,7 +42955,7 @@
       <c r="L792" s="31"/>
       <c r="M792" s="29"/>
     </row>
-    <row r="793" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A793" s="29" t="s">
         <v>2542</v>
       </c>
@@ -42998,7 +42992,7 @@
       <c r="L793" s="31"/>
       <c r="M793" s="29"/>
     </row>
-    <row r="794" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A794" s="29" t="s">
         <v>2543</v>
       </c>
@@ -43035,7 +43029,7 @@
       <c r="L794" s="31"/>
       <c r="M794" s="29"/>
     </row>
-    <row r="795" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A795" s="29" t="s">
         <v>2544</v>
       </c>
@@ -43072,7 +43066,7 @@
       <c r="L795" s="31"/>
       <c r="M795" s="29"/>
     </row>
-    <row r="796" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A796" s="29" t="s">
         <v>2545</v>
       </c>
@@ -43109,7 +43103,7 @@
       <c r="L796" s="31"/>
       <c r="M796" s="29"/>
     </row>
-    <row r="797" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A797" s="29" t="s">
         <v>1845</v>
       </c>
@@ -43142,7 +43136,7 @@
       <c r="L797" s="31"/>
       <c r="M797" s="29"/>
     </row>
-    <row r="798" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A798" s="29" t="s">
         <v>1846</v>
       </c>
@@ -43175,7 +43169,7 @@
       <c r="L798" s="31"/>
       <c r="M798" s="29"/>
     </row>
-    <row r="799" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A799" s="29" t="s">
         <v>1651</v>
       </c>
@@ -43206,7 +43200,7 @@
       <c r="L799" s="31"/>
       <c r="M799" s="29"/>
     </row>
-    <row r="800" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A800" s="29" t="s">
         <v>1652</v>
       </c>
@@ -43237,7 +43231,7 @@
       <c r="L800" s="31"/>
       <c r="M800" s="29"/>
     </row>
-    <row r="801" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
         <v>1653</v>
       </c>
@@ -43268,7 +43262,7 @@
       <c r="L801" s="31"/>
       <c r="M801" s="29"/>
     </row>
-    <row r="802" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
         <v>1654</v>
       </c>
@@ -43299,7 +43293,7 @@
       <c r="L802" s="31"/>
       <c r="M802" s="29"/>
     </row>
-    <row r="803" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
         <v>1655</v>
       </c>
@@ -43330,7 +43324,7 @@
       <c r="L803" s="31"/>
       <c r="M803" s="29"/>
     </row>
-    <row r="804" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
         <v>1656</v>
       </c>
@@ -43361,7 +43355,7 @@
       <c r="L804" s="31"/>
       <c r="M804" s="29"/>
     </row>
-    <row r="805" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
         <v>1657</v>
       </c>
@@ -43392,7 +43386,7 @@
       <c r="L805" s="31"/>
       <c r="M805" s="29"/>
     </row>
-    <row r="806" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A806" s="29" t="s">
         <v>1658</v>
       </c>
@@ -43423,7 +43417,7 @@
       <c r="L806" s="31"/>
       <c r="M806" s="29"/>
     </row>
-    <row r="807" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A807" s="29" t="s">
         <v>1689</v>
       </c>
@@ -43452,7 +43446,7 @@
       <c r="L807" s="31"/>
       <c r="M807" s="29"/>
     </row>
-    <row r="808" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
         <v>1690</v>
       </c>
@@ -43481,7 +43475,7 @@
       <c r="L808" s="31"/>
       <c r="M808" s="29"/>
     </row>
-    <row r="809" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
         <v>1691</v>
       </c>
@@ -43510,7 +43504,7 @@
       <c r="L809" s="31"/>
       <c r="M809" s="29"/>
     </row>
-    <row r="810" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
         <v>1692</v>
       </c>
@@ -43539,7 +43533,7 @@
       <c r="L810" s="31"/>
       <c r="M810" s="29"/>
     </row>
-    <row r="811" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
         <v>1693</v>
       </c>
@@ -43568,7 +43562,7 @@
       <c r="L811" s="31"/>
       <c r="M811" s="29"/>
     </row>
-    <row r="812" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
         <v>1756</v>
       </c>
@@ -43597,7 +43591,7 @@
       <c r="L812" s="31"/>
       <c r="M812" s="29"/>
     </row>
-    <row r="813" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
         <v>1757</v>
       </c>
@@ -43626,7 +43620,7 @@
       <c r="L813" s="31"/>
       <c r="M813" s="29"/>
     </row>
-    <row r="814" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A814" s="29" t="s">
         <v>1758</v>
       </c>
@@ -43657,7 +43651,7 @@
       <c r="L814" s="31"/>
       <c r="M814" s="29"/>
     </row>
-    <row r="815" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A815" s="29" t="s">
         <v>1759</v>
       </c>
@@ -43688,7 +43682,7 @@
       <c r="L815" s="31"/>
       <c r="M815" s="29"/>
     </row>
-    <row r="816" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A816" s="29" t="s">
         <v>1760</v>
       </c>
@@ -43719,7 +43713,7 @@
       <c r="L816" s="31"/>
       <c r="M816" s="29"/>
     </row>
-    <row r="817" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
         <v>1768</v>
       </c>
@@ -43750,7 +43744,7 @@
       <c r="L817" s="31"/>
       <c r="M817" s="29"/>
     </row>
-    <row r="818" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
         <v>1769</v>
       </c>
@@ -43781,7 +43775,7 @@
       <c r="L818" s="31"/>
       <c r="M818" s="29"/>
     </row>
-    <row r="819" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A819" s="29" t="s">
         <v>1770</v>
       </c>
@@ -43812,7 +43806,7 @@
       <c r="L819" s="31"/>
       <c r="M819" s="29"/>
     </row>
-    <row r="820" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A820" s="29" t="s">
         <v>1771</v>
       </c>
@@ -43843,7 +43837,7 @@
       <c r="L820" s="31"/>
       <c r="M820" s="29"/>
     </row>
-    <row r="821" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A821" s="29" t="s">
         <v>1772</v>
       </c>
@@ -43874,7 +43868,7 @@
       <c r="L821" s="31"/>
       <c r="M821" s="29"/>
     </row>
-    <row r="822" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A822" s="29" t="s">
         <v>1792</v>
       </c>
@@ -43905,7 +43899,7 @@
       <c r="L822" s="31"/>
       <c r="M822" s="29"/>
     </row>
-    <row r="823" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A823" s="29" t="s">
         <v>1793</v>
       </c>
@@ -43936,7 +43930,7 @@
       <c r="L823" s="31"/>
       <c r="M823" s="29"/>
     </row>
-    <row r="824" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
         <v>1797</v>
       </c>
@@ -43967,7 +43961,7 @@
       <c r="L824" s="31"/>
       <c r="M824" s="29"/>
     </row>
-    <row r="825" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
         <v>1798</v>
       </c>
@@ -43998,7 +43992,7 @@
       <c r="L825" s="31"/>
       <c r="M825" s="29"/>
     </row>
-    <row r="826" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
         <v>1806</v>
       </c>
@@ -44029,7 +44023,7 @@
       <c r="L826" s="31"/>
       <c r="M826" s="29"/>
     </row>
-    <row r="827" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
         <v>1807</v>
       </c>
@@ -44060,7 +44054,7 @@
       <c r="L827" s="31"/>
       <c r="M827" s="29"/>
     </row>
-    <row r="828" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
         <v>1813</v>
       </c>
@@ -44091,7 +44085,7 @@
       <c r="L828" s="31"/>
       <c r="M828" s="29"/>
     </row>
-    <row r="829" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
         <v>1814</v>
       </c>
@@ -44122,7 +44116,7 @@
       <c r="L829" s="31"/>
       <c r="M829" s="29"/>
     </row>
-    <row r="830" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A830" s="29" t="s">
         <v>1817</v>
       </c>
@@ -44151,7 +44145,7 @@
       <c r="L830" s="31"/>
       <c r="M830" s="29"/>
     </row>
-    <row r="831" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A831" s="29" t="s">
         <v>1818</v>
       </c>
@@ -44180,7 +44174,7 @@
       <c r="L831" s="31"/>
       <c r="M831" s="29"/>
     </row>
-    <row r="832" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A832" s="29" t="s">
         <v>2546</v>
       </c>
@@ -44213,7 +44207,7 @@
       <c r="L832" s="31"/>
       <c r="M832" s="29"/>
     </row>
-    <row r="833" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A833" s="29" t="s">
         <v>2547</v>
       </c>
@@ -44246,7 +44240,7 @@
       <c r="L833" s="31"/>
       <c r="M833" s="29"/>
     </row>
-    <row r="834" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A834" s="29" t="s">
         <v>2548</v>
       </c>
@@ -44279,7 +44273,7 @@
       <c r="L834" s="31"/>
       <c r="M834" s="29"/>
     </row>
-    <row r="835" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A835" s="29" t="s">
         <v>2549</v>
       </c>
@@ -44312,7 +44306,7 @@
       <c r="L835" s="31"/>
       <c r="M835" s="29"/>
     </row>
-    <row r="836" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A836" s="29" t="s">
         <v>2550</v>
       </c>
@@ -44345,7 +44339,7 @@
       <c r="L836" s="31"/>
       <c r="M836" s="29"/>
     </row>
-    <row r="837" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A837" s="29" t="s">
         <v>2551</v>
       </c>
@@ -44378,7 +44372,7 @@
       <c r="L837" s="31"/>
       <c r="M837" s="29"/>
     </row>
-    <row r="838" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A838" s="29" t="s">
         <v>2552</v>
       </c>
@@ -44411,7 +44405,7 @@
       <c r="L838" s="31"/>
       <c r="M838" s="29"/>
     </row>
-    <row r="839" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A839" s="29" t="s">
         <v>2553</v>
       </c>
@@ -44444,7 +44438,7 @@
       <c r="L839" s="31"/>
       <c r="M839" s="29"/>
     </row>
-    <row r="840" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A840" s="29" t="s">
         <v>2554</v>
       </c>
@@ -44477,7 +44471,7 @@
       <c r="L840" s="31"/>
       <c r="M840" s="29"/>
     </row>
-    <row r="841" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A841" s="29" t="s">
         <v>2555</v>
       </c>
@@ -44510,7 +44504,7 @@
       <c r="L841" s="31"/>
       <c r="M841" s="29"/>
     </row>
-    <row r="842" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A842" s="29" t="s">
         <v>2556</v>
       </c>
@@ -44543,7 +44537,7 @@
       <c r="L842" s="31"/>
       <c r="M842" s="29"/>
     </row>
-    <row r="843" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A843" s="29" t="s">
         <v>2557</v>
       </c>
@@ -44576,7 +44570,7 @@
       <c r="L843" s="31"/>
       <c r="M843" s="29"/>
     </row>
-    <row r="844" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A844" s="29" t="s">
         <v>2558</v>
       </c>
@@ -44609,7 +44603,7 @@
       <c r="L844" s="31"/>
       <c r="M844" s="29"/>
     </row>
-    <row r="845" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A845" s="29" t="s">
         <v>2559</v>
       </c>
@@ -44642,7 +44636,7 @@
       <c r="L845" s="31"/>
       <c r="M845" s="29"/>
     </row>
-    <row r="846" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A846" s="29" t="s">
         <v>2560</v>
       </c>
@@ -44675,7 +44669,7 @@
       <c r="L846" s="31"/>
       <c r="M846" s="29"/>
     </row>
-    <row r="847" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A847" s="29" t="s">
         <v>2561</v>
       </c>
@@ -44708,7 +44702,7 @@
       <c r="L847" s="31"/>
       <c r="M847" s="29"/>
     </row>
-    <row r="848" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A848" s="29" t="s">
         <v>2562</v>
       </c>
@@ -44741,7 +44735,7 @@
       <c r="L848" s="31"/>
       <c r="M848" s="29"/>
     </row>
-    <row r="849" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A849" s="29" t="s">
         <v>2563</v>
       </c>
@@ -44774,7 +44768,7 @@
       <c r="L849" s="31"/>
       <c r="M849" s="29"/>
     </row>
-    <row r="850" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A850" s="29" t="s">
         <v>2564</v>
       </c>
@@ -44807,7 +44801,7 @@
       <c r="L850" s="31"/>
       <c r="M850" s="29"/>
     </row>
-    <row r="851" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A851" s="29" t="s">
         <v>2565</v>
       </c>
@@ -44840,7 +44834,7 @@
       <c r="L851" s="31"/>
       <c r="M851" s="29"/>
     </row>
-    <row r="852" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A852" s="29" t="s">
         <v>1965</v>
       </c>
@@ -44873,7 +44867,7 @@
       <c r="L852" s="31"/>
       <c r="M852" s="29"/>
     </row>
-    <row r="853" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A853" s="29" t="s">
         <v>1966</v>
       </c>
@@ -44906,7 +44900,7 @@
       <c r="L853" s="31"/>
       <c r="M853" s="29"/>
     </row>
-    <row r="854" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A854" s="29" t="s">
         <v>1871</v>
       </c>
@@ -44943,7 +44937,7 @@
       <c r="L854" s="31"/>
       <c r="M854" s="29"/>
     </row>
-    <row r="855" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A855" s="29" t="s">
         <v>1875</v>
       </c>
@@ -44968,7 +44962,7 @@
       <c r="L855" s="31"/>
       <c r="M855" s="29"/>
     </row>
-    <row r="856" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A856" s="29" t="s">
         <v>1874</v>
       </c>
@@ -45001,7 +44995,7 @@
       <c r="L856" s="31"/>
       <c r="M856" s="29"/>
     </row>
-    <row r="857" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A857" s="29" t="s">
         <v>1881</v>
       </c>
@@ -45034,7 +45028,7 @@
       <c r="L857" s="31"/>
       <c r="M857" s="29"/>
     </row>
-    <row r="858" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A858" s="29" t="s">
         <v>1882</v>
       </c>
@@ -45067,7 +45061,7 @@
       <c r="L858" s="31"/>
       <c r="M858" s="29"/>
     </row>
-    <row r="859" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A859" s="29" t="s">
         <v>1886</v>
       </c>
@@ -45100,7 +45094,7 @@
       <c r="L859" s="31"/>
       <c r="M859" s="29"/>
     </row>
-    <row r="860" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>2254</v>
       </c>
@@ -45131,7 +45125,7 @@
       <c r="L860" s="31"/>
       <c r="M860" s="29"/>
     </row>
-    <row r="861" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A861" s="29" t="s">
         <v>2275</v>
       </c>
@@ -45162,7 +45156,7 @@
       <c r="L861" s="31"/>
       <c r="M861" s="29"/>
     </row>
-    <row r="862" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A862" s="80" t="s">
         <v>2283</v>
       </c>
@@ -45193,7 +45187,7 @@
       <c r="L862" s="31"/>
       <c r="M862" s="29"/>
     </row>
-    <row r="863" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A863" s="29" t="s">
         <v>2278</v>
       </c>
@@ -45224,7 +45218,7 @@
       <c r="L863" s="31"/>
       <c r="M863" s="29"/>
     </row>
-    <row r="864" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A864" s="29" t="s">
         <v>1910</v>
       </c>
@@ -45259,7 +45253,7 @@
       <c r="L864" s="31"/>
       <c r="M864" s="29"/>
     </row>
-    <row r="865" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A865" s="29" t="s">
         <v>1904</v>
       </c>
@@ -45294,7 +45288,7 @@
       <c r="L865" s="31"/>
       <c r="M865" s="29"/>
     </row>
-    <row r="866" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A866" s="29" t="s">
         <v>1911</v>
       </c>
@@ -45331,7 +45325,7 @@
       <c r="L866" s="31"/>
       <c r="M866" s="29"/>
     </row>
-    <row r="867" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A867" s="29" t="s">
         <v>1912</v>
       </c>
@@ -45362,7 +45356,7 @@
       <c r="L867" s="31"/>
       <c r="M867" s="29"/>
     </row>
-    <row r="868" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A868" s="29" t="s">
         <v>1913</v>
       </c>
@@ -45397,7 +45391,7 @@
       <c r="L868" s="31"/>
       <c r="M868" s="29"/>
     </row>
-    <row r="869" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A869" s="29" t="s">
         <v>1914</v>
       </c>
@@ -45432,7 +45426,7 @@
       <c r="L869" s="31"/>
       <c r="M869" s="29"/>
     </row>
-    <row r="870" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A870" s="29" t="s">
         <v>1915</v>
       </c>
@@ -45465,7 +45459,7 @@
       <c r="L870" s="31"/>
       <c r="M870" s="29"/>
     </row>
-    <row r="871" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A871" s="29" t="s">
         <v>1916</v>
       </c>
@@ -45500,7 +45494,7 @@
       <c r="L871" s="31"/>
       <c r="M871" s="29"/>
     </row>
-    <row r="872" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A872" s="29" t="s">
         <v>1917</v>
       </c>
@@ -45529,7 +45523,7 @@
       <c r="L872" s="31"/>
       <c r="M872" s="29"/>
     </row>
-    <row r="873" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A873" s="29" t="s">
         <v>1918</v>
       </c>
@@ -45558,7 +45552,7 @@
       <c r="L873" s="31"/>
       <c r="M873" s="29"/>
     </row>
-    <row r="874" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A874" s="29" t="s">
         <v>1919</v>
       </c>
@@ -45595,7 +45589,7 @@
       <c r="L874" s="31"/>
       <c r="M874" s="29"/>
     </row>
-    <row r="875" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A875" s="29" t="s">
         <v>1920</v>
       </c>
@@ -45630,7 +45624,7 @@
       <c r="L875" s="31"/>
       <c r="M875" s="29"/>
     </row>
-    <row r="876" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A876" s="29" t="s">
         <v>2240</v>
       </c>
@@ -45663,7 +45657,7 @@
       <c r="L876" s="31"/>
       <c r="M876" s="29"/>
     </row>
-    <row r="877" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A877" s="29" t="s">
         <v>1962</v>
       </c>
@@ -45698,7 +45692,7 @@
       <c r="L877" s="31"/>
       <c r="M877" s="29"/>
     </row>
-    <row r="878" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A878" s="29" t="s">
         <v>1967</v>
       </c>
@@ -45733,7 +45727,7 @@
       <c r="L878" s="31"/>
       <c r="M878" s="29"/>
     </row>
-    <row r="879" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A879" s="29" t="s">
         <v>2239</v>
       </c>
@@ -45768,7 +45762,7 @@
       <c r="L879" s="31"/>
       <c r="M879" s="29"/>
     </row>
-    <row r="880" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A880" s="29" t="s">
         <v>2238</v>
       </c>
@@ -45803,7 +45797,7 @@
       <c r="L880" s="31"/>
       <c r="M880" s="29"/>
     </row>
-    <row r="881" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A881" s="29" t="s">
         <v>2237</v>
       </c>
@@ -45836,7 +45830,7 @@
       <c r="L881" s="31"/>
       <c r="M881" s="29"/>
     </row>
-    <row r="882" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A882" s="29" t="s">
         <v>1894</v>
       </c>
@@ -45869,7 +45863,7 @@
       <c r="L882" s="31"/>
       <c r="M882" s="29"/>
     </row>
-    <row r="883" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A883" s="29" t="s">
         <v>1895</v>
       </c>
@@ -45896,7 +45890,7 @@
       <c r="L883" s="31"/>
       <c r="M883" s="29"/>
     </row>
-    <row r="884" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A884" s="29" t="s">
         <v>1896</v>
       </c>
@@ -45931,7 +45925,7 @@
       <c r="L884" s="31"/>
       <c r="M884" s="29"/>
     </row>
-    <row r="885" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A885" s="29" t="s">
         <v>2255</v>
       </c>
@@ -45962,7 +45956,7 @@
       <c r="L885" s="31"/>
       <c r="M885" s="29"/>
     </row>
-    <row r="886" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A886" s="29" t="s">
         <v>2269</v>
       </c>
@@ -45997,7 +45991,7 @@
       <c r="L886" s="31"/>
       <c r="M886" s="29"/>
     </row>
-    <row r="887" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A887" s="29" t="s">
         <v>2270</v>
       </c>
@@ -46032,7 +46026,7 @@
       <c r="L887" s="31"/>
       <c r="M887" s="29"/>
     </row>
-    <row r="888" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A888" s="29" t="s">
         <v>2272</v>
       </c>
@@ -46067,7 +46061,7 @@
       <c r="L888" s="31"/>
       <c r="M888" s="29"/>
     </row>
-    <row r="889" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>2282</v>
       </c>
@@ -46104,7 +46098,7 @@
       <c r="L889" s="31"/>
       <c r="M889" s="29"/>
     </row>
-    <row r="890" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A890" s="29" t="s">
         <v>2317</v>
       </c>
@@ -46139,7 +46133,7 @@
       <c r="L890" s="31"/>
       <c r="M890" s="29"/>
     </row>
-    <row r="891" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A891" s="29" t="s">
         <v>2318</v>
       </c>
@@ -46174,7 +46168,7 @@
       <c r="L891" s="31"/>
       <c r="M891" s="29"/>
     </row>
-    <row r="892" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A892" s="29" t="s">
         <v>2319</v>
       </c>
@@ -46209,7 +46203,7 @@
       <c r="L892" s="31"/>
       <c r="M892" s="29"/>
     </row>
-    <row r="893" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A893" s="29" t="s">
         <v>2320</v>
       </c>
@@ -46244,7 +46238,7 @@
       <c r="L893" s="31"/>
       <c r="M893" s="29"/>
     </row>
-    <row r="894" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A894" s="29" t="s">
         <v>2321</v>
       </c>
@@ -46279,7 +46273,7 @@
       <c r="L894" s="31"/>
       <c r="M894" s="29"/>
     </row>
-    <row r="895" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A895" s="29" t="s">
         <v>2322</v>
       </c>
@@ -46314,7 +46308,7 @@
       <c r="L895" s="31"/>
       <c r="M895" s="29"/>
     </row>
-    <row r="896" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A896" s="29" t="s">
         <v>2323</v>
       </c>
@@ -46349,7 +46343,7 @@
       <c r="L896" s="31"/>
       <c r="M896" s="29"/>
     </row>
-    <row r="897" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A897" s="29" t="s">
         <v>2324</v>
       </c>
@@ -46384,7 +46378,7 @@
       <c r="L897" s="31"/>
       <c r="M897" s="29"/>
     </row>
-    <row r="898" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A898" s="29" t="s">
         <v>2325</v>
       </c>
@@ -46419,7 +46413,7 @@
       <c r="L898" s="31"/>
       <c r="M898" s="29"/>
     </row>
-    <row r="899" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A899" s="29" t="s">
         <v>2326</v>
       </c>
@@ -46454,7 +46448,7 @@
       <c r="L899" s="31"/>
       <c r="M899" s="29"/>
     </row>
-    <row r="900" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A900" s="29" t="s">
         <v>2327</v>
       </c>
@@ -46489,7 +46483,7 @@
       <c r="L900" s="31"/>
       <c r="M900" s="29"/>
     </row>
-    <row r="901" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A901" s="29" t="s">
         <v>2328</v>
       </c>
@@ -46524,7 +46518,7 @@
       <c r="L901" s="31"/>
       <c r="M901" s="29"/>
     </row>
-    <row r="902" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A902" s="29" t="s">
         <v>2329</v>
       </c>
@@ -46559,7 +46553,7 @@
       <c r="L902" s="31"/>
       <c r="M902" s="29"/>
     </row>
-    <row r="903" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A903" s="29" t="s">
         <v>2330</v>
       </c>
@@ -46594,7 +46588,7 @@
       <c r="L903" s="31"/>
       <c r="M903" s="29"/>
     </row>
-    <row r="904" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A904" s="29" t="s">
         <v>2331</v>
       </c>
@@ -46629,7 +46623,7 @@
       <c r="L904" s="31"/>
       <c r="M904" s="29"/>
     </row>
-    <row r="905" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A905" s="29" t="s">
         <v>2332</v>
       </c>
@@ -46664,7 +46658,7 @@
       <c r="L905" s="31"/>
       <c r="M905" s="29"/>
     </row>
-    <row r="906" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A906" s="29" t="s">
         <v>2333</v>
       </c>
@@ -46699,7 +46693,7 @@
       <c r="L906" s="31"/>
       <c r="M906" s="29"/>
     </row>
-    <row r="907" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A907" s="29" t="s">
         <v>2334</v>
       </c>
@@ -46734,7 +46728,7 @@
       <c r="L907" s="31"/>
       <c r="M907" s="29"/>
     </row>
-    <row r="908" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A908" s="29" t="s">
         <v>2335</v>
       </c>
@@ -46769,7 +46763,7 @@
       <c r="L908" s="31"/>
       <c r="M908" s="29"/>
     </row>
-    <row r="909" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A909" s="29" t="s">
         <v>2336</v>
       </c>
@@ -46804,7 +46798,7 @@
       <c r="L909" s="31"/>
       <c r="M909" s="29"/>
     </row>
-    <row r="910" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A910" s="29" t="s">
         <v>2337</v>
       </c>
@@ -46839,7 +46833,7 @@
       <c r="L910" s="31"/>
       <c r="M910" s="29"/>
     </row>
-    <row r="911" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A911" s="29" t="s">
         <v>2338</v>
       </c>
@@ -46874,7 +46868,7 @@
       <c r="L911" s="31"/>
       <c r="M911" s="29"/>
     </row>
-    <row r="912" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A912" s="29" t="s">
         <v>2339</v>
       </c>
@@ -46909,7 +46903,7 @@
       <c r="L912" s="31"/>
       <c r="M912" s="29"/>
     </row>
-    <row r="913" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A913" s="29" t="s">
         <v>2340</v>
       </c>
@@ -46944,7 +46938,7 @@
       <c r="L913" s="31"/>
       <c r="M913" s="29"/>
     </row>
-    <row r="914" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A914" s="29" t="s">
         <v>2341</v>
       </c>
@@ -46979,7 +46973,7 @@
       <c r="L914" s="31"/>
       <c r="M914" s="29"/>
     </row>
-    <row r="915" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A915" s="29" t="s">
         <v>2342</v>
       </c>
@@ -47014,7 +47008,7 @@
       <c r="L915" s="31"/>
       <c r="M915" s="29"/>
     </row>
-    <row r="916" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A916" s="29" t="s">
         <v>2343</v>
       </c>
@@ -47049,7 +47043,7 @@
       <c r="L916" s="31"/>
       <c r="M916" s="29"/>
     </row>
-    <row r="917" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A917" s="29" t="s">
         <v>2344</v>
       </c>
@@ -47084,7 +47078,7 @@
       <c r="L917" s="31"/>
       <c r="M917" s="29"/>
     </row>
-    <row r="918" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A918" s="29" t="s">
         <v>2345</v>
       </c>
@@ -47119,7 +47113,7 @@
       <c r="L918" s="31"/>
       <c r="M918" s="29"/>
     </row>
-    <row r="919" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A919" s="29" t="s">
         <v>2346</v>
       </c>
@@ -47154,7 +47148,7 @@
       <c r="L919" s="31"/>
       <c r="M919" s="29"/>
     </row>
-    <row r="920" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A920" s="29" t="s">
         <v>2347</v>
       </c>
@@ -47189,7 +47183,7 @@
       <c r="L920" s="31"/>
       <c r="M920" s="29"/>
     </row>
-    <row r="921" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A921" s="29" t="s">
         <v>2348</v>
       </c>
@@ -47224,7 +47218,7 @@
       <c r="L921" s="31"/>
       <c r="M921" s="29"/>
     </row>
-    <row r="922" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A922" s="29" t="s">
         <v>2349</v>
       </c>
@@ -47259,7 +47253,7 @@
       <c r="L922" s="31"/>
       <c r="M922" s="29"/>
     </row>
-    <row r="923" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A923" s="29" t="s">
         <v>2350</v>
       </c>
@@ -47294,7 +47288,7 @@
       <c r="L923" s="31"/>
       <c r="M923" s="29"/>
     </row>
-    <row r="924" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A924" s="29" t="s">
         <v>2351</v>
       </c>
@@ -47329,7 +47323,7 @@
       <c r="L924" s="31"/>
       <c r="M924" s="29"/>
     </row>
-    <row r="925" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A925" s="29" t="s">
         <v>2352</v>
       </c>
@@ -47364,7 +47358,7 @@
       <c r="L925" s="31"/>
       <c r="M925" s="29"/>
     </row>
-    <row r="926" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A926" s="29" t="s">
         <v>2353</v>
       </c>
@@ -47399,7 +47393,7 @@
       <c r="L926" s="31"/>
       <c r="M926" s="29"/>
     </row>
-    <row r="927" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A927" s="29" t="s">
         <v>2566</v>
       </c>
@@ -47434,7 +47428,7 @@
       <c r="L927" s="31"/>
       <c r="M927" s="29"/>
     </row>
-    <row r="928" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A928" s="29" t="s">
         <v>2567</v>
       </c>
@@ -47469,7 +47463,7 @@
       <c r="L928" s="31"/>
       <c r="M928" s="29"/>
     </row>
-    <row r="929" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A929" s="29" t="s">
         <v>2568</v>
       </c>
@@ -47504,7 +47498,7 @@
       <c r="L929" s="31"/>
       <c r="M929" s="29"/>
     </row>
-    <row r="930" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A930" s="29" t="s">
         <v>2358</v>
       </c>
@@ -47539,7 +47533,7 @@
       <c r="L930" s="31"/>
       <c r="M930" s="29"/>
     </row>
-    <row r="931" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A931" s="29" t="s">
         <v>2366</v>
       </c>
@@ -47564,7 +47558,7 @@
       <c r="L931" s="31"/>
       <c r="M931" s="29"/>
     </row>
-    <row r="932" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A932" s="29" t="s">
         <v>2368</v>
       </c>
@@ -47589,7 +47583,7 @@
       <c r="L932" s="31"/>
       <c r="M932" s="29"/>
     </row>
-    <row r="933" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A933" s="29" t="s">
         <v>2371</v>
       </c>
@@ -47616,7 +47610,7 @@
       <c r="L933" s="31"/>
       <c r="M933" s="29"/>
     </row>
-    <row r="934" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A934" s="29" t="s">
         <v>2374</v>
       </c>
@@ -47643,7 +47637,7 @@
       <c r="L934" s="31"/>
       <c r="M934" s="29"/>
     </row>
-    <row r="935" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A935" s="29" t="s">
         <v>2377</v>
       </c>
@@ -47668,7 +47662,7 @@
       <c r="L935" s="31"/>
       <c r="M935" s="29"/>
     </row>
-    <row r="936" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A936" s="29" t="s">
         <v>2381</v>
       </c>
@@ -47693,7 +47687,7 @@
       <c r="L936" s="31"/>
       <c r="M936" s="29"/>
     </row>
-    <row r="937" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A937" s="29" t="s">
         <v>2382</v>
       </c>
@@ -47718,7 +47712,7 @@
       <c r="L937" s="31"/>
       <c r="M937" s="29"/>
     </row>
-    <row r="938" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A938" s="29" t="s">
         <v>2383</v>
       </c>
@@ -47743,7 +47737,7 @@
       <c r="L938" s="31"/>
       <c r="M938" s="29"/>
     </row>
-    <row r="939" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A939" s="29" t="s">
         <v>2389</v>
       </c>
@@ -47770,7 +47764,7 @@
       <c r="L939" s="31"/>
       <c r="M939" s="29"/>
     </row>
-    <row r="940" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A940" s="29" t="s">
         <v>2390</v>
       </c>
@@ -47795,7 +47789,7 @@
       <c r="L940" s="31"/>
       <c r="M940" s="29"/>
     </row>
-    <row r="941" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A941" s="29" t="s">
         <v>2392</v>
       </c>
@@ -47820,7 +47814,7 @@
       <c r="L941" s="31"/>
       <c r="M941" s="29"/>
     </row>
-    <row r="942" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A942" s="29" t="s">
         <v>2393</v>
       </c>
@@ -47845,7 +47839,7 @@
       <c r="L942" s="31"/>
       <c r="M942" s="29"/>
     </row>
-    <row r="943" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A943" s="29" t="s">
         <v>2394</v>
       </c>
@@ -47870,7 +47864,7 @@
       <c r="L943" s="31"/>
       <c r="M943" s="29"/>
     </row>
-    <row r="944" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A944" s="29" t="s">
         <v>2395</v>
       </c>
@@ -47895,7 +47889,7 @@
       <c r="L944" s="31"/>
       <c r="M944" s="29"/>
     </row>
-    <row r="945" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A945" s="29" t="s">
         <v>2397</v>
       </c>
@@ -47920,7 +47914,7 @@
       <c r="L945" s="31"/>
       <c r="M945" s="29"/>
     </row>
-    <row r="946" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>2365</v>
       </c>
@@ -47947,7 +47941,7 @@
       <c r="L946" s="31"/>
       <c r="M946" s="29"/>
     </row>
-    <row r="947" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A947" s="29" t="s">
         <v>2570</v>
       </c>
@@ -47980,7 +47974,7 @@
       <c r="L947" s="31"/>
       <c r="M947" s="29"/>
     </row>
-    <row r="948" spans="1:13" ht="17" hidden="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A948" s="29" t="s">
         <v>2574</v>
       </c>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD25743-B5FF-B14D-8BD5-C35440FD73A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC71E99-6CD2-5346-B215-9DF306354AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6900" yWindow="1760" windowWidth="23340" windowHeight="14260" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="12" r:id="rId3"/>
+    <pivotCache cacheId="13" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -8236,7 +8236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8451,6 +8451,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17334,7 +17336,70 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17567,69 +17632,6 @@
     </i>
     <i>
       <x v="53"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -25401,13 +25403,13 @@
       <c r="M233" s="29"/>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A234" s="39" t="s">
+      <c r="A234" s="120" t="s">
         <v>518</v>
       </c>
-      <c r="B234" s="40"/>
-      <c r="C234" s="39"/>
-      <c r="D234" s="40"/>
-      <c r="E234" s="39"/>
+      <c r="B234" s="121"/>
+      <c r="C234" s="120"/>
+      <c r="D234" s="121"/>
+      <c r="E234" s="120"/>
       <c r="F234" s="31" t="s">
         <v>512</v>
       </c>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9492C04D-52D6-2C46-99CC-F3C01445A124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9FBFF-0FF0-E846-B08C-BF5B18C3C68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3740" yWindow="1740" windowWidth="26500" windowHeight="14260" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="16" r:id="rId3"/>
-    <pivotCache cacheId="22" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7881" uniqueCount="2638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7906" uniqueCount="2649">
   <si>
     <t>Tag</t>
   </si>
@@ -7955,6 +7955,39 @@
   </si>
   <si>
     <t>in_77</t>
+  </si>
+  <si>
+    <t>d_o_120</t>
+  </si>
+  <si>
+    <t>ip127</t>
+  </si>
+  <si>
+    <t>A&amp;H</t>
+  </si>
+  <si>
+    <t>reference Mic</t>
+  </si>
+  <si>
+    <t>rt970</t>
+  </si>
+  <si>
+    <t>ZVIU-A005</t>
+  </si>
+  <si>
+    <t>2605-0500</t>
+  </si>
+  <si>
+    <t>Stg Dsp TV</t>
+  </si>
+  <si>
+    <t>2310-0904</t>
+  </si>
+  <si>
+    <t>33m</t>
+  </si>
+  <si>
+    <t>avshop.ca</t>
   </si>
 </sst>
 </file>
@@ -8377,7 +8410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8592,25 +8625,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8621,9 +8636,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8693,6 +8705,52 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -8813,86 +8871,6 @@
         <scheme val="major"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -8955,6 +8933,40 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
     </dxf>
     <dxf>
       <border outline="0">
@@ -17482,7 +17494,70 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17738,86 +17813,23 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M973" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="A1:M972" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="10" totalsRowDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{B4B079C1-C2FD-4543-BF85-C40BEF0990F3}" name="SrcPort" dataDxfId="17" totalsRowDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{AC3F24B7-C4B3-CC4C-A7E3-6BB3319549AD}" name="DstTag" dataDxfId="16" totalsRowDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{723F3509-3335-1241-A5F2-61206DF5595A}" name="DstPort" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{7D4B1BBD-F461-7E4D-A272-8B68F8EE10FB}" name="Type" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{AECEAF7F-6B15-0348-8A77-06BCE8B4829E}" name="Protocol" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{342ADFC8-8081-D246-A6B4-8A5EE1D7A44F}" name="Length" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{52DF302F-1C2C-3641-87D6-1971497058A4}" name="Labelled?" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{C0483DE7-3B56-B145-9C6E-0E6DE59EDB05}" name="Usage" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{5CD47A7F-4A34-3A46-926E-FFBED1348BD5}" name="Notes" dataDxfId="14" totalsRowDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{5C50ECE5-BC4B-6C47-90C1-11D93DE5D81A}" name="Invoice" dataDxfId="13" totalsRowDxfId="0"/>
-    <tableColumn id="12" xr3:uid="{939C157F-5419-B846-9271-37F3BBF6433E}" name="Pathway" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B4B079C1-C2FD-4543-BF85-C40BEF0990F3}" name="SrcPort" dataDxfId="15" totalsRowDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{AC3F24B7-C4B3-CC4C-A7E3-6BB3319549AD}" name="DstTag" dataDxfId="14" totalsRowDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{723F3509-3335-1241-A5F2-61206DF5595A}" name="DstPort" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{7D4B1BBD-F461-7E4D-A272-8B68F8EE10FB}" name="Type" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{AECEAF7F-6B15-0348-8A77-06BCE8B4829E}" name="Protocol" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{342ADFC8-8081-D246-A6B4-8A5EE1D7A44F}" name="Length" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{52DF302F-1C2C-3641-87D6-1971497058A4}" name="Labelled?" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{C0483DE7-3B56-B145-9C6E-0E6DE59EDB05}" name="Usage" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{5CD47A7F-4A34-3A46-926E-FFBED1348BD5}" name="Notes" dataDxfId="7" totalsRowDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{5C50ECE5-BC4B-6C47-90C1-11D93DE5D81A}" name="Invoice" dataDxfId="6" totalsRowDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{939C157F-5419-B846-9271-37F3BBF6433E}" name="Pathway" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21756,10 +21768,18 @@
       <c r="A120" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="B120" s="22"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="22"/>
-      <c r="E120" s="23"/>
+      <c r="B120" s="22" t="s">
+        <v>2643</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D120" s="22" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E120" s="23" t="s">
+        <v>344</v>
+      </c>
       <c r="F120" s="23" t="s">
         <v>38</v>
       </c>
@@ -21772,7 +21792,9 @@
       <c r="I120" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="J120" s="23"/>
+      <c r="J120" s="23" t="s">
+        <v>2645</v>
+      </c>
       <c r="K120" s="23"/>
       <c r="L120" s="23"/>
       <c r="M120" s="24"/>
@@ -48047,13 +48069,13 @@
       <c r="E945" s="82" t="s">
         <v>2571</v>
       </c>
-      <c r="F945" s="126" t="s">
+      <c r="F945" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G945" s="126" t="s">
+      <c r="G945" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H945" s="127">
+      <c r="H945" s="23">
         <v>0</v>
       </c>
       <c r="I945" s="19" t="s">
@@ -48063,7 +48085,7 @@
         <v>1280</v>
       </c>
       <c r="K945" s="29"/>
-      <c r="L945" s="126"/>
+      <c r="L945" s="31"/>
       <c r="M945" s="29"/>
     </row>
     <row r="946" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -48082,13 +48104,13 @@
       <c r="E946" s="82" t="s">
         <v>2572</v>
       </c>
-      <c r="F946" s="126" t="s">
+      <c r="F946" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G946" s="126" t="s">
+      <c r="G946" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H946" s="127">
+      <c r="H946" s="23">
         <v>0</v>
       </c>
       <c r="I946" s="19" t="s">
@@ -48098,256 +48120,256 @@
         <v>1281</v>
       </c>
       <c r="K946" s="29"/>
-      <c r="L946" s="126"/>
+      <c r="L946" s="31"/>
       <c r="M946" s="29"/>
     </row>
     <row r="947" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A947" s="29" t="s">
         <v>2591</v>
       </c>
-      <c r="B947" s="128" t="s">
+      <c r="B947" s="100" t="s">
         <v>2570</v>
       </c>
-      <c r="C947" s="122" t="s">
+      <c r="C947" s="83" t="s">
         <v>876</v>
       </c>
-      <c r="D947" s="123" t="s">
+      <c r="D947" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E947" s="122" t="s">
+      <c r="E947" s="83" t="s">
         <v>2573</v>
       </c>
-      <c r="F947" s="126" t="s">
+      <c r="F947" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G947" s="126" t="s">
+      <c r="G947" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H947" s="129">
+      <c r="H947" s="29">
         <v>0</v>
       </c>
-      <c r="I947" s="125" t="s">
+      <c r="I947" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J947" s="29" t="s">
         <v>1282</v>
       </c>
       <c r="K947" s="29"/>
-      <c r="L947" s="126"/>
+      <c r="L947" s="31"/>
       <c r="M947" s="29"/>
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A948" s="29" t="s">
         <v>2592</v>
       </c>
-      <c r="B948" s="128" t="s">
+      <c r="B948" s="100" t="s">
         <v>2570</v>
       </c>
-      <c r="C948" s="122" t="s">
+      <c r="C948" s="83" t="s">
         <v>875</v>
       </c>
-      <c r="D948" s="123" t="s">
+      <c r="D948" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E948" s="122" t="s">
+      <c r="E948" s="83" t="s">
         <v>2574</v>
       </c>
-      <c r="F948" s="126" t="s">
+      <c r="F948" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G948" s="126" t="s">
+      <c r="G948" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H948" s="129">
+      <c r="H948" s="29">
         <v>0</v>
       </c>
-      <c r="I948" s="125" t="s">
+      <c r="I948" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J948" s="29" t="s">
         <v>1283</v>
       </c>
       <c r="K948" s="29"/>
-      <c r="L948" s="126"/>
+      <c r="L948" s="31"/>
       <c r="M948" s="29"/>
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A949" s="29" t="s">
         <v>2593</v>
       </c>
-      <c r="B949" s="128" t="s">
+      <c r="B949" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="C949" s="122" t="s">
+      <c r="C949" s="83" t="s">
         <v>520</v>
       </c>
-      <c r="D949" s="123" t="s">
+      <c r="D949" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E949" s="122" t="s">
+      <c r="E949" s="83" t="s">
         <v>2575</v>
       </c>
-      <c r="F949" s="126" t="s">
+      <c r="F949" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G949" s="126" t="s">
+      <c r="G949" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H949" s="129">
+      <c r="H949" s="29">
         <v>0</v>
       </c>
-      <c r="I949" s="125" t="s">
+      <c r="I949" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J949" s="29" t="s">
         <v>1284</v>
       </c>
       <c r="K949" s="29"/>
-      <c r="L949" s="126"/>
+      <c r="L949" s="31"/>
       <c r="M949" s="29"/>
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A950" s="29" t="s">
         <v>2594</v>
       </c>
-      <c r="B950" s="128" t="s">
+      <c r="B950" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="C950" s="122" t="s">
+      <c r="C950" s="83" t="s">
         <v>522</v>
       </c>
-      <c r="D950" s="123" t="s">
+      <c r="D950" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E950" s="122" t="s">
+      <c r="E950" s="83" t="s">
         <v>2576</v>
       </c>
-      <c r="F950" s="126" t="s">
+      <c r="F950" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G950" s="126" t="s">
+      <c r="G950" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H950" s="129">
+      <c r="H950" s="29">
         <v>0</v>
       </c>
-      <c r="I950" s="125" t="s">
+      <c r="I950" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J950" s="29" t="s">
         <v>1285</v>
       </c>
       <c r="K950" s="29"/>
-      <c r="L950" s="126"/>
+      <c r="L950" s="31"/>
       <c r="M950" s="29"/>
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A951" s="29" t="s">
         <v>2595</v>
       </c>
-      <c r="B951" s="128" t="s">
+      <c r="B951" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="C951" s="122" t="s">
+      <c r="C951" s="83" t="s">
         <v>876</v>
       </c>
-      <c r="D951" s="123" t="s">
+      <c r="D951" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E951" s="122" t="s">
+      <c r="E951" s="83" t="s">
         <v>2577</v>
       </c>
-      <c r="F951" s="126" t="s">
+      <c r="F951" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G951" s="126" t="s">
+      <c r="G951" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H951" s="129">
+      <c r="H951" s="29">
         <v>0</v>
       </c>
-      <c r="I951" s="125" t="s">
+      <c r="I951" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J951" s="29" t="s">
         <v>1286</v>
       </c>
       <c r="K951" s="29"/>
-      <c r="L951" s="126"/>
+      <c r="L951" s="31"/>
       <c r="M951" s="29"/>
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A952" s="29" t="s">
         <v>2596</v>
       </c>
-      <c r="B952" s="128" t="s">
+      <c r="B952" s="100" t="s">
         <v>357</v>
       </c>
-      <c r="C952" s="122" t="s">
+      <c r="C952" s="83" t="s">
         <v>875</v>
       </c>
-      <c r="D952" s="123" t="s">
+      <c r="D952" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E952" s="122" t="s">
+      <c r="E952" s="83" t="s">
         <v>2578</v>
       </c>
-      <c r="F952" s="126" t="s">
+      <c r="F952" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G952" s="126" t="s">
+      <c r="G952" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H952" s="129">
+      <c r="H952" s="29">
         <v>0</v>
       </c>
-      <c r="I952" s="125" t="s">
+      <c r="I952" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J952" s="29" t="s">
         <v>1287</v>
       </c>
       <c r="K952" s="29"/>
-      <c r="L952" s="126"/>
+      <c r="L952" s="31"/>
       <c r="M952" s="29"/>
     </row>
     <row r="953" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A953" s="29" t="s">
         <v>2597</v>
       </c>
-      <c r="B953" s="128" t="s">
+      <c r="B953" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="C953" s="122" t="s">
+      <c r="C953" s="83" t="s">
         <v>520</v>
       </c>
-      <c r="D953" s="123" t="s">
+      <c r="D953" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E953" s="122" t="s">
+      <c r="E953" s="83" t="s">
         <v>2579</v>
       </c>
-      <c r="F953" s="126" t="s">
+      <c r="F953" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G953" s="126" t="s">
+      <c r="G953" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H953" s="129">
+      <c r="H953" s="29">
         <v>0</v>
       </c>
-      <c r="I953" s="125" t="s">
+      <c r="I953" s="120" t="s">
         <v>71</v>
       </c>
       <c r="J953" s="29" t="s">
         <v>1288</v>
       </c>
       <c r="K953" s="29"/>
-      <c r="L953" s="126"/>
+      <c r="L953" s="31"/>
       <c r="M953" s="29"/>
     </row>
     <row r="954" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A954" s="124" t="s">
+      <c r="A954" s="29" t="s">
         <v>2598</v>
       </c>
       <c r="B954" s="113" t="s">
@@ -48362,503 +48384,543 @@
       <c r="E954" s="82" t="s">
         <v>2580</v>
       </c>
-      <c r="F954" s="130" t="s">
+      <c r="F954" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G954" s="130" t="s">
+      <c r="G954" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H954" s="127">
+      <c r="H954" s="23">
         <v>0</v>
       </c>
       <c r="I954" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="J954" s="124" t="s">
+      <c r="J954" s="29" t="s">
         <v>1289</v>
       </c>
-      <c r="K954" s="124"/>
-      <c r="L954" s="130"/>
-      <c r="M954" s="124"/>
+      <c r="K954" s="29"/>
+      <c r="L954" s="31"/>
+      <c r="M954" s="29"/>
     </row>
     <row r="955" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A955" s="124" t="s">
+      <c r="A955" s="29" t="s">
         <v>2599</v>
       </c>
-      <c r="B955" s="128" t="s">
+      <c r="B955" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="C955" s="122" t="s">
+      <c r="C955" s="83" t="s">
         <v>876</v>
       </c>
-      <c r="D955" s="123" t="s">
+      <c r="D955" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E955" s="122" t="s">
+      <c r="E955" s="83" t="s">
         <v>2581</v>
       </c>
-      <c r="F955" s="130" t="s">
+      <c r="F955" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G955" s="130" t="s">
+      <c r="G955" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H955" s="129">
+      <c r="H955" s="29">
         <v>0</v>
       </c>
-      <c r="I955" s="125" t="s">
+      <c r="I955" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J955" s="124" t="s">
+      <c r="J955" s="29" t="s">
         <v>1291</v>
       </c>
-      <c r="K955" s="124"/>
-      <c r="L955" s="130"/>
-      <c r="M955" s="124"/>
+      <c r="K955" s="29"/>
+      <c r="L955" s="31"/>
+      <c r="M955" s="29"/>
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A956" s="124" t="s">
+      <c r="A956" s="29" t="s">
         <v>2600</v>
       </c>
-      <c r="B956" s="128" t="s">
+      <c r="B956" s="100" t="s">
         <v>358</v>
       </c>
-      <c r="C956" s="122" t="s">
+      <c r="C956" s="83" t="s">
         <v>875</v>
       </c>
-      <c r="D956" s="123" t="s">
+      <c r="D956" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E956" s="122" t="s">
+      <c r="E956" s="83" t="s">
         <v>2582</v>
       </c>
-      <c r="F956" s="130" t="s">
+      <c r="F956" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G956" s="130" t="s">
+      <c r="G956" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H956" s="129">
+      <c r="H956" s="29">
         <v>0</v>
       </c>
-      <c r="I956" s="125" t="s">
+      <c r="I956" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J956" s="124" t="s">
+      <c r="J956" s="29" t="s">
         <v>1292</v>
       </c>
-      <c r="K956" s="124"/>
-      <c r="L956" s="130"/>
-      <c r="M956" s="124"/>
+      <c r="K956" s="29"/>
+      <c r="L956" s="31"/>
+      <c r="M956" s="29"/>
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A957" s="124" t="s">
+      <c r="A957" s="29" t="s">
         <v>2601</v>
       </c>
-      <c r="B957" s="128" t="s">
+      <c r="B957" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="C957" s="122" t="s">
+      <c r="C957" s="83" t="s">
         <v>520</v>
       </c>
-      <c r="D957" s="123" t="s">
+      <c r="D957" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E957" s="122" t="s">
+      <c r="E957" s="83" t="s">
         <v>2583</v>
       </c>
-      <c r="F957" s="130" t="s">
+      <c r="F957" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G957" s="130" t="s">
+      <c r="G957" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H957" s="129">
+      <c r="H957" s="29">
         <v>0</v>
       </c>
-      <c r="I957" s="125" t="s">
+      <c r="I957" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J957" s="124" t="s">
+      <c r="J957" s="29" t="s">
         <v>1293</v>
       </c>
-      <c r="K957" s="124"/>
-      <c r="L957" s="130"/>
-      <c r="M957" s="124"/>
+      <c r="K957" s="29"/>
+      <c r="L957" s="31"/>
+      <c r="M957" s="29"/>
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A958" s="124" t="s">
+      <c r="A958" s="29" t="s">
         <v>2602</v>
       </c>
-      <c r="B958" s="128" t="s">
+      <c r="B958" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="C958" s="122" t="s">
+      <c r="C958" s="83" t="s">
         <v>522</v>
       </c>
-      <c r="D958" s="123" t="s">
+      <c r="D958" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E958" s="122" t="s">
+      <c r="E958" s="83" t="s">
         <v>2584</v>
       </c>
-      <c r="F958" s="130" t="s">
+      <c r="F958" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G958" s="130" t="s">
+      <c r="G958" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H958" s="129">
+      <c r="H958" s="29">
         <v>0</v>
       </c>
-      <c r="I958" s="125" t="s">
+      <c r="I958" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J958" s="124" t="s">
+      <c r="J958" s="29" t="s">
         <v>2587</v>
       </c>
-      <c r="K958" s="124"/>
-      <c r="L958" s="130"/>
-      <c r="M958" s="124"/>
+      <c r="K958" s="29"/>
+      <c r="L958" s="31"/>
+      <c r="M958" s="29"/>
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A959" s="124" t="s">
+      <c r="A959" s="29" t="s">
         <v>2603</v>
       </c>
-      <c r="B959" s="128" t="s">
+      <c r="B959" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="C959" s="122" t="s">
+      <c r="C959" s="83" t="s">
         <v>876</v>
       </c>
-      <c r="D959" s="123" t="s">
+      <c r="D959" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E959" s="122" t="s">
+      <c r="E959" s="83" t="s">
         <v>2585</v>
       </c>
-      <c r="F959" s="130" t="s">
+      <c r="F959" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G959" s="130" t="s">
+      <c r="G959" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H959" s="129">
+      <c r="H959" s="29">
         <v>0</v>
       </c>
-      <c r="I959" s="125" t="s">
+      <c r="I959" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J959" s="124" t="s">
+      <c r="J959" s="29" t="s">
         <v>2588</v>
       </c>
-      <c r="K959" s="124"/>
-      <c r="L959" s="130"/>
-      <c r="M959" s="124"/>
+      <c r="K959" s="29"/>
+      <c r="L959" s="31"/>
+      <c r="M959" s="29"/>
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A960" s="124" t="s">
+      <c r="A960" s="29" t="s">
         <v>2604</v>
       </c>
-      <c r="B960" s="128" t="s">
+      <c r="B960" s="100" t="s">
         <v>359</v>
       </c>
-      <c r="C960" s="122" t="s">
+      <c r="C960" s="83" t="s">
         <v>875</v>
       </c>
-      <c r="D960" s="123" t="s">
+      <c r="D960" s="85" t="s">
         <v>1250</v>
       </c>
-      <c r="E960" s="122" t="s">
+      <c r="E960" s="83" t="s">
         <v>2586</v>
       </c>
-      <c r="F960" s="130" t="s">
+      <c r="F960" s="31" t="s">
         <v>1771</v>
       </c>
-      <c r="G960" s="130" t="s">
+      <c r="G960" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="H960" s="129">
+      <c r="H960" s="29">
         <v>0</v>
       </c>
-      <c r="I960" s="125" t="s">
+      <c r="I960" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="J960" s="124" t="s">
+      <c r="J960" s="29" t="s">
         <v>1296</v>
       </c>
-      <c r="K960" s="124"/>
-      <c r="L960" s="130"/>
-      <c r="M960" s="124"/>
+      <c r="K960" s="29"/>
+      <c r="L960" s="31"/>
+      <c r="M960" s="29"/>
     </row>
     <row r="961" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A961" s="124" t="s">
+      <c r="A961" s="29" t="s">
         <v>1254</v>
       </c>
-      <c r="B961" s="128" t="s">
+      <c r="B961" s="100" t="s">
         <v>2620</v>
       </c>
-      <c r="C961" s="122"/>
-      <c r="D961" s="123" t="s">
+      <c r="C961" s="83"/>
+      <c r="D961" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E961" s="122" t="s">
+      <c r="E961" s="83" t="s">
         <v>519</v>
       </c>
-      <c r="F961" s="130"/>
-      <c r="G961" s="130"/>
-      <c r="H961" s="129"/>
-      <c r="I961" s="125"/>
+      <c r="F961" s="31"/>
+      <c r="G961" s="31"/>
+      <c r="H961" s="29"/>
+      <c r="I961" s="120"/>
       <c r="J961" s="35" t="s">
         <v>2606</v>
       </c>
-      <c r="K961" s="124"/>
-      <c r="L961" s="130"/>
-      <c r="M961" s="124"/>
+      <c r="K961" s="29"/>
+      <c r="L961" s="31"/>
+      <c r="M961" s="29"/>
     </row>
     <row r="962" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A962" s="124" t="s">
+      <c r="A962" s="29" t="s">
         <v>1255</v>
       </c>
-      <c r="B962" s="128"/>
-      <c r="C962" s="122"/>
-      <c r="D962" s="123" t="s">
+      <c r="B962" s="100"/>
+      <c r="C962" s="83"/>
+      <c r="D962" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E962" s="122" t="s">
+      <c r="E962" s="83" t="s">
         <v>524</v>
       </c>
-      <c r="F962" s="130"/>
-      <c r="G962" s="130"/>
-      <c r="H962" s="129"/>
-      <c r="I962" s="125"/>
+      <c r="F962" s="31"/>
+      <c r="G962" s="31"/>
+      <c r="H962" s="29"/>
+      <c r="I962" s="120"/>
       <c r="J962" s="35" t="s">
         <v>2606</v>
       </c>
-      <c r="K962" s="124"/>
-      <c r="L962" s="130"/>
-      <c r="M962" s="124"/>
+      <c r="K962" s="29"/>
+      <c r="L962" s="31"/>
+      <c r="M962" s="29"/>
     </row>
     <row r="963" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A963" s="124" t="s">
+      <c r="A963" s="29" t="s">
         <v>1257</v>
       </c>
-      <c r="B963" s="128" t="s">
+      <c r="B963" s="100" t="s">
         <v>2616</v>
       </c>
-      <c r="C963" s="122"/>
-      <c r="D963" s="123" t="s">
+      <c r="C963" s="83"/>
+      <c r="D963" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E963" s="122" t="s">
+      <c r="E963" s="83" t="s">
         <v>871</v>
       </c>
-      <c r="F963" s="130"/>
-      <c r="G963" s="130"/>
-      <c r="H963" s="129"/>
-      <c r="I963" s="125"/>
+      <c r="F963" s="31"/>
+      <c r="G963" s="31"/>
+      <c r="H963" s="29"/>
+      <c r="I963" s="120"/>
       <c r="J963" s="33" t="s">
         <v>2607</v>
       </c>
-      <c r="K963" s="124"/>
-      <c r="L963" s="130"/>
-      <c r="M963" s="124"/>
+      <c r="K963" s="29"/>
+      <c r="L963" s="31"/>
+      <c r="M963" s="29"/>
     </row>
     <row r="964" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A964" s="124" t="s">
+      <c r="A964" s="29" t="s">
         <v>1259</v>
       </c>
-      <c r="B964" s="128" t="s">
+      <c r="B964" s="100" t="s">
         <v>2617</v>
       </c>
-      <c r="C964" s="122"/>
-      <c r="D964" s="123" t="s">
+      <c r="C964" s="83"/>
+      <c r="D964" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E964" s="122" t="s">
+      <c r="E964" s="83" t="s">
         <v>872</v>
       </c>
-      <c r="F964" s="130"/>
-      <c r="G964" s="130"/>
-      <c r="H964" s="129"/>
-      <c r="I964" s="125"/>
+      <c r="F964" s="31"/>
+      <c r="G964" s="31"/>
+      <c r="H964" s="29"/>
+      <c r="I964" s="120"/>
       <c r="J964" s="33" t="s">
         <v>2607</v>
       </c>
-      <c r="K964" s="124"/>
-      <c r="L964" s="130"/>
-      <c r="M964" s="124"/>
+      <c r="K964" s="29"/>
+      <c r="L964" s="31"/>
+      <c r="M964" s="29"/>
     </row>
     <row r="965" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A965" s="124" t="s">
+      <c r="A965" s="29" t="s">
         <v>2615</v>
       </c>
-      <c r="B965" s="128"/>
-      <c r="C965" s="122"/>
-      <c r="D965" s="123" t="s">
+      <c r="B965" s="100"/>
+      <c r="C965" s="83"/>
+      <c r="D965" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E965" s="122" t="s">
+      <c r="E965" s="83" t="s">
         <v>2367</v>
       </c>
-      <c r="F965" s="130"/>
-      <c r="G965" s="130"/>
-      <c r="H965" s="129"/>
-      <c r="I965" s="125"/>
+      <c r="F965" s="31"/>
+      <c r="G965" s="31"/>
+      <c r="H965" s="29"/>
+      <c r="I965" s="120"/>
       <c r="J965" s="19" t="s">
         <v>1077</v>
       </c>
-      <c r="K965" s="124"/>
-      <c r="L965" s="130"/>
-      <c r="M965" s="124"/>
+      <c r="K965" s="29"/>
+      <c r="L965" s="31"/>
+      <c r="M965" s="29"/>
     </row>
     <row r="966" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A966" s="124" t="s">
+      <c r="A966" s="29" t="s">
         <v>2614</v>
       </c>
       <c r="B966" s="113"/>
-      <c r="C966" s="131"/>
+      <c r="C966" s="121"/>
       <c r="D966" s="79" t="s">
         <v>2605</v>
       </c>
       <c r="E966" s="80" t="s">
         <v>2610</v>
       </c>
-      <c r="F966" s="130"/>
-      <c r="G966" s="130"/>
-      <c r="H966" s="127"/>
+      <c r="F966" s="31"/>
+      <c r="G966" s="31"/>
+      <c r="H966" s="23"/>
       <c r="I966" s="19"/>
       <c r="J966" s="35" t="s">
         <v>1077</v>
       </c>
-      <c r="K966" s="124"/>
-      <c r="L966" s="130"/>
-      <c r="M966" s="124"/>
+      <c r="K966" s="29"/>
+      <c r="L966" s="31"/>
+      <c r="M966" s="29"/>
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A967" s="124" t="s">
+      <c r="A967" s="29" t="s">
         <v>1741</v>
       </c>
-      <c r="B967" s="128" t="s">
+      <c r="B967" s="100" t="s">
         <v>2618</v>
       </c>
-      <c r="C967" s="132"/>
-      <c r="D967" s="123" t="s">
+      <c r="C967" s="122"/>
+      <c r="D967" s="85" t="s">
         <v>2605</v>
       </c>
       <c r="E967" s="69" t="s">
         <v>2611</v>
       </c>
-      <c r="F967" s="130"/>
-      <c r="G967" s="130"/>
-      <c r="H967" s="129"/>
-      <c r="I967" s="125"/>
+      <c r="F967" s="31"/>
+      <c r="G967" s="31"/>
+      <c r="H967" s="29"/>
+      <c r="I967" s="120"/>
       <c r="J967" s="33" t="s">
         <v>2608</v>
       </c>
-      <c r="K967" s="124"/>
-      <c r="L967" s="130"/>
-      <c r="M967" s="124"/>
+      <c r="K967" s="29"/>
+      <c r="L967" s="31"/>
+      <c r="M967" s="29"/>
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A968" s="124" t="s">
+      <c r="A968" s="29" t="s">
         <v>2613</v>
       </c>
-      <c r="B968" s="128" t="s">
+      <c r="B968" s="100" t="s">
         <v>2619</v>
       </c>
-      <c r="C968" s="133"/>
-      <c r="D968" s="123" t="s">
+      <c r="C968" s="123"/>
+      <c r="D968" s="85" t="s">
         <v>2605</v>
       </c>
-      <c r="E968" s="136" t="s">
+      <c r="E968" s="125" t="s">
         <v>2612</v>
       </c>
-      <c r="F968" s="130"/>
-      <c r="G968" s="130"/>
-      <c r="H968" s="129"/>
-      <c r="I968" s="125"/>
+      <c r="F968" s="31"/>
+      <c r="G968" s="31"/>
+      <c r="H968" s="29"/>
+      <c r="I968" s="120"/>
       <c r="J968" s="35" t="s">
         <v>2609</v>
       </c>
-      <c r="K968" s="124"/>
-      <c r="L968" s="130"/>
-      <c r="M968" s="124"/>
+      <c r="K968" s="29"/>
+      <c r="L968" s="31"/>
+      <c r="M968" s="29"/>
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A969" s="120" t="s">
+      <c r="A969" t="s">
         <v>2566</v>
       </c>
       <c r="B969" s="15" t="s">
         <v>1463</v>
       </c>
-      <c r="C969" s="121"/>
       <c r="D969" s="15" t="s">
         <v>2567</v>
       </c>
-      <c r="E969" s="120"/>
-      <c r="F969" s="120" t="s">
+      <c r="F969" t="s">
         <v>1771</v>
       </c>
-      <c r="G969" s="120" t="s">
+      <c r="G969" t="s">
         <v>2568</v>
       </c>
-      <c r="H969" s="120" t="s">
+      <c r="H969" t="s">
         <v>1359</v>
       </c>
-      <c r="I969" s="120" t="s">
+      <c r="I969" t="s">
         <v>71</v>
       </c>
-      <c r="J969" s="120" t="s">
+      <c r="J969" t="s">
         <v>2569</v>
       </c>
-      <c r="K969" s="124"/>
-      <c r="L969" s="130"/>
-      <c r="M969" s="124"/>
+      <c r="K969" s="29"/>
+      <c r="L969" s="31"/>
+      <c r="M969" s="29"/>
     </row>
     <row r="970" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A970" s="124"/>
-      <c r="B970" s="128"/>
-      <c r="C970" s="134"/>
-      <c r="D970" s="135"/>
-      <c r="E970" s="122"/>
-      <c r="F970" s="130"/>
-      <c r="G970" s="130"/>
-      <c r="H970" s="129"/>
-      <c r="I970" s="125"/>
-      <c r="J970" s="124"/>
-      <c r="K970" s="124"/>
-      <c r="L970" s="130"/>
-      <c r="M970" s="124"/>
+      <c r="A970" s="29" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B970" s="100" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C970" s="124" t="s">
+        <v>2639</v>
+      </c>
+      <c r="D970" s="85" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E970" s="83" t="s">
+        <v>2638</v>
+      </c>
+      <c r="F970" s="31" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G970" s="31" t="s">
+        <v>2640</v>
+      </c>
+      <c r="H970" s="29">
+        <v>0</v>
+      </c>
+      <c r="I970" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="J970" s="29" t="s">
+        <v>2641</v>
+      </c>
+      <c r="K970" s="29"/>
+      <c r="L970" s="31"/>
+      <c r="M970" s="29"/>
     </row>
     <row r="971" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A971" s="29"/>
-      <c r="B971" s="113"/>
-      <c r="C971" s="82"/>
-      <c r="D971" s="79"/>
-      <c r="E971" s="82"/>
-      <c r="F971" s="126"/>
-      <c r="G971" s="126"/>
-      <c r="H971" s="127"/>
-      <c r="I971" s="19"/>
-      <c r="J971" s="29"/>
+      <c r="A971" s="29" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B971" s="113" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C971" s="82" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D971" s="79" t="s">
+        <v>2643</v>
+      </c>
+      <c r="E971" s="82" t="s">
+        <v>230</v>
+      </c>
+      <c r="F971" s="31" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G971" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H971" s="23" t="s">
+        <v>2647</v>
+      </c>
+      <c r="I971" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J971" s="29" t="s">
+        <v>2645</v>
+      </c>
       <c r="K971" s="29"/>
-      <c r="L971" s="126"/>
+      <c r="L971" s="31" t="s">
+        <v>2648</v>
+      </c>
       <c r="M971" s="29"/>
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29"/>
-      <c r="B972" s="128"/>
-      <c r="C972" s="122"/>
-      <c r="D972" s="123"/>
-      <c r="E972" s="122"/>
-      <c r="F972" s="126"/>
-      <c r="G972" s="126"/>
-      <c r="H972" s="129"/>
-      <c r="I972" s="125"/>
+      <c r="B972" s="100"/>
+      <c r="C972" s="83"/>
+      <c r="D972" s="85"/>
+      <c r="E972" s="83"/>
+      <c r="F972" s="31"/>
+      <c r="G972" s="31"/>
+      <c r="H972" s="29"/>
+      <c r="I972" s="120"/>
       <c r="J972" s="29"/>
       <c r="K972" s="29"/>
-      <c r="L972" s="126"/>
+      <c r="L972" s="31"/>
       <c r="M972" s="29"/>
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.2">

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9FBFF-0FF0-E846-B08C-BF5B18C3C68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE78FC76-205D-5445-9966-DBDC6D43ED15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3740" yWindow="1740" windowWidth="26500" windowHeight="14260" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
+    <workbookView xWindow="3740" yWindow="1720" windowWidth="26500" windowHeight="14260" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
   <sheets>
     <sheet name="Cables" sheetId="1" r:id="rId1"/>
@@ -46327,7 +46327,7 @@
         <v>1135</v>
       </c>
       <c r="C891" s="83" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D891" s="83" t="s">
         <v>1135</v>
@@ -46348,7 +46348,7 @@
         <v>71</v>
       </c>
       <c r="J891" s="29" t="s">
-        <v>34</v>
+        <v>2645</v>
       </c>
       <c r="K891" s="29"/>
       <c r="L891" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9941B9BD-A116-654C-BB2A-3CC9D2B9EBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B16922D-7949-6D42-B1CF-5887D51B5285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="2320" windowWidth="29320" windowHeight="16220" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
+    <workbookView xWindow="7120" yWindow="2320" windowWidth="23120" windowHeight="16220" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
   <sheets>
     <sheet name="Cables" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7956" uniqueCount="2663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7983" uniqueCount="2665">
   <si>
     <t>Tag</t>
   </si>
@@ -5707,9 +5707,6 @@
     <t>2m?</t>
   </si>
   <si>
-    <t>switch</t>
-  </si>
-  <si>
     <t>short jumper</t>
   </si>
   <si>
@@ -8030,6 +8027,15 @@
   </si>
   <si>
     <t>temp974</t>
+  </si>
+  <si>
+    <t>jump974</t>
+  </si>
+  <si>
+    <t>jump975</t>
+  </si>
+  <si>
+    <t>jump976</t>
   </si>
 </sst>
 </file>
@@ -8445,7 +8451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8676,6 +8682,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9155,7 +9162,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Terry Doner" refreshedDate="46030.710642245373" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="442" xr:uid="{966EC718-ADB8-7746-9366-54097C9D57FA}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M973" sheet="Cables"/>
+    <worksheetSource ref="A1:M978" sheet="Cables"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Tag" numFmtId="0">
@@ -17529,70 +17536,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -17848,9 +17792,72 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M974" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M973" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M979" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+  <autoFilter ref="A1:M978" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
@@ -18167,7 +18174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B91ADC-4569-1C4E-B002-1ED2E647C959}">
-  <dimension ref="A1:W974"/>
+  <dimension ref="A1:W979"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -19067,7 +19074,7 @@
         <v>66</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="F30" s="23" t="s">
         <v>67</v>
@@ -19082,7 +19089,7 @@
         <v>29</v>
       </c>
       <c r="J30" s="23" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -19102,7 +19109,7 @@
         <v>66</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>67</v>
@@ -19117,7 +19124,7 @@
         <v>29</v>
       </c>
       <c r="J31" s="23" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="K31" s="19"/>
       <c r="L31" s="19"/>
@@ -19137,7 +19144,7 @@
         <v>66</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>67</v>
@@ -19322,10 +19329,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="105" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E38" s="106" t="s">
         <v>2207</v>
-      </c>
-      <c r="E38" s="106" t="s">
-        <v>2208</v>
       </c>
       <c r="F38" s="89" t="s">
         <v>1765</v>
@@ -19595,7 +19602,7 @@
         <v>71</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
@@ -19647,7 +19654,7 @@
         <v>38</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>104</v>
@@ -19665,7 +19672,7 @@
         <v>71</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
@@ -20026,7 +20033,7 @@
         <v>38</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="I62" s="19" t="s">
         <v>110</v>
@@ -20241,7 +20248,7 @@
         <v>154</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>162</v>
@@ -20280,7 +20287,7 @@
         <v>169</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="E70" s="23" t="s">
         <v>208</v>
@@ -20349,7 +20356,7 @@
         <v>42</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="F72" s="23" t="s">
         <v>38</v>
@@ -20364,10 +20371,10 @@
         <v>110</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="L72" s="23"/>
       <c r="M72" s="24"/>
@@ -20383,7 +20390,7 @@
         <v>158</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="E73" s="23" t="s">
         <v>136</v>
@@ -20399,7 +20406,7 @@
         <v>110</v>
       </c>
       <c r="J73" s="23" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K73" s="23"/>
       <c r="L73" s="19"/>
@@ -20416,7 +20423,7 @@
         <v>159</v>
       </c>
       <c r="D74" s="22" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E74" s="23" t="s">
         <v>136</v>
@@ -20432,7 +20439,7 @@
         <v>110</v>
       </c>
       <c r="J74" s="23" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K74" s="23"/>
       <c r="L74" s="23"/>
@@ -20449,7 +20456,7 @@
         <v>160</v>
       </c>
       <c r="D75" s="22" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E75" s="23" t="s">
         <v>136</v>
@@ -20465,7 +20472,7 @@
         <v>110</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K75" s="23"/>
       <c r="L75" s="19"/>
@@ -20473,7 +20480,7 @@
     </row>
     <row r="76" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B76" s="22" t="s">
         <v>42</v>
@@ -20500,7 +20507,7 @@
         <v>71</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K76" s="23"/>
       <c r="L76" s="22"/>
@@ -20508,7 +20515,7 @@
     </row>
     <row r="77" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="B77" s="22" t="s">
         <v>42</v>
@@ -20535,7 +20542,7 @@
         <v>71</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K77" s="23"/>
       <c r="L77" s="22"/>
@@ -20543,7 +20550,7 @@
     </row>
     <row r="78" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="B78" s="22" t="s">
         <v>42</v>
@@ -20570,7 +20577,7 @@
         <v>71</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K78" s="23"/>
       <c r="L78" s="22"/>
@@ -20578,19 +20585,19 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C79" s="23">
         <v>39</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="F79" s="22" t="s">
         <v>247</v>
@@ -20603,7 +20610,7 @@
         <v>71</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K79" s="23"/>
       <c r="L79" s="22"/>
@@ -20611,19 +20618,19 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C80" s="23">
         <v>41</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="F80" s="22" t="s">
         <v>247</v>
@@ -20636,7 +20643,7 @@
         <v>71</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K80" s="23"/>
       <c r="L80" s="22"/>
@@ -20644,19 +20651,19 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C81" s="23">
         <v>43</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="F81" s="22" t="s">
         <v>247</v>
@@ -20669,7 +20676,7 @@
         <v>71</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K81" s="23"/>
       <c r="L81" s="22"/>
@@ -21066,7 +21073,7 @@
         <v>110</v>
       </c>
       <c r="J94" s="23" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="K94" s="23"/>
       <c r="L94" s="23"/>
@@ -21224,13 +21231,13 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>1881</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="D101" s="22" t="s">
         <v>64</v>
@@ -21257,7 +21264,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B102" s="22" t="s">
         <v>225</v>
@@ -21290,7 +21297,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B103" s="22" t="s">
         <v>224</v>
@@ -21804,13 +21811,13 @@
         <v>316</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>162</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="E120" s="23" t="s">
         <v>344</v>
@@ -21828,7 +21835,7 @@
         <v>110</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="K120" s="23"/>
       <c r="L120" s="23"/>
@@ -22106,13 +22113,13 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="B131" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C131" s="23" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="D131" s="22" t="s">
         <v>42</v>
@@ -22133,7 +22140,7 @@
         <v>71</v>
       </c>
       <c r="J131" s="23" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23"/>
@@ -22141,7 +22148,7 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="21" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="B132" s="22" t="s">
         <v>42</v>
@@ -22168,7 +22175,7 @@
         <v>71</v>
       </c>
       <c r="J132" s="23" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="K132" s="23"/>
       <c r="L132" s="19"/>
@@ -22748,7 +22755,7 @@
         <v>66</v>
       </c>
       <c r="E149" s="29" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F149" s="23" t="s">
         <v>1764</v>
@@ -22781,7 +22788,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="29" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="F150" s="23" t="s">
         <v>1764</v>
@@ -22814,7 +22821,7 @@
         <v>66</v>
       </c>
       <c r="E151" s="29" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="F151" s="23" t="s">
         <v>1764</v>
@@ -22847,7 +22854,7 @@
         <v>66</v>
       </c>
       <c r="E152" s="29" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F152" s="23" t="s">
         <v>1764</v>
@@ -22874,13 +22881,13 @@
         <v>1249</v>
       </c>
       <c r="C153" s="78" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="D153" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="F153" s="23" t="s">
         <v>1764</v>
@@ -22895,7 +22902,7 @@
         <v>29</v>
       </c>
       <c r="J153" s="29" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="K153" s="29"/>
       <c r="L153" s="29"/>
@@ -22909,13 +22916,13 @@
         <v>1249</v>
       </c>
       <c r="C154" s="78" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="D154" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="F154" s="23" t="s">
         <v>1764</v>
@@ -22930,7 +22937,7 @@
         <v>29</v>
       </c>
       <c r="J154" s="29" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="K154" s="29"/>
       <c r="L154" s="29"/>
@@ -22944,13 +22951,13 @@
         <v>1249</v>
       </c>
       <c r="C155" s="78" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="D155" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F155" s="23" t="s">
         <v>1764</v>
@@ -22965,7 +22972,7 @@
         <v>29</v>
       </c>
       <c r="J155" s="29" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="K155" s="29"/>
       <c r="L155" s="29"/>
@@ -22979,13 +22986,13 @@
         <v>1249</v>
       </c>
       <c r="C156" s="78" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="D156" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="F156" s="23" t="s">
         <v>1764</v>
@@ -23000,7 +23007,7 @@
         <v>29</v>
       </c>
       <c r="J156" s="29" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="K156" s="29"/>
       <c r="L156" s="29"/>
@@ -23014,13 +23021,13 @@
         <v>1249</v>
       </c>
       <c r="C157" s="78" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="D157" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="F157" s="23" t="s">
         <v>1764</v>
@@ -23035,7 +23042,7 @@
         <v>29</v>
       </c>
       <c r="J157" s="29" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="K157" s="29"/>
       <c r="L157" s="29"/>
@@ -23049,13 +23056,13 @@
         <v>1249</v>
       </c>
       <c r="C158" s="78" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="D158" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E158" s="29" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="F158" s="23" t="s">
         <v>1764</v>
@@ -23070,7 +23077,7 @@
         <v>29</v>
       </c>
       <c r="J158" s="29" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="K158" s="29"/>
       <c r="L158" s="29"/>
@@ -23084,13 +23091,13 @@
         <v>1249</v>
       </c>
       <c r="C159" s="78" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="D159" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E159" s="29" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F159" s="23" t="s">
         <v>1764</v>
@@ -23105,7 +23112,7 @@
         <v>29</v>
       </c>
       <c r="J159" s="29" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="K159" s="29"/>
       <c r="L159" s="29"/>
@@ -23119,13 +23126,13 @@
         <v>1249</v>
       </c>
       <c r="C160" s="78" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="D160" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E160" s="29" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="F160" s="23" t="s">
         <v>1764</v>
@@ -23140,7 +23147,7 @@
         <v>29</v>
       </c>
       <c r="J160" s="29" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="K160" s="29"/>
       <c r="L160" s="29"/>
@@ -23154,13 +23161,13 @@
         <v>1249</v>
       </c>
       <c r="C161" s="78" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="D161" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E161" s="29" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="F161" s="23" t="s">
         <v>1764</v>
@@ -23175,7 +23182,7 @@
         <v>29</v>
       </c>
       <c r="J161" s="29" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="K161" s="29"/>
       <c r="L161" s="29"/>
@@ -23189,13 +23196,13 @@
         <v>1249</v>
       </c>
       <c r="C162" s="78" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="D162" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E162" s="29" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F162" s="23" t="s">
         <v>1764</v>
@@ -23224,13 +23231,13 @@
         <v>1249</v>
       </c>
       <c r="C163" s="78" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="D163" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F163" s="23" t="s">
         <v>1764</v>
@@ -23245,7 +23252,7 @@
         <v>29</v>
       </c>
       <c r="J163" s="29" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="K163" s="29"/>
       <c r="L163" s="29"/>
@@ -23259,13 +23266,13 @@
         <v>1249</v>
       </c>
       <c r="C164" s="78" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="D164" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E164" s="29" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>1764</v>
@@ -23280,7 +23287,7 @@
         <v>29</v>
       </c>
       <c r="J164" s="29" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="K164" s="29"/>
       <c r="L164" s="29"/>
@@ -23294,13 +23301,13 @@
         <v>1249</v>
       </c>
       <c r="C165" s="78" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="D165" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E165" s="29" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="F165" s="23" t="s">
         <v>1764</v>
@@ -23315,7 +23322,7 @@
         <v>29</v>
       </c>
       <c r="J165" s="29" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="K165" s="29"/>
       <c r="L165" s="29"/>
@@ -23329,13 +23336,13 @@
         <v>1249</v>
       </c>
       <c r="C166" s="78" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E166" s="29" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F166" s="23" t="s">
         <v>1764</v>
@@ -23364,13 +23371,13 @@
         <v>1249</v>
       </c>
       <c r="C167" s="78" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="D167" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="F167" s="23" t="s">
         <v>1764</v>
@@ -23399,13 +23406,13 @@
         <v>1249</v>
       </c>
       <c r="C168" s="78" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="D168" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="F168" s="23" t="s">
         <v>1764</v>
@@ -23434,13 +23441,13 @@
         <v>1249</v>
       </c>
       <c r="C169" s="78" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="F169" s="23" t="s">
         <v>1764</v>
@@ -23469,13 +23476,13 @@
         <v>1249</v>
       </c>
       <c r="C170" s="78" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="D170" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E170" s="29" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F170" s="23" t="s">
         <v>1764</v>
@@ -23504,13 +23511,13 @@
         <v>1249</v>
       </c>
       <c r="C171" s="78" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="D171" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E171" s="29" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>1764</v>
@@ -23539,13 +23546,13 @@
         <v>1249</v>
       </c>
       <c r="C172" s="78" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="D172" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E172" s="29" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="F172" s="23" t="s">
         <v>1764</v>
@@ -23574,13 +23581,13 @@
         <v>1249</v>
       </c>
       <c r="C173" s="78" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="D173" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E173" s="29" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F173" s="23" t="s">
         <v>1764</v>
@@ -23609,13 +23616,13 @@
         <v>1249</v>
       </c>
       <c r="C174" s="78" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="D174" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E174" s="29" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="F174" s="23" t="s">
         <v>1764</v>
@@ -23644,13 +23651,13 @@
         <v>1249</v>
       </c>
       <c r="C175" s="78" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="D175" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E175" s="29" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F175" s="23" t="s">
         <v>1764</v>
@@ -23679,13 +23686,13 @@
         <v>1249</v>
       </c>
       <c r="C176" s="78" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="D176" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E176" s="29" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="F176" s="23" t="s">
         <v>1764</v>
@@ -23714,13 +23721,13 @@
         <v>1249</v>
       </c>
       <c r="C177" s="78" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="D177" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E177" s="29" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F177" s="23" t="s">
         <v>1764</v>
@@ -23749,13 +23756,13 @@
         <v>1249</v>
       </c>
       <c r="C178" s="78" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="D178" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="F178" s="23" t="s">
         <v>1764</v>
@@ -23784,13 +23791,13 @@
         <v>1249</v>
       </c>
       <c r="C179" s="78" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E179" s="29" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="F179" s="23" t="s">
         <v>1764</v>
@@ -23819,13 +23826,13 @@
         <v>1249</v>
       </c>
       <c r="C180" s="78" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="D180" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F180" s="23" t="s">
         <v>1764</v>
@@ -23854,13 +23861,13 @@
         <v>1249</v>
       </c>
       <c r="C181" s="78" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="D181" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E181" s="29" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="F181" s="23" t="s">
         <v>1764</v>
@@ -23875,7 +23882,7 @@
         <v>29</v>
       </c>
       <c r="J181" s="29" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="K181" s="29"/>
       <c r="L181" s="29"/>
@@ -23889,13 +23896,13 @@
         <v>1249</v>
       </c>
       <c r="C182" s="78" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="D182" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E182" s="29" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="F182" s="23" t="s">
         <v>1764</v>
@@ -23910,7 +23917,7 @@
         <v>29</v>
       </c>
       <c r="J182" s="29" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="K182" s="29"/>
       <c r="L182" s="29"/>
@@ -23924,13 +23931,13 @@
         <v>1249</v>
       </c>
       <c r="C183" s="78" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="D183" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="F183" s="23" t="s">
         <v>1764</v>
@@ -23945,7 +23952,7 @@
         <v>29</v>
       </c>
       <c r="J183" s="29" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="K183" s="29"/>
       <c r="L183" s="29"/>
@@ -23959,13 +23966,13 @@
         <v>1249</v>
       </c>
       <c r="C184" s="78" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="D184" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="F184" s="23" t="s">
         <v>1764</v>
@@ -23994,13 +24001,13 @@
         <v>1249</v>
       </c>
       <c r="C185" s="78" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="D185" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E185" s="29" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="F185" s="23" t="s">
         <v>1764</v>
@@ -24029,13 +24036,13 @@
         <v>1249</v>
       </c>
       <c r="C186" s="78" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="D186" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="F186" s="23" t="s">
         <v>1764</v>
@@ -24050,7 +24057,7 @@
         <v>29</v>
       </c>
       <c r="J186" s="29" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="K186" s="29"/>
       <c r="L186" s="29"/>
@@ -24064,13 +24071,13 @@
         <v>1249</v>
       </c>
       <c r="C187" s="78" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F187" s="23" t="s">
         <v>1764</v>
@@ -24085,7 +24092,7 @@
         <v>29</v>
       </c>
       <c r="J187" s="29" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="K187" s="29"/>
       <c r="L187" s="29"/>
@@ -24099,13 +24106,13 @@
         <v>1249</v>
       </c>
       <c r="C188" s="78" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="F188" s="23" t="s">
         <v>1764</v>
@@ -24120,7 +24127,7 @@
         <v>29</v>
       </c>
       <c r="J188" s="29" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="K188" s="29"/>
       <c r="L188" s="29"/>
@@ -24134,13 +24141,13 @@
         <v>1249</v>
       </c>
       <c r="C189" s="78" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="F189" s="23" t="s">
         <v>1764</v>
@@ -24155,7 +24162,7 @@
         <v>29</v>
       </c>
       <c r="J189" s="29" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="K189" s="29"/>
       <c r="L189" s="29"/>
@@ -24169,13 +24176,13 @@
         <v>1249</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="D190" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F190" s="23" t="s">
         <v>1764</v>
@@ -24190,7 +24197,7 @@
         <v>29</v>
       </c>
       <c r="J190" s="29" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="K190" s="29"/>
       <c r="L190" s="29"/>
@@ -24204,13 +24211,13 @@
         <v>1249</v>
       </c>
       <c r="C191" s="78" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="D191" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="F191" s="23" t="s">
         <v>1764</v>
@@ -24225,7 +24232,7 @@
         <v>29</v>
       </c>
       <c r="J191" s="29" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="K191" s="29"/>
       <c r="L191" s="29"/>
@@ -24239,13 +24246,13 @@
         <v>1249</v>
       </c>
       <c r="C192" s="78" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D192" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F192" s="23" t="s">
         <v>1764</v>
@@ -24272,13 +24279,13 @@
         <v>1249</v>
       </c>
       <c r="C193" s="78" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="D193" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="F193" s="23" t="s">
         <v>1764</v>
@@ -24305,13 +24312,13 @@
         <v>1249</v>
       </c>
       <c r="C194" s="78" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="F194" s="23" t="s">
         <v>1764</v>
@@ -24338,13 +24345,13 @@
         <v>1249</v>
       </c>
       <c r="C195" s="78" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="D195" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="F195" s="23" t="s">
         <v>1764</v>
@@ -24371,13 +24378,13 @@
         <v>1249</v>
       </c>
       <c r="C196" s="78" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D196" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="F196" s="23" t="s">
         <v>1764</v>
@@ -24392,7 +24399,7 @@
         <v>29</v>
       </c>
       <c r="J196" s="29" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="K196" s="29"/>
       <c r="L196" s="29"/>
@@ -24406,13 +24413,13 @@
         <v>1249</v>
       </c>
       <c r="C197" s="78" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D197" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="F197" s="23" t="s">
         <v>1764</v>
@@ -24427,7 +24434,7 @@
         <v>29</v>
       </c>
       <c r="J197" s="29" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="K197" s="29"/>
       <c r="L197" s="29"/>
@@ -24441,13 +24448,13 @@
         <v>1249</v>
       </c>
       <c r="C198" s="78" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="D198" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="F198" s="23" t="s">
         <v>1764</v>
@@ -24474,13 +24481,13 @@
         <v>1249</v>
       </c>
       <c r="C199" s="78" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D199" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E199" s="29" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="F199" s="23" t="s">
         <v>1764</v>
@@ -24507,13 +24514,13 @@
         <v>1249</v>
       </c>
       <c r="C200" s="78" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="D200" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="F200" s="23" t="s">
         <v>1764</v>
@@ -24540,13 +24547,13 @@
         <v>1249</v>
       </c>
       <c r="C201" s="78" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D201" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E201" s="29" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="F201" s="23" t="s">
         <v>1764</v>
@@ -24573,13 +24580,13 @@
         <v>1249</v>
       </c>
       <c r="C202" s="78" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D202" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E202" s="29" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="F202" s="23" t="s">
         <v>1764</v>
@@ -24594,7 +24601,7 @@
         <v>29</v>
       </c>
       <c r="J202" s="29" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="K202" s="29"/>
       <c r="L202" s="31"/>
@@ -24608,13 +24615,13 @@
         <v>1249</v>
       </c>
       <c r="C203" s="78" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="D203" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E203" s="29" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="F203" s="23" t="s">
         <v>1764</v>
@@ -24629,7 +24636,7 @@
         <v>29</v>
       </c>
       <c r="J203" s="29" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="K203" s="29"/>
       <c r="L203" s="31"/>
@@ -24643,13 +24650,13 @@
         <v>1249</v>
       </c>
       <c r="C204" s="78" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E204" s="29" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F204" s="23" t="s">
         <v>1764</v>
@@ -24664,7 +24671,7 @@
         <v>29</v>
       </c>
       <c r="J204" s="29" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="K204" s="29"/>
       <c r="L204" s="31"/>
@@ -24678,13 +24685,13 @@
         <v>1249</v>
       </c>
       <c r="C205" s="78" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D205" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E205" s="29" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="F205" s="23" t="s">
         <v>1764</v>
@@ -24711,13 +24718,13 @@
         <v>1249</v>
       </c>
       <c r="C206" s="78" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D206" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="F206" s="23" t="s">
         <v>1764</v>
@@ -24744,13 +24751,13 @@
         <v>1249</v>
       </c>
       <c r="C207" s="78" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="D207" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E207" s="29" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="F207" s="23" t="s">
         <v>1764</v>
@@ -24777,13 +24784,13 @@
         <v>1249</v>
       </c>
       <c r="C208" s="78" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="D208" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E208" s="29" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F208" s="23" t="s">
         <v>1764</v>
@@ -24810,13 +24817,13 @@
         <v>1249</v>
       </c>
       <c r="C209" s="78" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="D209" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E209" s="29" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="F209" s="23" t="s">
         <v>1764</v>
@@ -24843,13 +24850,13 @@
         <v>1249</v>
       </c>
       <c r="C210" s="78" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="D210" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E210" s="29" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F210" s="23" t="s">
         <v>1764</v>
@@ -24876,13 +24883,13 @@
         <v>1249</v>
       </c>
       <c r="C211" s="78" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="D211" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E211" s="29" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="F211" s="23" t="s">
         <v>1764</v>
@@ -24909,13 +24916,13 @@
         <v>1249</v>
       </c>
       <c r="C212" s="78" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="D212" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E212" s="29" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="F212" s="23" t="s">
         <v>1764</v>
@@ -24942,13 +24949,13 @@
         <v>1249</v>
       </c>
       <c r="C213" s="78" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="D213" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E213" s="29" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="F213" s="23" t="s">
         <v>1764</v>
@@ -24975,13 +24982,13 @@
         <v>1249</v>
       </c>
       <c r="C214" s="78" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E214" s="29" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>1764</v>
@@ -25008,13 +25015,13 @@
         <v>1249</v>
       </c>
       <c r="C215" s="78" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E215" s="29" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>1764</v>
@@ -25041,13 +25048,13 @@
         <v>1249</v>
       </c>
       <c r="C216" s="78" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="D216" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E216" s="29" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="F216" s="23" t="s">
         <v>1764</v>
@@ -25326,16 +25333,16 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>1134</v>
       </c>
       <c r="C225" s="36" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="D225" s="31" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="E225" s="36" t="s">
         <v>230</v>
@@ -25353,7 +25360,7 @@
         <v>110</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="K225" s="31"/>
       <c r="L225" s="31" t="s">
@@ -27016,7 +27023,7 @@
         <v>110</v>
       </c>
       <c r="J282" s="54" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="K282" s="29"/>
       <c r="L282" s="31"/>
@@ -29958,7 +29965,7 @@
         <v>981</v>
       </c>
       <c r="C379" s="29" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D379" s="31" t="s">
         <v>993</v>
@@ -29991,7 +29998,7 @@
         <v>981</v>
       </c>
       <c r="C380" s="29" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D380" s="52" t="s">
         <v>994</v>
@@ -30024,7 +30031,7 @@
         <v>981</v>
       </c>
       <c r="C381" s="29" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D381" s="29" t="s">
         <v>140</v>
@@ -30057,7 +30064,7 @@
         <v>981</v>
       </c>
       <c r="C382" s="29" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D382" s="29" t="s">
         <v>853</v>
@@ -30088,7 +30095,7 @@
         <v>981</v>
       </c>
       <c r="C383" s="29" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D383" s="29" t="s">
         <v>874</v>
@@ -30125,7 +30132,7 @@
         <v>981</v>
       </c>
       <c r="E384" s="35" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="F384" s="31" t="s">
         <v>247</v>
@@ -30150,13 +30157,13 @@
         <v>981</v>
       </c>
       <c r="C385" s="29" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="D385" s="29" t="s">
         <v>981</v>
       </c>
       <c r="E385" s="29" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="F385" s="31"/>
       <c r="G385" s="31"/>
@@ -30183,7 +30190,7 @@
         <v>981</v>
       </c>
       <c r="E386" s="29" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F386" s="31"/>
       <c r="G386" s="31"/>
@@ -30210,7 +30217,7 @@
         <v>981</v>
       </c>
       <c r="E387" s="29" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="F387" s="31"/>
       <c r="G387" s="31"/>
@@ -30237,7 +30244,7 @@
         <v>981</v>
       </c>
       <c r="E388" s="29" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F388" s="31"/>
       <c r="G388" s="31"/>
@@ -30264,7 +30271,7 @@
         <v>981</v>
       </c>
       <c r="E389" s="29" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F389" s="31"/>
       <c r="G389" s="31"/>
@@ -31053,7 +31060,7 @@
         <v>32</v>
       </c>
       <c r="D419" s="31" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E419" s="29" t="s">
         <v>32</v>
@@ -31084,7 +31091,7 @@
         <v>5</v>
       </c>
       <c r="D420" s="31" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E420" s="29" t="s">
         <v>190</v>
@@ -31203,13 +31210,13 @@
         <v>64</v>
       </c>
       <c r="C424" s="29" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="D424" s="31" t="s">
         <v>1037</v>
       </c>
       <c r="E424" s="29" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F424" s="31" t="s">
         <v>32</v>
@@ -31234,13 +31241,13 @@
         <v>769</v>
       </c>
       <c r="C425" s="29" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="D425" s="31" t="s">
         <v>1038</v>
       </c>
       <c r="E425" s="29" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F425" s="31" t="s">
         <v>32</v>
@@ -31545,7 +31552,7 @@
         <v>1043</v>
       </c>
       <c r="E434" s="29" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="F434" s="31" t="s">
         <v>510</v>
@@ -31580,7 +31587,7 @@
         <v>1043</v>
       </c>
       <c r="E435" s="29" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="F435" s="31" t="s">
         <v>510</v>
@@ -31615,7 +31622,7 @@
         <v>1043</v>
       </c>
       <c r="E436" s="29" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="F436" s="31" t="s">
         <v>510</v>
@@ -32088,7 +32095,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="B451" s="80"/>
       <c r="C451" s="73"/>
@@ -32099,7 +32106,7 @@
       </c>
       <c r="G451" s="31"/>
       <c r="H451" s="23" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="I451" s="19" t="s">
         <v>110</v>
@@ -32659,7 +32666,7 @@
       <c r="H467" s="29"/>
       <c r="I467" s="29"/>
       <c r="J467" s="54" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="K467" s="33"/>
       <c r="L467" s="31"/>
@@ -32735,7 +32742,7 @@
         <v>27</v>
       </c>
       <c r="C470" s="53" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="D470" s="58"/>
       <c r="E470" s="53"/>
@@ -32748,7 +32755,7 @@
       <c r="H470" s="29"/>
       <c r="I470" s="29"/>
       <c r="J470" s="54" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="K470" s="35"/>
       <c r="L470" s="31"/>
@@ -32783,10 +32790,10 @@
         <v>29</v>
       </c>
       <c r="J471" s="54" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="K471" s="33" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="L471" s="31"/>
       <c r="M471" s="29"/>
@@ -33178,7 +33185,7 @@
     </row>
     <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="29" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B483" s="22" t="s">
         <v>77</v>
@@ -33209,13 +33216,13 @@
     </row>
     <row r="484" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A484" s="29" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B484" s="29" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C484" s="53" t="s">
         <v>2654</v>
-      </c>
-      <c r="B484" s="29" t="s">
-        <v>2653</v>
-      </c>
-      <c r="C484" s="53" t="s">
-        <v>2655</v>
       </c>
       <c r="D484" s="58" t="s">
         <v>1134</v>
@@ -33244,16 +33251,16 @@
     </row>
     <row r="485" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A485" s="29" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="B485" s="29" t="s">
         <v>1134</v>
       </c>
       <c r="C485" s="73" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D485" s="84" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="E485" s="73" t="s">
         <v>230</v>
@@ -33271,7 +33278,7 @@
         <v>110</v>
       </c>
       <c r="J485" s="29" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="K485" s="33"/>
       <c r="L485" s="31"/>
@@ -33279,13 +33286,13 @@
     </row>
     <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="29" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B486" s="29" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C486" s="53" t="s">
         <v>2205</v>
-      </c>
-      <c r="B486" s="29" t="s">
-        <v>2207</v>
-      </c>
-      <c r="C486" s="53" t="s">
-        <v>2206</v>
       </c>
       <c r="D486" s="58" t="s">
         <v>1134</v>
@@ -33704,7 +33711,7 @@
         <v>110</v>
       </c>
       <c r="J498" s="54" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="K498" s="33"/>
       <c r="L498" s="31"/>
@@ -33741,7 +33748,7 @@
         <v>110</v>
       </c>
       <c r="J499" s="29" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="K499" s="33"/>
       <c r="L499" s="31"/>
@@ -33982,7 +33989,7 @@
         <v>110</v>
       </c>
       <c r="J506" s="29" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="K506" s="29"/>
       <c r="L506" s="31" t="s">
@@ -33995,13 +34002,13 @@
         <v>1105</v>
       </c>
       <c r="B507" s="31" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="C507" s="29" t="s">
         <v>162</v>
       </c>
       <c r="D507" s="31" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="E507" s="29" t="s">
         <v>208</v>
@@ -34166,7 +34173,7 @@
         <v>162</v>
       </c>
       <c r="D512" s="29" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="E512" s="29" t="s">
         <v>138</v>
@@ -34184,7 +34191,7 @@
         <v>110</v>
       </c>
       <c r="J512" s="29" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K512" s="29"/>
       <c r="L512" s="31"/>
@@ -34201,7 +34208,7 @@
         <v>162</v>
       </c>
       <c r="D513" s="29" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E513" s="29" t="s">
         <v>138</v>
@@ -34219,7 +34226,7 @@
         <v>110</v>
       </c>
       <c r="J513" s="29" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K513" s="29"/>
       <c r="L513" s="31"/>
@@ -34236,7 +34243,7 @@
         <v>162</v>
       </c>
       <c r="D514" s="29" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E514" s="29" t="s">
         <v>138</v>
@@ -34254,7 +34261,7 @@
         <v>110</v>
       </c>
       <c r="J514" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K514" s="29"/>
       <c r="L514" s="31"/>
@@ -34289,7 +34296,7 @@
         <v>110</v>
       </c>
       <c r="J515" s="29" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K515" s="29"/>
       <c r="L515" s="31"/>
@@ -34324,7 +34331,7 @@
         <v>110</v>
       </c>
       <c r="J516" s="29" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K516" s="29"/>
       <c r="L516" s="31"/>
@@ -34359,7 +34366,7 @@
         <v>110</v>
       </c>
       <c r="J517" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K517" s="29"/>
       <c r="L517" s="31"/>
@@ -34449,7 +34456,7 @@
         <v>1043</v>
       </c>
       <c r="E520" s="29" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="F520" s="31" t="s">
         <v>1764</v>
@@ -34486,7 +34493,7 @@
         <v>1043</v>
       </c>
       <c r="E521" s="29" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="F521" s="31" t="s">
         <v>1764</v>
@@ -34523,7 +34530,7 @@
         <v>1043</v>
       </c>
       <c r="E522" s="29" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="F522" s="31" t="s">
         <v>1764</v>
@@ -34560,7 +34567,7 @@
         <v>1043</v>
       </c>
       <c r="E523" s="29" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="F523" s="31" t="s">
         <v>1764</v>
@@ -34597,7 +34604,7 @@
         <v>1043</v>
       </c>
       <c r="E524" s="29" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F524" s="31" t="s">
         <v>1764</v>
@@ -34634,7 +34641,7 @@
         <v>1043</v>
       </c>
       <c r="E525" s="29" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="F525" s="31" t="s">
         <v>1764</v>
@@ -34671,7 +34678,7 @@
         <v>1043</v>
       </c>
       <c r="E526" s="29" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="F526" s="31" t="s">
         <v>1764</v>
@@ -34708,7 +34715,7 @@
         <v>1043</v>
       </c>
       <c r="E527" s="29" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="F527" s="31" t="s">
         <v>1764</v>
@@ -34745,7 +34752,7 @@
         <v>1043</v>
       </c>
       <c r="E528" s="29" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="F528" s="31" t="s">
         <v>1764</v>
@@ -34782,7 +34789,7 @@
         <v>1043</v>
       </c>
       <c r="E529" s="29" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="F529" s="89" t="s">
         <v>1764</v>
@@ -34819,7 +34826,7 @@
         <v>1043</v>
       </c>
       <c r="E530" s="29" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="F530" s="89" t="s">
         <v>1764</v>
@@ -34856,7 +34863,7 @@
         <v>1043</v>
       </c>
       <c r="E531" s="29" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="F531" s="89" t="s">
         <v>1764</v>
@@ -34893,7 +34900,7 @@
         <v>1043</v>
       </c>
       <c r="E532" s="29" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="F532" s="89" t="s">
         <v>1764</v>
@@ -35025,7 +35032,7 @@
         <v>1765</v>
       </c>
       <c r="G536" s="23" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="H536" s="31" t="s">
         <v>209</v>
@@ -35134,7 +35141,7 @@
         <v>1255</v>
       </c>
       <c r="B540" s="59" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C540" s="36" t="s">
         <v>1256</v>
@@ -35453,7 +35460,7 @@
         <v>1375</v>
       </c>
       <c r="B551" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C551" s="73" t="s">
         <v>1723</v>
@@ -35482,7 +35489,7 @@
         <v>1376</v>
       </c>
       <c r="B552" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C552" s="73" t="s">
         <v>1724</v>
@@ -35511,7 +35518,7 @@
         <v>1377</v>
       </c>
       <c r="B553" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C553" s="73" t="s">
         <v>1725</v>
@@ -35540,7 +35547,7 @@
         <v>1378</v>
       </c>
       <c r="B554" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C554" s="73" t="s">
         <v>1726</v>
@@ -35569,7 +35576,7 @@
         <v>1379</v>
       </c>
       <c r="B555" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C555" s="73" t="s">
         <v>1727</v>
@@ -35598,7 +35605,7 @@
         <v>1380</v>
       </c>
       <c r="B556" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C556" s="73" t="s">
         <v>1728</v>
@@ -35627,7 +35634,7 @@
         <v>1381</v>
       </c>
       <c r="B557" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C557" s="73" t="s">
         <v>1729</v>
@@ -35656,7 +35663,7 @@
         <v>1382</v>
       </c>
       <c r="B558" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C558" s="73" t="s">
         <v>1730</v>
@@ -35685,7 +35692,7 @@
         <v>1383</v>
       </c>
       <c r="B559" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C559" s="73" t="s">
         <v>1731</v>
@@ -35714,7 +35721,7 @@
         <v>1384</v>
       </c>
       <c r="B560" s="73" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="C560" s="73" t="s">
         <v>1732</v>
@@ -35746,7 +35753,7 @@
         <v>1712</v>
       </c>
       <c r="C561" s="73" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="D561" s="73" t="s">
         <v>1257</v>
@@ -35772,7 +35779,7 @@
         <v>1735</v>
       </c>
       <c r="B562" s="95" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C562" s="73" t="s">
         <v>1253</v>
@@ -35804,13 +35811,13 @@
         <v>1865</v>
       </c>
       <c r="C563" s="73" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D563" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E563" s="73" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="F563" s="31" t="s">
         <v>247</v>
@@ -35837,13 +35844,13 @@
         <v>1865</v>
       </c>
       <c r="C564" s="73" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D564" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E564" s="73" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F564" s="31" t="s">
         <v>247</v>
@@ -35870,13 +35877,13 @@
         <v>1865</v>
       </c>
       <c r="C565" s="73" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D565" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E565" s="73" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="F565" s="31" t="s">
         <v>247</v>
@@ -35903,13 +35910,13 @@
         <v>1865</v>
       </c>
       <c r="C566" s="73" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D566" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E566" s="73" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="F566" s="31" t="s">
         <v>247</v>
@@ -35936,13 +35943,13 @@
         <v>1865</v>
       </c>
       <c r="C567" s="73" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D567" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E567" s="73" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="F567" s="31" t="s">
         <v>247</v>
@@ -35969,13 +35976,13 @@
         <v>1865</v>
       </c>
       <c r="C568" s="73" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="D568" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E568" s="73" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="F568" s="31" t="s">
         <v>247</v>
@@ -36002,13 +36009,13 @@
         <v>1865</v>
       </c>
       <c r="C569" s="73" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="D569" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E569" s="73" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F569" s="31" t="s">
         <v>247</v>
@@ -36035,13 +36042,13 @@
         <v>1865</v>
       </c>
       <c r="C570" s="73" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="D570" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E570" s="73" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F570" s="31" t="s">
         <v>247</v>
@@ -36068,13 +36075,13 @@
         <v>1866</v>
       </c>
       <c r="C571" s="73" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D571" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E571" s="73" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="F571" s="31" t="s">
         <v>247</v>
@@ -36101,13 +36108,13 @@
         <v>1866</v>
       </c>
       <c r="C572" s="73" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="D572" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E572" s="73" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="F572" s="31" t="s">
         <v>247</v>
@@ -36134,13 +36141,13 @@
         <v>1866</v>
       </c>
       <c r="C573" s="73" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="D573" s="73" t="s">
         <v>1860</v>
       </c>
       <c r="E573" s="73" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="F573" s="31" t="s">
         <v>247</v>
@@ -37088,7 +37095,7 @@
         <v>1043</v>
       </c>
       <c r="E603" s="81" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="F603" s="31" t="s">
         <v>1405</v>
@@ -37119,7 +37126,7 @@
         <v>1043</v>
       </c>
       <c r="E604" s="81" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="F604" s="31" t="s">
         <v>1405</v>
@@ -37212,7 +37219,7 @@
         <v>1043</v>
       </c>
       <c r="E607" s="81" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="F607" s="31" t="s">
         <v>1405</v>
@@ -37243,7 +37250,7 @@
         <v>1043</v>
       </c>
       <c r="E608" s="81" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="F608" s="31" t="s">
         <v>1405</v>
@@ -37274,7 +37281,7 @@
         <v>1043</v>
       </c>
       <c r="E609" s="81" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="F609" s="31" t="s">
         <v>1405</v>
@@ -37305,7 +37312,7 @@
         <v>1043</v>
       </c>
       <c r="E610" s="81" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="F610" s="31" t="s">
         <v>1405</v>
@@ -37336,7 +37343,7 @@
         <v>1043</v>
       </c>
       <c r="E611" s="81" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="F611" s="31" t="s">
         <v>1405</v>
@@ -37367,7 +37374,7 @@
         <v>1043</v>
       </c>
       <c r="E612" s="81" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="F612" s="31" t="s">
         <v>1405</v>
@@ -37398,7 +37405,7 @@
         <v>1043</v>
       </c>
       <c r="E613" s="81" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="F613" s="31" t="s">
         <v>1405</v>
@@ -37431,7 +37438,7 @@
         <v>1043</v>
       </c>
       <c r="E614" s="81" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="F614" s="31" t="s">
         <v>1405</v>
@@ -37464,7 +37471,7 @@
         <v>1043</v>
       </c>
       <c r="E615" s="82" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="F615" s="31" t="s">
         <v>1405</v>
@@ -37495,7 +37502,7 @@
         <v>1043</v>
       </c>
       <c r="E616" s="82" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="F616" s="31" t="s">
         <v>1405</v>
@@ -37526,7 +37533,7 @@
         <v>1043</v>
       </c>
       <c r="E617" s="82" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="F617" s="31" t="s">
         <v>1405</v>
@@ -37557,7 +37564,7 @@
         <v>1043</v>
       </c>
       <c r="E618" s="82" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="F618" s="31" t="s">
         <v>1405</v>
@@ -37590,7 +37597,7 @@
         <v>1043</v>
       </c>
       <c r="E619" s="82" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="F619" s="31" t="s">
         <v>1405</v>
@@ -37623,7 +37630,7 @@
         <v>1043</v>
       </c>
       <c r="E620" s="82" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="F620" s="31" t="s">
         <v>1405</v>
@@ -37654,7 +37661,7 @@
         <v>1043</v>
       </c>
       <c r="E621" s="82" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="F621" s="31" t="s">
         <v>1405</v>
@@ -37685,7 +37692,7 @@
         <v>1043</v>
       </c>
       <c r="E622" s="82" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="F622" s="31" t="s">
         <v>1405</v>
@@ -37830,7 +37837,7 @@
         <v>1249</v>
       </c>
       <c r="C627" s="83" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D627" s="85" t="s">
         <v>1460</v>
@@ -37865,7 +37872,7 @@
         <v>1249</v>
       </c>
       <c r="C628" s="83" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="D628" s="85" t="s">
         <v>1460</v>
@@ -37900,7 +37907,7 @@
         <v>1249</v>
       </c>
       <c r="C629" s="83" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D629" s="85" t="s">
         <v>1460</v>
@@ -37935,7 +37942,7 @@
         <v>1249</v>
       </c>
       <c r="C630" s="83" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="D630" s="85" t="s">
         <v>1460</v>
@@ -37970,7 +37977,7 @@
         <v>1249</v>
       </c>
       <c r="C631" s="83" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D631" s="85" t="s">
         <v>1460</v>
@@ -38081,7 +38088,7 @@
         <v>1497</v>
       </c>
       <c r="E634" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F634" s="23" t="s">
         <v>1764</v>
@@ -38116,7 +38123,7 @@
         <v>1497</v>
       </c>
       <c r="E635" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F635" s="23" t="s">
         <v>1764</v>
@@ -38151,7 +38158,7 @@
         <v>1497</v>
       </c>
       <c r="E636" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F636" s="23" t="s">
         <v>1764</v>
@@ -38186,7 +38193,7 @@
         <v>1496</v>
       </c>
       <c r="E637" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F637" s="23" t="s">
         <v>1764</v>
@@ -38221,7 +38228,7 @@
         <v>1496</v>
       </c>
       <c r="E638" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F638" s="23" t="s">
         <v>1764</v>
@@ -38256,7 +38263,7 @@
         <v>1496</v>
       </c>
       <c r="E639" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F639" s="23" t="s">
         <v>1764</v>
@@ -38291,7 +38298,7 @@
         <v>1498</v>
       </c>
       <c r="E640" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F640" s="23" t="s">
         <v>1764</v>
@@ -38326,7 +38333,7 @@
         <v>1498</v>
       </c>
       <c r="E641" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F641" s="23" t="s">
         <v>1764</v>
@@ -38361,7 +38368,7 @@
         <v>1498</v>
       </c>
       <c r="E642" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F642" s="23" t="s">
         <v>1764</v>
@@ -38396,7 +38403,7 @@
         <v>1499</v>
       </c>
       <c r="E643" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F643" s="23" t="s">
         <v>1764</v>
@@ -38431,7 +38438,7 @@
         <v>1499</v>
       </c>
       <c r="E644" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F644" s="23" t="s">
         <v>1764</v>
@@ -38466,7 +38473,7 @@
         <v>1499</v>
       </c>
       <c r="E645" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F645" s="23" t="s">
         <v>1764</v>
@@ -38501,7 +38508,7 @@
         <v>1500</v>
       </c>
       <c r="E646" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F646" s="23" t="s">
         <v>1764</v>
@@ -38536,7 +38543,7 @@
         <v>1500</v>
       </c>
       <c r="E647" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F647" s="23" t="s">
         <v>1764</v>
@@ -38571,7 +38578,7 @@
         <v>1500</v>
       </c>
       <c r="E648" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F648" s="23" t="s">
         <v>1764</v>
@@ -38606,7 +38613,7 @@
         <v>1501</v>
       </c>
       <c r="E649" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F649" s="23" t="s">
         <v>1764</v>
@@ -38641,7 +38648,7 @@
         <v>1501</v>
       </c>
       <c r="E650" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F650" s="23" t="s">
         <v>1764</v>
@@ -38676,7 +38683,7 @@
         <v>1501</v>
       </c>
       <c r="E651" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F651" s="23" t="s">
         <v>1764</v>
@@ -38711,7 +38718,7 @@
         <v>1502</v>
       </c>
       <c r="E652" s="84" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F652" s="23" t="s">
         <v>1764</v>
@@ -38746,7 +38753,7 @@
         <v>1502</v>
       </c>
       <c r="E653" s="84" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F653" s="23" t="s">
         <v>1764</v>
@@ -38781,7 +38788,7 @@
         <v>1502</v>
       </c>
       <c r="E654" s="84" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F654" s="23" t="s">
         <v>1764</v>
@@ -38937,7 +38944,7 @@
     </row>
     <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="29" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="B660" s="83" t="s">
         <v>66</v>
@@ -38972,7 +38979,7 @@
     </row>
     <row r="661" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="29" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B661" s="83" t="s">
         <v>66</v>
@@ -39007,7 +39014,7 @@
     </row>
     <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="29" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="B662" s="85" t="s">
         <v>246</v>
@@ -39038,7 +39045,7 @@
     </row>
     <row r="663" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A663" s="29" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="B663" s="85" t="s">
         <v>246</v>
@@ -39069,19 +39076,19 @@
     </row>
     <row r="664" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A664" s="29" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="B664" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C664" s="73" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="D664" s="79" t="s">
         <v>1771</v>
       </c>
       <c r="E664" s="73" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="F664" s="23" t="s">
         <v>1764</v>
@@ -39100,19 +39107,19 @@
     </row>
     <row r="665" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A665" s="29" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B665" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C665" s="73" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="D665" s="79" t="s">
         <v>1771</v>
       </c>
       <c r="E665" s="73" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="F665" s="23" t="s">
         <v>1764</v>
@@ -39131,19 +39138,19 @@
     </row>
     <row r="666" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A666" s="29" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="B666" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C666" s="82" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="D666" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E666" s="82" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="F666" s="23" t="s">
         <v>1764</v>
@@ -39162,19 +39169,19 @@
     </row>
     <row r="667" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A667" s="29" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="B667" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C667" s="83" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="D667" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E667" s="83" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="F667" s="23" t="s">
         <v>1764</v>
@@ -39193,19 +39200,19 @@
     </row>
     <row r="668" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A668" s="29" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="B668" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C668" s="83" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="D668" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E668" s="83" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="F668" s="23" t="s">
         <v>1764</v>
@@ -39224,19 +39231,19 @@
     </row>
     <row r="669" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A669" s="29" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="B669" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C669" s="83" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="D669" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E669" s="83" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="F669" s="23" t="s">
         <v>1764</v>
@@ -39255,19 +39262,19 @@
     </row>
     <row r="670" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A670" s="29" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="B670" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C670" s="83" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="D670" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E670" s="83" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="F670" s="23" t="s">
         <v>1764</v>
@@ -39286,19 +39293,19 @@
     </row>
     <row r="671" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A671" s="29" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="B671" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C671" s="83" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="D671" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E671" s="83" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="F671" s="23" t="s">
         <v>1764</v>
@@ -39317,19 +39324,19 @@
     </row>
     <row r="672" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A672" s="29" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="B672" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C672" s="83" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="D672" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E672" s="83" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="F672" s="23" t="s">
         <v>1764</v>
@@ -39348,19 +39355,19 @@
     </row>
     <row r="673" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A673" s="29" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="B673" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C673" s="98" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="D673" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E673" s="98" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="F673" s="23" t="s">
         <v>1764</v>
@@ -39379,19 +39386,19 @@
     </row>
     <row r="674" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A674" s="29" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="B674" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C674" s="82" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="D674" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E674" s="82" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="F674" s="23" t="s">
         <v>1764</v>
@@ -39410,19 +39417,19 @@
     </row>
     <row r="675" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A675" s="29" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B675" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C675" s="83" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="D675" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E675" s="83" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="F675" s="23" t="s">
         <v>1764</v>
@@ -39441,19 +39448,19 @@
     </row>
     <row r="676" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A676" s="29" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="B676" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C676" s="83" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="D676" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E676" s="83" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="F676" s="23" t="s">
         <v>1764</v>
@@ -39472,19 +39479,19 @@
     </row>
     <row r="677" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A677" s="29" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="B677" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C677" s="98" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="D677" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E677" s="98" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="F677" s="23" t="s">
         <v>1764</v>
@@ -39503,19 +39510,19 @@
     </row>
     <row r="678" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A678" s="29" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="B678" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C678" s="82" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="D678" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E678" s="82" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="F678" s="23" t="s">
         <v>1764</v>
@@ -39534,19 +39541,19 @@
     </row>
     <row r="679" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A679" s="29" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="B679" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C679" s="98" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="D679" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E679" s="98" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="F679" s="23" t="s">
         <v>1764</v>
@@ -39565,19 +39572,19 @@
     </row>
     <row r="680" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A680" s="29" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B680" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C680" s="73" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="D680" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E680" s="73" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="F680" s="23" t="s">
         <v>1764</v>
@@ -39596,19 +39603,19 @@
     </row>
     <row r="681" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A681" s="29" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="B681" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C681" s="73" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="D681" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E681" s="73" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="F681" s="23" t="s">
         <v>1764</v>
@@ -39627,19 +39634,19 @@
     </row>
     <row r="682" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A682" s="29" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="B682" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C682" s="73" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="D682" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E682" s="73" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="F682" s="23" t="s">
         <v>1764</v>
@@ -39658,19 +39665,19 @@
     </row>
     <row r="683" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A683" s="29" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B683" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C683" s="73" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="D683" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E683" s="73" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="F683" s="23" t="s">
         <v>1764</v>
@@ -39689,19 +39696,19 @@
     </row>
     <row r="684" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A684" s="29" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="B684" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C684" s="82" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="D684" s="79" t="s">
         <v>1521</v>
       </c>
       <c r="E684" s="82" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="F684" s="23" t="s">
         <v>1764</v>
@@ -39724,19 +39731,19 @@
     </row>
     <row r="685" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A685" s="29" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="B685" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C685" s="82" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="D685" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E685" s="83" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="F685" s="23" t="s">
         <v>1764</v>
@@ -39759,19 +39766,19 @@
     </row>
     <row r="686" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A686" s="29" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="B686" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C686" s="82" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D686" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E686" s="83" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="F686" s="23" t="s">
         <v>1764</v>
@@ -39794,19 +39801,19 @@
     </row>
     <row r="687" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A687" s="29" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="B687" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C687" s="82" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="D687" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E687" s="83" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="F687" s="23" t="s">
         <v>1764</v>
@@ -39829,19 +39836,19 @@
     </row>
     <row r="688" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A688" s="29" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="B688" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C688" s="82" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="D688" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E688" s="83" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="F688" s="23" t="s">
         <v>1764</v>
@@ -39864,19 +39871,19 @@
     </row>
     <row r="689" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A689" s="29" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B689" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C689" s="82" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="D689" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E689" s="83" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="F689" s="23" t="s">
         <v>1764</v>
@@ -39899,19 +39906,19 @@
     </row>
     <row r="690" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A690" s="29" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="B690" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C690" s="82" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="D690" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E690" s="83" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="F690" s="23" t="s">
         <v>1764</v>
@@ -39934,19 +39941,19 @@
     </row>
     <row r="691" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A691" s="29" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B691" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C691" s="82" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="D691" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E691" s="83" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="F691" s="23" t="s">
         <v>1764</v>
@@ -39969,19 +39976,19 @@
     </row>
     <row r="692" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A692" s="29" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="B692" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C692" s="73" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="D692" s="84" t="s">
         <v>1767</v>
       </c>
       <c r="E692" s="73" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="F692" s="22" t="s">
         <v>1764</v>
@@ -40004,13 +40011,13 @@
     </row>
     <row r="693" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A693" s="29" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B693" s="80" t="s">
         <v>1249</v>
       </c>
       <c r="C693" s="73" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="D693" s="84" t="s">
         <v>1747</v>
@@ -40735,7 +40742,7 @@
     </row>
     <row r="718" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A718" s="29" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="B718" s="82" t="s">
         <v>769</v>
@@ -40747,7 +40754,7 @@
         <v>1249</v>
       </c>
       <c r="E718" s="81" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F718" s="23" t="s">
         <v>1764</v>
@@ -40768,7 +40775,7 @@
     </row>
     <row r="719" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B719" s="82" t="s">
         <v>769</v>
@@ -40780,7 +40787,7 @@
         <v>1249</v>
       </c>
       <c r="E719" s="86" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F719" s="23" t="s">
         <v>1764</v>
@@ -40801,7 +40808,7 @@
     </row>
     <row r="720" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A720" s="29" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="B720" s="82" t="s">
         <v>769</v>
@@ -40813,7 +40820,7 @@
         <v>1249</v>
       </c>
       <c r="E720" s="86" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F720" s="23" t="s">
         <v>1764</v>
@@ -40834,7 +40841,7 @@
     </row>
     <row r="721" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="B721" s="82" t="s">
         <v>769</v>
@@ -40846,7 +40853,7 @@
         <v>1249</v>
       </c>
       <c r="E721" s="86" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F721" s="23" t="s">
         <v>1764</v>
@@ -40867,7 +40874,7 @@
     </row>
     <row r="722" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A722" s="29" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B722" s="82" t="s">
         <v>769</v>
@@ -40879,7 +40886,7 @@
         <v>1249</v>
       </c>
       <c r="E722" s="86" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F722" s="23" t="s">
         <v>1764</v>
@@ -40900,7 +40907,7 @@
     </row>
     <row r="723" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A723" s="29" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="B723" s="82" t="s">
         <v>769</v>
@@ -40912,7 +40919,7 @@
         <v>1249</v>
       </c>
       <c r="E723" s="86" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F723" s="23" t="s">
         <v>1764</v>
@@ -40933,7 +40940,7 @@
     </row>
     <row r="724" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A724" s="29" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="B724" s="82" t="s">
         <v>769</v>
@@ -40945,7 +40952,7 @@
         <v>1249</v>
       </c>
       <c r="E724" s="86" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="F724" s="23" t="s">
         <v>1764</v>
@@ -40966,7 +40973,7 @@
     </row>
     <row r="725" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A725" s="29" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B725" s="82" t="s">
         <v>769</v>
@@ -40978,7 +40985,7 @@
         <v>1249</v>
       </c>
       <c r="E725" s="86" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F725" s="23" t="s">
         <v>1764</v>
@@ -40999,7 +41006,7 @@
     </row>
     <row r="726" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A726" s="29" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="B726" s="82" t="s">
         <v>769</v>
@@ -41011,7 +41018,7 @@
         <v>1249</v>
       </c>
       <c r="E726" s="86" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F726" s="23" t="s">
         <v>1764</v>
@@ -41032,7 +41039,7 @@
     </row>
     <row r="727" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A727" s="29" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="B727" s="82" t="s">
         <v>769</v>
@@ -41044,7 +41051,7 @@
         <v>1249</v>
       </c>
       <c r="E727" s="86" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="F727" s="23" t="s">
         <v>1764</v>
@@ -41065,7 +41072,7 @@
     </row>
     <row r="728" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A728" s="29" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="B728" s="82" t="s">
         <v>769</v>
@@ -41077,7 +41084,7 @@
         <v>1249</v>
       </c>
       <c r="E728" s="86" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F728" s="23" t="s">
         <v>1764</v>
@@ -41098,7 +41105,7 @@
     </row>
     <row r="729" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A729" s="29" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="B729" s="82" t="s">
         <v>769</v>
@@ -41110,7 +41117,7 @@
         <v>1249</v>
       </c>
       <c r="E729" s="86" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="F729" s="23" t="s">
         <v>1764</v>
@@ -41131,7 +41138,7 @@
     </row>
     <row r="730" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A730" s="29" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="B730" s="82" t="s">
         <v>769</v>
@@ -41143,7 +41150,7 @@
         <v>1249</v>
       </c>
       <c r="E730" s="86" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F730" s="23" t="s">
         <v>1764</v>
@@ -41164,7 +41171,7 @@
     </row>
     <row r="731" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A731" s="29" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="B731" s="82" t="s">
         <v>769</v>
@@ -41176,7 +41183,7 @@
         <v>1249</v>
       </c>
       <c r="E731" s="86" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="F731" s="23" t="s">
         <v>1764</v>
@@ -41197,7 +41204,7 @@
     </row>
     <row r="732" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A732" s="29" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="B732" s="82" t="s">
         <v>769</v>
@@ -41209,7 +41216,7 @@
         <v>1249</v>
       </c>
       <c r="E732" s="86" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="F732" s="23" t="s">
         <v>1764</v>
@@ -41230,7 +41237,7 @@
     </row>
     <row r="733" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A733" s="29" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="B733" s="82" t="s">
         <v>769</v>
@@ -41242,7 +41249,7 @@
         <v>1249</v>
       </c>
       <c r="E733" s="86" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F733" s="23" t="s">
         <v>1764</v>
@@ -41263,7 +41270,7 @@
     </row>
     <row r="734" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A734" s="29" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="B734" s="82" t="s">
         <v>769</v>
@@ -41275,7 +41282,7 @@
         <v>1249</v>
       </c>
       <c r="E734" s="86" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="F734" s="23" t="s">
         <v>1764</v>
@@ -41296,7 +41303,7 @@
     </row>
     <row r="735" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A735" s="29" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="B735" s="82" t="s">
         <v>769</v>
@@ -41308,7 +41315,7 @@
         <v>1249</v>
       </c>
       <c r="E735" s="86" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="F735" s="23" t="s">
         <v>1764</v>
@@ -41329,7 +41336,7 @@
     </row>
     <row r="736" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A736" s="29" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B736" s="82" t="s">
         <v>769</v>
@@ -41341,7 +41348,7 @@
         <v>1249</v>
       </c>
       <c r="E736" s="86" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="F736" s="23" t="s">
         <v>1764</v>
@@ -41362,7 +41369,7 @@
     </row>
     <row r="737" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A737" s="29" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B737" s="82" t="s">
         <v>769</v>
@@ -41374,7 +41381,7 @@
         <v>1249</v>
       </c>
       <c r="E737" s="86" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="F737" s="23" t="s">
         <v>1764</v>
@@ -41395,7 +41402,7 @@
     </row>
     <row r="738" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A738" s="29" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="B738" s="82" t="s">
         <v>769</v>
@@ -41407,7 +41414,7 @@
         <v>1249</v>
       </c>
       <c r="E738" s="86" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="F738" s="23" t="s">
         <v>1764</v>
@@ -41428,7 +41435,7 @@
     </row>
     <row r="739" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A739" s="29" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="B739" s="82" t="s">
         <v>769</v>
@@ -41440,7 +41447,7 @@
         <v>1249</v>
       </c>
       <c r="E739" s="86" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="F739" s="23" t="s">
         <v>1764</v>
@@ -41461,7 +41468,7 @@
     </row>
     <row r="740" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A740" s="29" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="B740" s="82" t="s">
         <v>769</v>
@@ -41473,7 +41480,7 @@
         <v>1249</v>
       </c>
       <c r="E740" s="86" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="F740" s="23" t="s">
         <v>1764</v>
@@ -41494,7 +41501,7 @@
     </row>
     <row r="741" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A741" s="29" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="B741" s="82" t="s">
         <v>769</v>
@@ -41506,7 +41513,7 @@
         <v>1249</v>
       </c>
       <c r="E741" s="86" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="F741" s="23" t="s">
         <v>1764</v>
@@ -41527,7 +41534,7 @@
     </row>
     <row r="742" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A742" s="29" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="B742" s="82" t="s">
         <v>769</v>
@@ -41539,7 +41546,7 @@
         <v>1249</v>
       </c>
       <c r="E742" s="86" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="F742" s="23" t="s">
         <v>1764</v>
@@ -41560,7 +41567,7 @@
     </row>
     <row r="743" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A743" s="29" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="B743" s="82" t="s">
         <v>769</v>
@@ -41572,7 +41579,7 @@
         <v>1249</v>
       </c>
       <c r="E743" s="86" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="F743" s="23" t="s">
         <v>1764</v>
@@ -41593,7 +41600,7 @@
     </row>
     <row r="744" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A744" s="29" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B744" s="82" t="s">
         <v>769</v>
@@ -41605,7 +41612,7 @@
         <v>1249</v>
       </c>
       <c r="E744" s="86" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="F744" s="23" t="s">
         <v>1764</v>
@@ -41626,7 +41633,7 @@
     </row>
     <row r="745" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A745" s="29" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B745" s="82" t="s">
         <v>769</v>
@@ -41638,7 +41645,7 @@
         <v>1249</v>
       </c>
       <c r="E745" s="86" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="F745" s="23" t="s">
         <v>1764</v>
@@ -41659,7 +41666,7 @@
     </row>
     <row r="746" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A746" s="29" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="B746" s="82" t="s">
         <v>769</v>
@@ -41671,7 +41678,7 @@
         <v>1249</v>
       </c>
       <c r="E746" s="86" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F746" s="23" t="s">
         <v>1764</v>
@@ -41692,7 +41699,7 @@
     </row>
     <row r="747" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A747" s="29" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="B747" s="82" t="s">
         <v>769</v>
@@ -41704,7 +41711,7 @@
         <v>1249</v>
       </c>
       <c r="E747" s="86" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F747" s="23" t="s">
         <v>1764</v>
@@ -41725,7 +41732,7 @@
     </row>
     <row r="748" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A748" s="29" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B748" s="82" t="s">
         <v>769</v>
@@ -41737,7 +41744,7 @@
         <v>1249</v>
       </c>
       <c r="E748" s="86" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F748" s="23" t="s">
         <v>1764</v>
@@ -41758,7 +41765,7 @@
     </row>
     <row r="749" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A749" s="29" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B749" s="82" t="s">
         <v>769</v>
@@ -41770,7 +41777,7 @@
         <v>1249</v>
       </c>
       <c r="E749" s="86" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F749" s="23" t="s">
         <v>1764</v>
@@ -41791,7 +41798,7 @@
     </row>
     <row r="750" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A750" s="29" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="B750" s="82" t="s">
         <v>769</v>
@@ -41803,7 +41810,7 @@
         <v>1249</v>
       </c>
       <c r="E750" s="86" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F750" s="23" t="s">
         <v>1764</v>
@@ -41824,7 +41831,7 @@
     </row>
     <row r="751" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A751" s="29" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="B751" s="82" t="s">
         <v>769</v>
@@ -41836,7 +41843,7 @@
         <v>1249</v>
       </c>
       <c r="E751" s="86" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F751" s="23" t="s">
         <v>1764</v>
@@ -41857,7 +41864,7 @@
     </row>
     <row r="752" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A752" s="29" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="B752" s="82" t="s">
         <v>769</v>
@@ -41869,7 +41876,7 @@
         <v>1249</v>
       </c>
       <c r="E752" s="86" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="F752" s="23" t="s">
         <v>1764</v>
@@ -41890,7 +41897,7 @@
     </row>
     <row r="753" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A753" s="29" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B753" s="82" t="s">
         <v>769</v>
@@ -41902,7 +41909,7 @@
         <v>1249</v>
       </c>
       <c r="E753" s="86" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F753" s="23" t="s">
         <v>1764</v>
@@ -41923,7 +41930,7 @@
     </row>
     <row r="754" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A754" s="29" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="B754" s="82" t="s">
         <v>769</v>
@@ -41935,7 +41942,7 @@
         <v>1249</v>
       </c>
       <c r="E754" s="86" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F754" s="23" t="s">
         <v>1764</v>
@@ -41956,7 +41963,7 @@
     </row>
     <row r="755" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A755" s="29" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B755" s="82" t="s">
         <v>769</v>
@@ -41968,7 +41975,7 @@
         <v>1249</v>
       </c>
       <c r="E755" s="83" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="F755" s="23" t="s">
         <v>1764</v>
@@ -41989,7 +41996,7 @@
     </row>
     <row r="756" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A756" s="29" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B756" s="82" t="s">
         <v>769</v>
@@ -42001,7 +42008,7 @@
         <v>1249</v>
       </c>
       <c r="E756" s="83" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="F756" s="23" t="s">
         <v>1764</v>
@@ -42022,7 +42029,7 @@
     </row>
     <row r="757" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A757" s="29" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B757" s="82" t="s">
         <v>769</v>
@@ -42034,7 +42041,7 @@
         <v>1249</v>
       </c>
       <c r="E757" s="83" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="F757" s="23" t="s">
         <v>1764</v>
@@ -42055,7 +42062,7 @@
     </row>
     <row r="758" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A758" s="29" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B758" s="82" t="s">
         <v>769</v>
@@ -42067,7 +42074,7 @@
         <v>1249</v>
       </c>
       <c r="E758" s="83" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F758" s="23" t="s">
         <v>1764</v>
@@ -42088,7 +42095,7 @@
     </row>
     <row r="759" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A759" s="29" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="B759" s="82" t="s">
         <v>769</v>
@@ -42100,7 +42107,7 @@
         <v>1249</v>
       </c>
       <c r="E759" s="83" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="F759" s="23" t="s">
         <v>1764</v>
@@ -42121,7 +42128,7 @@
     </row>
     <row r="760" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A760" s="29" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B760" s="82" t="s">
         <v>769</v>
@@ -42133,7 +42140,7 @@
         <v>1249</v>
       </c>
       <c r="E760" s="83" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F760" s="23" t="s">
         <v>1764</v>
@@ -42154,7 +42161,7 @@
     </row>
     <row r="761" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A761" s="29" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="B761" s="82" t="s">
         <v>769</v>
@@ -42166,7 +42173,7 @@
         <v>1249</v>
       </c>
       <c r="E761" s="83" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F761" s="23" t="s">
         <v>1764</v>
@@ -42187,7 +42194,7 @@
     </row>
     <row r="762" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A762" s="29" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B762" s="82" t="s">
         <v>769</v>
@@ -42199,7 +42206,7 @@
         <v>1249</v>
       </c>
       <c r="E762" s="83" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F762" s="23" t="s">
         <v>1764</v>
@@ -42220,7 +42227,7 @@
     </row>
     <row r="763" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A763" s="29" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B763" s="82" t="s">
         <v>769</v>
@@ -42232,7 +42239,7 @@
         <v>1249</v>
       </c>
       <c r="E763" s="83" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F763" s="23" t="s">
         <v>1764</v>
@@ -42253,7 +42260,7 @@
     </row>
     <row r="764" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A764" s="29" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B764" s="82" t="s">
         <v>769</v>
@@ -42265,7 +42272,7 @@
         <v>1249</v>
       </c>
       <c r="E764" s="83" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F764" s="23" t="s">
         <v>1764</v>
@@ -42286,7 +42293,7 @@
     </row>
     <row r="765" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A765" s="29" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="B765" s="82" t="s">
         <v>769</v>
@@ -42298,7 +42305,7 @@
         <v>1249</v>
       </c>
       <c r="E765" s="83" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F765" s="23" t="s">
         <v>1764</v>
@@ -42319,7 +42326,7 @@
     </row>
     <row r="766" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A766" s="29" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="B766" s="82" t="s">
         <v>769</v>
@@ -42331,7 +42338,7 @@
         <v>1249</v>
       </c>
       <c r="E766" s="83" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F766" s="23" t="s">
         <v>1764</v>
@@ -42352,7 +42359,7 @@
     </row>
     <row r="767" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A767" s="29" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B767" s="82" t="s">
         <v>769</v>
@@ -42364,7 +42371,7 @@
         <v>1249</v>
       </c>
       <c r="E767" s="83" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F767" s="23" t="s">
         <v>1764</v>
@@ -42385,7 +42392,7 @@
     </row>
     <row r="768" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A768" s="29" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="B768" s="82" t="s">
         <v>769</v>
@@ -42397,7 +42404,7 @@
         <v>1249</v>
       </c>
       <c r="E768" s="83" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F768" s="23" t="s">
         <v>1764</v>
@@ -42418,7 +42425,7 @@
     </row>
     <row r="769" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A769" s="29" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="B769" s="82" t="s">
         <v>769</v>
@@ -42430,7 +42437,7 @@
         <v>1249</v>
       </c>
       <c r="E769" s="83" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F769" s="23" t="s">
         <v>1764</v>
@@ -42451,7 +42458,7 @@
     </row>
     <row r="770" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A770" s="29" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="B770" s="82" t="s">
         <v>769</v>
@@ -42463,7 +42470,7 @@
         <v>1249</v>
       </c>
       <c r="E770" s="83" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F770" s="23" t="s">
         <v>1764</v>
@@ -42484,7 +42491,7 @@
     </row>
     <row r="771" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A771" s="29" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="B771" s="82" t="s">
         <v>769</v>
@@ -42496,7 +42503,7 @@
         <v>1249</v>
       </c>
       <c r="E771" s="83" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F771" s="23" t="s">
         <v>1764</v>
@@ -42517,7 +42524,7 @@
     </row>
     <row r="772" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A772" s="29" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="B772" s="82" t="s">
         <v>769</v>
@@ -42529,7 +42536,7 @@
         <v>1249</v>
       </c>
       <c r="E772" s="83" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F772" s="23" t="s">
         <v>1764</v>
@@ -42550,7 +42557,7 @@
     </row>
     <row r="773" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A773" s="29" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="B773" s="82" t="s">
         <v>769</v>
@@ -42562,7 +42569,7 @@
         <v>1249</v>
       </c>
       <c r="E773" s="83" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F773" s="23" t="s">
         <v>1764</v>
@@ -42583,7 +42590,7 @@
     </row>
     <row r="774" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A774" s="29" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="B774" s="82" t="s">
         <v>769</v>
@@ -42595,7 +42602,7 @@
         <v>1249</v>
       </c>
       <c r="E774" s="83" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F774" s="23" t="s">
         <v>1764</v>
@@ -42616,7 +42623,7 @@
     </row>
     <row r="775" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A775" s="29" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B775" s="82" t="s">
         <v>769</v>
@@ -42628,7 +42635,7 @@
         <v>1249</v>
       </c>
       <c r="E775" s="83" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="F775" s="23" t="s">
         <v>1764</v>
@@ -42649,7 +42656,7 @@
     </row>
     <row r="776" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A776" s="29" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="B776" s="82" t="s">
         <v>769</v>
@@ -42661,7 +42668,7 @@
         <v>1249</v>
       </c>
       <c r="E776" s="83" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="F776" s="23" t="s">
         <v>1764</v>
@@ -42682,7 +42689,7 @@
     </row>
     <row r="777" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A777" s="29" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="B777" s="82" t="s">
         <v>769</v>
@@ -42694,7 +42701,7 @@
         <v>1249</v>
       </c>
       <c r="E777" s="83" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="F777" s="23" t="s">
         <v>1764</v>
@@ -42715,7 +42722,7 @@
     </row>
     <row r="778" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A778" s="29" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="B778" s="82" t="s">
         <v>769</v>
@@ -42727,7 +42734,7 @@
         <v>1249</v>
       </c>
       <c r="E778" s="83" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="F778" s="23" t="s">
         <v>1764</v>
@@ -42748,7 +42755,7 @@
     </row>
     <row r="779" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A779" s="29" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="B779" s="82" t="s">
         <v>769</v>
@@ -42760,7 +42767,7 @@
         <v>1249</v>
       </c>
       <c r="E779" s="83" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="F779" s="23" t="s">
         <v>1764</v>
@@ -42781,7 +42788,7 @@
     </row>
     <row r="780" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A780" s="29" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B780" s="82" t="s">
         <v>769</v>
@@ -42793,7 +42800,7 @@
         <v>1249</v>
       </c>
       <c r="E780" s="83" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="F780" s="23" t="s">
         <v>1764</v>
@@ -42814,7 +42821,7 @@
     </row>
     <row r="781" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A781" s="29" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B781" s="82" t="s">
         <v>769</v>
@@ -42826,7 +42833,7 @@
         <v>1249</v>
       </c>
       <c r="E781" s="83" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="F781" s="23" t="s">
         <v>1764</v>
@@ -42847,7 +42854,7 @@
     </row>
     <row r="782" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A782" s="29" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="B782" s="82" t="s">
         <v>769</v>
@@ -42859,7 +42866,7 @@
         <v>1249</v>
       </c>
       <c r="E782" s="83" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="F782" s="23" t="s">
         <v>1764</v>
@@ -42880,7 +42887,7 @@
     </row>
     <row r="783" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A783" s="29" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B783" s="82" t="s">
         <v>769</v>
@@ -42892,7 +42899,7 @@
         <v>1249</v>
       </c>
       <c r="E783" s="83" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="F783" s="23" t="s">
         <v>1764</v>
@@ -42913,7 +42920,7 @@
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A784" s="29" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B784" s="83" t="s">
         <v>1746</v>
@@ -42950,7 +42957,7 @@
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A785" s="29" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="B785" s="83" t="s">
         <v>1746</v>
@@ -42987,7 +42994,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A786" s="29" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B786" s="83" t="s">
         <v>1746</v>
@@ -43024,7 +43031,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A787" s="29" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B787" s="83" t="s">
         <v>1746</v>
@@ -43061,7 +43068,7 @@
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A788" s="29" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B788" s="83" t="s">
         <v>1746</v>
@@ -43098,7 +43105,7 @@
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A789" s="29" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="B789" s="83" t="s">
         <v>1746</v>
@@ -43135,7 +43142,7 @@
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A790" s="29" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B790" s="83" t="s">
         <v>1746</v>
@@ -43172,7 +43179,7 @@
     </row>
     <row r="791" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A791" s="29" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B791" s="83" t="s">
         <v>1746</v>
@@ -43671,13 +43678,13 @@
         <v>1742</v>
       </c>
       <c r="B807" s="83" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C807" s="83" t="s">
         <v>1260</v>
       </c>
       <c r="D807" s="85" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="E807" s="83" t="s">
         <v>1262</v>
@@ -43757,10 +43764,10 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="B810" s="101" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C810" s="83" t="s">
         <v>1367</v>
@@ -43769,7 +43776,7 @@
         <v>1865</v>
       </c>
       <c r="E810" s="83" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="F810" s="31" t="s">
         <v>247</v>
@@ -43780,11 +43787,11 @@
       <c r="H810" s="29"/>
       <c r="I810" s="29"/>
       <c r="J810" s="29" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K810" s="29"/>
       <c r="L810" s="31" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="M810" s="29"/>
     </row>
@@ -43793,7 +43800,7 @@
         <v>1752</v>
       </c>
       <c r="B811" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C811" s="83" t="s">
         <v>1263</v>
@@ -43824,7 +43831,7 @@
         <v>1753</v>
       </c>
       <c r="B812" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C812" s="83" t="s">
         <v>1748</v>
@@ -43855,7 +43862,7 @@
         <v>1754</v>
       </c>
       <c r="B813" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C813" s="83" t="s">
         <v>1749</v>
@@ -43886,7 +43893,7 @@
         <v>1755</v>
       </c>
       <c r="B814" s="83" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C814" s="83" t="s">
         <v>1750</v>
@@ -43917,7 +43924,7 @@
         <v>1756</v>
       </c>
       <c r="B815" s="83" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C815" s="83" t="s">
         <v>1751</v>
@@ -43948,7 +43955,7 @@
         <v>1774</v>
       </c>
       <c r="B816" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C816" s="73" t="s">
         <v>1776</v>
@@ -43979,7 +43986,7 @@
         <v>1775</v>
       </c>
       <c r="B817" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C817" s="83" t="s">
         <v>1773</v>
@@ -44010,7 +44017,7 @@
         <v>1779</v>
       </c>
       <c r="B818" s="96" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="C818" s="83" t="s">
         <v>1777</v>
@@ -44251,7 +44258,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1746</v>
@@ -44284,7 +44291,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1746</v>
@@ -44317,7 +44324,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1746</v>
@@ -44350,7 +44357,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1746</v>
@@ -44383,7 +44390,7 @@
     </row>
     <row r="830" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A830" s="29" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B830" s="83" t="s">
         <v>1746</v>
@@ -44416,7 +44423,7 @@
     </row>
     <row r="831" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A831" s="29" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="B831" s="83" t="s">
         <v>1746</v>
@@ -44449,7 +44456,7 @@
     </row>
     <row r="832" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A832" s="29" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="B832" s="83" t="s">
         <v>1746</v>
@@ -44482,7 +44489,7 @@
     </row>
     <row r="833" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A833" s="29" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="B833" s="83" t="s">
         <v>1746</v>
@@ -44515,7 +44522,7 @@
     </row>
     <row r="834" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A834" s="29" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="B834" s="83" t="s">
         <v>1746</v>
@@ -44548,7 +44555,7 @@
     </row>
     <row r="835" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A835" s="29" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B835" s="83" t="s">
         <v>1746</v>
@@ -44581,7 +44588,7 @@
     </row>
     <row r="836" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A836" s="29" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B836" s="83" t="s">
         <v>1746</v>
@@ -44614,7 +44621,7 @@
     </row>
     <row r="837" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A837" s="29" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B837" s="83" t="s">
         <v>1746</v>
@@ -44647,7 +44654,7 @@
     </row>
     <row r="838" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A838" s="29" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="B838" s="83" t="s">
         <v>1746</v>
@@ -44680,7 +44687,7 @@
     </row>
     <row r="839" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A839" s="29" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="B839" s="83" t="s">
         <v>1746</v>
@@ -44713,7 +44720,7 @@
     </row>
     <row r="840" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A840" s="29" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B840" s="83" t="s">
         <v>1746</v>
@@ -44746,7 +44753,7 @@
     </row>
     <row r="841" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A841" s="29" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="B841" s="83" t="s">
         <v>1746</v>
@@ -44779,7 +44786,7 @@
     </row>
     <row r="842" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A842" s="29" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="B842" s="83" t="s">
         <v>1746</v>
@@ -44812,7 +44819,7 @@
     </row>
     <row r="843" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A843" s="29" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B843" s="83" t="s">
         <v>1746</v>
@@ -44845,7 +44852,7 @@
     </row>
     <row r="844" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A844" s="29" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B844" s="83" t="s">
         <v>1746</v>
@@ -44878,7 +44885,7 @@
     </row>
     <row r="845" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A845" s="29" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B845" s="83" t="s">
         <v>1746</v>
@@ -44911,7 +44918,7 @@
     </row>
     <row r="846" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A846" s="29" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="B846" s="101" t="s">
         <v>1846</v>
@@ -44936,7 +44943,7 @@
         <v>110</v>
       </c>
       <c r="J846" s="29" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="K846" s="29"/>
       <c r="L846" s="31"/>
@@ -44944,7 +44951,7 @@
     </row>
     <row r="847" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A847" s="29" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="B847" s="101" t="s">
         <v>1846</v>
@@ -44969,7 +44976,7 @@
         <v>110</v>
       </c>
       <c r="J847" s="29" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="K847" s="29"/>
       <c r="L847" s="31"/>
@@ -44983,7 +44990,7 @@
         <v>1860</v>
       </c>
       <c r="C848" s="83" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="D848" s="85" t="s">
         <v>1861</v>
@@ -45075,7 +45082,7 @@
         <v>1863</v>
       </c>
       <c r="B851" s="101" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C851" s="83" t="s">
         <v>1327</v>
@@ -45084,7 +45091,7 @@
         <v>1865</v>
       </c>
       <c r="E851" s="83" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="F851" s="31" t="s">
         <v>247</v>
@@ -45105,10 +45112,10 @@
     </row>
     <row r="852" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A852" s="29" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="B852" s="100" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C852" s="82" t="s">
         <v>1368</v>
@@ -45117,12 +45124,12 @@
         <v>1865</v>
       </c>
       <c r="E852" s="82" t="s">
-        <v>2640</v>
-      </c>
-      <c r="F852" s="125" t="s">
-        <v>1890</v>
-      </c>
-      <c r="G852" s="125" t="s">
+        <v>2639</v>
+      </c>
+      <c r="F852" s="31" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G852" s="31" t="s">
         <v>1661</v>
       </c>
       <c r="H852" s="29" t="s">
@@ -45132,11 +45139,11 @@
         <v>71</v>
       </c>
       <c r="J852" s="29" t="s">
+        <v>2640</v>
+      </c>
+      <c r="K852" s="29"/>
+      <c r="L852" s="31" t="s">
         <v>2641</v>
-      </c>
-      <c r="K852" s="29"/>
-      <c r="L852" s="125" t="s">
-        <v>2642</v>
       </c>
       <c r="M852" s="29"/>
     </row>
@@ -45145,7 +45152,7 @@
         <v>1864</v>
       </c>
       <c r="B853" s="101" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C853" s="83" t="s">
         <v>1328</v>
@@ -45154,7 +45161,7 @@
         <v>1865</v>
       </c>
       <c r="E853" s="83" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F853" s="31" t="s">
         <v>247</v>
@@ -45208,7 +45215,7 @@
     </row>
     <row r="855" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B855" t="s">
         <v>1874</v>
@@ -45239,13 +45246,13 @@
     </row>
     <row r="856" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A856" s="29" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B856" s="100" t="s">
         <v>2254</v>
       </c>
-      <c r="B856" s="100" t="s">
-        <v>2255</v>
-      </c>
       <c r="C856" s="83" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="D856" s="83" t="s">
         <v>1874</v>
@@ -45262,7 +45269,7 @@
       <c r="H856" s="29"/>
       <c r="I856" s="29"/>
       <c r="J856" s="29" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="K856" s="29"/>
       <c r="L856" s="31"/>
@@ -45270,13 +45277,13 @@
     </row>
     <row r="857" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A857" s="80" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B857" s="80" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="C857" s="83" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="D857" s="83" t="s">
         <v>1874</v>
@@ -45293,7 +45300,7 @@
       <c r="H857" s="29"/>
       <c r="I857" s="29"/>
       <c r="J857" s="29" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="K857" s="29"/>
       <c r="L857" s="31"/>
@@ -45301,13 +45308,13 @@
     </row>
     <row r="858" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A858" s="29" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B858" s="101" t="s">
         <v>1880</v>
       </c>
       <c r="C858" s="83" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="D858" s="83" t="s">
         <v>1874</v>
@@ -45324,7 +45331,7 @@
       <c r="H858" s="29"/>
       <c r="I858" s="29"/>
       <c r="J858" s="29" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="K858" s="29"/>
       <c r="L858" s="31"/>
@@ -45332,7 +45339,7 @@
     </row>
     <row r="859" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A859" s="29" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B859" s="80" t="s">
         <v>1134</v>
@@ -45365,7 +45372,7 @@
       <c r="L859" s="31"/>
       <c r="M859" s="29"/>
     </row>
-    <row r="860" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A860" s="29" t="s">
         <v>1886</v>
       </c>
@@ -45373,7 +45380,7 @@
         <v>1865</v>
       </c>
       <c r="C860" s="83" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="D860" s="83" t="s">
         <v>222</v>
@@ -45400,30 +45407,30 @@
       <c r="L860" s="31"/>
       <c r="M860" s="29"/>
     </row>
-    <row r="861" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A861" s="29" t="s">
-        <v>1893</v>
-      </c>
-      <c r="B861" s="85" t="s">
-        <v>1888</v>
-      </c>
-      <c r="C861" s="83" t="s">
-        <v>1352</v>
+        <v>1892</v>
+      </c>
+      <c r="B861" s="100" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C861" s="82" t="s">
+        <v>1329</v>
       </c>
       <c r="D861" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="E861" s="83" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F861" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G861" s="31" t="s">
         <v>1661</v>
       </c>
       <c r="H861" s="29" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="I861" s="29" t="s">
         <v>71</v>
@@ -45432,21 +45439,21 @@
         <v>477</v>
       </c>
       <c r="K861" s="29" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="L861" s="31"/>
       <c r="M861" s="29"/>
     </row>
     <row r="862" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A862" s="29" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B862" s="85"/>
       <c r="C862" s="83"/>
       <c r="D862" s="85"/>
       <c r="E862" s="83"/>
       <c r="F862" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G862" s="31" t="s">
         <v>1661</v>
@@ -45464,14 +45471,14 @@
     </row>
     <row r="863" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A863" s="29" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B863" s="100"/>
       <c r="C863" s="82"/>
       <c r="D863" s="79"/>
       <c r="E863" s="82"/>
       <c r="F863" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G863" s="31" t="s">
         <v>1661</v>
@@ -45489,22 +45496,22 @@
     </row>
     <row r="864" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A864" s="29" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B864" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C864" s="83" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="D864" s="85" t="s">
         <v>42</v>
       </c>
       <c r="E864" s="83" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="F864" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G864" s="31" t="s">
         <v>1661</v>
@@ -45516,7 +45523,7 @@
         <v>110</v>
       </c>
       <c r="J864" s="29" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="K864" s="29"/>
       <c r="L864" s="31"/>
@@ -45524,20 +45531,20 @@
     </row>
     <row r="865" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A865" s="29" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B865" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C865" s="83" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="D865" s="85" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="E865" s="83"/>
       <c r="F865" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G865" s="31" t="s">
         <v>1661</v>
@@ -45549,7 +45556,7 @@
         <v>110</v>
       </c>
       <c r="J865" s="85" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="K865" s="29"/>
       <c r="L865" s="31"/>
@@ -45557,22 +45564,22 @@
     </row>
     <row r="866" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A866" s="29" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B866" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C866" s="83" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="D866" s="85" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="E866" s="83" t="s">
         <v>190</v>
       </c>
       <c r="F866" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G866" s="31" t="s">
         <v>1661</v>
@@ -45584,7 +45591,7 @@
         <v>110</v>
       </c>
       <c r="J866" s="85" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="K866" s="29"/>
       <c r="L866" s="31"/>
@@ -45592,13 +45599,13 @@
     </row>
     <row r="867" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A867" s="29" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B867" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C867" s="83" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="D867" s="85" t="s">
         <v>1136</v>
@@ -45607,7 +45614,7 @@
         <v>1661</v>
       </c>
       <c r="F867" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G867" s="31" t="s">
         <v>1661</v>
@@ -45619,7 +45626,7 @@
         <v>110</v>
       </c>
       <c r="J867" s="29" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="K867" s="29"/>
       <c r="L867" s="31"/>
@@ -45627,13 +45634,13 @@
     </row>
     <row r="868" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A868" s="29" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B868" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C868" s="83" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="D868" s="85" t="s">
         <v>1134</v>
@@ -45642,7 +45649,7 @@
         <v>1661</v>
       </c>
       <c r="F868" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G868" s="31" t="s">
         <v>1661</v>
@@ -45654,7 +45661,7 @@
         <v>110</v>
       </c>
       <c r="J868" s="29" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K868" s="29"/>
       <c r="L868" s="31"/>
@@ -45662,13 +45669,13 @@
     </row>
     <row r="869" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A869" s="29" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B869" s="85" t="s">
         <v>1865</v>
       </c>
       <c r="C869" s="83" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="D869" s="85" t="s">
         <v>211</v>
@@ -45677,7 +45684,7 @@
         <v>1661</v>
       </c>
       <c r="F869" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G869" s="31" t="s">
         <v>1661</v>
@@ -45689,23 +45696,23 @@
         <v>110</v>
       </c>
       <c r="J869" s="29" t="s">
+        <v>2220</v>
+      </c>
+      <c r="K869" s="29" t="s">
         <v>2221</v>
-      </c>
-      <c r="K869" s="29" t="s">
-        <v>2222</v>
       </c>
       <c r="L869" s="31"/>
       <c r="M869" s="29"/>
     </row>
     <row r="870" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A870" s="29" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B870" s="85" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C870" s="83" t="s">
         <v>2211</v>
-      </c>
-      <c r="C870" s="83" t="s">
-        <v>2212</v>
       </c>
       <c r="D870" s="85" t="s">
         <v>1038</v>
@@ -45714,7 +45721,7 @@
         <v>1661</v>
       </c>
       <c r="F870" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G870" s="31" t="s">
         <v>1661</v>
@@ -45726,7 +45733,7 @@
         <v>110</v>
       </c>
       <c r="J870" s="29" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="K870" s="29"/>
       <c r="L870" s="31"/>
@@ -45734,25 +45741,25 @@
     </row>
     <row r="871" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A871" s="29" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="B871" s="58" t="s">
         <v>33</v>
       </c>
       <c r="C871" s="83" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="D871" s="29" t="s">
         <v>27</v>
       </c>
       <c r="E871" s="83" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F871" s="31" t="s">
         <v>1188</v>
       </c>
       <c r="G871" s="31" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H871" s="29">
         <v>0</v>
@@ -45767,7 +45774,7 @@
     </row>
     <row r="872" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A872" s="29" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="B872" s="83" t="s">
         <v>1849</v>
@@ -45794,7 +45801,7 @@
         <v>110</v>
       </c>
       <c r="J872" s="29" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="K872" s="29"/>
       <c r="L872" s="31"/>
@@ -45802,7 +45809,7 @@
     </row>
     <row r="873" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A873" s="29" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B873" s="83" t="s">
         <v>1849</v>
@@ -45829,7 +45836,7 @@
         <v>110</v>
       </c>
       <c r="J873" s="29" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="K873" s="29"/>
       <c r="L873" s="31"/>
@@ -45837,7 +45844,7 @@
     </row>
     <row r="874" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A874" s="29" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="B874" s="83" t="s">
         <v>769</v>
@@ -45849,7 +45856,7 @@
         <v>66</v>
       </c>
       <c r="E874" s="83" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="F874" s="31" t="s">
         <v>1764</v>
@@ -45864,7 +45871,7 @@
         <v>71</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -45872,7 +45879,7 @@
     </row>
     <row r="875" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A875" s="29" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B875" s="83" t="s">
         <v>769</v>
@@ -45884,7 +45891,7 @@
         <v>66</v>
       </c>
       <c r="E875" s="83" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="F875" s="31" t="s">
         <v>1764</v>
@@ -45899,7 +45906,7 @@
         <v>71</v>
       </c>
       <c r="J875" s="29" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="K875" s="29"/>
       <c r="L875" s="31"/>
@@ -45907,22 +45914,22 @@
     </row>
     <row r="876" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A876" s="29" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B876" s="83" t="s">
         <v>1865</v>
       </c>
       <c r="C876" s="83" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D876" s="85" t="s">
         <v>2213</v>
-      </c>
-      <c r="D876" s="85" t="s">
-        <v>2214</v>
       </c>
       <c r="E876" s="83" t="s">
         <v>1322</v>
       </c>
       <c r="F876" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G876" s="31" t="s">
         <v>1661</v>
@@ -45946,16 +45953,16 @@
         <v>1865</v>
       </c>
       <c r="C877" s="83" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D877" s="85" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="E877" s="83" t="s">
         <v>1323</v>
       </c>
       <c r="F877" s="31" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G877" s="31" t="s">
         <v>1661</v>
@@ -45973,10 +45980,10 @@
     </row>
     <row r="878" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A878" s="29" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="B878" s="100" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C878" s="82" t="s">
         <v>1321</v>
@@ -45985,7 +45992,7 @@
         <v>1865</v>
       </c>
       <c r="E878" s="82" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="F878" s="31" t="s">
         <v>247</v>
@@ -46000,11 +46007,11 @@
         <v>71</v>
       </c>
       <c r="J878" s="29" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="K878" s="29"/>
-      <c r="L878" s="125" t="s">
-        <v>2642</v>
+      <c r="L878" s="31" t="s">
+        <v>2641</v>
       </c>
       <c r="M878" s="29"/>
     </row>
@@ -46013,7 +46020,7 @@
         <v>1877</v>
       </c>
       <c r="B879" s="85" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="C879" s="83" t="s">
         <v>1361</v>
@@ -46022,7 +46029,7 @@
         <v>1865</v>
       </c>
       <c r="E879" s="83" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F879" s="31"/>
       <c r="G879" s="31"/>
@@ -46043,19 +46050,19 @@
         <v>1862</v>
       </c>
       <c r="C880" s="83" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="D880" s="85" t="s">
         <v>1861</v>
       </c>
       <c r="E880" s="83" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="F880" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G880" s="31" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H880" s="29">
         <v>0</v>
@@ -46064,7 +46071,7 @@
         <v>71</v>
       </c>
       <c r="J880" s="29" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="K880" s="29"/>
       <c r="L880" s="31"/>
@@ -46072,13 +46079,13 @@
     </row>
     <row r="881" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A881" s="29" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B881" s="83" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="C881" s="83" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="D881" t="s">
         <v>1874</v>
@@ -46095,7 +46102,7 @@
       <c r="H881" s="29"/>
       <c r="I881" s="29"/>
       <c r="J881" s="29" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="K881" s="29"/>
       <c r="L881" s="31"/>
@@ -46103,7 +46110,7 @@
     </row>
     <row r="882" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A882" s="29" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B882" s="83" t="s">
         <v>27</v>
@@ -46130,7 +46137,7 @@
         <v>71</v>
       </c>
       <c r="J882" s="29" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="K882" s="29"/>
       <c r="L882" s="31"/>
@@ -46138,7 +46145,7 @@
     </row>
     <row r="883" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A883" s="29" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="B883" s="83" t="s">
         <v>27</v>
@@ -46150,7 +46157,7 @@
         <v>27</v>
       </c>
       <c r="E883" s="83" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="F883" s="31" t="s">
         <v>1764</v>
@@ -46165,7 +46172,7 @@
         <v>71</v>
       </c>
       <c r="J883" s="29" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="K883" s="29"/>
       <c r="L883" s="31"/>
@@ -46173,7 +46180,7 @@
     </row>
     <row r="884" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A884" s="29" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="B884" s="83" t="s">
         <v>27</v>
@@ -46185,7 +46192,7 @@
         <v>27</v>
       </c>
       <c r="E884" s="83" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="F884" s="31" t="s">
         <v>1764</v>
@@ -46200,7 +46207,7 @@
         <v>71</v>
       </c>
       <c r="J884" s="29" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="K884" s="29"/>
       <c r="L884" s="31"/>
@@ -46208,13 +46215,13 @@
     </row>
     <row r="885" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B885" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C885" s="83" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="D885" s="83" t="s">
         <v>55</v>
@@ -46235,17 +46242,17 @@
         <v>110</v>
       </c>
       <c r="J885" s="83" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="K885" s="83" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="L885" s="31"/>
       <c r="M885" s="29"/>
     </row>
     <row r="886" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A886" s="29" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B886" s="83" t="s">
         <v>1134</v>
@@ -46263,7 +46270,7 @@
         <v>1764</v>
       </c>
       <c r="G886" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H886" s="29">
         <v>0</v>
@@ -46272,7 +46279,7 @@
         <v>71</v>
       </c>
       <c r="J886" s="29" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K886" s="29"/>
       <c r="L886" s="31"/>
@@ -46280,7 +46287,7 @@
     </row>
     <row r="887" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A887" s="29" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B887" s="83" t="s">
         <v>1134</v>
@@ -46298,7 +46305,7 @@
         <v>1764</v>
       </c>
       <c r="G887" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H887" s="29">
         <v>0</v>
@@ -46307,7 +46314,7 @@
         <v>71</v>
       </c>
       <c r="J887" s="29" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K887" s="29"/>
       <c r="L887" s="31"/>
@@ -46315,7 +46322,7 @@
     </row>
     <row r="888" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A888" s="29" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="B888" s="83" t="s">
         <v>1134</v>
@@ -46333,7 +46340,7 @@
         <v>1764</v>
       </c>
       <c r="G888" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H888" s="29">
         <v>0</v>
@@ -46342,7 +46349,7 @@
         <v>71</v>
       </c>
       <c r="J888" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K888" s="29"/>
       <c r="L888" s="31"/>
@@ -46350,7 +46357,7 @@
     </row>
     <row r="889" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A889" s="29" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="B889" s="83" t="s">
         <v>1134</v>
@@ -46368,7 +46375,7 @@
         <v>1764</v>
       </c>
       <c r="G889" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H889" s="29">
         <v>0</v>
@@ -46377,7 +46384,7 @@
         <v>71</v>
       </c>
       <c r="J889" s="83" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K889" s="29"/>
       <c r="L889" s="31"/>
@@ -46385,7 +46392,7 @@
     </row>
     <row r="890" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A890" s="29" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="B890" s="83" t="s">
         <v>1134</v>
@@ -46403,7 +46410,7 @@
         <v>1764</v>
       </c>
       <c r="G890" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H890" s="29">
         <v>0</v>
@@ -46420,7 +46427,7 @@
     </row>
     <row r="891" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A891" s="29" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="B891" s="83" t="s">
         <v>1134</v>
@@ -46438,7 +46445,7 @@
         <v>1764</v>
       </c>
       <c r="G891" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H891" s="29">
         <v>0</v>
@@ -46447,7 +46454,7 @@
         <v>71</v>
       </c>
       <c r="J891" s="29" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="K891" s="29"/>
       <c r="L891" s="31"/>
@@ -46455,7 +46462,7 @@
     </row>
     <row r="892" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A892" s="29" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B892" s="83" t="s">
         <v>1134</v>
@@ -46473,7 +46480,7 @@
         <v>1764</v>
       </c>
       <c r="G892" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H892" s="29">
         <v>0</v>
@@ -46482,7 +46489,7 @@
         <v>71</v>
       </c>
       <c r="J892" s="29" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="K892" s="29"/>
       <c r="L892" s="31"/>
@@ -46490,7 +46497,7 @@
     </row>
     <row r="893" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A893" s="29" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B893" s="83" t="s">
         <v>1134</v>
@@ -46508,7 +46515,7 @@
         <v>1764</v>
       </c>
       <c r="G893" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H893" s="29">
         <v>0</v>
@@ -46517,7 +46524,7 @@
         <v>71</v>
       </c>
       <c r="J893" s="29" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="K893" s="29"/>
       <c r="L893" s="31"/>
@@ -46525,7 +46532,7 @@
     </row>
     <row r="894" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A894" s="29" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B894" s="83" t="s">
         <v>1134</v>
@@ -46543,7 +46550,7 @@
         <v>1764</v>
       </c>
       <c r="G894" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H894" s="29">
         <v>0</v>
@@ -46552,7 +46559,7 @@
         <v>71</v>
       </c>
       <c r="J894" s="29" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="K894" s="29"/>
       <c r="L894" s="31"/>
@@ -46560,7 +46567,7 @@
     </row>
     <row r="895" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A895" s="29" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="B895" s="83" t="s">
         <v>1134</v>
@@ -46578,7 +46585,7 @@
         <v>1764</v>
       </c>
       <c r="G895" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H895" s="29">
         <v>0</v>
@@ -46587,7 +46594,7 @@
         <v>71</v>
       </c>
       <c r="J895" s="29" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="K895" s="29"/>
       <c r="L895" s="31"/>
@@ -46595,7 +46602,7 @@
     </row>
     <row r="896" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A896" s="29" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B896" s="83" t="s">
         <v>1134</v>
@@ -46613,7 +46620,7 @@
         <v>1764</v>
       </c>
       <c r="G896" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H896" s="29">
         <v>0</v>
@@ -46622,7 +46629,7 @@
         <v>71</v>
       </c>
       <c r="J896" s="29" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="K896" s="29"/>
       <c r="L896" s="31"/>
@@ -46630,7 +46637,7 @@
     </row>
     <row r="897" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A897" s="29" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B897" s="83" t="s">
         <v>1134</v>
@@ -46648,7 +46655,7 @@
         <v>1764</v>
       </c>
       <c r="G897" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H897" s="29">
         <v>0</v>
@@ -46657,7 +46664,7 @@
         <v>71</v>
       </c>
       <c r="J897" s="29" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="K897" s="29"/>
       <c r="L897" s="31"/>
@@ -46665,7 +46672,7 @@
     </row>
     <row r="898" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A898" s="29" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B898" s="83" t="s">
         <v>1134</v>
@@ -46683,7 +46690,7 @@
         <v>1764</v>
       </c>
       <c r="G898" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H898" s="29">
         <v>0</v>
@@ -46692,7 +46699,7 @@
         <v>71</v>
       </c>
       <c r="J898" s="29" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="K898" s="29"/>
       <c r="L898" s="31"/>
@@ -46700,7 +46707,7 @@
     </row>
     <row r="899" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A899" s="29" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B899" s="83" t="s">
         <v>1134</v>
@@ -46718,7 +46725,7 @@
         <v>1764</v>
       </c>
       <c r="G899" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H899" s="29">
         <v>0</v>
@@ -46727,7 +46734,7 @@
         <v>71</v>
       </c>
       <c r="J899" s="29" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="K899" s="29"/>
       <c r="L899" s="31"/>
@@ -46735,7 +46742,7 @@
     </row>
     <row r="900" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A900" s="29" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B900" s="83" t="s">
         <v>1134</v>
@@ -46753,7 +46760,7 @@
         <v>1764</v>
       </c>
       <c r="G900" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H900" s="29">
         <v>0</v>
@@ -46762,7 +46769,7 @@
         <v>71</v>
       </c>
       <c r="J900" s="29" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="K900" s="29"/>
       <c r="L900" s="31"/>
@@ -46770,7 +46777,7 @@
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A901" s="29" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B901" s="83" t="s">
         <v>1134</v>
@@ -46788,7 +46795,7 @@
         <v>1764</v>
       </c>
       <c r="G901" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H901" s="29">
         <v>0</v>
@@ -46797,7 +46804,7 @@
         <v>71</v>
       </c>
       <c r="J901" s="29" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="K901" s="29"/>
       <c r="L901" s="31"/>
@@ -46805,7 +46812,7 @@
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A902" s="29" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B902" s="83" t="s">
         <v>1134</v>
@@ -46823,7 +46830,7 @@
         <v>1764</v>
       </c>
       <c r="G902" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H902" s="29">
         <v>0</v>
@@ -46832,7 +46839,7 @@
         <v>71</v>
       </c>
       <c r="J902" s="29" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="K902" s="29"/>
       <c r="L902" s="31"/>
@@ -46840,7 +46847,7 @@
     </row>
     <row r="903" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A903" s="29" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="B903" s="83" t="s">
         <v>1134</v>
@@ -46858,7 +46865,7 @@
         <v>1764</v>
       </c>
       <c r="G903" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H903" s="29">
         <v>0</v>
@@ -46867,7 +46874,7 @@
         <v>71</v>
       </c>
       <c r="J903" s="29" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="K903" s="29"/>
       <c r="L903" s="31"/>
@@ -46875,7 +46882,7 @@
     </row>
     <row r="904" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A904" s="29" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="B904" s="83" t="s">
         <v>1134</v>
@@ -46893,7 +46900,7 @@
         <v>1764</v>
       </c>
       <c r="G904" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H904" s="29">
         <v>0</v>
@@ -46902,7 +46909,7 @@
         <v>71</v>
       </c>
       <c r="J904" s="29" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="K904" s="29"/>
       <c r="L904" s="31"/>
@@ -46910,7 +46917,7 @@
     </row>
     <row r="905" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A905" s="29" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B905" s="83" t="s">
         <v>1134</v>
@@ -46928,7 +46935,7 @@
         <v>1764</v>
       </c>
       <c r="G905" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H905" s="29">
         <v>0</v>
@@ -46937,7 +46944,7 @@
         <v>71</v>
       </c>
       <c r="J905" s="29" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="K905" s="29"/>
       <c r="L905" s="31"/>
@@ -46945,7 +46952,7 @@
     </row>
     <row r="906" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A906" s="29" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B906" s="83" t="s">
         <v>1134</v>
@@ -46963,7 +46970,7 @@
         <v>1764</v>
       </c>
       <c r="G906" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H906" s="29">
         <v>0</v>
@@ -46972,7 +46979,7 @@
         <v>71</v>
       </c>
       <c r="J906" s="29" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="K906" s="29"/>
       <c r="L906" s="31"/>
@@ -46980,7 +46987,7 @@
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A907" s="29" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B907" s="83" t="s">
         <v>1134</v>
@@ -46998,7 +47005,7 @@
         <v>1764</v>
       </c>
       <c r="G907" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H907" s="29">
         <v>0</v>
@@ -47015,7 +47022,7 @@
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A908" s="29" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="B908" s="83" t="s">
         <v>1134</v>
@@ -47027,13 +47034,13 @@
         <v>1134</v>
       </c>
       <c r="E908" s="83" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="F908" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G908" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H908" s="29">
         <v>0</v>
@@ -47042,7 +47049,7 @@
         <v>71</v>
       </c>
       <c r="J908" s="29" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="K908" s="29"/>
       <c r="L908" s="31"/>
@@ -47050,7 +47057,7 @@
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A909" s="29" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B909" s="83" t="s">
         <v>1134</v>
@@ -47062,13 +47069,13 @@
         <v>1134</v>
       </c>
       <c r="E909" s="83" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="F909" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G909" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H909" s="29">
         <v>0</v>
@@ -47077,7 +47084,7 @@
         <v>71</v>
       </c>
       <c r="J909" s="29" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="K909" s="29"/>
       <c r="L909" s="31"/>
@@ -47085,7 +47092,7 @@
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A910" s="29" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="B910" s="83" t="s">
         <v>1134</v>
@@ -47103,7 +47110,7 @@
         <v>1764</v>
       </c>
       <c r="G910" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H910" s="29">
         <v>0</v>
@@ -47120,7 +47127,7 @@
     </row>
     <row r="911" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A911" s="29" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="B911" s="83" t="s">
         <v>1134</v>
@@ -47138,7 +47145,7 @@
         <v>1764</v>
       </c>
       <c r="G911" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H911" s="29">
         <v>0</v>
@@ -47155,7 +47162,7 @@
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A912" s="29" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="B912" s="83" t="s">
         <v>1134</v>
@@ -47173,7 +47180,7 @@
         <v>1764</v>
       </c>
       <c r="G912" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H912" s="29">
         <v>0</v>
@@ -47190,7 +47197,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A913" s="29" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="B913" s="83" t="s">
         <v>1134</v>
@@ -47208,7 +47215,7 @@
         <v>1764</v>
       </c>
       <c r="G913" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H913" s="29">
         <v>0</v>
@@ -47217,7 +47224,7 @@
         <v>71</v>
       </c>
       <c r="J913" s="29" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="K913" s="29"/>
       <c r="L913" s="31"/>
@@ -47225,7 +47232,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A914" s="29" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="B914" s="83" t="s">
         <v>1134</v>
@@ -47243,7 +47250,7 @@
         <v>1764</v>
       </c>
       <c r="G914" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H914" s="29">
         <v>0</v>
@@ -47252,7 +47259,7 @@
         <v>71</v>
       </c>
       <c r="J914" s="29" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="K914" s="29"/>
       <c r="L914" s="31"/>
@@ -47260,7 +47267,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A915" s="29" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="B915" s="83" t="s">
         <v>1134</v>
@@ -47272,13 +47279,13 @@
         <v>1134</v>
       </c>
       <c r="E915" s="83" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="F915" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G915" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H915" s="29">
         <v>0</v>
@@ -47295,25 +47302,25 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A916" s="29" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="B916" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C916" s="83" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="D916" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="E916" s="83" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="F916" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G916" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H916" s="29">
         <v>0</v>
@@ -47330,7 +47337,7 @@
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A917" s="29" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="B917" s="83" t="s">
         <v>1134</v>
@@ -47342,13 +47349,13 @@
         <v>1134</v>
       </c>
       <c r="E917" s="83" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="F917" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G917" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H917" s="29">
         <v>0</v>
@@ -47357,7 +47364,7 @@
         <v>71</v>
       </c>
       <c r="J917" s="29" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="K917" s="29"/>
       <c r="L917" s="31"/>
@@ -47365,7 +47372,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A918" s="29" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="B918" s="83" t="s">
         <v>1134</v>
@@ -47377,13 +47384,13 @@
         <v>1134</v>
       </c>
       <c r="E918" s="83" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="F918" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G918" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H918" s="29">
         <v>0</v>
@@ -47392,7 +47399,7 @@
         <v>71</v>
       </c>
       <c r="J918" s="29" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="K918" s="29"/>
       <c r="L918" s="31"/>
@@ -47400,7 +47407,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A919" s="29" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B919" s="83" t="s">
         <v>1134</v>
@@ -47412,13 +47419,13 @@
         <v>1134</v>
       </c>
       <c r="E919" s="83" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="F919" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G919" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H919" s="29">
         <v>0</v>
@@ -47435,7 +47442,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A920" s="29" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="B920" s="83" t="s">
         <v>1134</v>
@@ -47447,13 +47454,13 @@
         <v>1134</v>
       </c>
       <c r="E920" s="83" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="F920" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G920" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H920" s="29">
         <v>0</v>
@@ -47470,25 +47477,25 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A921" s="29" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="B921" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C921" s="83" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="D921" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="E921" s="83" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="F921" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G921" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H921" s="29">
         <v>0</v>
@@ -47505,7 +47512,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A922" s="29" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="B922" s="83" t="s">
         <v>1134</v>
@@ -47517,13 +47524,13 @@
         <v>1134</v>
       </c>
       <c r="E922" s="83" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="F922" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G922" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H922" s="29">
         <v>0</v>
@@ -47532,7 +47539,7 @@
         <v>71</v>
       </c>
       <c r="J922" s="29" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="K922" s="29"/>
       <c r="L922" s="31"/>
@@ -47540,7 +47547,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A923" s="29" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B923" s="83" t="s">
         <v>1134</v>
@@ -47558,7 +47565,7 @@
         <v>1764</v>
       </c>
       <c r="G923" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H923" s="29">
         <v>0</v>
@@ -47575,7 +47582,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A924" s="29" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B924" s="83" t="s">
         <v>1134</v>
@@ -47593,7 +47600,7 @@
         <v>1764</v>
       </c>
       <c r="G924" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H924" s="29">
         <v>0</v>
@@ -47610,7 +47617,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A925" s="29" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B925" s="83" t="s">
         <v>1134</v>
@@ -47628,7 +47635,7 @@
         <v>1764</v>
       </c>
       <c r="G925" s="31" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="H925" s="29">
         <v>0</v>
@@ -47645,13 +47652,13 @@
     </row>
     <row r="926" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A926" s="29" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B926" s="29" t="s">
+        <v>2335</v>
+      </c>
+      <c r="C926" s="29" t="s">
         <v>2337</v>
-      </c>
-      <c r="B926" s="29" t="s">
-        <v>2336</v>
-      </c>
-      <c r="C926" s="29" t="s">
-        <v>2338</v>
       </c>
       <c r="D926" s="29" t="s">
         <v>1134</v>
@@ -47672,7 +47679,7 @@
         <v>110</v>
       </c>
       <c r="J926" s="29" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="K926" s="29"/>
       <c r="L926" s="31"/>
@@ -47680,7 +47687,7 @@
     </row>
     <row r="927" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A927" s="29" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="B927" s="114"/>
       <c r="C927" s="115"/>
@@ -47705,7 +47712,7 @@
     </row>
     <row r="928" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A928" s="29" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B928" s="112"/>
       <c r="C928" s="82"/>
@@ -47730,18 +47737,18 @@
     </row>
     <row r="929" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A929" s="29" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="B929" s="80"/>
       <c r="C929" s="73"/>
       <c r="D929" s="84"/>
       <c r="E929" s="73"/>
       <c r="F929" s="31" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="G929" s="31"/>
       <c r="H929" s="23" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="I929" s="19" t="s">
         <v>110</v>
@@ -47750,14 +47757,14 @@
         <v>464</v>
       </c>
       <c r="K929" s="29" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="L929" s="31"/>
       <c r="M929" s="29"/>
     </row>
     <row r="930" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A930" s="29" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="B930" s="80"/>
       <c r="C930" s="73"/>
@@ -47777,14 +47784,14 @@
         <v>464</v>
       </c>
       <c r="K930" s="29" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="L930" s="31"/>
       <c r="M930" s="29"/>
     </row>
     <row r="931" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A931" s="29" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="B931" s="80"/>
       <c r="C931" s="73"/>
@@ -47795,21 +47802,21 @@
       </c>
       <c r="G931" s="31"/>
       <c r="H931" s="23" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="I931" s="19" t="s">
         <v>110</v>
       </c>
       <c r="J931" s="29"/>
       <c r="K931" s="29" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="L931" s="31"/>
       <c r="M931" s="29"/>
     </row>
     <row r="932" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A932" s="29" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="B932" s="80"/>
       <c r="C932" s="73"/>
@@ -47834,7 +47841,7 @@
     </row>
     <row r="933" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A933" s="29" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="B933" s="80"/>
       <c r="C933" s="73"/>
@@ -47859,7 +47866,7 @@
     </row>
     <row r="934" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A934" s="29" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="B934" s="80"/>
       <c r="C934" s="73"/>
@@ -47870,10 +47877,10 @@
       </c>
       <c r="G934" s="31"/>
       <c r="H934" s="23" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I934" s="19" t="s">
         <v>2363</v>
-      </c>
-      <c r="I934" s="19" t="s">
-        <v>2364</v>
       </c>
       <c r="J934" s="29" t="s">
         <v>464</v>
@@ -47884,18 +47891,18 @@
     </row>
     <row r="935" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A935" s="29" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="B935" s="80"/>
       <c r="C935" s="73"/>
       <c r="D935" s="84"/>
       <c r="E935" s="73"/>
       <c r="F935" s="31" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="G935" s="31"/>
       <c r="H935" s="23" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="I935" s="19" t="s">
         <v>110</v>
@@ -47904,21 +47911,21 @@
         <v>464</v>
       </c>
       <c r="K935" s="29" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="L935" s="31"/>
       <c r="M935" s="29"/>
     </row>
     <row r="936" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A936" s="29" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="B936" s="80"/>
       <c r="C936" s="73"/>
       <c r="D936" s="84"/>
       <c r="E936" s="73"/>
       <c r="F936" s="31" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="G936" s="31"/>
       <c r="H936" s="23">
@@ -47936,7 +47943,7 @@
     </row>
     <row r="937" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A937" s="29" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="B937" s="80"/>
       <c r="C937" s="73"/>
@@ -47947,7 +47954,7 @@
       </c>
       <c r="G937" s="31"/>
       <c r="H937" s="23" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="I937" s="19" t="s">
         <v>110</v>
@@ -47961,7 +47968,7 @@
     </row>
     <row r="938" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A938" s="29" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="B938" s="80"/>
       <c r="C938" s="73"/>
@@ -47972,7 +47979,7 @@
       </c>
       <c r="G938" s="31"/>
       <c r="H938" s="23" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="I938" s="19" t="s">
         <v>110</v>
@@ -47986,7 +47993,7 @@
     </row>
     <row r="939" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A939" s="29" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B939" s="80"/>
       <c r="C939" s="73"/>
@@ -47997,7 +48004,7 @@
       </c>
       <c r="G939" s="31"/>
       <c r="H939" s="23" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="I939" s="19" t="s">
         <v>110</v>
@@ -48011,14 +48018,14 @@
     </row>
     <row r="940" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A940" s="29" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="B940" s="80"/>
       <c r="C940" s="73"/>
       <c r="D940" s="84"/>
       <c r="E940" s="73"/>
       <c r="F940" s="31" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="G940" s="31"/>
       <c r="H940" s="23" t="s">
@@ -48036,14 +48043,14 @@
     </row>
     <row r="941" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A941" s="29" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="B941" s="112"/>
       <c r="C941" s="82"/>
       <c r="D941" s="79"/>
       <c r="E941" s="82"/>
       <c r="F941" s="31" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="G941" s="31"/>
       <c r="H941" s="23" t="s">
@@ -48061,7 +48068,7 @@
     </row>
     <row r="942" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B942" s="113"/>
       <c r="C942" s="113"/>
@@ -48088,16 +48095,16 @@
     </row>
     <row r="943" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A943" s="29" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="B943" s="101" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C943" s="82" t="s">
         <v>1353</v>
       </c>
       <c r="D943" s="79" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="E943" s="82" t="s">
         <v>1190</v>
@@ -48106,7 +48113,7 @@
         <v>1355</v>
       </c>
       <c r="G943" s="31" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="H943" s="23">
         <v>0</v>
@@ -48121,16 +48128,16 @@
     </row>
     <row r="944" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A944" s="29" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B944" s="101" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C944" s="82" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D944" s="79" t="s">
         <v>2539</v>
-      </c>
-      <c r="B944" s="101" t="s">
-        <v>2534</v>
-      </c>
-      <c r="C944" s="82" t="s">
-        <v>2538</v>
-      </c>
-      <c r="D944" s="79" t="s">
-        <v>2540</v>
       </c>
       <c r="E944" s="82" t="s">
         <v>1190</v>
@@ -48139,7 +48146,7 @@
         <v>1355</v>
       </c>
       <c r="G944" s="31" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="H944" s="23">
         <v>0</v>
@@ -48154,10 +48161,10 @@
     </row>
     <row r="945" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A945" s="29" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B945" s="112" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C945" s="82" t="s">
         <v>520</v>
@@ -48166,7 +48173,7 @@
         <v>1249</v>
       </c>
       <c r="E945" s="82" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="F945" s="31" t="s">
         <v>1764</v>
@@ -48189,10 +48196,10 @@
     </row>
     <row r="946" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A946" s="29" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="B946" s="112" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C946" s="82" t="s">
         <v>522</v>
@@ -48201,7 +48208,7 @@
         <v>1249</v>
       </c>
       <c r="E946" s="82" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="F946" s="31" t="s">
         <v>1764</v>
@@ -48224,10 +48231,10 @@
     </row>
     <row r="947" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A947" s="29" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="B947" s="100" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C947" s="83" t="s">
         <v>876</v>
@@ -48236,7 +48243,7 @@
         <v>1249</v>
       </c>
       <c r="E947" s="83" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="F947" s="31" t="s">
         <v>1764</v>
@@ -48259,10 +48266,10 @@
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A948" s="29" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="B948" s="100" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C948" s="83" t="s">
         <v>875</v>
@@ -48271,7 +48278,7 @@
         <v>1249</v>
       </c>
       <c r="E948" s="83" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="F948" s="31" t="s">
         <v>1764</v>
@@ -48294,7 +48301,7 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A949" s="29" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="B949" s="100" t="s">
         <v>357</v>
@@ -48306,7 +48313,7 @@
         <v>1249</v>
       </c>
       <c r="E949" s="83" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="F949" s="31" t="s">
         <v>1764</v>
@@ -48329,7 +48336,7 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A950" s="29" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="B950" s="100" t="s">
         <v>357</v>
@@ -48341,7 +48348,7 @@
         <v>1249</v>
       </c>
       <c r="E950" s="83" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="F950" s="31" t="s">
         <v>1764</v>
@@ -48364,7 +48371,7 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A951" s="29" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="B951" s="100" t="s">
         <v>357</v>
@@ -48376,7 +48383,7 @@
         <v>1249</v>
       </c>
       <c r="E951" s="83" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="F951" s="31" t="s">
         <v>1764</v>
@@ -48399,7 +48406,7 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A952" s="29" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="B952" s="100" t="s">
         <v>357</v>
@@ -48411,7 +48418,7 @@
         <v>1249</v>
       </c>
       <c r="E952" s="83" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="F952" s="31" t="s">
         <v>1764</v>
@@ -48434,7 +48441,7 @@
     </row>
     <row r="953" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A953" s="29" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="B953" s="100" t="s">
         <v>358</v>
@@ -48446,7 +48453,7 @@
         <v>1249</v>
       </c>
       <c r="E953" s="83" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="F953" s="31" t="s">
         <v>1764</v>
@@ -48469,7 +48476,7 @@
     </row>
     <row r="954" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A954" s="29" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="B954" s="112" t="s">
         <v>358</v>
@@ -48481,7 +48488,7 @@
         <v>1249</v>
       </c>
       <c r="E954" s="82" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="F954" s="31" t="s">
         <v>1764</v>
@@ -48504,7 +48511,7 @@
     </row>
     <row r="955" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A955" s="29" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="B955" s="100" t="s">
         <v>358</v>
@@ -48516,7 +48523,7 @@
         <v>1249</v>
       </c>
       <c r="E955" s="83" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="F955" s="31" t="s">
         <v>1764</v>
@@ -48539,7 +48546,7 @@
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A956" s="29" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="B956" s="100" t="s">
         <v>358</v>
@@ -48551,7 +48558,7 @@
         <v>1249</v>
       </c>
       <c r="E956" s="83" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="F956" s="31" t="s">
         <v>1764</v>
@@ -48574,7 +48581,7 @@
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A957" s="29" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="B957" s="100" t="s">
         <v>359</v>
@@ -48586,7 +48593,7 @@
         <v>1249</v>
       </c>
       <c r="E957" s="83" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="F957" s="31" t="s">
         <v>1764</v>
@@ -48609,7 +48616,7 @@
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A958" s="29" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="B958" s="100" t="s">
         <v>359</v>
@@ -48621,7 +48628,7 @@
         <v>1249</v>
       </c>
       <c r="E958" s="83" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="F958" s="31" t="s">
         <v>1764</v>
@@ -48636,7 +48643,7 @@
         <v>71</v>
       </c>
       <c r="J958" s="29" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="K958" s="29"/>
       <c r="L958" s="31"/>
@@ -48644,7 +48651,7 @@
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A959" s="29" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="B959" s="100" t="s">
         <v>359</v>
@@ -48656,7 +48663,7 @@
         <v>1249</v>
       </c>
       <c r="E959" s="83" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="F959" s="31" t="s">
         <v>1764</v>
@@ -48671,7 +48678,7 @@
         <v>71</v>
       </c>
       <c r="J959" s="29" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="K959" s="29"/>
       <c r="L959" s="31"/>
@@ -48679,7 +48686,7 @@
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A960" s="29" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="B960" s="100" t="s">
         <v>359</v>
@@ -48691,7 +48698,7 @@
         <v>1249</v>
       </c>
       <c r="E960" s="83" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="F960" s="31" t="s">
         <v>1764</v>
@@ -48717,11 +48724,11 @@
         <v>1253</v>
       </c>
       <c r="B961" s="100" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="C961" s="83"/>
       <c r="D961" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E961" s="83" t="s">
         <v>519</v>
@@ -48731,7 +48738,7 @@
       <c r="H961" s="29"/>
       <c r="I961" s="119"/>
       <c r="J961" s="35" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="K961" s="29"/>
       <c r="L961" s="31"/>
@@ -48744,7 +48751,7 @@
       <c r="B962" s="100"/>
       <c r="C962" s="83"/>
       <c r="D962" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E962" s="83" t="s">
         <v>524</v>
@@ -48754,7 +48761,7 @@
       <c r="H962" s="29"/>
       <c r="I962" s="119"/>
       <c r="J962" s="35" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="K962" s="29"/>
       <c r="L962" s="31"/>
@@ -48765,11 +48772,11 @@
         <v>1256</v>
       </c>
       <c r="B963" s="100" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="C963" s="83"/>
       <c r="D963" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E963" s="83" t="s">
         <v>871</v>
@@ -48779,7 +48786,7 @@
       <c r="H963" s="29"/>
       <c r="I963" s="119"/>
       <c r="J963" s="33" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="K963" s="29"/>
       <c r="L963" s="31"/>
@@ -48790,11 +48797,11 @@
         <v>1258</v>
       </c>
       <c r="B964" s="100" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="C964" s="83"/>
       <c r="D964" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E964" s="83" t="s">
         <v>872</v>
@@ -48804,7 +48811,7 @@
       <c r="H964" s="29"/>
       <c r="I964" s="119"/>
       <c r="J964" s="33" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="K964" s="29"/>
       <c r="L964" s="31"/>
@@ -48812,15 +48819,15 @@
     </row>
     <row r="965" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A965" s="29" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="B965" s="100"/>
       <c r="C965" s="83"/>
       <c r="D965" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E965" s="83" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="F965" s="31"/>
       <c r="G965" s="31"/>
@@ -48835,15 +48842,15 @@
     </row>
     <row r="966" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="B966" s="112"/>
       <c r="C966" s="120"/>
       <c r="D966" s="79" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E966" s="80" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="F966" s="31"/>
       <c r="G966" s="31"/>
@@ -48861,21 +48868,21 @@
         <v>1738</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="C967" s="121"/>
       <c r="D967" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E967" s="69" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="F967" s="31"/>
       <c r="G967" s="31"/>
       <c r="H967" s="29"/>
       <c r="I967" s="119"/>
       <c r="J967" s="33" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="K967" s="29"/>
       <c r="L967" s="31"/>
@@ -48883,24 +48890,24 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="C968" s="122"/>
       <c r="D968" s="85" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="E968" s="124" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="F968" s="31"/>
       <c r="G968" s="31"/>
       <c r="H968" s="29"/>
       <c r="I968" s="119"/>
       <c r="J968" s="35" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="K968" s="29"/>
       <c r="L968" s="31"/>
@@ -48908,19 +48915,19 @@
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="B969" s="15" t="s">
         <v>1460</v>
       </c>
       <c r="D969" s="15" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="F969" t="s">
         <v>1764</v>
       </c>
       <c r="G969" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="H969" t="s">
         <v>1356</v>
@@ -48929,7 +48936,7 @@
         <v>71</v>
       </c>
       <c r="J969" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="K969" s="29"/>
       <c r="L969" s="31"/>
@@ -48937,25 +48944,25 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A970" s="29" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="B970" s="100" t="s">
         <v>1043</v>
       </c>
       <c r="C970" s="123" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="D970" s="85" t="s">
         <v>1249</v>
       </c>
       <c r="E970" s="83" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F970" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G970" s="31" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="H970" s="29">
         <v>0</v>
@@ -48964,7 +48971,7 @@
         <v>71</v>
       </c>
       <c r="J970" s="29" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="K970" s="29"/>
       <c r="L970" s="31"/>
@@ -48972,7 +48979,7 @@
     </row>
     <row r="971" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A971" s="29" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="B971" s="112" t="s">
         <v>1134</v>
@@ -48981,7 +48988,7 @@
         <v>1227</v>
       </c>
       <c r="D971" s="79" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="E971" s="82" t="s">
         <v>230</v>
@@ -48993,35 +49000,35 @@
         <v>35</v>
       </c>
       <c r="H971" s="23" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="I971" s="19" t="s">
         <v>110</v>
       </c>
       <c r="J971" s="29" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="K971" s="29"/>
       <c r="L971" s="31" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="M971" s="29"/>
     </row>
     <row r="972" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A972" s="29" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C972" s="83" t="s">
         <v>1365</v>
       </c>
       <c r="D972" s="85" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="E972" s="83" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="F972" s="31" t="s">
         <v>247</v>
@@ -49034,27 +49041,27 @@
         <v>71</v>
       </c>
       <c r="J972" s="29" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="K972" s="29"/>
       <c r="L972" s="31"/>
       <c r="M972" s="29"/>
     </row>
-    <row r="973" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A973" s="29" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="B973" s="100" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="C973" s="82" t="s">
         <v>1366</v>
       </c>
       <c r="D973" s="79" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="E973" s="82" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="F973" s="31" t="s">
         <v>247</v>
@@ -49067,15 +49074,144 @@
         <v>71</v>
       </c>
       <c r="J973" s="29" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="K973" s="29"/>
-      <c r="L973" s="125"/>
+      <c r="L973" s="31"/>
       <c r="M973" s="29"/>
     </row>
-    <row r="974" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="K974" s="113"/>
-      <c r="L974" s="3"/>
+    <row r="974" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A974" s="29" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B974" s="100" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C974" s="82" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D974" s="85" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E974" s="83" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F974" s="31" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G974" s="31" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H974" s="29" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I974" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J974" s="29"/>
+      <c r="K974" s="29"/>
+      <c r="L974" s="125"/>
+      <c r="M974" s="29"/>
+    </row>
+    <row r="975" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A975" s="29" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B975" s="100" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C975" s="82" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D975" s="85" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E975" s="83" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F975" s="31" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G975" s="31" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H975" s="29" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I975" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J975" s="29"/>
+      <c r="K975" s="29"/>
+      <c r="L975" s="125"/>
+      <c r="M975" s="29"/>
+    </row>
+    <row r="976" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A976" s="29" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B976" s="100" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C976" s="82" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D976" s="85" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E976" s="83" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F976" s="31" t="s">
+        <v>1889</v>
+      </c>
+      <c r="G976" s="31" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H976" s="29" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I976" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J976" s="29"/>
+      <c r="K976" s="29"/>
+      <c r="L976" s="125"/>
+      <c r="M976" s="29"/>
+    </row>
+    <row r="977" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A977" s="29"/>
+      <c r="B977" s="100"/>
+      <c r="C977" s="82"/>
+      <c r="D977" s="79"/>
+      <c r="E977" s="82"/>
+      <c r="F977" s="125"/>
+      <c r="G977" s="125"/>
+      <c r="H977" s="126"/>
+      <c r="I977" s="119"/>
+      <c r="J977" s="29"/>
+      <c r="K977" s="29"/>
+      <c r="L977" s="125"/>
+      <c r="M977" s="29"/>
+    </row>
+    <row r="978" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A978" s="29"/>
+      <c r="B978" s="100"/>
+      <c r="C978" s="82"/>
+      <c r="D978" s="79"/>
+      <c r="E978" s="82"/>
+      <c r="F978" s="125"/>
+      <c r="G978" s="125"/>
+      <c r="H978" s="126"/>
+      <c r="I978" s="119"/>
+      <c r="J978" s="29"/>
+      <c r="K978" s="29"/>
+      <c r="L978" s="125"/>
+      <c r="M978" s="29"/>
+    </row>
+    <row r="979" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K979" s="113"/>
+      <c r="L979" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B16922D-7949-6D42-B1CF-5887D51B5285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05538F8-0CC6-7142-B16D-D183515D153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="2320" windowWidth="23120" windowHeight="16220" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7983" uniqueCount="2665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7984" uniqueCount="2663">
   <si>
     <t>Tag</t>
   </si>
@@ -5812,57 +5812,12 @@
     <t>R_08</t>
   </si>
   <si>
-    <t>R_09</t>
-  </si>
-  <si>
-    <t>F_05</t>
-  </si>
-  <si>
-    <t>F_01</t>
-  </si>
-  <si>
-    <t>F_02</t>
-  </si>
-  <si>
-    <t>F_03</t>
-  </si>
-  <si>
-    <t>F_04</t>
-  </si>
-  <si>
-    <t>F_07</t>
-  </si>
-  <si>
-    <t>F_08</t>
-  </si>
-  <si>
-    <t>F_09</t>
-  </si>
-  <si>
     <t>F_11</t>
   </si>
   <si>
     <t>F_06</t>
   </si>
   <si>
-    <t>R_10</t>
-  </si>
-  <si>
-    <t>R_11</t>
-  </si>
-  <si>
-    <t>R_12</t>
-  </si>
-  <si>
-    <t>R_13</t>
-  </si>
-  <si>
-    <t>R_14</t>
-  </si>
-  <si>
-    <t>R_15</t>
-  </si>
-  <si>
     <t>2604-0101</t>
   </si>
   <si>
@@ -7960,9 +7915,6 @@
     <t>jump854</t>
   </si>
   <si>
-    <t>F_15</t>
-  </si>
-  <si>
     <t>ATEM</t>
   </si>
   <si>
@@ -8036,6 +7988,48 @@
   </si>
   <si>
     <t>jump976</t>
+  </si>
+  <si>
+    <t>F07</t>
+  </si>
+  <si>
+    <t>F08</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>F05</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>F02</t>
+  </si>
+  <si>
+    <t>F03</t>
+  </si>
+  <si>
+    <t>F04</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>Network</t>
   </si>
 </sst>
 </file>
@@ -19074,7 +19068,7 @@
         <v>66</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>2198</v>
+        <v>2183</v>
       </c>
       <c r="F30" s="23" t="s">
         <v>67</v>
@@ -19089,7 +19083,7 @@
         <v>29</v>
       </c>
       <c r="J30" s="23" t="s">
-        <v>2201</v>
+        <v>2186</v>
       </c>
       <c r="K30" s="23"/>
       <c r="L30" s="23"/>
@@ -19109,7 +19103,7 @@
         <v>66</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>2199</v>
+        <v>2184</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>67</v>
@@ -19124,7 +19118,7 @@
         <v>29</v>
       </c>
       <c r="J31" s="23" t="s">
-        <v>2201</v>
+        <v>2186</v>
       </c>
       <c r="K31" s="19"/>
       <c r="L31" s="19"/>
@@ -19144,7 +19138,7 @@
         <v>66</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>2200</v>
+        <v>2185</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>67</v>
@@ -19329,10 +19323,10 @@
         <v>56</v>
       </c>
       <c r="D38" s="105" t="s">
-        <v>2206</v>
+        <v>2191</v>
       </c>
       <c r="E38" s="106" t="s">
-        <v>2207</v>
+        <v>2192</v>
       </c>
       <c r="F38" s="89" t="s">
         <v>1765</v>
@@ -19602,7 +19596,7 @@
         <v>71</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>2240</v>
+        <v>2225</v>
       </c>
       <c r="K47" s="23"/>
       <c r="L47" s="23"/>
@@ -19654,7 +19648,7 @@
         <v>38</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>2241</v>
+        <v>2226</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>104</v>
@@ -19672,7 +19666,7 @@
         <v>71</v>
       </c>
       <c r="J49" s="23" t="s">
-        <v>2242</v>
+        <v>2227</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23"/>
@@ -20033,7 +20027,7 @@
         <v>38</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>2345</v>
+        <v>2330</v>
       </c>
       <c r="I62" s="19" t="s">
         <v>110</v>
@@ -20248,7 +20242,7 @@
         <v>154</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>2258</v>
+        <v>2243</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>162</v>
@@ -20287,7 +20281,7 @@
         <v>169</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>2335</v>
+        <v>2320</v>
       </c>
       <c r="E70" s="23" t="s">
         <v>208</v>
@@ -20356,7 +20350,7 @@
         <v>42</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>2356</v>
+        <v>2341</v>
       </c>
       <c r="F72" s="23" t="s">
         <v>38</v>
@@ -20371,10 +20365,10 @@
         <v>110</v>
       </c>
       <c r="J72" s="23" t="s">
-        <v>2338</v>
+        <v>2323</v>
       </c>
       <c r="K72" s="23" t="s">
-        <v>2340</v>
+        <v>2325</v>
       </c>
       <c r="L72" s="23"/>
       <c r="M72" s="24"/>
@@ -20390,7 +20384,7 @@
         <v>158</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>2546</v>
+        <v>2531</v>
       </c>
       <c r="E73" s="23" t="s">
         <v>136</v>
@@ -20406,7 +20400,7 @@
         <v>110</v>
       </c>
       <c r="J73" s="23" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K73" s="23"/>
       <c r="L73" s="19"/>
@@ -20423,7 +20417,7 @@
         <v>159</v>
       </c>
       <c r="D74" s="22" t="s">
-        <v>2547</v>
+        <v>2532</v>
       </c>
       <c r="E74" s="23" t="s">
         <v>136</v>
@@ -20439,7 +20433,7 @@
         <v>110</v>
       </c>
       <c r="J74" s="23" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K74" s="23"/>
       <c r="L74" s="23"/>
@@ -20456,7 +20450,7 @@
         <v>160</v>
       </c>
       <c r="D75" s="22" t="s">
-        <v>2548</v>
+        <v>2533</v>
       </c>
       <c r="E75" s="23" t="s">
         <v>136</v>
@@ -20472,7 +20466,7 @@
         <v>110</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K75" s="23"/>
       <c r="L75" s="19"/>
@@ -20480,7 +20474,7 @@
     </row>
     <row r="76" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>2397</v>
+        <v>2382</v>
       </c>
       <c r="B76" s="22" t="s">
         <v>42</v>
@@ -20507,7 +20501,7 @@
         <v>71</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K76" s="23"/>
       <c r="L76" s="22"/>
@@ -20515,7 +20509,7 @@
     </row>
     <row r="77" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>2398</v>
+        <v>2383</v>
       </c>
       <c r="B77" s="22" t="s">
         <v>42</v>
@@ -20542,7 +20536,7 @@
         <v>71</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K77" s="23"/>
       <c r="L77" s="22"/>
@@ -20550,7 +20544,7 @@
     </row>
     <row r="78" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
-        <v>2399</v>
+        <v>2384</v>
       </c>
       <c r="B78" s="22" t="s">
         <v>42</v>
@@ -20577,7 +20571,7 @@
         <v>71</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K78" s="23"/>
       <c r="L78" s="22"/>
@@ -20585,19 +20579,19 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
-        <v>2551</v>
+        <v>2536</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>2549</v>
+        <v>2534</v>
       </c>
       <c r="C79" s="23">
         <v>39</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>2546</v>
+        <v>2531</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>2550</v>
+        <v>2535</v>
       </c>
       <c r="F79" s="22" t="s">
         <v>247</v>
@@ -20610,7 +20604,7 @@
         <v>71</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K79" s="23"/>
       <c r="L79" s="22"/>
@@ -20618,19 +20612,19 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
-        <v>2552</v>
+        <v>2537</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>2549</v>
+        <v>2534</v>
       </c>
       <c r="C80" s="23">
         <v>41</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>2547</v>
+        <v>2532</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>2550</v>
+        <v>2535</v>
       </c>
       <c r="F80" s="22" t="s">
         <v>247</v>
@@ -20643,7 +20637,7 @@
         <v>71</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K80" s="23"/>
       <c r="L80" s="22"/>
@@ -20651,19 +20645,19 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
-        <v>2553</v>
+        <v>2538</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>2549</v>
+        <v>2534</v>
       </c>
       <c r="C81" s="23">
         <v>43</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>2548</v>
+        <v>2533</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>2550</v>
+        <v>2535</v>
       </c>
       <c r="F81" s="22" t="s">
         <v>247</v>
@@ -20676,7 +20670,7 @@
         <v>71</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K81" s="23"/>
       <c r="L81" s="22"/>
@@ -21073,7 +21067,7 @@
         <v>110</v>
       </c>
       <c r="J94" s="23" t="s">
-        <v>2223</v>
+        <v>2208</v>
       </c>
       <c r="K94" s="23"/>
       <c r="L94" s="23"/>
@@ -21231,13 +21225,13 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
-        <v>2543</v>
+        <v>2528</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>1881</v>
       </c>
       <c r="C101" s="23" t="s">
-        <v>2545</v>
+        <v>2530</v>
       </c>
       <c r="D101" s="22" t="s">
         <v>64</v>
@@ -21264,7 +21258,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="22" t="s">
-        <v>2542</v>
+        <v>2527</v>
       </c>
       <c r="B102" s="22" t="s">
         <v>225</v>
@@ -21297,7 +21291,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
-        <v>2544</v>
+        <v>2529</v>
       </c>
       <c r="B103" s="22" t="s">
         <v>224</v>
@@ -21811,13 +21805,13 @@
         <v>316</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>2632</v>
+        <v>2617</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>162</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>2633</v>
+        <v>2618</v>
       </c>
       <c r="E120" s="23" t="s">
         <v>344</v>
@@ -21835,7 +21829,7 @@
         <v>110</v>
       </c>
       <c r="J120" s="23" t="s">
-        <v>2634</v>
+        <v>2619</v>
       </c>
       <c r="K120" s="23"/>
       <c r="L120" s="23"/>
@@ -22113,13 +22107,13 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="21" t="s">
-        <v>2342</v>
+        <v>2327</v>
       </c>
       <c r="B131" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C131" s="23" t="s">
-        <v>2356</v>
+        <v>2341</v>
       </c>
       <c r="D131" s="22" t="s">
         <v>42</v>
@@ -22140,7 +22134,7 @@
         <v>71</v>
       </c>
       <c r="J131" s="23" t="s">
-        <v>2341</v>
+        <v>2326</v>
       </c>
       <c r="K131" s="23"/>
       <c r="L131" s="23"/>
@@ -22148,7 +22142,7 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="21" t="s">
-        <v>2554</v>
+        <v>2539</v>
       </c>
       <c r="B132" s="22" t="s">
         <v>42</v>
@@ -22175,7 +22169,7 @@
         <v>71</v>
       </c>
       <c r="J132" s="23" t="s">
-        <v>2240</v>
+        <v>2225</v>
       </c>
       <c r="K132" s="23"/>
       <c r="L132" s="19"/>
@@ -22755,7 +22749,7 @@
         <v>66</v>
       </c>
       <c r="E149" s="29" t="s">
-        <v>2042</v>
+        <v>2027</v>
       </c>
       <c r="F149" s="23" t="s">
         <v>1764</v>
@@ -22788,7 +22782,7 @@
         <v>66</v>
       </c>
       <c r="E150" s="29" t="s">
-        <v>2043</v>
+        <v>2028</v>
       </c>
       <c r="F150" s="23" t="s">
         <v>1764</v>
@@ -22821,7 +22815,7 @@
         <v>66</v>
       </c>
       <c r="E151" s="29" t="s">
-        <v>2044</v>
+        <v>2029</v>
       </c>
       <c r="F151" s="23" t="s">
         <v>1764</v>
@@ -22854,7 +22848,7 @@
         <v>66</v>
       </c>
       <c r="E152" s="29" t="s">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="F152" s="23" t="s">
         <v>1764</v>
@@ -22881,13 +22875,13 @@
         <v>1249</v>
       </c>
       <c r="C153" s="78" t="s">
-        <v>2093</v>
+        <v>2078</v>
       </c>
       <c r="D153" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>2046</v>
+        <v>2031</v>
       </c>
       <c r="F153" s="23" t="s">
         <v>1764</v>
@@ -22902,7 +22896,7 @@
         <v>29</v>
       </c>
       <c r="J153" s="29" t="s">
-        <v>1946</v>
+        <v>1931</v>
       </c>
       <c r="K153" s="29"/>
       <c r="L153" s="29"/>
@@ -22916,13 +22910,13 @@
         <v>1249</v>
       </c>
       <c r="C154" s="78" t="s">
-        <v>2094</v>
+        <v>2079</v>
       </c>
       <c r="D154" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>2047</v>
+        <v>2032</v>
       </c>
       <c r="F154" s="23" t="s">
         <v>1764</v>
@@ -22937,7 +22931,7 @@
         <v>29</v>
       </c>
       <c r="J154" s="29" t="s">
-        <v>1947</v>
+        <v>1932</v>
       </c>
       <c r="K154" s="29"/>
       <c r="L154" s="29"/>
@@ -22951,13 +22945,13 @@
         <v>1249</v>
       </c>
       <c r="C155" s="78" t="s">
-        <v>2095</v>
+        <v>2080</v>
       </c>
       <c r="D155" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>2042</v>
+        <v>2027</v>
       </c>
       <c r="F155" s="23" t="s">
         <v>1764</v>
@@ -22972,7 +22966,7 @@
         <v>29</v>
       </c>
       <c r="J155" s="29" t="s">
-        <v>1948</v>
+        <v>1933</v>
       </c>
       <c r="K155" s="29"/>
       <c r="L155" s="29"/>
@@ -22986,13 +22980,13 @@
         <v>1249</v>
       </c>
       <c r="C156" s="78" t="s">
-        <v>2096</v>
+        <v>2081</v>
       </c>
       <c r="D156" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>2043</v>
+        <v>2028</v>
       </c>
       <c r="F156" s="23" t="s">
         <v>1764</v>
@@ -23007,7 +23001,7 @@
         <v>29</v>
       </c>
       <c r="J156" s="29" t="s">
-        <v>1949</v>
+        <v>1934</v>
       </c>
       <c r="K156" s="29"/>
       <c r="L156" s="29"/>
@@ -23021,13 +23015,13 @@
         <v>1249</v>
       </c>
       <c r="C157" s="78" t="s">
-        <v>2097</v>
+        <v>2082</v>
       </c>
       <c r="D157" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>2044</v>
+        <v>2029</v>
       </c>
       <c r="F157" s="23" t="s">
         <v>1764</v>
@@ -23042,7 +23036,7 @@
         <v>29</v>
       </c>
       <c r="J157" s="29" t="s">
-        <v>1950</v>
+        <v>1935</v>
       </c>
       <c r="K157" s="29"/>
       <c r="L157" s="29"/>
@@ -23056,13 +23050,13 @@
         <v>1249</v>
       </c>
       <c r="C158" s="78" t="s">
-        <v>2098</v>
+        <v>2083</v>
       </c>
       <c r="D158" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E158" s="29" t="s">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="F158" s="23" t="s">
         <v>1764</v>
@@ -23077,7 +23071,7 @@
         <v>29</v>
       </c>
       <c r="J158" s="29" t="s">
-        <v>1951</v>
+        <v>1936</v>
       </c>
       <c r="K158" s="29"/>
       <c r="L158" s="29"/>
@@ -23091,13 +23085,13 @@
         <v>1249</v>
       </c>
       <c r="C159" s="78" t="s">
-        <v>2099</v>
+        <v>2084</v>
       </c>
       <c r="D159" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E159" s="29" t="s">
-        <v>2048</v>
+        <v>2033</v>
       </c>
       <c r="F159" s="23" t="s">
         <v>1764</v>
@@ -23112,7 +23106,7 @@
         <v>29</v>
       </c>
       <c r="J159" s="29" t="s">
-        <v>1952</v>
+        <v>1937</v>
       </c>
       <c r="K159" s="29"/>
       <c r="L159" s="29"/>
@@ -23126,13 +23120,13 @@
         <v>1249</v>
       </c>
       <c r="C160" s="78" t="s">
-        <v>2100</v>
+        <v>2085</v>
       </c>
       <c r="D160" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E160" s="29" t="s">
-        <v>2049</v>
+        <v>2034</v>
       </c>
       <c r="F160" s="23" t="s">
         <v>1764</v>
@@ -23147,7 +23141,7 @@
         <v>29</v>
       </c>
       <c r="J160" s="29" t="s">
-        <v>1953</v>
+        <v>1938</v>
       </c>
       <c r="K160" s="29"/>
       <c r="L160" s="29"/>
@@ -23161,13 +23155,13 @@
         <v>1249</v>
       </c>
       <c r="C161" s="78" t="s">
-        <v>2101</v>
+        <v>2086</v>
       </c>
       <c r="D161" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E161" s="29" t="s">
-        <v>2050</v>
+        <v>2035</v>
       </c>
       <c r="F161" s="23" t="s">
         <v>1764</v>
@@ -23182,7 +23176,7 @@
         <v>29</v>
       </c>
       <c r="J161" s="29" t="s">
-        <v>1954</v>
+        <v>1939</v>
       </c>
       <c r="K161" s="29"/>
       <c r="L161" s="29"/>
@@ -23196,13 +23190,13 @@
         <v>1249</v>
       </c>
       <c r="C162" s="78" t="s">
-        <v>2102</v>
+        <v>2087</v>
       </c>
       <c r="D162" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E162" s="29" t="s">
-        <v>2051</v>
+        <v>2036</v>
       </c>
       <c r="F162" s="23" t="s">
         <v>1764</v>
@@ -23231,13 +23225,13 @@
         <v>1249</v>
       </c>
       <c r="C163" s="78" t="s">
-        <v>2103</v>
+        <v>2088</v>
       </c>
       <c r="D163" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>2052</v>
+        <v>2037</v>
       </c>
       <c r="F163" s="23" t="s">
         <v>1764</v>
@@ -23252,7 +23246,7 @@
         <v>29</v>
       </c>
       <c r="J163" s="29" t="s">
-        <v>1955</v>
+        <v>1940</v>
       </c>
       <c r="K163" s="29"/>
       <c r="L163" s="29"/>
@@ -23266,13 +23260,13 @@
         <v>1249</v>
       </c>
       <c r="C164" s="78" t="s">
-        <v>2104</v>
+        <v>2089</v>
       </c>
       <c r="D164" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E164" s="29" t="s">
-        <v>2053</v>
+        <v>2038</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>1764</v>
@@ -23287,7 +23281,7 @@
         <v>29</v>
       </c>
       <c r="J164" s="29" t="s">
-        <v>1956</v>
+        <v>1941</v>
       </c>
       <c r="K164" s="29"/>
       <c r="L164" s="29"/>
@@ -23301,13 +23295,13 @@
         <v>1249</v>
       </c>
       <c r="C165" s="78" t="s">
-        <v>2105</v>
+        <v>2090</v>
       </c>
       <c r="D165" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E165" s="29" t="s">
-        <v>2054</v>
+        <v>2039</v>
       </c>
       <c r="F165" s="23" t="s">
         <v>1764</v>
@@ -23322,7 +23316,7 @@
         <v>29</v>
       </c>
       <c r="J165" s="29" t="s">
-        <v>1957</v>
+        <v>1942</v>
       </c>
       <c r="K165" s="29"/>
       <c r="L165" s="29"/>
@@ -23336,13 +23330,13 @@
         <v>1249</v>
       </c>
       <c r="C166" s="78" t="s">
-        <v>2106</v>
+        <v>2091</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E166" s="29" t="s">
-        <v>2055</v>
+        <v>2040</v>
       </c>
       <c r="F166" s="23" t="s">
         <v>1764</v>
@@ -23371,13 +23365,13 @@
         <v>1249</v>
       </c>
       <c r="C167" s="78" t="s">
-        <v>2107</v>
+        <v>2092</v>
       </c>
       <c r="D167" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>2056</v>
+        <v>2041</v>
       </c>
       <c r="F167" s="23" t="s">
         <v>1764</v>
@@ -23406,13 +23400,13 @@
         <v>1249</v>
       </c>
       <c r="C168" s="78" t="s">
-        <v>2108</v>
+        <v>2093</v>
       </c>
       <c r="D168" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>2057</v>
+        <v>2042</v>
       </c>
       <c r="F168" s="23" t="s">
         <v>1764</v>
@@ -23441,13 +23435,13 @@
         <v>1249</v>
       </c>
       <c r="C169" s="78" t="s">
-        <v>2109</v>
+        <v>2094</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>2058</v>
+        <v>2043</v>
       </c>
       <c r="F169" s="23" t="s">
         <v>1764</v>
@@ -23476,13 +23470,13 @@
         <v>1249</v>
       </c>
       <c r="C170" s="78" t="s">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="D170" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E170" s="29" t="s">
-        <v>2059</v>
+        <v>2044</v>
       </c>
       <c r="F170" s="23" t="s">
         <v>1764</v>
@@ -23511,13 +23505,13 @@
         <v>1249</v>
       </c>
       <c r="C171" s="78" t="s">
-        <v>2111</v>
+        <v>2096</v>
       </c>
       <c r="D171" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E171" s="29" t="s">
-        <v>2060</v>
+        <v>2045</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>1764</v>
@@ -23546,13 +23540,13 @@
         <v>1249</v>
       </c>
       <c r="C172" s="78" t="s">
-        <v>2112</v>
+        <v>2097</v>
       </c>
       <c r="D172" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E172" s="29" t="s">
-        <v>2061</v>
+        <v>2046</v>
       </c>
       <c r="F172" s="23" t="s">
         <v>1764</v>
@@ -23581,13 +23575,13 @@
         <v>1249</v>
       </c>
       <c r="C173" s="78" t="s">
-        <v>2113</v>
+        <v>2098</v>
       </c>
       <c r="D173" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E173" s="29" t="s">
-        <v>2062</v>
+        <v>2047</v>
       </c>
       <c r="F173" s="23" t="s">
         <v>1764</v>
@@ -23616,13 +23610,13 @@
         <v>1249</v>
       </c>
       <c r="C174" s="78" t="s">
-        <v>2114</v>
+        <v>2099</v>
       </c>
       <c r="D174" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E174" s="29" t="s">
-        <v>2063</v>
+        <v>2048</v>
       </c>
       <c r="F174" s="23" t="s">
         <v>1764</v>
@@ -23651,13 +23645,13 @@
         <v>1249</v>
       </c>
       <c r="C175" s="78" t="s">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="D175" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E175" s="29" t="s">
-        <v>2064</v>
+        <v>2049</v>
       </c>
       <c r="F175" s="23" t="s">
         <v>1764</v>
@@ -23686,13 +23680,13 @@
         <v>1249</v>
       </c>
       <c r="C176" s="78" t="s">
-        <v>2116</v>
+        <v>2101</v>
       </c>
       <c r="D176" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E176" s="29" t="s">
-        <v>2065</v>
+        <v>2050</v>
       </c>
       <c r="F176" s="23" t="s">
         <v>1764</v>
@@ -23721,13 +23715,13 @@
         <v>1249</v>
       </c>
       <c r="C177" s="78" t="s">
-        <v>2117</v>
+        <v>2102</v>
       </c>
       <c r="D177" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E177" s="29" t="s">
-        <v>2066</v>
+        <v>2051</v>
       </c>
       <c r="F177" s="23" t="s">
         <v>1764</v>
@@ -23756,13 +23750,13 @@
         <v>1249</v>
       </c>
       <c r="C178" s="78" t="s">
-        <v>2118</v>
+        <v>2103</v>
       </c>
       <c r="D178" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>2067</v>
+        <v>2052</v>
       </c>
       <c r="F178" s="23" t="s">
         <v>1764</v>
@@ -23791,13 +23785,13 @@
         <v>1249</v>
       </c>
       <c r="C179" s="78" t="s">
-        <v>2119</v>
+        <v>2104</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E179" s="29" t="s">
-        <v>2068</v>
+        <v>2053</v>
       </c>
       <c r="F179" s="23" t="s">
         <v>1764</v>
@@ -23826,13 +23820,13 @@
         <v>1249</v>
       </c>
       <c r="C180" s="78" t="s">
-        <v>2120</v>
+        <v>2105</v>
       </c>
       <c r="D180" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>2069</v>
+        <v>2054</v>
       </c>
       <c r="F180" s="23" t="s">
         <v>1764</v>
@@ -23861,13 +23855,13 @@
         <v>1249</v>
       </c>
       <c r="C181" s="78" t="s">
-        <v>2121</v>
+        <v>2106</v>
       </c>
       <c r="D181" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E181" s="29" t="s">
-        <v>2070</v>
+        <v>2055</v>
       </c>
       <c r="F181" s="23" t="s">
         <v>1764</v>
@@ -23882,7 +23876,7 @@
         <v>29</v>
       </c>
       <c r="J181" s="29" t="s">
-        <v>1958</v>
+        <v>1943</v>
       </c>
       <c r="K181" s="29"/>
       <c r="L181" s="29"/>
@@ -23896,13 +23890,13 @@
         <v>1249</v>
       </c>
       <c r="C182" s="78" t="s">
-        <v>2122</v>
+        <v>2107</v>
       </c>
       <c r="D182" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E182" s="29" t="s">
-        <v>2071</v>
+        <v>2056</v>
       </c>
       <c r="F182" s="23" t="s">
         <v>1764</v>
@@ -23917,7 +23911,7 @@
         <v>29</v>
       </c>
       <c r="J182" s="29" t="s">
-        <v>1961</v>
+        <v>1946</v>
       </c>
       <c r="K182" s="29"/>
       <c r="L182" s="29"/>
@@ -23931,13 +23925,13 @@
         <v>1249</v>
       </c>
       <c r="C183" s="78" t="s">
-        <v>2123</v>
+        <v>2108</v>
       </c>
       <c r="D183" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>2072</v>
+        <v>2057</v>
       </c>
       <c r="F183" s="23" t="s">
         <v>1764</v>
@@ -23952,7 +23946,7 @@
         <v>29</v>
       </c>
       <c r="J183" s="29" t="s">
-        <v>1962</v>
+        <v>1947</v>
       </c>
       <c r="K183" s="29"/>
       <c r="L183" s="29"/>
@@ -23966,13 +23960,13 @@
         <v>1249</v>
       </c>
       <c r="C184" s="78" t="s">
-        <v>2124</v>
+        <v>2109</v>
       </c>
       <c r="D184" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>2073</v>
+        <v>2058</v>
       </c>
       <c r="F184" s="23" t="s">
         <v>1764</v>
@@ -24001,13 +23995,13 @@
         <v>1249</v>
       </c>
       <c r="C185" s="78" t="s">
-        <v>2125</v>
+        <v>2110</v>
       </c>
       <c r="D185" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E185" s="29" t="s">
-        <v>2074</v>
+        <v>2059</v>
       </c>
       <c r="F185" s="23" t="s">
         <v>1764</v>
@@ -24036,13 +24030,13 @@
         <v>1249</v>
       </c>
       <c r="C186" s="78" t="s">
-        <v>2126</v>
+        <v>2111</v>
       </c>
       <c r="D186" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>2075</v>
+        <v>2060</v>
       </c>
       <c r="F186" s="23" t="s">
         <v>1764</v>
@@ -24057,7 +24051,7 @@
         <v>29</v>
       </c>
       <c r="J186" s="29" t="s">
-        <v>1941</v>
+        <v>1926</v>
       </c>
       <c r="K186" s="29"/>
       <c r="L186" s="29"/>
@@ -24071,13 +24065,13 @@
         <v>1249</v>
       </c>
       <c r="C187" s="78" t="s">
-        <v>2127</v>
+        <v>2112</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>2076</v>
+        <v>2061</v>
       </c>
       <c r="F187" s="23" t="s">
         <v>1764</v>
@@ -24092,7 +24086,7 @@
         <v>29</v>
       </c>
       <c r="J187" s="29" t="s">
-        <v>1942</v>
+        <v>1927</v>
       </c>
       <c r="K187" s="29"/>
       <c r="L187" s="29"/>
@@ -24106,13 +24100,13 @@
         <v>1249</v>
       </c>
       <c r="C188" s="78" t="s">
-        <v>2128</v>
+        <v>2113</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F188" s="23" t="s">
         <v>1764</v>
@@ -24127,7 +24121,7 @@
         <v>29</v>
       </c>
       <c r="J188" s="29" t="s">
-        <v>1963</v>
+        <v>1948</v>
       </c>
       <c r="K188" s="29"/>
       <c r="L188" s="29"/>
@@ -24141,13 +24135,13 @@
         <v>1249</v>
       </c>
       <c r="C189" s="78" t="s">
-        <v>2129</v>
+        <v>2114</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>2078</v>
+        <v>2063</v>
       </c>
       <c r="F189" s="23" t="s">
         <v>1764</v>
@@ -24162,7 +24156,7 @@
         <v>29</v>
       </c>
       <c r="J189" s="29" t="s">
-        <v>1964</v>
+        <v>1949</v>
       </c>
       <c r="K189" s="29"/>
       <c r="L189" s="29"/>
@@ -24176,13 +24170,13 @@
         <v>1249</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>2130</v>
+        <v>2115</v>
       </c>
       <c r="D190" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>2079</v>
+        <v>2064</v>
       </c>
       <c r="F190" s="23" t="s">
         <v>1764</v>
@@ -24197,7 +24191,7 @@
         <v>29</v>
       </c>
       <c r="J190" s="29" t="s">
-        <v>1965</v>
+        <v>1950</v>
       </c>
       <c r="K190" s="29"/>
       <c r="L190" s="29"/>
@@ -24211,13 +24205,13 @@
         <v>1249</v>
       </c>
       <c r="C191" s="78" t="s">
-        <v>2131</v>
+        <v>2116</v>
       </c>
       <c r="D191" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>2080</v>
+        <v>2065</v>
       </c>
       <c r="F191" s="23" t="s">
         <v>1764</v>
@@ -24232,7 +24226,7 @@
         <v>29</v>
       </c>
       <c r="J191" s="29" t="s">
-        <v>1966</v>
+        <v>1951</v>
       </c>
       <c r="K191" s="29"/>
       <c r="L191" s="29"/>
@@ -24246,13 +24240,13 @@
         <v>1249</v>
       </c>
       <c r="C192" s="78" t="s">
-        <v>2132</v>
+        <v>2117</v>
       </c>
       <c r="D192" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>2081</v>
+        <v>2066</v>
       </c>
       <c r="F192" s="23" t="s">
         <v>1764</v>
@@ -24279,13 +24273,13 @@
         <v>1249</v>
       </c>
       <c r="C193" s="78" t="s">
-        <v>2133</v>
+        <v>2118</v>
       </c>
       <c r="D193" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>2082</v>
+        <v>2067</v>
       </c>
       <c r="F193" s="23" t="s">
         <v>1764</v>
@@ -24312,13 +24306,13 @@
         <v>1249</v>
       </c>
       <c r="C194" s="78" t="s">
-        <v>2134</v>
+        <v>2119</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>2083</v>
+        <v>2068</v>
       </c>
       <c r="F194" s="23" t="s">
         <v>1764</v>
@@ -24345,13 +24339,13 @@
         <v>1249</v>
       </c>
       <c r="C195" s="78" t="s">
-        <v>2135</v>
+        <v>2120</v>
       </c>
       <c r="D195" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>2084</v>
+        <v>2069</v>
       </c>
       <c r="F195" s="23" t="s">
         <v>1764</v>
@@ -24378,13 +24372,13 @@
         <v>1249</v>
       </c>
       <c r="C196" s="78" t="s">
-        <v>2136</v>
+        <v>2121</v>
       </c>
       <c r="D196" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>2085</v>
+        <v>2070</v>
       </c>
       <c r="F196" s="23" t="s">
         <v>1764</v>
@@ -24399,7 +24393,7 @@
         <v>29</v>
       </c>
       <c r="J196" s="29" t="s">
-        <v>1959</v>
+        <v>1944</v>
       </c>
       <c r="K196" s="29"/>
       <c r="L196" s="29"/>
@@ -24413,13 +24407,13 @@
         <v>1249</v>
       </c>
       <c r="C197" s="78" t="s">
-        <v>2137</v>
+        <v>2122</v>
       </c>
       <c r="D197" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>2086</v>
+        <v>2071</v>
       </c>
       <c r="F197" s="23" t="s">
         <v>1764</v>
@@ -24434,7 +24428,7 @@
         <v>29</v>
       </c>
       <c r="J197" s="29" t="s">
-        <v>1960</v>
+        <v>1945</v>
       </c>
       <c r="K197" s="29"/>
       <c r="L197" s="29"/>
@@ -24448,13 +24442,13 @@
         <v>1249</v>
       </c>
       <c r="C198" s="78" t="s">
-        <v>2138</v>
+        <v>2123</v>
       </c>
       <c r="D198" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>2087</v>
+        <v>2072</v>
       </c>
       <c r="F198" s="23" t="s">
         <v>1764</v>
@@ -24481,13 +24475,13 @@
         <v>1249</v>
       </c>
       <c r="C199" s="78" t="s">
-        <v>2139</v>
+        <v>2124</v>
       </c>
       <c r="D199" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E199" s="29" t="s">
-        <v>2088</v>
+        <v>2073</v>
       </c>
       <c r="F199" s="23" t="s">
         <v>1764</v>
@@ -24514,13 +24508,13 @@
         <v>1249</v>
       </c>
       <c r="C200" s="78" t="s">
-        <v>2140</v>
+        <v>2125</v>
       </c>
       <c r="D200" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>2089</v>
+        <v>2074</v>
       </c>
       <c r="F200" s="23" t="s">
         <v>1764</v>
@@ -24547,13 +24541,13 @@
         <v>1249</v>
       </c>
       <c r="C201" s="78" t="s">
-        <v>2141</v>
+        <v>2126</v>
       </c>
       <c r="D201" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E201" s="29" t="s">
-        <v>2055</v>
+        <v>2040</v>
       </c>
       <c r="F201" s="23" t="s">
         <v>1764</v>
@@ -24580,13 +24574,13 @@
         <v>1249</v>
       </c>
       <c r="C202" s="78" t="s">
-        <v>2142</v>
+        <v>2127</v>
       </c>
       <c r="D202" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E202" s="29" t="s">
-        <v>2090</v>
+        <v>2075</v>
       </c>
       <c r="F202" s="23" t="s">
         <v>1764</v>
@@ -24601,7 +24595,7 @@
         <v>29</v>
       </c>
       <c r="J202" s="29" t="s">
-        <v>1967</v>
+        <v>1952</v>
       </c>
       <c r="K202" s="29"/>
       <c r="L202" s="31"/>
@@ -24615,13 +24609,13 @@
         <v>1249</v>
       </c>
       <c r="C203" s="78" t="s">
-        <v>2143</v>
+        <v>2128</v>
       </c>
       <c r="D203" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E203" s="29" t="s">
-        <v>2091</v>
+        <v>2076</v>
       </c>
       <c r="F203" s="23" t="s">
         <v>1764</v>
@@ -24636,7 +24630,7 @@
         <v>29</v>
       </c>
       <c r="J203" s="29" t="s">
-        <v>1968</v>
+        <v>1953</v>
       </c>
       <c r="K203" s="29"/>
       <c r="L203" s="31"/>
@@ -24650,13 +24644,13 @@
         <v>1249</v>
       </c>
       <c r="C204" s="78" t="s">
-        <v>2144</v>
+        <v>2129</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E204" s="29" t="s">
-        <v>2092</v>
+        <v>2077</v>
       </c>
       <c r="F204" s="23" t="s">
         <v>1764</v>
@@ -24671,7 +24665,7 @@
         <v>29</v>
       </c>
       <c r="J204" s="29" t="s">
-        <v>1969</v>
+        <v>1954</v>
       </c>
       <c r="K204" s="29"/>
       <c r="L204" s="31"/>
@@ -24685,13 +24679,13 @@
         <v>1249</v>
       </c>
       <c r="C205" s="78" t="s">
-        <v>2145</v>
+        <v>2130</v>
       </c>
       <c r="D205" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E205" s="29" t="s">
-        <v>2059</v>
+        <v>2044</v>
       </c>
       <c r="F205" s="23" t="s">
         <v>1764</v>
@@ -24718,13 +24712,13 @@
         <v>1249</v>
       </c>
       <c r="C206" s="78" t="s">
-        <v>2146</v>
+        <v>2131</v>
       </c>
       <c r="D206" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>2060</v>
+        <v>2045</v>
       </c>
       <c r="F206" s="23" t="s">
         <v>1764</v>
@@ -24751,13 +24745,13 @@
         <v>1249</v>
       </c>
       <c r="C207" s="78" t="s">
-        <v>2147</v>
+        <v>2132</v>
       </c>
       <c r="D207" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E207" s="29" t="s">
-        <v>2061</v>
+        <v>2046</v>
       </c>
       <c r="F207" s="23" t="s">
         <v>1764</v>
@@ -24784,13 +24778,13 @@
         <v>1249</v>
       </c>
       <c r="C208" s="78" t="s">
-        <v>2148</v>
+        <v>2133</v>
       </c>
       <c r="D208" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E208" s="29" t="s">
-        <v>2062</v>
+        <v>2047</v>
       </c>
       <c r="F208" s="23" t="s">
         <v>1764</v>
@@ -24817,13 +24811,13 @@
         <v>1249</v>
       </c>
       <c r="C209" s="78" t="s">
-        <v>2149</v>
+        <v>2134</v>
       </c>
       <c r="D209" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E209" s="29" t="s">
-        <v>2063</v>
+        <v>2048</v>
       </c>
       <c r="F209" s="23" t="s">
         <v>1764</v>
@@ -24850,13 +24844,13 @@
         <v>1249</v>
       </c>
       <c r="C210" s="78" t="s">
-        <v>2150</v>
+        <v>2135</v>
       </c>
       <c r="D210" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E210" s="29" t="s">
-        <v>2064</v>
+        <v>2049</v>
       </c>
       <c r="F210" s="23" t="s">
         <v>1764</v>
@@ -24883,13 +24877,13 @@
         <v>1249</v>
       </c>
       <c r="C211" s="78" t="s">
-        <v>2151</v>
+        <v>2136</v>
       </c>
       <c r="D211" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E211" s="29" t="s">
-        <v>2068</v>
+        <v>2053</v>
       </c>
       <c r="F211" s="23" t="s">
         <v>1764</v>
@@ -24916,13 +24910,13 @@
         <v>1249</v>
       </c>
       <c r="C212" s="78" t="s">
-        <v>2152</v>
+        <v>2137</v>
       </c>
       <c r="D212" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E212" s="29" t="s">
-        <v>2069</v>
+        <v>2054</v>
       </c>
       <c r="F212" s="23" t="s">
         <v>1764</v>
@@ -24949,13 +24943,13 @@
         <v>1249</v>
       </c>
       <c r="C213" s="78" t="s">
-        <v>2153</v>
+        <v>2138</v>
       </c>
       <c r="D213" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E213" s="29" t="s">
-        <v>2065</v>
+        <v>2050</v>
       </c>
       <c r="F213" s="23" t="s">
         <v>1764</v>
@@ -24982,13 +24976,13 @@
         <v>1249</v>
       </c>
       <c r="C214" s="78" t="s">
-        <v>2154</v>
+        <v>2139</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E214" s="29" t="s">
-        <v>2066</v>
+        <v>2051</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>1764</v>
@@ -25015,13 +25009,13 @@
         <v>1249</v>
       </c>
       <c r="C215" s="78" t="s">
-        <v>2155</v>
+        <v>2140</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E215" s="29" t="s">
-        <v>2067</v>
+        <v>2052</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>1764</v>
@@ -25048,13 +25042,13 @@
         <v>1249</v>
       </c>
       <c r="C216" s="78" t="s">
-        <v>2156</v>
+        <v>2141</v>
       </c>
       <c r="D216" s="31" t="s">
         <v>66</v>
       </c>
       <c r="E216" s="29" t="s">
-        <v>2070</v>
+        <v>2055</v>
       </c>
       <c r="F216" s="23" t="s">
         <v>1764</v>
@@ -25333,16 +25327,16 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>2257</v>
+        <v>2242</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>1134</v>
       </c>
       <c r="C225" s="36" t="s">
-        <v>2245</v>
+        <v>2230</v>
       </c>
       <c r="D225" s="31" t="s">
-        <v>2258</v>
+        <v>2243</v>
       </c>
       <c r="E225" s="36" t="s">
         <v>230</v>
@@ -25360,7 +25354,7 @@
         <v>110</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>2244</v>
+        <v>2229</v>
       </c>
       <c r="K225" s="31"/>
       <c r="L225" s="31" t="s">
@@ -27023,7 +27017,7 @@
         <v>110</v>
       </c>
       <c r="J282" s="54" t="s">
-        <v>2229</v>
+        <v>2214</v>
       </c>
       <c r="K282" s="29"/>
       <c r="L282" s="31"/>
@@ -30132,7 +30126,7 @@
         <v>981</v>
       </c>
       <c r="E384" s="35" t="s">
-        <v>2401</v>
+        <v>2386</v>
       </c>
       <c r="F384" s="31" t="s">
         <v>247</v>
@@ -30157,13 +30151,13 @@
         <v>981</v>
       </c>
       <c r="C385" s="29" t="s">
-        <v>1933</v>
+        <v>1924</v>
       </c>
       <c r="D385" s="29" t="s">
         <v>981</v>
       </c>
       <c r="E385" s="29" t="s">
-        <v>1924</v>
+        <v>2652</v>
       </c>
       <c r="F385" s="31"/>
       <c r="G385" s="31"/>
@@ -30190,7 +30184,7 @@
         <v>981</v>
       </c>
       <c r="E386" s="29" t="s">
-        <v>1925</v>
+        <v>2653</v>
       </c>
       <c r="F386" s="31"/>
       <c r="G386" s="31"/>
@@ -30217,7 +30211,7 @@
         <v>981</v>
       </c>
       <c r="E387" s="29" t="s">
-        <v>1926</v>
+        <v>2654</v>
       </c>
       <c r="F387" s="31"/>
       <c r="G387" s="31"/>
@@ -30244,7 +30238,7 @@
         <v>981</v>
       </c>
       <c r="E388" s="29" t="s">
-        <v>1927</v>
+        <v>2655</v>
       </c>
       <c r="F388" s="31"/>
       <c r="G388" s="31"/>
@@ -30271,7 +30265,7 @@
         <v>981</v>
       </c>
       <c r="E389" s="29" t="s">
-        <v>1928</v>
+        <v>2656</v>
       </c>
       <c r="F389" s="31"/>
       <c r="G389" s="31"/>
@@ -31060,7 +31054,7 @@
         <v>32</v>
       </c>
       <c r="D419" s="31" t="s">
-        <v>2400</v>
+        <v>2385</v>
       </c>
       <c r="E419" s="29" t="s">
         <v>32</v>
@@ -31091,7 +31085,7 @@
         <v>5</v>
       </c>
       <c r="D420" s="31" t="s">
-        <v>2400</v>
+        <v>2385</v>
       </c>
       <c r="E420" s="29" t="s">
         <v>190</v>
@@ -31552,7 +31546,7 @@
         <v>1043</v>
       </c>
       <c r="E434" s="29" t="s">
-        <v>2376</v>
+        <v>2361</v>
       </c>
       <c r="F434" s="31" t="s">
         <v>510</v>
@@ -31587,7 +31581,7 @@
         <v>1043</v>
       </c>
       <c r="E435" s="29" t="s">
-        <v>2377</v>
+        <v>2362</v>
       </c>
       <c r="F435" s="31" t="s">
         <v>510</v>
@@ -31622,7 +31616,7 @@
         <v>1043</v>
       </c>
       <c r="E436" s="29" t="s">
-        <v>2378</v>
+        <v>2363</v>
       </c>
       <c r="F436" s="31" t="s">
         <v>510</v>
@@ -32095,7 +32089,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2357</v>
+        <v>2342</v>
       </c>
       <c r="B451" s="80"/>
       <c r="C451" s="73"/>
@@ -32106,7 +32100,7 @@
       </c>
       <c r="G451" s="31"/>
       <c r="H451" s="23" t="s">
-        <v>2358</v>
+        <v>2343</v>
       </c>
       <c r="I451" s="19" t="s">
         <v>110</v>
@@ -32666,7 +32660,7 @@
       <c r="H467" s="29"/>
       <c r="I467" s="29"/>
       <c r="J467" s="54" t="s">
-        <v>2228</v>
+        <v>2213</v>
       </c>
       <c r="K467" s="33"/>
       <c r="L467" s="31"/>
@@ -32755,7 +32749,7 @@
       <c r="H470" s="29"/>
       <c r="I470" s="29"/>
       <c r="J470" s="54" t="s">
-        <v>2230</v>
+        <v>2215</v>
       </c>
       <c r="K470" s="35"/>
       <c r="L470" s="31"/>
@@ -32790,10 +32784,10 @@
         <v>29</v>
       </c>
       <c r="J471" s="54" t="s">
-        <v>2229</v>
+        <v>2214</v>
       </c>
       <c r="K471" s="33" t="s">
-        <v>2239</v>
+        <v>2224</v>
       </c>
       <c r="L471" s="31"/>
       <c r="M471" s="29"/>
@@ -33185,7 +33179,7 @@
     </row>
     <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="29" t="s">
-        <v>2203</v>
+        <v>2188</v>
       </c>
       <c r="B483" s="22" t="s">
         <v>77</v>
@@ -33216,13 +33210,13 @@
     </row>
     <row r="484" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A484" s="29" t="s">
-        <v>2653</v>
+        <v>2637</v>
       </c>
       <c r="B484" s="29" t="s">
-        <v>2652</v>
+        <v>2636</v>
       </c>
       <c r="C484" s="53" t="s">
-        <v>2654</v>
+        <v>2638</v>
       </c>
       <c r="D484" s="58" t="s">
         <v>1134</v>
@@ -33251,16 +33245,16 @@
     </row>
     <row r="485" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A485" s="29" t="s">
-        <v>2655</v>
+        <v>2639</v>
       </c>
       <c r="B485" s="29" t="s">
         <v>1134</v>
       </c>
       <c r="C485" s="73" t="s">
-        <v>2265</v>
+        <v>2250</v>
       </c>
       <c r="D485" s="84" t="s">
-        <v>2656</v>
+        <v>2640</v>
       </c>
       <c r="E485" s="73" t="s">
         <v>230</v>
@@ -33278,7 +33272,7 @@
         <v>110</v>
       </c>
       <c r="J485" s="29" t="s">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="K485" s="33"/>
       <c r="L485" s="31"/>
@@ -33286,13 +33280,13 @@
     </row>
     <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="29" t="s">
-        <v>2204</v>
+        <v>2189</v>
       </c>
       <c r="B486" s="29" t="s">
-        <v>2206</v>
+        <v>2191</v>
       </c>
       <c r="C486" s="53" t="s">
-        <v>2205</v>
+        <v>2190</v>
       </c>
       <c r="D486" s="58" t="s">
         <v>1134</v>
@@ -33711,7 +33705,7 @@
         <v>110</v>
       </c>
       <c r="J498" s="54" t="s">
-        <v>2224</v>
+        <v>2209</v>
       </c>
       <c r="K498" s="33"/>
       <c r="L498" s="31"/>
@@ -33748,7 +33742,7 @@
         <v>110</v>
       </c>
       <c r="J499" s="29" t="s">
-        <v>2224</v>
+        <v>2209</v>
       </c>
       <c r="K499" s="33"/>
       <c r="L499" s="31"/>
@@ -33989,7 +33983,7 @@
         <v>110</v>
       </c>
       <c r="J506" s="29" t="s">
-        <v>2541</v>
+        <v>2526</v>
       </c>
       <c r="K506" s="29"/>
       <c r="L506" s="31" t="s">
@@ -34002,13 +33996,13 @@
         <v>1105</v>
       </c>
       <c r="B507" s="31" t="s">
-        <v>2651</v>
+        <v>2635</v>
       </c>
       <c r="C507" s="29" t="s">
         <v>162</v>
       </c>
       <c r="D507" s="31" t="s">
-        <v>2652</v>
+        <v>2636</v>
       </c>
       <c r="E507" s="29" t="s">
         <v>208</v>
@@ -34173,7 +34167,7 @@
         <v>162</v>
       </c>
       <c r="D512" s="29" t="s">
-        <v>2546</v>
+        <v>2531</v>
       </c>
       <c r="E512" s="29" t="s">
         <v>138</v>
@@ -34191,7 +34185,7 @@
         <v>110</v>
       </c>
       <c r="J512" s="29" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K512" s="29"/>
       <c r="L512" s="31"/>
@@ -34208,7 +34202,7 @@
         <v>162</v>
       </c>
       <c r="D513" s="29" t="s">
-        <v>2547</v>
+        <v>2532</v>
       </c>
       <c r="E513" s="29" t="s">
         <v>138</v>
@@ -34226,7 +34220,7 @@
         <v>110</v>
       </c>
       <c r="J513" s="29" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K513" s="29"/>
       <c r="L513" s="31"/>
@@ -34243,7 +34237,7 @@
         <v>162</v>
       </c>
       <c r="D514" s="29" t="s">
-        <v>2548</v>
+        <v>2533</v>
       </c>
       <c r="E514" s="29" t="s">
         <v>138</v>
@@ -34261,7 +34255,7 @@
         <v>110</v>
       </c>
       <c r="J514" s="29" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K514" s="29"/>
       <c r="L514" s="31"/>
@@ -34296,7 +34290,7 @@
         <v>110</v>
       </c>
       <c r="J515" s="29" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K515" s="29"/>
       <c r="L515" s="31"/>
@@ -34331,7 +34325,7 @@
         <v>110</v>
       </c>
       <c r="J516" s="29" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K516" s="29"/>
       <c r="L516" s="31"/>
@@ -34366,7 +34360,7 @@
         <v>110</v>
       </c>
       <c r="J517" s="29" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K517" s="29"/>
       <c r="L517" s="31"/>
@@ -34456,7 +34450,7 @@
         <v>1043</v>
       </c>
       <c r="E520" s="29" t="s">
-        <v>2614</v>
+        <v>2599</v>
       </c>
       <c r="F520" s="31" t="s">
         <v>1764</v>
@@ -34493,7 +34487,7 @@
         <v>1043</v>
       </c>
       <c r="E521" s="29" t="s">
-        <v>2615</v>
+        <v>2600</v>
       </c>
       <c r="F521" s="31" t="s">
         <v>1764</v>
@@ -34530,7 +34524,7 @@
         <v>1043</v>
       </c>
       <c r="E522" s="29" t="s">
-        <v>2616</v>
+        <v>2601</v>
       </c>
       <c r="F522" s="31" t="s">
         <v>1764</v>
@@ -34567,7 +34561,7 @@
         <v>1043</v>
       </c>
       <c r="E523" s="29" t="s">
-        <v>2617</v>
+        <v>2602</v>
       </c>
       <c r="F523" s="31" t="s">
         <v>1764</v>
@@ -34604,7 +34598,7 @@
         <v>1043</v>
       </c>
       <c r="E524" s="29" t="s">
-        <v>2618</v>
+        <v>2603</v>
       </c>
       <c r="F524" s="31" t="s">
         <v>1764</v>
@@ -34641,7 +34635,7 @@
         <v>1043</v>
       </c>
       <c r="E525" s="29" t="s">
-        <v>2619</v>
+        <v>2604</v>
       </c>
       <c r="F525" s="31" t="s">
         <v>1764</v>
@@ -34678,7 +34672,7 @@
         <v>1043</v>
       </c>
       <c r="E526" s="29" t="s">
-        <v>2620</v>
+        <v>2605</v>
       </c>
       <c r="F526" s="31" t="s">
         <v>1764</v>
@@ -34715,7 +34709,7 @@
         <v>1043</v>
       </c>
       <c r="E527" s="29" t="s">
-        <v>2621</v>
+        <v>2606</v>
       </c>
       <c r="F527" s="31" t="s">
         <v>1764</v>
@@ -34752,7 +34746,7 @@
         <v>1043</v>
       </c>
       <c r="E528" s="29" t="s">
-        <v>2622</v>
+        <v>2607</v>
       </c>
       <c r="F528" s="31" t="s">
         <v>1764</v>
@@ -34789,7 +34783,7 @@
         <v>1043</v>
       </c>
       <c r="E529" s="29" t="s">
-        <v>2623</v>
+        <v>2608</v>
       </c>
       <c r="F529" s="89" t="s">
         <v>1764</v>
@@ -34826,7 +34820,7 @@
         <v>1043</v>
       </c>
       <c r="E530" s="29" t="s">
-        <v>2624</v>
+        <v>2609</v>
       </c>
       <c r="F530" s="89" t="s">
         <v>1764</v>
@@ -34863,7 +34857,7 @@
         <v>1043</v>
       </c>
       <c r="E531" s="29" t="s">
-        <v>2625</v>
+        <v>2610</v>
       </c>
       <c r="F531" s="89" t="s">
         <v>1764</v>
@@ -34900,7 +34894,7 @@
         <v>1043</v>
       </c>
       <c r="E532" s="29" t="s">
-        <v>2626</v>
+        <v>2611</v>
       </c>
       <c r="F532" s="89" t="s">
         <v>1764</v>
@@ -35032,7 +35026,7 @@
         <v>1765</v>
       </c>
       <c r="G536" s="23" t="s">
-        <v>2202</v>
+        <v>2187</v>
       </c>
       <c r="H536" s="31" t="s">
         <v>209</v>
@@ -35753,7 +35747,7 @@
         <v>1712</v>
       </c>
       <c r="C561" s="73" t="s">
-        <v>2613</v>
+        <v>2598</v>
       </c>
       <c r="D561" s="73" t="s">
         <v>1257</v>
@@ -35817,7 +35811,7 @@
         <v>1860</v>
       </c>
       <c r="E563" s="73" t="s">
-        <v>1919</v>
+        <v>2657</v>
       </c>
       <c r="F563" s="31" t="s">
         <v>247</v>
@@ -35850,7 +35844,7 @@
         <v>1860</v>
       </c>
       <c r="E564" s="73" t="s">
-        <v>1920</v>
+        <v>2386</v>
       </c>
       <c r="F564" s="31" t="s">
         <v>247</v>
@@ -35883,7 +35877,7 @@
         <v>1860</v>
       </c>
       <c r="E565" s="73" t="s">
-        <v>1921</v>
+        <v>2658</v>
       </c>
       <c r="F565" s="31" t="s">
         <v>247</v>
@@ -35916,7 +35910,7 @@
         <v>1860</v>
       </c>
       <c r="E566" s="73" t="s">
-        <v>1922</v>
+        <v>2659</v>
       </c>
       <c r="F566" s="31" t="s">
         <v>247</v>
@@ -35949,7 +35943,7 @@
         <v>1860</v>
       </c>
       <c r="E567" s="73" t="s">
-        <v>1923</v>
+        <v>2629</v>
       </c>
       <c r="F567" s="31" t="s">
         <v>247</v>
@@ -35982,7 +35976,7 @@
         <v>1860</v>
       </c>
       <c r="E568" s="73" t="s">
-        <v>1934</v>
+        <v>2660</v>
       </c>
       <c r="F568" s="31" t="s">
         <v>247</v>
@@ -36015,7 +36009,7 @@
         <v>1860</v>
       </c>
       <c r="E569" s="73" t="s">
-        <v>1935</v>
+        <v>2192</v>
       </c>
       <c r="F569" s="31" t="s">
         <v>247</v>
@@ -36048,7 +36042,7 @@
         <v>1860</v>
       </c>
       <c r="E570" s="73" t="s">
-        <v>1936</v>
+        <v>2317</v>
       </c>
       <c r="F570" s="31" t="s">
         <v>247</v>
@@ -36081,7 +36075,7 @@
         <v>1860</v>
       </c>
       <c r="E571" s="73" t="s">
-        <v>1937</v>
+        <v>2194</v>
       </c>
       <c r="F571" s="31" t="s">
         <v>247</v>
@@ -36114,7 +36108,7 @@
         <v>1860</v>
       </c>
       <c r="E572" s="73" t="s">
-        <v>1938</v>
+        <v>2193</v>
       </c>
       <c r="F572" s="31" t="s">
         <v>247</v>
@@ -36147,7 +36141,7 @@
         <v>1860</v>
       </c>
       <c r="E573" s="73" t="s">
-        <v>1939</v>
+        <v>2661</v>
       </c>
       <c r="F573" s="31" t="s">
         <v>247</v>
@@ -37095,7 +37089,7 @@
         <v>1043</v>
       </c>
       <c r="E603" s="81" t="s">
-        <v>2379</v>
+        <v>2364</v>
       </c>
       <c r="F603" s="31" t="s">
         <v>1405</v>
@@ -37126,7 +37120,7 @@
         <v>1043</v>
       </c>
       <c r="E604" s="81" t="s">
-        <v>2380</v>
+        <v>2365</v>
       </c>
       <c r="F604" s="31" t="s">
         <v>1405</v>
@@ -37219,7 +37213,7 @@
         <v>1043</v>
       </c>
       <c r="E607" s="81" t="s">
-        <v>2381</v>
+        <v>2366</v>
       </c>
       <c r="F607" s="31" t="s">
         <v>1405</v>
@@ -37250,7 +37244,7 @@
         <v>1043</v>
       </c>
       <c r="E608" s="81" t="s">
-        <v>2382</v>
+        <v>2367</v>
       </c>
       <c r="F608" s="31" t="s">
         <v>1405</v>
@@ -37281,7 +37275,7 @@
         <v>1043</v>
       </c>
       <c r="E609" s="81" t="s">
-        <v>2383</v>
+        <v>2368</v>
       </c>
       <c r="F609" s="31" t="s">
         <v>1405</v>
@@ -37312,7 +37306,7 @@
         <v>1043</v>
       </c>
       <c r="E610" s="81" t="s">
-        <v>2384</v>
+        <v>2369</v>
       </c>
       <c r="F610" s="31" t="s">
         <v>1405</v>
@@ -37343,7 +37337,7 @@
         <v>1043</v>
       </c>
       <c r="E611" s="81" t="s">
-        <v>2385</v>
+        <v>2370</v>
       </c>
       <c r="F611" s="31" t="s">
         <v>1405</v>
@@ -37374,7 +37368,7 @@
         <v>1043</v>
       </c>
       <c r="E612" s="81" t="s">
-        <v>2386</v>
+        <v>2371</v>
       </c>
       <c r="F612" s="31" t="s">
         <v>1405</v>
@@ -37405,7 +37399,7 @@
         <v>1043</v>
       </c>
       <c r="E613" s="81" t="s">
-        <v>2387</v>
+        <v>2372</v>
       </c>
       <c r="F613" s="31" t="s">
         <v>1405</v>
@@ -37438,7 +37432,7 @@
         <v>1043</v>
       </c>
       <c r="E614" s="81" t="s">
-        <v>2388</v>
+        <v>2373</v>
       </c>
       <c r="F614" s="31" t="s">
         <v>1405</v>
@@ -37471,7 +37465,7 @@
         <v>1043</v>
       </c>
       <c r="E615" s="82" t="s">
-        <v>2389</v>
+        <v>2374</v>
       </c>
       <c r="F615" s="31" t="s">
         <v>1405</v>
@@ -37502,7 +37496,7 @@
         <v>1043</v>
       </c>
       <c r="E616" s="82" t="s">
-        <v>2390</v>
+        <v>2375</v>
       </c>
       <c r="F616" s="31" t="s">
         <v>1405</v>
@@ -37533,7 +37527,7 @@
         <v>1043</v>
       </c>
       <c r="E617" s="82" t="s">
-        <v>2391</v>
+        <v>2376</v>
       </c>
       <c r="F617" s="31" t="s">
         <v>1405</v>
@@ -37564,7 +37558,7 @@
         <v>1043</v>
       </c>
       <c r="E618" s="82" t="s">
-        <v>2392</v>
+        <v>2377</v>
       </c>
       <c r="F618" s="31" t="s">
         <v>1405</v>
@@ -37597,7 +37591,7 @@
         <v>1043</v>
       </c>
       <c r="E619" s="82" t="s">
-        <v>2393</v>
+        <v>2378</v>
       </c>
       <c r="F619" s="31" t="s">
         <v>1405</v>
@@ -37630,7 +37624,7 @@
         <v>1043</v>
       </c>
       <c r="E620" s="82" t="s">
-        <v>2394</v>
+        <v>2379</v>
       </c>
       <c r="F620" s="31" t="s">
         <v>1405</v>
@@ -37661,7 +37655,7 @@
         <v>1043</v>
       </c>
       <c r="E621" s="82" t="s">
-        <v>2395</v>
+        <v>2380</v>
       </c>
       <c r="F621" s="31" t="s">
         <v>1405</v>
@@ -37692,7 +37686,7 @@
         <v>1043</v>
       </c>
       <c r="E622" s="82" t="s">
-        <v>2396</v>
+        <v>2381</v>
       </c>
       <c r="F622" s="31" t="s">
         <v>1405</v>
@@ -37837,7 +37831,7 @@
         <v>1249</v>
       </c>
       <c r="C627" s="83" t="s">
-        <v>2157</v>
+        <v>2142</v>
       </c>
       <c r="D627" s="85" t="s">
         <v>1460</v>
@@ -37872,7 +37866,7 @@
         <v>1249</v>
       </c>
       <c r="C628" s="83" t="s">
-        <v>2158</v>
+        <v>2143</v>
       </c>
       <c r="D628" s="85" t="s">
         <v>1460</v>
@@ -37907,7 +37901,7 @@
         <v>1249</v>
       </c>
       <c r="C629" s="83" t="s">
-        <v>2159</v>
+        <v>2144</v>
       </c>
       <c r="D629" s="85" t="s">
         <v>1460</v>
@@ -37942,7 +37936,7 @@
         <v>1249</v>
       </c>
       <c r="C630" s="83" t="s">
-        <v>2160</v>
+        <v>2145</v>
       </c>
       <c r="D630" s="85" t="s">
         <v>1460</v>
@@ -37977,7 +37971,7 @@
         <v>1249</v>
       </c>
       <c r="C631" s="83" t="s">
-        <v>2161</v>
+        <v>2146</v>
       </c>
       <c r="D631" s="85" t="s">
         <v>1460</v>
@@ -38088,7 +38082,7 @@
         <v>1497</v>
       </c>
       <c r="E634" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F634" s="23" t="s">
         <v>1764</v>
@@ -38123,7 +38117,7 @@
         <v>1497</v>
       </c>
       <c r="E635" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F635" s="23" t="s">
         <v>1764</v>
@@ -38158,7 +38152,7 @@
         <v>1497</v>
       </c>
       <c r="E636" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F636" s="23" t="s">
         <v>1764</v>
@@ -38193,7 +38187,7 @@
         <v>1496</v>
       </c>
       <c r="E637" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F637" s="23" t="s">
         <v>1764</v>
@@ -38228,7 +38222,7 @@
         <v>1496</v>
       </c>
       <c r="E638" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F638" s="23" t="s">
         <v>1764</v>
@@ -38263,7 +38257,7 @@
         <v>1496</v>
       </c>
       <c r="E639" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F639" s="23" t="s">
         <v>1764</v>
@@ -38298,7 +38292,7 @@
         <v>1498</v>
       </c>
       <c r="E640" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F640" s="23" t="s">
         <v>1764</v>
@@ -38333,7 +38327,7 @@
         <v>1498</v>
       </c>
       <c r="E641" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F641" s="23" t="s">
         <v>1764</v>
@@ -38368,7 +38362,7 @@
         <v>1498</v>
       </c>
       <c r="E642" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F642" s="23" t="s">
         <v>1764</v>
@@ -38403,7 +38397,7 @@
         <v>1499</v>
       </c>
       <c r="E643" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F643" s="23" t="s">
         <v>1764</v>
@@ -38438,7 +38432,7 @@
         <v>1499</v>
       </c>
       <c r="E644" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F644" s="23" t="s">
         <v>1764</v>
@@ -38473,7 +38467,7 @@
         <v>1499</v>
       </c>
       <c r="E645" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F645" s="23" t="s">
         <v>1764</v>
@@ -38508,7 +38502,7 @@
         <v>1500</v>
       </c>
       <c r="E646" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F646" s="23" t="s">
         <v>1764</v>
@@ -38543,7 +38537,7 @@
         <v>1500</v>
       </c>
       <c r="E647" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F647" s="23" t="s">
         <v>1764</v>
@@ -38578,7 +38572,7 @@
         <v>1500</v>
       </c>
       <c r="E648" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F648" s="23" t="s">
         <v>1764</v>
@@ -38613,7 +38607,7 @@
         <v>1501</v>
       </c>
       <c r="E649" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F649" s="23" t="s">
         <v>1764</v>
@@ -38648,7 +38642,7 @@
         <v>1501</v>
       </c>
       <c r="E650" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F650" s="23" t="s">
         <v>1764</v>
@@ -38683,7 +38677,7 @@
         <v>1501</v>
       </c>
       <c r="E651" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F651" s="23" t="s">
         <v>1764</v>
@@ -38718,7 +38712,7 @@
         <v>1502</v>
       </c>
       <c r="E652" s="84" t="s">
-        <v>2610</v>
+        <v>2595</v>
       </c>
       <c r="F652" s="23" t="s">
         <v>1764</v>
@@ -38753,7 +38747,7 @@
         <v>1502</v>
       </c>
       <c r="E653" s="84" t="s">
-        <v>2611</v>
+        <v>2596</v>
       </c>
       <c r="F653" s="23" t="s">
         <v>1764</v>
@@ -38788,7 +38782,7 @@
         <v>1502</v>
       </c>
       <c r="E654" s="84" t="s">
-        <v>2612</v>
+        <v>2597</v>
       </c>
       <c r="F654" s="23" t="s">
         <v>1764</v>
@@ -38944,7 +38938,7 @@
     </row>
     <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="29" t="s">
-        <v>2402</v>
+        <v>2387</v>
       </c>
       <c r="B660" s="83" t="s">
         <v>66</v>
@@ -38979,7 +38973,7 @@
     </row>
     <row r="661" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="29" t="s">
-        <v>2403</v>
+        <v>2388</v>
       </c>
       <c r="B661" s="83" t="s">
         <v>66</v>
@@ -39014,7 +39008,7 @@
     </row>
     <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="29" t="s">
-        <v>2404</v>
+        <v>2389</v>
       </c>
       <c r="B662" s="85" t="s">
         <v>246</v>
@@ -39045,7 +39039,7 @@
     </row>
     <row r="663" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A663" s="29" t="s">
-        <v>2405</v>
+        <v>2390</v>
       </c>
       <c r="B663" s="85" t="s">
         <v>246</v>
@@ -39076,19 +39070,19 @@
     </row>
     <row r="664" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A664" s="29" t="s">
-        <v>2406</v>
+        <v>2391</v>
       </c>
       <c r="B664" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C664" s="73" t="s">
-        <v>2162</v>
+        <v>2147</v>
       </c>
       <c r="D664" s="79" t="s">
         <v>1771</v>
       </c>
       <c r="E664" s="73" t="s">
-        <v>2036</v>
+        <v>2021</v>
       </c>
       <c r="F664" s="23" t="s">
         <v>1764</v>
@@ -39107,19 +39101,19 @@
     </row>
     <row r="665" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A665" s="29" t="s">
-        <v>2407</v>
+        <v>2392</v>
       </c>
       <c r="B665" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C665" s="73" t="s">
-        <v>2163</v>
+        <v>2148</v>
       </c>
       <c r="D665" s="79" t="s">
         <v>1771</v>
       </c>
       <c r="E665" s="73" t="s">
-        <v>2037</v>
+        <v>2022</v>
       </c>
       <c r="F665" s="23" t="s">
         <v>1764</v>
@@ -39138,19 +39132,19 @@
     </row>
     <row r="666" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A666" s="29" t="s">
-        <v>2408</v>
+        <v>2393</v>
       </c>
       <c r="B666" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C666" s="82" t="s">
-        <v>2106</v>
+        <v>2091</v>
       </c>
       <c r="D666" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E666" s="82" t="s">
-        <v>2180</v>
+        <v>2165</v>
       </c>
       <c r="F666" s="23" t="s">
         <v>1764</v>
@@ -39169,19 +39163,19 @@
     </row>
     <row r="667" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A667" s="29" t="s">
-        <v>2409</v>
+        <v>2394</v>
       </c>
       <c r="B667" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C667" s="83" t="s">
-        <v>2107</v>
+        <v>2092</v>
       </c>
       <c r="D667" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E667" s="83" t="s">
-        <v>2181</v>
+        <v>2166</v>
       </c>
       <c r="F667" s="23" t="s">
         <v>1764</v>
@@ -39200,19 +39194,19 @@
     </row>
     <row r="668" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A668" s="29" t="s">
-        <v>2410</v>
+        <v>2395</v>
       </c>
       <c r="B668" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C668" s="83" t="s">
-        <v>2101</v>
+        <v>2086</v>
       </c>
       <c r="D668" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E668" s="83" t="s">
-        <v>2182</v>
+        <v>2167</v>
       </c>
       <c r="F668" s="23" t="s">
         <v>1764</v>
@@ -39231,19 +39225,19 @@
     </row>
     <row r="669" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A669" s="29" t="s">
-        <v>2411</v>
+        <v>2396</v>
       </c>
       <c r="B669" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C669" s="83" t="s">
-        <v>2109</v>
+        <v>2094</v>
       </c>
       <c r="D669" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E669" s="83" t="s">
-        <v>2183</v>
+        <v>2168</v>
       </c>
       <c r="F669" s="23" t="s">
         <v>1764</v>
@@ -39262,19 +39256,19 @@
     </row>
     <row r="670" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A670" s="29" t="s">
-        <v>2412</v>
+        <v>2397</v>
       </c>
       <c r="B670" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C670" s="83" t="s">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="D670" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E670" s="83" t="s">
-        <v>2184</v>
+        <v>2169</v>
       </c>
       <c r="F670" s="23" t="s">
         <v>1764</v>
@@ -39293,19 +39287,19 @@
     </row>
     <row r="671" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A671" s="29" t="s">
-        <v>2413</v>
+        <v>2398</v>
       </c>
       <c r="B671" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C671" s="83" t="s">
-        <v>2111</v>
+        <v>2096</v>
       </c>
       <c r="D671" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E671" s="83" t="s">
-        <v>2185</v>
+        <v>2170</v>
       </c>
       <c r="F671" s="23" t="s">
         <v>1764</v>
@@ -39324,19 +39318,19 @@
     </row>
     <row r="672" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A672" s="29" t="s">
-        <v>2414</v>
+        <v>2399</v>
       </c>
       <c r="B672" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C672" s="83" t="s">
-        <v>2112</v>
+        <v>2097</v>
       </c>
       <c r="D672" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E672" s="83" t="s">
-        <v>2186</v>
+        <v>2171</v>
       </c>
       <c r="F672" s="23" t="s">
         <v>1764</v>
@@ -39355,19 +39349,19 @@
     </row>
     <row r="673" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A673" s="29" t="s">
-        <v>2415</v>
+        <v>2400</v>
       </c>
       <c r="B673" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C673" s="98" t="s">
-        <v>2113</v>
+        <v>2098</v>
       </c>
       <c r="D673" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E673" s="98" t="s">
-        <v>2187</v>
+        <v>2172</v>
       </c>
       <c r="F673" s="23" t="s">
         <v>1764</v>
@@ -39386,19 +39380,19 @@
     </row>
     <row r="674" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A674" s="29" t="s">
-        <v>2416</v>
+        <v>2401</v>
       </c>
       <c r="B674" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C674" s="82" t="s">
-        <v>2114</v>
+        <v>2099</v>
       </c>
       <c r="D674" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E674" s="82" t="s">
-        <v>2188</v>
+        <v>2173</v>
       </c>
       <c r="F674" s="23" t="s">
         <v>1764</v>
@@ -39417,19 +39411,19 @@
     </row>
     <row r="675" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A675" s="29" t="s">
-        <v>2417</v>
+        <v>2402</v>
       </c>
       <c r="B675" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C675" s="83" t="s">
-        <v>2164</v>
+        <v>2149</v>
       </c>
       <c r="D675" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E675" s="83" t="s">
-        <v>2189</v>
+        <v>2174</v>
       </c>
       <c r="F675" s="23" t="s">
         <v>1764</v>
@@ -39448,19 +39442,19 @@
     </row>
     <row r="676" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A676" s="29" t="s">
-        <v>2418</v>
+        <v>2403</v>
       </c>
       <c r="B676" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C676" s="83" t="s">
-        <v>2116</v>
+        <v>2101</v>
       </c>
       <c r="D676" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E676" s="83" t="s">
-        <v>2190</v>
+        <v>2175</v>
       </c>
       <c r="F676" s="23" t="s">
         <v>1764</v>
@@ -39479,19 +39473,19 @@
     </row>
     <row r="677" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A677" s="29" t="s">
-        <v>2419</v>
+        <v>2404</v>
       </c>
       <c r="B677" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C677" s="98" t="s">
-        <v>2117</v>
+        <v>2102</v>
       </c>
       <c r="D677" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E677" s="98" t="s">
-        <v>2191</v>
+        <v>2176</v>
       </c>
       <c r="F677" s="23" t="s">
         <v>1764</v>
@@ -39510,19 +39504,19 @@
     </row>
     <row r="678" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A678" s="29" t="s">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="B678" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C678" s="82" t="s">
-        <v>2118</v>
+        <v>2103</v>
       </c>
       <c r="D678" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E678" s="82" t="s">
-        <v>2192</v>
+        <v>2177</v>
       </c>
       <c r="F678" s="23" t="s">
         <v>1764</v>
@@ -39541,19 +39535,19 @@
     </row>
     <row r="679" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A679" s="29" t="s">
-        <v>2421</v>
+        <v>2406</v>
       </c>
       <c r="B679" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C679" s="98" t="s">
-        <v>2119</v>
+        <v>2104</v>
       </c>
       <c r="D679" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E679" s="98" t="s">
-        <v>2193</v>
+        <v>2178</v>
       </c>
       <c r="F679" s="23" t="s">
         <v>1764</v>
@@ -39572,19 +39566,19 @@
     </row>
     <row r="680" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A680" s="29" t="s">
-        <v>2422</v>
+        <v>2407</v>
       </c>
       <c r="B680" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C680" s="73" t="s">
-        <v>2120</v>
+        <v>2105</v>
       </c>
       <c r="D680" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E680" s="73" t="s">
-        <v>2194</v>
+        <v>2179</v>
       </c>
       <c r="F680" s="23" t="s">
         <v>1764</v>
@@ -39603,19 +39597,19 @@
     </row>
     <row r="681" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A681" s="29" t="s">
-        <v>2423</v>
+        <v>2408</v>
       </c>
       <c r="B681" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C681" s="73" t="s">
-        <v>2121</v>
+        <v>2106</v>
       </c>
       <c r="D681" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E681" s="73" t="s">
-        <v>2195</v>
+        <v>2180</v>
       </c>
       <c r="F681" s="23" t="s">
         <v>1764</v>
@@ -39634,19 +39628,19 @@
     </row>
     <row r="682" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A682" s="29" t="s">
-        <v>2424</v>
+        <v>2409</v>
       </c>
       <c r="B682" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C682" s="73" t="s">
-        <v>2162</v>
+        <v>2147</v>
       </c>
       <c r="D682" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E682" s="73" t="s">
-        <v>2196</v>
+        <v>2181</v>
       </c>
       <c r="F682" s="23" t="s">
         <v>1764</v>
@@ -39665,19 +39659,19 @@
     </row>
     <row r="683" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A683" s="29" t="s">
-        <v>2425</v>
+        <v>2410</v>
       </c>
       <c r="B683" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C683" s="73" t="s">
-        <v>2163</v>
+        <v>2148</v>
       </c>
       <c r="D683" s="79" t="s">
         <v>1747</v>
       </c>
       <c r="E683" s="73" t="s">
-        <v>2197</v>
+        <v>2182</v>
       </c>
       <c r="F683" s="23" t="s">
         <v>1764</v>
@@ -39696,19 +39690,19 @@
     </row>
     <row r="684" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A684" s="29" t="s">
-        <v>2426</v>
+        <v>2411</v>
       </c>
       <c r="B684" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C684" s="82" t="s">
-        <v>2165</v>
+        <v>2150</v>
       </c>
       <c r="D684" s="79" t="s">
         <v>1521</v>
       </c>
       <c r="E684" s="82" t="s">
-        <v>2175</v>
+        <v>2160</v>
       </c>
       <c r="F684" s="23" t="s">
         <v>1764</v>
@@ -39731,19 +39725,19 @@
     </row>
     <row r="685" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A685" s="29" t="s">
-        <v>2427</v>
+        <v>2412</v>
       </c>
       <c r="B685" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C685" s="82" t="s">
-        <v>2166</v>
+        <v>2151</v>
       </c>
       <c r="D685" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E685" s="83" t="s">
-        <v>2176</v>
+        <v>2161</v>
       </c>
       <c r="F685" s="23" t="s">
         <v>1764</v>
@@ -39766,19 +39760,19 @@
     </row>
     <row r="686" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A686" s="29" t="s">
-        <v>2428</v>
+        <v>2413</v>
       </c>
       <c r="B686" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C686" s="82" t="s">
-        <v>2167</v>
+        <v>2152</v>
       </c>
       <c r="D686" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E686" s="83" t="s">
-        <v>2177</v>
+        <v>2162</v>
       </c>
       <c r="F686" s="23" t="s">
         <v>1764</v>
@@ -39801,19 +39795,19 @@
     </row>
     <row r="687" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A687" s="29" t="s">
-        <v>2429</v>
+        <v>2414</v>
       </c>
       <c r="B687" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C687" s="82" t="s">
-        <v>2168</v>
+        <v>2153</v>
       </c>
       <c r="D687" s="85" t="s">
         <v>1521</v>
       </c>
       <c r="E687" s="83" t="s">
-        <v>2178</v>
+        <v>2163</v>
       </c>
       <c r="F687" s="23" t="s">
         <v>1764</v>
@@ -39836,19 +39830,19 @@
     </row>
     <row r="688" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A688" s="29" t="s">
-        <v>2430</v>
+        <v>2415</v>
       </c>
       <c r="B688" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C688" s="82" t="s">
-        <v>2169</v>
+        <v>2154</v>
       </c>
       <c r="D688" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E688" s="83" t="s">
-        <v>2175</v>
+        <v>2160</v>
       </c>
       <c r="F688" s="23" t="s">
         <v>1764</v>
@@ -39871,19 +39865,19 @@
     </row>
     <row r="689" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A689" s="29" t="s">
-        <v>2431</v>
+        <v>2416</v>
       </c>
       <c r="B689" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C689" s="82" t="s">
-        <v>2170</v>
+        <v>2155</v>
       </c>
       <c r="D689" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E689" s="83" t="s">
-        <v>2176</v>
+        <v>2161</v>
       </c>
       <c r="F689" s="23" t="s">
         <v>1764</v>
@@ -39906,19 +39900,19 @@
     </row>
     <row r="690" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A690" s="29" t="s">
-        <v>2432</v>
+        <v>2417</v>
       </c>
       <c r="B690" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C690" s="82" t="s">
-        <v>2171</v>
+        <v>2156</v>
       </c>
       <c r="D690" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E690" s="83" t="s">
-        <v>2177</v>
+        <v>2162</v>
       </c>
       <c r="F690" s="23" t="s">
         <v>1764</v>
@@ -39941,19 +39935,19 @@
     </row>
     <row r="691" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A691" s="29" t="s">
-        <v>2433</v>
+        <v>2418</v>
       </c>
       <c r="B691" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C691" s="82" t="s">
-        <v>2172</v>
+        <v>2157</v>
       </c>
       <c r="D691" s="85" t="s">
         <v>1522</v>
       </c>
       <c r="E691" s="83" t="s">
-        <v>2178</v>
+        <v>2163</v>
       </c>
       <c r="F691" s="23" t="s">
         <v>1764</v>
@@ -39976,19 +39970,19 @@
     </row>
     <row r="692" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A692" s="29" t="s">
-        <v>2434</v>
+        <v>2419</v>
       </c>
       <c r="B692" s="82" t="s">
         <v>1249</v>
       </c>
       <c r="C692" s="73" t="s">
-        <v>2173</v>
+        <v>2158</v>
       </c>
       <c r="D692" s="84" t="s">
         <v>1767</v>
       </c>
       <c r="E692" s="73" t="s">
-        <v>2179</v>
+        <v>2164</v>
       </c>
       <c r="F692" s="22" t="s">
         <v>1764</v>
@@ -40011,13 +40005,13 @@
     </row>
     <row r="693" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A693" s="29" t="s">
-        <v>2435</v>
+        <v>2420</v>
       </c>
       <c r="B693" s="80" t="s">
         <v>1249</v>
       </c>
       <c r="C693" s="73" t="s">
-        <v>2174</v>
+        <v>2159</v>
       </c>
       <c r="D693" s="84" t="s">
         <v>1747</v>
@@ -40742,7 +40736,7 @@
     </row>
     <row r="718" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A718" s="29" t="s">
-        <v>2436</v>
+        <v>2421</v>
       </c>
       <c r="B718" s="82" t="s">
         <v>769</v>
@@ -40754,7 +40748,7 @@
         <v>1249</v>
       </c>
       <c r="E718" s="81" t="s">
-        <v>1970</v>
+        <v>1955</v>
       </c>
       <c r="F718" s="23" t="s">
         <v>1764</v>
@@ -40775,7 +40769,7 @@
     </row>
     <row r="719" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2437</v>
+        <v>2422</v>
       </c>
       <c r="B719" s="82" t="s">
         <v>769</v>
@@ -40787,7 +40781,7 @@
         <v>1249</v>
       </c>
       <c r="E719" s="86" t="s">
-        <v>1971</v>
+        <v>1956</v>
       </c>
       <c r="F719" s="23" t="s">
         <v>1764</v>
@@ -40808,7 +40802,7 @@
     </row>
     <row r="720" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A720" s="29" t="s">
-        <v>2438</v>
+        <v>2423</v>
       </c>
       <c r="B720" s="82" t="s">
         <v>769</v>
@@ -40820,7 +40814,7 @@
         <v>1249</v>
       </c>
       <c r="E720" s="86" t="s">
-        <v>1972</v>
+        <v>1957</v>
       </c>
       <c r="F720" s="23" t="s">
         <v>1764</v>
@@ -40841,7 +40835,7 @@
     </row>
     <row r="721" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2439</v>
+        <v>2424</v>
       </c>
       <c r="B721" s="82" t="s">
         <v>769</v>
@@ -40853,7 +40847,7 @@
         <v>1249</v>
       </c>
       <c r="E721" s="86" t="s">
-        <v>1973</v>
+        <v>1958</v>
       </c>
       <c r="F721" s="23" t="s">
         <v>1764</v>
@@ -40874,7 +40868,7 @@
     </row>
     <row r="722" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A722" s="29" t="s">
-        <v>2440</v>
+        <v>2425</v>
       </c>
       <c r="B722" s="82" t="s">
         <v>769</v>
@@ -40886,7 +40880,7 @@
         <v>1249</v>
       </c>
       <c r="E722" s="86" t="s">
-        <v>1974</v>
+        <v>1959</v>
       </c>
       <c r="F722" s="23" t="s">
         <v>1764</v>
@@ -40907,7 +40901,7 @@
     </row>
     <row r="723" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A723" s="29" t="s">
-        <v>2441</v>
+        <v>2426</v>
       </c>
       <c r="B723" s="82" t="s">
         <v>769</v>
@@ -40919,7 +40913,7 @@
         <v>1249</v>
       </c>
       <c r="E723" s="86" t="s">
-        <v>1975</v>
+        <v>1960</v>
       </c>
       <c r="F723" s="23" t="s">
         <v>1764</v>
@@ -40940,7 +40934,7 @@
     </row>
     <row r="724" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A724" s="29" t="s">
-        <v>2442</v>
+        <v>2427</v>
       </c>
       <c r="B724" s="82" t="s">
         <v>769</v>
@@ -40952,7 +40946,7 @@
         <v>1249</v>
       </c>
       <c r="E724" s="86" t="s">
-        <v>1976</v>
+        <v>1961</v>
       </c>
       <c r="F724" s="23" t="s">
         <v>1764</v>
@@ -40973,7 +40967,7 @@
     </row>
     <row r="725" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A725" s="29" t="s">
-        <v>2443</v>
+        <v>2428</v>
       </c>
       <c r="B725" s="82" t="s">
         <v>769</v>
@@ -40985,7 +40979,7 @@
         <v>1249</v>
       </c>
       <c r="E725" s="86" t="s">
-        <v>1977</v>
+        <v>1962</v>
       </c>
       <c r="F725" s="23" t="s">
         <v>1764</v>
@@ -41006,7 +41000,7 @@
     </row>
     <row r="726" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A726" s="29" t="s">
-        <v>2444</v>
+        <v>2429</v>
       </c>
       <c r="B726" s="82" t="s">
         <v>769</v>
@@ -41018,7 +41012,7 @@
         <v>1249</v>
       </c>
       <c r="E726" s="86" t="s">
-        <v>1978</v>
+        <v>1963</v>
       </c>
       <c r="F726" s="23" t="s">
         <v>1764</v>
@@ -41039,7 +41033,7 @@
     </row>
     <row r="727" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A727" s="29" t="s">
-        <v>2445</v>
+        <v>2430</v>
       </c>
       <c r="B727" s="82" t="s">
         <v>769</v>
@@ -41051,7 +41045,7 @@
         <v>1249</v>
       </c>
       <c r="E727" s="86" t="s">
-        <v>1979</v>
+        <v>1964</v>
       </c>
       <c r="F727" s="23" t="s">
         <v>1764</v>
@@ -41072,7 +41066,7 @@
     </row>
     <row r="728" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A728" s="29" t="s">
-        <v>2446</v>
+        <v>2431</v>
       </c>
       <c r="B728" s="82" t="s">
         <v>769</v>
@@ -41084,7 +41078,7 @@
         <v>1249</v>
       </c>
       <c r="E728" s="86" t="s">
-        <v>1980</v>
+        <v>1965</v>
       </c>
       <c r="F728" s="23" t="s">
         <v>1764</v>
@@ -41105,7 +41099,7 @@
     </row>
     <row r="729" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A729" s="29" t="s">
-        <v>2447</v>
+        <v>2432</v>
       </c>
       <c r="B729" s="82" t="s">
         <v>769</v>
@@ -41117,7 +41111,7 @@
         <v>1249</v>
       </c>
       <c r="E729" s="86" t="s">
-        <v>1981</v>
+        <v>1966</v>
       </c>
       <c r="F729" s="23" t="s">
         <v>1764</v>
@@ -41138,7 +41132,7 @@
     </row>
     <row r="730" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A730" s="29" t="s">
-        <v>2448</v>
+        <v>2433</v>
       </c>
       <c r="B730" s="82" t="s">
         <v>769</v>
@@ -41150,7 +41144,7 @@
         <v>1249</v>
       </c>
       <c r="E730" s="86" t="s">
-        <v>1982</v>
+        <v>1967</v>
       </c>
       <c r="F730" s="23" t="s">
         <v>1764</v>
@@ -41171,7 +41165,7 @@
     </row>
     <row r="731" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A731" s="29" t="s">
-        <v>2449</v>
+        <v>2434</v>
       </c>
       <c r="B731" s="82" t="s">
         <v>769</v>
@@ -41183,7 +41177,7 @@
         <v>1249</v>
       </c>
       <c r="E731" s="86" t="s">
-        <v>1983</v>
+        <v>1968</v>
       </c>
       <c r="F731" s="23" t="s">
         <v>1764</v>
@@ -41204,7 +41198,7 @@
     </row>
     <row r="732" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A732" s="29" t="s">
-        <v>2450</v>
+        <v>2435</v>
       </c>
       <c r="B732" s="82" t="s">
         <v>769</v>
@@ -41216,7 +41210,7 @@
         <v>1249</v>
       </c>
       <c r="E732" s="86" t="s">
-        <v>1984</v>
+        <v>1969</v>
       </c>
       <c r="F732" s="23" t="s">
         <v>1764</v>
@@ -41237,7 +41231,7 @@
     </row>
     <row r="733" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A733" s="29" t="s">
-        <v>2451</v>
+        <v>2436</v>
       </c>
       <c r="B733" s="82" t="s">
         <v>769</v>
@@ -41249,7 +41243,7 @@
         <v>1249</v>
       </c>
       <c r="E733" s="86" t="s">
-        <v>1985</v>
+        <v>1970</v>
       </c>
       <c r="F733" s="23" t="s">
         <v>1764</v>
@@ -41270,7 +41264,7 @@
     </row>
     <row r="734" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A734" s="29" t="s">
-        <v>2452</v>
+        <v>2437</v>
       </c>
       <c r="B734" s="82" t="s">
         <v>769</v>
@@ -41282,7 +41276,7 @@
         <v>1249</v>
       </c>
       <c r="E734" s="86" t="s">
-        <v>1986</v>
+        <v>1971</v>
       </c>
       <c r="F734" s="23" t="s">
         <v>1764</v>
@@ -41303,7 +41297,7 @@
     </row>
     <row r="735" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A735" s="29" t="s">
-        <v>2453</v>
+        <v>2438</v>
       </c>
       <c r="B735" s="82" t="s">
         <v>769</v>
@@ -41315,7 +41309,7 @@
         <v>1249</v>
       </c>
       <c r="E735" s="86" t="s">
-        <v>1987</v>
+        <v>1972</v>
       </c>
       <c r="F735" s="23" t="s">
         <v>1764</v>
@@ -41336,7 +41330,7 @@
     </row>
     <row r="736" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A736" s="29" t="s">
-        <v>2454</v>
+        <v>2439</v>
       </c>
       <c r="B736" s="82" t="s">
         <v>769</v>
@@ -41348,7 +41342,7 @@
         <v>1249</v>
       </c>
       <c r="E736" s="86" t="s">
-        <v>1988</v>
+        <v>1973</v>
       </c>
       <c r="F736" s="23" t="s">
         <v>1764</v>
@@ -41369,7 +41363,7 @@
     </row>
     <row r="737" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A737" s="29" t="s">
-        <v>2455</v>
+        <v>2440</v>
       </c>
       <c r="B737" s="82" t="s">
         <v>769</v>
@@ -41381,7 +41375,7 @@
         <v>1249</v>
       </c>
       <c r="E737" s="86" t="s">
-        <v>1989</v>
+        <v>1974</v>
       </c>
       <c r="F737" s="23" t="s">
         <v>1764</v>
@@ -41402,7 +41396,7 @@
     </row>
     <row r="738" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A738" s="29" t="s">
-        <v>2456</v>
+        <v>2441</v>
       </c>
       <c r="B738" s="82" t="s">
         <v>769</v>
@@ -41414,7 +41408,7 @@
         <v>1249</v>
       </c>
       <c r="E738" s="86" t="s">
-        <v>1990</v>
+        <v>1975</v>
       </c>
       <c r="F738" s="23" t="s">
         <v>1764</v>
@@ -41435,7 +41429,7 @@
     </row>
     <row r="739" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A739" s="29" t="s">
-        <v>2457</v>
+        <v>2442</v>
       </c>
       <c r="B739" s="82" t="s">
         <v>769</v>
@@ -41447,7 +41441,7 @@
         <v>1249</v>
       </c>
       <c r="E739" s="86" t="s">
-        <v>1991</v>
+        <v>1976</v>
       </c>
       <c r="F739" s="23" t="s">
         <v>1764</v>
@@ -41468,7 +41462,7 @@
     </row>
     <row r="740" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A740" s="29" t="s">
-        <v>2458</v>
+        <v>2443</v>
       </c>
       <c r="B740" s="82" t="s">
         <v>769</v>
@@ -41480,7 +41474,7 @@
         <v>1249</v>
       </c>
       <c r="E740" s="86" t="s">
-        <v>1992</v>
+        <v>1977</v>
       </c>
       <c r="F740" s="23" t="s">
         <v>1764</v>
@@ -41501,7 +41495,7 @@
     </row>
     <row r="741" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A741" s="29" t="s">
-        <v>2459</v>
+        <v>2444</v>
       </c>
       <c r="B741" s="82" t="s">
         <v>769</v>
@@ -41513,7 +41507,7 @@
         <v>1249</v>
       </c>
       <c r="E741" s="86" t="s">
-        <v>1993</v>
+        <v>1978</v>
       </c>
       <c r="F741" s="23" t="s">
         <v>1764</v>
@@ -41534,7 +41528,7 @@
     </row>
     <row r="742" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A742" s="29" t="s">
-        <v>2460</v>
+        <v>2445</v>
       </c>
       <c r="B742" s="82" t="s">
         <v>769</v>
@@ -41546,7 +41540,7 @@
         <v>1249</v>
       </c>
       <c r="E742" s="86" t="s">
-        <v>1994</v>
+        <v>1979</v>
       </c>
       <c r="F742" s="23" t="s">
         <v>1764</v>
@@ -41567,7 +41561,7 @@
     </row>
     <row r="743" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A743" s="29" t="s">
-        <v>2461</v>
+        <v>2446</v>
       </c>
       <c r="B743" s="82" t="s">
         <v>769</v>
@@ -41579,7 +41573,7 @@
         <v>1249</v>
       </c>
       <c r="E743" s="86" t="s">
-        <v>1995</v>
+        <v>1980</v>
       </c>
       <c r="F743" s="23" t="s">
         <v>1764</v>
@@ -41600,7 +41594,7 @@
     </row>
     <row r="744" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A744" s="29" t="s">
-        <v>2462</v>
+        <v>2447</v>
       </c>
       <c r="B744" s="82" t="s">
         <v>769</v>
@@ -41612,7 +41606,7 @@
         <v>1249</v>
       </c>
       <c r="E744" s="86" t="s">
-        <v>1996</v>
+        <v>1981</v>
       </c>
       <c r="F744" s="23" t="s">
         <v>1764</v>
@@ -41633,7 +41627,7 @@
     </row>
     <row r="745" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A745" s="29" t="s">
-        <v>2463</v>
+        <v>2448</v>
       </c>
       <c r="B745" s="82" t="s">
         <v>769</v>
@@ -41645,7 +41639,7 @@
         <v>1249</v>
       </c>
       <c r="E745" s="86" t="s">
-        <v>1997</v>
+        <v>1982</v>
       </c>
       <c r="F745" s="23" t="s">
         <v>1764</v>
@@ -41666,7 +41660,7 @@
     </row>
     <row r="746" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A746" s="29" t="s">
-        <v>2464</v>
+        <v>2449</v>
       </c>
       <c r="B746" s="82" t="s">
         <v>769</v>
@@ -41678,7 +41672,7 @@
         <v>1249</v>
       </c>
       <c r="E746" s="86" t="s">
-        <v>1998</v>
+        <v>1983</v>
       </c>
       <c r="F746" s="23" t="s">
         <v>1764</v>
@@ -41699,7 +41693,7 @@
     </row>
     <row r="747" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A747" s="29" t="s">
-        <v>2465</v>
+        <v>2450</v>
       </c>
       <c r="B747" s="82" t="s">
         <v>769</v>
@@ -41711,7 +41705,7 @@
         <v>1249</v>
       </c>
       <c r="E747" s="86" t="s">
-        <v>1999</v>
+        <v>1984</v>
       </c>
       <c r="F747" s="23" t="s">
         <v>1764</v>
@@ -41732,7 +41726,7 @@
     </row>
     <row r="748" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A748" s="29" t="s">
-        <v>2466</v>
+        <v>2451</v>
       </c>
       <c r="B748" s="82" t="s">
         <v>769</v>
@@ -41744,7 +41738,7 @@
         <v>1249</v>
       </c>
       <c r="E748" s="86" t="s">
-        <v>2000</v>
+        <v>1985</v>
       </c>
       <c r="F748" s="23" t="s">
         <v>1764</v>
@@ -41765,7 +41759,7 @@
     </row>
     <row r="749" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A749" s="29" t="s">
-        <v>2467</v>
+        <v>2452</v>
       </c>
       <c r="B749" s="82" t="s">
         <v>769</v>
@@ -41777,7 +41771,7 @@
         <v>1249</v>
       </c>
       <c r="E749" s="86" t="s">
-        <v>2001</v>
+        <v>1986</v>
       </c>
       <c r="F749" s="23" t="s">
         <v>1764</v>
@@ -41798,7 +41792,7 @@
     </row>
     <row r="750" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A750" s="29" t="s">
-        <v>2468</v>
+        <v>2453</v>
       </c>
       <c r="B750" s="82" t="s">
         <v>769</v>
@@ -41810,7 +41804,7 @@
         <v>1249</v>
       </c>
       <c r="E750" s="86" t="s">
-        <v>2002</v>
+        <v>1987</v>
       </c>
       <c r="F750" s="23" t="s">
         <v>1764</v>
@@ -41831,7 +41825,7 @@
     </row>
     <row r="751" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A751" s="29" t="s">
-        <v>2469</v>
+        <v>2454</v>
       </c>
       <c r="B751" s="82" t="s">
         <v>769</v>
@@ -41843,7 +41837,7 @@
         <v>1249</v>
       </c>
       <c r="E751" s="86" t="s">
-        <v>2003</v>
+        <v>1988</v>
       </c>
       <c r="F751" s="23" t="s">
         <v>1764</v>
@@ -41864,7 +41858,7 @@
     </row>
     <row r="752" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A752" s="29" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="B752" s="82" t="s">
         <v>769</v>
@@ -41876,7 +41870,7 @@
         <v>1249</v>
       </c>
       <c r="E752" s="86" t="s">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="F752" s="23" t="s">
         <v>1764</v>
@@ -41897,7 +41891,7 @@
     </row>
     <row r="753" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A753" s="29" t="s">
-        <v>2471</v>
+        <v>2456</v>
       </c>
       <c r="B753" s="82" t="s">
         <v>769</v>
@@ -41909,7 +41903,7 @@
         <v>1249</v>
       </c>
       <c r="E753" s="86" t="s">
-        <v>2005</v>
+        <v>1990</v>
       </c>
       <c r="F753" s="23" t="s">
         <v>1764</v>
@@ -41930,7 +41924,7 @@
     </row>
     <row r="754" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A754" s="29" t="s">
-        <v>2472</v>
+        <v>2457</v>
       </c>
       <c r="B754" s="82" t="s">
         <v>769</v>
@@ -41942,7 +41936,7 @@
         <v>1249</v>
       </c>
       <c r="E754" s="86" t="s">
-        <v>2006</v>
+        <v>1991</v>
       </c>
       <c r="F754" s="23" t="s">
         <v>1764</v>
@@ -41963,7 +41957,7 @@
     </row>
     <row r="755" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A755" s="29" t="s">
-        <v>2473</v>
+        <v>2458</v>
       </c>
       <c r="B755" s="82" t="s">
         <v>769</v>
@@ -41975,7 +41969,7 @@
         <v>1249</v>
       </c>
       <c r="E755" s="83" t="s">
-        <v>2007</v>
+        <v>1992</v>
       </c>
       <c r="F755" s="23" t="s">
         <v>1764</v>
@@ -41996,7 +41990,7 @@
     </row>
     <row r="756" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A756" s="29" t="s">
-        <v>2474</v>
+        <v>2459</v>
       </c>
       <c r="B756" s="82" t="s">
         <v>769</v>
@@ -42008,7 +42002,7 @@
         <v>1249</v>
       </c>
       <c r="E756" s="83" t="s">
-        <v>2008</v>
+        <v>1993</v>
       </c>
       <c r="F756" s="23" t="s">
         <v>1764</v>
@@ -42029,7 +42023,7 @@
     </row>
     <row r="757" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A757" s="29" t="s">
-        <v>2475</v>
+        <v>2460</v>
       </c>
       <c r="B757" s="82" t="s">
         <v>769</v>
@@ -42041,7 +42035,7 @@
         <v>1249</v>
       </c>
       <c r="E757" s="83" t="s">
-        <v>2009</v>
+        <v>1994</v>
       </c>
       <c r="F757" s="23" t="s">
         <v>1764</v>
@@ -42062,7 +42056,7 @@
     </row>
     <row r="758" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A758" s="29" t="s">
-        <v>2476</v>
+        <v>2461</v>
       </c>
       <c r="B758" s="82" t="s">
         <v>769</v>
@@ -42074,7 +42068,7 @@
         <v>1249</v>
       </c>
       <c r="E758" s="83" t="s">
-        <v>2010</v>
+        <v>1995</v>
       </c>
       <c r="F758" s="23" t="s">
         <v>1764</v>
@@ -42095,7 +42089,7 @@
     </row>
     <row r="759" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A759" s="29" t="s">
-        <v>2477</v>
+        <v>2462</v>
       </c>
       <c r="B759" s="82" t="s">
         <v>769</v>
@@ -42107,7 +42101,7 @@
         <v>1249</v>
       </c>
       <c r="E759" s="83" t="s">
-        <v>2011</v>
+        <v>1996</v>
       </c>
       <c r="F759" s="23" t="s">
         <v>1764</v>
@@ -42128,7 +42122,7 @@
     </row>
     <row r="760" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A760" s="29" t="s">
-        <v>2478</v>
+        <v>2463</v>
       </c>
       <c r="B760" s="82" t="s">
         <v>769</v>
@@ -42140,7 +42134,7 @@
         <v>1249</v>
       </c>
       <c r="E760" s="83" t="s">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="F760" s="23" t="s">
         <v>1764</v>
@@ -42161,7 +42155,7 @@
     </row>
     <row r="761" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A761" s="29" t="s">
-        <v>2479</v>
+        <v>2464</v>
       </c>
       <c r="B761" s="82" t="s">
         <v>769</v>
@@ -42173,7 +42167,7 @@
         <v>1249</v>
       </c>
       <c r="E761" s="83" t="s">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="F761" s="23" t="s">
         <v>1764</v>
@@ -42194,7 +42188,7 @@
     </row>
     <row r="762" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A762" s="29" t="s">
-        <v>2480</v>
+        <v>2465</v>
       </c>
       <c r="B762" s="82" t="s">
         <v>769</v>
@@ -42206,7 +42200,7 @@
         <v>1249</v>
       </c>
       <c r="E762" s="83" t="s">
-        <v>2014</v>
+        <v>1999</v>
       </c>
       <c r="F762" s="23" t="s">
         <v>1764</v>
@@ -42227,7 +42221,7 @@
     </row>
     <row r="763" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A763" s="29" t="s">
-        <v>2481</v>
+        <v>2466</v>
       </c>
       <c r="B763" s="82" t="s">
         <v>769</v>
@@ -42239,7 +42233,7 @@
         <v>1249</v>
       </c>
       <c r="E763" s="83" t="s">
-        <v>2015</v>
+        <v>2000</v>
       </c>
       <c r="F763" s="23" t="s">
         <v>1764</v>
@@ -42260,7 +42254,7 @@
     </row>
     <row r="764" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A764" s="29" t="s">
-        <v>2482</v>
+        <v>2467</v>
       </c>
       <c r="B764" s="82" t="s">
         <v>769</v>
@@ -42272,7 +42266,7 @@
         <v>1249</v>
       </c>
       <c r="E764" s="83" t="s">
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="F764" s="23" t="s">
         <v>1764</v>
@@ -42293,7 +42287,7 @@
     </row>
     <row r="765" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A765" s="29" t="s">
-        <v>2483</v>
+        <v>2468</v>
       </c>
       <c r="B765" s="82" t="s">
         <v>769</v>
@@ -42305,7 +42299,7 @@
         <v>1249</v>
       </c>
       <c r="E765" s="83" t="s">
-        <v>2017</v>
+        <v>2002</v>
       </c>
       <c r="F765" s="23" t="s">
         <v>1764</v>
@@ -42326,7 +42320,7 @@
     </row>
     <row r="766" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A766" s="29" t="s">
-        <v>2484</v>
+        <v>2469</v>
       </c>
       <c r="B766" s="82" t="s">
         <v>769</v>
@@ -42338,7 +42332,7 @@
         <v>1249</v>
       </c>
       <c r="E766" s="83" t="s">
-        <v>2018</v>
+        <v>2003</v>
       </c>
       <c r="F766" s="23" t="s">
         <v>1764</v>
@@ -42359,7 +42353,7 @@
     </row>
     <row r="767" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A767" s="29" t="s">
-        <v>2485</v>
+        <v>2470</v>
       </c>
       <c r="B767" s="82" t="s">
         <v>769</v>
@@ -42371,7 +42365,7 @@
         <v>1249</v>
       </c>
       <c r="E767" s="83" t="s">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="F767" s="23" t="s">
         <v>1764</v>
@@ -42392,7 +42386,7 @@
     </row>
     <row r="768" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A768" s="29" t="s">
-        <v>2486</v>
+        <v>2471</v>
       </c>
       <c r="B768" s="82" t="s">
         <v>769</v>
@@ -42404,7 +42398,7 @@
         <v>1249</v>
       </c>
       <c r="E768" s="83" t="s">
-        <v>2020</v>
+        <v>2005</v>
       </c>
       <c r="F768" s="23" t="s">
         <v>1764</v>
@@ -42425,7 +42419,7 @@
     </row>
     <row r="769" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A769" s="29" t="s">
-        <v>2487</v>
+        <v>2472</v>
       </c>
       <c r="B769" s="82" t="s">
         <v>769</v>
@@ -42437,7 +42431,7 @@
         <v>1249</v>
       </c>
       <c r="E769" s="83" t="s">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="F769" s="23" t="s">
         <v>1764</v>
@@ -42458,7 +42452,7 @@
     </row>
     <row r="770" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A770" s="29" t="s">
-        <v>2488</v>
+        <v>2473</v>
       </c>
       <c r="B770" s="82" t="s">
         <v>769</v>
@@ -42470,7 +42464,7 @@
         <v>1249</v>
       </c>
       <c r="E770" s="83" t="s">
-        <v>2022</v>
+        <v>2007</v>
       </c>
       <c r="F770" s="23" t="s">
         <v>1764</v>
@@ -42491,7 +42485,7 @@
     </row>
     <row r="771" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A771" s="29" t="s">
-        <v>2489</v>
+        <v>2474</v>
       </c>
       <c r="B771" s="82" t="s">
         <v>769</v>
@@ -42503,7 +42497,7 @@
         <v>1249</v>
       </c>
       <c r="E771" s="83" t="s">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="F771" s="23" t="s">
         <v>1764</v>
@@ -42524,7 +42518,7 @@
     </row>
     <row r="772" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A772" s="29" t="s">
-        <v>2490</v>
+        <v>2475</v>
       </c>
       <c r="B772" s="82" t="s">
         <v>769</v>
@@ -42536,7 +42530,7 @@
         <v>1249</v>
       </c>
       <c r="E772" s="83" t="s">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="F772" s="23" t="s">
         <v>1764</v>
@@ -42557,7 +42551,7 @@
     </row>
     <row r="773" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A773" s="29" t="s">
-        <v>2491</v>
+        <v>2476</v>
       </c>
       <c r="B773" s="82" t="s">
         <v>769</v>
@@ -42569,7 +42563,7 @@
         <v>1249</v>
       </c>
       <c r="E773" s="83" t="s">
-        <v>2025</v>
+        <v>2010</v>
       </c>
       <c r="F773" s="23" t="s">
         <v>1764</v>
@@ -42590,7 +42584,7 @@
     </row>
     <row r="774" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A774" s="29" t="s">
-        <v>2492</v>
+        <v>2477</v>
       </c>
       <c r="B774" s="82" t="s">
         <v>769</v>
@@ -42602,7 +42596,7 @@
         <v>1249</v>
       </c>
       <c r="E774" s="83" t="s">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="F774" s="23" t="s">
         <v>1764</v>
@@ -42623,7 +42617,7 @@
     </row>
     <row r="775" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A775" s="29" t="s">
-        <v>2493</v>
+        <v>2478</v>
       </c>
       <c r="B775" s="82" t="s">
         <v>769</v>
@@ -42635,7 +42629,7 @@
         <v>1249</v>
       </c>
       <c r="E775" s="83" t="s">
-        <v>2027</v>
+        <v>2012</v>
       </c>
       <c r="F775" s="23" t="s">
         <v>1764</v>
@@ -42656,7 +42650,7 @@
     </row>
     <row r="776" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A776" s="29" t="s">
-        <v>2494</v>
+        <v>2479</v>
       </c>
       <c r="B776" s="82" t="s">
         <v>769</v>
@@ -42668,7 +42662,7 @@
         <v>1249</v>
       </c>
       <c r="E776" s="83" t="s">
-        <v>2028</v>
+        <v>2013</v>
       </c>
       <c r="F776" s="23" t="s">
         <v>1764</v>
@@ -42689,7 +42683,7 @@
     </row>
     <row r="777" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A777" s="29" t="s">
-        <v>2495</v>
+        <v>2480</v>
       </c>
       <c r="B777" s="82" t="s">
         <v>769</v>
@@ -42701,7 +42695,7 @@
         <v>1249</v>
       </c>
       <c r="E777" s="83" t="s">
-        <v>2029</v>
+        <v>2014</v>
       </c>
       <c r="F777" s="23" t="s">
         <v>1764</v>
@@ -42722,7 +42716,7 @@
     </row>
     <row r="778" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A778" s="29" t="s">
-        <v>2496</v>
+        <v>2481</v>
       </c>
       <c r="B778" s="82" t="s">
         <v>769</v>
@@ -42734,7 +42728,7 @@
         <v>1249</v>
       </c>
       <c r="E778" s="83" t="s">
-        <v>2030</v>
+        <v>2015</v>
       </c>
       <c r="F778" s="23" t="s">
         <v>1764</v>
@@ -42755,7 +42749,7 @@
     </row>
     <row r="779" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A779" s="29" t="s">
-        <v>2497</v>
+        <v>2482</v>
       </c>
       <c r="B779" s="82" t="s">
         <v>769</v>
@@ -42767,7 +42761,7 @@
         <v>1249</v>
       </c>
       <c r="E779" s="83" t="s">
-        <v>2031</v>
+        <v>2016</v>
       </c>
       <c r="F779" s="23" t="s">
         <v>1764</v>
@@ -42788,7 +42782,7 @@
     </row>
     <row r="780" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A780" s="29" t="s">
-        <v>2498</v>
+        <v>2483</v>
       </c>
       <c r="B780" s="82" t="s">
         <v>769</v>
@@ -42800,7 +42794,7 @@
         <v>1249</v>
       </c>
       <c r="E780" s="83" t="s">
-        <v>2032</v>
+        <v>2017</v>
       </c>
       <c r="F780" s="23" t="s">
         <v>1764</v>
@@ -42821,7 +42815,7 @@
     </row>
     <row r="781" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A781" s="29" t="s">
-        <v>2499</v>
+        <v>2484</v>
       </c>
       <c r="B781" s="82" t="s">
         <v>769</v>
@@ -42833,7 +42827,7 @@
         <v>1249</v>
       </c>
       <c r="E781" s="83" t="s">
-        <v>2033</v>
+        <v>2018</v>
       </c>
       <c r="F781" s="23" t="s">
         <v>1764</v>
@@ -42854,7 +42848,7 @@
     </row>
     <row r="782" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A782" s="29" t="s">
-        <v>2500</v>
+        <v>2485</v>
       </c>
       <c r="B782" s="82" t="s">
         <v>769</v>
@@ -42866,7 +42860,7 @@
         <v>1249</v>
       </c>
       <c r="E782" s="83" t="s">
-        <v>2034</v>
+        <v>2019</v>
       </c>
       <c r="F782" s="23" t="s">
         <v>1764</v>
@@ -42887,7 +42881,7 @@
     </row>
     <row r="783" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A783" s="29" t="s">
-        <v>2501</v>
+        <v>2486</v>
       </c>
       <c r="B783" s="82" t="s">
         <v>769</v>
@@ -42899,7 +42893,7 @@
         <v>1249</v>
       </c>
       <c r="E783" s="83" t="s">
-        <v>2035</v>
+        <v>2020</v>
       </c>
       <c r="F783" s="23" t="s">
         <v>1764</v>
@@ -42920,7 +42914,7 @@
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A784" s="29" t="s">
-        <v>2502</v>
+        <v>2487</v>
       </c>
       <c r="B784" s="83" t="s">
         <v>1746</v>
@@ -42957,7 +42951,7 @@
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A785" s="29" t="s">
-        <v>2503</v>
+        <v>2488</v>
       </c>
       <c r="B785" s="83" t="s">
         <v>1746</v>
@@ -42994,7 +42988,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A786" s="29" t="s">
-        <v>2504</v>
+        <v>2489</v>
       </c>
       <c r="B786" s="83" t="s">
         <v>1746</v>
@@ -43031,7 +43025,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A787" s="29" t="s">
-        <v>2505</v>
+        <v>2490</v>
       </c>
       <c r="B787" s="83" t="s">
         <v>1746</v>
@@ -43068,7 +43062,7 @@
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A788" s="29" t="s">
-        <v>2506</v>
+        <v>2491</v>
       </c>
       <c r="B788" s="83" t="s">
         <v>1746</v>
@@ -43105,7 +43099,7 @@
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A789" s="29" t="s">
-        <v>2507</v>
+        <v>2492</v>
       </c>
       <c r="B789" s="83" t="s">
         <v>1746</v>
@@ -43142,7 +43136,7 @@
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A790" s="29" t="s">
-        <v>2508</v>
+        <v>2493</v>
       </c>
       <c r="B790" s="83" t="s">
         <v>1746</v>
@@ -43179,7 +43173,7 @@
     </row>
     <row r="791" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A791" s="29" t="s">
-        <v>2509</v>
+        <v>2494</v>
       </c>
       <c r="B791" s="83" t="s">
         <v>1746</v>
@@ -43764,7 +43758,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2646</v>
+        <v>2630</v>
       </c>
       <c r="B810" s="101" t="s">
         <v>1911</v>
@@ -43776,7 +43770,7 @@
         <v>1865</v>
       </c>
       <c r="E810" s="83" t="s">
-        <v>2643</v>
+        <v>2627</v>
       </c>
       <c r="F810" s="31" t="s">
         <v>247</v>
@@ -43787,11 +43781,11 @@
       <c r="H810" s="29"/>
       <c r="I810" s="29"/>
       <c r="J810" s="29" t="s">
-        <v>2642</v>
+        <v>2626</v>
       </c>
       <c r="K810" s="29"/>
       <c r="L810" s="31" t="s">
-        <v>2647</v>
+        <v>2631</v>
       </c>
       <c r="M810" s="29"/>
     </row>
@@ -44258,7 +44252,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2510</v>
+        <v>2495</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1746</v>
@@ -44291,7 +44285,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2511</v>
+        <v>2496</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1746</v>
@@ -44324,7 +44318,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>2512</v>
+        <v>2497</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1746</v>
@@ -44357,7 +44351,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>2513</v>
+        <v>2498</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1746</v>
@@ -44390,7 +44384,7 @@
     </row>
     <row r="830" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A830" s="29" t="s">
-        <v>2514</v>
+        <v>2499</v>
       </c>
       <c r="B830" s="83" t="s">
         <v>1746</v>
@@ -44423,7 +44417,7 @@
     </row>
     <row r="831" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A831" s="29" t="s">
-        <v>2515</v>
+        <v>2500</v>
       </c>
       <c r="B831" s="83" t="s">
         <v>1746</v>
@@ -44456,7 +44450,7 @@
     </row>
     <row r="832" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A832" s="29" t="s">
-        <v>2516</v>
+        <v>2501</v>
       </c>
       <c r="B832" s="83" t="s">
         <v>1746</v>
@@ -44489,7 +44483,7 @@
     </row>
     <row r="833" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A833" s="29" t="s">
-        <v>2517</v>
+        <v>2502</v>
       </c>
       <c r="B833" s="83" t="s">
         <v>1746</v>
@@ -44522,7 +44516,7 @@
     </row>
     <row r="834" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A834" s="29" t="s">
-        <v>2518</v>
+        <v>2503</v>
       </c>
       <c r="B834" s="83" t="s">
         <v>1746</v>
@@ -44555,7 +44549,7 @@
     </row>
     <row r="835" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A835" s="29" t="s">
-        <v>2519</v>
+        <v>2504</v>
       </c>
       <c r="B835" s="83" t="s">
         <v>1746</v>
@@ -44588,7 +44582,7 @@
     </row>
     <row r="836" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A836" s="29" t="s">
-        <v>2520</v>
+        <v>2505</v>
       </c>
       <c r="B836" s="83" t="s">
         <v>1746</v>
@@ -44621,7 +44615,7 @@
     </row>
     <row r="837" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A837" s="29" t="s">
-        <v>2521</v>
+        <v>2506</v>
       </c>
       <c r="B837" s="83" t="s">
         <v>1746</v>
@@ -44654,7 +44648,7 @@
     </row>
     <row r="838" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A838" s="29" t="s">
-        <v>2522</v>
+        <v>2507</v>
       </c>
       <c r="B838" s="83" t="s">
         <v>1746</v>
@@ -44687,7 +44681,7 @@
     </row>
     <row r="839" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A839" s="29" t="s">
-        <v>2523</v>
+        <v>2508</v>
       </c>
       <c r="B839" s="83" t="s">
         <v>1746</v>
@@ -44720,7 +44714,7 @@
     </row>
     <row r="840" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A840" s="29" t="s">
-        <v>2524</v>
+        <v>2509</v>
       </c>
       <c r="B840" s="83" t="s">
         <v>1746</v>
@@ -44753,7 +44747,7 @@
     </row>
     <row r="841" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A841" s="29" t="s">
-        <v>2525</v>
+        <v>2510</v>
       </c>
       <c r="B841" s="83" t="s">
         <v>1746</v>
@@ -44786,7 +44780,7 @@
     </row>
     <row r="842" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A842" s="29" t="s">
-        <v>2526</v>
+        <v>2511</v>
       </c>
       <c r="B842" s="83" t="s">
         <v>1746</v>
@@ -44819,7 +44813,7 @@
     </row>
     <row r="843" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A843" s="29" t="s">
-        <v>2527</v>
+        <v>2512</v>
       </c>
       <c r="B843" s="83" t="s">
         <v>1746</v>
@@ -44852,7 +44846,7 @@
     </row>
     <row r="844" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A844" s="29" t="s">
-        <v>2528</v>
+        <v>2513</v>
       </c>
       <c r="B844" s="83" t="s">
         <v>1746</v>
@@ -44885,7 +44879,7 @@
     </row>
     <row r="845" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A845" s="29" t="s">
-        <v>2529</v>
+        <v>2514</v>
       </c>
       <c r="B845" s="83" t="s">
         <v>1746</v>
@@ -44918,7 +44912,7 @@
     </row>
     <row r="846" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A846" s="29" t="s">
-        <v>1943</v>
+        <v>1928</v>
       </c>
       <c r="B846" s="101" t="s">
         <v>1846</v>
@@ -44943,7 +44937,7 @@
         <v>110</v>
       </c>
       <c r="J846" s="29" t="s">
-        <v>1941</v>
+        <v>1926</v>
       </c>
       <c r="K846" s="29"/>
       <c r="L846" s="31"/>
@@ -44951,7 +44945,7 @@
     </row>
     <row r="847" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A847" s="29" t="s">
-        <v>1944</v>
+        <v>1929</v>
       </c>
       <c r="B847" s="101" t="s">
         <v>1846</v>
@@ -44976,7 +44970,7 @@
         <v>110</v>
       </c>
       <c r="J847" s="29" t="s">
-        <v>1942</v>
+        <v>1927</v>
       </c>
       <c r="K847" s="29"/>
       <c r="L847" s="31"/>
@@ -44990,7 +44984,7 @@
         <v>1860</v>
       </c>
       <c r="C848" s="83" t="s">
-        <v>1932</v>
+        <v>1923</v>
       </c>
       <c r="D848" s="85" t="s">
         <v>1861</v>
@@ -45091,7 +45085,7 @@
         <v>1865</v>
       </c>
       <c r="E851" s="83" t="s">
-        <v>1929</v>
+        <v>2649</v>
       </c>
       <c r="F851" s="31" t="s">
         <v>247</v>
@@ -45112,7 +45106,7 @@
     </row>
     <row r="852" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A852" s="29" t="s">
-        <v>2638</v>
+        <v>2623</v>
       </c>
       <c r="B852" s="100" t="s">
         <v>1911</v>
@@ -45124,7 +45118,7 @@
         <v>1865</v>
       </c>
       <c r="E852" s="82" t="s">
-        <v>2639</v>
+        <v>2628</v>
       </c>
       <c r="F852" s="31" t="s">
         <v>1889</v>
@@ -45139,11 +45133,11 @@
         <v>71</v>
       </c>
       <c r="J852" s="29" t="s">
-        <v>2640</v>
+        <v>2624</v>
       </c>
       <c r="K852" s="29"/>
       <c r="L852" s="31" t="s">
-        <v>2641</v>
+        <v>2625</v>
       </c>
       <c r="M852" s="29"/>
     </row>
@@ -45161,7 +45155,7 @@
         <v>1865</v>
       </c>
       <c r="E853" s="83" t="s">
-        <v>1930</v>
+        <v>2650</v>
       </c>
       <c r="F853" s="31" t="s">
         <v>247</v>
@@ -45215,7 +45209,7 @@
     </row>
     <row r="855" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
-        <v>2232</v>
+        <v>2217</v>
       </c>
       <c r="B855" t="s">
         <v>1874</v>
@@ -45246,13 +45240,13 @@
     </row>
     <row r="856" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A856" s="29" t="s">
-        <v>2253</v>
+        <v>2238</v>
       </c>
       <c r="B856" s="100" t="s">
-        <v>2254</v>
+        <v>2239</v>
       </c>
       <c r="C856" s="83" t="s">
-        <v>2231</v>
+        <v>2216</v>
       </c>
       <c r="D856" s="83" t="s">
         <v>1874</v>
@@ -45269,7 +45263,7 @@
       <c r="H856" s="29"/>
       <c r="I856" s="29"/>
       <c r="J856" s="29" t="s">
-        <v>2234</v>
+        <v>2219</v>
       </c>
       <c r="K856" s="29"/>
       <c r="L856" s="31"/>
@@ -45277,13 +45271,13 @@
     </row>
     <row r="857" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A857" s="80" t="s">
-        <v>2261</v>
+        <v>2246</v>
       </c>
       <c r="B857" s="80" t="s">
-        <v>2255</v>
+        <v>2240</v>
       </c>
       <c r="C857" s="83" t="s">
-        <v>2231</v>
+        <v>2216</v>
       </c>
       <c r="D857" s="83" t="s">
         <v>1874</v>
@@ -45300,7 +45294,7 @@
       <c r="H857" s="29"/>
       <c r="I857" s="29"/>
       <c r="J857" s="29" t="s">
-        <v>2235</v>
+        <v>2220</v>
       </c>
       <c r="K857" s="29"/>
       <c r="L857" s="31"/>
@@ -45308,13 +45302,13 @@
     </row>
     <row r="858" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A858" s="29" t="s">
-        <v>2256</v>
+        <v>2241</v>
       </c>
       <c r="B858" s="101" t="s">
         <v>1880</v>
       </c>
       <c r="C858" s="83" t="s">
-        <v>2231</v>
+        <v>2216</v>
       </c>
       <c r="D858" s="83" t="s">
         <v>1874</v>
@@ -45331,7 +45325,7 @@
       <c r="H858" s="29"/>
       <c r="I858" s="29"/>
       <c r="J858" s="29" t="s">
-        <v>2236</v>
+        <v>2221</v>
       </c>
       <c r="K858" s="29"/>
       <c r="L858" s="31"/>
@@ -45380,7 +45374,7 @@
         <v>1865</v>
       </c>
       <c r="C860" s="83" t="s">
-        <v>2645</v>
+        <v>2629</v>
       </c>
       <c r="D860" s="83" t="s">
         <v>222</v>
@@ -45421,7 +45415,7 @@
         <v>1865</v>
       </c>
       <c r="E861" s="83" t="s">
-        <v>1931</v>
+        <v>2651</v>
       </c>
       <c r="F861" s="31" t="s">
         <v>1889</v>
@@ -45502,13 +45496,13 @@
         <v>1865</v>
       </c>
       <c r="C864" s="83" t="s">
-        <v>2332</v>
+        <v>2317</v>
       </c>
       <c r="D864" s="85" t="s">
         <v>42</v>
       </c>
       <c r="E864" s="83" t="s">
-        <v>2333</v>
+        <v>2318</v>
       </c>
       <c r="F864" s="31" t="s">
         <v>1889</v>
@@ -45523,7 +45517,7 @@
         <v>110</v>
       </c>
       <c r="J864" s="29" t="s">
-        <v>2334</v>
+        <v>2319</v>
       </c>
       <c r="K864" s="29"/>
       <c r="L864" s="31"/>
@@ -45537,12 +45531,14 @@
         <v>1865</v>
       </c>
       <c r="C865" s="83" t="s">
-        <v>2209</v>
+        <v>2194</v>
       </c>
       <c r="D865" s="85" t="s">
-        <v>1904</v>
-      </c>
-      <c r="E865" s="83"/>
+        <v>1862</v>
+      </c>
+      <c r="E865" s="83" t="s">
+        <v>2535</v>
+      </c>
       <c r="F865" s="31" t="s">
         <v>1889</v>
       </c>
@@ -45570,13 +45566,13 @@
         <v>1865</v>
       </c>
       <c r="C866" s="83" t="s">
-        <v>2208</v>
+        <v>2193</v>
       </c>
       <c r="D866" s="85" t="s">
         <v>1905</v>
       </c>
       <c r="E866" s="83" t="s">
-        <v>190</v>
+        <v>2662</v>
       </c>
       <c r="F866" s="31" t="s">
         <v>1889</v>
@@ -45605,7 +45601,7 @@
         <v>1865</v>
       </c>
       <c r="C867" s="83" t="s">
-        <v>2644</v>
+        <v>2628</v>
       </c>
       <c r="D867" s="85" t="s">
         <v>1136</v>
@@ -45626,7 +45622,7 @@
         <v>110</v>
       </c>
       <c r="J867" s="29" t="s">
-        <v>2640</v>
+        <v>2624</v>
       </c>
       <c r="K867" s="29"/>
       <c r="L867" s="31"/>
@@ -45640,7 +45636,7 @@
         <v>1865</v>
       </c>
       <c r="C868" s="83" t="s">
-        <v>2643</v>
+        <v>2627</v>
       </c>
       <c r="D868" s="85" t="s">
         <v>1134</v>
@@ -45661,7 +45657,7 @@
         <v>110</v>
       </c>
       <c r="J868" s="29" t="s">
-        <v>2642</v>
+        <v>2626</v>
       </c>
       <c r="K868" s="29"/>
       <c r="L868" s="31"/>
@@ -45675,7 +45671,7 @@
         <v>1865</v>
       </c>
       <c r="C869" s="83" t="s">
-        <v>2219</v>
+        <v>2204</v>
       </c>
       <c r="D869" s="85" t="s">
         <v>211</v>
@@ -45696,10 +45692,10 @@
         <v>110</v>
       </c>
       <c r="J869" s="29" t="s">
-        <v>2220</v>
+        <v>2205</v>
       </c>
       <c r="K869" s="29" t="s">
-        <v>2221</v>
+        <v>2206</v>
       </c>
       <c r="L869" s="31"/>
       <c r="M869" s="29"/>
@@ -45709,10 +45705,10 @@
         <v>1901</v>
       </c>
       <c r="B870" s="85" t="s">
-        <v>2210</v>
+        <v>2195</v>
       </c>
       <c r="C870" s="83" t="s">
-        <v>2211</v>
+        <v>2196</v>
       </c>
       <c r="D870" s="85" t="s">
         <v>1038</v>
@@ -45733,7 +45729,7 @@
         <v>110</v>
       </c>
       <c r="J870" s="29" t="s">
-        <v>2339</v>
+        <v>2324</v>
       </c>
       <c r="K870" s="29"/>
       <c r="L870" s="31"/>
@@ -45741,7 +45737,7 @@
     </row>
     <row r="871" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A871" s="29" t="s">
-        <v>2218</v>
+        <v>2203</v>
       </c>
       <c r="B871" s="58" t="s">
         <v>33</v>
@@ -45774,7 +45770,7 @@
     </row>
     <row r="872" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A872" s="29" t="s">
-        <v>1940</v>
+        <v>1925</v>
       </c>
       <c r="B872" s="83" t="s">
         <v>1849</v>
@@ -45801,7 +45797,7 @@
         <v>110</v>
       </c>
       <c r="J872" s="29" t="s">
-        <v>1941</v>
+        <v>1926</v>
       </c>
       <c r="K872" s="29"/>
       <c r="L872" s="31"/>
@@ -45809,7 +45805,7 @@
     </row>
     <row r="873" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A873" s="29" t="s">
-        <v>1945</v>
+        <v>1930</v>
       </c>
       <c r="B873" s="83" t="s">
         <v>1849</v>
@@ -45836,7 +45832,7 @@
         <v>110</v>
       </c>
       <c r="J873" s="29" t="s">
-        <v>1942</v>
+        <v>1927</v>
       </c>
       <c r="K873" s="29"/>
       <c r="L873" s="31"/>
@@ -45844,7 +45840,7 @@
     </row>
     <row r="874" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A874" s="29" t="s">
-        <v>2217</v>
+        <v>2202</v>
       </c>
       <c r="B874" s="83" t="s">
         <v>769</v>
@@ -45856,7 +45852,7 @@
         <v>66</v>
       </c>
       <c r="E874" s="83" t="s">
-        <v>2038</v>
+        <v>2023</v>
       </c>
       <c r="F874" s="31" t="s">
         <v>1764</v>
@@ -45871,7 +45867,7 @@
         <v>71</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>2040</v>
+        <v>2025</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -45879,7 +45875,7 @@
     </row>
     <row r="875" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A875" s="29" t="s">
-        <v>2216</v>
+        <v>2201</v>
       </c>
       <c r="B875" s="83" t="s">
         <v>769</v>
@@ -45891,7 +45887,7 @@
         <v>66</v>
       </c>
       <c r="E875" s="83" t="s">
-        <v>2039</v>
+        <v>2024</v>
       </c>
       <c r="F875" s="31" t="s">
         <v>1764</v>
@@ -45906,7 +45902,7 @@
         <v>71</v>
       </c>
       <c r="J875" s="29" t="s">
-        <v>2041</v>
+        <v>2026</v>
       </c>
       <c r="K875" s="29"/>
       <c r="L875" s="31"/>
@@ -45914,16 +45910,16 @@
     </row>
     <row r="876" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A876" s="29" t="s">
-        <v>2215</v>
+        <v>2200</v>
       </c>
       <c r="B876" s="83" t="s">
         <v>1865</v>
       </c>
       <c r="C876" s="83" t="s">
-        <v>2212</v>
+        <v>2197</v>
       </c>
       <c r="D876" s="85" t="s">
-        <v>2213</v>
+        <v>2198</v>
       </c>
       <c r="E876" s="83" t="s">
         <v>1322</v>
@@ -45953,10 +45949,10 @@
         <v>1865</v>
       </c>
       <c r="C877" s="83" t="s">
-        <v>2214</v>
+        <v>2199</v>
       </c>
       <c r="D877" s="85" t="s">
-        <v>2213</v>
+        <v>2198</v>
       </c>
       <c r="E877" s="83" t="s">
         <v>1323</v>
@@ -45980,7 +45976,7 @@
     </row>
     <row r="878" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A878" s="29" t="s">
-        <v>2648</v>
+        <v>2632</v>
       </c>
       <c r="B878" s="100" t="s">
         <v>1911</v>
@@ -45992,7 +45988,7 @@
         <v>1865</v>
       </c>
       <c r="E878" s="82" t="s">
-        <v>2649</v>
+        <v>2633</v>
       </c>
       <c r="F878" s="31" t="s">
         <v>247</v>
@@ -46007,11 +46003,11 @@
         <v>71</v>
       </c>
       <c r="J878" s="29" t="s">
-        <v>2650</v>
+        <v>2634</v>
       </c>
       <c r="K878" s="29"/>
       <c r="L878" s="31" t="s">
-        <v>2641</v>
+        <v>2625</v>
       </c>
       <c r="M878" s="29"/>
     </row>
@@ -46020,7 +46016,7 @@
         <v>1877</v>
       </c>
       <c r="B879" s="85" t="s">
-        <v>2213</v>
+        <v>2198</v>
       </c>
       <c r="C879" s="83" t="s">
         <v>1361</v>
@@ -46029,7 +46025,7 @@
         <v>1865</v>
       </c>
       <c r="E879" s="83" t="s">
-        <v>2222</v>
+        <v>2207</v>
       </c>
       <c r="F879" s="31"/>
       <c r="G879" s="31"/>
@@ -46050,13 +46046,13 @@
         <v>1862</v>
       </c>
       <c r="C880" s="83" t="s">
-        <v>2225</v>
+        <v>2210</v>
       </c>
       <c r="D880" s="85" t="s">
         <v>1861</v>
       </c>
       <c r="E880" s="83" t="s">
-        <v>2226</v>
+        <v>2211</v>
       </c>
       <c r="F880" s="31" t="s">
         <v>1764</v>
@@ -46071,7 +46067,7 @@
         <v>71</v>
       </c>
       <c r="J880" s="29" t="s">
-        <v>2227</v>
+        <v>2212</v>
       </c>
       <c r="K880" s="29"/>
       <c r="L880" s="31"/>
@@ -46079,13 +46075,13 @@
     </row>
     <row r="881" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A881" s="29" t="s">
-        <v>2233</v>
+        <v>2218</v>
       </c>
       <c r="B881" s="83" t="s">
-        <v>2238</v>
+        <v>2223</v>
       </c>
       <c r="C881" s="83" t="s">
-        <v>2231</v>
+        <v>2216</v>
       </c>
       <c r="D881" t="s">
         <v>1874</v>
@@ -46102,7 +46098,7 @@
       <c r="H881" s="29"/>
       <c r="I881" s="29"/>
       <c r="J881" s="29" t="s">
-        <v>2237</v>
+        <v>2222</v>
       </c>
       <c r="K881" s="29"/>
       <c r="L881" s="31"/>
@@ -46110,7 +46106,7 @@
     </row>
     <row r="882" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A882" s="29" t="s">
-        <v>2247</v>
+        <v>2232</v>
       </c>
       <c r="B882" s="83" t="s">
         <v>27</v>
@@ -46137,7 +46133,7 @@
         <v>71</v>
       </c>
       <c r="J882" s="29" t="s">
-        <v>2243</v>
+        <v>2228</v>
       </c>
       <c r="K882" s="29"/>
       <c r="L882" s="31"/>
@@ -46145,7 +46141,7 @@
     </row>
     <row r="883" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A883" s="29" t="s">
-        <v>2248</v>
+        <v>2233</v>
       </c>
       <c r="B883" s="83" t="s">
         <v>27</v>
@@ -46157,7 +46153,7 @@
         <v>27</v>
       </c>
       <c r="E883" s="83" t="s">
-        <v>2249</v>
+        <v>2234</v>
       </c>
       <c r="F883" s="31" t="s">
         <v>1764</v>
@@ -46172,7 +46168,7 @@
         <v>71</v>
       </c>
       <c r="J883" s="29" t="s">
-        <v>2252</v>
+        <v>2237</v>
       </c>
       <c r="K883" s="29"/>
       <c r="L883" s="31"/>
@@ -46180,7 +46176,7 @@
     </row>
     <row r="884" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A884" s="29" t="s">
-        <v>2250</v>
+        <v>2235</v>
       </c>
       <c r="B884" s="83" t="s">
         <v>27</v>
@@ -46192,7 +46188,7 @@
         <v>27</v>
       </c>
       <c r="E884" s="83" t="s">
-        <v>2251</v>
+        <v>2236</v>
       </c>
       <c r="F884" s="31" t="s">
         <v>1764</v>
@@ -46207,7 +46203,7 @@
         <v>71</v>
       </c>
       <c r="J884" s="29" t="s">
-        <v>2252</v>
+        <v>2237</v>
       </c>
       <c r="K884" s="29"/>
       <c r="L884" s="31"/>
@@ -46215,13 +46211,13 @@
     </row>
     <row r="885" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
-        <v>2260</v>
+        <v>2245</v>
       </c>
       <c r="B885" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C885" s="83" t="s">
-        <v>2246</v>
+        <v>2231</v>
       </c>
       <c r="D885" s="83" t="s">
         <v>55</v>
@@ -46242,17 +46238,17 @@
         <v>110</v>
       </c>
       <c r="J885" s="83" t="s">
-        <v>2243</v>
+        <v>2228</v>
       </c>
       <c r="K885" s="83" t="s">
-        <v>2259</v>
+        <v>2244</v>
       </c>
       <c r="L885" s="31"/>
       <c r="M885" s="29"/>
     </row>
     <row r="886" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A886" s="29" t="s">
-        <v>2295</v>
+        <v>2280</v>
       </c>
       <c r="B886" s="83" t="s">
         <v>1134</v>
@@ -46270,7 +46266,7 @@
         <v>1764</v>
       </c>
       <c r="G886" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H886" s="29">
         <v>0</v>
@@ -46279,7 +46275,7 @@
         <v>71</v>
       </c>
       <c r="J886" s="29" t="s">
-        <v>2270</v>
+        <v>2255</v>
       </c>
       <c r="K886" s="29"/>
       <c r="L886" s="31"/>
@@ -46287,7 +46283,7 @@
     </row>
     <row r="887" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A887" s="29" t="s">
-        <v>2296</v>
+        <v>2281</v>
       </c>
       <c r="B887" s="83" t="s">
         <v>1134</v>
@@ -46305,7 +46301,7 @@
         <v>1764</v>
       </c>
       <c r="G887" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H887" s="29">
         <v>0</v>
@@ -46314,7 +46310,7 @@
         <v>71</v>
       </c>
       <c r="J887" s="29" t="s">
-        <v>2271</v>
+        <v>2256</v>
       </c>
       <c r="K887" s="29"/>
       <c r="L887" s="31"/>
@@ -46322,7 +46318,7 @@
     </row>
     <row r="888" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A888" s="29" t="s">
-        <v>2297</v>
+        <v>2282</v>
       </c>
       <c r="B888" s="83" t="s">
         <v>1134</v>
@@ -46340,7 +46336,7 @@
         <v>1764</v>
       </c>
       <c r="G888" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H888" s="29">
         <v>0</v>
@@ -46349,7 +46345,7 @@
         <v>71</v>
       </c>
       <c r="J888" s="29" t="s">
-        <v>2272</v>
+        <v>2257</v>
       </c>
       <c r="K888" s="29"/>
       <c r="L888" s="31"/>
@@ -46357,7 +46353,7 @@
     </row>
     <row r="889" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A889" s="29" t="s">
-        <v>2298</v>
+        <v>2283</v>
       </c>
       <c r="B889" s="83" t="s">
         <v>1134</v>
@@ -46375,7 +46371,7 @@
         <v>1764</v>
       </c>
       <c r="G889" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H889" s="29">
         <v>0</v>
@@ -46384,7 +46380,7 @@
         <v>71</v>
       </c>
       <c r="J889" s="83" t="s">
-        <v>2540</v>
+        <v>2525</v>
       </c>
       <c r="K889" s="29"/>
       <c r="L889" s="31"/>
@@ -46392,7 +46388,7 @@
     </row>
     <row r="890" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A890" s="29" t="s">
-        <v>2299</v>
+        <v>2284</v>
       </c>
       <c r="B890" s="83" t="s">
         <v>1134</v>
@@ -46410,7 +46406,7 @@
         <v>1764</v>
       </c>
       <c r="G890" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H890" s="29">
         <v>0</v>
@@ -46427,7 +46423,7 @@
     </row>
     <row r="891" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A891" s="29" t="s">
-        <v>2300</v>
+        <v>2285</v>
       </c>
       <c r="B891" s="83" t="s">
         <v>1134</v>
@@ -46445,7 +46441,7 @@
         <v>1764</v>
       </c>
       <c r="G891" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H891" s="29">
         <v>0</v>
@@ -46454,7 +46450,7 @@
         <v>71</v>
       </c>
       <c r="J891" s="29" t="s">
-        <v>2634</v>
+        <v>2619</v>
       </c>
       <c r="K891" s="29"/>
       <c r="L891" s="31"/>
@@ -46462,7 +46458,7 @@
     </row>
     <row r="892" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A892" s="29" t="s">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="B892" s="83" t="s">
         <v>1134</v>
@@ -46480,7 +46476,7 @@
         <v>1764</v>
       </c>
       <c r="G892" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H892" s="29">
         <v>0</v>
@@ -46489,7 +46485,7 @@
         <v>71</v>
       </c>
       <c r="J892" s="29" t="s">
-        <v>2273</v>
+        <v>2258</v>
       </c>
       <c r="K892" s="29"/>
       <c r="L892" s="31"/>
@@ -46497,7 +46493,7 @@
     </row>
     <row r="893" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A893" s="29" t="s">
-        <v>2302</v>
+        <v>2287</v>
       </c>
       <c r="B893" s="83" t="s">
         <v>1134</v>
@@ -46515,7 +46511,7 @@
         <v>1764</v>
       </c>
       <c r="G893" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H893" s="29">
         <v>0</v>
@@ -46524,7 +46520,7 @@
         <v>71</v>
       </c>
       <c r="J893" s="29" t="s">
-        <v>2274</v>
+        <v>2259</v>
       </c>
       <c r="K893" s="29"/>
       <c r="L893" s="31"/>
@@ -46532,7 +46528,7 @@
     </row>
     <row r="894" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A894" s="29" t="s">
-        <v>2303</v>
+        <v>2288</v>
       </c>
       <c r="B894" s="83" t="s">
         <v>1134</v>
@@ -46550,7 +46546,7 @@
         <v>1764</v>
       </c>
       <c r="G894" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H894" s="29">
         <v>0</v>
@@ -46559,7 +46555,7 @@
         <v>71</v>
       </c>
       <c r="J894" s="29" t="s">
-        <v>2275</v>
+        <v>2260</v>
       </c>
       <c r="K894" s="29"/>
       <c r="L894" s="31"/>
@@ -46567,7 +46563,7 @@
     </row>
     <row r="895" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A895" s="29" t="s">
-        <v>2304</v>
+        <v>2289</v>
       </c>
       <c r="B895" s="83" t="s">
         <v>1134</v>
@@ -46585,7 +46581,7 @@
         <v>1764</v>
       </c>
       <c r="G895" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H895" s="29">
         <v>0</v>
@@ -46594,7 +46590,7 @@
         <v>71</v>
       </c>
       <c r="J895" s="29" t="s">
-        <v>2276</v>
+        <v>2261</v>
       </c>
       <c r="K895" s="29"/>
       <c r="L895" s="31"/>
@@ -46602,7 +46598,7 @@
     </row>
     <row r="896" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A896" s="29" t="s">
-        <v>2305</v>
+        <v>2290</v>
       </c>
       <c r="B896" s="83" t="s">
         <v>1134</v>
@@ -46620,7 +46616,7 @@
         <v>1764</v>
       </c>
       <c r="G896" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H896" s="29">
         <v>0</v>
@@ -46629,7 +46625,7 @@
         <v>71</v>
       </c>
       <c r="J896" s="29" t="s">
-        <v>2277</v>
+        <v>2262</v>
       </c>
       <c r="K896" s="29"/>
       <c r="L896" s="31"/>
@@ -46637,7 +46633,7 @@
     </row>
     <row r="897" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A897" s="29" t="s">
-        <v>2306</v>
+        <v>2291</v>
       </c>
       <c r="B897" s="83" t="s">
         <v>1134</v>
@@ -46655,7 +46651,7 @@
         <v>1764</v>
       </c>
       <c r="G897" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H897" s="29">
         <v>0</v>
@@ -46664,7 +46660,7 @@
         <v>71</v>
       </c>
       <c r="J897" s="29" t="s">
-        <v>2278</v>
+        <v>2263</v>
       </c>
       <c r="K897" s="29"/>
       <c r="L897" s="31"/>
@@ -46672,7 +46668,7 @@
     </row>
     <row r="898" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A898" s="29" t="s">
-        <v>2307</v>
+        <v>2292</v>
       </c>
       <c r="B898" s="83" t="s">
         <v>1134</v>
@@ -46690,7 +46686,7 @@
         <v>1764</v>
       </c>
       <c r="G898" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H898" s="29">
         <v>0</v>
@@ -46699,7 +46695,7 @@
         <v>71</v>
       </c>
       <c r="J898" s="29" t="s">
-        <v>2279</v>
+        <v>2264</v>
       </c>
       <c r="K898" s="29"/>
       <c r="L898" s="31"/>
@@ -46707,7 +46703,7 @@
     </row>
     <row r="899" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A899" s="29" t="s">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="B899" s="83" t="s">
         <v>1134</v>
@@ -46725,7 +46721,7 @@
         <v>1764</v>
       </c>
       <c r="G899" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H899" s="29">
         <v>0</v>
@@ -46734,7 +46730,7 @@
         <v>71</v>
       </c>
       <c r="J899" s="29" t="s">
-        <v>2280</v>
+        <v>2265</v>
       </c>
       <c r="K899" s="29"/>
       <c r="L899" s="31"/>
@@ -46742,13 +46738,13 @@
     </row>
     <row r="900" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A900" s="29" t="s">
-        <v>2309</v>
+        <v>2294</v>
       </c>
       <c r="B900" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C900" s="83" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D900" s="83" t="s">
         <v>1134</v>
@@ -46760,7 +46756,7 @@
         <v>1764</v>
       </c>
       <c r="G900" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H900" s="29">
         <v>0</v>
@@ -46769,7 +46765,7 @@
         <v>71</v>
       </c>
       <c r="J900" s="29" t="s">
-        <v>2281</v>
+        <v>2266</v>
       </c>
       <c r="K900" s="29"/>
       <c r="L900" s="31"/>
@@ -46777,7 +46773,7 @@
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A901" s="29" t="s">
-        <v>2310</v>
+        <v>2295</v>
       </c>
       <c r="B901" s="83" t="s">
         <v>1134</v>
@@ -46795,7 +46791,7 @@
         <v>1764</v>
       </c>
       <c r="G901" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H901" s="29">
         <v>0</v>
@@ -46804,7 +46800,7 @@
         <v>71</v>
       </c>
       <c r="J901" s="29" t="s">
-        <v>2282</v>
+        <v>2267</v>
       </c>
       <c r="K901" s="29"/>
       <c r="L901" s="31"/>
@@ -46812,7 +46808,7 @@
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A902" s="29" t="s">
-        <v>2311</v>
+        <v>2296</v>
       </c>
       <c r="B902" s="83" t="s">
         <v>1134</v>
@@ -46830,7 +46826,7 @@
         <v>1764</v>
       </c>
       <c r="G902" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H902" s="29">
         <v>0</v>
@@ -46839,7 +46835,7 @@
         <v>71</v>
       </c>
       <c r="J902" s="29" t="s">
-        <v>2283</v>
+        <v>2268</v>
       </c>
       <c r="K902" s="29"/>
       <c r="L902" s="31"/>
@@ -46847,7 +46843,7 @@
     </row>
     <row r="903" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A903" s="29" t="s">
-        <v>2312</v>
+        <v>2297</v>
       </c>
       <c r="B903" s="83" t="s">
         <v>1134</v>
@@ -46865,7 +46861,7 @@
         <v>1764</v>
       </c>
       <c r="G903" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H903" s="29">
         <v>0</v>
@@ -46874,7 +46870,7 @@
         <v>71</v>
       </c>
       <c r="J903" s="29" t="s">
-        <v>2284</v>
+        <v>2269</v>
       </c>
       <c r="K903" s="29"/>
       <c r="L903" s="31"/>
@@ -46882,7 +46878,7 @@
     </row>
     <row r="904" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A904" s="29" t="s">
-        <v>2313</v>
+        <v>2298</v>
       </c>
       <c r="B904" s="83" t="s">
         <v>1134</v>
@@ -46900,7 +46896,7 @@
         <v>1764</v>
       </c>
       <c r="G904" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H904" s="29">
         <v>0</v>
@@ -46909,7 +46905,7 @@
         <v>71</v>
       </c>
       <c r="J904" s="29" t="s">
-        <v>2285</v>
+        <v>2270</v>
       </c>
       <c r="K904" s="29"/>
       <c r="L904" s="31"/>
@@ -46917,7 +46913,7 @@
     </row>
     <row r="905" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A905" s="29" t="s">
-        <v>2314</v>
+        <v>2299</v>
       </c>
       <c r="B905" s="83" t="s">
         <v>1134</v>
@@ -46935,7 +46931,7 @@
         <v>1764</v>
       </c>
       <c r="G905" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H905" s="29">
         <v>0</v>
@@ -46944,7 +46940,7 @@
         <v>71</v>
       </c>
       <c r="J905" s="29" t="s">
-        <v>2286</v>
+        <v>2271</v>
       </c>
       <c r="K905" s="29"/>
       <c r="L905" s="31"/>
@@ -46952,7 +46948,7 @@
     </row>
     <row r="906" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A906" s="29" t="s">
-        <v>2315</v>
+        <v>2300</v>
       </c>
       <c r="B906" s="83" t="s">
         <v>1134</v>
@@ -46970,7 +46966,7 @@
         <v>1764</v>
       </c>
       <c r="G906" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H906" s="29">
         <v>0</v>
@@ -46979,7 +46975,7 @@
         <v>71</v>
       </c>
       <c r="J906" s="29" t="s">
-        <v>2287</v>
+        <v>2272</v>
       </c>
       <c r="K906" s="29"/>
       <c r="L906" s="31"/>
@@ -46987,7 +46983,7 @@
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A907" s="29" t="s">
-        <v>2316</v>
+        <v>2301</v>
       </c>
       <c r="B907" s="83" t="s">
         <v>1134</v>
@@ -47005,7 +47001,7 @@
         <v>1764</v>
       </c>
       <c r="G907" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H907" s="29">
         <v>0</v>
@@ -47022,7 +47018,7 @@
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A908" s="29" t="s">
-        <v>2317</v>
+        <v>2302</v>
       </c>
       <c r="B908" s="83" t="s">
         <v>1134</v>
@@ -47034,13 +47030,13 @@
         <v>1134</v>
       </c>
       <c r="E908" s="83" t="s">
-        <v>2262</v>
+        <v>2247</v>
       </c>
       <c r="F908" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G908" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H908" s="29">
         <v>0</v>
@@ -47049,7 +47045,7 @@
         <v>71</v>
       </c>
       <c r="J908" s="29" t="s">
-        <v>2288</v>
+        <v>2273</v>
       </c>
       <c r="K908" s="29"/>
       <c r="L908" s="31"/>
@@ -47057,7 +47053,7 @@
     </row>
     <row r="909" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A909" s="29" t="s">
-        <v>2318</v>
+        <v>2303</v>
       </c>
       <c r="B909" s="83" t="s">
         <v>1134</v>
@@ -47069,13 +47065,13 @@
         <v>1134</v>
       </c>
       <c r="E909" s="83" t="s">
-        <v>2263</v>
+        <v>2248</v>
       </c>
       <c r="F909" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G909" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H909" s="29">
         <v>0</v>
@@ -47084,7 +47080,7 @@
         <v>71</v>
       </c>
       <c r="J909" s="29" t="s">
-        <v>2289</v>
+        <v>2274</v>
       </c>
       <c r="K909" s="29"/>
       <c r="L909" s="31"/>
@@ -47092,7 +47088,7 @@
     </row>
     <row r="910" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A910" s="29" t="s">
-        <v>2319</v>
+        <v>2304</v>
       </c>
       <c r="B910" s="83" t="s">
         <v>1134</v>
@@ -47110,7 +47106,7 @@
         <v>1764</v>
       </c>
       <c r="G910" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H910" s="29">
         <v>0</v>
@@ -47127,7 +47123,7 @@
     </row>
     <row r="911" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A911" s="29" t="s">
-        <v>2320</v>
+        <v>2305</v>
       </c>
       <c r="B911" s="83" t="s">
         <v>1134</v>
@@ -47145,7 +47141,7 @@
         <v>1764</v>
       </c>
       <c r="G911" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H911" s="29">
         <v>0</v>
@@ -47162,7 +47158,7 @@
     </row>
     <row r="912" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A912" s="29" t="s">
-        <v>2321</v>
+        <v>2306</v>
       </c>
       <c r="B912" s="83" t="s">
         <v>1134</v>
@@ -47180,7 +47176,7 @@
         <v>1764</v>
       </c>
       <c r="G912" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H912" s="29">
         <v>0</v>
@@ -47197,7 +47193,7 @@
     </row>
     <row r="913" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A913" s="29" t="s">
-        <v>2322</v>
+        <v>2307</v>
       </c>
       <c r="B913" s="83" t="s">
         <v>1134</v>
@@ -47215,7 +47211,7 @@
         <v>1764</v>
       </c>
       <c r="G913" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H913" s="29">
         <v>0</v>
@@ -47224,7 +47220,7 @@
         <v>71</v>
       </c>
       <c r="J913" s="29" t="s">
-        <v>2290</v>
+        <v>2275</v>
       </c>
       <c r="K913" s="29"/>
       <c r="L913" s="31"/>
@@ -47232,7 +47228,7 @@
     </row>
     <row r="914" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A914" s="29" t="s">
-        <v>2323</v>
+        <v>2308</v>
       </c>
       <c r="B914" s="83" t="s">
         <v>1134</v>
@@ -47250,7 +47246,7 @@
         <v>1764</v>
       </c>
       <c r="G914" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H914" s="29">
         <v>0</v>
@@ -47259,7 +47255,7 @@
         <v>71</v>
       </c>
       <c r="J914" s="29" t="s">
-        <v>2291</v>
+        <v>2276</v>
       </c>
       <c r="K914" s="29"/>
       <c r="L914" s="31"/>
@@ -47267,7 +47263,7 @@
     </row>
     <row r="915" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A915" s="29" t="s">
-        <v>2324</v>
+        <v>2309</v>
       </c>
       <c r="B915" s="83" t="s">
         <v>1134</v>
@@ -47279,13 +47275,13 @@
         <v>1134</v>
       </c>
       <c r="E915" s="83" t="s">
-        <v>2264</v>
+        <v>2249</v>
       </c>
       <c r="F915" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G915" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H915" s="29">
         <v>0</v>
@@ -47302,25 +47298,25 @@
     </row>
     <row r="916" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A916" s="29" t="s">
-        <v>2325</v>
+        <v>2310</v>
       </c>
       <c r="B916" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C916" s="83" t="s">
-        <v>2380</v>
+        <v>2365</v>
       </c>
       <c r="D916" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="E916" s="83" t="s">
-        <v>2265</v>
+        <v>2250</v>
       </c>
       <c r="F916" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G916" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H916" s="29">
         <v>0</v>
@@ -47337,7 +47333,7 @@
     </row>
     <row r="917" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A917" s="29" t="s">
-        <v>2326</v>
+        <v>2311</v>
       </c>
       <c r="B917" s="83" t="s">
         <v>1134</v>
@@ -47349,13 +47345,13 @@
         <v>1134</v>
       </c>
       <c r="E917" s="83" t="s">
-        <v>2266</v>
+        <v>2251</v>
       </c>
       <c r="F917" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G917" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H917" s="29">
         <v>0</v>
@@ -47364,7 +47360,7 @@
         <v>71</v>
       </c>
       <c r="J917" s="29" t="s">
-        <v>2292</v>
+        <v>2277</v>
       </c>
       <c r="K917" s="29"/>
       <c r="L917" s="31"/>
@@ -47372,7 +47368,7 @@
     </row>
     <row r="918" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A918" s="29" t="s">
-        <v>2327</v>
+        <v>2312</v>
       </c>
       <c r="B918" s="83" t="s">
         <v>1134</v>
@@ -47384,13 +47380,13 @@
         <v>1134</v>
       </c>
       <c r="E918" s="83" t="s">
-        <v>2245</v>
+        <v>2230</v>
       </c>
       <c r="F918" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G918" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H918" s="29">
         <v>0</v>
@@ -47399,7 +47395,7 @@
         <v>71</v>
       </c>
       <c r="J918" s="29" t="s">
-        <v>2288</v>
+        <v>2273</v>
       </c>
       <c r="K918" s="29"/>
       <c r="L918" s="31"/>
@@ -47407,7 +47403,7 @@
     </row>
     <row r="919" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A919" s="29" t="s">
-        <v>2328</v>
+        <v>2313</v>
       </c>
       <c r="B919" s="83" t="s">
         <v>1134</v>
@@ -47419,13 +47415,13 @@
         <v>1134</v>
       </c>
       <c r="E919" s="83" t="s">
-        <v>2267</v>
+        <v>2252</v>
       </c>
       <c r="F919" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G919" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H919" s="29">
         <v>0</v>
@@ -47442,7 +47438,7 @@
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A920" s="29" t="s">
-        <v>2329</v>
+        <v>2314</v>
       </c>
       <c r="B920" s="83" t="s">
         <v>1134</v>
@@ -47454,13 +47450,13 @@
         <v>1134</v>
       </c>
       <c r="E920" s="83" t="s">
-        <v>2268</v>
+        <v>2253</v>
       </c>
       <c r="F920" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G920" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H920" s="29">
         <v>0</v>
@@ -47477,25 +47473,25 @@
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A921" s="29" t="s">
-        <v>2330</v>
+        <v>2315</v>
       </c>
       <c r="B921" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="C921" s="83" t="s">
-        <v>2383</v>
+        <v>2368</v>
       </c>
       <c r="D921" s="83" t="s">
         <v>1134</v>
       </c>
       <c r="E921" s="83" t="s">
-        <v>2269</v>
+        <v>2254</v>
       </c>
       <c r="F921" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G921" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H921" s="29">
         <v>0</v>
@@ -47512,7 +47508,7 @@
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A922" s="29" t="s">
-        <v>2331</v>
+        <v>2316</v>
       </c>
       <c r="B922" s="83" t="s">
         <v>1134</v>
@@ -47524,13 +47520,13 @@
         <v>1134</v>
       </c>
       <c r="E922" s="83" t="s">
-        <v>2246</v>
+        <v>2231</v>
       </c>
       <c r="F922" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G922" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H922" s="29">
         <v>0</v>
@@ -47539,7 +47535,7 @@
         <v>71</v>
       </c>
       <c r="J922" s="29" t="s">
-        <v>2293</v>
+        <v>2278</v>
       </c>
       <c r="K922" s="29"/>
       <c r="L922" s="31"/>
@@ -47547,7 +47543,7 @@
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A923" s="29" t="s">
-        <v>2530</v>
+        <v>2515</v>
       </c>
       <c r="B923" s="83" t="s">
         <v>1134</v>
@@ -47565,7 +47561,7 @@
         <v>1764</v>
       </c>
       <c r="G923" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H923" s="29">
         <v>0</v>
@@ -47582,7 +47578,7 @@
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A924" s="29" t="s">
-        <v>2531</v>
+        <v>2516</v>
       </c>
       <c r="B924" s="83" t="s">
         <v>1134</v>
@@ -47600,7 +47596,7 @@
         <v>1764</v>
       </c>
       <c r="G924" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H924" s="29">
         <v>0</v>
@@ -47617,7 +47613,7 @@
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A925" s="29" t="s">
-        <v>2532</v>
+        <v>2517</v>
       </c>
       <c r="B925" s="83" t="s">
         <v>1134</v>
@@ -47635,7 +47631,7 @@
         <v>1764</v>
       </c>
       <c r="G925" s="31" t="s">
-        <v>2294</v>
+        <v>2279</v>
       </c>
       <c r="H925" s="29">
         <v>0</v>
@@ -47652,13 +47648,13 @@
     </row>
     <row r="926" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A926" s="29" t="s">
-        <v>2336</v>
+        <v>2321</v>
       </c>
       <c r="B926" s="29" t="s">
-        <v>2335</v>
+        <v>2320</v>
       </c>
       <c r="C926" s="29" t="s">
-        <v>2337</v>
+        <v>2322</v>
       </c>
       <c r="D926" s="29" t="s">
         <v>1134</v>
@@ -47679,7 +47675,7 @@
         <v>110</v>
       </c>
       <c r="J926" s="29" t="s">
-        <v>2338</v>
+        <v>2323</v>
       </c>
       <c r="K926" s="29"/>
       <c r="L926" s="31"/>
@@ -47687,7 +47683,7 @@
     </row>
     <row r="927" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A927" s="29" t="s">
-        <v>2344</v>
+        <v>2329</v>
       </c>
       <c r="B927" s="114"/>
       <c r="C927" s="115"/>
@@ -47712,7 +47708,7 @@
     </row>
     <row r="928" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A928" s="29" t="s">
-        <v>2346</v>
+        <v>2331</v>
       </c>
       <c r="B928" s="112"/>
       <c r="C928" s="82"/>
@@ -47737,18 +47733,18 @@
     </row>
     <row r="929" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A929" s="29" t="s">
-        <v>2349</v>
+        <v>2334</v>
       </c>
       <c r="B929" s="80"/>
       <c r="C929" s="73"/>
       <c r="D929" s="84"/>
       <c r="E929" s="73"/>
       <c r="F929" s="31" t="s">
-        <v>2348</v>
+        <v>2333</v>
       </c>
       <c r="G929" s="31"/>
       <c r="H929" s="23" t="s">
-        <v>2347</v>
+        <v>2332</v>
       </c>
       <c r="I929" s="19" t="s">
         <v>110</v>
@@ -47757,14 +47753,14 @@
         <v>464</v>
       </c>
       <c r="K929" s="29" t="s">
-        <v>2350</v>
+        <v>2335</v>
       </c>
       <c r="L929" s="31"/>
       <c r="M929" s="29"/>
     </row>
     <row r="930" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A930" s="29" t="s">
-        <v>2352</v>
+        <v>2337</v>
       </c>
       <c r="B930" s="80"/>
       <c r="C930" s="73"/>
@@ -47784,14 +47780,14 @@
         <v>464</v>
       </c>
       <c r="K930" s="29" t="s">
-        <v>2351</v>
+        <v>2336</v>
       </c>
       <c r="L930" s="31"/>
       <c r="M930" s="29"/>
     </row>
     <row r="931" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A931" s="29" t="s">
-        <v>2355</v>
+        <v>2340</v>
       </c>
       <c r="B931" s="80"/>
       <c r="C931" s="73"/>
@@ -47802,21 +47798,21 @@
       </c>
       <c r="G931" s="31"/>
       <c r="H931" s="23" t="s">
-        <v>2353</v>
+        <v>2338</v>
       </c>
       <c r="I931" s="19" t="s">
         <v>110</v>
       </c>
       <c r="J931" s="29"/>
       <c r="K931" s="29" t="s">
-        <v>2354</v>
+        <v>2339</v>
       </c>
       <c r="L931" s="31"/>
       <c r="M931" s="29"/>
     </row>
     <row r="932" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A932" s="29" t="s">
-        <v>2359</v>
+        <v>2344</v>
       </c>
       <c r="B932" s="80"/>
       <c r="C932" s="73"/>
@@ -47841,7 +47837,7 @@
     </row>
     <row r="933" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A933" s="29" t="s">
-        <v>2360</v>
+        <v>2345</v>
       </c>
       <c r="B933" s="80"/>
       <c r="C933" s="73"/>
@@ -47866,7 +47862,7 @@
     </row>
     <row r="934" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A934" s="29" t="s">
-        <v>2361</v>
+        <v>2346</v>
       </c>
       <c r="B934" s="80"/>
       <c r="C934" s="73"/>
@@ -47877,10 +47873,10 @@
       </c>
       <c r="G934" s="31"/>
       <c r="H934" s="23" t="s">
-        <v>2362</v>
+        <v>2347</v>
       </c>
       <c r="I934" s="19" t="s">
-        <v>2363</v>
+        <v>2348</v>
       </c>
       <c r="J934" s="29" t="s">
         <v>464</v>
@@ -47891,18 +47887,18 @@
     </row>
     <row r="935" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A935" s="29" t="s">
-        <v>2367</v>
+        <v>2352</v>
       </c>
       <c r="B935" s="80"/>
       <c r="C935" s="73"/>
       <c r="D935" s="84"/>
       <c r="E935" s="73"/>
       <c r="F935" s="31" t="s">
-        <v>2365</v>
+        <v>2350</v>
       </c>
       <c r="G935" s="31"/>
       <c r="H935" s="23" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="I935" s="19" t="s">
         <v>110</v>
@@ -47911,21 +47907,21 @@
         <v>464</v>
       </c>
       <c r="K935" s="29" t="s">
-        <v>2366</v>
+        <v>2351</v>
       </c>
       <c r="L935" s="31"/>
       <c r="M935" s="29"/>
     </row>
     <row r="936" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A936" s="29" t="s">
-        <v>2368</v>
+        <v>2353</v>
       </c>
       <c r="B936" s="80"/>
       <c r="C936" s="73"/>
       <c r="D936" s="84"/>
       <c r="E936" s="73"/>
       <c r="F936" s="31" t="s">
-        <v>2369</v>
+        <v>2354</v>
       </c>
       <c r="G936" s="31"/>
       <c r="H936" s="23">
@@ -47943,7 +47939,7 @@
     </row>
     <row r="937" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A937" s="29" t="s">
-        <v>2370</v>
+        <v>2355</v>
       </c>
       <c r="B937" s="80"/>
       <c r="C937" s="73"/>
@@ -47954,7 +47950,7 @@
       </c>
       <c r="G937" s="31"/>
       <c r="H937" s="23" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="I937" s="19" t="s">
         <v>110</v>
@@ -47968,7 +47964,7 @@
     </row>
     <row r="938" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A938" s="29" t="s">
-        <v>2371</v>
+        <v>2356</v>
       </c>
       <c r="B938" s="80"/>
       <c r="C938" s="73"/>
@@ -47979,7 +47975,7 @@
       </c>
       <c r="G938" s="31"/>
       <c r="H938" s="23" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="I938" s="19" t="s">
         <v>110</v>
@@ -47993,7 +47989,7 @@
     </row>
     <row r="939" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A939" s="29" t="s">
-        <v>2372</v>
+        <v>2357</v>
       </c>
       <c r="B939" s="80"/>
       <c r="C939" s="73"/>
@@ -48004,7 +48000,7 @@
       </c>
       <c r="G939" s="31"/>
       <c r="H939" s="23" t="s">
-        <v>2364</v>
+        <v>2349</v>
       </c>
       <c r="I939" s="19" t="s">
         <v>110</v>
@@ -48018,14 +48014,14 @@
     </row>
     <row r="940" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A940" s="29" t="s">
-        <v>2373</v>
+        <v>2358</v>
       </c>
       <c r="B940" s="80"/>
       <c r="C940" s="73"/>
       <c r="D940" s="84"/>
       <c r="E940" s="73"/>
       <c r="F940" s="31" t="s">
-        <v>2374</v>
+        <v>2359</v>
       </c>
       <c r="G940" s="31"/>
       <c r="H940" s="23" t="s">
@@ -48043,14 +48039,14 @@
     </row>
     <row r="941" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A941" s="29" t="s">
-        <v>2375</v>
+        <v>2360</v>
       </c>
       <c r="B941" s="112"/>
       <c r="C941" s="82"/>
       <c r="D941" s="79"/>
       <c r="E941" s="82"/>
       <c r="F941" s="31" t="s">
-        <v>2374</v>
+        <v>2359</v>
       </c>
       <c r="G941" s="31"/>
       <c r="H941" s="23" t="s">
@@ -48068,7 +48064,7 @@
     </row>
     <row r="942" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>2343</v>
+        <v>2328</v>
       </c>
       <c r="B942" s="113"/>
       <c r="C942" s="113"/>
@@ -48095,16 +48091,16 @@
     </row>
     <row r="943" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A943" s="29" t="s">
-        <v>2534</v>
+        <v>2519</v>
       </c>
       <c r="B943" s="101" t="s">
-        <v>2533</v>
+        <v>2518</v>
       </c>
       <c r="C943" s="82" t="s">
         <v>1353</v>
       </c>
       <c r="D943" s="79" t="s">
-        <v>2535</v>
+        <v>2520</v>
       </c>
       <c r="E943" s="82" t="s">
         <v>1190</v>
@@ -48113,7 +48109,7 @@
         <v>1355</v>
       </c>
       <c r="G943" s="31" t="s">
-        <v>2536</v>
+        <v>2521</v>
       </c>
       <c r="H943" s="23">
         <v>0</v>
@@ -48128,16 +48124,16 @@
     </row>
     <row r="944" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A944" s="29" t="s">
-        <v>2538</v>
+        <v>2523</v>
       </c>
       <c r="B944" s="101" t="s">
-        <v>2533</v>
+        <v>2518</v>
       </c>
       <c r="C944" s="82" t="s">
-        <v>2537</v>
+        <v>2522</v>
       </c>
       <c r="D944" s="79" t="s">
-        <v>2539</v>
+        <v>2524</v>
       </c>
       <c r="E944" s="82" t="s">
         <v>1190</v>
@@ -48146,7 +48142,7 @@
         <v>1355</v>
       </c>
       <c r="G944" s="31" t="s">
-        <v>2536</v>
+        <v>2521</v>
       </c>
       <c r="H944" s="23">
         <v>0</v>
@@ -48161,10 +48157,10 @@
     </row>
     <row r="945" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A945" s="29" t="s">
-        <v>2578</v>
+        <v>2563</v>
       </c>
       <c r="B945" s="112" t="s">
-        <v>2559</v>
+        <v>2544</v>
       </c>
       <c r="C945" s="82" t="s">
         <v>520</v>
@@ -48173,7 +48169,7 @@
         <v>1249</v>
       </c>
       <c r="E945" s="82" t="s">
-        <v>2560</v>
+        <v>2545</v>
       </c>
       <c r="F945" s="31" t="s">
         <v>1764</v>
@@ -48196,10 +48192,10 @@
     </row>
     <row r="946" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A946" s="29" t="s">
-        <v>2579</v>
+        <v>2564</v>
       </c>
       <c r="B946" s="112" t="s">
-        <v>2559</v>
+        <v>2544</v>
       </c>
       <c r="C946" s="82" t="s">
         <v>522</v>
@@ -48208,7 +48204,7 @@
         <v>1249</v>
       </c>
       <c r="E946" s="82" t="s">
-        <v>2561</v>
+        <v>2546</v>
       </c>
       <c r="F946" s="31" t="s">
         <v>1764</v>
@@ -48231,10 +48227,10 @@
     </row>
     <row r="947" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A947" s="29" t="s">
-        <v>2580</v>
+        <v>2565</v>
       </c>
       <c r="B947" s="100" t="s">
-        <v>2559</v>
+        <v>2544</v>
       </c>
       <c r="C947" s="83" t="s">
         <v>876</v>
@@ -48243,7 +48239,7 @@
         <v>1249</v>
       </c>
       <c r="E947" s="83" t="s">
-        <v>2562</v>
+        <v>2547</v>
       </c>
       <c r="F947" s="31" t="s">
         <v>1764</v>
@@ -48266,10 +48262,10 @@
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A948" s="29" t="s">
-        <v>2581</v>
+        <v>2566</v>
       </c>
       <c r="B948" s="100" t="s">
-        <v>2559</v>
+        <v>2544</v>
       </c>
       <c r="C948" s="83" t="s">
         <v>875</v>
@@ -48278,7 +48274,7 @@
         <v>1249</v>
       </c>
       <c r="E948" s="83" t="s">
-        <v>2563</v>
+        <v>2548</v>
       </c>
       <c r="F948" s="31" t="s">
         <v>1764</v>
@@ -48301,7 +48297,7 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A949" s="29" t="s">
-        <v>2582</v>
+        <v>2567</v>
       </c>
       <c r="B949" s="100" t="s">
         <v>357</v>
@@ -48313,7 +48309,7 @@
         <v>1249</v>
       </c>
       <c r="E949" s="83" t="s">
-        <v>2564</v>
+        <v>2549</v>
       </c>
       <c r="F949" s="31" t="s">
         <v>1764</v>
@@ -48336,7 +48332,7 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A950" s="29" t="s">
-        <v>2583</v>
+        <v>2568</v>
       </c>
       <c r="B950" s="100" t="s">
         <v>357</v>
@@ -48348,7 +48344,7 @@
         <v>1249</v>
       </c>
       <c r="E950" s="83" t="s">
-        <v>2565</v>
+        <v>2550</v>
       </c>
       <c r="F950" s="31" t="s">
         <v>1764</v>
@@ -48371,7 +48367,7 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A951" s="29" t="s">
-        <v>2584</v>
+        <v>2569</v>
       </c>
       <c r="B951" s="100" t="s">
         <v>357</v>
@@ -48383,7 +48379,7 @@
         <v>1249</v>
       </c>
       <c r="E951" s="83" t="s">
-        <v>2566</v>
+        <v>2551</v>
       </c>
       <c r="F951" s="31" t="s">
         <v>1764</v>
@@ -48406,7 +48402,7 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A952" s="29" t="s">
-        <v>2585</v>
+        <v>2570</v>
       </c>
       <c r="B952" s="100" t="s">
         <v>357</v>
@@ -48418,7 +48414,7 @@
         <v>1249</v>
       </c>
       <c r="E952" s="83" t="s">
-        <v>2567</v>
+        <v>2552</v>
       </c>
       <c r="F952" s="31" t="s">
         <v>1764</v>
@@ -48441,7 +48437,7 @@
     </row>
     <row r="953" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A953" s="29" t="s">
-        <v>2586</v>
+        <v>2571</v>
       </c>
       <c r="B953" s="100" t="s">
         <v>358</v>
@@ -48453,7 +48449,7 @@
         <v>1249</v>
       </c>
       <c r="E953" s="83" t="s">
-        <v>2568</v>
+        <v>2553</v>
       </c>
       <c r="F953" s="31" t="s">
         <v>1764</v>
@@ -48476,7 +48472,7 @@
     </row>
     <row r="954" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A954" s="29" t="s">
-        <v>2587</v>
+        <v>2572</v>
       </c>
       <c r="B954" s="112" t="s">
         <v>358</v>
@@ -48488,7 +48484,7 @@
         <v>1249</v>
       </c>
       <c r="E954" s="82" t="s">
-        <v>2569</v>
+        <v>2554</v>
       </c>
       <c r="F954" s="31" t="s">
         <v>1764</v>
@@ -48511,7 +48507,7 @@
     </row>
     <row r="955" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A955" s="29" t="s">
-        <v>2588</v>
+        <v>2573</v>
       </c>
       <c r="B955" s="100" t="s">
         <v>358</v>
@@ -48523,7 +48519,7 @@
         <v>1249</v>
       </c>
       <c r="E955" s="83" t="s">
-        <v>2570</v>
+        <v>2555</v>
       </c>
       <c r="F955" s="31" t="s">
         <v>1764</v>
@@ -48546,7 +48542,7 @@
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A956" s="29" t="s">
-        <v>2589</v>
+        <v>2574</v>
       </c>
       <c r="B956" s="100" t="s">
         <v>358</v>
@@ -48558,7 +48554,7 @@
         <v>1249</v>
       </c>
       <c r="E956" s="83" t="s">
-        <v>2571</v>
+        <v>2556</v>
       </c>
       <c r="F956" s="31" t="s">
         <v>1764</v>
@@ -48581,7 +48577,7 @@
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A957" s="29" t="s">
-        <v>2590</v>
+        <v>2575</v>
       </c>
       <c r="B957" s="100" t="s">
         <v>359</v>
@@ -48593,7 +48589,7 @@
         <v>1249</v>
       </c>
       <c r="E957" s="83" t="s">
-        <v>2572</v>
+        <v>2557</v>
       </c>
       <c r="F957" s="31" t="s">
         <v>1764</v>
@@ -48616,7 +48612,7 @@
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A958" s="29" t="s">
-        <v>2591</v>
+        <v>2576</v>
       </c>
       <c r="B958" s="100" t="s">
         <v>359</v>
@@ -48628,7 +48624,7 @@
         <v>1249</v>
       </c>
       <c r="E958" s="83" t="s">
-        <v>2573</v>
+        <v>2558</v>
       </c>
       <c r="F958" s="31" t="s">
         <v>1764</v>
@@ -48643,7 +48639,7 @@
         <v>71</v>
       </c>
       <c r="J958" s="29" t="s">
-        <v>2576</v>
+        <v>2561</v>
       </c>
       <c r="K958" s="29"/>
       <c r="L958" s="31"/>
@@ -48651,7 +48647,7 @@
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A959" s="29" t="s">
-        <v>2592</v>
+        <v>2577</v>
       </c>
       <c r="B959" s="100" t="s">
         <v>359</v>
@@ -48663,7 +48659,7 @@
         <v>1249</v>
       </c>
       <c r="E959" s="83" t="s">
-        <v>2574</v>
+        <v>2559</v>
       </c>
       <c r="F959" s="31" t="s">
         <v>1764</v>
@@ -48678,7 +48674,7 @@
         <v>71</v>
       </c>
       <c r="J959" s="29" t="s">
-        <v>2577</v>
+        <v>2562</v>
       </c>
       <c r="K959" s="29"/>
       <c r="L959" s="31"/>
@@ -48686,7 +48682,7 @@
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A960" s="29" t="s">
-        <v>2593</v>
+        <v>2578</v>
       </c>
       <c r="B960" s="100" t="s">
         <v>359</v>
@@ -48698,7 +48694,7 @@
         <v>1249</v>
       </c>
       <c r="E960" s="83" t="s">
-        <v>2575</v>
+        <v>2560</v>
       </c>
       <c r="F960" s="31" t="s">
         <v>1764</v>
@@ -48724,11 +48720,11 @@
         <v>1253</v>
       </c>
       <c r="B961" s="100" t="s">
-        <v>2609</v>
+        <v>2594</v>
       </c>
       <c r="C961" s="83"/>
       <c r="D961" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E961" s="83" t="s">
         <v>519</v>
@@ -48738,7 +48734,7 @@
       <c r="H961" s="29"/>
       <c r="I961" s="119"/>
       <c r="J961" s="35" t="s">
-        <v>2595</v>
+        <v>2580</v>
       </c>
       <c r="K961" s="29"/>
       <c r="L961" s="31"/>
@@ -48751,7 +48747,7 @@
       <c r="B962" s="100"/>
       <c r="C962" s="83"/>
       <c r="D962" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E962" s="83" t="s">
         <v>524</v>
@@ -48761,7 +48757,7 @@
       <c r="H962" s="29"/>
       <c r="I962" s="119"/>
       <c r="J962" s="35" t="s">
-        <v>2595</v>
+        <v>2580</v>
       </c>
       <c r="K962" s="29"/>
       <c r="L962" s="31"/>
@@ -48772,11 +48768,11 @@
         <v>1256</v>
       </c>
       <c r="B963" s="100" t="s">
-        <v>2605</v>
+        <v>2590</v>
       </c>
       <c r="C963" s="83"/>
       <c r="D963" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E963" s="83" t="s">
         <v>871</v>
@@ -48786,7 +48782,7 @@
       <c r="H963" s="29"/>
       <c r="I963" s="119"/>
       <c r="J963" s="33" t="s">
-        <v>2596</v>
+        <v>2581</v>
       </c>
       <c r="K963" s="29"/>
       <c r="L963" s="31"/>
@@ -48797,11 +48793,11 @@
         <v>1258</v>
       </c>
       <c r="B964" s="100" t="s">
-        <v>2606</v>
+        <v>2591</v>
       </c>
       <c r="C964" s="83"/>
       <c r="D964" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E964" s="83" t="s">
         <v>872</v>
@@ -48811,7 +48807,7 @@
       <c r="H964" s="29"/>
       <c r="I964" s="119"/>
       <c r="J964" s="33" t="s">
-        <v>2596</v>
+        <v>2581</v>
       </c>
       <c r="K964" s="29"/>
       <c r="L964" s="31"/>
@@ -48819,15 +48815,15 @@
     </row>
     <row r="965" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A965" s="29" t="s">
-        <v>2604</v>
+        <v>2589</v>
       </c>
       <c r="B965" s="100"/>
       <c r="C965" s="83"/>
       <c r="D965" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E965" s="83" t="s">
-        <v>2356</v>
+        <v>2341</v>
       </c>
       <c r="F965" s="31"/>
       <c r="G965" s="31"/>
@@ -48842,15 +48838,15 @@
     </row>
     <row r="966" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>2603</v>
+        <v>2588</v>
       </c>
       <c r="B966" s="112"/>
       <c r="C966" s="120"/>
       <c r="D966" s="79" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E966" s="80" t="s">
-        <v>2599</v>
+        <v>2584</v>
       </c>
       <c r="F966" s="31"/>
       <c r="G966" s="31"/>
@@ -48868,21 +48864,21 @@
         <v>1738</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>2607</v>
+        <v>2592</v>
       </c>
       <c r="C967" s="121"/>
       <c r="D967" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E967" s="69" t="s">
-        <v>2600</v>
+        <v>2585</v>
       </c>
       <c r="F967" s="31"/>
       <c r="G967" s="31"/>
       <c r="H967" s="29"/>
       <c r="I967" s="119"/>
       <c r="J967" s="33" t="s">
-        <v>2597</v>
+        <v>2582</v>
       </c>
       <c r="K967" s="29"/>
       <c r="L967" s="31"/>
@@ -48890,24 +48886,24 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>2602</v>
+        <v>2587</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>2608</v>
+        <v>2593</v>
       </c>
       <c r="C968" s="122"/>
       <c r="D968" s="85" t="s">
-        <v>2594</v>
+        <v>2579</v>
       </c>
       <c r="E968" s="124" t="s">
-        <v>2601</v>
+        <v>2586</v>
       </c>
       <c r="F968" s="31"/>
       <c r="G968" s="31"/>
       <c r="H968" s="29"/>
       <c r="I968" s="119"/>
       <c r="J968" s="35" t="s">
-        <v>2598</v>
+        <v>2583</v>
       </c>
       <c r="K968" s="29"/>
       <c r="L968" s="31"/>
@@ -48915,19 +48911,19 @@
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="B969" s="15" t="s">
         <v>1460</v>
       </c>
       <c r="D969" s="15" t="s">
-        <v>2556</v>
+        <v>2541</v>
       </c>
       <c r="F969" t="s">
         <v>1764</v>
       </c>
       <c r="G969" t="s">
-        <v>2557</v>
+        <v>2542</v>
       </c>
       <c r="H969" t="s">
         <v>1356</v>
@@ -48936,7 +48932,7 @@
         <v>71</v>
       </c>
       <c r="J969" t="s">
-        <v>2558</v>
+        <v>2543</v>
       </c>
       <c r="K969" s="29"/>
       <c r="L969" s="31"/>
@@ -48944,25 +48940,25 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A970" s="29" t="s">
-        <v>2631</v>
+        <v>2616</v>
       </c>
       <c r="B970" s="100" t="s">
         <v>1043</v>
       </c>
       <c r="C970" s="123" t="s">
-        <v>2628</v>
+        <v>2613</v>
       </c>
       <c r="D970" s="85" t="s">
         <v>1249</v>
       </c>
       <c r="E970" s="83" t="s">
-        <v>2627</v>
+        <v>2612</v>
       </c>
       <c r="F970" s="31" t="s">
         <v>1764</v>
       </c>
       <c r="G970" s="31" t="s">
-        <v>2629</v>
+        <v>2614</v>
       </c>
       <c r="H970" s="29">
         <v>0</v>
@@ -48971,7 +48967,7 @@
         <v>71</v>
       </c>
       <c r="J970" s="29" t="s">
-        <v>2630</v>
+        <v>2615</v>
       </c>
       <c r="K970" s="29"/>
       <c r="L970" s="31"/>
@@ -48979,7 +48975,7 @@
     </row>
     <row r="971" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A971" s="29" t="s">
-        <v>2635</v>
+        <v>2620</v>
       </c>
       <c r="B971" s="112" t="s">
         <v>1134</v>
@@ -48988,7 +48984,7 @@
         <v>1227</v>
       </c>
       <c r="D971" s="79" t="s">
-        <v>2632</v>
+        <v>2617</v>
       </c>
       <c r="E971" s="82" t="s">
         <v>230</v>
@@ -49000,23 +48996,23 @@
         <v>35</v>
       </c>
       <c r="H971" s="23" t="s">
-        <v>2636</v>
+        <v>2621</v>
       </c>
       <c r="I971" s="19" t="s">
         <v>110</v>
       </c>
       <c r="J971" s="29" t="s">
-        <v>2634</v>
+        <v>2619</v>
       </c>
       <c r="K971" s="29"/>
       <c r="L971" s="31" t="s">
-        <v>2637</v>
+        <v>2622</v>
       </c>
       <c r="M971" s="29"/>
     </row>
     <row r="972" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A972" s="29" t="s">
-        <v>2658</v>
+        <v>2642</v>
       </c>
       <c r="B972" s="100" t="s">
         <v>1911</v>
@@ -49025,10 +49021,10 @@
         <v>1365</v>
       </c>
       <c r="D972" s="85" t="s">
-        <v>2651</v>
+        <v>2635</v>
       </c>
       <c r="E972" s="83" t="s">
-        <v>2659</v>
+        <v>2643</v>
       </c>
       <c r="F972" s="31" t="s">
         <v>247</v>
@@ -49041,7 +49037,7 @@
         <v>71</v>
       </c>
       <c r="J972" s="29" t="s">
-        <v>2660</v>
+        <v>2644</v>
       </c>
       <c r="K972" s="29"/>
       <c r="L972" s="31"/>
@@ -49049,7 +49045,7 @@
     </row>
     <row r="973" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A973" s="29" t="s">
-        <v>2661</v>
+        <v>2645</v>
       </c>
       <c r="B973" s="100" t="s">
         <v>1911</v>
@@ -49058,10 +49054,10 @@
         <v>1366</v>
       </c>
       <c r="D973" s="79" t="s">
-        <v>2656</v>
+        <v>2640</v>
       </c>
       <c r="E973" s="82" t="s">
-        <v>2659</v>
+        <v>2643</v>
       </c>
       <c r="F973" s="31" t="s">
         <v>247</v>
@@ -49074,7 +49070,7 @@
         <v>71</v>
       </c>
       <c r="J973" s="29" t="s">
-        <v>2660</v>
+        <v>2644</v>
       </c>
       <c r="K973" s="29"/>
       <c r="L973" s="31"/>
@@ -49082,7 +49078,7 @@
     </row>
     <row r="974" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A974" s="29" t="s">
-        <v>2662</v>
+        <v>2646</v>
       </c>
       <c r="B974" s="100" t="s">
         <v>1911</v>
@@ -49094,7 +49090,7 @@
         <v>1865</v>
       </c>
       <c r="E974" s="83" t="s">
-        <v>2212</v>
+        <v>2197</v>
       </c>
       <c r="F974" s="31" t="s">
         <v>1889</v>
@@ -49115,7 +49111,7 @@
     </row>
     <row r="975" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A975" s="29" t="s">
-        <v>2663</v>
+        <v>2647</v>
       </c>
       <c r="B975" s="100" t="s">
         <v>1911</v>
@@ -49127,7 +49123,7 @@
         <v>1865</v>
       </c>
       <c r="E975" s="83" t="s">
-        <v>2214</v>
+        <v>2199</v>
       </c>
       <c r="F975" s="31" t="s">
         <v>1889</v>
@@ -49148,7 +49144,7 @@
     </row>
     <row r="976" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A976" s="29" t="s">
-        <v>2664</v>
+        <v>2648</v>
       </c>
       <c r="B976" s="100" t="s">
         <v>1911</v>
@@ -49160,7 +49156,7 @@
         <v>1865</v>
       </c>
       <c r="E976" s="83" t="s">
-        <v>2222</v>
+        <v>2207</v>
       </c>
       <c r="F976" s="31" t="s">
         <v>1889</v>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F12B49A-3C6C-CA41-BB2F-616945A94B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1087F3B-767F-F64F-9B35-222FFCEF60AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1540" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId3"/>
-    <pivotCache cacheId="29" r:id="rId4"/>
+    <pivotCache cacheId="31" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8936" uniqueCount="2798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9128" uniqueCount="2822">
   <si>
     <t>Tag</t>
   </si>
@@ -8435,6 +8435,78 @@
   </si>
   <si>
     <t>pt1097</t>
+  </si>
+  <si>
+    <t>pt1098</t>
+  </si>
+  <si>
+    <t>pt1099</t>
+  </si>
+  <si>
+    <t>pt1100</t>
+  </si>
+  <si>
+    <t>pt1101</t>
+  </si>
+  <si>
+    <t>pt1102</t>
+  </si>
+  <si>
+    <t>pt1103</t>
+  </si>
+  <si>
+    <t>pt1104</t>
+  </si>
+  <si>
+    <t>pt1105</t>
+  </si>
+  <si>
+    <t>pt1106</t>
+  </si>
+  <si>
+    <t>pt1107</t>
+  </si>
+  <si>
+    <t>pt1108</t>
+  </si>
+  <si>
+    <t>pt1109</t>
+  </si>
+  <si>
+    <t>pt1110</t>
+  </si>
+  <si>
+    <t>pt1111</t>
+  </si>
+  <si>
+    <t>pt1112</t>
+  </si>
+  <si>
+    <t>pt1113</t>
+  </si>
+  <si>
+    <t>pt1114</t>
+  </si>
+  <si>
+    <t>pt1115</t>
+  </si>
+  <si>
+    <t>pt1116</t>
+  </si>
+  <si>
+    <t>pt1117</t>
+  </si>
+  <si>
+    <t>pt1118</t>
+  </si>
+  <si>
+    <t>pt1119</t>
+  </si>
+  <si>
+    <t>pt1120</t>
+  </si>
+  <si>
+    <t>pt1121</t>
   </si>
 </sst>
 </file>
@@ -9579,7 +9651,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Terry Doner" refreshedDate="46030.710642245373" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="442" xr:uid="{966EC718-ADB8-7746-9366-54097C9D57FA}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M1097" sheet="Cables"/>
+    <worksheetSource ref="A1:M1121" sheet="Cables"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Tag" numFmtId="0">
@@ -17953,7 +18025,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="29" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18273,8 +18345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1098" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M1097" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1122" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+  <autoFilter ref="A1:M1121" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
@@ -18591,7 +18663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B91ADC-4569-1C4E-B002-1ED2E647C959}">
-  <dimension ref="A1:W1098"/>
+  <dimension ref="A1:W1122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -53524,7 +53596,7 @@
       <c r="L1096" s="125"/>
       <c r="M1096" s="29"/>
     </row>
-    <row r="1097" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1097" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1097" s="29" t="s">
         <v>2797</v>
       </c>
@@ -53557,10 +53629,802 @@
       <c r="L1097" s="125"/>
       <c r="M1097" s="29"/>
     </row>
-    <row r="1098" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1098" s="83"/>
-      <c r="K1098" s="113"/>
-      <c r="L1098" s="3"/>
+    <row r="1098" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1098" s="29" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B1098" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1098" s="82" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D1098" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1098" s="82" t="s">
+        <v>2562</v>
+      </c>
+      <c r="F1098" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1098" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1098" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1098" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1098" s="129"/>
+      <c r="K1098" s="129"/>
+      <c r="L1098" s="130"/>
+      <c r="M1098" s="129"/>
+    </row>
+    <row r="1099" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1099" s="29" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B1099" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1099" s="82" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D1099" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1099" s="82" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F1099" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1099" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1099" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1099" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1099" s="29"/>
+      <c r="K1099" s="29"/>
+      <c r="L1099" s="125"/>
+      <c r="M1099" s="29"/>
+    </row>
+    <row r="1100" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1100" s="29" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B1100" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1100" s="82" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D1100" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1100" s="82" t="s">
+        <v>2564</v>
+      </c>
+      <c r="F1100" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1100" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1100" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1100" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1100" s="29"/>
+      <c r="K1100" s="29"/>
+      <c r="L1100" s="125"/>
+      <c r="M1100" s="29"/>
+    </row>
+    <row r="1101" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1101" s="29" t="s">
+        <v>2801</v>
+      </c>
+      <c r="B1101" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1101" s="82" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D1101" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1101" s="82" t="s">
+        <v>2565</v>
+      </c>
+      <c r="F1101" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1101" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1101" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1101" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1101" s="29"/>
+      <c r="K1101" s="29"/>
+      <c r="L1101" s="125"/>
+      <c r="M1101" s="29"/>
+    </row>
+    <row r="1102" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1102" s="29" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B1102" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1102" s="82" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D1102" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1102" s="82" t="s">
+        <v>2561</v>
+      </c>
+      <c r="F1102" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1102" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1102" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1102" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1102" s="29"/>
+      <c r="K1102" s="29"/>
+      <c r="L1102" s="125"/>
+      <c r="M1102" s="29"/>
+    </row>
+    <row r="1103" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1103" s="29" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B1103" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1103" s="82" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1103" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1103" s="82" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F1103" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1103" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1103" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1103" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1103" s="29"/>
+      <c r="K1103" s="29"/>
+      <c r="L1103" s="125"/>
+      <c r="M1103" s="29"/>
+    </row>
+    <row r="1104" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1104" s="29" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B1104" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1104" s="82" t="s">
+        <v>2567</v>
+      </c>
+      <c r="D1104" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1104" s="82" t="s">
+        <v>2558</v>
+      </c>
+      <c r="F1104" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1104" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1104" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1104" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1104" s="29"/>
+      <c r="K1104" s="29"/>
+      <c r="L1104" s="125"/>
+      <c r="M1104" s="29"/>
+    </row>
+    <row r="1105" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1105" s="29" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B1105" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1105" s="82" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D1105" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1105" s="82" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F1105" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1105" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1105" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1105" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1105" s="29"/>
+      <c r="K1105" s="29"/>
+      <c r="L1105" s="125"/>
+      <c r="M1105" s="29"/>
+    </row>
+    <row r="1106" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1106" s="29" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B1106" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1106" s="82" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D1106" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1106" s="82" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F1106" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1106" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1106" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1106" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1106" s="29"/>
+      <c r="K1106" s="29"/>
+      <c r="L1106" s="125"/>
+      <c r="M1106" s="29"/>
+    </row>
+    <row r="1107" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1107" s="29" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B1107" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1107" s="82" t="s">
+        <v>2569</v>
+      </c>
+      <c r="D1107" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1107" s="82" t="s">
+        <v>2663</v>
+      </c>
+      <c r="F1107" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1107" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1107" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1107" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1107" s="29"/>
+      <c r="K1107" s="29"/>
+      <c r="L1107" s="125"/>
+      <c r="M1107" s="29"/>
+    </row>
+    <row r="1108" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1108" s="29" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B1108" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1108" s="82" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D1108" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1108" s="82" t="s">
+        <v>2109</v>
+      </c>
+      <c r="F1108" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1108" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1108" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1108" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1108" s="29"/>
+      <c r="K1108" s="29"/>
+      <c r="L1108" s="125"/>
+      <c r="M1108" s="29"/>
+    </row>
+    <row r="1109" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1109" s="29" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B1109" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1109" s="82" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D1109" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1109" s="82" t="s">
+        <v>2543</v>
+      </c>
+      <c r="F1109" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1109" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1109" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1109" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1109" s="29"/>
+      <c r="K1109" s="29"/>
+      <c r="L1109" s="125"/>
+      <c r="M1109" s="29"/>
+    </row>
+    <row r="1110" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1110" s="29" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B1110" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1110" s="82" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D1110" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1110" s="82" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F1110" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1110" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1110" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1110" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1110" s="29"/>
+      <c r="K1110" s="29"/>
+      <c r="L1110" s="125"/>
+      <c r="M1110" s="29"/>
+    </row>
+    <row r="1111" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1111" s="29" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1111" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1111" s="82" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D1111" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1111" s="82" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F1111" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1111" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1111" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1111" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1111" s="29"/>
+      <c r="K1111" s="29"/>
+      <c r="L1111" s="125"/>
+      <c r="M1111" s="29"/>
+    </row>
+    <row r="1112" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1112" s="29" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B1112" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1112" s="82" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D1112" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1112" s="82" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F1112" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1112" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1112" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1112" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1112" s="29"/>
+      <c r="K1112" s="29"/>
+      <c r="L1112" s="125"/>
+      <c r="M1112" s="29"/>
+    </row>
+    <row r="1113" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1113" s="29" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1113" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1113" s="82" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D1113" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1113" s="82" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F1113" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1113" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1113" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1113" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1113" s="29"/>
+      <c r="K1113" s="29"/>
+      <c r="L1113" s="125"/>
+      <c r="M1113" s="29"/>
+    </row>
+    <row r="1114" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1114" s="29" t="s">
+        <v>2814</v>
+      </c>
+      <c r="B1114" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1114" s="82" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D1114" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1114" s="82" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1114" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1114" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1114" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1114" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1114" s="29"/>
+      <c r="K1114" s="29"/>
+      <c r="L1114" s="125"/>
+      <c r="M1114" s="29"/>
+    </row>
+    <row r="1115" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1115" s="29" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B1115" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1115" s="82" t="s">
+        <v>2671</v>
+      </c>
+      <c r="D1115" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1115" s="82" t="s">
+        <v>2664</v>
+      </c>
+      <c r="F1115" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1115" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1115" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1115" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1115" s="29"/>
+      <c r="K1115" s="29"/>
+      <c r="L1115" s="125"/>
+      <c r="M1115" s="29"/>
+    </row>
+    <row r="1116" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1116" s="29" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B1116" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1116" s="82" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D1116" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1116" s="82" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F1116" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1116" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1116" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1116" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1116" s="29"/>
+      <c r="K1116" s="29"/>
+      <c r="L1116" s="125"/>
+      <c r="M1116" s="29"/>
+    </row>
+    <row r="1117" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1117" s="29" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B1117" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1117" s="82" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D1117" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1117" s="82" t="s">
+        <v>2666</v>
+      </c>
+      <c r="F1117" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1117" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1117" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1117" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1117" s="29"/>
+      <c r="K1117" s="29"/>
+      <c r="L1117" s="125"/>
+      <c r="M1117" s="29"/>
+    </row>
+    <row r="1118" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1118" s="29" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B1118" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1118" s="82" t="s">
+        <v>2674</v>
+      </c>
+      <c r="D1118" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1118" s="82" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F1118" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1118" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1118" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1118" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1118" s="29"/>
+      <c r="K1118" s="29"/>
+      <c r="L1118" s="125"/>
+      <c r="M1118" s="29"/>
+    </row>
+    <row r="1119" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1119" s="29" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B1119" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1119" s="82" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D1119" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1119" s="82" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F1119" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1119" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1119" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1119" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1119" s="29"/>
+      <c r="K1119" s="29"/>
+      <c r="L1119" s="125"/>
+      <c r="M1119" s="29"/>
+    </row>
+    <row r="1120" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1120" s="29" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B1120" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1120" s="82" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D1120" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1120" s="82" t="s">
+        <v>2669</v>
+      </c>
+      <c r="F1120" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1120" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1120" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1120" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1120" s="29"/>
+      <c r="K1120" s="29"/>
+      <c r="L1120" s="125"/>
+      <c r="M1120" s="29"/>
+    </row>
+    <row r="1121" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1121" s="29" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B1121" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1121" s="82" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D1121" s="112" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E1121" s="82" t="s">
+        <v>2670</v>
+      </c>
+      <c r="F1121" s="125" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G1121" s="125" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H1121" s="126">
+        <v>0</v>
+      </c>
+      <c r="I1121" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1121" s="29"/>
+      <c r="K1121" s="29"/>
+      <c r="L1121" s="125"/>
+      <c r="M1121" s="29"/>
+    </row>
+    <row r="1122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B1122" s="83"/>
+      <c r="K1122" s="113"/>
+      <c r="L1122" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1087F3B-767F-F64F-9B35-222FFCEF60AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D82C1B-214D-C84C-9020-06D0DB94ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1540" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9128" uniqueCount="2822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9138" uniqueCount="2825">
   <si>
     <t>Tag</t>
   </si>
@@ -8507,6 +8507,15 @@
   </si>
   <si>
     <t>pt1121</t>
+  </si>
+  <si>
+    <t>2602-2800</t>
+  </si>
+  <si>
+    <t>undoc877</t>
+  </si>
+  <si>
+    <t>Need to record cable id</t>
   </si>
 </sst>
 </file>
@@ -46439,17 +46448,37 @@
       <c r="M876" s="29"/>
     </row>
     <row r="877" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A877" s="29"/>
-      <c r="B877" s="83"/>
-      <c r="C877" s="83"/>
-      <c r="D877" s="85"/>
-      <c r="E877" s="83"/>
-      <c r="F877" s="31"/>
-      <c r="G877" s="31"/>
-      <c r="H877" s="29"/>
-      <c r="I877" s="29"/>
+      <c r="A877" s="29" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B877" s="83" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C877" s="83" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D877" s="85" t="s">
+        <v>2822</v>
+      </c>
+      <c r="E877" s="83" t="s">
+        <v>359</v>
+      </c>
+      <c r="F877" s="31" t="s">
+        <v>1706</v>
+      </c>
+      <c r="G877" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H877" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="I877" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="J877" s="29"/>
-      <c r="K877" s="29"/>
+      <c r="K877" s="29" t="s">
+        <v>2824</v>
+      </c>
       <c r="L877" s="31"/>
       <c r="M877" s="29"/>
     </row>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D82C1B-214D-C84C-9020-06D0DB94ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D060BD4-17E1-7245-8979-8081A6D8AEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1540" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9138" uniqueCount="2825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9138" uniqueCount="2824">
   <si>
     <t>Tag</t>
   </si>
@@ -8507,9 +8507,6 @@
   </si>
   <si>
     <t>pt1121</t>
-  </si>
-  <si>
-    <t>2602-2800</t>
   </si>
   <si>
     <t>undoc877</t>
@@ -46449,7 +46446,7 @@
     </row>
     <row r="877" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A877" s="29" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="B877" s="83" t="s">
         <v>1121</v>
@@ -46458,7 +46455,7 @@
         <v>1758</v>
       </c>
       <c r="D877" s="85" t="s">
-        <v>2822</v>
+        <v>1123</v>
       </c>
       <c r="E877" s="83" t="s">
         <v>359</v>
@@ -46477,7 +46474,7 @@
       </c>
       <c r="J877" s="29"/>
       <c r="K877" s="29" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="L877" s="31"/>
       <c r="M877" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB3EC3D-F758-C044-ADCB-215F8A18BB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E2EEBD-7308-5C46-9195-6262185D5291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1520" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9897" uniqueCount="2945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9861" uniqueCount="2941">
   <si>
     <t>Tag</t>
   </si>
@@ -8710,9 +8710,6 @@
     <t>Core</t>
   </si>
   <si>
-    <t>W-CAT6-060</t>
-  </si>
-  <si>
     <t>W-Cat6-060</t>
   </si>
   <si>
@@ -8744,15 +8741,6 @@
   </si>
   <si>
     <t>notag1176</t>
-  </si>
-  <si>
-    <t>W-CAT6-061</t>
-  </si>
-  <si>
-    <t>W-CAT6-062</t>
-  </si>
-  <si>
-    <t>W-CAT6-063</t>
   </si>
   <si>
     <t>W-CAT6-064</t>
@@ -10031,7 +10019,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Terry Doner" refreshedDate="46030.710642245373" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="442" xr:uid="{966EC718-ADB8-7746-9366-54097C9D57FA}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M1325" sheet="Cables"/>
+    <worksheetSource ref="A1:M1321" sheet="Cables"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Tag" numFmtId="0">
@@ -18725,8 +18713,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1326" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M1325" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1322" totalsRowCount="1" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+  <autoFilter ref="A1:M1321" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="16" totalsRowDxfId="4"/>
@@ -19043,7 +19031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B91ADC-4569-1C4E-B002-1ED2E647C959}">
-  <dimension ref="A1:W1326"/>
+  <dimension ref="A1:W1322"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -32091,7 +32079,7 @@
     </row>
     <row r="424" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A424" s="29" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
       <c r="B424" s="31" t="s">
         <v>2735</v>
@@ -36091,7 +36079,7 @@
         <v>1823</v>
       </c>
       <c r="C542" s="82" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
       <c r="D542" s="70" t="s">
         <v>1167</v>
@@ -36120,7 +36108,7 @@
         <v>1823</v>
       </c>
       <c r="C543" s="36" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="D543" s="70" t="s">
         <v>1168</v>
@@ -56462,7 +56450,7 @@
     </row>
     <row r="1173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1173" s="29" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="B1173" s="135" t="s">
         <v>2860</v>
@@ -56493,7 +56481,7 @@
     </row>
     <row r="1174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="B1174" s="135" t="s">
         <v>2860</v>
@@ -56524,7 +56512,7 @@
     </row>
     <row r="1175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1175" s="29" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="B1175" s="135" t="s">
         <v>2860</v>
@@ -56555,7 +56543,7 @@
     </row>
     <row r="1176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="B1176" s="135" t="s">
         <v>2860</v>
@@ -56586,7 +56574,7 @@
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B1177" s="135" t="s">
         <v>2860</v>
@@ -56617,16 +56605,16 @@
     </row>
     <row r="1178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1178" s="29" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B1178" s="135" t="s">
         <v>2860</v>
       </c>
       <c r="C1178" s="125" t="s">
-        <v>2650</v>
+        <v>2657</v>
       </c>
       <c r="D1178" s="126" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1178" s="125" t="s">
         <v>2106</v>
@@ -56644,7 +56632,7 @@
         <v>63</v>
       </c>
       <c r="J1178" s="29" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="K1178" s="29"/>
       <c r="L1178" s="127"/>
@@ -56652,16 +56640,16 @@
     </row>
     <row r="1179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1179" s="29" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="B1179" s="135" t="s">
         <v>2860</v>
       </c>
       <c r="C1179" s="125" t="s">
-        <v>2651</v>
+        <v>2658</v>
       </c>
       <c r="D1179" s="126" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1179" s="125" t="s">
         <v>2657</v>
@@ -56679,7 +56667,7 @@
         <v>63</v>
       </c>
       <c r="J1179" s="29" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="K1179" s="29"/>
       <c r="L1179" s="127"/>
@@ -56687,16 +56675,16 @@
     </row>
     <row r="1180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1180" s="29" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B1180" s="135" t="s">
         <v>2860</v>
       </c>
       <c r="C1180" s="125" t="s">
-        <v>2652</v>
+        <v>2659</v>
       </c>
       <c r="D1180" s="126" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1180" s="125" t="s">
         <v>2658</v>
@@ -56714,7 +56702,7 @@
         <v>63</v>
       </c>
       <c r="J1180" s="29" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="K1180" s="29"/>
       <c r="L1180" s="127"/>
@@ -56722,16 +56710,16 @@
     </row>
     <row r="1181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1181" s="29" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="B1181" s="135" t="s">
         <v>2860</v>
       </c>
       <c r="C1181" s="125" t="s">
-        <v>2653</v>
+        <v>2660</v>
       </c>
       <c r="D1181" s="126" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1181" s="125" t="s">
         <v>2659</v>
@@ -56749,7 +56737,7 @@
         <v>63</v>
       </c>
       <c r="J1181" s="29" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="K1181" s="29"/>
       <c r="L1181" s="127"/>
@@ -56757,7 +56745,7 @@
     </row>
     <row r="1182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1182" s="29" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="B1182" s="135" t="s">
         <v>2860</v>
@@ -56774,7 +56762,7 @@
         <v>63</v>
       </c>
       <c r="J1182" s="29" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="K1182" s="29" t="s">
         <v>452</v>
@@ -56782,9 +56770,9 @@
       <c r="L1182" s="127"/>
       <c r="M1182" s="29"/>
     </row>
-    <row r="1183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1183" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="29" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="B1183" s="135" t="s">
         <v>2860</v>
@@ -56801,7 +56789,7 @@
         <v>63</v>
       </c>
       <c r="J1183" s="29" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="K1183" s="29" t="s">
         <v>452</v>
@@ -56809,21 +56797,21 @@
       <c r="L1183" s="127"/>
       <c r="M1183" s="29"/>
     </row>
-    <row r="1184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1184" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="29" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B1184" s="135" t="s">
-        <v>2860</v>
+        <v>2900</v>
+      </c>
+      <c r="B1184" s="126" t="s">
+        <v>2926</v>
       </c>
       <c r="C1184" s="125" t="s">
-        <v>2657</v>
-      </c>
-      <c r="D1184" s="126" t="s">
-        <v>2930</v>
+        <v>2660</v>
+      </c>
+      <c r="D1184" s="79" t="s">
+        <v>2735</v>
       </c>
       <c r="E1184" s="125" t="s">
-        <v>1341</v>
+        <v>2644</v>
       </c>
       <c r="F1184" s="127" t="s">
         <v>1800</v>
@@ -56838,7 +56826,9 @@
         <v>99</v>
       </c>
       <c r="J1184" s="29"/>
-      <c r="K1184" s="29"/>
+      <c r="K1184" s="29" t="s">
+        <v>2904</v>
+      </c>
       <c r="L1184" s="127"/>
       <c r="M1184" s="29"/>
     </row>
@@ -56846,17 +56836,17 @@
       <c r="A1185" s="29" t="s">
         <v>2901</v>
       </c>
-      <c r="B1185" s="135" t="s">
-        <v>2860</v>
+      <c r="B1185" s="126" t="s">
+        <v>2926</v>
       </c>
       <c r="C1185" s="125" t="s">
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="D1185" s="126" t="s">
-        <v>2930</v>
+        <v>2735</v>
       </c>
       <c r="E1185" s="125" t="s">
-        <v>1342</v>
+        <v>2102</v>
       </c>
       <c r="F1185" s="127" t="s">
         <v>1800</v>
@@ -56871,7 +56861,9 @@
         <v>99</v>
       </c>
       <c r="J1185" s="29"/>
-      <c r="K1185" s="29"/>
+      <c r="K1185" s="29" t="s">
+        <v>2904</v>
+      </c>
       <c r="L1185" s="127"/>
       <c r="M1185" s="29"/>
     </row>
@@ -56879,17 +56871,17 @@
       <c r="A1186" s="29" t="s">
         <v>2902</v>
       </c>
-      <c r="B1186" s="135" t="s">
-        <v>2860</v>
+      <c r="B1186" s="126" t="s">
+        <v>2926</v>
       </c>
       <c r="C1186" s="125" t="s">
-        <v>2659</v>
+        <v>2662</v>
       </c>
       <c r="D1186" s="126" t="s">
-        <v>2930</v>
+        <v>2735</v>
       </c>
       <c r="E1186" s="125" t="s">
-        <v>1343</v>
+        <v>2552</v>
       </c>
       <c r="F1186" s="127" t="s">
         <v>1800</v>
@@ -56904,7 +56896,9 @@
         <v>99</v>
       </c>
       <c r="J1186" s="29"/>
-      <c r="K1186" s="29"/>
+      <c r="K1186" s="29" t="s">
+        <v>2904</v>
+      </c>
       <c r="L1186" s="127"/>
       <c r="M1186" s="29"/>
     </row>
@@ -56912,20 +56906,20 @@
       <c r="A1187" s="29" t="s">
         <v>2903</v>
       </c>
-      <c r="B1187" s="135" t="s">
-        <v>2860</v>
+      <c r="B1187" s="126" t="s">
+        <v>2926</v>
       </c>
       <c r="C1187" s="125" t="s">
-        <v>2660</v>
+        <v>2663</v>
       </c>
       <c r="D1187" s="126" t="s">
-        <v>2930</v>
+        <v>2735</v>
       </c>
       <c r="E1187" s="125" t="s">
-        <v>1344</v>
+        <v>2286</v>
       </c>
       <c r="F1187" s="127" t="s">
-        <v>1800</v>
+        <v>479</v>
       </c>
       <c r="G1187" s="127" t="s">
         <v>1611</v>
@@ -56937,29 +56931,29 @@
         <v>99</v>
       </c>
       <c r="J1187" s="29"/>
-      <c r="K1187" s="29"/>
+      <c r="K1187" s="29" t="s">
+        <v>2904</v>
+      </c>
       <c r="L1187" s="127"/>
       <c r="M1187" s="29"/>
     </row>
     <row r="1188" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="29" t="s">
-        <v>2904</v>
-      </c>
-      <c r="B1188" s="126" t="s">
-        <v>2930</v>
+        <v>2907</v>
+      </c>
+      <c r="B1188" s="80" t="s">
+        <v>2908</v>
       </c>
       <c r="C1188" s="125" t="s">
-        <v>2660</v>
-      </c>
-      <c r="D1188" s="79" t="s">
-        <v>2735</v>
+        <v>2909</v>
+      </c>
+      <c r="D1188" s="126" t="s">
+        <v>2910</v>
       </c>
       <c r="E1188" s="125" t="s">
-        <v>2644</v>
-      </c>
-      <c r="F1188" s="127" t="s">
-        <v>1800</v>
-      </c>
+        <v>2911</v>
+      </c>
+      <c r="F1188" s="127"/>
       <c r="G1188" s="127" t="s">
         <v>1611</v>
       </c>
@@ -56967,34 +56961,30 @@
         <v>26</v>
       </c>
       <c r="I1188" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1188" s="29"/>
-      <c r="K1188" s="29" t="s">
-        <v>2908</v>
-      </c>
+      <c r="K1188" s="29"/>
       <c r="L1188" s="127"/>
       <c r="M1188" s="29"/>
     </row>
     <row r="1189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1189" s="29" t="s">
-        <v>2905</v>
+        <v>2913</v>
       </c>
       <c r="B1189" s="126" t="s">
-        <v>2930</v>
+        <v>2910</v>
       </c>
       <c r="C1189" s="125" t="s">
-        <v>2661</v>
+        <v>2434</v>
       </c>
       <c r="D1189" s="126" t="s">
-        <v>2735</v>
+        <v>1823</v>
       </c>
       <c r="E1189" s="125" t="s">
-        <v>2102</v>
-      </c>
-      <c r="F1189" s="127" t="s">
-        <v>1800</v>
-      </c>
+        <v>2912</v>
+      </c>
+      <c r="F1189" s="127"/>
       <c r="G1189" s="127" t="s">
         <v>1611</v>
       </c>
@@ -57002,30 +56992,28 @@
         <v>26</v>
       </c>
       <c r="I1189" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1189" s="29"/>
-      <c r="K1189" s="29" t="s">
-        <v>2908</v>
-      </c>
+      <c r="K1189" s="29"/>
       <c r="L1189" s="127"/>
       <c r="M1189" s="29"/>
     </row>
     <row r="1190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1190" s="29" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B1190" s="126" t="s">
-        <v>2930</v>
+        <v>2916</v>
+      </c>
+      <c r="B1190" s="135" t="s">
+        <v>1823</v>
       </c>
       <c r="C1190" s="125" t="s">
-        <v>2662</v>
+        <v>2915</v>
       </c>
       <c r="D1190" s="126" t="s">
-        <v>2735</v>
+        <v>2914</v>
       </c>
       <c r="E1190" s="125" t="s">
-        <v>2552</v>
+        <v>2434</v>
       </c>
       <c r="F1190" s="127" t="s">
         <v>1800</v>
@@ -57037,33 +57025,31 @@
         <v>26</v>
       </c>
       <c r="I1190" s="119" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="J1190" s="29"/>
-      <c r="K1190" s="29" t="s">
-        <v>2908</v>
-      </c>
+      <c r="K1190" s="29"/>
       <c r="L1190" s="127"/>
       <c r="M1190" s="29"/>
     </row>
-    <row r="1191" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1191" s="29" t="s">
-        <v>2907</v>
-      </c>
-      <c r="B1191" s="126" t="s">
-        <v>2930</v>
+        <v>2919</v>
+      </c>
+      <c r="B1191" s="135" t="s">
+        <v>1823</v>
       </c>
       <c r="C1191" s="125" t="s">
-        <v>2663</v>
+        <v>2917</v>
       </c>
       <c r="D1191" s="126" t="s">
-        <v>2735</v>
+        <v>2918</v>
       </c>
       <c r="E1191" s="125" t="s">
-        <v>2286</v>
+        <v>1611</v>
       </c>
       <c r="F1191" s="127" t="s">
-        <v>479</v>
+        <v>1800</v>
       </c>
       <c r="G1191" s="127" t="s">
         <v>1611</v>
@@ -57072,92 +57058,82 @@
         <v>26</v>
       </c>
       <c r="I1191" s="119" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="J1191" s="29"/>
-      <c r="K1191" s="29" t="s">
-        <v>2908</v>
-      </c>
+      <c r="K1191" s="29"/>
       <c r="L1191" s="127"/>
       <c r="M1191" s="29"/>
     </row>
-    <row r="1192" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1192" s="29" t="s">
-        <v>2911</v>
-      </c>
-      <c r="B1192" s="80" t="s">
-        <v>2912</v>
-      </c>
-      <c r="C1192" s="125" t="s">
-        <v>2913</v>
-      </c>
-      <c r="D1192" s="126" t="s">
-        <v>2914</v>
-      </c>
-      <c r="E1192" s="125" t="s">
-        <v>2915</v>
-      </c>
-      <c r="F1192" s="127"/>
+        <v>2920</v>
+      </c>
+      <c r="B1192" s="135"/>
+      <c r="C1192" s="125"/>
+      <c r="D1192" s="126"/>
+      <c r="E1192" s="125"/>
+      <c r="F1192" s="127" t="s">
+        <v>30</v>
+      </c>
       <c r="G1192" s="127" t="s">
-        <v>1611</v>
+        <v>30</v>
       </c>
       <c r="H1192" s="128" t="s">
-        <v>26</v>
+        <v>667</v>
       </c>
       <c r="I1192" s="119" t="s">
-        <v>519</v>
+        <v>99</v>
       </c>
       <c r="J1192" s="29"/>
-      <c r="K1192" s="29"/>
-      <c r="L1192" s="127"/>
+      <c r="K1192" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="L1192" s="127" t="s">
+        <v>652</v>
+      </c>
       <c r="M1192" s="29"/>
     </row>
     <row r="1193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1193" s="29" t="s">
-        <v>2917</v>
-      </c>
-      <c r="B1193" s="126" t="s">
-        <v>2914</v>
-      </c>
-      <c r="C1193" s="125" t="s">
-        <v>2434</v>
-      </c>
-      <c r="D1193" s="126" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E1193" s="125" t="s">
-        <v>2916</v>
-      </c>
-      <c r="F1193" s="127"/>
+        <v>2921</v>
+      </c>
+      <c r="B1193" s="135"/>
+      <c r="C1193" s="125"/>
+      <c r="D1193" s="126"/>
+      <c r="E1193" s="125"/>
+      <c r="F1193" s="127" t="s">
+        <v>30</v>
+      </c>
       <c r="G1193" s="127" t="s">
-        <v>1611</v>
+        <v>30</v>
       </c>
       <c r="H1193" s="128" t="s">
-        <v>26</v>
+        <v>2922</v>
       </c>
       <c r="I1193" s="119" t="s">
-        <v>519</v>
+        <v>99</v>
       </c>
       <c r="J1193" s="29"/>
-      <c r="K1193" s="29"/>
-      <c r="L1193" s="127"/>
+      <c r="K1193" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="L1193" s="127" t="s">
+        <v>652</v>
+      </c>
       <c r="M1193" s="29"/>
     </row>
     <row r="1194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1194" s="29" t="s">
-        <v>2920</v>
-      </c>
-      <c r="B1194" s="135" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C1194" s="125" t="s">
-        <v>2919</v>
-      </c>
+        <v>2924</v>
+      </c>
+      <c r="B1194" s="135"/>
+      <c r="C1194" s="125"/>
       <c r="D1194" s="126" t="s">
-        <v>2918</v>
+        <v>2735</v>
       </c>
       <c r="E1194" s="125" t="s">
-        <v>2434</v>
+        <v>2642</v>
       </c>
       <c r="F1194" s="127" t="s">
         <v>1800</v>
@@ -57169,7 +57145,7 @@
         <v>26</v>
       </c>
       <c r="I1194" s="119" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="J1194" s="29"/>
       <c r="K1194" s="29"/>
@@ -57178,19 +57154,15 @@
     </row>
     <row r="1195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1195" s="29" t="s">
-        <v>2923</v>
-      </c>
-      <c r="B1195" s="135" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C1195" s="125" t="s">
-        <v>2921</v>
-      </c>
+        <v>2925</v>
+      </c>
+      <c r="B1195" s="135"/>
+      <c r="C1195" s="125"/>
       <c r="D1195" s="126" t="s">
-        <v>2922</v>
+        <v>2735</v>
       </c>
       <c r="E1195" s="125" t="s">
-        <v>1611</v>
+        <v>2643</v>
       </c>
       <c r="F1195" s="127" t="s">
         <v>1800</v>
@@ -57202,7 +57174,7 @@
         <v>26</v>
       </c>
       <c r="I1195" s="119" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="J1195" s="29"/>
       <c r="K1195" s="29"/>
@@ -57211,85 +57183,97 @@
     </row>
     <row r="1196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1196" s="29" t="s">
-        <v>2924</v>
-      </c>
-      <c r="B1196" s="135"/>
-      <c r="C1196" s="125"/>
-      <c r="D1196" s="126"/>
-      <c r="E1196" s="125"/>
+        <v>2927</v>
+      </c>
+      <c r="B1196" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1196" s="125" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D1196" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1196" s="125" t="s">
+        <v>2556</v>
+      </c>
       <c r="F1196" s="127" t="s">
-        <v>30</v>
+        <v>2646</v>
       </c>
       <c r="G1196" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1196" s="128" t="s">
-        <v>667</v>
+        <v>1611</v>
+      </c>
+      <c r="H1196" s="128">
+        <v>0</v>
       </c>
       <c r="I1196" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1196" s="29"/>
-      <c r="K1196" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="L1196" s="127" t="s">
-        <v>652</v>
-      </c>
+      <c r="K1196" s="29"/>
+      <c r="L1196" s="127"/>
       <c r="M1196" s="29"/>
     </row>
     <row r="1197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1197" s="29" t="s">
-        <v>2925</v>
-      </c>
-      <c r="B1197" s="135"/>
-      <c r="C1197" s="125"/>
-      <c r="D1197" s="126"/>
-      <c r="E1197" s="125"/>
+        <v>2928</v>
+      </c>
+      <c r="B1197" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1197" s="125" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D1197" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1197" s="125" t="s">
+        <v>2645</v>
+      </c>
       <c r="F1197" s="127" t="s">
-        <v>30</v>
+        <v>2646</v>
       </c>
       <c r="G1197" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1197" s="128" t="s">
-        <v>2926</v>
+        <v>1611</v>
+      </c>
+      <c r="H1197" s="128">
+        <v>0</v>
       </c>
       <c r="I1197" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1197" s="29"/>
-      <c r="K1197" s="29" t="s">
-        <v>452</v>
-      </c>
-      <c r="L1197" s="127" t="s">
-        <v>652</v>
-      </c>
+      <c r="K1197" s="29"/>
+      <c r="L1197" s="127"/>
       <c r="M1197" s="29"/>
     </row>
     <row r="1198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1198" s="29" t="s">
-        <v>2928</v>
-      </c>
-      <c r="B1198" s="135"/>
-      <c r="C1198" s="125"/>
-      <c r="D1198" s="126" t="s">
-        <v>2735</v>
+        <v>2929</v>
+      </c>
+      <c r="B1198" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1198" s="125" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D1198" s="135" t="s">
+        <v>2926</v>
       </c>
       <c r="E1198" s="125" t="s">
-        <v>2642</v>
+        <v>2106</v>
       </c>
       <c r="F1198" s="127" t="s">
-        <v>1800</v>
+        <v>2646</v>
       </c>
       <c r="G1198" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1198" s="128" t="s">
-        <v>26</v>
+      <c r="H1198" s="128">
+        <v>0</v>
       </c>
       <c r="I1198" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1198" s="29"/>
       <c r="K1198" s="29"/>
@@ -57298,27 +57282,31 @@
     </row>
     <row r="1199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1199" s="29" t="s">
-        <v>2929</v>
-      </c>
-      <c r="B1199" s="135"/>
-      <c r="C1199" s="125"/>
-      <c r="D1199" s="126" t="s">
-        <v>2735</v>
+        <v>2930</v>
+      </c>
+      <c r="B1199" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="C1199" s="125" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D1199" s="135" t="s">
+        <v>2926</v>
       </c>
       <c r="E1199" s="125" t="s">
-        <v>2643</v>
+        <v>2657</v>
       </c>
       <c r="F1199" s="127" t="s">
-        <v>1800</v>
+        <v>2646</v>
       </c>
       <c r="G1199" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1199" s="128" t="s">
-        <v>26</v>
+      <c r="H1199" s="128">
+        <v>0</v>
       </c>
       <c r="I1199" s="119" t="s">
-        <v>99</v>
+        <v>519</v>
       </c>
       <c r="J1199" s="29"/>
       <c r="K1199" s="29"/>
@@ -57330,16 +57318,16 @@
         <v>2931</v>
       </c>
       <c r="B1200" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1200" s="125" t="s">
-        <v>2526</v>
+        <v>2651</v>
       </c>
       <c r="D1200" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1200" s="125" t="s">
-        <v>2556</v>
+        <v>2658</v>
       </c>
       <c r="F1200" s="127" t="s">
         <v>2646</v>
@@ -57363,16 +57351,16 @@
         <v>2932</v>
       </c>
       <c r="B1201" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1201" s="125" t="s">
-        <v>2525</v>
+        <v>2652</v>
       </c>
       <c r="D1201" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1201" s="125" t="s">
-        <v>2645</v>
+        <v>2659</v>
       </c>
       <c r="F1201" s="127" t="s">
         <v>2646</v>
@@ -57396,16 +57384,16 @@
         <v>2933</v>
       </c>
       <c r="B1202" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1202" s="125" t="s">
-        <v>2109</v>
+        <v>2653</v>
       </c>
       <c r="D1202" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1202" s="125" t="s">
-        <v>2106</v>
+        <v>2660</v>
       </c>
       <c r="F1202" s="127" t="s">
         <v>2646</v>
@@ -57429,16 +57417,16 @@
         <v>2934</v>
       </c>
       <c r="B1203" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1203" s="125" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="D1203" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1203" s="125" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
       <c r="F1203" s="127" t="s">
         <v>2646</v>
@@ -57462,16 +57450,16 @@
         <v>2935</v>
       </c>
       <c r="B1204" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1204" s="125" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="D1204" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1204" s="125" t="s">
-        <v>2658</v>
+        <v>2662</v>
       </c>
       <c r="F1204" s="127" t="s">
         <v>2646</v>
@@ -57495,16 +57483,16 @@
         <v>2936</v>
       </c>
       <c r="B1205" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1205" s="125" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="D1205" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="E1205" s="125" t="s">
-        <v>2659</v>
+        <v>2663</v>
       </c>
       <c r="F1205" s="127" t="s">
         <v>2646</v>
@@ -57528,25 +57516,25 @@
         <v>2937</v>
       </c>
       <c r="B1206" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1206" s="125" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D1206" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1206" s="125" t="s">
         <v>2653</v>
       </c>
-      <c r="D1206" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1206" s="125" t="s">
-        <v>2660</v>
-      </c>
       <c r="F1206" s="127" t="s">
-        <v>2646</v>
+        <v>1800</v>
       </c>
       <c r="G1206" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1206" s="128">
-        <v>0</v>
+      <c r="H1206" s="128" t="s">
+        <v>1780</v>
       </c>
       <c r="I1206" s="119" t="s">
         <v>519</v>
@@ -57561,25 +57549,25 @@
         <v>2938</v>
       </c>
       <c r="B1207" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1207" s="125" t="s">
+        <v>2650</v>
+      </c>
+      <c r="D1207" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1207" s="125" t="s">
         <v>2654</v>
       </c>
-      <c r="D1207" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1207" s="125" t="s">
-        <v>2661</v>
-      </c>
       <c r="F1207" s="127" t="s">
-        <v>2646</v>
+        <v>1800</v>
       </c>
       <c r="G1207" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1207" s="128">
-        <v>0</v>
+      <c r="H1207" s="128" t="s">
+        <v>1780</v>
       </c>
       <c r="I1207" s="119" t="s">
         <v>519</v>
@@ -57594,25 +57582,25 @@
         <v>2939</v>
       </c>
       <c r="B1208" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1208" s="125" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D1208" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1208" s="125" t="s">
         <v>2655</v>
       </c>
-      <c r="D1208" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1208" s="125" t="s">
-        <v>2662</v>
-      </c>
       <c r="F1208" s="127" t="s">
-        <v>2646</v>
+        <v>1800</v>
       </c>
       <c r="G1208" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1208" s="128">
-        <v>0</v>
+      <c r="H1208" s="128" t="s">
+        <v>1780</v>
       </c>
       <c r="I1208" s="119" t="s">
         <v>519</v>
@@ -57627,25 +57615,25 @@
         <v>2940</v>
       </c>
       <c r="B1209" s="135" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="C1209" s="125" t="s">
+        <v>2652</v>
+      </c>
+      <c r="D1209" s="135" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1209" s="125" t="s">
         <v>2656</v>
       </c>
-      <c r="D1209" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1209" s="125" t="s">
-        <v>2663</v>
-      </c>
       <c r="F1209" s="127" t="s">
-        <v>2646</v>
+        <v>1800</v>
       </c>
       <c r="G1209" s="127" t="s">
         <v>1611</v>
       </c>
-      <c r="H1209" s="128">
-        <v>0</v>
+      <c r="H1209" s="128" t="s">
+        <v>1780</v>
       </c>
       <c r="I1209" s="119" t="s">
         <v>519</v>
@@ -57656,132 +57644,60 @@
       <c r="M1209" s="29"/>
     </row>
     <row r="1210" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1210" s="29" t="s">
-        <v>2941</v>
-      </c>
-      <c r="B1210" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C1210" s="125" t="s">
-        <v>2109</v>
-      </c>
-      <c r="D1210" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1210" s="125" t="s">
-        <v>2653</v>
-      </c>
-      <c r="F1210" s="127" t="s">
-        <v>1800</v>
-      </c>
-      <c r="G1210" s="127" t="s">
-        <v>1611</v>
-      </c>
-      <c r="H1210" s="128" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I1210" s="119" t="s">
-        <v>519</v>
-      </c>
+      <c r="A1210" s="29"/>
+      <c r="B1210" s="135"/>
+      <c r="C1210" s="125"/>
+      <c r="D1210" s="126"/>
+      <c r="E1210" s="125"/>
+      <c r="F1210" s="127"/>
+      <c r="G1210" s="127"/>
+      <c r="H1210" s="128"/>
+      <c r="I1210" s="119"/>
       <c r="J1210" s="29"/>
       <c r="K1210" s="29"/>
       <c r="L1210" s="127"/>
       <c r="M1210" s="29"/>
     </row>
     <row r="1211" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1211" s="29" t="s">
-        <v>2942</v>
-      </c>
-      <c r="B1211" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C1211" s="125" t="s">
-        <v>2650</v>
-      </c>
-      <c r="D1211" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1211" s="125" t="s">
-        <v>2654</v>
-      </c>
-      <c r="F1211" s="127" t="s">
-        <v>1800</v>
-      </c>
-      <c r="G1211" s="127" t="s">
-        <v>1611</v>
-      </c>
-      <c r="H1211" s="128" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I1211" s="119" t="s">
-        <v>519</v>
-      </c>
+      <c r="A1211" s="29"/>
+      <c r="B1211" s="135"/>
+      <c r="C1211" s="125"/>
+      <c r="D1211" s="126"/>
+      <c r="E1211" s="125"/>
+      <c r="F1211" s="127"/>
+      <c r="G1211" s="127"/>
+      <c r="H1211" s="128"/>
+      <c r="I1211" s="119"/>
       <c r="J1211" s="29"/>
       <c r="K1211" s="29"/>
       <c r="L1211" s="127"/>
       <c r="M1211" s="29"/>
     </row>
     <row r="1212" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1212" s="29" t="s">
-        <v>2943</v>
-      </c>
-      <c r="B1212" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C1212" s="125" t="s">
-        <v>2651</v>
-      </c>
-      <c r="D1212" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1212" s="125" t="s">
-        <v>2655</v>
-      </c>
-      <c r="F1212" s="127" t="s">
-        <v>1800</v>
-      </c>
-      <c r="G1212" s="127" t="s">
-        <v>1611</v>
-      </c>
-      <c r="H1212" s="128" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I1212" s="119" t="s">
-        <v>519</v>
-      </c>
+      <c r="A1212" s="29"/>
+      <c r="B1212" s="135"/>
+      <c r="C1212" s="125"/>
+      <c r="D1212" s="126"/>
+      <c r="E1212" s="125"/>
+      <c r="F1212" s="127"/>
+      <c r="G1212" s="127"/>
+      <c r="H1212" s="128"/>
+      <c r="I1212" s="119"/>
       <c r="J1212" s="29"/>
       <c r="K1212" s="29"/>
       <c r="L1212" s="127"/>
       <c r="M1212" s="29"/>
     </row>
     <row r="1213" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1213" s="29" t="s">
-        <v>2944</v>
-      </c>
-      <c r="B1213" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C1213" s="125" t="s">
-        <v>2652</v>
-      </c>
-      <c r="D1213" s="135" t="s">
-        <v>2930</v>
-      </c>
-      <c r="E1213" s="125" t="s">
-        <v>2656</v>
-      </c>
-      <c r="F1213" s="127" t="s">
-        <v>1800</v>
-      </c>
-      <c r="G1213" s="127" t="s">
-        <v>1611</v>
-      </c>
-      <c r="H1213" s="128" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I1213" s="119" t="s">
-        <v>519</v>
-      </c>
+      <c r="A1213" s="29"/>
+      <c r="B1213" s="135"/>
+      <c r="C1213" s="125"/>
+      <c r="D1213" s="126"/>
+      <c r="E1213" s="125"/>
+      <c r="F1213" s="127"/>
+      <c r="G1213" s="127"/>
+      <c r="H1213" s="128"/>
+      <c r="I1213" s="119"/>
       <c r="J1213" s="29"/>
       <c r="K1213" s="29"/>
       <c r="L1213" s="127"/>
@@ -59393,84 +59309,24 @@
       <c r="M1320" s="29"/>
     </row>
     <row r="1321" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1321" s="29"/>
+      <c r="A1321" s="131"/>
       <c r="B1321" s="135"/>
       <c r="C1321" s="125"/>
       <c r="D1321" s="126"/>
       <c r="E1321" s="125"/>
-      <c r="F1321" s="127"/>
-      <c r="G1321" s="127"/>
-      <c r="H1321" s="128"/>
-      <c r="I1321" s="119"/>
-      <c r="J1321" s="29"/>
-      <c r="K1321" s="29"/>
-      <c r="L1321" s="127"/>
-      <c r="M1321" s="29"/>
+      <c r="F1321" s="132"/>
+      <c r="G1321" s="132"/>
+      <c r="H1321" s="133"/>
+      <c r="I1321" s="134"/>
+      <c r="J1321" s="131"/>
+      <c r="K1321" s="131"/>
+      <c r="L1321" s="132"/>
+      <c r="M1321" s="131"/>
     </row>
     <row r="1322" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1322" s="29"/>
-      <c r="B1322" s="135"/>
-      <c r="C1322" s="125"/>
-      <c r="D1322" s="126"/>
-      <c r="E1322" s="125"/>
-      <c r="F1322" s="127"/>
-      <c r="G1322" s="127"/>
-      <c r="H1322" s="128"/>
-      <c r="I1322" s="119"/>
-      <c r="J1322" s="29"/>
-      <c r="K1322" s="29"/>
-      <c r="L1322" s="127"/>
-      <c r="M1322" s="29"/>
-    </row>
-    <row r="1323" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1323" s="29"/>
-      <c r="B1323" s="135"/>
-      <c r="C1323" s="125"/>
-      <c r="D1323" s="126"/>
-      <c r="E1323" s="125"/>
-      <c r="F1323" s="127"/>
-      <c r="G1323" s="127"/>
-      <c r="H1323" s="128"/>
-      <c r="I1323" s="119"/>
-      <c r="J1323" s="29"/>
-      <c r="K1323" s="29"/>
-      <c r="L1323" s="127"/>
-      <c r="M1323" s="29"/>
-    </row>
-    <row r="1324" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1324" s="29"/>
-      <c r="B1324" s="135"/>
-      <c r="C1324" s="125"/>
-      <c r="D1324" s="126"/>
-      <c r="E1324" s="125"/>
-      <c r="F1324" s="127"/>
-      <c r="G1324" s="127"/>
-      <c r="H1324" s="128"/>
-      <c r="I1324" s="119"/>
-      <c r="J1324" s="29"/>
-      <c r="K1324" s="29"/>
-      <c r="L1324" s="127"/>
-      <c r="M1324" s="29"/>
-    </row>
-    <row r="1325" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1325" s="131"/>
-      <c r="B1325" s="135"/>
-      <c r="C1325" s="125"/>
-      <c r="D1325" s="126"/>
-      <c r="E1325" s="125"/>
-      <c r="F1325" s="132"/>
-      <c r="G1325" s="132"/>
-      <c r="H1325" s="133"/>
-      <c r="I1325" s="134"/>
-      <c r="J1325" s="131"/>
-      <c r="K1325" s="131"/>
-      <c r="L1325" s="132"/>
-      <c r="M1325" s="131"/>
-    </row>
-    <row r="1326" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B1326" s="83"/>
-      <c r="K1326" s="113"/>
-      <c r="L1326" s="3"/>
+      <c r="B1322" s="83"/>
+      <c r="K1322" s="113"/>
+      <c r="L1322" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398277C8-A777-5B4E-B658-CD1A3553119C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD290A05-0F58-524B-9B6E-00BD58A919FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1520" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId3"/>
-    <pivotCache cacheId="37" r:id="rId4"/>
+    <pivotCache cacheId="38" r:id="rId3"/>
+    <pivotCache cacheId="39" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9863" uniqueCount="2961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9993" uniqueCount="2989">
   <si>
     <t>Tag</t>
   </si>
@@ -8924,6 +8924,90 @@
   </si>
   <si>
     <t>a224</t>
+  </si>
+  <si>
+    <t>2401-1901</t>
+  </si>
+  <si>
+    <t>light blue</t>
+  </si>
+  <si>
+    <t>shure-radio</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>rt1211</t>
+  </si>
+  <si>
+    <t>rt1212</t>
+  </si>
+  <si>
+    <t>rt1213</t>
+  </si>
+  <si>
+    <t>rt1214</t>
+  </si>
+  <si>
+    <t>rt1215</t>
+  </si>
+  <si>
+    <t>rt1216</t>
+  </si>
+  <si>
+    <t>rt1217</t>
+  </si>
+  <si>
+    <t>rt1218</t>
+  </si>
+  <si>
+    <t>rt1219</t>
+  </si>
+  <si>
+    <t>rt1220</t>
+  </si>
+  <si>
+    <t>rt1221</t>
+  </si>
+  <si>
+    <t>rt1222</t>
+  </si>
+  <si>
+    <t>rt1223</t>
+  </si>
+  <si>
+    <t>rt1224</t>
+  </si>
+  <si>
+    <t>rt1225</t>
+  </si>
+  <si>
+    <t>rt1226</t>
+  </si>
+  <si>
+    <t>ZAMU-A007</t>
+  </si>
+  <si>
+    <t>ZAMU-A006</t>
+  </si>
+  <si>
+    <t>ZAMU-B004</t>
+  </si>
+  <si>
+    <t>ZAMU-B005</t>
+  </si>
+  <si>
+    <t>ZAMU-B006</t>
+  </si>
+  <si>
+    <t>ZAMU-B007</t>
+  </si>
+  <si>
+    <t>ZAMU-B008</t>
+  </si>
+  <si>
+    <t>ZAMU-B009</t>
   </si>
 </sst>
 </file>
@@ -9339,7 +9423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9567,6 +9651,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -18436,7 +18526,70 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18669,69 +18822,6 @@
     </i>
     <i>
       <x v="53"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -48712,7 +48802,9 @@
       <c r="I932" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J932" s="29"/>
+      <c r="J932" s="29" t="s">
+        <v>452</v>
+      </c>
       <c r="K932" s="29"/>
       <c r="L932" s="31"/>
       <c r="M932" s="29"/>
@@ -48789,7 +48881,9 @@
       <c r="I935" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J935" s="29"/>
+      <c r="J935" s="29" t="s">
+        <v>452</v>
+      </c>
       <c r="K935" s="29" t="s">
         <v>2140</v>
       </c>
@@ -57690,257 +57784,545 @@
       <c r="L1209" s="31"/>
       <c r="M1209" s="29"/>
     </row>
-    <row r="1210" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1210" s="29"/>
+    <row r="1210" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1210" s="29" t="s">
+        <v>2961</v>
+      </c>
       <c r="B1210" s="100"/>
       <c r="C1210" s="83"/>
       <c r="D1210" s="85"/>
       <c r="E1210" s="83"/>
-      <c r="F1210" s="31"/>
-      <c r="G1210" s="31"/>
-      <c r="H1210" s="29"/>
-      <c r="I1210" s="119"/>
-      <c r="J1210" s="29"/>
-      <c r="K1210" s="29"/>
+      <c r="F1210" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1210" s="31" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H1210" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="I1210" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1210" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="K1210" s="29" t="s">
+        <v>2962</v>
+      </c>
       <c r="L1210" s="31"/>
       <c r="M1210" s="29"/>
     </row>
-    <row r="1211" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1211" s="29"/>
-      <c r="B1211" s="100"/>
-      <c r="C1211" s="83"/>
-      <c r="D1211" s="85"/>
-      <c r="E1211" s="83"/>
-      <c r="F1211" s="31"/>
-      <c r="G1211" s="31"/>
-      <c r="H1211" s="29"/>
-      <c r="I1211" s="119"/>
-      <c r="J1211" s="29"/>
+    <row r="1211" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1211" s="29" t="s">
+        <v>2965</v>
+      </c>
+      <c r="B1211" s="112" t="s">
+        <v>2981</v>
+      </c>
+      <c r="C1211" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1211" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1211" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1211" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1211" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1211" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1211" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1211" s="29" t="s">
+        <v>1257</v>
+      </c>
       <c r="K1211" s="29"/>
       <c r="L1211" s="31"/>
       <c r="M1211" s="29"/>
     </row>
     <row r="1212" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1212" s="29"/>
-      <c r="B1212" s="100"/>
-      <c r="C1212" s="83"/>
-      <c r="D1212" s="85"/>
-      <c r="E1212" s="83"/>
-      <c r="F1212" s="31"/>
-      <c r="G1212" s="31"/>
-      <c r="H1212" s="29"/>
-      <c r="I1212" s="119"/>
-      <c r="J1212" s="29"/>
+      <c r="A1212" s="29" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B1212" s="125" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C1212" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1212" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1212" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1212" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1212" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1212" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1212" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1212" s="29" t="s">
+        <v>1258</v>
+      </c>
       <c r="K1212" s="29"/>
       <c r="L1212" s="31"/>
       <c r="M1212" s="29"/>
     </row>
     <row r="1213" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1213" s="29"/>
-      <c r="B1213" s="100"/>
-      <c r="C1213" s="83"/>
-      <c r="D1213" s="85"/>
-      <c r="E1213" s="83"/>
-      <c r="F1213" s="31"/>
-      <c r="G1213" s="31"/>
-      <c r="H1213" s="29"/>
-      <c r="I1213" s="119"/>
-      <c r="J1213" s="29"/>
+      <c r="A1213" s="29" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B1213" s="125" t="s">
+        <v>2983</v>
+      </c>
+      <c r="C1213" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1213" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1213" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1213" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1213" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1213" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1213" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1213" s="29" t="s">
+        <v>1259</v>
+      </c>
       <c r="K1213" s="29"/>
       <c r="L1213" s="31"/>
       <c r="M1213" s="29"/>
     </row>
     <row r="1214" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1214" s="29"/>
-      <c r="B1214" s="100"/>
-      <c r="C1214" s="83"/>
-      <c r="D1214" s="85"/>
-      <c r="E1214" s="83"/>
-      <c r="F1214" s="31"/>
-      <c r="G1214" s="31"/>
-      <c r="H1214" s="29"/>
-      <c r="I1214" s="119"/>
-      <c r="J1214" s="29"/>
+      <c r="A1214" s="29" t="s">
+        <v>2968</v>
+      </c>
+      <c r="B1214" s="125" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C1214" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1214" s="100" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1214" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1214" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1214" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1214" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1214" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1214" s="29" t="s">
+        <v>1260</v>
+      </c>
       <c r="K1214" s="29"/>
       <c r="L1214" s="31"/>
       <c r="M1214" s="29"/>
     </row>
     <row r="1215" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1215" s="29"/>
-      <c r="B1215" s="100"/>
-      <c r="C1215" s="83"/>
-      <c r="D1215" s="85"/>
-      <c r="E1215" s="83"/>
-      <c r="F1215" s="31"/>
-      <c r="G1215" s="31"/>
-      <c r="H1215" s="29"/>
-      <c r="I1215" s="119"/>
-      <c r="J1215" s="29"/>
+      <c r="A1215" s="29" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B1215" s="125" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C1215" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1215" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1215" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1215" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1215" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1215" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1215" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1215" s="29" t="s">
+        <v>1261</v>
+      </c>
       <c r="K1215" s="29"/>
       <c r="L1215" s="31"/>
       <c r="M1215" s="29"/>
     </row>
     <row r="1216" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1216" s="29"/>
-      <c r="B1216" s="100"/>
-      <c r="C1216" s="83"/>
-      <c r="D1216" s="85"/>
-      <c r="E1216" s="83"/>
-      <c r="F1216" s="31"/>
-      <c r="G1216" s="31"/>
-      <c r="H1216" s="29"/>
-      <c r="I1216" s="119"/>
-      <c r="J1216" s="29"/>
+      <c r="A1216" s="29" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1216" s="125" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C1216" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1216" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1216" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1216" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1216" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1216" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1216" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1216" s="29" t="s">
+        <v>1262</v>
+      </c>
       <c r="K1216" s="29"/>
       <c r="L1216" s="31"/>
       <c r="M1216" s="29"/>
     </row>
     <row r="1217" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1217" s="29"/>
-      <c r="B1217" s="100"/>
-      <c r="C1217" s="83"/>
-      <c r="D1217" s="85"/>
-      <c r="E1217" s="83"/>
-      <c r="F1217" s="31"/>
-      <c r="G1217" s="31"/>
-      <c r="H1217" s="29"/>
-      <c r="I1217" s="119"/>
-      <c r="J1217" s="29"/>
+      <c r="A1217" s="29" t="s">
+        <v>2971</v>
+      </c>
+      <c r="B1217" s="125" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C1217" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1217" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1217" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1217" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1217" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1217" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1217" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1217" s="29" t="s">
+        <v>1263</v>
+      </c>
       <c r="K1217" s="29"/>
       <c r="L1217" s="31"/>
       <c r="M1217" s="29"/>
     </row>
     <row r="1218" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1218" s="29"/>
-      <c r="B1218" s="100"/>
-      <c r="C1218" s="83"/>
-      <c r="D1218" s="85"/>
-      <c r="E1218" s="83"/>
-      <c r="F1218" s="31"/>
-      <c r="G1218" s="31"/>
-      <c r="H1218" s="29"/>
-      <c r="I1218" s="119"/>
-      <c r="J1218" s="29"/>
+      <c r="A1218" s="29" t="s">
+        <v>2972</v>
+      </c>
+      <c r="B1218" s="125" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C1218" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1218" s="100" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1218" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1218" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1218" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1218" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1218" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1218" s="29" t="s">
+        <v>1264</v>
+      </c>
       <c r="K1218" s="29"/>
       <c r="L1218" s="31"/>
       <c r="M1218" s="29"/>
     </row>
     <row r="1219" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1219" s="29"/>
-      <c r="B1219" s="100"/>
+      <c r="A1219" s="29" t="s">
+        <v>2973</v>
+      </c>
+      <c r="B1219" s="125"/>
       <c r="C1219" s="83"/>
-      <c r="D1219" s="85"/>
-      <c r="E1219" s="83"/>
-      <c r="F1219" s="31"/>
-      <c r="G1219" s="31"/>
-      <c r="H1219" s="29"/>
-      <c r="I1219" s="119"/>
+      <c r="D1219" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1219" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1219" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1219" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1219" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1219" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1219" s="29"/>
       <c r="K1219" s="29"/>
       <c r="L1219" s="31"/>
       <c r="M1219" s="29"/>
     </row>
     <row r="1220" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1220" s="29"/>
-      <c r="B1220" s="100"/>
+      <c r="A1220" s="29" t="s">
+        <v>2974</v>
+      </c>
+      <c r="B1220" s="125"/>
       <c r="C1220" s="83"/>
-      <c r="D1220" s="85"/>
-      <c r="E1220" s="83"/>
-      <c r="F1220" s="31"/>
-      <c r="G1220" s="31"/>
-      <c r="H1220" s="29"/>
-      <c r="I1220" s="119"/>
+      <c r="D1220" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1220" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1220" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1220" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1220" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1220" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1220" s="29"/>
       <c r="K1220" s="29"/>
       <c r="L1220" s="31"/>
       <c r="M1220" s="29"/>
     </row>
     <row r="1221" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1221" s="29"/>
-      <c r="B1221" s="100"/>
+      <c r="A1221" s="29" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B1221" s="125"/>
       <c r="C1221" s="83"/>
-      <c r="D1221" s="85"/>
-      <c r="E1221" s="83"/>
-      <c r="F1221" s="31"/>
-      <c r="G1221" s="31"/>
-      <c r="H1221" s="29"/>
-      <c r="I1221" s="119"/>
+      <c r="D1221" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1221" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1221" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1221" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1221" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1221" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1221" s="29"/>
       <c r="K1221" s="29"/>
       <c r="L1221" s="31"/>
       <c r="M1221" s="29"/>
     </row>
     <row r="1222" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1222" s="29"/>
-      <c r="B1222" s="100"/>
+      <c r="A1222" s="29" t="s">
+        <v>2976</v>
+      </c>
+      <c r="B1222" s="125"/>
       <c r="C1222" s="83"/>
-      <c r="D1222" s="85"/>
-      <c r="E1222" s="83"/>
-      <c r="F1222" s="31"/>
-      <c r="G1222" s="31"/>
-      <c r="H1222" s="29"/>
-      <c r="I1222" s="119"/>
+      <c r="D1222" s="100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1222" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1222" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1222" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1222" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1222" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1222" s="29"/>
       <c r="K1222" s="29"/>
       <c r="L1222" s="31"/>
       <c r="M1222" s="29"/>
     </row>
     <row r="1223" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1223" s="29"/>
-      <c r="B1223" s="100"/>
+      <c r="A1223" s="29" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B1223" s="125"/>
       <c r="C1223" s="83"/>
-      <c r="D1223" s="85"/>
-      <c r="E1223" s="83"/>
-      <c r="F1223" s="31"/>
-      <c r="G1223" s="31"/>
-      <c r="H1223" s="29"/>
-      <c r="I1223" s="119"/>
+      <c r="D1223" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1223" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1223" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1223" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1223" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1223" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1223" s="29"/>
       <c r="K1223" s="29"/>
       <c r="L1223" s="31"/>
       <c r="M1223" s="29"/>
     </row>
     <row r="1224" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1224" s="29"/>
-      <c r="B1224" s="100"/>
+      <c r="A1224" s="29" t="s">
+        <v>2978</v>
+      </c>
+      <c r="B1224" s="125"/>
       <c r="C1224" s="83"/>
-      <c r="D1224" s="85"/>
-      <c r="E1224" s="83"/>
-      <c r="F1224" s="31"/>
-      <c r="G1224" s="31"/>
-      <c r="H1224" s="29"/>
-      <c r="I1224" s="119"/>
+      <c r="D1224" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1224" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1224" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1224" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1224" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1224" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1224" s="29"/>
       <c r="K1224" s="29"/>
       <c r="L1224" s="31"/>
       <c r="M1224" s="29"/>
     </row>
     <row r="1225" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1225" s="29"/>
-      <c r="B1225" s="100"/>
+      <c r="A1225" s="29" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B1225" s="125"/>
       <c r="C1225" s="83"/>
-      <c r="D1225" s="85"/>
-      <c r="E1225" s="83"/>
-      <c r="F1225" s="31"/>
-      <c r="G1225" s="31"/>
-      <c r="H1225" s="29"/>
-      <c r="I1225" s="119"/>
+      <c r="D1225" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1225" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1225" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1225" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1225" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1225" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1225" s="29"/>
       <c r="K1225" s="29"/>
       <c r="L1225" s="31"/>
       <c r="M1225" s="29"/>
     </row>
     <row r="1226" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1226" s="29"/>
-      <c r="B1226" s="100"/>
+      <c r="A1226" s="29" t="s">
+        <v>2980</v>
+      </c>
+      <c r="B1226" s="126"/>
       <c r="C1226" s="83"/>
-      <c r="D1226" s="85"/>
-      <c r="E1226" s="83"/>
-      <c r="F1226" s="31"/>
-      <c r="G1226" s="31"/>
-      <c r="H1226" s="29"/>
-      <c r="I1226" s="119"/>
-      <c r="J1226" s="29"/>
+      <c r="D1226" s="100" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1226" s="83" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F1226" s="31" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G1226" s="31" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1226" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1226" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1226" s="29" t="s">
+        <v>1273</v>
+      </c>
       <c r="K1226" s="29"/>
       <c r="L1226" s="31"/>
       <c r="M1226" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD290A05-0F58-524B-9B6E-00BD58A919FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268B8998-2301-2847-A7BB-820BD2A98451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7120" yWindow="1520" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9993" uniqueCount="2989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10016" uniqueCount="2996">
   <si>
     <t>Tag</t>
   </si>
@@ -9008,6 +9008,27 @@
   </si>
   <si>
     <t>ZAMU-B009</t>
+  </si>
+  <si>
+    <t>ZAMU-B010</t>
+  </si>
+  <si>
+    <t>ZAMU-G001</t>
+  </si>
+  <si>
+    <t>ZAMU-G002</t>
+  </si>
+  <si>
+    <t>ZAMU-G003</t>
+  </si>
+  <si>
+    <t>ZAMU-B012</t>
+  </si>
+  <si>
+    <t>ZAMU-B015</t>
+  </si>
+  <si>
+    <t>ZAMU-A002 or ZAMU-A003</t>
   </si>
 </sst>
 </file>
@@ -9122,7 +9143,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9180,6 +9201,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBA4EFF"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -9423,7 +9450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9657,6 +9684,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -58097,8 +58130,12 @@
       <c r="A1219" s="29" t="s">
         <v>2973</v>
       </c>
-      <c r="B1219" s="125"/>
-      <c r="C1219" s="83"/>
+      <c r="B1219" s="125" t="s">
+        <v>2989</v>
+      </c>
+      <c r="C1219" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1219" s="100" t="s">
         <v>346</v>
       </c>
@@ -58117,7 +58154,9 @@
       <c r="I1219" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1219" s="29"/>
+      <c r="J1219" s="29" t="s">
+        <v>1265</v>
+      </c>
       <c r="K1219" s="29"/>
       <c r="L1219" s="31"/>
       <c r="M1219" s="29"/>
@@ -58126,8 +58165,12 @@
       <c r="A1220" s="29" t="s">
         <v>2974</v>
       </c>
-      <c r="B1220" s="125"/>
-      <c r="C1220" s="83"/>
+      <c r="B1220" s="125" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C1220" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1220" s="100" t="s">
         <v>346</v>
       </c>
@@ -58146,7 +58189,9 @@
       <c r="I1220" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1220" s="29"/>
+      <c r="J1220" s="29" t="s">
+        <v>1266</v>
+      </c>
       <c r="K1220" s="29"/>
       <c r="L1220" s="31"/>
       <c r="M1220" s="29"/>
@@ -58155,8 +58200,12 @@
       <c r="A1221" s="29" t="s">
         <v>2975</v>
       </c>
-      <c r="B1221" s="125"/>
-      <c r="C1221" s="83"/>
+      <c r="B1221" s="128" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C1221" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1221" s="100" t="s">
         <v>346</v>
       </c>
@@ -58175,7 +58224,9 @@
       <c r="I1221" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1221" s="29"/>
+      <c r="J1221" s="29" t="s">
+        <v>1268</v>
+      </c>
       <c r="K1221" s="29"/>
       <c r="L1221" s="31"/>
       <c r="M1221" s="29"/>
@@ -58184,8 +58235,12 @@
       <c r="A1222" s="29" t="s">
         <v>2976</v>
       </c>
-      <c r="B1222" s="125"/>
-      <c r="C1222" s="83"/>
+      <c r="B1222" s="128" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C1222" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1222" s="100" t="s">
         <v>346</v>
       </c>
@@ -58204,7 +58259,9 @@
       <c r="I1222" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1222" s="29"/>
+      <c r="J1222" s="29" t="s">
+        <v>1269</v>
+      </c>
       <c r="K1222" s="29"/>
       <c r="L1222" s="31"/>
       <c r="M1222" s="29"/>
@@ -58213,8 +58270,12 @@
       <c r="A1223" s="29" t="s">
         <v>2977</v>
       </c>
-      <c r="B1223" s="125"/>
-      <c r="C1223" s="83"/>
+      <c r="B1223" s="125" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C1223" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1223" s="100" t="s">
         <v>347</v>
       </c>
@@ -58233,7 +58294,9 @@
       <c r="I1223" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1223" s="29"/>
+      <c r="J1223" s="29" t="s">
+        <v>1270</v>
+      </c>
       <c r="K1223" s="29"/>
       <c r="L1223" s="31"/>
       <c r="M1223" s="29"/>
@@ -58242,8 +58305,12 @@
       <c r="A1224" s="29" t="s">
         <v>2978</v>
       </c>
-      <c r="B1224" s="125"/>
-      <c r="C1224" s="83"/>
+      <c r="B1224" s="125" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C1224" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1224" s="100" t="s">
         <v>347</v>
       </c>
@@ -58262,7 +58329,9 @@
       <c r="I1224" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1224" s="29"/>
+      <c r="J1224" s="29" t="s">
+        <v>2359</v>
+      </c>
       <c r="K1224" s="29"/>
       <c r="L1224" s="31"/>
       <c r="M1224" s="29"/>
@@ -58271,8 +58340,12 @@
       <c r="A1225" s="29" t="s">
         <v>2979</v>
       </c>
-      <c r="B1225" s="125"/>
-      <c r="C1225" s="83"/>
+      <c r="B1225" s="127" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C1225" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1225" s="100" t="s">
         <v>347</v>
       </c>
@@ -58291,7 +58364,9 @@
       <c r="I1225" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="J1225" s="29"/>
+      <c r="J1225" s="29" t="s">
+        <v>2360</v>
+      </c>
       <c r="K1225" s="29"/>
       <c r="L1225" s="31"/>
       <c r="M1225" s="29"/>
@@ -58300,8 +58375,12 @@
       <c r="A1226" s="29" t="s">
         <v>2980</v>
       </c>
-      <c r="B1226" s="126"/>
-      <c r="C1226" s="83"/>
+      <c r="B1226" s="126" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C1226" s="83" t="s">
+        <v>2964</v>
+      </c>
       <c r="D1226" s="100" t="s">
         <v>347</v>
       </c>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBB6F18-29BD-3740-AD7B-51DF1B6469D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9414C106-B1B8-BB49-8AE8-269E3C57F134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7120" yWindow="1520" windowWidth="23120" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
+    <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
   <sheets>
     <sheet name="Cables" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10007" uniqueCount="3018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10109" uniqueCount="3054">
   <si>
     <t>Tag</t>
   </si>
@@ -9095,6 +9095,114 @@
   </si>
   <si>
     <t>a829</t>
+  </si>
+  <si>
+    <t>faderport</t>
+  </si>
+  <si>
+    <t>2510-0601</t>
+  </si>
+  <si>
+    <t>2510-0602</t>
+  </si>
+  <si>
+    <t>2510-0603</t>
+  </si>
+  <si>
+    <t>2510-0604</t>
+  </si>
+  <si>
+    <t>2510-0605</t>
+  </si>
+  <si>
+    <t>2510-0606</t>
+  </si>
+  <si>
+    <t>2510-0607</t>
+  </si>
+  <si>
+    <t>2510-0608</t>
+  </si>
+  <si>
+    <t>2510-0609</t>
+  </si>
+  <si>
+    <t>2510-0610</t>
+  </si>
+  <si>
+    <t>524.425MHz</t>
+  </si>
+  <si>
+    <t>526.875MHz</t>
+  </si>
+  <si>
+    <t>522.250MHz</t>
+  </si>
+  <si>
+    <t>523.550MHz</t>
+  </si>
+  <si>
+    <t>rt1229</t>
+  </si>
+  <si>
+    <t>rt1230</t>
+  </si>
+  <si>
+    <t>rt1231</t>
+  </si>
+  <si>
+    <t>rt1232</t>
+  </si>
+  <si>
+    <t>rt1233</t>
+  </si>
+  <si>
+    <t>rt1234</t>
+  </si>
+  <si>
+    <t>rt1235</t>
+  </si>
+  <si>
+    <t>rt1236</t>
+  </si>
+  <si>
+    <t>rt1237</t>
+  </si>
+  <si>
+    <t>rt1238</t>
+  </si>
+  <si>
+    <t>IEM Unit 1</t>
+  </si>
+  <si>
+    <t>IEM Unit 2</t>
+  </si>
+  <si>
+    <t>IEM Unit 3</t>
+  </si>
+  <si>
+    <t>IEM Unit 4</t>
+  </si>
+  <si>
+    <t>IEM Unit 5</t>
+  </si>
+  <si>
+    <t>IEM Unit 6</t>
+  </si>
+  <si>
+    <t>IEM Unit 7</t>
+  </si>
+  <si>
+    <t>IEM Unit 8</t>
+  </si>
+  <si>
+    <t>IEM Unit 9</t>
+  </si>
+  <si>
+    <t>IEM Unit 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel association is notional </t>
   </si>
 </sst>
 </file>
@@ -21924,13 +22032,13 @@
         <v>188</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C89" s="23" t="s">
         <v>236</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E89" s="23" t="s">
         <v>55</v>
@@ -21938,14 +22046,18 @@
       <c r="F89" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="G89" s="23"/>
+      <c r="G89" s="23" t="s">
+        <v>55</v>
+      </c>
       <c r="H89" s="23" t="s">
         <v>36</v>
       </c>
       <c r="I89" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="J89" s="23"/>
+      <c r="J89" s="23" t="s">
+        <v>3018</v>
+      </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
       <c r="M89" s="24"/>
@@ -58490,152 +58602,372 @@
       <c r="M1228" s="29"/>
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1229" s="29"/>
-      <c r="B1229" s="100"/>
-      <c r="C1229" s="83"/>
-      <c r="D1229" s="85"/>
-      <c r="E1229" s="83"/>
-      <c r="F1229" s="31"/>
-      <c r="G1229" s="31"/>
-      <c r="H1229" s="29"/>
-      <c r="I1229" s="119"/>
-      <c r="J1229" s="29"/>
-      <c r="K1229" s="29"/>
+      <c r="A1229" s="29" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B1229" s="100" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1229" s="83" t="s">
+        <v>3029</v>
+      </c>
+      <c r="D1229" s="85" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E1229" s="83" t="s">
+        <v>3029</v>
+      </c>
+      <c r="F1229" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1229" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1229" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1229" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1229" s="29" t="s">
+        <v>3043</v>
+      </c>
+      <c r="K1229" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1229" s="31"/>
       <c r="M1229" s="29"/>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1230" s="29"/>
-      <c r="B1230" s="100"/>
-      <c r="C1230" s="83"/>
-      <c r="D1230" s="85"/>
-      <c r="E1230" s="83"/>
-      <c r="F1230" s="31"/>
-      <c r="G1230" s="31"/>
-      <c r="H1230" s="29"/>
-      <c r="I1230" s="119"/>
-      <c r="J1230" s="29"/>
-      <c r="K1230" s="29"/>
+      <c r="A1230" s="29" t="s">
+        <v>3034</v>
+      </c>
+      <c r="B1230" s="100" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1230" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D1230" s="85" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E1230" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="F1230" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1230" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1230" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1230" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1230" s="29" t="s">
+        <v>3044</v>
+      </c>
+      <c r="K1230" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1230" s="31"/>
       <c r="M1230" s="29"/>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1231" s="29"/>
-      <c r="B1231" s="100"/>
-      <c r="C1231" s="83"/>
-      <c r="D1231" s="85"/>
-      <c r="E1231" s="83"/>
-      <c r="F1231" s="31"/>
-      <c r="G1231" s="31"/>
-      <c r="H1231" s="29"/>
-      <c r="I1231" s="119"/>
-      <c r="J1231" s="29"/>
-      <c r="K1231" s="29"/>
+      <c r="A1231" s="29" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B1231" s="100" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1231" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D1231" s="85" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E1231" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="F1231" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1231" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1231" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1231" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1231" s="29" t="s">
+        <v>3045</v>
+      </c>
+      <c r="K1231" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1231" s="31"/>
       <c r="M1231" s="29"/>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1232" s="29"/>
-      <c r="B1232" s="100"/>
-      <c r="C1232" s="83"/>
-      <c r="D1232" s="85"/>
-      <c r="E1232" s="83"/>
-      <c r="F1232" s="31"/>
-      <c r="G1232" s="31"/>
-      <c r="H1232" s="29"/>
-      <c r="I1232" s="119"/>
-      <c r="J1232" s="29"/>
-      <c r="K1232" s="29"/>
+      <c r="A1232" s="29" t="s">
+        <v>3036</v>
+      </c>
+      <c r="B1232" s="100" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C1232" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D1232" s="85" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E1232" s="83" t="s">
+        <v>3030</v>
+      </c>
+      <c r="F1232" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1232" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1232" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1232" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1232" s="29" t="s">
+        <v>3046</v>
+      </c>
+      <c r="K1232" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1232" s="31"/>
       <c r="M1232" s="29"/>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1233" s="29"/>
-      <c r="B1233" s="100"/>
-      <c r="C1233" s="83"/>
-      <c r="D1233" s="85"/>
-      <c r="E1233" s="83"/>
-      <c r="F1233" s="31"/>
-      <c r="G1233" s="31"/>
-      <c r="H1233" s="29"/>
-      <c r="I1233" s="119"/>
-      <c r="J1233" s="29"/>
-      <c r="K1233" s="29"/>
+      <c r="A1233" s="29" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B1233" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1233" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="D1233" s="85" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E1233" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1233" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1233" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1233" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1233" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1233" s="29" t="s">
+        <v>3047</v>
+      </c>
+      <c r="K1233" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1233" s="31"/>
       <c r="M1233" s="29"/>
     </row>
     <row r="1234" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1234" s="29"/>
-      <c r="B1234" s="100"/>
-      <c r="C1234" s="83"/>
-      <c r="D1234" s="85"/>
-      <c r="E1234" s="83"/>
-      <c r="F1234" s="31"/>
-      <c r="G1234" s="31"/>
-      <c r="H1234" s="29"/>
-      <c r="I1234" s="119"/>
-      <c r="J1234" s="29"/>
-      <c r="K1234" s="29"/>
+      <c r="A1234" s="29" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B1234" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1234" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="D1234" s="85" t="s">
+        <v>3024</v>
+      </c>
+      <c r="E1234" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1234" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1234" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1234" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1234" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1234" s="29" t="s">
+        <v>3048</v>
+      </c>
+      <c r="K1234" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1234" s="31"/>
       <c r="M1234" s="29"/>
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1235" s="29"/>
-      <c r="B1235" s="100"/>
-      <c r="C1235" s="83"/>
-      <c r="D1235" s="85"/>
-      <c r="E1235" s="83"/>
-      <c r="F1235" s="31"/>
-      <c r="G1235" s="31"/>
-      <c r="H1235" s="29"/>
-      <c r="I1235" s="119"/>
-      <c r="J1235" s="29"/>
-      <c r="K1235" s="29"/>
+      <c r="A1235" s="29" t="s">
+        <v>3039</v>
+      </c>
+      <c r="B1235" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1235" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="D1235" s="85" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E1235" s="83" t="s">
+        <v>3031</v>
+      </c>
+      <c r="F1235" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1235" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1235" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1235" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1235" s="29" t="s">
+        <v>3049</v>
+      </c>
+      <c r="K1235" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1235" s="31"/>
       <c r="M1235" s="29"/>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1236" s="29"/>
-      <c r="B1236" s="100"/>
-      <c r="C1236" s="83"/>
-      <c r="D1236" s="85"/>
-      <c r="E1236" s="83"/>
-      <c r="F1236" s="31"/>
-      <c r="G1236" s="31"/>
-      <c r="H1236" s="29"/>
-      <c r="I1236" s="119"/>
-      <c r="J1236" s="29"/>
-      <c r="K1236" s="29"/>
+      <c r="A1236" s="29" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B1236" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1236" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1236" s="85" t="s">
+        <v>3026</v>
+      </c>
+      <c r="E1236" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="F1236" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1236" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1236" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1236" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1236" s="29" t="s">
+        <v>3050</v>
+      </c>
+      <c r="K1236" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1236" s="31"/>
       <c r="M1236" s="29"/>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1237" s="29"/>
-      <c r="B1237" s="100"/>
-      <c r="C1237" s="83"/>
-      <c r="D1237" s="85"/>
-      <c r="E1237" s="83"/>
-      <c r="F1237" s="31"/>
-      <c r="G1237" s="31"/>
-      <c r="H1237" s="29"/>
-      <c r="I1237" s="119"/>
-      <c r="J1237" s="29"/>
-      <c r="K1237" s="29"/>
+      <c r="A1237" s="29" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B1237" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1237" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1237" s="85" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E1237" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="F1237" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1237" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1237" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1237" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1237" s="29" t="s">
+        <v>3051</v>
+      </c>
+      <c r="K1237" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1237" s="31"/>
       <c r="M1237" s="29"/>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1238" s="29"/>
-      <c r="B1238" s="100"/>
-      <c r="C1238" s="83"/>
-      <c r="D1238" s="85"/>
-      <c r="E1238" s="83"/>
-      <c r="F1238" s="31"/>
-      <c r="G1238" s="31"/>
-      <c r="H1238" s="29"/>
-      <c r="I1238" s="119"/>
-      <c r="J1238" s="29"/>
-      <c r="K1238" s="29"/>
+      <c r="A1238" s="29" t="s">
+        <v>3042</v>
+      </c>
+      <c r="B1238" s="100" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C1238" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D1238" s="85" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E1238" s="83" t="s">
+        <v>3032</v>
+      </c>
+      <c r="F1238" s="31" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G1238" s="31" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1238" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1238" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1238" s="29" t="s">
+        <v>3052</v>
+      </c>
+      <c r="K1238" s="29" t="s">
+        <v>3053</v>
+      </c>
       <c r="L1238" s="31"/>
       <c r="M1238" s="29"/>
     </row>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC20681-08D4-8248-A758-51D934B78088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229176E8-5063-C94D-B5B8-3A245C21A986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10102" uniqueCount="3052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10132" uniqueCount="3061">
   <si>
     <t>Tag</t>
   </si>
@@ -9197,6 +9197,33 @@
   </si>
   <si>
     <t>temp cable - true label unknown</t>
+  </si>
+  <si>
+    <t>2605-1402</t>
+  </si>
+  <si>
+    <t>audio-xlr</t>
+  </si>
+  <si>
+    <t>9m</t>
+  </si>
+  <si>
+    <t>ProPresenter Talkback</t>
+  </si>
+  <si>
+    <t>2605-1400</t>
+  </si>
+  <si>
+    <t>2605-1401</t>
+  </si>
+  <si>
+    <t>tbd</t>
+  </si>
+  <si>
+    <t>Stage Display TV</t>
+  </si>
+  <si>
+    <t>jump1242</t>
   </si>
 </sst>
 </file>
@@ -50195,18 +50222,10 @@
       <c r="A975" s="29" t="s">
         <v>2282</v>
       </c>
-      <c r="B975" s="112" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C975" s="82" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D975" s="79" t="s">
-        <v>2279</v>
-      </c>
-      <c r="E975" s="82" t="s">
-        <v>218</v>
-      </c>
+      <c r="B975" s="112"/>
+      <c r="C975" s="82"/>
+      <c r="D975" s="79"/>
+      <c r="E975" s="82"/>
       <c r="F975" s="31" t="s">
         <v>1564</v>
       </c>
@@ -50219,9 +50238,7 @@
       <c r="I975" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J975" s="29" t="s">
-        <v>2281</v>
-      </c>
+      <c r="J975" s="29"/>
       <c r="K975" s="29"/>
       <c r="L975" s="31" t="s">
         <v>2284</v>
@@ -58952,60 +58969,130 @@
       <c r="M1238" s="29"/>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1239" s="29"/>
+      <c r="A1239" s="29" t="s">
+        <v>3052</v>
+      </c>
       <c r="B1239" s="100"/>
       <c r="C1239" s="83"/>
-      <c r="D1239" s="85"/>
+      <c r="D1239" s="85" t="s">
+        <v>2241</v>
+      </c>
       <c r="E1239" s="83"/>
-      <c r="F1239" s="31"/>
-      <c r="G1239" s="31"/>
-      <c r="H1239" s="29"/>
-      <c r="I1239" s="119"/>
-      <c r="J1239" s="29"/>
+      <c r="F1239" s="31" t="s">
+        <v>3053</v>
+      </c>
+      <c r="G1239" s="31" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H1239" s="29" t="s">
+        <v>3054</v>
+      </c>
+      <c r="I1239" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1239" s="29" t="s">
+        <v>3055</v>
+      </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
       <c r="M1239" s="29"/>
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1240" s="29"/>
-      <c r="B1240" s="100"/>
-      <c r="C1240" s="83"/>
-      <c r="D1240" s="85"/>
-      <c r="E1240" s="83"/>
-      <c r="F1240" s="31"/>
-      <c r="G1240" s="31"/>
-      <c r="H1240" s="29"/>
-      <c r="I1240" s="119"/>
-      <c r="J1240" s="29"/>
+      <c r="A1240" s="29" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1240" s="100" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C1240" s="83" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D1240" s="85" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E1240" s="83" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1240" s="31" t="s">
+        <v>1564</v>
+      </c>
+      <c r="G1240" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1240" s="29" t="s">
+        <v>3058</v>
+      </c>
+      <c r="I1240" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1240" s="29" t="s">
+        <v>3059</v>
+      </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
       <c r="M1240" s="29"/>
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1241" s="29"/>
-      <c r="B1241" s="100"/>
-      <c r="C1241" s="83"/>
-      <c r="D1241" s="85"/>
-      <c r="E1241" s="83"/>
-      <c r="F1241" s="31"/>
-      <c r="G1241" s="31"/>
-      <c r="H1241" s="29"/>
-      <c r="I1241" s="119"/>
-      <c r="J1241" s="29"/>
+      <c r="A1241" s="29" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B1241" s="29" t="s">
+        <v>1642</v>
+      </c>
+      <c r="C1241" s="83" t="s">
+        <v>2421</v>
+      </c>
+      <c r="D1241" s="85" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E1241" s="83" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F1241" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1241" s="31" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H1241" s="29" t="s">
+        <v>3058</v>
+      </c>
+      <c r="I1241" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1241" s="29" t="s">
+        <v>3059</v>
+      </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
       <c r="M1241" s="29"/>
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1242" s="29"/>
-      <c r="B1242" s="100"/>
-      <c r="C1242" s="83"/>
-      <c r="D1242" s="85"/>
-      <c r="E1242" s="83"/>
-      <c r="F1242" s="31"/>
-      <c r="G1242" s="31"/>
+      <c r="A1242" s="29" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1242" s="100" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C1242" s="83" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D1242" s="29" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E1242" s="83" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F1242" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1242" s="31" t="s">
+        <v>1491</v>
+      </c>
       <c r="H1242" s="29"/>
-      <c r="I1242" s="119"/>
+      <c r="I1242" s="119" t="s">
+        <v>63</v>
+      </c>
       <c r="J1242" s="29"/>
       <c r="K1242" s="29"/>
       <c r="L1242" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229176E8-5063-C94D-B5B8-3A245C21A986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF16B82-320E-3346-BCE2-E4E420C70853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="38" r:id="rId3"/>
-    <pivotCache cacheId="39" r:id="rId4"/>
+    <pivotCache cacheId="42" r:id="rId3"/>
+    <pivotCache cacheId="43" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10132" uniqueCount="3061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10153" uniqueCount="3069">
   <si>
     <t>Tag</t>
   </si>
@@ -9224,6 +9224,30 @@
   </si>
   <si>
     <t>jump1242</t>
+  </si>
+  <si>
+    <t>25m</t>
+  </si>
+  <si>
+    <t>2605-1500</t>
+  </si>
+  <si>
+    <t>2605-1502</t>
+  </si>
+  <si>
+    <t>2605-1503</t>
+  </si>
+  <si>
+    <t>tbd1243</t>
+  </si>
+  <si>
+    <t>tbd1244</t>
+  </si>
+  <si>
+    <t>not yet</t>
+  </si>
+  <si>
+    <t>Nursery Stream Deck</t>
   </si>
 </sst>
 </file>
@@ -9645,7 +9669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9875,19 +9899,15 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18755,7 +18775,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="38" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18818,7 +18838,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="43" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19838,7 +19858,7 @@
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="129"/>
+      <c r="H15" s="29"/>
       <c r="I15" s="119"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -19878,7 +19898,7 @@
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
-      <c r="H17" s="129"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="119"/>
       <c r="J17" s="23"/>
       <c r="K17" s="23"/>
@@ -58007,7 +58027,7 @@
       <c r="A1212" s="29" t="s">
         <v>2830</v>
       </c>
-      <c r="B1212" s="125" t="s">
+      <c r="B1212" s="100" t="s">
         <v>2846</v>
       </c>
       <c r="C1212" s="83" t="s">
@@ -58042,7 +58062,7 @@
       <c r="A1213" s="29" t="s">
         <v>2831</v>
       </c>
-      <c r="B1213" s="125" t="s">
+      <c r="B1213" s="100" t="s">
         <v>2847</v>
       </c>
       <c r="C1213" s="83" t="s">
@@ -58077,7 +58097,7 @@
       <c r="A1214" s="29" t="s">
         <v>2832</v>
       </c>
-      <c r="B1214" s="125" t="s">
+      <c r="B1214" s="100" t="s">
         <v>2848</v>
       </c>
       <c r="C1214" s="83" t="s">
@@ -58112,7 +58132,7 @@
       <c r="A1215" s="29" t="s">
         <v>2833</v>
       </c>
-      <c r="B1215" s="125" t="s">
+      <c r="B1215" s="100" t="s">
         <v>2849</v>
       </c>
       <c r="C1215" s="83" t="s">
@@ -58147,7 +58167,7 @@
       <c r="A1216" s="29" t="s">
         <v>2834</v>
       </c>
-      <c r="B1216" s="125" t="s">
+      <c r="B1216" s="100" t="s">
         <v>2850</v>
       </c>
       <c r="C1216" s="83" t="s">
@@ -58182,7 +58202,7 @@
       <c r="A1217" s="29" t="s">
         <v>2835</v>
       </c>
-      <c r="B1217" s="125" t="s">
+      <c r="B1217" s="100" t="s">
         <v>2851</v>
       </c>
       <c r="C1217" s="83" t="s">
@@ -58217,7 +58237,7 @@
       <c r="A1218" s="29" t="s">
         <v>2836</v>
       </c>
-      <c r="B1218" s="125" t="s">
+      <c r="B1218" s="100" t="s">
         <v>2852</v>
       </c>
       <c r="C1218" s="83" t="s">
@@ -58252,7 +58272,7 @@
       <c r="A1219" s="29" t="s">
         <v>2837</v>
       </c>
-      <c r="B1219" s="125" t="s">
+      <c r="B1219" s="100" t="s">
         <v>2853</v>
       </c>
       <c r="C1219" s="83" t="s">
@@ -58287,7 +58307,7 @@
       <c r="A1220" s="29" t="s">
         <v>2838</v>
       </c>
-      <c r="B1220" s="125" t="s">
+      <c r="B1220" s="100" t="s">
         <v>2854</v>
       </c>
       <c r="C1220" s="83" t="s">
@@ -58322,7 +58342,7 @@
       <c r="A1221" s="29" t="s">
         <v>2839</v>
       </c>
-      <c r="B1221" s="128" t="s">
+      <c r="B1221" s="127" t="s">
         <v>2859</v>
       </c>
       <c r="C1221" s="83" t="s">
@@ -58357,7 +58377,7 @@
       <c r="A1222" s="29" t="s">
         <v>2840</v>
       </c>
-      <c r="B1222" s="128" t="s">
+      <c r="B1222" s="127" t="s">
         <v>2859</v>
       </c>
       <c r="C1222" s="83" t="s">
@@ -58392,7 +58412,7 @@
       <c r="A1223" s="29" t="s">
         <v>2841</v>
       </c>
-      <c r="B1223" s="125" t="s">
+      <c r="B1223" s="100" t="s">
         <v>2857</v>
       </c>
       <c r="C1223" s="83" t="s">
@@ -58427,7 +58447,7 @@
       <c r="A1224" s="29" t="s">
         <v>2842</v>
       </c>
-      <c r="B1224" s="125" t="s">
+      <c r="B1224" s="100" t="s">
         <v>2855</v>
       </c>
       <c r="C1224" s="83" t="s">
@@ -58462,7 +58482,7 @@
       <c r="A1225" s="29" t="s">
         <v>2843</v>
       </c>
-      <c r="B1225" s="127" t="s">
+      <c r="B1225" s="126" t="s">
         <v>2856</v>
       </c>
       <c r="C1225" s="83" t="s">
@@ -58497,7 +58517,7 @@
       <c r="A1226" s="29" t="s">
         <v>2844</v>
       </c>
-      <c r="B1226" s="126" t="s">
+      <c r="B1226" s="125" t="s">
         <v>2858</v>
       </c>
       <c r="C1226" s="83" t="s">
@@ -58972,12 +58992,18 @@
       <c r="A1239" s="29" t="s">
         <v>3052</v>
       </c>
-      <c r="B1239" s="100"/>
-      <c r="C1239" s="83"/>
+      <c r="B1239" s="100" t="s">
+        <v>3062</v>
+      </c>
+      <c r="C1239" s="83" t="s">
+        <v>772</v>
+      </c>
       <c r="D1239" s="85" t="s">
         <v>2241</v>
       </c>
-      <c r="E1239" s="83"/>
+      <c r="E1239" s="83" t="s">
+        <v>2006</v>
+      </c>
       <c r="F1239" s="31" t="s">
         <v>3053</v>
       </c>
@@ -59020,7 +59046,7 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3058</v>
+        <v>3061</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>99</v>
@@ -59055,7 +59081,7 @@
         <v>1491</v>
       </c>
       <c r="H1241" s="29" t="s">
-        <v>3058</v>
+        <v>1122</v>
       </c>
       <c r="I1241" s="119" t="s">
         <v>99</v>
@@ -59099,31 +59125,67 @@
       <c r="M1242" s="29"/>
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1243" s="29"/>
-      <c r="B1243" s="100"/>
-      <c r="C1243" s="83"/>
-      <c r="D1243" s="85"/>
-      <c r="E1243" s="83"/>
-      <c r="F1243" s="31"/>
-      <c r="G1243" s="31"/>
+      <c r="A1243" s="29" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1243" s="100" t="s">
+        <v>3063</v>
+      </c>
+      <c r="C1243" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1243" s="85" t="s">
+        <v>3064</v>
+      </c>
+      <c r="E1243" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1243" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1243" s="31" t="s">
+        <v>55</v>
+      </c>
       <c r="H1243" s="29"/>
-      <c r="I1243" s="119"/>
-      <c r="J1243" s="29"/>
+      <c r="I1243" s="119" t="s">
+        <v>3067</v>
+      </c>
+      <c r="J1243" s="29" t="s">
+        <v>3068</v>
+      </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
       <c r="M1243" s="29"/>
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1244" s="29"/>
-      <c r="B1244" s="100"/>
-      <c r="C1244" s="83"/>
-      <c r="D1244" s="85"/>
-      <c r="E1244" s="83"/>
-      <c r="F1244" s="31"/>
-      <c r="G1244" s="31"/>
+      <c r="A1244" s="29" t="s">
+        <v>3066</v>
+      </c>
+      <c r="B1244" s="85" t="s">
+        <v>3064</v>
+      </c>
+      <c r="C1244" s="83" t="s">
+        <v>2198</v>
+      </c>
+      <c r="D1244" s="29" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E1244" s="83" t="s">
+        <v>3058</v>
+      </c>
+      <c r="F1244" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1244" s="31" t="s">
+        <v>1491</v>
+      </c>
       <c r="H1244" s="29"/>
-      <c r="I1244" s="119"/>
-      <c r="J1244" s="29"/>
+      <c r="I1244" s="119" t="s">
+        <v>3067</v>
+      </c>
+      <c r="J1244" s="29" t="s">
+        <v>3068</v>
+      </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>
       <c r="M1244" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581B6396-7691-BC47-BCB7-246BD1613674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C922BD61-058B-5F47-A8E7-AD5D526F943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10166" uniqueCount="3068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10166" uniqueCount="3067">
   <si>
     <t>Tag</t>
   </si>
@@ -9179,9 +9179,6 @@
   </si>
   <si>
     <t>2605-1402</t>
-  </si>
-  <si>
-    <t>audio-xlr</t>
   </si>
   <si>
     <t>9m</t>
@@ -49982,7 +49979,7 @@
         <v>1179</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>347</v>
@@ -50011,7 +50008,7 @@
         <v>1180</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>348</v>
@@ -50040,7 +50037,7 @@
         <v>1181</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>347</v>
@@ -50069,7 +50066,7 @@
         <v>1182</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>348</v>
@@ -50136,7 +50133,7 @@
         <v>1542</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>772</v>
@@ -50151,7 +50148,7 @@
         <v>497</v>
       </c>
       <c r="G971" s="31" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="H971" s="29"/>
       <c r="I971" s="119" t="s">
@@ -50166,10 +50163,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>772</v>
@@ -50184,7 +50181,7 @@
         <v>497</v>
       </c>
       <c r="G972" s="31" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="H972" s="29"/>
       <c r="I972" s="119" t="s">
@@ -59016,7 +59013,7 @@
         <v>3045</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>772</v>
@@ -59028,19 +59025,19 @@
         <v>2006</v>
       </c>
       <c r="F1239" s="31" t="s">
-        <v>3046</v>
+        <v>497</v>
       </c>
       <c r="G1239" s="31" t="s">
         <v>1495</v>
       </c>
       <c r="H1239" s="29" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="I1239" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1239" s="29" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
@@ -59048,7 +59045,7 @@
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1240" s="29" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="B1240" s="100" t="s">
         <v>1063</v>
@@ -59069,13 +59066,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59083,7 +59080,7 @@
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1241" s="29" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="B1241" s="29" t="s">
         <v>1642</v>
@@ -59110,7 +59107,7 @@
         <v>99</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59118,7 +59115,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1685</v>
@@ -59149,16 +59146,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>55</v>
@@ -59171,10 +59168,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
+        <v>3059</v>
+      </c>
+      <c r="J1243" s="29" t="s">
         <v>3060</v>
-      </c>
-      <c r="J1243" s="29" t="s">
-        <v>3061</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59182,10 +59179,10 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B1244" s="85" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C1244" s="83" t="s">
         <v>2198</v>
@@ -59194,7 +59191,7 @@
         <v>1642</v>
       </c>
       <c r="E1244" s="83" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="F1244" s="31" t="s">
         <v>234</v>
@@ -59204,10 +59201,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
+        <v>3059</v>
+      </c>
+      <c r="J1244" s="29" t="s">
         <v>3060</v>
-      </c>
-      <c r="J1244" s="29" t="s">
-        <v>3061</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C922BD61-058B-5F47-A8E7-AD5D526F943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8A3988-4A89-9B40-8A5E-E26D168F7C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10166" uniqueCount="3067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10166" uniqueCount="3066">
   <si>
     <t>Tag</t>
   </si>
@@ -9227,9 +9227,6 @@
   </si>
   <si>
     <t>2410-1700</t>
-  </si>
-  <si>
-    <t>aa_mic</t>
   </si>
   <si>
     <t>2408-0100</t>
@@ -49979,7 +49976,7 @@
         <v>1179</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>347</v>
@@ -50008,7 +50005,7 @@
         <v>1180</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>348</v>
@@ -50037,7 +50034,7 @@
         <v>1181</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>347</v>
@@ -50066,7 +50063,7 @@
         <v>1182</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>348</v>
@@ -50148,7 +50145,7 @@
         <v>497</v>
       </c>
       <c r="G971" s="31" t="s">
-        <v>3062</v>
+        <v>1495</v>
       </c>
       <c r="H971" s="29"/>
       <c r="I971" s="119" t="s">
@@ -50163,10 +50160,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>772</v>
@@ -50181,7 +50178,7 @@
         <v>497</v>
       </c>
       <c r="G972" s="31" t="s">
-        <v>3062</v>
+        <v>1495</v>
       </c>
       <c r="H972" s="29"/>
       <c r="I972" s="119" t="s">

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A068A0-298E-9D4A-9AAF-2EAD96735043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F204DCCC-656D-2D42-BFFF-D94C2A092148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10162" uniqueCount="3068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10164" uniqueCount="3069">
   <si>
     <t>Tag</t>
   </si>
@@ -8593,9 +8593,6 @@
     <t>ZAMU-B015</t>
   </si>
   <si>
-    <t>ZAMU-A002 or ZAMU-A003</t>
-  </si>
-  <si>
     <t>2509-1703-F03</t>
   </si>
   <si>
@@ -8779,9 +8776,6 @@
     <t>a441</t>
   </si>
   <si>
-    <t>a442</t>
-  </si>
-  <si>
     <t>a443</t>
   </si>
   <si>
@@ -9245,6 +9239,15 @@
   </si>
   <si>
     <t>unk2R</t>
+  </si>
+  <si>
+    <t>2605-1700</t>
+  </si>
+  <si>
+    <t>Beta52</t>
+  </si>
+  <si>
+    <t>ZAMU-A003</t>
   </si>
 </sst>
 </file>
@@ -9359,7 +9362,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9417,12 +9420,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBA4EFF"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -9902,7 +9899,7 @@
     <xf numFmtId="49" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -22094,7 +22091,7 @@
         <v>63</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
@@ -22630,7 +22627,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="B108" s="22" t="s">
         <v>226</v>
@@ -22639,7 +22636,7 @@
         <v>136</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>136</v>
@@ -22723,7 +22720,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="B111" s="22" t="s">
         <v>242</v>
@@ -22820,7 +22817,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="B114" s="22" t="s">
         <v>245</v>
@@ -22853,7 +22850,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="B115" s="22" t="s">
         <v>245</v>
@@ -22882,7 +22879,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="B116" s="22" t="s">
         <v>245</v>
@@ -22911,7 +22908,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="B117" s="22" t="s">
         <v>263</v>
@@ -22938,7 +22935,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="B118" s="22" t="s">
         <v>265</v>
@@ -26755,7 +26752,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="29" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B233" s="31" t="s">
         <v>500</v>
@@ -26786,7 +26783,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="29" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="B234" s="31" t="s">
         <v>501</v>
@@ -26817,7 +26814,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="29" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="B235" s="31" t="s">
         <v>502</v>
@@ -26958,7 +26955,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="29" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="B240" s="31"/>
       <c r="C240" s="29"/>
@@ -26983,7 +26980,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="29" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="B241" s="31" t="s">
         <v>522</v>
@@ -27012,7 +27009,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="29" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="B242" s="31" t="s">
         <v>525</v>
@@ -27355,7 +27352,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="29" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="B253" s="31" t="s">
         <v>532</v>
@@ -27409,7 +27406,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="29" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="B255" s="31" t="s">
         <v>612</v>
@@ -27521,7 +27518,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="29" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B259" s="31" t="s">
         <v>536</v>
@@ -27937,7 +27934,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="29" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="B273" s="31" t="s">
         <v>536</v>
@@ -30069,7 +30066,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="29" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B343" s="31" t="s">
         <v>261</v>
@@ -30338,7 +30335,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="29" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="B352" s="29" t="s">
         <v>822</v>
@@ -30369,7 +30366,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="29" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="B353" s="29" t="s">
         <v>822</v>
@@ -30400,7 +30397,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="29" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="B354" s="29" t="s">
         <v>822</v>
@@ -30431,7 +30428,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="29" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="B355" s="29" t="s">
         <v>822</v>
@@ -30462,7 +30459,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="29" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="B356" s="31" t="s">
         <v>843</v>
@@ -30493,7 +30490,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="29" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="B357" s="31" t="s">
         <v>843</v>
@@ -30524,7 +30521,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="29" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="B358" s="31" t="s">
         <v>843</v>
@@ -30555,7 +30552,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="29" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B359" s="31" t="s">
         <v>843</v>
@@ -31025,7 +31022,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="B375" s="31" t="s">
         <v>263</v>
@@ -31056,7 +31053,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B376" s="31" t="s">
         <v>263</v>
@@ -31087,7 +31084,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="B377" s="31" t="s">
         <v>265</v>
@@ -31118,7 +31115,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="B378" s="31" t="s">
         <v>265</v>
@@ -31149,7 +31146,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="B379" s="31" t="s">
         <v>245</v>
@@ -31180,7 +31177,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="B380" s="31" t="s">
         <v>261</v>
@@ -31569,7 +31566,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="B393" s="31" t="s">
         <v>911</v>
@@ -31596,7 +31593,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="B394" s="31" t="s">
         <v>912</v>
@@ -31623,7 +31620,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="B395" s="29" t="s">
         <v>913</v>
@@ -31646,7 +31643,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="B396" s="29" t="s">
         <v>915</v>
@@ -31669,7 +31666,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="B397" s="29" t="s">
         <v>913</v>
@@ -31692,7 +31689,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="B398" s="31" t="s">
         <v>917</v>
@@ -31715,7 +31712,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="B399" s="31" t="s">
         <v>918</v>
@@ -31738,7 +31735,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="B400" s="31" t="s">
         <v>919</v>
@@ -31761,7 +31758,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="B401" s="31" t="s">
         <v>920</v>
@@ -31784,7 +31781,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="B402" s="31" t="s">
         <v>921</v>
@@ -31807,7 +31804,7 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="B403" s="31" t="s">
         <v>922</v>
@@ -31830,7 +31827,7 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="B404" s="31" t="s">
         <v>923</v>
@@ -31853,7 +31850,7 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="B405" s="31" t="s">
         <v>924</v>
@@ -31876,7 +31873,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="B406" s="31" t="s">
         <v>910</v>
@@ -32025,7 +32022,7 @@
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="B411" s="31" t="s">
         <v>261</v>
@@ -32050,7 +32047,7 @@
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="B412" s="31" t="s">
         <v>261</v>
@@ -32075,7 +32072,7 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="B413" s="31" t="s">
         <v>261</v>
@@ -32100,7 +32097,7 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="B414" s="31" t="s">
         <v>261</v>
@@ -32854,7 +32851,7 @@
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="B438" s="31" t="s">
         <v>995</v>
@@ -32889,7 +32886,7 @@
     </row>
     <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="B439" s="31" t="s">
         <v>995</v>
@@ -32924,7 +32921,7 @@
     </row>
     <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="29" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="B440" s="31" t="s">
         <v>995</v>
@@ -32959,7 +32956,7 @@
     </row>
     <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="29" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="B441" s="87" t="s">
         <v>1068</v>
@@ -32992,7 +32989,7 @@
     </row>
     <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
-        <v>2912</v>
+        <v>3066</v>
       </c>
       <c r="B442" s="87" t="s">
         <v>1471</v>
@@ -33013,17 +33010,21 @@
         <v>1495</v>
       </c>
       <c r="H442" s="29"/>
-      <c r="I442" s="29"/>
+      <c r="I442" s="29" t="s">
+        <v>99</v>
+      </c>
       <c r="J442" s="29" t="s">
         <v>1069</v>
       </c>
-      <c r="K442" s="29"/>
+      <c r="K442" s="29" t="s">
+        <v>3067</v>
+      </c>
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
     <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="29" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="B443" s="29" t="s">
         <v>1617</v>
@@ -33052,7 +33053,7 @@
     </row>
     <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="B444" s="87" t="s">
         <v>1624</v>
@@ -33085,7 +33086,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="B445" t="s">
         <v>1619</v>
@@ -33116,7 +33117,7 @@
     </row>
     <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="B446" t="s">
         <v>1620</v>
@@ -33147,7 +33148,7 @@
     </row>
     <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="B447" t="s">
         <v>1621</v>
@@ -33178,7 +33179,7 @@
     </row>
     <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="29" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="B448" t="s">
         <v>1622</v>
@@ -33209,7 +33210,7 @@
     </row>
     <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="29" t="s">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="B449" s="87" t="s">
         <v>1623</v>
@@ -33242,7 +33243,7 @@
     </row>
     <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="29" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="B450" s="87" t="s">
         <v>1469</v>
@@ -33273,7 +33274,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="B451" s="87" t="s">
         <v>1470</v>
@@ -33304,7 +33305,7 @@
     </row>
     <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="B452" s="31" t="s">
         <v>1257</v>
@@ -33984,7 +33985,7 @@
         <v>27</v>
       </c>
       <c r="H471" s="29" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="I471" s="29" t="s">
         <v>99</v>
@@ -33998,7 +33999,7 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="B472" s="29" t="s">
         <v>19</v>
@@ -34064,7 +34065,7 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="B474" s="29" t="s">
         <v>19</v>
@@ -34645,7 +34646,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="B491" s="32"/>
       <c r="C491" s="53" t="s">
@@ -34894,7 +34895,7 @@
     </row>
     <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="34" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="B498" s="59" t="s">
         <v>1124</v>
@@ -35236,7 +35237,7 @@
     </row>
     <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="B508" s="32"/>
       <c r="C508" s="53"/>
@@ -35263,7 +35264,7 @@
     </row>
     <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="24" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="B509" s="22"/>
       <c r="C509" s="25"/>
@@ -36408,7 +36409,7 @@
     </row>
     <row r="542" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="29" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="B542" s="59" t="s">
         <v>1687</v>
@@ -36437,7 +36438,7 @@
     </row>
     <row r="543" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="29" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="B543" s="59" t="s">
         <v>1687</v>
@@ -36466,7 +36467,7 @@
     </row>
     <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="29" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="B544" s="59" t="s">
         <v>1687</v>
@@ -36498,7 +36499,7 @@
         <v>1511</v>
       </c>
       <c r="B545" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C545" s="36">
         <v>2</v>
@@ -36527,7 +36528,7 @@
         <v>1512</v>
       </c>
       <c r="B546" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C546" s="36">
         <v>3</v>
@@ -36556,7 +36557,7 @@
         <v>1513</v>
       </c>
       <c r="B547" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C547" s="36">
         <v>4</v>
@@ -36585,7 +36586,7 @@
         <v>1514</v>
       </c>
       <c r="B548" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C548" s="36">
         <v>5</v>
@@ -36614,7 +36615,7 @@
         <v>1515</v>
       </c>
       <c r="B549" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C549" s="36">
         <v>6</v>
@@ -36643,7 +36644,7 @@
         <v>1516</v>
       </c>
       <c r="B550" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C550" s="36">
         <v>7</v>
@@ -36672,7 +36673,7 @@
         <v>1517</v>
       </c>
       <c r="B551" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C551" s="36">
         <v>8</v>
@@ -36701,7 +36702,7 @@
         <v>1518</v>
       </c>
       <c r="B552" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C552" s="36">
         <v>9</v>
@@ -36730,7 +36731,7 @@
         <v>1519</v>
       </c>
       <c r="B553" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C553" s="36">
         <v>10</v>
@@ -36759,7 +36760,7 @@
         <v>1520</v>
       </c>
       <c r="B554" s="73" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C554" s="36">
         <v>11</v>
@@ -37078,7 +37079,7 @@
         <v>1290</v>
       </c>
       <c r="B565" s="84" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C565" s="73" t="s">
         <v>2251</v>
@@ -38265,7 +38266,7 @@
     </row>
     <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="29" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="B603" s="73" t="s">
         <v>1302</v>
@@ -38298,7 +38299,7 @@
     </row>
     <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="29" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="B604" s="73" t="s">
         <v>1302</v>
@@ -38331,7 +38332,7 @@
     </row>
     <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="29" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="B605" s="73" t="s">
         <v>1302</v>
@@ -38364,7 +38365,7 @@
     </row>
     <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="29" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="B606" s="73" t="s">
         <v>1302</v>
@@ -38397,7 +38398,7 @@
     </row>
     <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="29" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="B607" s="73" t="s">
         <v>1302</v>
@@ -38428,7 +38429,7 @@
     </row>
     <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="29" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="B608" s="73" t="s">
         <v>1302</v>
@@ -38459,7 +38460,7 @@
     </row>
     <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="29" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="B609" s="73" t="s">
         <v>1302</v>
@@ -38490,7 +38491,7 @@
     </row>
     <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="29" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="B610" s="73" t="s">
         <v>1302</v>
@@ -38521,7 +38522,7 @@
     </row>
     <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="29" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="B611" s="73" t="s">
         <v>1302</v>
@@ -38552,7 +38553,7 @@
     </row>
     <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="29" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
       <c r="B612" s="73" t="s">
         <v>1302</v>
@@ -38583,7 +38584,7 @@
     </row>
     <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="29" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="B613" s="73" t="s">
         <v>1302</v>
@@ -38614,7 +38615,7 @@
     </row>
     <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="29" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="B614" s="73" t="s">
         <v>1302</v>
@@ -38645,7 +38646,7 @@
     </row>
     <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="29" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="B615" s="73" t="s">
         <v>1302</v>
@@ -38676,7 +38677,7 @@
     </row>
     <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="29" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
       <c r="B616" s="73" t="s">
         <v>1302</v>
@@ -38707,7 +38708,7 @@
     </row>
     <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="29" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="B617" s="73" t="s">
         <v>1302</v>
@@ -38740,7 +38741,7 @@
     </row>
     <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="29" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="B618" s="73" t="s">
         <v>1302</v>
@@ -38773,7 +38774,7 @@
     </row>
     <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="29" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="B619" s="82" t="s">
         <v>1291</v>
@@ -38804,7 +38805,7 @@
     </row>
     <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="29" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="B620" s="82" t="s">
         <v>1291</v>
@@ -38835,7 +38836,7 @@
     </row>
     <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="29" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="B621" s="82" t="s">
         <v>1291</v>
@@ -38866,7 +38867,7 @@
     </row>
     <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="29" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="B622" s="82" t="s">
         <v>1291</v>
@@ -38899,7 +38900,7 @@
     </row>
     <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="29" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="B623" s="83" t="s">
         <v>1296</v>
@@ -38932,7 +38933,7 @@
     </row>
     <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="29" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="B624" s="83" t="s">
         <v>1296</v>
@@ -38963,7 +38964,7 @@
     </row>
     <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="29" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="B625" s="83" t="s">
         <v>1296</v>
@@ -38994,7 +38995,7 @@
     </row>
     <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="29" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="B626" s="83" t="s">
         <v>1296</v>
@@ -39091,7 +39092,7 @@
     </row>
     <row r="629" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A629" s="29" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="B629" s="82" t="s">
         <v>1350</v>
@@ -39118,7 +39119,7 @@
     </row>
     <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="B630" s="83" t="s">
         <v>1350</v>
@@ -41342,7 +41343,7 @@
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="B698" s="85" t="s">
         <v>1383</v>
@@ -41371,7 +41372,7 @@
     </row>
     <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="B699" s="85" t="s">
         <v>1383</v>
@@ -41400,7 +41401,7 @@
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="B700" s="85" t="s">
         <v>1383</v>
@@ -41429,7 +41430,7 @@
     </row>
     <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="B701" s="85" t="s">
         <v>1383</v>
@@ -41458,7 +41459,7 @@
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="B702" s="85" t="s">
         <v>1383</v>
@@ -41487,7 +41488,7 @@
     </row>
     <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="B703" s="85" t="s">
         <v>1383</v>
@@ -41516,7 +41517,7 @@
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="B704" s="85" t="s">
         <v>1383</v>
@@ -41545,7 +41546,7 @@
     </row>
     <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="B705" s="85" t="s">
         <v>1383</v>
@@ -41574,7 +41575,7 @@
     </row>
     <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="B706" s="85" t="s">
         <v>1383</v>
@@ -41603,7 +41604,7 @@
     </row>
     <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="B707" s="85" t="s">
         <v>1383</v>
@@ -41632,7 +41633,7 @@
     </row>
     <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="B708" s="85" t="s">
         <v>1383</v>
@@ -41661,7 +41662,7 @@
     </row>
     <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="B709" s="85" t="s">
         <v>1383</v>
@@ -41690,7 +41691,7 @@
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="B710" s="85" t="s">
         <v>1383</v>
@@ -41719,7 +41720,7 @@
     </row>
     <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="B711" s="85" t="s">
         <v>1383</v>
@@ -41748,7 +41749,7 @@
     </row>
     <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B712" s="85" t="s">
         <v>1383</v>
@@ -41777,7 +41778,7 @@
     </row>
     <row r="713" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A713" s="29" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="B713" s="85" t="s">
         <v>1383</v>
@@ -41806,7 +41807,7 @@
     </row>
     <row r="714" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A714" s="29" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="B714" s="85" t="s">
         <v>1384</v>
@@ -41835,7 +41836,7 @@
     </row>
     <row r="715" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A715" s="29" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="B715" s="85" t="s">
         <v>1384</v>
@@ -41864,7 +41865,7 @@
     </row>
     <row r="716" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A716" s="29" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="B716" s="85" t="s">
         <v>1384</v>
@@ -41893,7 +41894,7 @@
     </row>
     <row r="717" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A717" s="29" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="B717" s="85" t="s">
         <v>1384</v>
@@ -41922,7 +41923,7 @@
     </row>
     <row r="718" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A718" s="29" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="B718" s="85" t="s">
         <v>1384</v>
@@ -41951,7 +41952,7 @@
     </row>
     <row r="719" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="B719" s="85" t="s">
         <v>1384</v>
@@ -41980,7 +41981,7 @@
     </row>
     <row r="720" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A720" s="29" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="B720" s="85" t="s">
         <v>1384</v>
@@ -42009,7 +42010,7 @@
     </row>
     <row r="721" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="B721" s="85" t="s">
         <v>1384</v>
@@ -44671,7 +44672,7 @@
     </row>
     <row r="801" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="B801" s="83" t="s">
         <v>1543</v>
@@ -44702,7 +44703,7 @@
     </row>
     <row r="802" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="B802" s="83" t="s">
         <v>1543</v>
@@ -44733,7 +44734,7 @@
     </row>
     <row r="803" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="B803" s="83" t="s">
         <v>1543</v>
@@ -44764,7 +44765,7 @@
     </row>
     <row r="804" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="B804" s="83" t="s">
         <v>1543</v>
@@ -44795,7 +44796,7 @@
     </row>
     <row r="805" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="B805" s="83" t="s">
         <v>1543</v>
@@ -44826,7 +44827,7 @@
     </row>
     <row r="806" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A806" s="29" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="B806" s="85" t="s">
         <v>1498</v>
@@ -44855,7 +44856,7 @@
     </row>
     <row r="807" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A807" s="29" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="B807" s="85" t="s">
         <v>1498</v>
@@ -44884,7 +44885,7 @@
     </row>
     <row r="808" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="B808" s="85" t="s">
         <v>1499</v>
@@ -44913,7 +44914,7 @@
     </row>
     <row r="809" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B809" s="85" t="s">
         <v>1499</v>
@@ -44942,7 +44943,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="B810" s="85" t="s">
         <v>1502</v>
@@ -44986,19 +44987,19 @@
     </row>
     <row r="812" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="B812" s="83" t="s">
         <v>1688</v>
       </c>
       <c r="C812" s="83" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="D812" s="85" t="s">
         <v>1685</v>
       </c>
       <c r="E812" s="83" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="F812" s="31" t="s">
         <v>234</v>
@@ -45009,7 +45010,7 @@
       <c r="H812" s="29"/>
       <c r="I812" s="29"/>
       <c r="J812" s="29" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="K812" s="29"/>
       <c r="L812" s="31"/>
@@ -45127,7 +45128,7 @@
     </row>
     <row r="817" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B817" s="96" t="s">
         <v>1687</v>
@@ -45158,7 +45159,7 @@
     </row>
     <row r="818" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="B818" s="83" t="s">
         <v>1688</v>
@@ -45189,7 +45190,7 @@
     </row>
     <row r="819" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A819" s="29" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="B819" s="83" t="s">
         <v>1688</v>
@@ -45344,7 +45345,7 @@
     </row>
     <row r="824" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="B824" s="83" t="s">
         <v>1586</v>
@@ -45375,7 +45376,7 @@
     </row>
     <row r="825" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="B825" s="83" t="s">
         <v>1587</v>
@@ -45406,7 +45407,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1590</v>
@@ -45437,7 +45438,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1591</v>
@@ -45468,7 +45469,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1592</v>
@@ -45497,7 +45498,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1592</v>
@@ -49979,10 +49980,10 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A965" s="29" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>347</v>
@@ -50008,10 +50009,10 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>348</v>
@@ -50037,10 +50038,10 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A967" s="29" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>347</v>
@@ -50066,10 +50067,10 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>348</v>
@@ -50128,7 +50129,7 @@
         <v>1542</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>772</v>
@@ -50158,10 +50159,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>772</v>
@@ -58358,7 +58359,7 @@
         <v>2830</v>
       </c>
       <c r="B1221" s="127" t="s">
-        <v>2850</v>
+        <v>2206</v>
       </c>
       <c r="C1221" s="83" t="s">
         <v>2819</v>
@@ -58393,7 +58394,7 @@
         <v>2831</v>
       </c>
       <c r="B1222" s="127" t="s">
-        <v>2850</v>
+        <v>3068</v>
       </c>
       <c r="C1222" s="83" t="s">
         <v>2819</v>
@@ -58565,10 +58566,10 @@
     </row>
     <row r="1227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1227" s="29" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="B1227" s="100" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="C1227" s="83" t="s">
         <v>2819</v>
@@ -58592,7 +58593,7 @@
         <v>63</v>
       </c>
       <c r="J1227" s="29" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="K1227" s="29"/>
       <c r="L1227" s="31"/>
@@ -58600,10 +58601,10 @@
     </row>
     <row r="1228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1228" s="29" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="B1228" s="100" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="C1228" s="83" t="s">
         <v>2819</v>
@@ -58627,7 +58628,7 @@
         <v>63</v>
       </c>
       <c r="J1228" s="29" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="K1228" s="29"/>
       <c r="L1228" s="31"/>
@@ -58635,19 +58636,19 @@
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1229" s="29" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="B1229" s="100" t="s">
         <v>1498</v>
       </c>
       <c r="C1229" s="83" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="D1229" s="85" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="E1229" s="83" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="F1229" s="31" t="s">
         <v>1563</v>
@@ -58662,29 +58663,29 @@
         <v>63</v>
       </c>
       <c r="J1229" s="29" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="K1229" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1229" s="31"/>
       <c r="M1229" s="29"/>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1230" s="29" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="B1230" s="100" t="s">
         <v>1498</v>
       </c>
       <c r="C1230" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="D1230" s="85" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="E1230" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>1563</v>
@@ -58699,29 +58700,29 @@
         <v>63</v>
       </c>
       <c r="J1230" s="29" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="K1230" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1230" s="31"/>
       <c r="M1230" s="29"/>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1231" s="29" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="B1231" s="100" t="s">
         <v>1498</v>
       </c>
       <c r="C1231" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="D1231" s="85" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="E1231" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="F1231" s="31" t="s">
         <v>1563</v>
@@ -58736,29 +58737,29 @@
         <v>63</v>
       </c>
       <c r="J1231" s="29" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="K1231" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1231" s="31"/>
       <c r="M1231" s="29"/>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1232" s="29" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="B1232" s="100" t="s">
         <v>1498</v>
       </c>
       <c r="C1232" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="D1232" s="85" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="E1232" s="83" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>1563</v>
@@ -58773,29 +58774,29 @@
         <v>63</v>
       </c>
       <c r="J1232" s="29" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="K1232" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1232" s="31"/>
       <c r="M1232" s="29"/>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1233" s="29" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="B1233" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1233" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="D1233" s="85" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="E1233" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="F1233" s="31" t="s">
         <v>1563</v>
@@ -58810,29 +58811,29 @@
         <v>63</v>
       </c>
       <c r="J1233" s="29" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="K1233" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1233" s="31"/>
       <c r="M1233" s="29"/>
     </row>
     <row r="1234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1234" s="29" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="B1234" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1234" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="D1234" s="85" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="E1234" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="F1234" s="31" t="s">
         <v>1563</v>
@@ -58847,29 +58848,29 @@
         <v>63</v>
       </c>
       <c r="J1234" s="29" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="K1234" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1234" s="31"/>
       <c r="M1234" s="29"/>
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1235" s="29" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="B1235" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1235" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="D1235" s="85" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="E1235" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="F1235" s="31" t="s">
         <v>1563</v>
@@ -58884,29 +58885,29 @@
         <v>63</v>
       </c>
       <c r="J1235" s="29" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="K1235" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1235" s="31"/>
       <c r="M1235" s="29"/>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1236" s="29" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="B1236" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1236" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D1236" s="85" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="E1236" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="F1236" s="31" t="s">
         <v>1563</v>
@@ -58921,29 +58922,29 @@
         <v>63</v>
       </c>
       <c r="J1236" s="29" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="K1236" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1236" s="31"/>
       <c r="M1236" s="29"/>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1237" s="29" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="B1237" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1237" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D1237" s="85" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="E1237" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>1563</v>
@@ -58958,29 +58959,29 @@
         <v>63</v>
       </c>
       <c r="J1237" s="29" t="s">
+        <v>3033</v>
+      </c>
+      <c r="K1237" s="29" t="s">
         <v>3035</v>
-      </c>
-      <c r="K1237" s="29" t="s">
-        <v>3037</v>
       </c>
       <c r="L1237" s="31"/>
       <c r="M1237" s="29"/>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1238" s="29" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="B1238" s="100" t="s">
         <v>1499</v>
       </c>
       <c r="C1238" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="D1238" s="85" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="E1238" s="83" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="F1238" s="31" t="s">
         <v>1563</v>
@@ -58995,20 +58996,20 @@
         <v>63</v>
       </c>
       <c r="J1238" s="29" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="K1238" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="L1238" s="31"/>
       <c r="M1238" s="29"/>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1239" s="29" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>772</v>
@@ -59026,13 +59027,13 @@
         <v>1495</v>
       </c>
       <c r="H1239" s="29" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="I1239" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1239" s="29" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
@@ -59040,7 +59041,7 @@
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1240" s="29" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="B1240" s="100" t="s">
         <v>1063</v>
@@ -59061,13 +59062,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59075,7 +59076,7 @@
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1241" s="29" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="B1241" s="29" t="s">
         <v>1642</v>
@@ -59102,7 +59103,7 @@
         <v>99</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59110,7 +59111,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1685</v>
@@ -59141,16 +59142,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>55</v>
@@ -59163,10 +59164,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="J1243" s="29" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59174,10 +59175,10 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="B1244" s="85" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="C1244" s="83" t="s">
         <v>2198</v>
@@ -59186,7 +59187,7 @@
         <v>1642</v>
       </c>
       <c r="E1244" s="83" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="F1244" s="31" t="s">
         <v>234</v>
@@ -59196,10 +59197,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="J1244" s="29" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FB94EC-4CB1-424A-A446-BF6259C8DFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E943448-C3E1-824D-B179-749F0AFB7992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10180" uniqueCount="3075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10212" uniqueCount="3083">
   <si>
     <t>Tag</t>
   </si>
@@ -9266,6 +9266,30 @@
   </si>
   <si>
     <t>2408-2704</t>
+  </si>
+  <si>
+    <t>2605-2503</t>
+  </si>
+  <si>
+    <t>streamdeck</t>
+  </si>
+  <si>
+    <t>.225m</t>
+  </si>
+  <si>
+    <t>2605-2502</t>
+  </si>
+  <si>
+    <t>ProP Stream Deck</t>
+  </si>
+  <si>
+    <t>2605-2504</t>
+  </si>
+  <si>
+    <t>2605-2505</t>
+  </si>
+  <si>
+    <t>~5m</t>
   </si>
 </sst>
 </file>
@@ -9442,7 +9466,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -9677,11 +9701,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="FF4472C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9915,6 +9950,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -59284,46 +59322,110 @@
       <c r="M1246" s="29"/>
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1247" s="29"/>
-      <c r="B1247" s="100"/>
-      <c r="C1247" s="83"/>
-      <c r="D1247" s="85"/>
-      <c r="E1247" s="83"/>
-      <c r="F1247" s="31"/>
-      <c r="G1247" s="31"/>
-      <c r="H1247" s="29"/>
-      <c r="I1247" s="119"/>
-      <c r="J1247" s="29"/>
+      <c r="A1247" s="29" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B1247" s="100" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C1247" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1247" s="85" t="s">
+        <v>3076</v>
+      </c>
+      <c r="E1247" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1247" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1247" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1247" s="29" t="s">
+        <v>3077</v>
+      </c>
+      <c r="I1247" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1247" s="29" t="s">
+        <v>3055</v>
+      </c>
       <c r="K1247" s="29"/>
-      <c r="L1247" s="31"/>
+      <c r="L1247" s="31" t="s">
+        <v>641</v>
+      </c>
       <c r="M1247" s="29"/>
     </row>
-    <row r="1248" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1248" s="29"/>
-      <c r="B1248" s="100"/>
-      <c r="C1248" s="83"/>
-      <c r="D1248" s="85"/>
-      <c r="E1248" s="83"/>
-      <c r="F1248" s="31"/>
-      <c r="G1248" s="31"/>
-      <c r="H1248" s="29"/>
-      <c r="I1248" s="119"/>
-      <c r="J1248" s="29"/>
+    <row r="1248" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1248" s="29" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B1248" s="100" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C1248" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1248" s="85" t="s">
+        <v>3080</v>
+      </c>
+      <c r="E1248" s="83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1248" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1248" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1248" s="29" t="s">
+        <v>3077</v>
+      </c>
+      <c r="I1248" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1248" s="29" t="s">
+        <v>3079</v>
+      </c>
       <c r="K1248" s="29"/>
-      <c r="L1248" s="31"/>
+      <c r="L1248" s="31" t="s">
+        <v>641</v>
+      </c>
       <c r="M1248" s="29"/>
     </row>
-    <row r="1249" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1249" s="29"/>
-      <c r="B1249" s="100"/>
-      <c r="C1249" s="83"/>
-      <c r="D1249" s="85"/>
-      <c r="E1249" s="83"/>
-      <c r="F1249" s="31"/>
-      <c r="G1249" s="31"/>
-      <c r="H1249" s="29"/>
-      <c r="I1249" s="119"/>
-      <c r="J1249" s="29"/>
+    <row r="1249" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1249" s="29" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B1249" s="127" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1249" s="83" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D1249" s="85" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E1249" s="83" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F1249" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1249" s="31" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H1249" s="29" t="s">
+        <v>3082</v>
+      </c>
+      <c r="I1249" s="119" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1249" s="29" t="s">
+        <v>3079</v>
+      </c>
       <c r="K1249" s="29"/>
       <c r="L1249" s="31"/>
       <c r="M1249" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E943448-C3E1-824D-B179-749F0AFB7992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B70D4CE-9154-814A-9475-3244D221D142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10212" uniqueCount="3083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10212" uniqueCount="3084">
   <si>
     <t>Tag</t>
   </si>
@@ -9178,9 +9178,6 @@
     <t>2605-1401</t>
   </si>
   <si>
-    <t>tbd</t>
-  </si>
-  <si>
     <t>Stage Display TV</t>
   </si>
   <si>
@@ -9289,7 +9286,13 @@
     <t>2605-2505</t>
   </si>
   <si>
+    <t>2605-2500</t>
+  </si>
+  <si>
     <t>~5m</t>
+  </si>
+  <si>
+    <t>unk1244</t>
   </si>
 </sst>
 </file>
@@ -20411,7 +20414,7 @@
         <v>150</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>196</v>
@@ -20429,7 +20432,7 @@
         <v>99</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>116</v>
@@ -28436,7 +28439,7 @@
         <v>637</v>
       </c>
       <c r="B289" s="31" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C289" s="29" t="s">
         <v>150</v>
@@ -28460,10 +28463,10 @@
         <v>99</v>
       </c>
       <c r="J289" s="29" t="s">
+        <v>3068</v>
+      </c>
+      <c r="K289" s="29" t="s">
         <v>3069</v>
-      </c>
-      <c r="K289" s="29" t="s">
-        <v>3070</v>
       </c>
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
@@ -33058,7 +33061,7 @@
     </row>
     <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B442" s="87" t="s">
         <v>1471</v>
@@ -33086,7 +33089,7 @@
         <v>1069</v>
       </c>
       <c r="K442" s="29" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
@@ -50049,10 +50052,10 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A965" s="29" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>347</v>
@@ -50078,10 +50081,10 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>348</v>
@@ -50107,10 +50110,10 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A967" s="29" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>347</v>
@@ -50136,10 +50139,10 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>348</v>
@@ -50198,7 +50201,7 @@
         <v>1542</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>772</v>
@@ -50228,10 +50231,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>772</v>
@@ -50267,7 +50270,7 @@
         <v>1355</v>
       </c>
       <c r="D973" s="15" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="F973" t="s">
         <v>1563</v>
@@ -55315,7 +55318,7 @@
         <v>1541</v>
       </c>
       <c r="D1126" s="29" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E1126" s="82" t="s">
         <v>2198</v>
@@ -58463,7 +58466,7 @@
         <v>2830</v>
       </c>
       <c r="B1222" s="83" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="C1222" s="83" t="s">
         <v>2818</v>
@@ -59078,7 +59081,7 @@
         <v>3040</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>772</v>
@@ -59131,13 +59134,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59172,7 +59175,7 @@
         <v>99</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59180,7 +59183,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1685</v>
@@ -59211,16 +59214,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>55</v>
@@ -59233,10 +59236,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
+        <v>3053</v>
+      </c>
+      <c r="J1243" s="29" t="s">
         <v>3054</v>
-      </c>
-      <c r="J1243" s="29" t="s">
-        <v>3055</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59244,19 +59247,19 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3053</v>
-      </c>
-      <c r="B1244" s="85" t="s">
-        <v>3051</v>
+        <v>3052</v>
+      </c>
+      <c r="B1244" s="29" t="s">
+        <v>1642</v>
       </c>
       <c r="C1244" s="83" t="s">
+        <v>3083</v>
+      </c>
+      <c r="D1244" s="100" t="s">
+        <v>3050</v>
+      </c>
+      <c r="E1244" s="83" t="s">
         <v>2198</v>
-      </c>
-      <c r="D1244" s="29" t="s">
-        <v>1642</v>
-      </c>
-      <c r="E1244" s="83" t="s">
-        <v>3045</v>
       </c>
       <c r="F1244" s="31" t="s">
         <v>234</v>
@@ -59266,10 +59269,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
+        <v>3053</v>
+      </c>
+      <c r="J1244" s="29" t="s">
         <v>3054</v>
-      </c>
-      <c r="J1244" s="29" t="s">
-        <v>3055</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>
@@ -59277,10 +59280,10 @@
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1245" s="29" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="B1245" s="100" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="C1245" s="83" t="s">
         <v>216</v>
@@ -59296,7 +59299,7 @@
       <c r="H1245" s="29"/>
       <c r="I1245" s="119"/>
       <c r="J1245" s="29" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="K1245" s="29"/>
       <c r="L1245" s="31"/>
@@ -59304,7 +59307,7 @@
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1246" s="29" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B1246" s="100"/>
       <c r="C1246" s="83"/>
@@ -59323,16 +59326,16 @@
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1247" s="29" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="B1247" s="100" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="C1247" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D1247" s="85" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E1247" s="83" t="s">
         <v>55</v>
@@ -59344,13 +59347,13 @@
         <v>55</v>
       </c>
       <c r="H1247" s="29" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="I1247" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1247" s="29" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="K1247" s="29"/>
       <c r="L1247" s="31" t="s">
@@ -59360,16 +59363,16 @@
     </row>
     <row r="1248" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1248" s="29" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="B1248" s="100" t="s">
-        <v>3051</v>
+        <v>3081</v>
       </c>
       <c r="C1248" s="83" t="s">
         <v>55</v>
       </c>
       <c r="D1248" s="85" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E1248" s="83" t="s">
         <v>55</v>
@@ -59381,13 +59384,13 @@
         <v>55</v>
       </c>
       <c r="H1248" s="29" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="I1248" s="119" t="s">
         <v>99</v>
       </c>
       <c r="J1248" s="29" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="K1248" s="29"/>
       <c r="L1248" s="31" t="s">
@@ -59397,7 +59400,7 @@
     </row>
     <row r="1249" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="29" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="B1249" s="127" t="s">
         <v>1639</v>
@@ -59406,7 +59409,7 @@
         <v>2301</v>
       </c>
       <c r="D1249" s="85" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="E1249" s="83" t="s">
         <v>2198</v>
@@ -59424,7 +59427,7 @@
         <v>99</v>
       </c>
       <c r="J1249" s="29" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="K1249" s="29"/>
       <c r="L1249" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B70D4CE-9154-814A-9475-3244D221D142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE8331D-0974-9B43-84A0-64E86EA39D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -59409,7 +59409,7 @@
         <v>2301</v>
       </c>
       <c r="D1249" s="85" t="s">
-        <v>3050</v>
+        <v>3081</v>
       </c>
       <c r="E1249" s="83" t="s">
         <v>2198</v>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE8331D-0974-9B43-84A0-64E86EA39D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19488184-23A5-F346-A38C-B3253D85E9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10212" uniqueCount="3084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10221" uniqueCount="3088">
   <si>
     <t>Tag</t>
   </si>
@@ -9293,6 +9293,18 @@
   </si>
   <si>
     <t>unk1244</t>
+  </si>
+  <si>
+    <t>rt1250</t>
+  </si>
+  <si>
+    <t>unk1250</t>
+  </si>
+  <si>
+    <t>elgato</t>
+  </si>
+  <si>
+    <t>ProP Stream Deck to Companion</t>
   </si>
 </sst>
 </file>
@@ -59434,16 +59446,36 @@
       <c r="M1249" s="29"/>
     </row>
     <row r="1250" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1250" s="29"/>
-      <c r="B1250" s="100"/>
-      <c r="C1250" s="83"/>
-      <c r="D1250" s="85"/>
-      <c r="E1250" s="83"/>
-      <c r="F1250" s="31"/>
-      <c r="G1250" s="31"/>
-      <c r="H1250" s="29"/>
-      <c r="I1250" s="119"/>
-      <c r="J1250" s="29"/>
+      <c r="A1250" s="29" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1250" s="100" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C1250" s="83" t="s">
+        <v>3085</v>
+      </c>
+      <c r="D1250" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1250" s="83" t="s">
+        <v>3085</v>
+      </c>
+      <c r="F1250" s="31" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G1250" s="31" t="s">
+        <v>3086</v>
+      </c>
+      <c r="H1250" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1250" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1250" s="29" t="s">
+        <v>3087</v>
+      </c>
       <c r="K1250" s="29"/>
       <c r="L1250" s="31"/>
       <c r="M1250" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19488184-23A5-F346-A38C-B3253D85E9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3472D5-F74C-1E45-9952-B8CFA7F56C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -9298,13 +9298,13 @@
     <t>rt1250</t>
   </si>
   <si>
-    <t>unk1250</t>
-  </si>
-  <si>
     <t>elgato</t>
   </si>
   <si>
     <t>ProP Stream Deck to Companion</t>
+  </si>
+  <si>
+    <t>5343</t>
   </si>
 </sst>
 </file>
@@ -59445,27 +59445,27 @@
       <c r="L1249" s="31"/>
       <c r="M1249" s="29"/>
     </row>
-    <row r="1250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1250" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="29" t="s">
         <v>3084</v>
       </c>
-      <c r="B1250" s="100" t="s">
+      <c r="B1250" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1250" s="83" t="s">
+        <v>2293</v>
+      </c>
+      <c r="D1250" s="100" t="s">
         <v>3079</v>
       </c>
-      <c r="C1250" s="83" t="s">
-        <v>3085</v>
-      </c>
-      <c r="D1250" s="85" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1250" s="83" t="s">
-        <v>3085</v>
+      <c r="E1250" s="86" t="s">
+        <v>3087</v>
       </c>
       <c r="F1250" s="31" t="s">
         <v>1563</v>
       </c>
       <c r="G1250" s="31" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="H1250" s="29">
         <v>0</v>
@@ -59474,16 +59474,16 @@
         <v>63</v>
       </c>
       <c r="J1250" s="29" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="K1250" s="29"/>
       <c r="L1250" s="31"/>
       <c r="M1250" s="29"/>
     </row>
-    <row r="1251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1251" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="29"/>
-      <c r="B1251" s="100"/>
-      <c r="C1251" s="83"/>
+      <c r="B1251" s="80"/>
+      <c r="C1251" s="82"/>
       <c r="D1251" s="85"/>
       <c r="E1251" s="83"/>
       <c r="F1251" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3472D5-F74C-1E45-9952-B8CFA7F56C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D6A91-8EBF-294D-A172-44E0AA1E7039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10221" uniqueCount="3088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10230" uniqueCount="3089">
   <si>
     <t>Tag</t>
   </si>
@@ -9305,6 +9305,9 @@
   </si>
   <si>
     <t>5343</t>
+  </si>
+  <si>
+    <t>jump1251</t>
   </si>
 </sst>
 </file>
@@ -59481,16 +59484,34 @@
       <c r="M1250" s="29"/>
     </row>
     <row r="1251" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A1251" s="29"/>
-      <c r="B1251" s="80"/>
-      <c r="C1251" s="82"/>
-      <c r="D1251" s="85"/>
-      <c r="E1251" s="83"/>
-      <c r="F1251" s="31"/>
-      <c r="G1251" s="31"/>
+      <c r="A1251" s="29" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1251" s="80" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C1251" s="82" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D1251" s="29" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E1251" s="83" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F1251" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G1251" s="31" t="s">
+        <v>1491</v>
+      </c>
       <c r="H1251" s="29"/>
-      <c r="I1251" s="119"/>
-      <c r="J1251" s="29"/>
+      <c r="I1251" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1251" s="29" t="s">
+        <v>3078</v>
+      </c>
       <c r="K1251" s="29"/>
       <c r="L1251" s="31"/>
       <c r="M1251" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50D6A91-8EBF-294D-A172-44E0AA1E7039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84177932-EF07-D444-A20F-8DFAFA599D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10230" uniqueCount="3089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10225" uniqueCount="3089">
   <si>
     <t>Tag</t>
   </si>
@@ -19931,25 +19931,15 @@
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
-        <v>10</v>
-      </c>
+      <c r="A16" s="21"/>
       <c r="B16" s="22"/>
       <c r="C16" s="25"/>
       <c r="D16" s="22"/>
       <c r="E16" s="23"/>
-      <c r="F16" s="23" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>63</v>
-      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
       <c r="J16" s="23"/>
       <c r="K16" s="23"/>
       <c r="L16" s="19"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A6ACBC-C71A-7645-A74C-8C9CD671E260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A293D633-5F1B-8445-B504-6EE97FE41E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="9" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10250" uniqueCount="3096">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10295" uniqueCount="3109">
   <si>
     <t>Tag</t>
   </si>
@@ -9329,6 +9329,45 @@
   </si>
   <si>
     <t>.6m</t>
+  </si>
+  <si>
+    <t>unk13</t>
+  </si>
+  <si>
+    <t>Camera Control</t>
+  </si>
+  <si>
+    <t>unkport13</t>
+  </si>
+  <si>
+    <t>unkport14</t>
+  </si>
+  <si>
+    <t>unkport15</t>
+  </si>
+  <si>
+    <t>unkport16</t>
+  </si>
+  <si>
+    <t>ethernet</t>
+  </si>
+  <si>
+    <t>Cam 2-Centre</t>
+  </si>
+  <si>
+    <t>ipport</t>
+  </si>
+  <si>
+    <t>rt17</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>samsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP Control </t>
   </si>
 </sst>
 </file>
@@ -18861,7 +18900,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18924,7 +18963,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19943,76 +19982,166 @@
       <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
+      <c r="A13" s="21" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>3098</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>3102</v>
+      </c>
       <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
+      <c r="I13" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>3097</v>
+      </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
       <c r="M13" s="24"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
+      <c r="A14" s="21" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>3099</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>3102</v>
+      </c>
       <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
+      <c r="I14" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>441</v>
+      </c>
       <c r="K14" s="23"/>
       <c r="L14" s="19"/>
       <c r="M14" s="20"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
+      <c r="A15" s="21" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>3100</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>3102</v>
+      </c>
       <c r="H15" s="29"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="23"/>
+      <c r="I15" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>3103</v>
+      </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
+      <c r="A16" s="21" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>3101</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>3102</v>
+      </c>
       <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
+      <c r="I16" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>442</v>
+      </c>
       <c r="K16" s="23"/>
       <c r="L16" s="19"/>
       <c r="M16" s="20"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
+      <c r="A17" s="21" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>3106</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>3104</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>3107</v>
+      </c>
       <c r="H17" s="29"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="23"/>
+      <c r="I17" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>3108</v>
+      </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
       <c r="M17" s="24"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A293D633-5F1B-8445-B504-6EE97FE41E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BA6DEB-29F1-E641-9AD3-E70305E18348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="10" r:id="rId3"/>
+    <pivotCache cacheId="11" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10295" uniqueCount="3109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10306" uniqueCount="3120">
   <si>
     <t>Tag</t>
   </si>
@@ -9368,6 +9368,39 @@
   </si>
   <si>
     <t xml:space="preserve">IP Control </t>
+  </si>
+  <si>
+    <t>notag101</t>
+  </si>
+  <si>
+    <t>notag119</t>
+  </si>
+  <si>
+    <t>notag225</t>
+  </si>
+  <si>
+    <t>notag476</t>
+  </si>
+  <si>
+    <t>notag566</t>
+  </si>
+  <si>
+    <t>notag661</t>
+  </si>
+  <si>
+    <t>notag662</t>
+  </si>
+  <si>
+    <t>notag663</t>
+  </si>
+  <si>
+    <t>notag881</t>
+  </si>
+  <si>
+    <t>notag969</t>
+  </si>
+  <si>
+    <t>notag970</t>
   </si>
 </sst>
 </file>
@@ -18900,70 +18933,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19196,6 +19166,69 @@
     </i>
     <i>
       <x v="53"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -22654,7 +22687,9 @@
       <c r="M100" s="20"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A101" s="21"/>
+      <c r="A101" s="21" t="s">
+        <v>3109</v>
+      </c>
       <c r="B101" s="22" t="s">
         <v>53</v>
       </c>
@@ -23220,7 +23255,9 @@
       <c r="M118" s="24"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A119" s="21"/>
+      <c r="A119" s="21" t="s">
+        <v>3110</v>
+      </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
@@ -26780,7 +26817,9 @@
       <c r="M224" s="29"/>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A225" s="29"/>
+      <c r="A225" s="29" t="s">
+        <v>3111</v>
+      </c>
       <c r="B225" s="31"/>
       <c r="C225" s="29"/>
       <c r="D225" s="31"/>
@@ -34391,7 +34430,9 @@
       <c r="M475" s="29"/>
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A476" s="29"/>
+      <c r="A476" s="29" t="s">
+        <v>3112</v>
+      </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
       <c r="D476" s="58"/>
@@ -37367,7 +37408,9 @@
       <c r="M565" s="29"/>
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="29"/>
+      <c r="A566" s="29" t="s">
+        <v>3113</v>
+      </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
       <c r="D566" s="95"/>
@@ -40458,7 +40501,9 @@
       <c r="M660" s="29"/>
     </row>
     <row r="661" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A661" s="29"/>
+      <c r="A661" s="29" t="s">
+        <v>3114</v>
+      </c>
       <c r="B661" s="83"/>
       <c r="C661" s="29"/>
       <c r="D661" s="84"/>
@@ -40473,7 +40518,9 @@
       <c r="M661" s="29"/>
     </row>
     <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A662" s="29"/>
+      <c r="A662" s="29" t="s">
+        <v>3115</v>
+      </c>
       <c r="B662" s="83"/>
       <c r="C662" s="29"/>
       <c r="D662" s="84"/>
@@ -40488,7 +40535,9 @@
       <c r="M662" s="29"/>
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A663" s="29"/>
+      <c r="A663" s="29" t="s">
+        <v>3116</v>
+      </c>
       <c r="B663" s="83"/>
       <c r="C663" s="29"/>
       <c r="D663" s="84"/>
@@ -47474,7 +47523,9 @@
       <c r="M880" s="29"/>
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A881" s="29"/>
+      <c r="A881" s="29" t="s">
+        <v>3117</v>
+      </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
       <c r="D881" s="85"/>
@@ -50350,7 +50401,9 @@
       <c r="M968" s="29"/>
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A969" s="29"/>
+      <c r="A969" s="29" t="s">
+        <v>3118</v>
+      </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
       <c r="D969" s="85"/>
@@ -50365,7 +50418,9 @@
       <c r="M969" s="29"/>
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A970" s="29"/>
+      <c r="A970" s="29" t="s">
+        <v>3119</v>
+      </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>
       <c r="D970" s="79"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BA6DEB-29F1-E641-9AD3-E70305E18348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F9B77C-171A-F94C-87F5-0E92AED79AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10306" uniqueCount="3120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10308" uniqueCount="3122">
   <si>
     <t>Tag</t>
   </si>
@@ -9401,6 +9401,12 @@
   </si>
   <si>
     <t>notag970</t>
+  </si>
+  <si>
+    <t>notag811</t>
+  </si>
+  <si>
+    <t>notag813</t>
   </si>
 </sst>
 </file>
@@ -45283,7 +45289,9 @@
       <c r="M810" s="29"/>
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A811" s="29"/>
+      <c r="A811" s="29" t="s">
+        <v>3120</v>
+      </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
       <c r="D811" s="85"/>
@@ -45329,7 +45337,9 @@
       <c r="M812" s="29"/>
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A813" s="29"/>
+      <c r="A813" s="29" t="s">
+        <v>3121</v>
+      </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
       <c r="D813" s="85"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F9B77C-171A-F94C-87F5-0E92AED79AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F1C579-63CC-234A-A167-B0C99676172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId3"/>
-    <pivotCache cacheId="11" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10308" uniqueCount="3122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10318" uniqueCount="3125">
   <si>
     <t>Tag</t>
   </si>
@@ -9373,12 +9373,6 @@
     <t>notag101</t>
   </si>
   <si>
-    <t>notag119</t>
-  </si>
-  <si>
-    <t>notag225</t>
-  </si>
-  <si>
     <t>notag476</t>
   </si>
   <si>
@@ -9407,6 +9401,21 @@
   </si>
   <si>
     <t>notag813</t>
+  </si>
+  <si>
+    <t>2606-1000</t>
+  </si>
+  <si>
+    <t>usba-usbc</t>
+  </si>
+  <si>
+    <t>right angle usbc</t>
+  </si>
+  <si>
+    <t>rt225</t>
+  </si>
+  <si>
+    <t>Streamdeck</t>
   </si>
 </sst>
 </file>
@@ -18939,7 +18948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19196,7 +19205,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -23262,18 +23271,26 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
-        <v>3110</v>
+        <v>3120</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
-      <c r="F119" s="23"/>
-      <c r="G119" s="23"/>
+      <c r="F119" s="23" t="s">
+        <v>3121</v>
+      </c>
+      <c r="G119" s="23" t="s">
+        <v>52</v>
+      </c>
       <c r="H119" s="23"/>
       <c r="I119" s="23"/>
-      <c r="J119" s="23"/>
-      <c r="K119" s="23"/>
+      <c r="J119" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="K119" s="23" t="s">
+        <v>3122</v>
+      </c>
       <c r="L119" s="19"/>
       <c r="M119" s="20"/>
     </row>
@@ -26824,17 +26841,33 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>3111</v>
-      </c>
-      <c r="B225" s="31"/>
+        <v>3123</v>
+      </c>
+      <c r="B225" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="C225" s="29"/>
-      <c r="D225" s="31"/>
-      <c r="E225" s="29"/>
-      <c r="F225" s="31"/>
-      <c r="G225" s="31"/>
-      <c r="H225" s="29"/>
-      <c r="I225" s="29"/>
-      <c r="J225" s="29"/>
+      <c r="D225" s="31" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E225" s="29">
+        <v>5343</v>
+      </c>
+      <c r="F225" s="31" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G225" s="31" t="s">
+        <v>3070</v>
+      </c>
+      <c r="H225" s="29">
+        <v>0</v>
+      </c>
+      <c r="I225" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="J225" s="29" t="s">
+        <v>3124</v>
+      </c>
       <c r="K225" s="29"/>
       <c r="L225" s="31"/>
       <c r="M225" s="29"/>
@@ -34437,7 +34470,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -37415,7 +37448,7 @@
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
@@ -40508,7 +40541,7 @@
     </row>
     <row r="661" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="29" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="B661" s="83"/>
       <c r="C661" s="29"/>
@@ -40525,7 +40558,7 @@
     </row>
     <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="29" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="B662" s="83"/>
       <c r="C662" s="29"/>
@@ -40542,7 +40575,7 @@
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="B663" s="83"/>
       <c r="C663" s="29"/>
@@ -45290,7 +45323,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
@@ -45338,7 +45371,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
@@ -47534,7 +47567,7 @@
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A881" s="29" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
@@ -50412,7 +50445,7 @@
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A969" s="29" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
@@ -50429,7 +50462,7 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A970" s="29" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F1C579-63CC-234A-A167-B0C99676172F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7750DE2-E875-DB4D-9001-600A24446C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="17000" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10318" uniqueCount="3125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10366" uniqueCount="3138">
   <si>
     <t>Tag</t>
   </si>
@@ -9373,33 +9373,9 @@
     <t>notag101</t>
   </si>
   <si>
-    <t>notag476</t>
-  </si>
-  <si>
-    <t>notag566</t>
-  </si>
-  <si>
-    <t>notag661</t>
-  </si>
-  <si>
-    <t>notag662</t>
-  </si>
-  <si>
     <t>notag663</t>
   </si>
   <si>
-    <t>notag881</t>
-  </si>
-  <si>
-    <t>notag969</t>
-  </si>
-  <si>
-    <t>notag970</t>
-  </si>
-  <si>
-    <t>notag811</t>
-  </si>
-  <si>
     <t>notag813</t>
   </si>
   <si>
@@ -9416,6 +9392,69 @@
   </si>
   <si>
     <t>Streamdeck</t>
+  </si>
+  <si>
+    <t>1.55m</t>
+  </si>
+  <si>
+    <t>2606-1001</t>
+  </si>
+  <si>
+    <t>LibraryTV control</t>
+  </si>
+  <si>
+    <t>jump1255</t>
+  </si>
+  <si>
+    <t>blank476</t>
+  </si>
+  <si>
+    <t>blank566</t>
+  </si>
+  <si>
+    <t>blank811</t>
+  </si>
+  <si>
+    <t>blank881</t>
+  </si>
+  <si>
+    <t>blank969</t>
+  </si>
+  <si>
+    <t>blank970</t>
+  </si>
+  <si>
+    <t>2606-1300</t>
+  </si>
+  <si>
+    <t>2606-1301</t>
+  </si>
+  <si>
+    <t>47m</t>
+  </si>
+  <si>
+    <t>71m</t>
+  </si>
+  <si>
+    <t>2405-2501-F30</t>
+  </si>
+  <si>
+    <t>Intended to be uplink from NSCU-A001 to cisco switch in rack. Currently used for ITNET for CUMU-G002</t>
+  </si>
+  <si>
+    <t>amprack PP</t>
+  </si>
+  <si>
+    <t>tobe 24</t>
+  </si>
+  <si>
+    <t>Intended to be uplink from 2603-1200 (amp) to 2603-1203. Not yet terminated.</t>
+  </si>
+  <si>
+    <t>4 or 14 ?</t>
+  </si>
+  <si>
+    <t>temp patch awaiting switch</t>
   </si>
 </sst>
 </file>
@@ -18948,7 +18987,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19205,7 +19244,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -23271,25 +23310,27 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
-        <v>3120</v>
+        <v>3112</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
       <c r="F119" s="23" t="s">
-        <v>3121</v>
+        <v>3113</v>
       </c>
       <c r="G119" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H119" s="23"/>
+      <c r="H119" s="23" t="s">
+        <v>3117</v>
+      </c>
       <c r="I119" s="23"/>
       <c r="J119" s="23" t="s">
         <v>439</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>3122</v>
+        <v>3114</v>
       </c>
       <c r="L119" s="19"/>
       <c r="M119" s="20"/>
@@ -26841,7 +26882,7 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>3123</v>
+        <v>3115</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>53</v>
@@ -26866,7 +26907,7 @@
         <v>503</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>3124</v>
+        <v>3116</v>
       </c>
       <c r="K225" s="29"/>
       <c r="L225" s="31"/>
@@ -34470,7 +34511,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29" t="s">
-        <v>3110</v>
+        <v>3121</v>
       </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -37448,7 +37489,7 @@
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
-        <v>3111</v>
+        <v>3122</v>
       </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
@@ -40541,51 +40582,109 @@
     </row>
     <row r="661" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="29" t="s">
-        <v>3112</v>
-      </c>
-      <c r="B661" s="83"/>
-      <c r="C661" s="29"/>
-      <c r="D661" s="84"/>
-      <c r="E661" s="73"/>
-      <c r="F661" s="85"/>
-      <c r="G661" s="85"/>
-      <c r="H661" s="23"/>
-      <c r="I661" s="23"/>
-      <c r="J661" s="29"/>
-      <c r="K661" s="29"/>
+        <v>3127</v>
+      </c>
+      <c r="B661" s="83" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C661" s="29">
+        <v>24</v>
+      </c>
+      <c r="D661" s="84" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E661" s="73" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F661" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="G661" s="85" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H661" s="23" t="s">
+        <v>3129</v>
+      </c>
+      <c r="I661" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J661" s="29" t="s">
+        <v>3132</v>
+      </c>
+      <c r="K661" s="29" t="s">
+        <v>465</v>
+      </c>
       <c r="L661" s="31"/>
       <c r="M661" s="29"/>
     </row>
     <row r="662" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="29" t="s">
-        <v>3113</v>
-      </c>
-      <c r="B662" s="83"/>
-      <c r="C662" s="29"/>
-      <c r="D662" s="84"/>
-      <c r="E662" s="73"/>
-      <c r="F662" s="85"/>
-      <c r="G662" s="85"/>
-      <c r="H662" s="23"/>
-      <c r="I662" s="23"/>
-      <c r="J662" s="29"/>
-      <c r="K662" s="29"/>
+        <v>3128</v>
+      </c>
+      <c r="B662" s="83" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C662" s="29" t="s">
+        <v>3134</v>
+      </c>
+      <c r="D662" s="84" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E662" s="73" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F662" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="G662" s="85" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H662" s="23" t="s">
+        <v>3130</v>
+      </c>
+      <c r="I662" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J662" s="29" t="s">
+        <v>3135</v>
+      </c>
+      <c r="K662" s="29" t="s">
+        <v>989</v>
+      </c>
       <c r="L662" s="31"/>
       <c r="M662" s="29"/>
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
-        <v>3114</v>
-      </c>
-      <c r="B663" s="83"/>
-      <c r="C663" s="29"/>
-      <c r="D663" s="84"/>
-      <c r="E663" s="73"/>
-      <c r="F663" s="85"/>
-      <c r="G663" s="85"/>
-      <c r="H663" s="23"/>
-      <c r="I663" s="23"/>
-      <c r="J663" s="29"/>
+        <v>3110</v>
+      </c>
+      <c r="B663" s="84" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C663" s="73" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D663" s="84" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E663" s="73" t="s">
+        <v>3136</v>
+      </c>
+      <c r="F663" s="85" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G663" s="85" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H663" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="I663" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="J663" s="29" t="s">
+        <v>3137</v>
+      </c>
       <c r="K663" s="29"/>
       <c r="L663" s="31"/>
       <c r="M663" s="29"/>
@@ -45323,7 +45422,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
-        <v>3118</v>
+        <v>3123</v>
       </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
@@ -45371,7 +45470,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
-        <v>3119</v>
+        <v>3111</v>
       </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
@@ -47567,7 +47666,7 @@
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A881" s="29" t="s">
-        <v>3115</v>
+        <v>3124</v>
       </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
@@ -50445,7 +50544,7 @@
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A969" s="29" t="s">
-        <v>3116</v>
+        <v>3125</v>
       </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
@@ -50462,7 +50561,7 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A970" s="29" t="s">
-        <v>3117</v>
+        <v>3126</v>
       </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>
@@ -59855,31 +59954,69 @@
       <c r="M1253" s="29"/>
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1254" s="29"/>
-      <c r="B1254" s="100"/>
-      <c r="C1254" s="83"/>
-      <c r="D1254" s="85"/>
-      <c r="E1254" s="83"/>
-      <c r="F1254" s="31"/>
-      <c r="G1254" s="31"/>
-      <c r="H1254" s="29"/>
-      <c r="I1254" s="119"/>
-      <c r="J1254" s="29"/>
+      <c r="A1254" s="29" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B1254" s="29" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C1254" s="83" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D1254" s="85" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E1254" s="83" t="s">
+        <v>2183</v>
+      </c>
+      <c r="F1254" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1254" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1254" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="I1254" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1254" s="29" t="s">
+        <v>3119</v>
+      </c>
       <c r="K1254" s="29"/>
       <c r="L1254" s="31"/>
       <c r="M1254" s="29"/>
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1255" s="29"/>
-      <c r="B1255" s="100"/>
-      <c r="C1255" s="83"/>
-      <c r="D1255" s="85"/>
-      <c r="E1255" s="83"/>
-      <c r="F1255" s="31"/>
-      <c r="G1255" s="31"/>
+      <c r="A1255" s="29" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B1255" s="100" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1255" s="83" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D1255" s="29" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E1255" s="83" t="s">
+        <v>2390</v>
+      </c>
+      <c r="F1255" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1255" s="31" t="s">
+        <v>1478</v>
+      </c>
       <c r="H1255" s="29"/>
-      <c r="I1255" s="119"/>
-      <c r="J1255" s="29"/>
+      <c r="I1255" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1255" s="29" t="s">
+        <v>3119</v>
+      </c>
       <c r="K1255" s="29"/>
       <c r="L1255" s="31"/>
       <c r="M1255" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC6CC44-476E-6743-81CC-8E08BB1ED428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71DDFDE-6AE6-4A48-BC1B-317A9E4A4BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10559" uniqueCount="3161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="3163">
   <si>
     <t>Tag</t>
   </si>
@@ -9524,6 +9524,13 @@
   </si>
   <si>
     <t>pt1279</t>
+  </si>
+  <si>
+    <t>notag1280</t>
+  </si>
+  <si>
+    <t>uplink to switch in 2602-1800.
+Not sure which one it will be.</t>
   </si>
 </sst>
 </file>
@@ -9950,7 +9957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10187,6 +10194,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -60882,20 +60901,40 @@
       <c r="L1279" s="31"/>
       <c r="M1279" s="29"/>
     </row>
-    <row r="1280" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1280" s="29"/>
-      <c r="B1280" s="100"/>
-      <c r="C1280" s="83"/>
-      <c r="D1280" s="85"/>
-      <c r="E1280" s="83"/>
-      <c r="F1280" s="31"/>
-      <c r="G1280" s="31"/>
-      <c r="H1280" s="29"/>
-      <c r="I1280" s="119"/>
-      <c r="J1280" s="29"/>
-      <c r="K1280" s="29"/>
-      <c r="L1280" s="31"/>
-      <c r="M1280" s="29"/>
+    <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+      <c r="A1280" s="128" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B1280" s="100" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1280" s="83" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D1280" s="100" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E1280" s="83" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F1280" s="83" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1280" s="83" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1280" s="128" t="s">
+        <v>3061</v>
+      </c>
+      <c r="I1280" s="129" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1280" s="130" t="s">
+        <v>3162</v>
+      </c>
+      <c r="K1280" s="128"/>
+      <c r="L1280" s="83"/>
+      <c r="M1280" s="128"/>
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1281" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C817C3-3CAD-F846-A4FA-27B42C6807FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6842CB-D194-5D4E-B03F-8FC3ABD56680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -9436,9 +9436,6 @@
     <t>2405-2501-F30</t>
   </si>
   <si>
-    <t>amprack PP</t>
-  </si>
-  <si>
     <t>temp patch awaiting switch</t>
   </si>
   <si>
@@ -9524,15 +9521,18 @@
 Not sure which one it will be.</t>
   </si>
   <si>
-    <t>Intended to be uplink from NSCU-A001 to cisco switch in rack. 
-Currently used for ITNET for CUMU-G002</t>
-  </si>
-  <si>
-    <t>Intended to be uplink from 2603-1200 (amp) to 2603-1203. 
+    <t>ITNet to PP</t>
+  </si>
+  <si>
+    <t>Intended to be uplink from NSCU-A001 to NSCU-A004. 
+Temp used for ITNET for CUMU-G002.</t>
+  </si>
+  <si>
+    <t>2405-2501 PP</t>
+  </si>
+  <si>
+    <t>Intended to be uplink from 2603-1200 to 2603-1203. 
 Not yet terminated.</t>
-  </si>
-  <si>
-    <t>ITNet to PP</t>
   </si>
 </sst>
 </file>
@@ -40712,10 +40712,10 @@
         <v>3127</v>
       </c>
       <c r="B662" s="83" t="s">
-        <v>3131</v>
+        <v>3161</v>
       </c>
       <c r="C662" s="128" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="D662" s="84" t="s">
         <v>1629</v>
@@ -40736,7 +40736,7 @@
         <v>96</v>
       </c>
       <c r="J662" s="130" t="s">
-        <v>3161</v>
+        <v>3162</v>
       </c>
       <c r="K662" s="128" t="s">
         <v>989</v>
@@ -40773,7 +40773,7 @@
         <v>60</v>
       </c>
       <c r="J663" s="29" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="K663" s="29"/>
       <c r="L663" s="31"/>
@@ -47540,7 +47540,7 @@
         <v>96</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>3162</v>
+        <v>3159</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -60113,7 +60113,7 @@
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1256" s="29" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="B1256" s="100" t="s">
         <v>3130</v>
@@ -60146,7 +60146,7 @@
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1257" s="29" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B1257" s="100" t="s">
         <v>3130</v>
@@ -60179,7 +60179,7 @@
     </row>
     <row r="1258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1258" s="29" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="B1258" s="100" t="s">
         <v>3130</v>
@@ -60212,7 +60212,7 @@
     </row>
     <row r="1259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1259" s="29" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="B1259" s="100" t="s">
         <v>3130</v>
@@ -60245,7 +60245,7 @@
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1260" s="29" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B1260" s="100" t="s">
         <v>3130</v>
@@ -60278,7 +60278,7 @@
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1261" s="29" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="B1261" s="100" t="s">
         <v>3130</v>
@@ -60311,7 +60311,7 @@
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1262" s="29" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B1262" s="100" t="s">
         <v>3130</v>
@@ -60344,7 +60344,7 @@
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1263" s="29" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="B1263" s="100" t="s">
         <v>3130</v>
@@ -60377,7 +60377,7 @@
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1264" s="29" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1264" s="100" t="s">
         <v>3130</v>
@@ -60410,7 +60410,7 @@
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1265" s="29" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B1265" s="100" t="s">
         <v>3130</v>
@@ -60443,7 +60443,7 @@
     </row>
     <row r="1266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1266" s="29" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1266" s="100" t="s">
         <v>3130</v>
@@ -60476,7 +60476,7 @@
     </row>
     <row r="1267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1267" s="29" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="B1267" s="100" t="s">
         <v>3130</v>
@@ -60509,7 +60509,7 @@
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1268" s="29" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B1268" s="100" t="s">
         <v>3130</v>
@@ -60542,7 +60542,7 @@
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1269" s="29" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B1269" s="100" t="s">
         <v>3130</v>
@@ -60575,7 +60575,7 @@
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1270" s="29" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="B1270" s="100" t="s">
         <v>3130</v>
@@ -60608,7 +60608,7 @@
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1271" s="29" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="B1271" s="100" t="s">
         <v>3130</v>
@@ -60641,7 +60641,7 @@
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1272" s="29" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="B1272" s="100" t="s">
         <v>3130</v>
@@ -60674,7 +60674,7 @@
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1273" s="29" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B1273" s="100" t="s">
         <v>3130</v>
@@ -60707,7 +60707,7 @@
     </row>
     <row r="1274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1274" s="29" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B1274" s="100" t="s">
         <v>3130</v>
@@ -60740,7 +60740,7 @@
     </row>
     <row r="1275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1275" s="29" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B1275" s="100" t="s">
         <v>3130</v>
@@ -60773,7 +60773,7 @@
     </row>
     <row r="1276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1276" s="29" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="B1276" s="100" t="s">
         <v>3130</v>
@@ -60806,7 +60806,7 @@
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1277" s="29" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B1277" s="100" t="s">
         <v>3130</v>
@@ -60839,7 +60839,7 @@
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1278" s="29" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B1278" s="100" t="s">
         <v>3130</v>
@@ -60872,7 +60872,7 @@
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1279" s="29" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B1279" s="100" t="s">
         <v>3130</v>
@@ -60905,7 +60905,7 @@
     </row>
     <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1280" s="128" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B1280" s="100" t="s">
         <v>242</v>
@@ -60932,7 +60932,7 @@
         <v>60</v>
       </c>
       <c r="J1280" s="130" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="K1280" s="128"/>
       <c r="L1280" s="83"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6842CB-D194-5D4E-B03F-8FC3ABD56680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6C1C5B-F13B-0249-A65E-3E7FB15E373B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="3163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10793" uniqueCount="3205">
   <si>
     <t>Tag</t>
   </si>
@@ -7840,42 +7840,15 @@
     <t>ZAHU-0001-F28</t>
   </si>
   <si>
-    <t>MixRack</t>
-  </si>
-  <si>
-    <t>notag1160</t>
-  </si>
-  <si>
-    <t>notag1161</t>
-  </si>
-  <si>
-    <t>mixrack dante</t>
-  </si>
-  <si>
     <t>Amp1 Control</t>
   </si>
   <si>
     <t>Amp1 Dante</t>
   </si>
   <si>
-    <t xml:space="preserve">Amp2 Control </t>
-  </si>
-  <si>
     <t>Amp2 Dante</t>
   </si>
   <si>
-    <t>notag1162</t>
-  </si>
-  <si>
-    <t>notag1163</t>
-  </si>
-  <si>
-    <t>notag1164</t>
-  </si>
-  <si>
-    <t>notag1165</t>
-  </si>
-  <si>
     <t>Amp3 Control</t>
   </si>
   <si>
@@ -7891,33 +7864,12 @@
     <t>Amp5 Control</t>
   </si>
   <si>
-    <t>notag1166</t>
-  </si>
-  <si>
-    <t>notag1167</t>
-  </si>
-  <si>
-    <t>notag1168</t>
-  </si>
-  <si>
-    <t>notag1169</t>
-  </si>
-  <si>
-    <t>notag1170</t>
-  </si>
-  <si>
-    <t>notag1171</t>
-  </si>
-  <si>
     <t>Amp6 Dante</t>
   </si>
   <si>
     <t>Amp6 Control</t>
   </si>
   <si>
-    <t xml:space="preserve">Amp7 Control </t>
-  </si>
-  <si>
     <t>Amp7 Dante</t>
   </si>
   <si>
@@ -7940,21 +7892,6 @@
   </si>
   <si>
     <t>W-Cat6-NETSPARE2</t>
-  </si>
-  <si>
-    <t>notag1172</t>
-  </si>
-  <si>
-    <t>notag1173</t>
-  </si>
-  <si>
-    <t>notag1174</t>
-  </si>
-  <si>
-    <t>notag1175</t>
-  </si>
-  <si>
-    <t>notag1176</t>
   </si>
   <si>
     <t>W-CAT6-064</t>
@@ -9533,6 +9470,195 @@
   <si>
     <t>Intended to be uplink from 2603-1200 to 2603-1203. 
 Not yet terminated.</t>
+  </si>
+  <si>
+    <t>2601-1200</t>
+  </si>
+  <si>
+    <t>ZAHU-0001-F30</t>
+  </si>
+  <si>
+    <t>Mix Rack Network</t>
+  </si>
+  <si>
+    <t>MixRack Dante</t>
+  </si>
+  <si>
+    <t>Amp2 Control</t>
+  </si>
+  <si>
+    <t>Amp5 Dante</t>
+  </si>
+  <si>
+    <t>Amp7 Control</t>
+  </si>
+  <si>
+    <t>jump1305</t>
+  </si>
+  <si>
+    <t>jump1306</t>
+  </si>
+  <si>
+    <t>jump1307</t>
+  </si>
+  <si>
+    <t>jump1308</t>
+  </si>
+  <si>
+    <t>jump1281</t>
+  </si>
+  <si>
+    <t>jump1282</t>
+  </si>
+  <si>
+    <t>jump1283</t>
+  </si>
+  <si>
+    <t>jump1284</t>
+  </si>
+  <si>
+    <t>jump1285</t>
+  </si>
+  <si>
+    <t>jump1286</t>
+  </si>
+  <si>
+    <t>jump1287</t>
+  </si>
+  <si>
+    <t>jump1288</t>
+  </si>
+  <si>
+    <t>unused1289</t>
+  </si>
+  <si>
+    <t>unused1290</t>
+  </si>
+  <si>
+    <t>unused1291</t>
+  </si>
+  <si>
+    <t>unused1292</t>
+  </si>
+  <si>
+    <t>unused1293</t>
+  </si>
+  <si>
+    <t>unused1294</t>
+  </si>
+  <si>
+    <t>unused1295</t>
+  </si>
+  <si>
+    <t>unused1296</t>
+  </si>
+  <si>
+    <t>unused1297</t>
+  </si>
+  <si>
+    <t>unused1298</t>
+  </si>
+  <si>
+    <t>unused1299</t>
+  </si>
+  <si>
+    <t>unused1300</t>
+  </si>
+  <si>
+    <t>unused1301</t>
+  </si>
+  <si>
+    <t>unused1302</t>
+  </si>
+  <si>
+    <t>unused1303</t>
+  </si>
+  <si>
+    <t>unused1304</t>
+  </si>
+  <si>
+    <t>unused1309</t>
+  </si>
+  <si>
+    <t>unk1161</t>
+  </si>
+  <si>
+    <t>unk1162</t>
+  </si>
+  <si>
+    <t>unk1163</t>
+  </si>
+  <si>
+    <t>unk1164</t>
+  </si>
+  <si>
+    <t>unk1165</t>
+  </si>
+  <si>
+    <t>unk1166</t>
+  </si>
+  <si>
+    <t>unk1167</t>
+  </si>
+  <si>
+    <t>unk1168</t>
+  </si>
+  <si>
+    <t>unk1169</t>
+  </si>
+  <si>
+    <t>unk1170</t>
+  </si>
+  <si>
+    <t>unk1171</t>
+  </si>
+  <si>
+    <t>unk1172</t>
+  </si>
+  <si>
+    <t>unk1173</t>
+  </si>
+  <si>
+    <t>unk1174</t>
+  </si>
+  <si>
+    <t>unk1175</t>
+  </si>
+  <si>
+    <t>unk1176</t>
+  </si>
+  <si>
+    <t>unk1177</t>
+  </si>
+  <si>
+    <t>LANA</t>
+  </si>
+  <si>
+    <t>GPIO1</t>
+  </si>
+  <si>
+    <t>GPIO2</t>
+  </si>
+  <si>
+    <t>MICNP-016</t>
+  </si>
+  <si>
+    <t>2606-1400</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>2312-2101</t>
+  </si>
+  <si>
+    <t>rm in baclony</t>
+  </si>
+  <si>
+    <t>notag1311</t>
+  </si>
+  <si>
+    <t>notag1312</t>
   </si>
 </sst>
 </file>
@@ -9959,7 +10085,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10208,6 +10334,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -19077,69 +19206,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
@@ -19373,6 +19439,69 @@
     </i>
     <i>
       <x v="53"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -19781,7 +19910,7 @@
         <v>733</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>3079</v>
+        <v>3058</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>19</v>
@@ -19818,7 +19947,7 @@
         <v>733</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>3079</v>
+        <v>3058</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>19</v>
@@ -19855,7 +19984,7 @@
         <v>733</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>3080</v>
+        <v>3059</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>19</v>
@@ -19876,7 +20005,7 @@
         <v>60</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>3086</v>
+        <v>3065</v>
       </c>
       <c r="K4" s="19" t="s">
         <v>277</v>
@@ -19892,7 +20021,7 @@
         <v>733</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>3081</v>
+        <v>3060</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>19</v>
@@ -19913,7 +20042,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>3087</v>
+        <v>3066</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>279</v>
@@ -19929,7 +20058,7 @@
         <v>733</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>3082</v>
+        <v>3061</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>19</v>
@@ -19950,7 +20079,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>3088</v>
+        <v>3067</v>
       </c>
       <c r="K6" s="19" t="s">
         <v>280</v>
@@ -19966,7 +20095,7 @@
         <v>733</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>3083</v>
+        <v>3062</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>19</v>
@@ -19987,7 +20116,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>3089</v>
+        <v>3068</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>282</v>
@@ -20032,7 +20161,7 @@
         <v>733</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>3084</v>
+        <v>3063</v>
       </c>
       <c r="D9" s="103" t="s">
         <v>19</v>
@@ -20053,7 +20182,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>3090</v>
+        <v>3069</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>284</v>
@@ -20100,7 +20229,7 @@
         <v>733</v>
       </c>
       <c r="E11" s="104" t="s">
-        <v>3085</v>
+        <v>3064</v>
       </c>
       <c r="F11" s="102" t="s">
         <v>1550</v>
@@ -20115,7 +20244,7 @@
         <v>60</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>3091</v>
+        <v>3070</v>
       </c>
       <c r="K11" s="23" t="s">
         <v>285</v>
@@ -20125,10 +20254,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>3092</v>
+        <v>3071</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>3093</v>
+        <v>3072</v>
       </c>
       <c r="C12" s="91" t="s">
         <v>52</v>
@@ -20146,7 +20275,7 @@
         <v>52</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>3094</v>
+        <v>3073</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>503</v>
@@ -20160,13 +20289,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>3095</v>
+        <v>3074</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>263</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>3097</v>
+        <v>3076</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>72</v>
@@ -20178,14 +20307,14 @@
         <v>176</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>3101</v>
+        <v>3080</v>
       </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23" t="s">
         <v>503</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>3096</v>
+        <v>3075</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -20199,7 +20328,7 @@
         <v>263</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>3098</v>
+        <v>3077</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>65</v>
@@ -20211,7 +20340,7 @@
         <v>176</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>3101</v>
+        <v>3080</v>
       </c>
       <c r="H14" s="23"/>
       <c r="I14" s="23" t="s">
@@ -20232,7 +20361,7 @@
         <v>263</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>3099</v>
+        <v>3078</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>66</v>
@@ -20244,14 +20373,14 @@
         <v>176</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>3101</v>
+        <v>3080</v>
       </c>
       <c r="H15" s="29"/>
       <c r="I15" s="23" t="s">
         <v>503</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>3102</v>
+        <v>3081</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -20265,7 +20394,7 @@
         <v>263</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>3100</v>
+        <v>3079</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>67</v>
@@ -20277,7 +20406,7 @@
         <v>176</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>3101</v>
+        <v>3080</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="23" t="s">
@@ -20292,32 +20421,32 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>3104</v>
+        <v>3083</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>53</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>3105</v>
+        <v>3084</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>3103</v>
+        <v>3082</v>
       </c>
       <c r="F17" s="23" t="s">
         <v>1550</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>3106</v>
+        <v>3085</v>
       </c>
       <c r="H17" s="29"/>
       <c r="I17" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>3107</v>
+        <v>3086</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -20782,7 +20911,7 @@
         <v>147</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>3051</v>
+        <v>3030</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>193</v>
@@ -20800,7 +20929,7 @@
         <v>96</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>3052</v>
+        <v>3031</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>113</v>
@@ -22523,7 +22652,7 @@
         <v>60</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>2983</v>
+        <v>2962</v>
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
@@ -22832,7 +22961,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>3108</v>
+        <v>3087</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>53</v>
@@ -23061,7 +23190,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>3020</v>
+        <v>2999</v>
       </c>
       <c r="B108" s="22" t="s">
         <v>223</v>
@@ -23070,7 +23199,7 @@
         <v>133</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>3019</v>
+        <v>2998</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>133</v>
@@ -23154,7 +23283,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>2841</v>
+        <v>2820</v>
       </c>
       <c r="B111" s="22" t="s">
         <v>239</v>
@@ -23251,7 +23380,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>2842</v>
+        <v>2821</v>
       </c>
       <c r="B114" s="22" t="s">
         <v>242</v>
@@ -23284,7 +23413,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
-        <v>2843</v>
+        <v>2822</v>
       </c>
       <c r="B115" s="22" t="s">
         <v>242</v>
@@ -23313,7 +23442,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
-        <v>2844</v>
+        <v>2823</v>
       </c>
       <c r="B116" s="22" t="s">
         <v>242</v>
@@ -23342,7 +23471,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>2845</v>
+        <v>2824</v>
       </c>
       <c r="B117" s="22" t="s">
         <v>260</v>
@@ -23369,7 +23498,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>2846</v>
+        <v>2825</v>
       </c>
       <c r="B118" s="22" t="s">
         <v>262</v>
@@ -23400,27 +23529,27 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
-        <v>3111</v>
+        <v>3090</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
       <c r="F119" s="23" t="s">
-        <v>3112</v>
+        <v>3091</v>
       </c>
       <c r="G119" s="23" t="s">
         <v>52</v>
       </c>
       <c r="H119" s="23" t="s">
-        <v>3116</v>
+        <v>3095</v>
       </c>
       <c r="I119" s="23"/>
       <c r="J119" s="23" t="s">
         <v>439</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>3113</v>
+        <v>3092</v>
       </c>
       <c r="L119" s="19"/>
       <c r="M119" s="20"/>
@@ -24399,13 +24528,13 @@
         <v>223</v>
       </c>
       <c r="C150" s="29" t="s">
-        <v>2679</v>
+        <v>2658</v>
       </c>
       <c r="D150" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E150" s="29" t="s">
-        <v>2681</v>
+        <v>2660</v>
       </c>
       <c r="F150" s="23" t="s">
         <v>1550</v>
@@ -24432,13 +24561,13 @@
         <v>223</v>
       </c>
       <c r="C151" s="29" t="s">
-        <v>2680</v>
+        <v>2659</v>
       </c>
       <c r="D151" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E151" s="29" t="s">
-        <v>2682</v>
+        <v>2661</v>
       </c>
       <c r="F151" s="23" t="s">
         <v>1550</v>
@@ -24465,13 +24594,13 @@
         <v>53</v>
       </c>
       <c r="C152" s="29" t="s">
-        <v>2679</v>
+        <v>2658</v>
       </c>
       <c r="D152" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E152" s="29" t="s">
-        <v>2683</v>
+        <v>2662</v>
       </c>
       <c r="F152" s="23" t="s">
         <v>1550</v>
@@ -24498,13 +24627,13 @@
         <v>53</v>
       </c>
       <c r="C153" s="29" t="s">
-        <v>2680</v>
+        <v>2659</v>
       </c>
       <c r="D153" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>2684</v>
+        <v>2663</v>
       </c>
       <c r="F153" s="23" t="s">
         <v>1550</v>
@@ -24531,13 +24660,13 @@
         <v>1164</v>
       </c>
       <c r="C154" s="78" t="s">
-        <v>2733</v>
+        <v>2712</v>
       </c>
       <c r="D154" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>2685</v>
+        <v>2664</v>
       </c>
       <c r="F154" s="23" t="s">
         <v>1550</v>
@@ -24566,13 +24695,13 @@
         <v>1164</v>
       </c>
       <c r="C155" s="78" t="s">
-        <v>2734</v>
+        <v>2713</v>
       </c>
       <c r="D155" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>2686</v>
+        <v>2665</v>
       </c>
       <c r="F155" s="23" t="s">
         <v>1550</v>
@@ -24601,13 +24730,13 @@
         <v>1164</v>
       </c>
       <c r="C156" s="78" t="s">
-        <v>2735</v>
+        <v>2714</v>
       </c>
       <c r="D156" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>2681</v>
+        <v>2660</v>
       </c>
       <c r="F156" s="23" t="s">
         <v>1550</v>
@@ -24636,13 +24765,13 @@
         <v>1164</v>
       </c>
       <c r="C157" s="78" t="s">
-        <v>2736</v>
+        <v>2715</v>
       </c>
       <c r="D157" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>2682</v>
+        <v>2661</v>
       </c>
       <c r="F157" s="23" t="s">
         <v>1550</v>
@@ -24671,13 +24800,13 @@
         <v>1164</v>
       </c>
       <c r="C158" s="78" t="s">
-        <v>2737</v>
+        <v>2716</v>
       </c>
       <c r="D158" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E158" s="29" t="s">
-        <v>2683</v>
+        <v>2662</v>
       </c>
       <c r="F158" s="23" t="s">
         <v>1550</v>
@@ -24706,13 +24835,13 @@
         <v>1164</v>
       </c>
       <c r="C159" s="78" t="s">
-        <v>2738</v>
+        <v>2717</v>
       </c>
       <c r="D159" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E159" s="29" t="s">
-        <v>2684</v>
+        <v>2663</v>
       </c>
       <c r="F159" s="23" t="s">
         <v>1550</v>
@@ -24741,13 +24870,13 @@
         <v>1164</v>
       </c>
       <c r="C160" s="78" t="s">
-        <v>2739</v>
+        <v>2718</v>
       </c>
       <c r="D160" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E160" s="29" t="s">
-        <v>2687</v>
+        <v>2666</v>
       </c>
       <c r="F160" s="23" t="s">
         <v>1550</v>
@@ -24776,13 +24905,13 @@
         <v>1164</v>
       </c>
       <c r="C161" s="78" t="s">
-        <v>2740</v>
+        <v>2719</v>
       </c>
       <c r="D161" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E161" s="29" t="s">
-        <v>2688</v>
+        <v>2667</v>
       </c>
       <c r="F161" s="23" t="s">
         <v>1550</v>
@@ -24811,13 +24940,13 @@
         <v>1164</v>
       </c>
       <c r="C162" s="78" t="s">
-        <v>2741</v>
+        <v>2720</v>
       </c>
       <c r="D162" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E162" s="29" t="s">
-        <v>2689</v>
+        <v>2668</v>
       </c>
       <c r="F162" s="23" t="s">
         <v>1550</v>
@@ -24846,13 +24975,13 @@
         <v>1164</v>
       </c>
       <c r="C163" s="78" t="s">
-        <v>2742</v>
+        <v>2721</v>
       </c>
       <c r="D163" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>2690</v>
+        <v>2669</v>
       </c>
       <c r="F163" s="23" t="s">
         <v>1550</v>
@@ -24881,13 +25010,13 @@
         <v>1164</v>
       </c>
       <c r="C164" s="78" t="s">
-        <v>2743</v>
+        <v>2722</v>
       </c>
       <c r="D164" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E164" s="29" t="s">
-        <v>2691</v>
+        <v>2670</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>1550</v>
@@ -24916,13 +25045,13 @@
         <v>1164</v>
       </c>
       <c r="C165" s="78" t="s">
-        <v>2744</v>
+        <v>2723</v>
       </c>
       <c r="D165" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E165" s="29" t="s">
-        <v>2692</v>
+        <v>2671</v>
       </c>
       <c r="F165" s="23" t="s">
         <v>1550</v>
@@ -24951,13 +25080,13 @@
         <v>1164</v>
       </c>
       <c r="C166" s="78" t="s">
-        <v>2745</v>
+        <v>2724</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E166" s="29" t="s">
-        <v>2693</v>
+        <v>2672</v>
       </c>
       <c r="F166" s="23" t="s">
         <v>1550</v>
@@ -24986,13 +25115,13 @@
         <v>1164</v>
       </c>
       <c r="C167" s="78" t="s">
-        <v>2746</v>
+        <v>2725</v>
       </c>
       <c r="D167" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>2694</v>
+        <v>2673</v>
       </c>
       <c r="F167" s="23" t="s">
         <v>1550</v>
@@ -25021,13 +25150,13 @@
         <v>1164</v>
       </c>
       <c r="C168" s="78" t="s">
-        <v>2747</v>
+        <v>2726</v>
       </c>
       <c r="D168" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>2695</v>
+        <v>2674</v>
       </c>
       <c r="F168" s="23" t="s">
         <v>1550</v>
@@ -25056,13 +25185,13 @@
         <v>1164</v>
       </c>
       <c r="C169" s="78" t="s">
-        <v>2748</v>
+        <v>2727</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>2696</v>
+        <v>2675</v>
       </c>
       <c r="F169" s="23" t="s">
         <v>1550</v>
@@ -25091,13 +25220,13 @@
         <v>1164</v>
       </c>
       <c r="C170" s="78" t="s">
-        <v>2749</v>
+        <v>2728</v>
       </c>
       <c r="D170" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E170" s="29" t="s">
-        <v>2697</v>
+        <v>2676</v>
       </c>
       <c r="F170" s="23" t="s">
         <v>1550</v>
@@ -25126,13 +25255,13 @@
         <v>1164</v>
       </c>
       <c r="C171" s="78" t="s">
-        <v>2750</v>
+        <v>2729</v>
       </c>
       <c r="D171" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E171" s="29" t="s">
-        <v>2698</v>
+        <v>2677</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>1550</v>
@@ -25161,13 +25290,13 @@
         <v>1164</v>
       </c>
       <c r="C172" s="78" t="s">
-        <v>2751</v>
+        <v>2730</v>
       </c>
       <c r="D172" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E172" s="29" t="s">
-        <v>2699</v>
+        <v>2678</v>
       </c>
       <c r="F172" s="23" t="s">
         <v>1550</v>
@@ -25196,13 +25325,13 @@
         <v>1164</v>
       </c>
       <c r="C173" s="78" t="s">
-        <v>2752</v>
+        <v>2731</v>
       </c>
       <c r="D173" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E173" s="29" t="s">
-        <v>2700</v>
+        <v>2679</v>
       </c>
       <c r="F173" s="23" t="s">
         <v>1550</v>
@@ -25231,13 +25360,13 @@
         <v>1164</v>
       </c>
       <c r="C174" s="78" t="s">
-        <v>2753</v>
+        <v>2732</v>
       </c>
       <c r="D174" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E174" s="29" t="s">
-        <v>2701</v>
+        <v>2680</v>
       </c>
       <c r="F174" s="23" t="s">
         <v>1550</v>
@@ -25266,13 +25395,13 @@
         <v>1164</v>
       </c>
       <c r="C175" s="78" t="s">
-        <v>2754</v>
+        <v>2733</v>
       </c>
       <c r="D175" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E175" s="29" t="s">
-        <v>2702</v>
+        <v>2681</v>
       </c>
       <c r="F175" s="23" t="s">
         <v>1550</v>
@@ -25301,13 +25430,13 @@
         <v>1164</v>
       </c>
       <c r="C176" s="78" t="s">
-        <v>2755</v>
+        <v>2734</v>
       </c>
       <c r="D176" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E176" s="29" t="s">
-        <v>2703</v>
+        <v>2682</v>
       </c>
       <c r="F176" s="23" t="s">
         <v>1550</v>
@@ -25336,13 +25465,13 @@
         <v>1164</v>
       </c>
       <c r="C177" s="78" t="s">
-        <v>2756</v>
+        <v>2735</v>
       </c>
       <c r="D177" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E177" s="29" t="s">
-        <v>2704</v>
+        <v>2683</v>
       </c>
       <c r="F177" s="23" t="s">
         <v>1550</v>
@@ -25371,13 +25500,13 @@
         <v>1164</v>
       </c>
       <c r="C178" s="78" t="s">
-        <v>2757</v>
+        <v>2736</v>
       </c>
       <c r="D178" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>2705</v>
+        <v>2684</v>
       </c>
       <c r="F178" s="23" t="s">
         <v>1550</v>
@@ -25406,13 +25535,13 @@
         <v>1164</v>
       </c>
       <c r="C179" s="78" t="s">
-        <v>2758</v>
+        <v>2737</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E179" s="29" t="s">
-        <v>2706</v>
+        <v>2685</v>
       </c>
       <c r="F179" s="23" t="s">
         <v>1550</v>
@@ -25441,13 +25570,13 @@
         <v>1164</v>
       </c>
       <c r="C180" s="78" t="s">
-        <v>2759</v>
+        <v>2738</v>
       </c>
       <c r="D180" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>2707</v>
+        <v>2686</v>
       </c>
       <c r="F180" s="23" t="s">
         <v>1550</v>
@@ -25476,13 +25605,13 @@
         <v>1164</v>
       </c>
       <c r="C181" s="78" t="s">
-        <v>2760</v>
+        <v>2739</v>
       </c>
       <c r="D181" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E181" s="29" t="s">
-        <v>2708</v>
+        <v>2687</v>
       </c>
       <c r="F181" s="23" t="s">
         <v>1550</v>
@@ -25511,13 +25640,13 @@
         <v>1164</v>
       </c>
       <c r="C182" s="78" t="s">
-        <v>2761</v>
+        <v>2740</v>
       </c>
       <c r="D182" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E182" s="29" t="s">
-        <v>2709</v>
+        <v>2688</v>
       </c>
       <c r="F182" s="23" t="s">
         <v>1550</v>
@@ -25546,13 +25675,13 @@
         <v>1164</v>
       </c>
       <c r="C183" s="78" t="s">
-        <v>2762</v>
+        <v>2741</v>
       </c>
       <c r="D183" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>2710</v>
+        <v>2689</v>
       </c>
       <c r="F183" s="23" t="s">
         <v>1550</v>
@@ -25581,13 +25710,13 @@
         <v>1164</v>
       </c>
       <c r="C184" s="78" t="s">
-        <v>2763</v>
+        <v>2742</v>
       </c>
       <c r="D184" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>2711</v>
+        <v>2690</v>
       </c>
       <c r="F184" s="23" t="s">
         <v>1550</v>
@@ -25616,13 +25745,13 @@
         <v>1164</v>
       </c>
       <c r="C185" s="78" t="s">
-        <v>2764</v>
+        <v>2743</v>
       </c>
       <c r="D185" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E185" s="29" t="s">
-        <v>2712</v>
+        <v>2691</v>
       </c>
       <c r="F185" s="23" t="s">
         <v>1550</v>
@@ -25651,13 +25780,13 @@
         <v>1164</v>
       </c>
       <c r="C186" s="78" t="s">
-        <v>2765</v>
+        <v>2744</v>
       </c>
       <c r="D186" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>2713</v>
+        <v>2692</v>
       </c>
       <c r="F186" s="23" t="s">
         <v>1550</v>
@@ -25686,13 +25815,13 @@
         <v>1164</v>
       </c>
       <c r="C187" s="78" t="s">
-        <v>2766</v>
+        <v>2745</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>2714</v>
+        <v>2693</v>
       </c>
       <c r="F187" s="23" t="s">
         <v>1550</v>
@@ -25721,13 +25850,13 @@
         <v>1164</v>
       </c>
       <c r="C188" s="78" t="s">
-        <v>2767</v>
+        <v>2746</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>2715</v>
+        <v>2694</v>
       </c>
       <c r="F188" s="23" t="s">
         <v>1550</v>
@@ -25756,13 +25885,13 @@
         <v>1164</v>
       </c>
       <c r="C189" s="78" t="s">
-        <v>2768</v>
+        <v>2747</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>2716</v>
+        <v>2695</v>
       </c>
       <c r="F189" s="23" t="s">
         <v>1550</v>
@@ -25791,13 +25920,13 @@
         <v>1164</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>2769</v>
+        <v>2748</v>
       </c>
       <c r="D190" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>2717</v>
+        <v>2696</v>
       </c>
       <c r="F190" s="23" t="s">
         <v>1550</v>
@@ -25826,13 +25955,13 @@
         <v>1164</v>
       </c>
       <c r="C191" s="78" t="s">
-        <v>2770</v>
+        <v>2749</v>
       </c>
       <c r="D191" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>2718</v>
+        <v>2697</v>
       </c>
       <c r="F191" s="23" t="s">
         <v>1550</v>
@@ -25861,13 +25990,13 @@
         <v>1164</v>
       </c>
       <c r="C192" s="78" t="s">
-        <v>2771</v>
+        <v>2750</v>
       </c>
       <c r="D192" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>2719</v>
+        <v>2698</v>
       </c>
       <c r="F192" s="23" t="s">
         <v>1550</v>
@@ -25896,13 +26025,13 @@
         <v>1164</v>
       </c>
       <c r="C193" s="78" t="s">
-        <v>2772</v>
+        <v>2751</v>
       </c>
       <c r="D193" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>2720</v>
+        <v>2699</v>
       </c>
       <c r="F193" s="23" t="s">
         <v>1550</v>
@@ -25929,13 +26058,13 @@
         <v>1164</v>
       </c>
       <c r="C194" s="78" t="s">
-        <v>2773</v>
+        <v>2752</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>2721</v>
+        <v>2700</v>
       </c>
       <c r="F194" s="23" t="s">
         <v>1550</v>
@@ -25962,13 +26091,13 @@
         <v>1164</v>
       </c>
       <c r="C195" s="78" t="s">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="D195" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>2722</v>
+        <v>2701</v>
       </c>
       <c r="F195" s="23" t="s">
         <v>1550</v>
@@ -25995,13 +26124,13 @@
         <v>1164</v>
       </c>
       <c r="C196" s="78" t="s">
-        <v>2775</v>
+        <v>2754</v>
       </c>
       <c r="D196" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>2723</v>
+        <v>2702</v>
       </c>
       <c r="F196" s="23" t="s">
         <v>1550</v>
@@ -26028,13 +26157,13 @@
         <v>1164</v>
       </c>
       <c r="C197" s="78" t="s">
-        <v>2776</v>
+        <v>2755</v>
       </c>
       <c r="D197" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>2724</v>
+        <v>2703</v>
       </c>
       <c r="F197" s="23" t="s">
         <v>1550</v>
@@ -26063,13 +26192,13 @@
         <v>1164</v>
       </c>
       <c r="C198" s="78" t="s">
-        <v>2777</v>
+        <v>2756</v>
       </c>
       <c r="D198" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>2725</v>
+        <v>2704</v>
       </c>
       <c r="F198" s="23" t="s">
         <v>1550</v>
@@ -26098,13 +26227,13 @@
         <v>1164</v>
       </c>
       <c r="C199" s="78" t="s">
-        <v>2778</v>
+        <v>2757</v>
       </c>
       <c r="D199" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E199" s="29" t="s">
-        <v>2726</v>
+        <v>2705</v>
       </c>
       <c r="F199" s="23" t="s">
         <v>1550</v>
@@ -26131,13 +26260,13 @@
         <v>1164</v>
       </c>
       <c r="C200" s="78" t="s">
-        <v>2779</v>
+        <v>2758</v>
       </c>
       <c r="D200" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>2727</v>
+        <v>2706</v>
       </c>
       <c r="F200" s="23" t="s">
         <v>1550</v>
@@ -26164,13 +26293,13 @@
         <v>1164</v>
       </c>
       <c r="C201" s="78" t="s">
-        <v>2780</v>
+        <v>2759</v>
       </c>
       <c r="D201" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E201" s="29" t="s">
-        <v>2728</v>
+        <v>2707</v>
       </c>
       <c r="F201" s="23" t="s">
         <v>1550</v>
@@ -26197,13 +26326,13 @@
         <v>1164</v>
       </c>
       <c r="C202" s="78" t="s">
-        <v>2781</v>
+        <v>2760</v>
       </c>
       <c r="D202" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E202" s="29" t="s">
-        <v>2729</v>
+        <v>2708</v>
       </c>
       <c r="F202" s="23" t="s">
         <v>1550</v>
@@ -26230,13 +26359,13 @@
         <v>1164</v>
       </c>
       <c r="C203" s="78" t="s">
-        <v>2782</v>
+        <v>2761</v>
       </c>
       <c r="D203" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E203" s="29" t="s">
-        <v>2730</v>
+        <v>2709</v>
       </c>
       <c r="F203" s="23" t="s">
         <v>1550</v>
@@ -26265,13 +26394,13 @@
         <v>1164</v>
       </c>
       <c r="C204" s="78" t="s">
-        <v>2783</v>
+        <v>2762</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E204" s="29" t="s">
-        <v>2731</v>
+        <v>2710</v>
       </c>
       <c r="F204" s="23" t="s">
         <v>1550</v>
@@ -26300,13 +26429,13 @@
         <v>1164</v>
       </c>
       <c r="C205" s="78" t="s">
-        <v>2784</v>
+        <v>2763</v>
       </c>
       <c r="D205" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E205" s="29" t="s">
-        <v>2732</v>
+        <v>2711</v>
       </c>
       <c r="F205" s="23" t="s">
         <v>1550</v>
@@ -26335,13 +26464,13 @@
         <v>1164</v>
       </c>
       <c r="C206" s="78" t="s">
-        <v>2785</v>
+        <v>2764</v>
       </c>
       <c r="D206" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>2698</v>
+        <v>2677</v>
       </c>
       <c r="F206" s="23" t="s">
         <v>1550</v>
@@ -26368,13 +26497,13 @@
         <v>1164</v>
       </c>
       <c r="C207" s="78" t="s">
-        <v>2786</v>
+        <v>2765</v>
       </c>
       <c r="D207" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E207" s="29" t="s">
-        <v>2699</v>
+        <v>2678</v>
       </c>
       <c r="F207" s="23" t="s">
         <v>1550</v>
@@ -26401,13 +26530,13 @@
         <v>1164</v>
       </c>
       <c r="C208" s="78" t="s">
-        <v>2787</v>
+        <v>2766</v>
       </c>
       <c r="D208" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E208" s="29" t="s">
-        <v>2700</v>
+        <v>2679</v>
       </c>
       <c r="F208" s="23" t="s">
         <v>1550</v>
@@ -26434,13 +26563,13 @@
         <v>1164</v>
       </c>
       <c r="C209" s="78" t="s">
-        <v>2788</v>
+        <v>2767</v>
       </c>
       <c r="D209" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E209" s="29" t="s">
-        <v>2701</v>
+        <v>2680</v>
       </c>
       <c r="F209" s="23" t="s">
         <v>1550</v>
@@ -26467,13 +26596,13 @@
         <v>1164</v>
       </c>
       <c r="C210" s="78" t="s">
-        <v>2789</v>
+        <v>2768</v>
       </c>
       <c r="D210" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E210" s="29" t="s">
-        <v>2702</v>
+        <v>2681</v>
       </c>
       <c r="F210" s="23" t="s">
         <v>1550</v>
@@ -26500,13 +26629,13 @@
         <v>1164</v>
       </c>
       <c r="C211" s="78" t="s">
-        <v>2790</v>
+        <v>2769</v>
       </c>
       <c r="D211" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E211" s="29" t="s">
-        <v>2703</v>
+        <v>2682</v>
       </c>
       <c r="F211" s="23" t="s">
         <v>1550</v>
@@ -26533,13 +26662,13 @@
         <v>1164</v>
       </c>
       <c r="C212" s="78" t="s">
-        <v>2791</v>
+        <v>2770</v>
       </c>
       <c r="D212" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E212" s="29" t="s">
-        <v>2707</v>
+        <v>2686</v>
       </c>
       <c r="F212" s="23" t="s">
         <v>1550</v>
@@ -26566,13 +26695,13 @@
         <v>1164</v>
       </c>
       <c r="C213" s="78" t="s">
-        <v>2792</v>
+        <v>2771</v>
       </c>
       <c r="D213" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E213" s="29" t="s">
-        <v>2708</v>
+        <v>2687</v>
       </c>
       <c r="F213" s="23" t="s">
         <v>1550</v>
@@ -26599,13 +26728,13 @@
         <v>1164</v>
       </c>
       <c r="C214" s="78" t="s">
-        <v>2793</v>
+        <v>2772</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E214" s="29" t="s">
-        <v>2704</v>
+        <v>2683</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>1550</v>
@@ -26632,13 +26761,13 @@
         <v>1164</v>
       </c>
       <c r="C215" s="78" t="s">
-        <v>2794</v>
+        <v>2773</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E215" s="29" t="s">
-        <v>2705</v>
+        <v>2684</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>1550</v>
@@ -26665,13 +26794,13 @@
         <v>1164</v>
       </c>
       <c r="C216" s="78" t="s">
-        <v>2795</v>
+        <v>2774</v>
       </c>
       <c r="D216" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E216" s="29" t="s">
-        <v>2706</v>
+        <v>2685</v>
       </c>
       <c r="F216" s="23" t="s">
         <v>1550</v>
@@ -26698,13 +26827,13 @@
         <v>1164</v>
       </c>
       <c r="C217" s="78" t="s">
-        <v>2796</v>
+        <v>2775</v>
       </c>
       <c r="D217" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E217" s="29" t="s">
-        <v>2709</v>
+        <v>2688</v>
       </c>
       <c r="F217" s="23" t="s">
         <v>1550</v>
@@ -26900,7 +27029,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
-        <v>2797</v>
+        <v>2776</v>
       </c>
       <c r="B223" s="31" t="s">
         <v>457</v>
@@ -26937,7 +27066,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
-        <v>2798</v>
+        <v>2777</v>
       </c>
       <c r="B224" s="38" t="s">
         <v>459</v>
@@ -26972,14 +27101,14 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>3114</v>
+        <v>3093</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>53</v>
       </c>
       <c r="C225" s="29"/>
       <c r="D225" s="31" t="s">
-        <v>3061</v>
+        <v>3040</v>
       </c>
       <c r="E225" s="29">
         <v>5343</v>
@@ -26988,7 +27117,7 @@
         <v>1550</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>3069</v>
+        <v>3048</v>
       </c>
       <c r="H225" s="29">
         <v>0</v>
@@ -26997,7 +27126,7 @@
         <v>503</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>3115</v>
+        <v>3094</v>
       </c>
       <c r="K225" s="29"/>
       <c r="L225" s="31"/>
@@ -27216,7 +27345,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="29" t="s">
-        <v>2848</v>
+        <v>2827</v>
       </c>
       <c r="B233" s="31" t="s">
         <v>488</v>
@@ -27247,7 +27376,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="29" t="s">
-        <v>2849</v>
+        <v>2828</v>
       </c>
       <c r="B234" s="31" t="s">
         <v>489</v>
@@ -27278,7 +27407,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="29" t="s">
-        <v>2850</v>
+        <v>2829</v>
       </c>
       <c r="B235" s="31" t="s">
         <v>490</v>
@@ -27419,7 +27548,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="29" t="s">
-        <v>2847</v>
+        <v>2826</v>
       </c>
       <c r="B240" s="31"/>
       <c r="C240" s="29"/>
@@ -27444,7 +27573,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="29" t="s">
-        <v>2851</v>
+        <v>2830</v>
       </c>
       <c r="B241" s="31" t="s">
         <v>510</v>
@@ -27473,7 +27602,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="29" t="s">
-        <v>2852</v>
+        <v>2831</v>
       </c>
       <c r="B242" s="31" t="s">
         <v>513</v>
@@ -27816,7 +27945,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="29" t="s">
-        <v>2853</v>
+        <v>2832</v>
       </c>
       <c r="B253" s="31" t="s">
         <v>520</v>
@@ -27870,7 +27999,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="29" t="s">
-        <v>2854</v>
+        <v>2833</v>
       </c>
       <c r="B255" s="31" t="s">
         <v>600</v>
@@ -27982,7 +28111,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="29" t="s">
-        <v>2855</v>
+        <v>2834</v>
       </c>
       <c r="B259" s="31" t="s">
         <v>524</v>
@@ -28398,7 +28527,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="29" t="s">
-        <v>2856</v>
+        <v>2835</v>
       </c>
       <c r="B273" s="31" t="s">
         <v>524</v>
@@ -28839,7 +28968,7 @@
         <v>625</v>
       </c>
       <c r="B289" s="31" t="s">
-        <v>3051</v>
+        <v>3030</v>
       </c>
       <c r="C289" s="29" t="s">
         <v>147</v>
@@ -28863,10 +28992,10 @@
         <v>96</v>
       </c>
       <c r="J289" s="29" t="s">
-        <v>3052</v>
+        <v>3031</v>
       </c>
       <c r="K289" s="29" t="s">
-        <v>3053</v>
+        <v>3032</v>
       </c>
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
@@ -30176,7 +30305,7 @@
       </c>
       <c r="J331" s="29"/>
       <c r="K331" s="35" t="s">
-        <v>3078</v>
+        <v>3057</v>
       </c>
       <c r="L331" s="32"/>
       <c r="M331" s="35"/>
@@ -30538,7 +30667,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="29" t="s">
-        <v>2857</v>
+        <v>2836</v>
       </c>
       <c r="B343" s="31" t="s">
         <v>258</v>
@@ -30807,7 +30936,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="29" t="s">
-        <v>2858</v>
+        <v>2837</v>
       </c>
       <c r="B352" s="29" t="s">
         <v>809</v>
@@ -30838,7 +30967,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="29" t="s">
-        <v>2859</v>
+        <v>2838</v>
       </c>
       <c r="B353" s="29" t="s">
         <v>809</v>
@@ -30869,7 +30998,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="29" t="s">
-        <v>2860</v>
+        <v>2839</v>
       </c>
       <c r="B354" s="29" t="s">
         <v>809</v>
@@ -30900,7 +31029,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="29" t="s">
-        <v>2861</v>
+        <v>2840</v>
       </c>
       <c r="B355" s="29" t="s">
         <v>809</v>
@@ -30931,7 +31060,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="29" t="s">
-        <v>2862</v>
+        <v>2841</v>
       </c>
       <c r="B356" s="31" t="s">
         <v>830</v>
@@ -30962,7 +31091,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="29" t="s">
-        <v>2863</v>
+        <v>2842</v>
       </c>
       <c r="B357" s="31" t="s">
         <v>830</v>
@@ -30993,7 +31122,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="29" t="s">
-        <v>2864</v>
+        <v>2843</v>
       </c>
       <c r="B358" s="31" t="s">
         <v>830</v>
@@ -31024,7 +31153,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="29" t="s">
-        <v>2865</v>
+        <v>2844</v>
       </c>
       <c r="B359" s="31" t="s">
         <v>830</v>
@@ -31494,7 +31623,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
-        <v>2866</v>
+        <v>2845</v>
       </c>
       <c r="B375" s="31" t="s">
         <v>260</v>
@@ -31525,7 +31654,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
-        <v>2867</v>
+        <v>2846</v>
       </c>
       <c r="B376" s="31" t="s">
         <v>260</v>
@@ -31556,7 +31685,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
-        <v>2868</v>
+        <v>2847</v>
       </c>
       <c r="B377" s="31" t="s">
         <v>262</v>
@@ -31587,7 +31716,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
-        <v>2869</v>
+        <v>2848</v>
       </c>
       <c r="B378" s="31" t="s">
         <v>262</v>
@@ -31618,7 +31747,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
-        <v>2870</v>
+        <v>2849</v>
       </c>
       <c r="B379" s="31" t="s">
         <v>242</v>
@@ -31649,7 +31778,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
-        <v>2871</v>
+        <v>2850</v>
       </c>
       <c r="B380" s="31" t="s">
         <v>258</v>
@@ -32038,7 +32167,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
-        <v>2872</v>
+        <v>2851</v>
       </c>
       <c r="B393" s="31" t="s">
         <v>898</v>
@@ -32065,7 +32194,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
-        <v>2873</v>
+        <v>2852</v>
       </c>
       <c r="B394" s="31" t="s">
         <v>899</v>
@@ -32092,7 +32221,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
-        <v>2874</v>
+        <v>2853</v>
       </c>
       <c r="B395" s="29" t="s">
         <v>900</v>
@@ -32115,7 +32244,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
-        <v>2875</v>
+        <v>2854</v>
       </c>
       <c r="B396" s="29" t="s">
         <v>902</v>
@@ -32138,7 +32267,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
-        <v>2876</v>
+        <v>2855</v>
       </c>
       <c r="B397" s="29" t="s">
         <v>900</v>
@@ -32161,7 +32290,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
-        <v>2877</v>
+        <v>2856</v>
       </c>
       <c r="B398" s="31" t="s">
         <v>904</v>
@@ -32184,7 +32313,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
-        <v>2878</v>
+        <v>2857</v>
       </c>
       <c r="B399" s="31" t="s">
         <v>905</v>
@@ -32207,7 +32336,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
-        <v>2879</v>
+        <v>2858</v>
       </c>
       <c r="B400" s="31" t="s">
         <v>906</v>
@@ -32230,7 +32359,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
-        <v>2880</v>
+        <v>2859</v>
       </c>
       <c r="B401" s="31" t="s">
         <v>907</v>
@@ -32253,7 +32382,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
-        <v>2881</v>
+        <v>2860</v>
       </c>
       <c r="B402" s="31" t="s">
         <v>908</v>
@@ -32276,7 +32405,7 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
-        <v>2882</v>
+        <v>2861</v>
       </c>
       <c r="B403" s="31" t="s">
         <v>909</v>
@@ -32299,7 +32428,7 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
-        <v>2883</v>
+        <v>2862</v>
       </c>
       <c r="B404" s="31" t="s">
         <v>910</v>
@@ -32322,7 +32451,7 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
-        <v>2884</v>
+        <v>2863</v>
       </c>
       <c r="B405" s="31" t="s">
         <v>911</v>
@@ -32345,7 +32474,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
-        <v>2885</v>
+        <v>2864</v>
       </c>
       <c r="B406" s="31" t="s">
         <v>897</v>
@@ -32494,7 +32623,7 @@
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
-        <v>2886</v>
+        <v>2865</v>
       </c>
       <c r="B411" s="31" t="s">
         <v>258</v>
@@ -32519,7 +32648,7 @@
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
-        <v>2887</v>
+        <v>2866</v>
       </c>
       <c r="B412" s="31" t="s">
         <v>258</v>
@@ -32544,7 +32673,7 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
-        <v>2888</v>
+        <v>2867</v>
       </c>
       <c r="B413" s="31" t="s">
         <v>258</v>
@@ -32569,7 +32698,7 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
-        <v>2889</v>
+        <v>2868</v>
       </c>
       <c r="B414" s="31" t="s">
         <v>258</v>
@@ -32869,7 +32998,7 @@
     </row>
     <row r="424" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A424" s="29" t="s">
-        <v>2661</v>
+        <v>2640</v>
       </c>
       <c r="B424" s="31" t="s">
         <v>2473</v>
@@ -33323,7 +33452,7 @@
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
-        <v>2890</v>
+        <v>2869</v>
       </c>
       <c r="B438" s="31" t="s">
         <v>982</v>
@@ -33358,7 +33487,7 @@
     </row>
     <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
-        <v>2891</v>
+        <v>2870</v>
       </c>
       <c r="B439" s="31" t="s">
         <v>982</v>
@@ -33393,7 +33522,7 @@
     </row>
     <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="29" t="s">
-        <v>2892</v>
+        <v>2871</v>
       </c>
       <c r="B440" s="31" t="s">
         <v>982</v>
@@ -33428,7 +33557,7 @@
     </row>
     <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="29" t="s">
-        <v>2893</v>
+        <v>2872</v>
       </c>
       <c r="B441" s="87" t="s">
         <v>1055</v>
@@ -33461,7 +33590,7 @@
     </row>
     <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
-        <v>3048</v>
+        <v>3027</v>
       </c>
       <c r="B442" s="87" t="s">
         <v>1458</v>
@@ -33489,14 +33618,14 @@
         <v>1056</v>
       </c>
       <c r="K442" s="29" t="s">
-        <v>3049</v>
+        <v>3028</v>
       </c>
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
     <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="29" t="s">
-        <v>2894</v>
+        <v>2873</v>
       </c>
       <c r="B443" s="29" t="s">
         <v>1604</v>
@@ -33525,7 +33654,7 @@
     </row>
     <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
-        <v>2895</v>
+        <v>2874</v>
       </c>
       <c r="B444" s="87" t="s">
         <v>1611</v>
@@ -33558,7 +33687,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
-        <v>2896</v>
+        <v>2875</v>
       </c>
       <c r="B445" t="s">
         <v>1606</v>
@@ -33589,7 +33718,7 @@
     </row>
     <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
-        <v>2897</v>
+        <v>2876</v>
       </c>
       <c r="B446" t="s">
         <v>1607</v>
@@ -33620,7 +33749,7 @@
     </row>
     <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
-        <v>2898</v>
+        <v>2877</v>
       </c>
       <c r="B447" t="s">
         <v>1608</v>
@@ -33651,7 +33780,7 @@
     </row>
     <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="29" t="s">
-        <v>2899</v>
+        <v>2878</v>
       </c>
       <c r="B448" t="s">
         <v>1609</v>
@@ -33682,7 +33811,7 @@
     </row>
     <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="29" t="s">
-        <v>2900</v>
+        <v>2879</v>
       </c>
       <c r="B449" s="87" t="s">
         <v>1610</v>
@@ -33715,7 +33844,7 @@
     </row>
     <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="29" t="s">
-        <v>2901</v>
+        <v>2880</v>
       </c>
       <c r="B450" s="87" t="s">
         <v>1456</v>
@@ -33746,7 +33875,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2902</v>
+        <v>2881</v>
       </c>
       <c r="B451" s="87" t="s">
         <v>1457</v>
@@ -33777,7 +33906,7 @@
     </row>
     <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
-        <v>2903</v>
+        <v>2882</v>
       </c>
       <c r="B452" s="31" t="s">
         <v>1244</v>
@@ -34457,7 +34586,7 @@
         <v>27</v>
       </c>
       <c r="H471" s="29" t="s">
-        <v>2840</v>
+        <v>2819</v>
       </c>
       <c r="I471" s="29" t="s">
         <v>96</v>
@@ -34471,7 +34600,7 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
-        <v>2904</v>
+        <v>2883</v>
       </c>
       <c r="B472" s="29" t="s">
         <v>19</v>
@@ -34537,7 +34666,7 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
-        <v>2905</v>
+        <v>2884</v>
       </c>
       <c r="B474" s="29" t="s">
         <v>19</v>
@@ -34601,7 +34730,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29" t="s">
-        <v>3120</v>
+        <v>3099</v>
       </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -35120,7 +35249,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
-        <v>2906</v>
+        <v>2885</v>
       </c>
       <c r="B491" s="32"/>
       <c r="C491" s="53" t="s">
@@ -35369,7 +35498,7 @@
     </row>
     <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="34" t="s">
-        <v>2907</v>
+        <v>2886</v>
       </c>
       <c r="B498" s="59" t="s">
         <v>1111</v>
@@ -35711,7 +35840,7 @@
     </row>
     <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
-        <v>2908</v>
+        <v>2887</v>
       </c>
       <c r="B508" s="32"/>
       <c r="C508" s="53"/>
@@ -35738,7 +35867,7 @@
     </row>
     <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="24" t="s">
-        <v>2909</v>
+        <v>2888</v>
       </c>
       <c r="B509" s="22"/>
       <c r="C509" s="25"/>
@@ -36883,13 +37012,13 @@
     </row>
     <row r="542" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="29" t="s">
-        <v>2910</v>
+        <v>2889</v>
       </c>
       <c r="B542" s="59" t="s">
         <v>1674</v>
       </c>
       <c r="C542" s="82" t="s">
-        <v>2643</v>
+        <v>2622</v>
       </c>
       <c r="D542" s="70" t="s">
         <v>1099</v>
@@ -36912,13 +37041,13 @@
     </row>
     <row r="543" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="29" t="s">
-        <v>2911</v>
+        <v>2890</v>
       </c>
       <c r="B543" s="59" t="s">
         <v>1674</v>
       </c>
       <c r="C543" s="36" t="s">
-        <v>2644</v>
+        <v>2623</v>
       </c>
       <c r="D543" s="70" t="s">
         <v>1100</v>
@@ -36941,7 +37070,7 @@
     </row>
     <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="29" t="s">
-        <v>2912</v>
+        <v>2891</v>
       </c>
       <c r="B544" s="59" t="s">
         <v>1674</v>
@@ -36973,7 +37102,7 @@
         <v>1498</v>
       </c>
       <c r="B545" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C545" s="36">
         <v>2</v>
@@ -37002,7 +37131,7 @@
         <v>1499</v>
       </c>
       <c r="B546" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C546" s="36">
         <v>3</v>
@@ -37031,7 +37160,7 @@
         <v>1500</v>
       </c>
       <c r="B547" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C547" s="36">
         <v>4</v>
@@ -37060,7 +37189,7 @@
         <v>1501</v>
       </c>
       <c r="B548" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C548" s="36">
         <v>5</v>
@@ -37089,7 +37218,7 @@
         <v>1502</v>
       </c>
       <c r="B549" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C549" s="36">
         <v>6</v>
@@ -37118,7 +37247,7 @@
         <v>1503</v>
       </c>
       <c r="B550" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C550" s="36">
         <v>7</v>
@@ -37147,7 +37276,7 @@
         <v>1504</v>
       </c>
       <c r="B551" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C551" s="36">
         <v>8</v>
@@ -37176,7 +37305,7 @@
         <v>1505</v>
       </c>
       <c r="B552" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C552" s="36">
         <v>9</v>
@@ -37205,7 +37334,7 @@
         <v>1506</v>
       </c>
       <c r="B553" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C553" s="36">
         <v>10</v>
@@ -37234,7 +37363,7 @@
         <v>1507</v>
       </c>
       <c r="B554" s="73" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C554" s="36">
         <v>11</v>
@@ -37553,7 +37682,7 @@
         <v>1277</v>
       </c>
       <c r="B565" s="84" t="s">
-        <v>2833</v>
+        <v>2812</v>
       </c>
       <c r="C565" s="73" t="s">
         <v>2234</v>
@@ -37579,7 +37708,7 @@
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
-        <v>3121</v>
+        <v>3100</v>
       </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
@@ -38742,7 +38871,7 @@
     </row>
     <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="29" t="s">
-        <v>2913</v>
+        <v>2892</v>
       </c>
       <c r="B603" s="73" t="s">
         <v>1289</v>
@@ -38775,7 +38904,7 @@
     </row>
     <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="29" t="s">
-        <v>2914</v>
+        <v>2893</v>
       </c>
       <c r="B604" s="73" t="s">
         <v>1289</v>
@@ -38808,7 +38937,7 @@
     </row>
     <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="29" t="s">
-        <v>2915</v>
+        <v>2894</v>
       </c>
       <c r="B605" s="73" t="s">
         <v>1289</v>
@@ -38841,7 +38970,7 @@
     </row>
     <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="29" t="s">
-        <v>2916</v>
+        <v>2895</v>
       </c>
       <c r="B606" s="73" t="s">
         <v>1289</v>
@@ -38874,7 +39003,7 @@
     </row>
     <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="29" t="s">
-        <v>2917</v>
+        <v>2896</v>
       </c>
       <c r="B607" s="73" t="s">
         <v>1289</v>
@@ -38905,7 +39034,7 @@
     </row>
     <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="29" t="s">
-        <v>2918</v>
+        <v>2897</v>
       </c>
       <c r="B608" s="73" t="s">
         <v>1289</v>
@@ -38936,7 +39065,7 @@
     </row>
     <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="29" t="s">
-        <v>2919</v>
+        <v>2898</v>
       </c>
       <c r="B609" s="73" t="s">
         <v>1289</v>
@@ -38967,7 +39096,7 @@
     </row>
     <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="29" t="s">
-        <v>2920</v>
+        <v>2899</v>
       </c>
       <c r="B610" s="73" t="s">
         <v>1289</v>
@@ -38998,7 +39127,7 @@
     </row>
     <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="29" t="s">
-        <v>2921</v>
+        <v>2900</v>
       </c>
       <c r="B611" s="73" t="s">
         <v>1289</v>
@@ -39029,7 +39158,7 @@
     </row>
     <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="29" t="s">
-        <v>2922</v>
+        <v>2901</v>
       </c>
       <c r="B612" s="73" t="s">
         <v>1289</v>
@@ -39060,7 +39189,7 @@
     </row>
     <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="29" t="s">
-        <v>2923</v>
+        <v>2902</v>
       </c>
       <c r="B613" s="73" t="s">
         <v>1289</v>
@@ -39091,7 +39220,7 @@
     </row>
     <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="29" t="s">
-        <v>2924</v>
+        <v>2903</v>
       </c>
       <c r="B614" s="73" t="s">
         <v>1289</v>
@@ -39122,7 +39251,7 @@
     </row>
     <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="29" t="s">
-        <v>2925</v>
+        <v>2904</v>
       </c>
       <c r="B615" s="73" t="s">
         <v>1289</v>
@@ -39153,7 +39282,7 @@
     </row>
     <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="29" t="s">
-        <v>2926</v>
+        <v>2905</v>
       </c>
       <c r="B616" s="73" t="s">
         <v>1289</v>
@@ -39184,7 +39313,7 @@
     </row>
     <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="29" t="s">
-        <v>2927</v>
+        <v>2906</v>
       </c>
       <c r="B617" s="73" t="s">
         <v>1289</v>
@@ -39217,7 +39346,7 @@
     </row>
     <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="29" t="s">
-        <v>2928</v>
+        <v>2907</v>
       </c>
       <c r="B618" s="73" t="s">
         <v>1289</v>
@@ -39250,7 +39379,7 @@
     </row>
     <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="29" t="s">
-        <v>2929</v>
+        <v>2908</v>
       </c>
       <c r="B619" s="82" t="s">
         <v>1278</v>
@@ -39281,7 +39410,7 @@
     </row>
     <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="29" t="s">
-        <v>2930</v>
+        <v>2909</v>
       </c>
       <c r="B620" s="82" t="s">
         <v>1278</v>
@@ -39312,7 +39441,7 @@
     </row>
     <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="29" t="s">
-        <v>2931</v>
+        <v>2910</v>
       </c>
       <c r="B621" s="82" t="s">
         <v>1278</v>
@@ -39343,7 +39472,7 @@
     </row>
     <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="29" t="s">
-        <v>2932</v>
+        <v>2911</v>
       </c>
       <c r="B622" s="82" t="s">
         <v>1278</v>
@@ -39376,7 +39505,7 @@
     </row>
     <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="29" t="s">
-        <v>2933</v>
+        <v>2912</v>
       </c>
       <c r="B623" s="83" t="s">
         <v>1283</v>
@@ -39409,7 +39538,7 @@
     </row>
     <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="29" t="s">
-        <v>2934</v>
+        <v>2913</v>
       </c>
       <c r="B624" s="83" t="s">
         <v>1283</v>
@@ -39440,7 +39569,7 @@
     </row>
     <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="29" t="s">
-        <v>2935</v>
+        <v>2914</v>
       </c>
       <c r="B625" s="83" t="s">
         <v>1283</v>
@@ -39471,7 +39600,7 @@
     </row>
     <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="29" t="s">
-        <v>2936</v>
+        <v>2915</v>
       </c>
       <c r="B626" s="83" t="s">
         <v>1283</v>
@@ -39568,7 +39697,7 @@
     </row>
     <row r="629" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A629" s="29" t="s">
-        <v>2937</v>
+        <v>2916</v>
       </c>
       <c r="B629" s="82" t="s">
         <v>1337</v>
@@ -39595,7 +39724,7 @@
     </row>
     <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
-        <v>2938</v>
+        <v>2917</v>
       </c>
       <c r="B630" s="83" t="s">
         <v>1337</v>
@@ -40672,10 +40801,10 @@
     </row>
     <row r="661" spans="1:13" s="131" customFormat="1" ht="82" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="128" t="s">
-        <v>3126</v>
+        <v>3105</v>
       </c>
       <c r="B661" s="83" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C661" s="128" t="s">
         <v>2401</v>
@@ -40693,13 +40822,13 @@
         <v>1478</v>
       </c>
       <c r="H661" s="56" t="s">
-        <v>3128</v>
+        <v>3107</v>
       </c>
       <c r="I661" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J661" s="130" t="s">
-        <v>3160</v>
+        <v>3139</v>
       </c>
       <c r="K661" s="128" t="s">
         <v>465</v>
@@ -40709,13 +40838,13 @@
     </row>
     <row r="662" spans="1:13" s="131" customFormat="1" ht="66" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="128" t="s">
-        <v>3127</v>
+        <v>3106</v>
       </c>
       <c r="B662" s="83" t="s">
-        <v>3161</v>
+        <v>3140</v>
       </c>
       <c r="C662" s="128" t="s">
-        <v>3132</v>
+        <v>3111</v>
       </c>
       <c r="D662" s="84" t="s">
         <v>1629</v>
@@ -40730,13 +40859,13 @@
         <v>1478</v>
       </c>
       <c r="H662" s="56" t="s">
-        <v>3129</v>
+        <v>3108</v>
       </c>
       <c r="I662" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J662" s="130" t="s">
-        <v>3162</v>
+        <v>3141</v>
       </c>
       <c r="K662" s="128" t="s">
         <v>989</v>
@@ -40746,7 +40875,7 @@
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
-        <v>3109</v>
+        <v>3088</v>
       </c>
       <c r="B663" s="84" t="s">
         <v>1852</v>
@@ -40773,7 +40902,7 @@
         <v>60</v>
       </c>
       <c r="J663" s="29" t="s">
-        <v>3131</v>
+        <v>3110</v>
       </c>
       <c r="K663" s="29"/>
       <c r="L663" s="31"/>
@@ -41883,7 +42012,7 @@
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
-        <v>2939</v>
+        <v>2918</v>
       </c>
       <c r="B698" s="85" t="s">
         <v>1370</v>
@@ -41912,7 +42041,7 @@
     </row>
     <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
-        <v>2940</v>
+        <v>2919</v>
       </c>
       <c r="B699" s="85" t="s">
         <v>1370</v>
@@ -41941,7 +42070,7 @@
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
-        <v>2941</v>
+        <v>2920</v>
       </c>
       <c r="B700" s="85" t="s">
         <v>1370</v>
@@ -41970,7 +42099,7 @@
     </row>
     <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
-        <v>2942</v>
+        <v>2921</v>
       </c>
       <c r="B701" s="85" t="s">
         <v>1370</v>
@@ -41999,7 +42128,7 @@
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
-        <v>2943</v>
+        <v>2922</v>
       </c>
       <c r="B702" s="85" t="s">
         <v>1370</v>
@@ -42028,7 +42157,7 @@
     </row>
     <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
-        <v>2944</v>
+        <v>2923</v>
       </c>
       <c r="B703" s="85" t="s">
         <v>1370</v>
@@ -42057,7 +42186,7 @@
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
-        <v>2945</v>
+        <v>2924</v>
       </c>
       <c r="B704" s="85" t="s">
         <v>1370</v>
@@ -42086,7 +42215,7 @@
     </row>
     <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
-        <v>2946</v>
+        <v>2925</v>
       </c>
       <c r="B705" s="85" t="s">
         <v>1370</v>
@@ -42115,7 +42244,7 @@
     </row>
     <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
-        <v>2947</v>
+        <v>2926</v>
       </c>
       <c r="B706" s="85" t="s">
         <v>1370</v>
@@ -42144,7 +42273,7 @@
     </row>
     <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
-        <v>2948</v>
+        <v>2927</v>
       </c>
       <c r="B707" s="85" t="s">
         <v>1370</v>
@@ -42173,7 +42302,7 @@
     </row>
     <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
-        <v>2949</v>
+        <v>2928</v>
       </c>
       <c r="B708" s="85" t="s">
         <v>1370</v>
@@ -42202,7 +42331,7 @@
     </row>
     <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
-        <v>2950</v>
+        <v>2929</v>
       </c>
       <c r="B709" s="85" t="s">
         <v>1370</v>
@@ -42231,7 +42360,7 @@
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
-        <v>2951</v>
+        <v>2930</v>
       </c>
       <c r="B710" s="85" t="s">
         <v>1370</v>
@@ -42260,7 +42389,7 @@
     </row>
     <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
-        <v>2952</v>
+        <v>2931</v>
       </c>
       <c r="B711" s="85" t="s">
         <v>1370</v>
@@ -42289,7 +42418,7 @@
     </row>
     <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
-        <v>2953</v>
+        <v>2932</v>
       </c>
       <c r="B712" s="85" t="s">
         <v>1370</v>
@@ -42318,7 +42447,7 @@
     </row>
     <row r="713" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A713" s="29" t="s">
-        <v>2954</v>
+        <v>2933</v>
       </c>
       <c r="B713" s="85" t="s">
         <v>1370</v>
@@ -42347,7 +42476,7 @@
     </row>
     <row r="714" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A714" s="29" t="s">
-        <v>2955</v>
+        <v>2934</v>
       </c>
       <c r="B714" s="85" t="s">
         <v>1371</v>
@@ -42376,7 +42505,7 @@
     </row>
     <row r="715" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A715" s="29" t="s">
-        <v>2956</v>
+        <v>2935</v>
       </c>
       <c r="B715" s="85" t="s">
         <v>1371</v>
@@ -42405,7 +42534,7 @@
     </row>
     <row r="716" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A716" s="29" t="s">
-        <v>2957</v>
+        <v>2936</v>
       </c>
       <c r="B716" s="85" t="s">
         <v>1371</v>
@@ -42434,7 +42563,7 @@
     </row>
     <row r="717" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A717" s="29" t="s">
-        <v>2958</v>
+        <v>2937</v>
       </c>
       <c r="B717" s="85" t="s">
         <v>1371</v>
@@ -42463,7 +42592,7 @@
     </row>
     <row r="718" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A718" s="29" t="s">
-        <v>2959</v>
+        <v>2938</v>
       </c>
       <c r="B718" s="85" t="s">
         <v>1371</v>
@@ -42492,7 +42621,7 @@
     </row>
     <row r="719" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2960</v>
+        <v>2939</v>
       </c>
       <c r="B719" s="85" t="s">
         <v>1371</v>
@@ -42521,7 +42650,7 @@
     </row>
     <row r="720" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A720" s="29" t="s">
-        <v>2961</v>
+        <v>2940</v>
       </c>
       <c r="B720" s="85" t="s">
         <v>1371</v>
@@ -42550,7 +42679,7 @@
     </row>
     <row r="721" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2962</v>
+        <v>2941</v>
       </c>
       <c r="B721" s="85" t="s">
         <v>1371</v>
@@ -45212,7 +45341,7 @@
     </row>
     <row r="801" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
-        <v>2963</v>
+        <v>2942</v>
       </c>
       <c r="B801" s="83" t="s">
         <v>1530</v>
@@ -45243,7 +45372,7 @@
     </row>
     <row r="802" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
-        <v>2964</v>
+        <v>2943</v>
       </c>
       <c r="B802" s="83" t="s">
         <v>1530</v>
@@ -45274,7 +45403,7 @@
     </row>
     <row r="803" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
-        <v>2965</v>
+        <v>2944</v>
       </c>
       <c r="B803" s="83" t="s">
         <v>1530</v>
@@ -45305,7 +45434,7 @@
     </row>
     <row r="804" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
-        <v>2966</v>
+        <v>2945</v>
       </c>
       <c r="B804" s="83" t="s">
         <v>1530</v>
@@ -45336,7 +45465,7 @@
     </row>
     <row r="805" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
-        <v>2967</v>
+        <v>2946</v>
       </c>
       <c r="B805" s="83" t="s">
         <v>1530</v>
@@ -45367,7 +45496,7 @@
     </row>
     <row r="806" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A806" s="29" t="s">
-        <v>2968</v>
+        <v>2947</v>
       </c>
       <c r="B806" s="85" t="s">
         <v>1485</v>
@@ -45396,7 +45525,7 @@
     </row>
     <row r="807" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A807" s="29" t="s">
-        <v>2969</v>
+        <v>2948</v>
       </c>
       <c r="B807" s="85" t="s">
         <v>1485</v>
@@ -45425,7 +45554,7 @@
     </row>
     <row r="808" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
-        <v>2970</v>
+        <v>2949</v>
       </c>
       <c r="B808" s="85" t="s">
         <v>1486</v>
@@ -45454,7 +45583,7 @@
     </row>
     <row r="809" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
-        <v>2971</v>
+        <v>2950</v>
       </c>
       <c r="B809" s="85" t="s">
         <v>1486</v>
@@ -45483,7 +45612,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2972</v>
+        <v>2951</v>
       </c>
       <c r="B810" s="85" t="s">
         <v>1489</v>
@@ -45512,7 +45641,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
-        <v>3122</v>
+        <v>3101</v>
       </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
@@ -45529,19 +45658,19 @@
     </row>
     <row r="812" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
-        <v>2973</v>
+        <v>2952</v>
       </c>
       <c r="B812" s="83" t="s">
         <v>1675</v>
       </c>
       <c r="C812" s="83" t="s">
-        <v>3021</v>
+        <v>3000</v>
       </c>
       <c r="D812" s="85" t="s">
         <v>1672</v>
       </c>
       <c r="E812" s="83" t="s">
-        <v>3022</v>
+        <v>3001</v>
       </c>
       <c r="F812" s="31" t="s">
         <v>231</v>
@@ -45552,7 +45681,7 @@
       <c r="H812" s="29"/>
       <c r="I812" s="29"/>
       <c r="J812" s="29" t="s">
-        <v>3023</v>
+        <v>3002</v>
       </c>
       <c r="K812" s="29"/>
       <c r="L812" s="31"/>
@@ -45560,7 +45689,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
-        <v>3110</v>
+        <v>3089</v>
       </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
@@ -45672,7 +45801,7 @@
     </row>
     <row r="817" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
-        <v>2974</v>
+        <v>2953</v>
       </c>
       <c r="B817" s="96" t="s">
         <v>1674</v>
@@ -45703,7 +45832,7 @@
     </row>
     <row r="818" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
-        <v>2975</v>
+        <v>2954</v>
       </c>
       <c r="B818" s="83" t="s">
         <v>1675</v>
@@ -45734,7 +45863,7 @@
     </row>
     <row r="819" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A819" s="29" t="s">
-        <v>2976</v>
+        <v>2955</v>
       </c>
       <c r="B819" s="83" t="s">
         <v>1675</v>
@@ -45889,7 +46018,7 @@
     </row>
     <row r="824" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
-        <v>2977</v>
+        <v>2956</v>
       </c>
       <c r="B824" s="83" t="s">
         <v>1573</v>
@@ -45920,7 +46049,7 @@
     </row>
     <row r="825" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
-        <v>2978</v>
+        <v>2957</v>
       </c>
       <c r="B825" s="83" t="s">
         <v>1574</v>
@@ -45951,7 +46080,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2979</v>
+        <v>2958</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1577</v>
@@ -45982,7 +46111,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2980</v>
+        <v>2959</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1578</v>
@@ -46013,7 +46142,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>2981</v>
+        <v>2960</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1579</v>
@@ -46042,7 +46171,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>2982</v>
+        <v>2961</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1579</v>
@@ -47066,7 +47195,7 @@
       <c r="D860" s="83"/>
       <c r="E860" s="83"/>
       <c r="F860" s="31" t="s">
-        <v>3077</v>
+        <v>3056</v>
       </c>
       <c r="G860" s="31" t="s">
         <v>52</v>
@@ -47540,7 +47669,7 @@
         <v>96</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>3159</v>
+        <v>3138</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -47756,7 +47885,7 @@
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A881" s="29" t="s">
-        <v>3123</v>
+        <v>3102</v>
       </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
@@ -50518,10 +50647,10 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A965" s="29" t="s">
-        <v>3044</v>
+        <v>3023</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3043</v>
+        <v>3022</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>335</v>
@@ -50547,10 +50676,10 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>3045</v>
+        <v>3024</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3043</v>
+        <v>3022</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>336</v>
@@ -50576,10 +50705,10 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A967" s="29" t="s">
-        <v>3046</v>
+        <v>3025</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3042</v>
+        <v>3021</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>335</v>
@@ -50605,10 +50734,10 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>3047</v>
+        <v>3026</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3042</v>
+        <v>3021</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>336</v>
@@ -50634,7 +50763,7 @@
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A969" s="29" t="s">
-        <v>3124</v>
+        <v>3103</v>
       </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
@@ -50651,7 +50780,7 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A970" s="29" t="s">
-        <v>3125</v>
+        <v>3104</v>
       </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>
@@ -50671,7 +50800,7 @@
         <v>1529</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3039</v>
+        <v>3018</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>760</v>
@@ -50701,10 +50830,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3041</v>
+        <v>3020</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3040</v>
+        <v>3019</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>760</v>
@@ -50740,7 +50869,7 @@
         <v>1342</v>
       </c>
       <c r="D973" s="15" t="s">
-        <v>3057</v>
+        <v>3036</v>
       </c>
       <c r="F973" t="s">
         <v>1550</v>
@@ -55790,7 +55919,7 @@
         <v>1528</v>
       </c>
       <c r="D1126" s="29" t="s">
-        <v>3057</v>
+        <v>3036</v>
       </c>
       <c r="E1126" s="82" t="s">
         <v>2182</v>
@@ -55828,7 +55957,7 @@
         <v>1342</v>
       </c>
       <c r="E1127" s="83" t="s">
-        <v>2182</v>
+        <v>3195</v>
       </c>
       <c r="F1127" s="31" t="s">
         <v>1651</v>
@@ -56954,7 +57083,7 @@
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1161" s="29" t="s">
-        <v>2600</v>
+        <v>3178</v>
       </c>
       <c r="B1161" s="100" t="s">
         <v>2598</v>
@@ -56962,8 +57091,12 @@
       <c r="C1161" s="83" t="s">
         <v>2286</v>
       </c>
-      <c r="D1161" s="85"/>
-      <c r="E1161" s="83"/>
+      <c r="D1161" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1161" s="83" t="s">
+        <v>1247</v>
+      </c>
       <c r="F1161" s="31" t="s">
         <v>1651</v>
       </c>
@@ -56971,13 +57104,13 @@
         <v>1478</v>
       </c>
       <c r="H1161" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1161" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1161" s="29" t="s">
-        <v>2599</v>
+        <v>3144</v>
       </c>
       <c r="K1161" s="29"/>
       <c r="L1161" s="31"/>
@@ -56985,7 +57118,7 @@
     </row>
     <row r="1162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1162" s="29" t="s">
-        <v>2601</v>
+        <v>3179</v>
       </c>
       <c r="B1162" s="100" t="s">
         <v>2598</v>
@@ -56993,8 +57126,12 @@
       <c r="C1162" s="83" t="s">
         <v>2287</v>
       </c>
-      <c r="D1162" s="85"/>
-      <c r="E1162" s="83"/>
+      <c r="D1162" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1162" s="83" t="s">
+        <v>1249</v>
+      </c>
       <c r="F1162" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57002,13 +57139,13 @@
         <v>1478</v>
       </c>
       <c r="H1162" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1162" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1162" s="29" t="s">
-        <v>2602</v>
+        <v>3145</v>
       </c>
       <c r="K1162" s="29"/>
       <c r="L1162" s="31"/>
@@ -57016,7 +57153,7 @@
     </row>
     <row r="1163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1163" s="29" t="s">
-        <v>2607</v>
+        <v>3180</v>
       </c>
       <c r="B1163" s="100" t="s">
         <v>2598</v>
@@ -57024,8 +57161,12 @@
       <c r="C1163" s="83" t="s">
         <v>2288</v>
       </c>
-      <c r="D1163" s="85"/>
-      <c r="E1163" s="83"/>
+      <c r="D1163" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1163" s="83" t="s">
+        <v>1223</v>
+      </c>
       <c r="F1163" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57033,13 +57174,13 @@
         <v>1478</v>
       </c>
       <c r="H1163" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1163" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1163" s="29" t="s">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="K1163" s="29"/>
       <c r="L1163" s="31"/>
@@ -57047,7 +57188,7 @@
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1164" s="29" t="s">
-        <v>2608</v>
+        <v>3181</v>
       </c>
       <c r="B1164" s="100" t="s">
         <v>2598</v>
@@ -57055,8 +57196,12 @@
       <c r="C1164" s="83" t="s">
         <v>2289</v>
       </c>
-      <c r="D1164" s="85"/>
-      <c r="E1164" s="83"/>
+      <c r="D1164" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1164" s="83" t="s">
+        <v>1225</v>
+      </c>
       <c r="F1164" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57064,13 +57209,13 @@
         <v>1478</v>
       </c>
       <c r="H1164" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1164" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1164" s="29" t="s">
-        <v>2604</v>
+        <v>2600</v>
       </c>
       <c r="K1164" s="29"/>
       <c r="L1164" s="31"/>
@@ -57078,7 +57223,7 @@
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1165" s="29" t="s">
-        <v>2609</v>
+        <v>3182</v>
       </c>
       <c r="B1165" s="100" t="s">
         <v>2598</v>
@@ -57086,8 +57231,12 @@
       <c r="C1165" s="83" t="s">
         <v>2285</v>
       </c>
-      <c r="D1165" s="85"/>
-      <c r="E1165" s="83"/>
+      <c r="D1165" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1165" s="83" t="s">
+        <v>1227</v>
+      </c>
       <c r="F1165" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57095,13 +57244,13 @@
         <v>1478</v>
       </c>
       <c r="H1165" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1165" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1165" s="29" t="s">
-        <v>2605</v>
+        <v>3146</v>
       </c>
       <c r="K1165" s="29"/>
       <c r="L1165" s="31"/>
@@ -57109,7 +57258,7 @@
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1166" s="29" t="s">
-        <v>2610</v>
+        <v>3183</v>
       </c>
       <c r="B1166" s="100" t="s">
         <v>2598</v>
@@ -57117,8 +57266,12 @@
       <c r="C1166" s="83" t="s">
         <v>2386</v>
       </c>
-      <c r="D1166" s="85"/>
-      <c r="E1166" s="83"/>
+      <c r="D1166" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1166" s="83" t="s">
+        <v>1229</v>
+      </c>
       <c r="F1166" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57126,13 +57279,13 @@
         <v>1478</v>
       </c>
       <c r="H1166" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1166" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1166" s="29" t="s">
-        <v>2606</v>
+        <v>2601</v>
       </c>
       <c r="K1166" s="29"/>
       <c r="L1166" s="31"/>
@@ -57140,7 +57293,7 @@
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1167" s="29" t="s">
-        <v>2616</v>
+        <v>3184</v>
       </c>
       <c r="B1167" s="100" t="s">
         <v>2598</v>
@@ -57148,8 +57301,12 @@
       <c r="C1167" s="83" t="s">
         <v>2282</v>
       </c>
-      <c r="D1167" s="85"/>
-      <c r="E1167" s="83"/>
+      <c r="D1167" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1167" s="83" t="s">
+        <v>1231</v>
+      </c>
       <c r="F1167" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57157,13 +57314,13 @@
         <v>1478</v>
       </c>
       <c r="H1167" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1167" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1167" s="29" t="s">
-        <v>2611</v>
+        <v>2602</v>
       </c>
       <c r="K1167" s="29"/>
       <c r="L1167" s="31"/>
@@ -57171,7 +57328,7 @@
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1168" s="29" t="s">
-        <v>2617</v>
+        <v>3185</v>
       </c>
       <c r="B1168" s="100" t="s">
         <v>2598</v>
@@ -57179,8 +57336,12 @@
       <c r="C1168" s="83" t="s">
         <v>2283</v>
       </c>
-      <c r="D1168" s="85"/>
-      <c r="E1168" s="83"/>
+      <c r="D1168" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1168" s="83" t="s">
+        <v>1256</v>
+      </c>
       <c r="F1168" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57188,21 +57349,21 @@
         <v>1478</v>
       </c>
       <c r="H1168" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1168" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1168" s="29" t="s">
-        <v>2612</v>
+        <v>2603</v>
       </c>
       <c r="K1168" s="29"/>
       <c r="L1168" s="31"/>
       <c r="M1168" s="29"/>
     </row>
-    <row r="1169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1169" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="29" t="s">
-        <v>2618</v>
+        <v>3186</v>
       </c>
       <c r="B1169" s="100" t="s">
         <v>2598</v>
@@ -57210,8 +57371,12 @@
       <c r="C1169" s="83" t="s">
         <v>2284</v>
       </c>
-      <c r="D1169" s="85"/>
-      <c r="E1169" s="83"/>
+      <c r="D1169" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1169" s="83" t="s">
+        <v>1258</v>
+      </c>
       <c r="F1169" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57219,21 +57384,21 @@
         <v>1478</v>
       </c>
       <c r="H1169" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1169" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1169" s="29" t="s">
-        <v>2613</v>
+        <v>2604</v>
       </c>
       <c r="K1169" s="29"/>
       <c r="L1169" s="31"/>
       <c r="M1169" s="29"/>
     </row>
-    <row r="1170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1170" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="29" t="s">
-        <v>2619</v>
+        <v>3187</v>
       </c>
       <c r="B1170" s="100" t="s">
         <v>2598</v>
@@ -57241,8 +57406,12 @@
       <c r="C1170" s="83" t="s">
         <v>2387</v>
       </c>
-      <c r="D1170" s="85"/>
-      <c r="E1170" s="83"/>
+      <c r="D1170" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1170" s="82" t="s">
+        <v>1260</v>
+      </c>
       <c r="F1170" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57250,21 +57419,21 @@
         <v>1478</v>
       </c>
       <c r="H1170" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1170" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1170" s="29" t="s">
-        <v>2614</v>
+        <v>2605</v>
       </c>
       <c r="K1170" s="29"/>
       <c r="L1170" s="31"/>
       <c r="M1170" s="29"/>
     </row>
-    <row r="1171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1171" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="29" t="s">
-        <v>2620</v>
+        <v>3188</v>
       </c>
       <c r="B1171" s="100" t="s">
         <v>2598</v>
@@ -57272,8 +57441,12 @@
       <c r="C1171" s="83" t="s">
         <v>1847</v>
       </c>
-      <c r="D1171" s="85"/>
-      <c r="E1171" s="83"/>
+      <c r="D1171" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1171" s="83" t="s">
+        <v>1262</v>
+      </c>
       <c r="F1171" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57281,21 +57454,21 @@
         <v>1478</v>
       </c>
       <c r="H1171" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1171" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1171" s="29" t="s">
-        <v>2615</v>
+        <v>2606</v>
       </c>
       <c r="K1171" s="29"/>
       <c r="L1171" s="31"/>
       <c r="M1171" s="29"/>
     </row>
-    <row r="1172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1172" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="29" t="s">
-        <v>2621</v>
+        <v>3189</v>
       </c>
       <c r="B1172" s="100" t="s">
         <v>2598</v>
@@ -57303,8 +57476,12 @@
       <c r="C1172" s="83" t="s">
         <v>2267</v>
       </c>
-      <c r="D1172" s="85"/>
-      <c r="E1172" s="83"/>
+      <c r="D1172" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1172" s="82" t="s">
+        <v>1264</v>
+      </c>
       <c r="F1172" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57312,21 +57489,21 @@
         <v>1478</v>
       </c>
       <c r="H1172" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1172" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1172" s="29" t="s">
-        <v>2622</v>
+        <v>3147</v>
       </c>
       <c r="K1172" s="29"/>
       <c r="L1172" s="31"/>
       <c r="M1172" s="29"/>
     </row>
-    <row r="1173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1173" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="29" t="s">
-        <v>2633</v>
+        <v>3190</v>
       </c>
       <c r="B1173" s="100" t="s">
         <v>2598</v>
@@ -57334,8 +57511,12 @@
       <c r="C1173" s="83" t="s">
         <v>1854</v>
       </c>
-      <c r="D1173" s="85"/>
-      <c r="E1173" s="83"/>
+      <c r="D1173" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1173" s="83" t="s">
+        <v>1291</v>
+      </c>
       <c r="F1173" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57343,21 +57524,21 @@
         <v>1478</v>
       </c>
       <c r="H1173" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1173" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1173" s="29" t="s">
-        <v>2623</v>
+        <v>2608</v>
       </c>
       <c r="K1173" s="29"/>
       <c r="L1173" s="31"/>
       <c r="M1173" s="29"/>
     </row>
-    <row r="1174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1174" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>2634</v>
+        <v>3191</v>
       </c>
       <c r="B1174" s="100" t="s">
         <v>2598</v>
@@ -57365,8 +57546,12 @@
       <c r="C1174" s="83" t="s">
         <v>1855</v>
       </c>
-      <c r="D1174" s="85"/>
-      <c r="E1174" s="83"/>
+      <c r="D1174" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1174" s="82" t="s">
+        <v>1293</v>
+      </c>
       <c r="F1174" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57374,21 +57559,21 @@
         <v>1478</v>
       </c>
       <c r="H1174" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1174" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1174" s="29" t="s">
-        <v>2622</v>
+        <v>2607</v>
       </c>
       <c r="K1174" s="29"/>
       <c r="L1174" s="31"/>
       <c r="M1174" s="29"/>
     </row>
-    <row r="1175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1175" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="29" t="s">
-        <v>2635</v>
+        <v>3192</v>
       </c>
       <c r="B1175" s="100" t="s">
         <v>2598</v>
@@ -57396,8 +57581,12 @@
       <c r="C1175" s="83" t="s">
         <v>2264</v>
       </c>
-      <c r="D1175" s="85"/>
-      <c r="E1175" s="83"/>
+      <c r="D1175" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1175" s="83" t="s">
+        <v>1295</v>
+      </c>
       <c r="F1175" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57405,21 +57594,21 @@
         <v>1478</v>
       </c>
       <c r="H1175" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1175" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1175" s="29" t="s">
-        <v>2624</v>
+        <v>3148</v>
       </c>
       <c r="K1175" s="29"/>
       <c r="L1175" s="31"/>
       <c r="M1175" s="29"/>
     </row>
-    <row r="1176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1176" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>2636</v>
+        <v>3193</v>
       </c>
       <c r="B1176" s="100" t="s">
         <v>2598</v>
@@ -57427,8 +57616,12 @@
       <c r="C1176" s="83" t="s">
         <v>2263</v>
       </c>
-      <c r="D1176" s="85"/>
-      <c r="E1176" s="83"/>
+      <c r="D1176" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1176" s="82" t="s">
+        <v>1297</v>
+      </c>
       <c r="F1176" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57436,13 +57629,13 @@
         <v>1478</v>
       </c>
       <c r="H1176" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1176" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1176" s="29" t="s">
-        <v>2625</v>
+        <v>2609</v>
       </c>
       <c r="K1176" s="29"/>
       <c r="L1176" s="31"/>
@@ -57450,7 +57643,7 @@
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>2637</v>
+        <v>3194</v>
       </c>
       <c r="B1177" s="100" t="s">
         <v>2598</v>
@@ -57458,8 +57651,12 @@
       <c r="C1177" s="83" t="s">
         <v>1860</v>
       </c>
-      <c r="D1177" s="85"/>
-      <c r="E1177" s="83"/>
+      <c r="D1177" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1177" s="83" t="s">
+        <v>1299</v>
+      </c>
       <c r="F1177" s="31" t="s">
         <v>1651</v>
       </c>
@@ -57467,13 +57664,13 @@
         <v>1478</v>
       </c>
       <c r="H1177" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1177" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1177" s="29" t="s">
-        <v>2626</v>
+        <v>2610</v>
       </c>
       <c r="K1177" s="29"/>
       <c r="L1177" s="31"/>
@@ -57481,7 +57678,7 @@
     </row>
     <row r="1178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1178" s="29" t="s">
-        <v>2627</v>
+        <v>2611</v>
       </c>
       <c r="B1178" s="100" t="s">
         <v>2598</v>
@@ -57490,7 +57687,7 @@
         <v>2395</v>
       </c>
       <c r="D1178" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1178" s="83" t="s">
         <v>1857</v>
@@ -57502,13 +57699,13 @@
         <v>1478</v>
       </c>
       <c r="H1178" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1178" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1178" s="29" t="s">
-        <v>2627</v>
+        <v>2611</v>
       </c>
       <c r="K1178" s="29"/>
       <c r="L1178" s="31"/>
@@ -57516,7 +57713,7 @@
     </row>
     <row r="1179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1179" s="29" t="s">
-        <v>2628</v>
+        <v>2612</v>
       </c>
       <c r="B1179" s="100" t="s">
         <v>2598</v>
@@ -57525,7 +57722,7 @@
         <v>2396</v>
       </c>
       <c r="D1179" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1179" s="83" t="s">
         <v>2395</v>
@@ -57537,13 +57734,13 @@
         <v>1478</v>
       </c>
       <c r="H1179" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1179" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1179" s="29" t="s">
-        <v>2628</v>
+        <v>2612</v>
       </c>
       <c r="K1179" s="29"/>
       <c r="L1179" s="31"/>
@@ -57551,7 +57748,7 @@
     </row>
     <row r="1180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1180" s="29" t="s">
-        <v>2629</v>
+        <v>2613</v>
       </c>
       <c r="B1180" s="100" t="s">
         <v>2598</v>
@@ -57560,7 +57757,7 @@
         <v>2397</v>
       </c>
       <c r="D1180" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1180" s="83" t="s">
         <v>2396</v>
@@ -57572,13 +57769,13 @@
         <v>1478</v>
       </c>
       <c r="H1180" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1180" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1180" s="29" t="s">
-        <v>2629</v>
+        <v>2613</v>
       </c>
       <c r="K1180" s="29"/>
       <c r="L1180" s="31"/>
@@ -57586,7 +57783,7 @@
     </row>
     <row r="1181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1181" s="29" t="s">
-        <v>2630</v>
+        <v>2614</v>
       </c>
       <c r="B1181" s="100" t="s">
         <v>2598</v>
@@ -57595,7 +57792,7 @@
         <v>2398</v>
       </c>
       <c r="D1181" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1181" s="83" t="s">
         <v>2397</v>
@@ -57607,13 +57804,13 @@
         <v>1478</v>
       </c>
       <c r="H1181" s="29" t="s">
-        <v>26</v>
+        <v>1631</v>
       </c>
       <c r="I1181" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J1181" s="29" t="s">
-        <v>2630</v>
+        <v>2614</v>
       </c>
       <c r="K1181" s="29"/>
       <c r="L1181" s="31"/>
@@ -57621,7 +57818,7 @@
     </row>
     <row r="1182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1182" s="29" t="s">
-        <v>2631</v>
+        <v>2615</v>
       </c>
       <c r="B1182" s="100" t="s">
         <v>2598</v>
@@ -57638,17 +57835,15 @@
         <v>60</v>
       </c>
       <c r="J1182" s="29" t="s">
-        <v>2631</v>
-      </c>
-      <c r="K1182" s="29" t="s">
         <v>439</v>
       </c>
+      <c r="K1182" s="29"/>
       <c r="L1182" s="31"/>
       <c r="M1182" s="29"/>
     </row>
     <row r="1183" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="29" t="s">
-        <v>2632</v>
+        <v>2616</v>
       </c>
       <c r="B1183" s="100" t="s">
         <v>2598</v>
@@ -57665,20 +57860,18 @@
         <v>60</v>
       </c>
       <c r="J1183" s="29" t="s">
-        <v>2632</v>
-      </c>
-      <c r="K1183" s="29" t="s">
         <v>439</v>
       </c>
+      <c r="K1183" s="29"/>
       <c r="L1183" s="31"/>
       <c r="M1183" s="29"/>
     </row>
     <row r="1184" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="29" t="s">
-        <v>2638</v>
+        <v>2617</v>
       </c>
       <c r="B1184" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1184" s="83" t="s">
         <v>2398</v>
@@ -57703,17 +57896,17 @@
       </c>
       <c r="J1184" s="29"/>
       <c r="K1184" s="29" t="s">
-        <v>2642</v>
+        <v>2621</v>
       </c>
       <c r="L1184" s="31"/>
       <c r="M1184" s="29"/>
     </row>
     <row r="1185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1185" s="29" t="s">
-        <v>2639</v>
+        <v>2618</v>
       </c>
       <c r="B1185" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1185" s="83" t="s">
         <v>2399</v>
@@ -57738,17 +57931,17 @@
       </c>
       <c r="J1185" s="29"/>
       <c r="K1185" s="29" t="s">
-        <v>2642</v>
+        <v>2621</v>
       </c>
       <c r="L1185" s="31"/>
       <c r="M1185" s="29"/>
     </row>
     <row r="1186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1186" s="29" t="s">
-        <v>2640</v>
+        <v>2619</v>
       </c>
       <c r="B1186" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1186" s="83" t="s">
         <v>2400</v>
@@ -57773,17 +57966,17 @@
       </c>
       <c r="J1186" s="29"/>
       <c r="K1186" s="29" t="s">
-        <v>2642</v>
+        <v>2621</v>
       </c>
       <c r="L1186" s="31"/>
       <c r="M1186" s="29"/>
     </row>
     <row r="1187" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1187" s="29" t="s">
-        <v>2641</v>
+        <v>2620</v>
       </c>
       <c r="B1187" s="85" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1187" s="83" t="s">
         <v>2401</v>
@@ -57808,26 +58001,26 @@
       </c>
       <c r="J1187" s="29"/>
       <c r="K1187" s="29" t="s">
-        <v>2642</v>
+        <v>2621</v>
       </c>
       <c r="L1187" s="31"/>
       <c r="M1187" s="29"/>
     </row>
     <row r="1188" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="29" t="s">
-        <v>2645</v>
+        <v>2624</v>
       </c>
       <c r="B1188" s="80" t="s">
-        <v>2646</v>
+        <v>2625</v>
       </c>
       <c r="C1188" s="83" t="s">
-        <v>2647</v>
+        <v>2626</v>
       </c>
       <c r="D1188" s="85" t="s">
-        <v>2648</v>
+        <v>2627</v>
       </c>
       <c r="E1188" s="83" t="s">
-        <v>2649</v>
+        <v>2628</v>
       </c>
       <c r="F1188" s="31"/>
       <c r="G1188" s="31" t="s">
@@ -57846,10 +58039,10 @@
     </row>
     <row r="1189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1189" s="29" t="s">
-        <v>2651</v>
+        <v>2630</v>
       </c>
       <c r="B1189" s="85" t="s">
-        <v>2648</v>
+        <v>2627</v>
       </c>
       <c r="C1189" s="83" t="s">
         <v>2182</v>
@@ -57858,7 +58051,7 @@
         <v>1674</v>
       </c>
       <c r="E1189" s="83" t="s">
-        <v>2650</v>
+        <v>2629</v>
       </c>
       <c r="F1189" s="31"/>
       <c r="G1189" s="31" t="s">
@@ -57877,16 +58070,16 @@
     </row>
     <row r="1190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1190" s="29" t="s">
-        <v>2654</v>
+        <v>2633</v>
       </c>
       <c r="B1190" s="100" t="s">
         <v>1674</v>
       </c>
       <c r="C1190" s="83" t="s">
-        <v>2653</v>
+        <v>2632</v>
       </c>
       <c r="D1190" s="85" t="s">
-        <v>2652</v>
+        <v>2631</v>
       </c>
       <c r="E1190" s="83" t="s">
         <v>2182</v>
@@ -57910,16 +58103,16 @@
     </row>
     <row r="1191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1191" s="29" t="s">
-        <v>2657</v>
+        <v>2636</v>
       </c>
       <c r="B1191" s="100" t="s">
         <v>1674</v>
       </c>
       <c r="C1191" s="83" t="s">
-        <v>2655</v>
+        <v>2634</v>
       </c>
       <c r="D1191" s="85" t="s">
-        <v>2656</v>
+        <v>2635</v>
       </c>
       <c r="E1191" s="83" t="s">
         <v>1478</v>
@@ -57943,7 +58136,7 @@
     </row>
     <row r="1192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1192" s="29" t="s">
-        <v>2658</v>
+        <v>2637</v>
       </c>
       <c r="B1192" s="100"/>
       <c r="C1192" s="83"/>
@@ -57972,7 +58165,7 @@
     </row>
     <row r="1193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1193" s="29" t="s">
-        <v>2659</v>
+        <v>2638</v>
       </c>
       <c r="B1193" s="100"/>
       <c r="C1193" s="83"/>
@@ -57985,7 +58178,7 @@
         <v>30</v>
       </c>
       <c r="H1193" s="29" t="s">
-        <v>2660</v>
+        <v>2639</v>
       </c>
       <c r="I1193" s="119" t="s">
         <v>96</v>
@@ -58001,7 +58194,7 @@
     </row>
     <row r="1194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1194" s="29" t="s">
-        <v>2662</v>
+        <v>2641</v>
       </c>
       <c r="B1194" s="100"/>
       <c r="C1194" s="83"/>
@@ -58030,7 +58223,7 @@
     </row>
     <row r="1195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1195" s="29" t="s">
-        <v>2663</v>
+        <v>2642</v>
       </c>
       <c r="B1195" s="100"/>
       <c r="C1195" s="83"/>
@@ -58059,16 +58252,16 @@
     </row>
     <row r="1196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1196" s="29" t="s">
-        <v>2665</v>
+        <v>2644</v>
       </c>
       <c r="B1196" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1196" s="83" t="s">
         <v>2264</v>
       </c>
       <c r="D1196" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1196" s="83" t="s">
         <v>2294</v>
@@ -58092,16 +58285,16 @@
     </row>
     <row r="1197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1197" s="29" t="s">
-        <v>2666</v>
+        <v>2645</v>
       </c>
       <c r="B1197" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1197" s="83" t="s">
         <v>2263</v>
       </c>
       <c r="D1197" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1197" s="83" t="s">
         <v>2383</v>
@@ -58125,16 +58318,16 @@
     </row>
     <row r="1198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1198" s="29" t="s">
-        <v>2667</v>
+        <v>2646</v>
       </c>
       <c r="B1198" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1198" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1198" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1198" s="83" t="s">
         <v>1857</v>
@@ -58158,16 +58351,16 @@
     </row>
     <row r="1199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1199" s="29" t="s">
-        <v>2668</v>
+        <v>2647</v>
       </c>
       <c r="B1199" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1199" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1199" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1199" s="83" t="s">
         <v>2395</v>
@@ -58191,16 +58384,16 @@
     </row>
     <row r="1200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1200" s="29" t="s">
-        <v>2669</v>
+        <v>2648</v>
       </c>
       <c r="B1200" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1200" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1200" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1200" s="83" t="s">
         <v>2396</v>
@@ -58224,16 +58417,16 @@
     </row>
     <row r="1201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1201" s="29" t="s">
-        <v>2670</v>
+        <v>2649</v>
       </c>
       <c r="B1201" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1201" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1201" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1201" s="83" t="s">
         <v>2397</v>
@@ -58257,16 +58450,16 @@
     </row>
     <row r="1202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1202" s="29" t="s">
-        <v>2671</v>
+        <v>2650</v>
       </c>
       <c r="B1202" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1202" s="83" t="s">
         <v>2391</v>
       </c>
       <c r="D1202" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1202" s="83" t="s">
         <v>2398</v>
@@ -58290,16 +58483,16 @@
     </row>
     <row r="1203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1203" s="29" t="s">
-        <v>2672</v>
+        <v>2651</v>
       </c>
       <c r="B1203" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1203" s="83" t="s">
         <v>2392</v>
       </c>
       <c r="D1203" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1203" s="83" t="s">
         <v>2399</v>
@@ -58323,16 +58516,16 @@
     </row>
     <row r="1204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1204" s="29" t="s">
-        <v>2673</v>
+        <v>2652</v>
       </c>
       <c r="B1204" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1204" s="83" t="s">
         <v>2393</v>
       </c>
       <c r="D1204" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1204" s="83" t="s">
         <v>2400</v>
@@ -58356,16 +58549,16 @@
     </row>
     <row r="1205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1205" s="29" t="s">
-        <v>2674</v>
+        <v>2653</v>
       </c>
       <c r="B1205" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1205" s="83" t="s">
         <v>2394</v>
       </c>
       <c r="D1205" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1205" s="83" t="s">
         <v>2401</v>
@@ -58389,16 +58582,16 @@
     </row>
     <row r="1206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1206" s="29" t="s">
-        <v>2675</v>
+        <v>2654</v>
       </c>
       <c r="B1206" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1206" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1206" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1206" s="83" t="s">
         <v>2391</v>
@@ -58422,16 +58615,16 @@
     </row>
     <row r="1207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1207" s="29" t="s">
-        <v>2676</v>
+        <v>2655</v>
       </c>
       <c r="B1207" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1207" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1207" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1207" s="83" t="s">
         <v>2392</v>
@@ -58455,16 +58648,16 @@
     </row>
     <row r="1208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1208" s="29" t="s">
-        <v>2677</v>
+        <v>2656</v>
       </c>
       <c r="B1208" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1208" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1208" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1208" s="83" t="s">
         <v>2393</v>
@@ -58488,16 +58681,16 @@
     </row>
     <row r="1209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1209" s="29" t="s">
-        <v>2678</v>
+        <v>2657</v>
       </c>
       <c r="B1209" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="C1209" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1209" s="100" t="s">
-        <v>2664</v>
+        <v>2643</v>
       </c>
       <c r="E1209" s="83" t="s">
         <v>2394</v>
@@ -58521,7 +58714,7 @@
     </row>
     <row r="1210" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="29" t="s">
-        <v>2799</v>
+        <v>2778</v>
       </c>
       <c r="B1210" s="100"/>
       <c r="C1210" s="83"/>
@@ -58543,32 +58736,32 @@
         <v>439</v>
       </c>
       <c r="K1210" s="29" t="s">
-        <v>2800</v>
+        <v>2779</v>
       </c>
       <c r="L1210" s="31"/>
       <c r="M1210" s="29"/>
     </row>
     <row r="1211" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1211" s="29" t="s">
-        <v>2803</v>
+        <v>2782</v>
       </c>
       <c r="B1211" s="112" t="s">
-        <v>2819</v>
+        <v>2798</v>
       </c>
       <c r="C1211" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1211" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1211" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1211" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1211" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1211" s="29">
         <v>0</v>
@@ -58585,25 +58778,25 @@
     </row>
     <row r="1212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1212" s="29" t="s">
-        <v>2804</v>
+        <v>2783</v>
       </c>
       <c r="B1212" s="100" t="s">
-        <v>2820</v>
+        <v>2799</v>
       </c>
       <c r="C1212" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1212" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1212" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1212" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1212" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1212" s="29">
         <v>0</v>
@@ -58620,25 +58813,25 @@
     </row>
     <row r="1213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1213" s="29" t="s">
-        <v>2805</v>
+        <v>2784</v>
       </c>
       <c r="B1213" s="100" t="s">
-        <v>2821</v>
+        <v>2800</v>
       </c>
       <c r="C1213" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1213" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1213" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1213" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1213" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1213" s="29">
         <v>0</v>
@@ -58655,25 +58848,25 @@
     </row>
     <row r="1214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1214" s="29" t="s">
-        <v>2806</v>
+        <v>2785</v>
       </c>
       <c r="B1214" s="100" t="s">
-        <v>2822</v>
+        <v>2801</v>
       </c>
       <c r="C1214" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1214" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1214" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1214" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1214" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1214" s="29">
         <v>0</v>
@@ -58690,25 +58883,25 @@
     </row>
     <row r="1215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1215" s="29" t="s">
-        <v>2807</v>
+        <v>2786</v>
       </c>
       <c r="B1215" s="100" t="s">
-        <v>2823</v>
+        <v>2802</v>
       </c>
       <c r="C1215" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1215" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1215" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1215" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1215" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1215" s="29">
         <v>0</v>
@@ -58725,25 +58918,25 @@
     </row>
     <row r="1216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1216" s="29" t="s">
-        <v>2808</v>
+        <v>2787</v>
       </c>
       <c r="B1216" s="100" t="s">
-        <v>2824</v>
+        <v>2803</v>
       </c>
       <c r="C1216" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1216" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1216" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1216" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1216" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1216" s="29">
         <v>0</v>
@@ -58760,25 +58953,25 @@
     </row>
     <row r="1217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1217" s="29" t="s">
-        <v>2809</v>
+        <v>2788</v>
       </c>
       <c r="B1217" s="100" t="s">
-        <v>2825</v>
+        <v>2804</v>
       </c>
       <c r="C1217" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1217" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1217" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1217" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1217" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1217" s="29">
         <v>0</v>
@@ -58795,25 +58988,25 @@
     </row>
     <row r="1218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1218" s="29" t="s">
-        <v>2810</v>
+        <v>2789</v>
       </c>
       <c r="B1218" s="100" t="s">
-        <v>2826</v>
+        <v>2805</v>
       </c>
       <c r="C1218" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1218" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1218" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1218" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1218" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1218" s="29">
         <v>0</v>
@@ -58830,25 +59023,25 @@
     </row>
     <row r="1219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1219" s="29" t="s">
-        <v>2811</v>
+        <v>2790</v>
       </c>
       <c r="B1219" s="100" t="s">
-        <v>2827</v>
+        <v>2806</v>
       </c>
       <c r="C1219" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1219" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1219" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1219" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1219" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1219" s="29">
         <v>0</v>
@@ -58865,25 +59058,25 @@
     </row>
     <row r="1220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1220" s="29" t="s">
-        <v>2812</v>
+        <v>2791</v>
       </c>
       <c r="B1220" s="100" t="s">
-        <v>2828</v>
+        <v>2807</v>
       </c>
       <c r="C1220" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1220" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1220" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1220" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1220" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1220" s="29">
         <v>0</v>
@@ -58900,25 +59093,25 @@
     </row>
     <row r="1221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1221" s="29" t="s">
-        <v>2813</v>
+        <v>2792</v>
       </c>
       <c r="B1221" s="83" t="s">
         <v>2189</v>
       </c>
       <c r="C1221" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1221" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1221" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1221" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1221" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1221" s="29">
         <v>0</v>
@@ -58935,25 +59128,25 @@
     </row>
     <row r="1222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1222" s="29" t="s">
-        <v>2814</v>
+        <v>2793</v>
       </c>
       <c r="B1222" s="83" t="s">
-        <v>3050</v>
+        <v>3029</v>
       </c>
       <c r="C1222" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1222" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1222" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1222" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1222" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1222" s="29">
         <v>0</v>
@@ -58970,25 +59163,25 @@
     </row>
     <row r="1223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1223" s="29" t="s">
-        <v>2815</v>
+        <v>2794</v>
       </c>
       <c r="B1223" s="100" t="s">
-        <v>2831</v>
+        <v>2810</v>
       </c>
       <c r="C1223" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1223" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1223" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1223" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1223" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1223" s="29">
         <v>0</v>
@@ -59005,25 +59198,25 @@
     </row>
     <row r="1224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1224" s="29" t="s">
-        <v>2816</v>
+        <v>2795</v>
       </c>
       <c r="B1224" s="100" t="s">
-        <v>2829</v>
+        <v>2808</v>
       </c>
       <c r="C1224" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1224" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1224" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1224" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1224" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1224" s="29">
         <v>0</v>
@@ -59040,25 +59233,25 @@
     </row>
     <row r="1225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1225" s="29" t="s">
-        <v>2817</v>
+        <v>2796</v>
       </c>
       <c r="B1225" s="126" t="s">
-        <v>2830</v>
+        <v>2809</v>
       </c>
       <c r="C1225" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1225" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1225" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1225" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1225" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1225" s="29">
         <v>0</v>
@@ -59075,25 +59268,25 @@
     </row>
     <row r="1226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1226" s="29" t="s">
-        <v>2818</v>
+        <v>2797</v>
       </c>
       <c r="B1226" s="125" t="s">
-        <v>2832</v>
+        <v>2811</v>
       </c>
       <c r="C1226" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1226" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1226" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1226" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1226" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1226" s="29">
         <v>0</v>
@@ -59110,25 +59303,25 @@
     </row>
     <row r="1227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1227" s="29" t="s">
-        <v>2834</v>
+        <v>2813</v>
       </c>
       <c r="B1227" s="100" t="s">
-        <v>2838</v>
+        <v>2817</v>
       </c>
       <c r="C1227" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1227" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1227" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1227" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1227" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1227" s="29">
         <v>0</v>
@@ -59137,7 +59330,7 @@
         <v>60</v>
       </c>
       <c r="J1227" s="29" t="s">
-        <v>2836</v>
+        <v>2815</v>
       </c>
       <c r="K1227" s="29"/>
       <c r="L1227" s="31"/>
@@ -59145,25 +59338,25 @@
     </row>
     <row r="1228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1228" s="29" t="s">
-        <v>2835</v>
+        <v>2814</v>
       </c>
       <c r="B1228" s="100" t="s">
-        <v>2839</v>
+        <v>2818</v>
       </c>
       <c r="C1228" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="D1228" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1228" s="83" t="s">
-        <v>2802</v>
+        <v>2781</v>
       </c>
       <c r="F1228" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1228" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1228" s="29">
         <v>0</v>
@@ -59172,7 +59365,7 @@
         <v>60</v>
       </c>
       <c r="J1228" s="29" t="s">
-        <v>2837</v>
+        <v>2816</v>
       </c>
       <c r="K1228" s="29"/>
       <c r="L1228" s="31"/>
@@ -59180,25 +59373,25 @@
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1229" s="29" t="s">
-        <v>2998</v>
+        <v>2977</v>
       </c>
       <c r="B1229" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1229" s="83" t="s">
-        <v>2994</v>
+        <v>2973</v>
       </c>
       <c r="D1229" s="85" t="s">
-        <v>2984</v>
+        <v>2963</v>
       </c>
       <c r="E1229" s="83" t="s">
-        <v>2994</v>
+        <v>2973</v>
       </c>
       <c r="F1229" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1229" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1229" s="29">
         <v>0</v>
@@ -59207,35 +59400,35 @@
         <v>60</v>
       </c>
       <c r="J1229" s="29" t="s">
-        <v>3008</v>
+        <v>2987</v>
       </c>
       <c r="K1229" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1229" s="31"/>
       <c r="M1229" s="29"/>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1230" s="29" t="s">
-        <v>2999</v>
+        <v>2978</v>
       </c>
       <c r="B1230" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1230" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="D1230" s="85" t="s">
-        <v>2985</v>
+        <v>2964</v>
       </c>
       <c r="E1230" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1230" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1230" s="29">
         <v>0</v>
@@ -59244,35 +59437,35 @@
         <v>60</v>
       </c>
       <c r="J1230" s="29" t="s">
-        <v>3009</v>
+        <v>2988</v>
       </c>
       <c r="K1230" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1230" s="31"/>
       <c r="M1230" s="29"/>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1231" s="29" t="s">
-        <v>3000</v>
+        <v>2979</v>
       </c>
       <c r="B1231" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1231" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="D1231" s="85" t="s">
-        <v>2986</v>
+        <v>2965</v>
       </c>
       <c r="E1231" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="F1231" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1231" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1231" s="29">
         <v>0</v>
@@ -59281,35 +59474,35 @@
         <v>60</v>
       </c>
       <c r="J1231" s="29" t="s">
-        <v>3010</v>
+        <v>2989</v>
       </c>
       <c r="K1231" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1231" s="31"/>
       <c r="M1231" s="29"/>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1232" s="29" t="s">
-        <v>3001</v>
+        <v>2980</v>
       </c>
       <c r="B1232" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1232" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="D1232" s="85" t="s">
-        <v>2987</v>
+        <v>2966</v>
       </c>
       <c r="E1232" s="83" t="s">
-        <v>2995</v>
+        <v>2974</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1232" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1232" s="29">
         <v>0</v>
@@ -59318,35 +59511,35 @@
         <v>60</v>
       </c>
       <c r="J1232" s="29" t="s">
-        <v>3011</v>
+        <v>2990</v>
       </c>
       <c r="K1232" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1232" s="31"/>
       <c r="M1232" s="29"/>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1233" s="29" t="s">
-        <v>3002</v>
+        <v>2981</v>
       </c>
       <c r="B1233" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1233" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="D1233" s="85" t="s">
-        <v>2988</v>
+        <v>2967</v>
       </c>
       <c r="E1233" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="F1233" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1233" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1233" s="29">
         <v>0</v>
@@ -59355,35 +59548,35 @@
         <v>60</v>
       </c>
       <c r="J1233" s="29" t="s">
-        <v>3012</v>
+        <v>2991</v>
       </c>
       <c r="K1233" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1233" s="31"/>
       <c r="M1233" s="29"/>
     </row>
     <row r="1234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1234" s="29" t="s">
-        <v>3003</v>
+        <v>2982</v>
       </c>
       <c r="B1234" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1234" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="D1234" s="85" t="s">
-        <v>2989</v>
+        <v>2968</v>
       </c>
       <c r="E1234" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="F1234" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1234" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1234" s="29">
         <v>0</v>
@@ -59392,35 +59585,35 @@
         <v>60</v>
       </c>
       <c r="J1234" s="29" t="s">
-        <v>3013</v>
+        <v>2992</v>
       </c>
       <c r="K1234" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1234" s="31"/>
       <c r="M1234" s="29"/>
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1235" s="29" t="s">
-        <v>3004</v>
+        <v>2983</v>
       </c>
       <c r="B1235" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1235" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="D1235" s="85" t="s">
-        <v>2990</v>
+        <v>2969</v>
       </c>
       <c r="E1235" s="83" t="s">
-        <v>2996</v>
+        <v>2975</v>
       </c>
       <c r="F1235" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1235" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1235" s="29">
         <v>0</v>
@@ -59429,35 +59622,35 @@
         <v>60</v>
       </c>
       <c r="J1235" s="29" t="s">
-        <v>3014</v>
+        <v>2993</v>
       </c>
       <c r="K1235" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1235" s="31"/>
       <c r="M1235" s="29"/>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1236" s="29" t="s">
-        <v>3005</v>
+        <v>2984</v>
       </c>
       <c r="B1236" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1236" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="D1236" s="85" t="s">
-        <v>2991</v>
+        <v>2970</v>
       </c>
       <c r="E1236" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="F1236" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1236" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1236" s="29">
         <v>0</v>
@@ -59466,35 +59659,35 @@
         <v>60</v>
       </c>
       <c r="J1236" s="29" t="s">
-        <v>3015</v>
+        <v>2994</v>
       </c>
       <c r="K1236" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1236" s="31"/>
       <c r="M1236" s="29"/>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1237" s="29" t="s">
-        <v>3006</v>
+        <v>2985</v>
       </c>
       <c r="B1237" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1237" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="D1237" s="85" t="s">
-        <v>2992</v>
+        <v>2971</v>
       </c>
       <c r="E1237" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1237" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1237" s="29">
         <v>0</v>
@@ -59503,35 +59696,35 @@
         <v>60</v>
       </c>
       <c r="J1237" s="29" t="s">
-        <v>3016</v>
+        <v>2995</v>
       </c>
       <c r="K1237" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1237" s="31"/>
       <c r="M1237" s="29"/>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1238" s="29" t="s">
-        <v>3007</v>
+        <v>2986</v>
       </c>
       <c r="B1238" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1238" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="D1238" s="85" t="s">
-        <v>2993</v>
+        <v>2972</v>
       </c>
       <c r="E1238" s="83" t="s">
-        <v>2997</v>
+        <v>2976</v>
       </c>
       <c r="F1238" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1238" s="31" t="s">
-        <v>2801</v>
+        <v>2780</v>
       </c>
       <c r="H1238" s="29">
         <v>0</v>
@@ -59540,20 +59733,20 @@
         <v>60</v>
       </c>
       <c r="J1238" s="29" t="s">
-        <v>3017</v>
+        <v>2996</v>
       </c>
       <c r="K1238" s="29" t="s">
-        <v>3018</v>
+        <v>2997</v>
       </c>
       <c r="L1238" s="31"/>
       <c r="M1238" s="29"/>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1239" s="29" t="s">
-        <v>3024</v>
+        <v>3003</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>3032</v>
+        <v>3011</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>760</v>
@@ -59571,13 +59764,13 @@
         <v>1482</v>
       </c>
       <c r="H1239" s="29" t="s">
-        <v>3025</v>
+        <v>3004</v>
       </c>
       <c r="I1239" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1239" s="29" t="s">
-        <v>3026</v>
+        <v>3005</v>
       </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
@@ -59585,7 +59778,7 @@
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1240" s="29" t="s">
-        <v>3027</v>
+        <v>3006</v>
       </c>
       <c r="B1240" s="100" t="s">
         <v>1050</v>
@@ -59606,13 +59799,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3031</v>
+        <v>3010</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>3029</v>
+        <v>3008</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59620,7 +59813,7 @@
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1241" s="29" t="s">
-        <v>3028</v>
+        <v>3007</v>
       </c>
       <c r="B1241" s="29" t="s">
         <v>1629</v>
@@ -59647,7 +59840,7 @@
         <v>96</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>3029</v>
+        <v>3008</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59655,7 +59848,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>3030</v>
+        <v>3009</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1672</v>
@@ -59686,16 +59879,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3035</v>
+        <v>3014</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>3033</v>
+        <v>3012</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>3034</v>
+        <v>3013</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>52</v>
@@ -59708,10 +59901,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
-        <v>3037</v>
+        <v>3016</v>
       </c>
       <c r="J1243" s="29" t="s">
-        <v>3038</v>
+        <v>3017</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59719,16 +59912,16 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3036</v>
+        <v>3015</v>
       </c>
       <c r="B1244" s="29" t="s">
         <v>1629</v>
       </c>
       <c r="C1244" s="83" t="s">
-        <v>3067</v>
+        <v>3046</v>
       </c>
       <c r="D1244" s="100" t="s">
-        <v>3034</v>
+        <v>3013</v>
       </c>
       <c r="E1244" s="83" t="s">
         <v>2182</v>
@@ -59741,10 +59934,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
-        <v>3037</v>
+        <v>3016</v>
       </c>
       <c r="J1244" s="29" t="s">
-        <v>3038</v>
+        <v>3017</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>
@@ -59752,10 +59945,10 @@
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1245" s="29" t="s">
-        <v>3054</v>
+        <v>3033</v>
       </c>
       <c r="B1245" s="100" t="s">
-        <v>3051</v>
+        <v>3030</v>
       </c>
       <c r="C1245" s="83" t="s">
         <v>213</v>
@@ -59771,7 +59964,7 @@
       <c r="H1245" s="29"/>
       <c r="I1245" s="119"/>
       <c r="J1245" s="29" t="s">
-        <v>3056</v>
+        <v>3035</v>
       </c>
       <c r="K1245" s="29"/>
       <c r="L1245" s="31"/>
@@ -59779,7 +59972,7 @@
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1246" s="29" t="s">
-        <v>3055</v>
+        <v>3034</v>
       </c>
       <c r="B1246" s="100"/>
       <c r="C1246" s="83"/>
@@ -59798,16 +59991,16 @@
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1247" s="29" t="s">
-        <v>3058</v>
+        <v>3037</v>
       </c>
       <c r="B1247" s="100" t="s">
-        <v>3034</v>
+        <v>3013</v>
       </c>
       <c r="C1247" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1247" s="85" t="s">
-        <v>3059</v>
+        <v>3038</v>
       </c>
       <c r="E1247" s="83" t="s">
         <v>52</v>
@@ -59819,13 +60012,13 @@
         <v>52</v>
       </c>
       <c r="H1247" s="29" t="s">
-        <v>3060</v>
+        <v>3039</v>
       </c>
       <c r="I1247" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1247" s="29" t="s">
-        <v>3038</v>
+        <v>3017</v>
       </c>
       <c r="K1247" s="29"/>
       <c r="L1247" s="31" t="s">
@@ -59835,16 +60028,16 @@
     </row>
     <row r="1248" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1248" s="29" t="s">
-        <v>3061</v>
+        <v>3040</v>
       </c>
       <c r="B1248" s="100" t="s">
-        <v>3065</v>
+        <v>3044</v>
       </c>
       <c r="C1248" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1248" s="85" t="s">
-        <v>3063</v>
+        <v>3042</v>
       </c>
       <c r="E1248" s="83" t="s">
         <v>52</v>
@@ -59856,13 +60049,13 @@
         <v>52</v>
       </c>
       <c r="H1248" s="29" t="s">
-        <v>3060</v>
+        <v>3039</v>
       </c>
       <c r="I1248" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1248" s="29" t="s">
-        <v>3062</v>
+        <v>3041</v>
       </c>
       <c r="K1248" s="29"/>
       <c r="L1248" s="31" t="s">
@@ -59872,7 +60065,7 @@
     </row>
     <row r="1249" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="29" t="s">
-        <v>3064</v>
+        <v>3043</v>
       </c>
       <c r="B1249" s="127" t="s">
         <v>1626</v>
@@ -59881,7 +60074,7 @@
         <v>2285</v>
       </c>
       <c r="D1249" s="85" t="s">
-        <v>3065</v>
+        <v>3044</v>
       </c>
       <c r="E1249" s="83" t="s">
         <v>2182</v>
@@ -59893,13 +60086,13 @@
         <v>1478</v>
       </c>
       <c r="H1249" s="29" t="s">
-        <v>3066</v>
+        <v>3045</v>
       </c>
       <c r="I1249" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1249" s="29" t="s">
-        <v>3062</v>
+        <v>3041</v>
       </c>
       <c r="K1249" s="29"/>
       <c r="L1249" s="31"/>
@@ -59907,7 +60100,7 @@
     </row>
     <row r="1250" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="29" t="s">
-        <v>3068</v>
+        <v>3047</v>
       </c>
       <c r="B1250" s="85" t="s">
         <v>53</v>
@@ -59916,16 +60109,16 @@
         <v>2277</v>
       </c>
       <c r="D1250" s="100" t="s">
-        <v>3063</v>
+        <v>3042</v>
       </c>
       <c r="E1250" s="86" t="s">
-        <v>3071</v>
+        <v>3050</v>
       </c>
       <c r="F1250" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1250" s="31" t="s">
-        <v>3069</v>
+        <v>3048</v>
       </c>
       <c r="H1250" s="29">
         <v>0</v>
@@ -59934,7 +60127,7 @@
         <v>60</v>
       </c>
       <c r="J1250" s="29" t="s">
-        <v>3070</v>
+        <v>3049</v>
       </c>
       <c r="K1250" s="29"/>
       <c r="L1250" s="31"/>
@@ -59942,7 +60135,7 @@
     </row>
     <row r="1251" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="29" t="s">
-        <v>3072</v>
+        <v>3051</v>
       </c>
       <c r="B1251" s="80" t="s">
         <v>1672</v>
@@ -59967,7 +60160,7 @@
         <v>60</v>
       </c>
       <c r="J1251" s="29" t="s">
-        <v>3062</v>
+        <v>3041</v>
       </c>
       <c r="K1251" s="29"/>
       <c r="L1251" s="31"/>
@@ -59975,7 +60168,7 @@
     </row>
     <row r="1252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1252" s="29" t="s">
-        <v>3073</v>
+        <v>3052</v>
       </c>
       <c r="B1252" s="100" t="s">
         <v>2224</v>
@@ -59987,7 +60180,7 @@
         <v>968</v>
       </c>
       <c r="E1252" s="83" t="s">
-        <v>3074</v>
+        <v>3053</v>
       </c>
       <c r="F1252" s="31" t="s">
         <v>1550</v>
@@ -60002,7 +60195,7 @@
         <v>60</v>
       </c>
       <c r="J1252" s="29" t="s">
-        <v>3076</v>
+        <v>3055</v>
       </c>
       <c r="K1252" s="29"/>
       <c r="L1252" s="31"/>
@@ -60010,13 +60203,13 @@
     </row>
     <row r="1253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1253" s="29" t="s">
-        <v>3075</v>
+        <v>3054</v>
       </c>
       <c r="B1253" s="100" t="s">
         <v>968</v>
       </c>
       <c r="C1253" s="83" t="s">
-        <v>3074</v>
+        <v>3053</v>
       </c>
       <c r="D1253" s="85" t="s">
         <v>1164</v>
@@ -60037,7 +60230,7 @@
         <v>60</v>
       </c>
       <c r="J1253" s="29" t="s">
-        <v>3076</v>
+        <v>3055</v>
       </c>
       <c r="K1253" s="29"/>
       <c r="L1253" s="31"/>
@@ -60045,7 +60238,7 @@
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1254" s="29" t="s">
-        <v>3117</v>
+        <v>3096</v>
       </c>
       <c r="B1254" s="29" t="s">
         <v>1629</v>
@@ -60072,7 +60265,7 @@
         <v>96</v>
       </c>
       <c r="J1254" s="29" t="s">
-        <v>3118</v>
+        <v>3097</v>
       </c>
       <c r="K1254" s="29"/>
       <c r="L1254" s="31"/>
@@ -60080,7 +60273,7 @@
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1255" s="29" t="s">
-        <v>3119</v>
+        <v>3098</v>
       </c>
       <c r="B1255" s="100" t="s">
         <v>1672</v>
@@ -60105,7 +60298,7 @@
         <v>60</v>
       </c>
       <c r="J1255" s="29" t="s">
-        <v>3118</v>
+        <v>3097</v>
       </c>
       <c r="K1255" s="29"/>
       <c r="L1255" s="31"/>
@@ -60113,16 +60306,16 @@
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1256" s="29" t="s">
-        <v>3133</v>
+        <v>3112</v>
       </c>
       <c r="B1256" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1256" s="83" t="s">
         <v>2286</v>
       </c>
       <c r="D1256" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1256" s="83" t="s">
         <v>2380</v>
@@ -60146,16 +60339,16 @@
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1257" s="29" t="s">
-        <v>3134</v>
+        <v>3113</v>
       </c>
       <c r="B1257" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1257" s="83" t="s">
         <v>2287</v>
       </c>
       <c r="D1257" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1257" s="83" t="s">
         <v>2381</v>
@@ -60179,16 +60372,16 @@
     </row>
     <row r="1258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1258" s="29" t="s">
-        <v>3135</v>
+        <v>3114</v>
       </c>
       <c r="B1258" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1258" s="83" t="s">
         <v>2288</v>
       </c>
       <c r="D1258" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1258" s="83" t="s">
         <v>2382</v>
@@ -60212,16 +60405,16 @@
     </row>
     <row r="1259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1259" s="29" t="s">
-        <v>3136</v>
+        <v>3115</v>
       </c>
       <c r="B1259" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1259" s="83" t="s">
         <v>2289</v>
       </c>
       <c r="D1259" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1259" s="83" t="s">
         <v>1853</v>
@@ -60245,16 +60438,16 @@
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1260" s="29" t="s">
-        <v>3137</v>
+        <v>3116</v>
       </c>
       <c r="B1260" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1260" s="83" t="s">
         <v>2285</v>
       </c>
       <c r="D1260" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1260" s="83" t="s">
         <v>2290</v>
@@ -60278,16 +60471,16 @@
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1261" s="29" t="s">
-        <v>3138</v>
+        <v>3117</v>
       </c>
       <c r="B1261" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1261" s="83" t="s">
         <v>2386</v>
       </c>
       <c r="D1261" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1261" s="83" t="s">
         <v>2034</v>
@@ -60311,16 +60504,16 @@
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1262" s="29" t="s">
-        <v>3139</v>
+        <v>3118</v>
       </c>
       <c r="B1262" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1262" s="83" t="s">
         <v>2282</v>
       </c>
       <c r="D1262" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1262" s="83" t="s">
         <v>2291</v>
@@ -60344,16 +60537,16 @@
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1263" s="29" t="s">
-        <v>3140</v>
+        <v>3119</v>
       </c>
       <c r="B1263" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1263" s="83" t="s">
         <v>2283</v>
       </c>
       <c r="D1263" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1263" s="83" t="s">
         <v>2292</v>
@@ -60377,16 +60570,16 @@
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1264" s="29" t="s">
-        <v>3141</v>
+        <v>3120</v>
       </c>
       <c r="B1264" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1264" s="83" t="s">
         <v>2284</v>
       </c>
       <c r="D1264" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1264" s="83" t="s">
         <v>2265</v>
@@ -60410,16 +60603,16 @@
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1265" s="29" t="s">
-        <v>3142</v>
+        <v>3121</v>
       </c>
       <c r="B1265" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1265" s="83" t="s">
         <v>2387</v>
       </c>
       <c r="D1265" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1265" s="83" t="s">
         <v>2293</v>
@@ -60443,16 +60636,16 @@
     </row>
     <row r="1266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1266" s="29" t="s">
-        <v>3143</v>
+        <v>3122</v>
       </c>
       <c r="B1266" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1266" s="83" t="s">
         <v>1847</v>
       </c>
       <c r="D1266" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1266" s="83" t="s">
         <v>1849</v>
@@ -60476,16 +60669,16 @@
     </row>
     <row r="1267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1267" s="29" t="s">
-        <v>3144</v>
+        <v>3123</v>
       </c>
       <c r="B1267" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1267" s="83" t="s">
         <v>2267</v>
       </c>
       <c r="D1267" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1267" s="83" t="s">
         <v>1968</v>
@@ -60509,16 +60702,16 @@
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1268" s="29" t="s">
-        <v>3145</v>
+        <v>3124</v>
       </c>
       <c r="B1268" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1268" s="83" t="s">
         <v>1854</v>
       </c>
       <c r="D1268" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1268" s="83" t="s">
         <v>1851</v>
@@ -60542,16 +60735,16 @@
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1269" s="29" t="s">
-        <v>3146</v>
+        <v>3125</v>
       </c>
       <c r="B1269" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1269" s="83" t="s">
         <v>1855</v>
       </c>
       <c r="D1269" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1269" s="83" t="s">
         <v>1850</v>
@@ -60575,16 +60768,16 @@
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1270" s="29" t="s">
-        <v>3147</v>
+        <v>3126</v>
       </c>
       <c r="B1270" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1270" s="83" t="s">
         <v>2264</v>
       </c>
       <c r="D1270" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1270" s="83" t="s">
         <v>2294</v>
@@ -60608,16 +60801,16 @@
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1271" s="29" t="s">
-        <v>3148</v>
+        <v>3127</v>
       </c>
       <c r="B1271" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1271" s="83" t="s">
         <v>2263</v>
       </c>
       <c r="D1271" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1271" s="83" t="s">
         <v>2383</v>
@@ -60641,16 +60834,16 @@
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1272" s="29" t="s">
-        <v>3149</v>
+        <v>3128</v>
       </c>
       <c r="B1272" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1272" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1272" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1272" s="83" t="s">
         <v>1857</v>
@@ -60674,16 +60867,16 @@
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1273" s="29" t="s">
-        <v>3150</v>
+        <v>3129</v>
       </c>
       <c r="B1273" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1273" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1273" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1273" s="83" t="s">
         <v>2395</v>
@@ -60707,16 +60900,16 @@
     </row>
     <row r="1274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1274" s="29" t="s">
-        <v>3151</v>
+        <v>3130</v>
       </c>
       <c r="B1274" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1274" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1274" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1274" s="83" t="s">
         <v>2396</v>
@@ -60740,16 +60933,16 @@
     </row>
     <row r="1275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1275" s="29" t="s">
-        <v>3152</v>
+        <v>3131</v>
       </c>
       <c r="B1275" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1275" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1275" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1275" s="83" t="s">
         <v>2397</v>
@@ -60773,16 +60966,16 @@
     </row>
     <row r="1276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1276" s="29" t="s">
-        <v>3153</v>
+        <v>3132</v>
       </c>
       <c r="B1276" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1276" s="83" t="s">
         <v>2391</v>
       </c>
       <c r="D1276" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1276" s="83" t="s">
         <v>2398</v>
@@ -60806,16 +60999,16 @@
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1277" s="29" t="s">
-        <v>3154</v>
+        <v>3133</v>
       </c>
       <c r="B1277" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1277" s="83" t="s">
         <v>2392</v>
       </c>
       <c r="D1277" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1277" s="83" t="s">
         <v>2399</v>
@@ -60839,16 +61032,16 @@
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1278" s="29" t="s">
-        <v>3155</v>
+        <v>3134</v>
       </c>
       <c r="B1278" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1278" s="83" t="s">
         <v>2393</v>
       </c>
       <c r="D1278" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1278" s="83" t="s">
         <v>2400</v>
@@ -60872,16 +61065,16 @@
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1279" s="29" t="s">
-        <v>3156</v>
+        <v>3135</v>
       </c>
       <c r="B1279" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="C1279" s="83" t="s">
         <v>2394</v>
       </c>
       <c r="D1279" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1279" s="83" t="s">
         <v>2401</v>
@@ -60905,7 +61098,7 @@
     </row>
     <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1280" s="128" t="s">
-        <v>3157</v>
+        <v>3136</v>
       </c>
       <c r="B1280" s="100" t="s">
         <v>242</v>
@@ -60914,7 +61107,7 @@
         <v>1263</v>
       </c>
       <c r="D1280" s="100" t="s">
-        <v>3130</v>
+        <v>3109</v>
       </c>
       <c r="E1280" s="83" t="s">
         <v>2394</v>
@@ -60926,459 +61119,823 @@
         <v>1478</v>
       </c>
       <c r="H1280" s="128" t="s">
-        <v>3060</v>
+        <v>3039</v>
       </c>
       <c r="I1280" s="129" t="s">
         <v>60</v>
       </c>
       <c r="J1280" s="130" t="s">
-        <v>3158</v>
+        <v>3137</v>
       </c>
       <c r="K1280" s="128"/>
       <c r="L1280" s="83"/>
       <c r="M1280" s="128"/>
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1281" s="29"/>
-      <c r="B1281" s="100"/>
-      <c r="C1281" s="83"/>
-      <c r="D1281" s="85"/>
-      <c r="E1281" s="83"/>
-      <c r="F1281" s="31"/>
-      <c r="G1281" s="31"/>
-      <c r="H1281" s="29"/>
-      <c r="I1281" s="119"/>
+      <c r="A1281" s="29" t="s">
+        <v>3153</v>
+      </c>
+      <c r="B1281" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1281" s="83" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D1281" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1281" s="132" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F1281" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1281" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1281" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1281" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1281" s="29"/>
       <c r="K1281" s="29"/>
       <c r="L1281" s="31"/>
       <c r="M1281" s="29"/>
     </row>
     <row r="1282" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1282" s="29"/>
-      <c r="B1282" s="100"/>
-      <c r="C1282" s="83"/>
-      <c r="D1282" s="85"/>
-      <c r="E1282" s="83"/>
-      <c r="F1282" s="31"/>
-      <c r="G1282" s="31"/>
-      <c r="H1282" s="29"/>
-      <c r="I1282" s="119"/>
+      <c r="A1282" s="29" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B1282" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1282" s="83" t="s">
+        <v>2287</v>
+      </c>
+      <c r="D1282" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1282" s="83" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F1282" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1282" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1282" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1282" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1282" s="29"/>
       <c r="K1282" s="29"/>
       <c r="L1282" s="31"/>
       <c r="M1282" s="29"/>
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1283" s="29"/>
-      <c r="B1283" s="100"/>
-      <c r="C1283" s="83"/>
-      <c r="D1283" s="85"/>
-      <c r="E1283" s="83"/>
-      <c r="F1283" s="31"/>
-      <c r="G1283" s="31"/>
-      <c r="H1283" s="29"/>
-      <c r="I1283" s="119"/>
+      <c r="A1283" s="29" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B1283" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1283" s="83" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D1283" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1283" s="83" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F1283" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1283" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1283" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1283" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1283" s="29"/>
       <c r="K1283" s="29"/>
       <c r="L1283" s="31"/>
       <c r="M1283" s="29"/>
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1284" s="29"/>
-      <c r="B1284" s="100"/>
-      <c r="C1284" s="83"/>
-      <c r="D1284" s="85"/>
-      <c r="E1284" s="83"/>
-      <c r="F1284" s="31"/>
-      <c r="G1284" s="31"/>
-      <c r="H1284" s="29"/>
-      <c r="I1284" s="119"/>
+      <c r="A1284" s="29" t="s">
+        <v>3156</v>
+      </c>
+      <c r="B1284" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1284" s="83" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D1284" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1284" s="132" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F1284" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1284" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1284" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1284" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1284" s="29"/>
       <c r="K1284" s="29"/>
       <c r="L1284" s="31"/>
       <c r="M1284" s="29"/>
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1285" s="29"/>
-      <c r="B1285" s="100"/>
-      <c r="C1285" s="83"/>
-      <c r="D1285" s="85"/>
-      <c r="E1285" s="83"/>
-      <c r="F1285" s="31"/>
-      <c r="G1285" s="31"/>
-      <c r="H1285" s="29"/>
-      <c r="I1285" s="119"/>
+      <c r="A1285" s="29" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B1285" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1285" s="83" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D1285" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1285" s="83" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F1285" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1285" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1285" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1285" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1285" s="29"/>
       <c r="K1285" s="29"/>
       <c r="L1285" s="31"/>
       <c r="M1285" s="29"/>
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1286" s="29"/>
-      <c r="B1286" s="100"/>
-      <c r="C1286" s="83"/>
-      <c r="D1286" s="85"/>
-      <c r="E1286" s="83"/>
-      <c r="F1286" s="31"/>
-      <c r="G1286" s="31"/>
-      <c r="H1286" s="29"/>
-      <c r="I1286" s="119"/>
+      <c r="A1286" s="29" t="s">
+        <v>3158</v>
+      </c>
+      <c r="B1286" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1286" s="83" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D1286" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1286" s="83" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F1286" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1286" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1286" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1286" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1286" s="29"/>
       <c r="K1286" s="29"/>
       <c r="L1286" s="31"/>
       <c r="M1286" s="29"/>
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1287" s="29"/>
-      <c r="B1287" s="100"/>
-      <c r="C1287" s="83"/>
-      <c r="D1287" s="85"/>
-      <c r="E1287" s="83"/>
-      <c r="F1287" s="31"/>
-      <c r="G1287" s="31"/>
-      <c r="H1287" s="29"/>
-      <c r="I1287" s="119"/>
+      <c r="A1287" s="29" t="s">
+        <v>3159</v>
+      </c>
+      <c r="B1287" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1287" s="83" t="s">
+        <v>2282</v>
+      </c>
+      <c r="D1287" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1287" s="132" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F1287" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1287" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1287" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1287" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1287" s="29"/>
       <c r="K1287" s="29"/>
       <c r="L1287" s="31"/>
       <c r="M1287" s="29"/>
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1288" s="29"/>
-      <c r="B1288" s="100"/>
-      <c r="C1288" s="83"/>
-      <c r="D1288" s="85"/>
-      <c r="E1288" s="83"/>
-      <c r="F1288" s="31"/>
-      <c r="G1288" s="31"/>
-      <c r="H1288" s="29"/>
-      <c r="I1288" s="119"/>
+      <c r="A1288" s="29" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1288" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1288" s="83" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D1288" s="97" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1288" s="83" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F1288" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1288" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1288" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="I1288" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1288" s="29"/>
       <c r="K1288" s="29"/>
       <c r="L1288" s="31"/>
       <c r="M1288" s="29"/>
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1289" s="29"/>
-      <c r="B1289" s="100"/>
-      <c r="C1289" s="83"/>
+      <c r="A1289" s="29" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B1289" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1289" s="83" t="s">
+        <v>2284</v>
+      </c>
       <c r="D1289" s="85"/>
       <c r="E1289" s="83"/>
       <c r="F1289" s="31"/>
       <c r="G1289" s="31"/>
       <c r="H1289" s="29"/>
       <c r="I1289" s="119"/>
-      <c r="J1289" s="29"/>
+      <c r="J1289" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1289" s="29"/>
       <c r="L1289" s="31"/>
       <c r="M1289" s="29"/>
     </row>
     <row r="1290" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1290" s="29"/>
-      <c r="B1290" s="100"/>
-      <c r="C1290" s="83"/>
+      <c r="A1290" s="29" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B1290" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1290" s="83" t="s">
+        <v>2387</v>
+      </c>
       <c r="D1290" s="85"/>
       <c r="E1290" s="83"/>
       <c r="F1290" s="31"/>
       <c r="G1290" s="31"/>
       <c r="H1290" s="29"/>
       <c r="I1290" s="119"/>
-      <c r="J1290" s="29"/>
+      <c r="J1290" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1290" s="29"/>
       <c r="L1290" s="31"/>
       <c r="M1290" s="29"/>
     </row>
     <row r="1291" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1291" s="29"/>
-      <c r="B1291" s="100"/>
-      <c r="C1291" s="83"/>
+      <c r="A1291" s="29" t="s">
+        <v>3163</v>
+      </c>
+      <c r="B1291" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1291" s="83" t="s">
+        <v>1847</v>
+      </c>
       <c r="D1291" s="85"/>
       <c r="E1291" s="83"/>
       <c r="F1291" s="31"/>
       <c r="G1291" s="31"/>
       <c r="H1291" s="29"/>
       <c r="I1291" s="119"/>
-      <c r="J1291" s="29"/>
+      <c r="J1291" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1291" s="29"/>
       <c r="L1291" s="31"/>
       <c r="M1291" s="29"/>
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1292" s="29"/>
-      <c r="B1292" s="100"/>
-      <c r="C1292" s="83"/>
+      <c r="A1292" s="29" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1292" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1292" s="83" t="s">
+        <v>2267</v>
+      </c>
       <c r="D1292" s="85"/>
       <c r="E1292" s="83"/>
       <c r="F1292" s="31"/>
       <c r="G1292" s="31"/>
       <c r="H1292" s="29"/>
       <c r="I1292" s="119"/>
-      <c r="J1292" s="29"/>
+      <c r="J1292" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1292" s="29"/>
       <c r="L1292" s="31"/>
       <c r="M1292" s="29"/>
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1293" s="29"/>
-      <c r="B1293" s="100"/>
-      <c r="C1293" s="83"/>
+      <c r="A1293" s="29" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B1293" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1293" s="83" t="s">
+        <v>1854</v>
+      </c>
       <c r="D1293" s="85"/>
       <c r="E1293" s="83"/>
       <c r="F1293" s="31"/>
       <c r="G1293" s="31"/>
       <c r="H1293" s="29"/>
       <c r="I1293" s="119"/>
-      <c r="J1293" s="29"/>
+      <c r="J1293" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1293" s="29"/>
       <c r="L1293" s="31"/>
       <c r="M1293" s="29"/>
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1294" s="29"/>
-      <c r="B1294" s="100"/>
-      <c r="C1294" s="83"/>
+      <c r="A1294" s="29" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1294" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1294" s="83" t="s">
+        <v>1855</v>
+      </c>
       <c r="D1294" s="85"/>
       <c r="E1294" s="83"/>
       <c r="F1294" s="31"/>
       <c r="G1294" s="31"/>
       <c r="H1294" s="29"/>
       <c r="I1294" s="119"/>
-      <c r="J1294" s="29"/>
+      <c r="J1294" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1294" s="29"/>
       <c r="L1294" s="31"/>
       <c r="M1294" s="29"/>
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1295" s="29"/>
-      <c r="B1295" s="100"/>
-      <c r="C1295" s="83"/>
+      <c r="A1295" s="29" t="s">
+        <v>3167</v>
+      </c>
+      <c r="B1295" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1295" s="83" t="s">
+        <v>2264</v>
+      </c>
       <c r="D1295" s="85"/>
       <c r="E1295" s="83"/>
       <c r="F1295" s="31"/>
       <c r="G1295" s="31"/>
       <c r="H1295" s="29"/>
       <c r="I1295" s="119"/>
-      <c r="J1295" s="29"/>
+      <c r="J1295" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1295" s="29"/>
       <c r="L1295" s="31"/>
       <c r="M1295" s="29"/>
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1296" s="29"/>
-      <c r="B1296" s="100"/>
-      <c r="C1296" s="83"/>
+      <c r="A1296" s="29" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1296" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1296" s="83" t="s">
+        <v>2263</v>
+      </c>
       <c r="D1296" s="85"/>
       <c r="E1296" s="83"/>
       <c r="F1296" s="31"/>
       <c r="G1296" s="31"/>
       <c r="H1296" s="29"/>
       <c r="I1296" s="119"/>
-      <c r="J1296" s="29"/>
+      <c r="J1296" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1296" s="29"/>
       <c r="L1296" s="31"/>
       <c r="M1296" s="29"/>
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1297" s="29"/>
-      <c r="B1297" s="100"/>
-      <c r="C1297" s="83"/>
+      <c r="A1297" s="29" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B1297" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1297" s="83" t="s">
+        <v>1860</v>
+      </c>
       <c r="D1297" s="85"/>
       <c r="E1297" s="83"/>
       <c r="F1297" s="31"/>
       <c r="G1297" s="31"/>
       <c r="H1297" s="29"/>
       <c r="I1297" s="119"/>
-      <c r="J1297" s="29"/>
+      <c r="J1297" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1297" s="29"/>
       <c r="L1297" s="31"/>
       <c r="M1297" s="29"/>
     </row>
     <row r="1298" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1298" s="29"/>
-      <c r="B1298" s="100"/>
-      <c r="C1298" s="83"/>
+      <c r="A1298" s="29" t="s">
+        <v>3170</v>
+      </c>
+      <c r="B1298" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1298" s="83" t="s">
+        <v>2388</v>
+      </c>
       <c r="D1298" s="85"/>
       <c r="E1298" s="83"/>
       <c r="F1298" s="31"/>
       <c r="G1298" s="31"/>
       <c r="H1298" s="29"/>
       <c r="I1298" s="119"/>
-      <c r="J1298" s="29"/>
+      <c r="J1298" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1298" s="29"/>
       <c r="L1298" s="31"/>
       <c r="M1298" s="29"/>
     </row>
     <row r="1299" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1299" s="29"/>
-      <c r="B1299" s="100"/>
-      <c r="C1299" s="83"/>
+      <c r="A1299" s="29" t="s">
+        <v>3171</v>
+      </c>
+      <c r="B1299" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1299" s="83" t="s">
+        <v>2389</v>
+      </c>
       <c r="D1299" s="85"/>
       <c r="E1299" s="83"/>
       <c r="F1299" s="31"/>
       <c r="G1299" s="31"/>
       <c r="H1299" s="29"/>
       <c r="I1299" s="119"/>
-      <c r="J1299" s="29"/>
+      <c r="J1299" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1299" s="29"/>
       <c r="L1299" s="31"/>
       <c r="M1299" s="29"/>
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1300" s="29"/>
-      <c r="B1300" s="100"/>
-      <c r="C1300" s="83"/>
+      <c r="A1300" s="29" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1300" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1300" s="83" t="s">
+        <v>2390</v>
+      </c>
       <c r="D1300" s="85"/>
       <c r="E1300" s="83"/>
       <c r="F1300" s="31"/>
       <c r="G1300" s="31"/>
       <c r="H1300" s="29"/>
       <c r="I1300" s="119"/>
-      <c r="J1300" s="29"/>
+      <c r="J1300" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1300" s="29"/>
       <c r="L1300" s="31"/>
       <c r="M1300" s="29"/>
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1301" s="29"/>
-      <c r="B1301" s="100"/>
-      <c r="C1301" s="83"/>
+      <c r="A1301" s="29" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B1301" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1301" s="83" t="s">
+        <v>2391</v>
+      </c>
       <c r="D1301" s="85"/>
       <c r="E1301" s="83"/>
       <c r="F1301" s="31"/>
       <c r="G1301" s="31"/>
       <c r="H1301" s="29"/>
       <c r="I1301" s="119"/>
-      <c r="J1301" s="29"/>
+      <c r="J1301" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1301" s="29"/>
       <c r="L1301" s="31"/>
       <c r="M1301" s="29"/>
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1302" s="29"/>
-      <c r="B1302" s="100"/>
-      <c r="C1302" s="83"/>
+      <c r="A1302" s="29" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B1302" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1302" s="83" t="s">
+        <v>2392</v>
+      </c>
       <c r="D1302" s="85"/>
       <c r="E1302" s="83"/>
       <c r="F1302" s="31"/>
       <c r="G1302" s="31"/>
       <c r="H1302" s="29"/>
       <c r="I1302" s="119"/>
-      <c r="J1302" s="29"/>
+      <c r="J1302" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1302" s="29"/>
       <c r="L1302" s="31"/>
       <c r="M1302" s="29"/>
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1303" s="29"/>
-      <c r="B1303" s="100"/>
-      <c r="C1303" s="83"/>
+      <c r="A1303" s="29" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B1303" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1303" s="83" t="s">
+        <v>2393</v>
+      </c>
       <c r="D1303" s="85"/>
       <c r="E1303" s="83"/>
       <c r="F1303" s="31"/>
       <c r="G1303" s="31"/>
       <c r="H1303" s="29"/>
       <c r="I1303" s="119"/>
-      <c r="J1303" s="29"/>
+      <c r="J1303" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1303" s="29"/>
       <c r="L1303" s="31"/>
       <c r="M1303" s="29"/>
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1304" s="29"/>
-      <c r="B1304" s="100"/>
-      <c r="C1304" s="83"/>
+      <c r="A1304" s="29" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B1304" s="100" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1304" s="83" t="s">
+        <v>2394</v>
+      </c>
       <c r="D1304" s="85"/>
       <c r="E1304" s="83"/>
       <c r="F1304" s="31"/>
       <c r="G1304" s="31"/>
       <c r="H1304" s="29"/>
       <c r="I1304" s="119"/>
-      <c r="J1304" s="29"/>
+      <c r="J1304" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1304" s="29"/>
       <c r="L1304" s="31"/>
       <c r="M1304" s="29"/>
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1305" s="29"/>
-      <c r="B1305" s="100"/>
-      <c r="C1305" s="83"/>
-      <c r="D1305" s="85"/>
-      <c r="E1305" s="83"/>
-      <c r="F1305" s="31"/>
-      <c r="G1305" s="31"/>
-      <c r="H1305" s="29"/>
-      <c r="I1305" s="119"/>
+      <c r="A1305" s="29" t="s">
+        <v>3149</v>
+      </c>
+      <c r="B1305" s="100" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C1305" s="83" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D1305" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1305" s="83" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F1305" s="31" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1305" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1305" s="29" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I1305" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1305" s="29"/>
       <c r="K1305" s="29"/>
       <c r="L1305" s="31"/>
       <c r="M1305" s="29"/>
     </row>
     <row r="1306" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1306" s="29"/>
-      <c r="B1306" s="100"/>
-      <c r="C1306" s="83"/>
-      <c r="D1306" s="85"/>
-      <c r="E1306" s="83"/>
-      <c r="F1306" s="31"/>
-      <c r="G1306" s="31"/>
-      <c r="H1306" s="29"/>
-      <c r="I1306" s="119"/>
+      <c r="A1306" s="29" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B1306" s="100" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C1306" s="83" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D1306" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1306" s="83" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F1306" s="31" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1306" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1306" s="29" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I1306" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1306" s="29"/>
       <c r="K1306" s="29"/>
       <c r="L1306" s="31"/>
       <c r="M1306" s="29"/>
     </row>
     <row r="1307" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1307" s="29"/>
-      <c r="B1307" s="100"/>
-      <c r="C1307" s="83"/>
-      <c r="D1307" s="85"/>
-      <c r="E1307" s="83"/>
-      <c r="F1307" s="31"/>
-      <c r="G1307" s="31"/>
-      <c r="H1307" s="29"/>
-      <c r="I1307" s="119"/>
+      <c r="A1307" s="29" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B1307" s="100" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C1307" s="83" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D1307" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1307" s="83" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F1307" s="31" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1307" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1307" s="29" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I1307" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1307" s="29"/>
       <c r="K1307" s="29"/>
       <c r="L1307" s="31"/>
       <c r="M1307" s="29"/>
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1308" s="29"/>
-      <c r="B1308" s="100"/>
-      <c r="C1308" s="83"/>
-      <c r="D1308" s="85"/>
-      <c r="E1308" s="83"/>
-      <c r="F1308" s="31"/>
-      <c r="G1308" s="31"/>
-      <c r="H1308" s="29"/>
-      <c r="I1308" s="119"/>
+      <c r="A1308" s="29" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B1308" s="100" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C1308" s="83" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D1308" s="85" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1308" s="83" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F1308" s="31" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G1308" s="31" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H1308" s="29" t="s">
+        <v>1631</v>
+      </c>
+      <c r="I1308" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1308" s="29"/>
       <c r="K1308" s="29"/>
       <c r="L1308" s="31"/>
       <c r="M1308" s="29"/>
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1309" s="29"/>
-      <c r="B1309" s="100"/>
-      <c r="C1309" s="83"/>
+      <c r="A1309" s="29" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B1309" s="100" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C1309" s="83" t="s">
+        <v>2394</v>
+      </c>
       <c r="D1309" s="85"/>
       <c r="E1309" s="83"/>
       <c r="F1309" s="31"/>
       <c r="G1309" s="31"/>
       <c r="H1309" s="29"/>
-      <c r="I1309" s="119"/>
-      <c r="J1309" s="29"/>
+      <c r="I1309" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1309" s="29" t="s">
+        <v>439</v>
+      </c>
       <c r="K1309" s="29"/>
       <c r="L1309" s="31"/>
       <c r="M1309" s="29"/>
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1310" s="29"/>
-      <c r="B1310" s="100"/>
-      <c r="C1310" s="83"/>
-      <c r="D1310" s="85"/>
-      <c r="E1310" s="83"/>
+      <c r="A1310" s="29" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B1310" s="100" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C1310" s="83" t="s">
+        <v>3196</v>
+      </c>
+      <c r="D1310" s="85" t="s">
+        <v>3199</v>
+      </c>
+      <c r="E1310" s="83" t="s">
+        <v>3200</v>
+      </c>
       <c r="F1310" s="31"/>
       <c r="G1310" s="31"/>
       <c r="H1310" s="29"/>
@@ -61389,11 +61946,21 @@
       <c r="M1310" s="29"/>
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1311" s="29"/>
-      <c r="B1311" s="100"/>
-      <c r="C1311" s="83"/>
-      <c r="D1311" s="85"/>
-      <c r="E1311" s="83"/>
+      <c r="A1311" s="29" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B1311" s="100" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C1311" s="83" t="s">
+        <v>3197</v>
+      </c>
+      <c r="D1311" s="85" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E1311" s="83" t="s">
+        <v>3200</v>
+      </c>
       <c r="F1311" s="31"/>
       <c r="G1311" s="31"/>
       <c r="H1311" s="29"/>
@@ -61404,11 +61971,21 @@
       <c r="M1311" s="29"/>
     </row>
     <row r="1312" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1312" s="29"/>
-      <c r="B1312" s="100"/>
-      <c r="C1312" s="83"/>
-      <c r="D1312" s="85"/>
-      <c r="E1312" s="83"/>
+      <c r="A1312" s="29" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1312" s="85" t="s">
+        <v>3199</v>
+      </c>
+      <c r="C1312" s="83" t="s">
+        <v>3200</v>
+      </c>
+      <c r="D1312" s="85" t="s">
+        <v>3201</v>
+      </c>
+      <c r="E1312" s="83" t="s">
+        <v>3200</v>
+      </c>
       <c r="F1312" s="31"/>
       <c r="G1312" s="31"/>
       <c r="H1312" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6C1C5B-F13B-0249-A65E-3E7FB15E373B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60EF6A4-59A6-7F47-AE79-856850E2D07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8420" yWindow="1520" windowWidth="21820" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10793" uniqueCount="3205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10793" uniqueCount="3204">
   <si>
     <t>Tag</t>
   </si>
@@ -9470,9 +9470,6 @@
   <si>
     <t>Intended to be uplink from 2603-1200 to 2603-1203. 
 Not yet terminated.</t>
-  </si>
-  <si>
-    <t>2601-1200</t>
   </si>
   <si>
     <t>ZAHU-0001-F30</t>
@@ -55957,7 +55954,7 @@
         <v>1342</v>
       </c>
       <c r="E1127" s="83" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="F1127" s="31" t="s">
         <v>1651</v>
@@ -57083,7 +57080,7 @@
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1161" s="29" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="B1161" s="100" t="s">
         <v>2598</v>
@@ -57092,7 +57089,7 @@
         <v>2286</v>
       </c>
       <c r="D1161" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1161" s="83" t="s">
         <v>1247</v>
@@ -57110,7 +57107,7 @@
         <v>60</v>
       </c>
       <c r="J1161" s="29" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="K1161" s="29"/>
       <c r="L1161" s="31"/>
@@ -57118,7 +57115,7 @@
     </row>
     <row r="1162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1162" s="29" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B1162" s="100" t="s">
         <v>2598</v>
@@ -57127,7 +57124,7 @@
         <v>2287</v>
       </c>
       <c r="D1162" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1162" s="83" t="s">
         <v>1249</v>
@@ -57145,7 +57142,7 @@
         <v>60</v>
       </c>
       <c r="J1162" s="29" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="K1162" s="29"/>
       <c r="L1162" s="31"/>
@@ -57153,7 +57150,7 @@
     </row>
     <row r="1163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1163" s="29" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="B1163" s="100" t="s">
         <v>2598</v>
@@ -57162,7 +57159,7 @@
         <v>2288</v>
       </c>
       <c r="D1163" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1163" s="83" t="s">
         <v>1223</v>
@@ -57188,7 +57185,7 @@
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1164" s="29" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B1164" s="100" t="s">
         <v>2598</v>
@@ -57197,7 +57194,7 @@
         <v>2289</v>
       </c>
       <c r="D1164" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1164" s="83" t="s">
         <v>1225</v>
@@ -57223,7 +57220,7 @@
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1165" s="29" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="B1165" s="100" t="s">
         <v>2598</v>
@@ -57232,7 +57229,7 @@
         <v>2285</v>
       </c>
       <c r="D1165" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1165" s="83" t="s">
         <v>1227</v>
@@ -57250,7 +57247,7 @@
         <v>60</v>
       </c>
       <c r="J1165" s="29" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="K1165" s="29"/>
       <c r="L1165" s="31"/>
@@ -57258,7 +57255,7 @@
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1166" s="29" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B1166" s="100" t="s">
         <v>2598</v>
@@ -57267,7 +57264,7 @@
         <v>2386</v>
       </c>
       <c r="D1166" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1166" s="83" t="s">
         <v>1229</v>
@@ -57293,7 +57290,7 @@
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1167" s="29" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="B1167" s="100" t="s">
         <v>2598</v>
@@ -57302,7 +57299,7 @@
         <v>2282</v>
       </c>
       <c r="D1167" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1167" s="83" t="s">
         <v>1231</v>
@@ -57328,7 +57325,7 @@
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1168" s="29" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B1168" s="100" t="s">
         <v>2598</v>
@@ -57337,7 +57334,7 @@
         <v>2283</v>
       </c>
       <c r="D1168" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1168" s="83" t="s">
         <v>1256</v>
@@ -57363,7 +57360,7 @@
     </row>
     <row r="1169" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="29" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="B1169" s="100" t="s">
         <v>2598</v>
@@ -57372,7 +57369,7 @@
         <v>2284</v>
       </c>
       <c r="D1169" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1169" s="83" t="s">
         <v>1258</v>
@@ -57398,7 +57395,7 @@
     </row>
     <row r="1170" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="29" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="B1170" s="100" t="s">
         <v>2598</v>
@@ -57407,7 +57404,7 @@
         <v>2387</v>
       </c>
       <c r="D1170" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1170" s="82" t="s">
         <v>1260</v>
@@ -57433,7 +57430,7 @@
     </row>
     <row r="1171" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="29" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B1171" s="100" t="s">
         <v>2598</v>
@@ -57442,7 +57439,7 @@
         <v>1847</v>
       </c>
       <c r="D1171" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1171" s="83" t="s">
         <v>1262</v>
@@ -57468,7 +57465,7 @@
     </row>
     <row r="1172" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="29" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B1172" s="100" t="s">
         <v>2598</v>
@@ -57477,7 +57474,7 @@
         <v>2267</v>
       </c>
       <c r="D1172" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1172" s="82" t="s">
         <v>1264</v>
@@ -57495,7 +57492,7 @@
         <v>60</v>
       </c>
       <c r="J1172" s="29" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="K1172" s="29"/>
       <c r="L1172" s="31"/>
@@ -57503,7 +57500,7 @@
     </row>
     <row r="1173" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="29" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B1173" s="100" t="s">
         <v>2598</v>
@@ -57512,7 +57509,7 @@
         <v>1854</v>
       </c>
       <c r="D1173" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1173" s="83" t="s">
         <v>1291</v>
@@ -57538,7 +57535,7 @@
     </row>
     <row r="1174" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B1174" s="100" t="s">
         <v>2598</v>
@@ -57547,7 +57544,7 @@
         <v>1855</v>
       </c>
       <c r="D1174" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1174" s="82" t="s">
         <v>1293</v>
@@ -57573,7 +57570,7 @@
     </row>
     <row r="1175" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="29" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B1175" s="100" t="s">
         <v>2598</v>
@@ -57582,7 +57579,7 @@
         <v>2264</v>
       </c>
       <c r="D1175" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1175" s="83" t="s">
         <v>1295</v>
@@ -57600,7 +57597,7 @@
         <v>60</v>
       </c>
       <c r="J1175" s="29" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="K1175" s="29"/>
       <c r="L1175" s="31"/>
@@ -57608,7 +57605,7 @@
     </row>
     <row r="1176" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B1176" s="100" t="s">
         <v>2598</v>
@@ -57617,7 +57614,7 @@
         <v>2263</v>
       </c>
       <c r="D1176" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1176" s="82" t="s">
         <v>1297</v>
@@ -57643,7 +57640,7 @@
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B1177" s="100" t="s">
         <v>2598</v>
@@ -57652,7 +57649,7 @@
         <v>1860</v>
       </c>
       <c r="D1177" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1177" s="83" t="s">
         <v>1299</v>
@@ -61133,16 +61130,16 @@
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1281" s="29" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B1281" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1281" s="83" t="s">
         <v>2286</v>
       </c>
-      <c r="D1281" s="97" t="s">
-        <v>3142</v>
+      <c r="D1281" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1281" s="132" t="s">
         <v>1246</v>
@@ -61166,16 +61163,16 @@
     </row>
     <row r="1282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1282" s="29" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="B1282" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1282" s="83" t="s">
         <v>2287</v>
       </c>
-      <c r="D1282" s="97" t="s">
-        <v>3142</v>
+      <c r="D1282" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1282" s="83" t="s">
         <v>1248</v>
@@ -61199,16 +61196,16 @@
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1283" s="29" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B1283" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1283" s="83" t="s">
         <v>2288</v>
       </c>
-      <c r="D1283" s="97" t="s">
-        <v>3142</v>
+      <c r="D1283" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1283" s="83" t="s">
         <v>1222</v>
@@ -61232,16 +61229,16 @@
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1284" s="29" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B1284" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1284" s="83" t="s">
         <v>2289</v>
       </c>
-      <c r="D1284" s="97" t="s">
-        <v>3142</v>
+      <c r="D1284" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1284" s="132" t="s">
         <v>1224</v>
@@ -61265,16 +61262,16 @@
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1285" s="29" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B1285" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1285" s="83" t="s">
         <v>2285</v>
       </c>
-      <c r="D1285" s="97" t="s">
-        <v>3142</v>
+      <c r="D1285" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1285" s="83" t="s">
         <v>1226</v>
@@ -61298,16 +61295,16 @@
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1286" s="29" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="B1286" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1286" s="83" t="s">
         <v>2386</v>
       </c>
-      <c r="D1286" s="97" t="s">
-        <v>3142</v>
+      <c r="D1286" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1286" s="83" t="s">
         <v>1228</v>
@@ -61331,16 +61328,16 @@
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1287" s="29" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="B1287" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1287" s="83" t="s">
         <v>2282</v>
       </c>
-      <c r="D1287" s="97" t="s">
-        <v>3142</v>
+      <c r="D1287" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1287" s="132" t="s">
         <v>1230</v>
@@ -61364,16 +61361,16 @@
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1288" s="29" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="B1288" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1288" s="83" t="s">
         <v>2283</v>
       </c>
-      <c r="D1288" s="97" t="s">
-        <v>3142</v>
+      <c r="D1288" s="85" t="s">
+        <v>1674</v>
       </c>
       <c r="E1288" s="83" t="s">
         <v>1232</v>
@@ -61397,10 +61394,10 @@
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1289" s="29" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="B1289" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1289" s="83" t="s">
         <v>2284</v>
@@ -61420,10 +61417,10 @@
     </row>
     <row r="1290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1290" s="29" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="B1290" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1290" s="83" t="s">
         <v>2387</v>
@@ -61443,10 +61440,10 @@
     </row>
     <row r="1291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1291" s="29" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="B1291" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1291" s="83" t="s">
         <v>1847</v>
@@ -61466,10 +61463,10 @@
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1292" s="29" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B1292" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1292" s="83" t="s">
         <v>2267</v>
@@ -61489,10 +61486,10 @@
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1293" s="29" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="B1293" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1293" s="83" t="s">
         <v>1854</v>
@@ -61512,10 +61509,10 @@
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1294" s="29" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="B1294" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1294" s="83" t="s">
         <v>1855</v>
@@ -61535,10 +61532,10 @@
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1295" s="29" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="B1295" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1295" s="83" t="s">
         <v>2264</v>
@@ -61558,10 +61555,10 @@
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1296" s="29" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B1296" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1296" s="83" t="s">
         <v>2263</v>
@@ -61581,10 +61578,10 @@
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1297" s="29" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="B1297" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1297" s="83" t="s">
         <v>1860</v>
@@ -61604,10 +61601,10 @@
     </row>
     <row r="1298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1298" s="29" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="B1298" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1298" s="83" t="s">
         <v>2388</v>
@@ -61627,10 +61624,10 @@
     </row>
     <row r="1299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1299" s="29" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="B1299" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1299" s="83" t="s">
         <v>2389</v>
@@ -61650,10 +61647,10 @@
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1300" s="29" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="B1300" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1300" s="83" t="s">
         <v>2390</v>
@@ -61673,10 +61670,10 @@
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1301" s="29" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="B1301" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1301" s="83" t="s">
         <v>2391</v>
@@ -61696,10 +61693,10 @@
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1302" s="29" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B1302" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1302" s="83" t="s">
         <v>2392</v>
@@ -61719,10 +61716,10 @@
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1303" s="29" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="B1303" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1303" s="83" t="s">
         <v>2393</v>
@@ -61742,10 +61739,10 @@
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1304" s="29" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B1304" s="100" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="C1304" s="83" t="s">
         <v>2394</v>
@@ -61765,7 +61762,7 @@
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1305" s="29" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="B1305" s="100" t="s">
         <v>2598</v>
@@ -61774,7 +61771,7 @@
         <v>2388</v>
       </c>
       <c r="D1305" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1305" s="83" t="s">
         <v>1301</v>
@@ -61798,7 +61795,7 @@
     </row>
     <row r="1306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1306" s="29" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="B1306" s="100" t="s">
         <v>2598</v>
@@ -61807,7 +61804,7 @@
         <v>2389</v>
       </c>
       <c r="D1306" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1306" s="83" t="s">
         <v>1303</v>
@@ -61831,7 +61828,7 @@
     </row>
     <row r="1307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1307" s="29" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B1307" s="100" t="s">
         <v>2598</v>
@@ -61840,7 +61837,7 @@
         <v>2390</v>
       </c>
       <c r="D1307" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1307" s="83" t="s">
         <v>1305</v>
@@ -61864,7 +61861,7 @@
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1308" s="29" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B1308" s="100" t="s">
         <v>2598</v>
@@ -61873,7 +61870,7 @@
         <v>2391</v>
       </c>
       <c r="D1308" s="85" t="s">
-        <v>3142</v>
+        <v>1674</v>
       </c>
       <c r="E1308" s="83" t="s">
         <v>1280</v>
@@ -61897,7 +61894,7 @@
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1309" s="29" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="B1309" s="100" t="s">
         <v>2598</v>
@@ -61922,19 +61919,19 @@
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1310" s="29" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B1310" s="100" t="s">
         <v>1342</v>
       </c>
       <c r="C1310" s="83" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="D1310" s="85" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E1310" s="83" t="s">
         <v>3199</v>
-      </c>
-      <c r="E1310" s="83" t="s">
-        <v>3200</v>
       </c>
       <c r="F1310" s="31"/>
       <c r="G1310" s="31"/>
@@ -61947,19 +61944,19 @@
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1311" s="29" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B1311" s="100" t="s">
         <v>1342</v>
       </c>
       <c r="C1311" s="83" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="D1311" s="85" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="E1311" s="83" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="F1311" s="31"/>
       <c r="G1311" s="31"/>
@@ -61972,19 +61969,19 @@
     </row>
     <row r="1312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1312" s="29" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B1312" s="85" t="s">
+        <v>3198</v>
+      </c>
+      <c r="C1312" s="83" t="s">
         <v>3199</v>
       </c>
-      <c r="C1312" s="83" t="s">
+      <c r="D1312" s="85" t="s">
         <v>3200</v>
       </c>
-      <c r="D1312" s="85" t="s">
-        <v>3201</v>
-      </c>
       <c r="E1312" s="83" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="F1312" s="31"/>
       <c r="G1312" s="31"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6912888F-FCB2-1349-93EF-DB73BD8D23D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0638DE10-C301-5B47-B85E-F2A46D486308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10793" uniqueCount="3204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10815" uniqueCount="3212">
   <si>
     <t>Tag</t>
   </si>
@@ -9656,6 +9656,30 @@
   </si>
   <si>
     <t>notag1312</t>
+  </si>
+  <si>
+    <t>2606-1600</t>
+  </si>
+  <si>
+    <t>sdi_5</t>
+  </si>
+  <si>
+    <t>2nd stage display layout</t>
+  </si>
+  <si>
+    <t>avshop #461859</t>
+  </si>
+  <si>
+    <t>rack internal</t>
+  </si>
+  <si>
+    <t>rt1314</t>
+  </si>
+  <si>
+    <t>bmd</t>
+  </si>
+  <si>
+    <t>managed via videohubControl</t>
   </si>
 </sst>
 </file>
@@ -61971,7 +61995,7 @@
       <c r="L1311" s="31"/>
       <c r="M1311" s="29"/>
     </row>
-    <row r="1312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1312" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="29" t="s">
         <v>3203</v>
       </c>
@@ -61996,33 +62020,79 @@
       <c r="L1312" s="31"/>
       <c r="M1312" s="29"/>
     </row>
-    <row r="1313" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1313" s="29"/>
-      <c r="B1313" s="100"/>
-      <c r="C1313" s="83"/>
-      <c r="D1313" s="85"/>
-      <c r="E1313" s="83"/>
-      <c r="F1313" s="31"/>
-      <c r="G1313" s="31"/>
-      <c r="H1313" s="29"/>
-      <c r="I1313" s="119"/>
-      <c r="J1313" s="29"/>
+    <row r="1313" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A1313" s="29" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B1313" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1313" s="82" t="s">
+        <v>3205</v>
+      </c>
+      <c r="D1313" s="100" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E1313" s="83" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F1313" s="31" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G1313" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1313" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="I1313" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1313" s="29" t="s">
+        <v>3206</v>
+      </c>
       <c r="K1313" s="29"/>
-      <c r="L1313" s="31"/>
-      <c r="M1313" s="29"/>
+      <c r="L1313" s="31" t="s">
+        <v>3207</v>
+      </c>
+      <c r="M1313" s="29" t="s">
+        <v>3208</v>
+      </c>
     </row>
     <row r="1314" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1314" s="29"/>
-      <c r="B1314" s="100"/>
-      <c r="C1314" s="83"/>
-      <c r="D1314" s="85"/>
-      <c r="E1314" s="83"/>
-      <c r="F1314" s="31"/>
-      <c r="G1314" s="31"/>
-      <c r="H1314" s="29"/>
-      <c r="I1314" s="119"/>
-      <c r="J1314" s="29"/>
-      <c r="K1314" s="29"/>
+      <c r="A1314" s="29" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B1314" s="100" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C1314" s="83" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D1314" s="85" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E1314" s="83" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F1314" s="31" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G1314" s="31" t="s">
+        <v>3210</v>
+      </c>
+      <c r="H1314" s="29">
+        <v>0</v>
+      </c>
+      <c r="I1314" s="119" t="s">
+        <v>503</v>
+      </c>
+      <c r="J1314" s="29" t="s">
+        <v>3206</v>
+      </c>
+      <c r="K1314" s="29" t="s">
+        <v>3211</v>
+      </c>
       <c r="L1314" s="31"/>
       <c r="M1314" s="29"/>
     </row>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0638DE10-C301-5B47-B85E-F2A46D486308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51417865-EB53-8945-9043-F35BE07336BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -62034,7 +62034,7 @@
         <v>1050</v>
       </c>
       <c r="E1313" s="83" t="s">
-        <v>2229</v>
+        <v>347</v>
       </c>
       <c r="F1313" s="31" t="s">
         <v>1552</v>
@@ -62067,7 +62067,7 @@
         <v>1050</v>
       </c>
       <c r="C1314" s="83" t="s">
-        <v>2229</v>
+        <v>347</v>
       </c>
       <c r="D1314" s="85" t="s">
         <v>1050</v>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51417865-EB53-8945-9043-F35BE07336BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3910016-601A-EF46-A60E-F7664B5C9F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3910016-601A-EF46-A60E-F7664B5C9F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826982F7-618A-5D47-8771-4EECE83FE050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10815" uniqueCount="3212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10805" uniqueCount="3210">
   <si>
     <t>Tag</t>
   </si>
@@ -7706,15 +7706,6 @@
   </si>
   <si>
     <t>notag1124</t>
-  </si>
-  <si>
-    <t>Dante DAW</t>
-  </si>
-  <si>
-    <t>indirect via two patch panels</t>
-  </si>
-  <si>
-    <t>notag1125</t>
   </si>
   <si>
     <t>notag1126</t>
@@ -9680,6 +9671,9 @@
   </si>
   <si>
     <t>managed via videohubControl</t>
+  </si>
+  <si>
+    <t>unused1128</t>
   </si>
 </sst>
 </file>
@@ -10106,7 +10100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10360,10 +10354,6 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19231,7 +19221,70 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19464,69 +19517,6 @@
     </i>
     <i>
       <x v="53"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Tag" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{331FD294-EE6F-3D4E-A534-813A4D9D566E}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E5:F10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -19935,7 +19925,7 @@
         <v>733</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>3058</v>
+        <v>3055</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>19</v>
@@ -19972,7 +19962,7 @@
         <v>733</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>3058</v>
+        <v>3055</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>19</v>
@@ -20009,7 +19999,7 @@
         <v>733</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>3059</v>
+        <v>3056</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>19</v>
@@ -20030,7 +20020,7 @@
         <v>60</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>3065</v>
+        <v>3062</v>
       </c>
       <c r="K4" s="19" t="s">
         <v>277</v>
@@ -20046,7 +20036,7 @@
         <v>733</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>3060</v>
+        <v>3057</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>19</v>
@@ -20067,7 +20057,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>3066</v>
+        <v>3063</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>279</v>
@@ -20083,7 +20073,7 @@
         <v>733</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>19</v>
@@ -20104,7 +20094,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
       <c r="K6" s="19" t="s">
         <v>280</v>
@@ -20120,7 +20110,7 @@
         <v>733</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>19</v>
@@ -20141,7 +20131,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>282</v>
@@ -20186,7 +20176,7 @@
         <v>733</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="D9" s="103" t="s">
         <v>19</v>
@@ -20207,7 +20197,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>284</v>
@@ -20254,7 +20244,7 @@
         <v>733</v>
       </c>
       <c r="E11" s="104" t="s">
-        <v>3064</v>
+        <v>3061</v>
       </c>
       <c r="F11" s="102" t="s">
         <v>1550</v>
@@ -20269,7 +20259,7 @@
         <v>60</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>3070</v>
+        <v>3067</v>
       </c>
       <c r="K11" s="23" t="s">
         <v>285</v>
@@ -20279,10 +20269,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>3071</v>
+        <v>3068</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>3072</v>
+        <v>3069</v>
       </c>
       <c r="C12" s="91" t="s">
         <v>52</v>
@@ -20300,7 +20290,7 @@
         <v>52</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>3073</v>
+        <v>3070</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>503</v>
@@ -20314,13 +20304,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>3074</v>
+        <v>3071</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>263</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>3076</v>
+        <v>3073</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>72</v>
@@ -20332,14 +20322,14 @@
         <v>176</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23" t="s">
         <v>503</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>3075</v>
+        <v>3072</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -20353,7 +20343,7 @@
         <v>263</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>3077</v>
+        <v>3074</v>
       </c>
       <c r="D14" s="22" t="s">
         <v>65</v>
@@ -20365,7 +20355,7 @@
         <v>176</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="H14" s="23"/>
       <c r="I14" s="23" t="s">
@@ -20386,7 +20376,7 @@
         <v>263</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>3078</v>
+        <v>3075</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>66</v>
@@ -20398,14 +20388,14 @@
         <v>176</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="H15" s="29"/>
       <c r="I15" s="23" t="s">
         <v>503</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>3081</v>
+        <v>3078</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -20419,7 +20409,7 @@
         <v>263</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="D16" s="22" t="s">
         <v>67</v>
@@ -20431,7 +20421,7 @@
         <v>176</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="23" t="s">
@@ -20446,32 +20436,32 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>53</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>3084</v>
+        <v>3081</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>2254</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>3082</v>
+        <v>3079</v>
       </c>
       <c r="F17" s="23" t="s">
         <v>1550</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>3085</v>
+        <v>3082</v>
       </c>
       <c r="H17" s="29"/>
       <c r="I17" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>3086</v>
+        <v>3083</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -20936,7 +20926,7 @@
         <v>147</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>193</v>
@@ -20954,7 +20944,7 @@
         <v>96</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>3031</v>
+        <v>3028</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>113</v>
@@ -22677,7 +22667,7 @@
         <v>60</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>2962</v>
+        <v>2959</v>
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
@@ -22758,7 +22748,7 @@
         <v>60</v>
       </c>
       <c r="J92" s="23" t="s">
-        <v>2595</v>
+        <v>2592</v>
       </c>
       <c r="K92" s="23"/>
       <c r="L92" s="19"/>
@@ -22986,7 +22976,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>53</v>
@@ -23215,7 +23205,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="B108" s="22" t="s">
         <v>223</v>
@@ -23224,7 +23214,7 @@
         <v>133</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>2998</v>
+        <v>2995</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>133</v>
@@ -23308,7 +23298,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>2820</v>
+        <v>2817</v>
       </c>
       <c r="B111" s="22" t="s">
         <v>239</v>
@@ -23405,7 +23395,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>2821</v>
+        <v>2818</v>
       </c>
       <c r="B114" s="22" t="s">
         <v>242</v>
@@ -23438,7 +23428,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
-        <v>2822</v>
+        <v>2819</v>
       </c>
       <c r="B115" s="22" t="s">
         <v>242</v>
@@ -23467,7 +23457,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
       <c r="B116" s="22" t="s">
         <v>242</v>
@@ -23496,7 +23486,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
       <c r="B117" s="22" t="s">
         <v>260</v>
@@ -23523,7 +23513,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
       <c r="B118" s="22" t="s">
         <v>262</v>
@@ -23554,27 +23544,27 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
-        <v>3090</v>
+        <v>3087</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
       <c r="F119" s="23" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
       <c r="G119" s="23" t="s">
         <v>52</v>
       </c>
       <c r="H119" s="23" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="I119" s="23"/>
       <c r="J119" s="23" t="s">
         <v>439</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>3092</v>
+        <v>3089</v>
       </c>
       <c r="L119" s="19"/>
       <c r="M119" s="20"/>
@@ -24553,13 +24543,13 @@
         <v>223</v>
       </c>
       <c r="C150" s="29" t="s">
-        <v>2658</v>
+        <v>2655</v>
       </c>
       <c r="D150" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E150" s="29" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="F150" s="23" t="s">
         <v>1550</v>
@@ -24586,13 +24576,13 @@
         <v>223</v>
       </c>
       <c r="C151" s="29" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="D151" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E151" s="29" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
       <c r="F151" s="23" t="s">
         <v>1550</v>
@@ -24619,13 +24609,13 @@
         <v>53</v>
       </c>
       <c r="C152" s="29" t="s">
-        <v>2658</v>
+        <v>2655</v>
       </c>
       <c r="D152" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E152" s="29" t="s">
-        <v>2662</v>
+        <v>2659</v>
       </c>
       <c r="F152" s="23" t="s">
         <v>1550</v>
@@ -24652,13 +24642,13 @@
         <v>53</v>
       </c>
       <c r="C153" s="29" t="s">
-        <v>2659</v>
+        <v>2656</v>
       </c>
       <c r="D153" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E153" s="29" t="s">
-        <v>2663</v>
+        <v>2660</v>
       </c>
       <c r="F153" s="23" t="s">
         <v>1550</v>
@@ -24685,13 +24675,13 @@
         <v>1164</v>
       </c>
       <c r="C154" s="78" t="s">
-        <v>2712</v>
+        <v>2709</v>
       </c>
       <c r="D154" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>2664</v>
+        <v>2661</v>
       </c>
       <c r="F154" s="23" t="s">
         <v>1550</v>
@@ -24720,13 +24710,13 @@
         <v>1164</v>
       </c>
       <c r="C155" s="78" t="s">
-        <v>2713</v>
+        <v>2710</v>
       </c>
       <c r="D155" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E155" s="29" t="s">
-        <v>2665</v>
+        <v>2662</v>
       </c>
       <c r="F155" s="23" t="s">
         <v>1550</v>
@@ -24755,13 +24745,13 @@
         <v>1164</v>
       </c>
       <c r="C156" s="78" t="s">
-        <v>2714</v>
+        <v>2711</v>
       </c>
       <c r="D156" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E156" s="29" t="s">
-        <v>2660</v>
+        <v>2657</v>
       </c>
       <c r="F156" s="23" t="s">
         <v>1550</v>
@@ -24790,13 +24780,13 @@
         <v>1164</v>
       </c>
       <c r="C157" s="78" t="s">
-        <v>2715</v>
+        <v>2712</v>
       </c>
       <c r="D157" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>2661</v>
+        <v>2658</v>
       </c>
       <c r="F157" s="23" t="s">
         <v>1550</v>
@@ -24825,13 +24815,13 @@
         <v>1164</v>
       </c>
       <c r="C158" s="78" t="s">
-        <v>2716</v>
+        <v>2713</v>
       </c>
       <c r="D158" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E158" s="29" t="s">
-        <v>2662</v>
+        <v>2659</v>
       </c>
       <c r="F158" s="23" t="s">
         <v>1550</v>
@@ -24860,13 +24850,13 @@
         <v>1164</v>
       </c>
       <c r="C159" s="78" t="s">
-        <v>2717</v>
+        <v>2714</v>
       </c>
       <c r="D159" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E159" s="29" t="s">
-        <v>2663</v>
+        <v>2660</v>
       </c>
       <c r="F159" s="23" t="s">
         <v>1550</v>
@@ -24895,13 +24885,13 @@
         <v>1164</v>
       </c>
       <c r="C160" s="78" t="s">
-        <v>2718</v>
+        <v>2715</v>
       </c>
       <c r="D160" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E160" s="29" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="F160" s="23" t="s">
         <v>1550</v>
@@ -24930,13 +24920,13 @@
         <v>1164</v>
       </c>
       <c r="C161" s="78" t="s">
-        <v>2719</v>
+        <v>2716</v>
       </c>
       <c r="D161" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E161" s="29" t="s">
-        <v>2667</v>
+        <v>2664</v>
       </c>
       <c r="F161" s="23" t="s">
         <v>1550</v>
@@ -24965,13 +24955,13 @@
         <v>1164</v>
       </c>
       <c r="C162" s="78" t="s">
-        <v>2720</v>
+        <v>2717</v>
       </c>
       <c r="D162" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E162" s="29" t="s">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="F162" s="23" t="s">
         <v>1550</v>
@@ -25000,13 +24990,13 @@
         <v>1164</v>
       </c>
       <c r="C163" s="78" t="s">
-        <v>2721</v>
+        <v>2718</v>
       </c>
       <c r="D163" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E163" s="29" t="s">
-        <v>2669</v>
+        <v>2666</v>
       </c>
       <c r="F163" s="23" t="s">
         <v>1550</v>
@@ -25035,13 +25025,13 @@
         <v>1164</v>
       </c>
       <c r="C164" s="78" t="s">
-        <v>2722</v>
+        <v>2719</v>
       </c>
       <c r="D164" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E164" s="29" t="s">
-        <v>2670</v>
+        <v>2667</v>
       </c>
       <c r="F164" s="23" t="s">
         <v>1550</v>
@@ -25070,13 +25060,13 @@
         <v>1164</v>
       </c>
       <c r="C165" s="78" t="s">
-        <v>2723</v>
+        <v>2720</v>
       </c>
       <c r="D165" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E165" s="29" t="s">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="F165" s="23" t="s">
         <v>1550</v>
@@ -25105,13 +25095,13 @@
         <v>1164</v>
       </c>
       <c r="C166" s="78" t="s">
-        <v>2724</v>
+        <v>2721</v>
       </c>
       <c r="D166" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E166" s="29" t="s">
-        <v>2672</v>
+        <v>2669</v>
       </c>
       <c r="F166" s="23" t="s">
         <v>1550</v>
@@ -25140,13 +25130,13 @@
         <v>1164</v>
       </c>
       <c r="C167" s="78" t="s">
-        <v>2725</v>
+        <v>2722</v>
       </c>
       <c r="D167" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E167" s="29" t="s">
-        <v>2673</v>
+        <v>2670</v>
       </c>
       <c r="F167" s="23" t="s">
         <v>1550</v>
@@ -25175,13 +25165,13 @@
         <v>1164</v>
       </c>
       <c r="C168" s="78" t="s">
-        <v>2726</v>
+        <v>2723</v>
       </c>
       <c r="D168" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E168" s="29" t="s">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="F168" s="23" t="s">
         <v>1550</v>
@@ -25210,13 +25200,13 @@
         <v>1164</v>
       </c>
       <c r="C169" s="78" t="s">
-        <v>2727</v>
+        <v>2724</v>
       </c>
       <c r="D169" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E169" s="29" t="s">
-        <v>2675</v>
+        <v>2672</v>
       </c>
       <c r="F169" s="23" t="s">
         <v>1550</v>
@@ -25245,13 +25235,13 @@
         <v>1164</v>
       </c>
       <c r="C170" s="78" t="s">
-        <v>2728</v>
+        <v>2725</v>
       </c>
       <c r="D170" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E170" s="29" t="s">
-        <v>2676</v>
+        <v>2673</v>
       </c>
       <c r="F170" s="23" t="s">
         <v>1550</v>
@@ -25280,13 +25270,13 @@
         <v>1164</v>
       </c>
       <c r="C171" s="78" t="s">
-        <v>2729</v>
+        <v>2726</v>
       </c>
       <c r="D171" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E171" s="29" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="F171" s="23" t="s">
         <v>1550</v>
@@ -25315,13 +25305,13 @@
         <v>1164</v>
       </c>
       <c r="C172" s="78" t="s">
-        <v>2730</v>
+        <v>2727</v>
       </c>
       <c r="D172" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E172" s="29" t="s">
-        <v>2678</v>
+        <v>2675</v>
       </c>
       <c r="F172" s="23" t="s">
         <v>1550</v>
@@ -25350,13 +25340,13 @@
         <v>1164</v>
       </c>
       <c r="C173" s="78" t="s">
-        <v>2731</v>
+        <v>2728</v>
       </c>
       <c r="D173" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E173" s="29" t="s">
-        <v>2679</v>
+        <v>2676</v>
       </c>
       <c r="F173" s="23" t="s">
         <v>1550</v>
@@ -25385,13 +25375,13 @@
         <v>1164</v>
       </c>
       <c r="C174" s="78" t="s">
-        <v>2732</v>
+        <v>2729</v>
       </c>
       <c r="D174" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E174" s="29" t="s">
-        <v>2680</v>
+        <v>2677</v>
       </c>
       <c r="F174" s="23" t="s">
         <v>1550</v>
@@ -25420,13 +25410,13 @@
         <v>1164</v>
       </c>
       <c r="C175" s="78" t="s">
-        <v>2733</v>
+        <v>2730</v>
       </c>
       <c r="D175" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E175" s="29" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="F175" s="23" t="s">
         <v>1550</v>
@@ -25455,13 +25445,13 @@
         <v>1164</v>
       </c>
       <c r="C176" s="78" t="s">
-        <v>2734</v>
+        <v>2731</v>
       </c>
       <c r="D176" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E176" s="29" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="F176" s="23" t="s">
         <v>1550</v>
@@ -25490,13 +25480,13 @@
         <v>1164</v>
       </c>
       <c r="C177" s="78" t="s">
-        <v>2735</v>
+        <v>2732</v>
       </c>
       <c r="D177" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E177" s="29" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="F177" s="23" t="s">
         <v>1550</v>
@@ -25525,13 +25515,13 @@
         <v>1164</v>
       </c>
       <c r="C178" s="78" t="s">
-        <v>2736</v>
+        <v>2733</v>
       </c>
       <c r="D178" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E178" s="29" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="F178" s="23" t="s">
         <v>1550</v>
@@ -25560,13 +25550,13 @@
         <v>1164</v>
       </c>
       <c r="C179" s="78" t="s">
-        <v>2737</v>
+        <v>2734</v>
       </c>
       <c r="D179" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E179" s="29" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="F179" s="23" t="s">
         <v>1550</v>
@@ -25595,13 +25585,13 @@
         <v>1164</v>
       </c>
       <c r="C180" s="78" t="s">
-        <v>2738</v>
+        <v>2735</v>
       </c>
       <c r="D180" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E180" s="29" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="F180" s="23" t="s">
         <v>1550</v>
@@ -25630,13 +25620,13 @@
         <v>1164</v>
       </c>
       <c r="C181" s="78" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="D181" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E181" s="29" t="s">
-        <v>2687</v>
+        <v>2684</v>
       </c>
       <c r="F181" s="23" t="s">
         <v>1550</v>
@@ -25665,13 +25655,13 @@
         <v>1164</v>
       </c>
       <c r="C182" s="78" t="s">
-        <v>2740</v>
+        <v>2737</v>
       </c>
       <c r="D182" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E182" s="29" t="s">
-        <v>2688</v>
+        <v>2685</v>
       </c>
       <c r="F182" s="23" t="s">
         <v>1550</v>
@@ -25700,13 +25690,13 @@
         <v>1164</v>
       </c>
       <c r="C183" s="78" t="s">
-        <v>2741</v>
+        <v>2738</v>
       </c>
       <c r="D183" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E183" s="29" t="s">
-        <v>2689</v>
+        <v>2686</v>
       </c>
       <c r="F183" s="23" t="s">
         <v>1550</v>
@@ -25735,13 +25725,13 @@
         <v>1164</v>
       </c>
       <c r="C184" s="78" t="s">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="D184" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E184" s="29" t="s">
-        <v>2690</v>
+        <v>2687</v>
       </c>
       <c r="F184" s="23" t="s">
         <v>1550</v>
@@ -25770,13 +25760,13 @@
         <v>1164</v>
       </c>
       <c r="C185" s="78" t="s">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="D185" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E185" s="29" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="F185" s="23" t="s">
         <v>1550</v>
@@ -25805,13 +25795,13 @@
         <v>1164</v>
       </c>
       <c r="C186" s="78" t="s">
-        <v>2744</v>
+        <v>2741</v>
       </c>
       <c r="D186" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E186" s="29" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="F186" s="23" t="s">
         <v>1550</v>
@@ -25840,13 +25830,13 @@
         <v>1164</v>
       </c>
       <c r="C187" s="78" t="s">
-        <v>2745</v>
+        <v>2742</v>
       </c>
       <c r="D187" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E187" s="29" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="F187" s="23" t="s">
         <v>1550</v>
@@ -25875,13 +25865,13 @@
         <v>1164</v>
       </c>
       <c r="C188" s="78" t="s">
-        <v>2746</v>
+        <v>2743</v>
       </c>
       <c r="D188" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E188" s="29" t="s">
-        <v>2694</v>
+        <v>2691</v>
       </c>
       <c r="F188" s="23" t="s">
         <v>1550</v>
@@ -25910,13 +25900,13 @@
         <v>1164</v>
       </c>
       <c r="C189" s="78" t="s">
-        <v>2747</v>
+        <v>2744</v>
       </c>
       <c r="D189" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E189" s="29" t="s">
-        <v>2695</v>
+        <v>2692</v>
       </c>
       <c r="F189" s="23" t="s">
         <v>1550</v>
@@ -25945,13 +25935,13 @@
         <v>1164</v>
       </c>
       <c r="C190" s="78" t="s">
-        <v>2748</v>
+        <v>2745</v>
       </c>
       <c r="D190" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E190" s="29" t="s">
-        <v>2696</v>
+        <v>2693</v>
       </c>
       <c r="F190" s="23" t="s">
         <v>1550</v>
@@ -25980,13 +25970,13 @@
         <v>1164</v>
       </c>
       <c r="C191" s="78" t="s">
-        <v>2749</v>
+        <v>2746</v>
       </c>
       <c r="D191" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E191" s="29" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="F191" s="23" t="s">
         <v>1550</v>
@@ -26015,13 +26005,13 @@
         <v>1164</v>
       </c>
       <c r="C192" s="78" t="s">
-        <v>2750</v>
+        <v>2747</v>
       </c>
       <c r="D192" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E192" s="29" t="s">
-        <v>2698</v>
+        <v>2695</v>
       </c>
       <c r="F192" s="23" t="s">
         <v>1550</v>
@@ -26050,13 +26040,13 @@
         <v>1164</v>
       </c>
       <c r="C193" s="78" t="s">
-        <v>2751</v>
+        <v>2748</v>
       </c>
       <c r="D193" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E193" s="29" t="s">
-        <v>2699</v>
+        <v>2696</v>
       </c>
       <c r="F193" s="23" t="s">
         <v>1550</v>
@@ -26083,13 +26073,13 @@
         <v>1164</v>
       </c>
       <c r="C194" s="78" t="s">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="D194" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E194" s="29" t="s">
-        <v>2700</v>
+        <v>2697</v>
       </c>
       <c r="F194" s="23" t="s">
         <v>1550</v>
@@ -26116,13 +26106,13 @@
         <v>1164</v>
       </c>
       <c r="C195" s="78" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
       <c r="D195" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E195" s="29" t="s">
-        <v>2701</v>
+        <v>2698</v>
       </c>
       <c r="F195" s="23" t="s">
         <v>1550</v>
@@ -26149,13 +26139,13 @@
         <v>1164</v>
       </c>
       <c r="C196" s="78" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="D196" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E196" s="29" t="s">
-        <v>2702</v>
+        <v>2699</v>
       </c>
       <c r="F196" s="23" t="s">
         <v>1550</v>
@@ -26182,13 +26172,13 @@
         <v>1164</v>
       </c>
       <c r="C197" s="78" t="s">
-        <v>2755</v>
+        <v>2752</v>
       </c>
       <c r="D197" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E197" s="29" t="s">
-        <v>2703</v>
+        <v>2700</v>
       </c>
       <c r="F197" s="23" t="s">
         <v>1550</v>
@@ -26217,13 +26207,13 @@
         <v>1164</v>
       </c>
       <c r="C198" s="78" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="D198" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E198" s="29" t="s">
-        <v>2704</v>
+        <v>2701</v>
       </c>
       <c r="F198" s="23" t="s">
         <v>1550</v>
@@ -26252,13 +26242,13 @@
         <v>1164</v>
       </c>
       <c r="C199" s="78" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
       <c r="D199" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E199" s="29" t="s">
-        <v>2705</v>
+        <v>2702</v>
       </c>
       <c r="F199" s="23" t="s">
         <v>1550</v>
@@ -26285,13 +26275,13 @@
         <v>1164</v>
       </c>
       <c r="C200" s="78" t="s">
-        <v>2758</v>
+        <v>2755</v>
       </c>
       <c r="D200" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E200" s="29" t="s">
-        <v>2706</v>
+        <v>2703</v>
       </c>
       <c r="F200" s="23" t="s">
         <v>1550</v>
@@ -26318,13 +26308,13 @@
         <v>1164</v>
       </c>
       <c r="C201" s="78" t="s">
-        <v>2759</v>
+        <v>2756</v>
       </c>
       <c r="D201" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E201" s="29" t="s">
-        <v>2707</v>
+        <v>2704</v>
       </c>
       <c r="F201" s="23" t="s">
         <v>1550</v>
@@ -26351,13 +26341,13 @@
         <v>1164</v>
       </c>
       <c r="C202" s="78" t="s">
-        <v>2760</v>
+        <v>2757</v>
       </c>
       <c r="D202" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E202" s="29" t="s">
-        <v>2708</v>
+        <v>2705</v>
       </c>
       <c r="F202" s="23" t="s">
         <v>1550</v>
@@ -26384,13 +26374,13 @@
         <v>1164</v>
       </c>
       <c r="C203" s="78" t="s">
-        <v>2761</v>
+        <v>2758</v>
       </c>
       <c r="D203" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E203" s="29" t="s">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="F203" s="23" t="s">
         <v>1550</v>
@@ -26419,13 +26409,13 @@
         <v>1164</v>
       </c>
       <c r="C204" s="78" t="s">
-        <v>2762</v>
+        <v>2759</v>
       </c>
       <c r="D204" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E204" s="29" t="s">
-        <v>2710</v>
+        <v>2707</v>
       </c>
       <c r="F204" s="23" t="s">
         <v>1550</v>
@@ -26454,13 +26444,13 @@
         <v>1164</v>
       </c>
       <c r="C205" s="78" t="s">
-        <v>2763</v>
+        <v>2760</v>
       </c>
       <c r="D205" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E205" s="29" t="s">
-        <v>2711</v>
+        <v>2708</v>
       </c>
       <c r="F205" s="23" t="s">
         <v>1550</v>
@@ -26489,13 +26479,13 @@
         <v>1164</v>
       </c>
       <c r="C206" s="78" t="s">
-        <v>2764</v>
+        <v>2761</v>
       </c>
       <c r="D206" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E206" s="29" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="F206" s="23" t="s">
         <v>1550</v>
@@ -26522,13 +26512,13 @@
         <v>1164</v>
       </c>
       <c r="C207" s="78" t="s">
-        <v>2765</v>
+        <v>2762</v>
       </c>
       <c r="D207" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E207" s="29" t="s">
-        <v>2678</v>
+        <v>2675</v>
       </c>
       <c r="F207" s="23" t="s">
         <v>1550</v>
@@ -26555,13 +26545,13 @@
         <v>1164</v>
       </c>
       <c r="C208" s="78" t="s">
-        <v>2766</v>
+        <v>2763</v>
       </c>
       <c r="D208" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E208" s="29" t="s">
-        <v>2679</v>
+        <v>2676</v>
       </c>
       <c r="F208" s="23" t="s">
         <v>1550</v>
@@ -26588,13 +26578,13 @@
         <v>1164</v>
       </c>
       <c r="C209" s="78" t="s">
-        <v>2767</v>
+        <v>2764</v>
       </c>
       <c r="D209" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E209" s="29" t="s">
-        <v>2680</v>
+        <v>2677</v>
       </c>
       <c r="F209" s="23" t="s">
         <v>1550</v>
@@ -26621,13 +26611,13 @@
         <v>1164</v>
       </c>
       <c r="C210" s="78" t="s">
-        <v>2768</v>
+        <v>2765</v>
       </c>
       <c r="D210" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E210" s="29" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="F210" s="23" t="s">
         <v>1550</v>
@@ -26654,13 +26644,13 @@
         <v>1164</v>
       </c>
       <c r="C211" s="78" t="s">
-        <v>2769</v>
+        <v>2766</v>
       </c>
       <c r="D211" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E211" s="29" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="F211" s="23" t="s">
         <v>1550</v>
@@ -26687,13 +26677,13 @@
         <v>1164</v>
       </c>
       <c r="C212" s="78" t="s">
-        <v>2770</v>
+        <v>2767</v>
       </c>
       <c r="D212" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E212" s="29" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="F212" s="23" t="s">
         <v>1550</v>
@@ -26720,13 +26710,13 @@
         <v>1164</v>
       </c>
       <c r="C213" s="78" t="s">
-        <v>2771</v>
+        <v>2768</v>
       </c>
       <c r="D213" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E213" s="29" t="s">
-        <v>2687</v>
+        <v>2684</v>
       </c>
       <c r="F213" s="23" t="s">
         <v>1550</v>
@@ -26753,13 +26743,13 @@
         <v>1164</v>
       </c>
       <c r="C214" s="78" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E214" s="29" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>1550</v>
@@ -26786,13 +26776,13 @@
         <v>1164</v>
       </c>
       <c r="C215" s="78" t="s">
-        <v>2773</v>
+        <v>2770</v>
       </c>
       <c r="D215" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E215" s="29" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>1550</v>
@@ -26819,13 +26809,13 @@
         <v>1164</v>
       </c>
       <c r="C216" s="78" t="s">
-        <v>2774</v>
+        <v>2771</v>
       </c>
       <c r="D216" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E216" s="29" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="F216" s="23" t="s">
         <v>1550</v>
@@ -26852,13 +26842,13 @@
         <v>1164</v>
       </c>
       <c r="C217" s="78" t="s">
-        <v>2775</v>
+        <v>2772</v>
       </c>
       <c r="D217" s="31" t="s">
         <v>55</v>
       </c>
       <c r="E217" s="29" t="s">
-        <v>2688</v>
+        <v>2685</v>
       </c>
       <c r="F217" s="23" t="s">
         <v>1550</v>
@@ -27054,7 +27044,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="29" t="s">
-        <v>2776</v>
+        <v>2773</v>
       </c>
       <c r="B223" s="31" t="s">
         <v>457</v>
@@ -27091,7 +27081,7 @@
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="29" t="s">
-        <v>2777</v>
+        <v>2774</v>
       </c>
       <c r="B224" s="38" t="s">
         <v>459</v>
@@ -27126,14 +27116,14 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>3093</v>
+        <v>3090</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>53</v>
       </c>
       <c r="C225" s="29"/>
       <c r="D225" s="31" t="s">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="E225" s="29">
         <v>5343</v>
@@ -27142,7 +27132,7 @@
         <v>1550</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="H225" s="29">
         <v>0</v>
@@ -27151,7 +27141,7 @@
         <v>503</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
       <c r="K225" s="29"/>
       <c r="L225" s="31"/>
@@ -27370,7 +27360,7 @@
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="29" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
       <c r="B233" s="31" t="s">
         <v>488</v>
@@ -27401,7 +27391,7 @@
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="29" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
       <c r="B234" s="31" t="s">
         <v>489</v>
@@ -27432,7 +27422,7 @@
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="29" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
       <c r="B235" s="31" t="s">
         <v>490</v>
@@ -27573,7 +27563,7 @@
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="29" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
       <c r="B240" s="31"/>
       <c r="C240" s="29"/>
@@ -27598,7 +27588,7 @@
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="29" t="s">
-        <v>2830</v>
+        <v>2827</v>
       </c>
       <c r="B241" s="31" t="s">
         <v>510</v>
@@ -27627,7 +27617,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="29" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
       <c r="B242" s="31" t="s">
         <v>513</v>
@@ -27970,7 +27960,7 @@
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="29" t="s">
-        <v>2832</v>
+        <v>2829</v>
       </c>
       <c r="B253" s="31" t="s">
         <v>520</v>
@@ -28024,7 +28014,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="29" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
       <c r="B255" s="31" t="s">
         <v>600</v>
@@ -28136,7 +28126,7 @@
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="29" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
       <c r="B259" s="31" t="s">
         <v>524</v>
@@ -28552,7 +28542,7 @@
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="29" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="B273" s="31" t="s">
         <v>524</v>
@@ -28993,7 +28983,7 @@
         <v>625</v>
       </c>
       <c r="B289" s="31" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="C289" s="29" t="s">
         <v>147</v>
@@ -29017,10 +29007,10 @@
         <v>96</v>
       </c>
       <c r="J289" s="29" t="s">
-        <v>3031</v>
+        <v>3028</v>
       </c>
       <c r="K289" s="29" t="s">
-        <v>3032</v>
+        <v>3029</v>
       </c>
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
@@ -30330,7 +30320,7 @@
       </c>
       <c r="J331" s="29"/>
       <c r="K331" s="35" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="L331" s="32"/>
       <c r="M331" s="35"/>
@@ -30692,7 +30682,7 @@
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="29" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="B343" s="31" t="s">
         <v>258</v>
@@ -30961,7 +30951,7 @@
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="29" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
       <c r="B352" s="29" t="s">
         <v>809</v>
@@ -30992,7 +30982,7 @@
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="29" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
       <c r="B353" s="29" t="s">
         <v>809</v>
@@ -31023,7 +31013,7 @@
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="29" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="B354" s="29" t="s">
         <v>809</v>
@@ -31054,7 +31044,7 @@
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="29" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
       <c r="B355" s="29" t="s">
         <v>809</v>
@@ -31085,7 +31075,7 @@
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="29" t="s">
-        <v>2841</v>
+        <v>2838</v>
       </c>
       <c r="B356" s="31" t="s">
         <v>830</v>
@@ -31116,7 +31106,7 @@
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="29" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
       <c r="B357" s="31" t="s">
         <v>830</v>
@@ -31147,7 +31137,7 @@
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="29" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
       <c r="B358" s="31" t="s">
         <v>830</v>
@@ -31178,7 +31168,7 @@
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="29" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
       <c r="B359" s="31" t="s">
         <v>830</v>
@@ -31559,7 +31549,7 @@
     </row>
     <row r="372" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A372" s="29" t="s">
-        <v>2596</v>
+        <v>2593</v>
       </c>
       <c r="B372" s="31" t="s">
         <v>260</v>
@@ -31588,7 +31578,7 @@
     </row>
     <row r="373" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A373" s="29" t="s">
-        <v>2597</v>
+        <v>2594</v>
       </c>
       <c r="B373" s="31" t="s">
         <v>260</v>
@@ -31648,7 +31638,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
       <c r="B375" s="31" t="s">
         <v>260</v>
@@ -31679,7 +31669,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
       <c r="B376" s="31" t="s">
         <v>260</v>
@@ -31710,7 +31700,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
-        <v>2847</v>
+        <v>2844</v>
       </c>
       <c r="B377" s="31" t="s">
         <v>262</v>
@@ -31741,7 +31731,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
-        <v>2848</v>
+        <v>2845</v>
       </c>
       <c r="B378" s="31" t="s">
         <v>262</v>
@@ -31772,7 +31762,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
-        <v>2849</v>
+        <v>2846</v>
       </c>
       <c r="B379" s="31" t="s">
         <v>242</v>
@@ -31803,7 +31793,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
-        <v>2850</v>
+        <v>2847</v>
       </c>
       <c r="B380" s="31" t="s">
         <v>258</v>
@@ -32192,7 +32182,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
-        <v>2851</v>
+        <v>2848</v>
       </c>
       <c r="B393" s="31" t="s">
         <v>898</v>
@@ -32219,7 +32209,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
-        <v>2852</v>
+        <v>2849</v>
       </c>
       <c r="B394" s="31" t="s">
         <v>899</v>
@@ -32246,7 +32236,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
-        <v>2853</v>
+        <v>2850</v>
       </c>
       <c r="B395" s="29" t="s">
         <v>900</v>
@@ -32269,7 +32259,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
-        <v>2854</v>
+        <v>2851</v>
       </c>
       <c r="B396" s="29" t="s">
         <v>902</v>
@@ -32292,7 +32282,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
-        <v>2855</v>
+        <v>2852</v>
       </c>
       <c r="B397" s="29" t="s">
         <v>900</v>
@@ -32315,7 +32305,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
-        <v>2856</v>
+        <v>2853</v>
       </c>
       <c r="B398" s="31" t="s">
         <v>904</v>
@@ -32338,7 +32328,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
-        <v>2857</v>
+        <v>2854</v>
       </c>
       <c r="B399" s="31" t="s">
         <v>905</v>
@@ -32361,7 +32351,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
-        <v>2858</v>
+        <v>2855</v>
       </c>
       <c r="B400" s="31" t="s">
         <v>906</v>
@@ -32384,7 +32374,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
-        <v>2859</v>
+        <v>2856</v>
       </c>
       <c r="B401" s="31" t="s">
         <v>907</v>
@@ -32407,7 +32397,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
-        <v>2860</v>
+        <v>2857</v>
       </c>
       <c r="B402" s="31" t="s">
         <v>908</v>
@@ -32430,7 +32420,7 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
-        <v>2861</v>
+        <v>2858</v>
       </c>
       <c r="B403" s="31" t="s">
         <v>909</v>
@@ -32453,7 +32443,7 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
-        <v>2862</v>
+        <v>2859</v>
       </c>
       <c r="B404" s="31" t="s">
         <v>910</v>
@@ -32476,7 +32466,7 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
-        <v>2863</v>
+        <v>2860</v>
       </c>
       <c r="B405" s="31" t="s">
         <v>911</v>
@@ -32499,7 +32489,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
-        <v>2864</v>
+        <v>2861</v>
       </c>
       <c r="B406" s="31" t="s">
         <v>897</v>
@@ -32648,7 +32638,7 @@
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
-        <v>2865</v>
+        <v>2862</v>
       </c>
       <c r="B411" s="31" t="s">
         <v>258</v>
@@ -32673,7 +32663,7 @@
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
-        <v>2866</v>
+        <v>2863</v>
       </c>
       <c r="B412" s="31" t="s">
         <v>258</v>
@@ -32698,7 +32688,7 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
-        <v>2867</v>
+        <v>2864</v>
       </c>
       <c r="B413" s="31" t="s">
         <v>258</v>
@@ -32723,7 +32713,7 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
-        <v>2868</v>
+        <v>2865</v>
       </c>
       <c r="B414" s="31" t="s">
         <v>258</v>
@@ -33015,7 +33005,7 @@
         <v>96</v>
       </c>
       <c r="J423" s="29" t="s">
-        <v>2594</v>
+        <v>2591</v>
       </c>
       <c r="K423" s="29"/>
       <c r="L423" s="31"/>
@@ -33023,7 +33013,7 @@
     </row>
     <row r="424" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A424" s="29" t="s">
-        <v>2640</v>
+        <v>2637</v>
       </c>
       <c r="B424" s="31" t="s">
         <v>2473</v>
@@ -33058,7 +33048,7 @@
         <v>2033</v>
       </c>
       <c r="E425" s="29" t="s">
-        <v>2565</v>
+        <v>2562</v>
       </c>
       <c r="F425" s="31" t="s">
         <v>231</v>
@@ -33073,7 +33063,7 @@
         <v>96</v>
       </c>
       <c r="J425" s="31" t="s">
-        <v>2569</v>
+        <v>2566</v>
       </c>
       <c r="K425" s="29"/>
       <c r="L425" s="31"/>
@@ -33477,7 +33467,7 @@
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
-        <v>2869</v>
+        <v>2866</v>
       </c>
       <c r="B438" s="31" t="s">
         <v>982</v>
@@ -33512,7 +33502,7 @@
     </row>
     <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
-        <v>2870</v>
+        <v>2867</v>
       </c>
       <c r="B439" s="31" t="s">
         <v>982</v>
@@ -33547,7 +33537,7 @@
     </row>
     <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="29" t="s">
-        <v>2871</v>
+        <v>2868</v>
       </c>
       <c r="B440" s="31" t="s">
         <v>982</v>
@@ -33582,7 +33572,7 @@
     </row>
     <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="29" t="s">
-        <v>2872</v>
+        <v>2869</v>
       </c>
       <c r="B441" s="87" t="s">
         <v>1055</v>
@@ -33615,7 +33605,7 @@
     </row>
     <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
-        <v>3027</v>
+        <v>3024</v>
       </c>
       <c r="B442" s="87" t="s">
         <v>1458</v>
@@ -33643,14 +33633,14 @@
         <v>1056</v>
       </c>
       <c r="K442" s="29" t="s">
-        <v>3028</v>
+        <v>3025</v>
       </c>
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
     <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="29" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
       <c r="B443" s="29" t="s">
         <v>1604</v>
@@ -33679,7 +33669,7 @@
     </row>
     <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
-        <v>2874</v>
+        <v>2871</v>
       </c>
       <c r="B444" s="87" t="s">
         <v>1611</v>
@@ -33712,7 +33702,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
-        <v>2875</v>
+        <v>2872</v>
       </c>
       <c r="B445" t="s">
         <v>1606</v>
@@ -33743,7 +33733,7 @@
     </row>
     <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
-        <v>2876</v>
+        <v>2873</v>
       </c>
       <c r="B446" t="s">
         <v>1607</v>
@@ -33774,7 +33764,7 @@
     </row>
     <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
-        <v>2877</v>
+        <v>2874</v>
       </c>
       <c r="B447" t="s">
         <v>1608</v>
@@ -33805,7 +33795,7 @@
     </row>
     <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="29" t="s">
-        <v>2878</v>
+        <v>2875</v>
       </c>
       <c r="B448" t="s">
         <v>1609</v>
@@ -33836,7 +33826,7 @@
     </row>
     <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="29" t="s">
-        <v>2879</v>
+        <v>2876</v>
       </c>
       <c r="B449" s="87" t="s">
         <v>1610</v>
@@ -33869,7 +33859,7 @@
     </row>
     <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="29" t="s">
-        <v>2880</v>
+        <v>2877</v>
       </c>
       <c r="B450" s="87" t="s">
         <v>1456</v>
@@ -33900,7 +33890,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2881</v>
+        <v>2878</v>
       </c>
       <c r="B451" s="87" t="s">
         <v>1457</v>
@@ -33931,7 +33921,7 @@
     </row>
     <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
-        <v>2882</v>
+        <v>2879</v>
       </c>
       <c r="B452" s="31" t="s">
         <v>1244</v>
@@ -34611,7 +34601,7 @@
         <v>27</v>
       </c>
       <c r="H471" s="29" t="s">
-        <v>2819</v>
+        <v>2816</v>
       </c>
       <c r="I471" s="29" t="s">
         <v>96</v>
@@ -34625,7 +34615,7 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
-        <v>2883</v>
+        <v>2880</v>
       </c>
       <c r="B472" s="29" t="s">
         <v>19</v>
@@ -34691,7 +34681,7 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
-        <v>2884</v>
+        <v>2881</v>
       </c>
       <c r="B474" s="29" t="s">
         <v>19</v>
@@ -34755,7 +34745,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -35274,7 +35264,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
-        <v>2885</v>
+        <v>2882</v>
       </c>
       <c r="B491" s="32"/>
       <c r="C491" s="53" t="s">
@@ -35523,7 +35513,7 @@
     </row>
     <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="34" t="s">
-        <v>2886</v>
+        <v>2883</v>
       </c>
       <c r="B498" s="59" t="s">
         <v>1111</v>
@@ -35865,7 +35855,7 @@
     </row>
     <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
-        <v>2887</v>
+        <v>2884</v>
       </c>
       <c r="B508" s="32"/>
       <c r="C508" s="53"/>
@@ -35892,7 +35882,7 @@
     </row>
     <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="24" t="s">
-        <v>2888</v>
+        <v>2885</v>
       </c>
       <c r="B509" s="22"/>
       <c r="C509" s="25"/>
@@ -37037,13 +37027,13 @@
     </row>
     <row r="542" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="29" t="s">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="B542" s="59" t="s">
         <v>1674</v>
       </c>
       <c r="C542" s="82" t="s">
-        <v>2622</v>
+        <v>2619</v>
       </c>
       <c r="D542" s="70" t="s">
         <v>1099</v>
@@ -37066,13 +37056,13 @@
     </row>
     <row r="543" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="29" t="s">
-        <v>2890</v>
+        <v>2887</v>
       </c>
       <c r="B543" s="59" t="s">
         <v>1674</v>
       </c>
       <c r="C543" s="36" t="s">
-        <v>2623</v>
+        <v>2620</v>
       </c>
       <c r="D543" s="70" t="s">
         <v>1100</v>
@@ -37095,7 +37085,7 @@
     </row>
     <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="29" t="s">
-        <v>2891</v>
+        <v>2888</v>
       </c>
       <c r="B544" s="59" t="s">
         <v>1674</v>
@@ -37127,7 +37117,7 @@
         <v>1498</v>
       </c>
       <c r="B545" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C545" s="36">
         <v>2</v>
@@ -37156,7 +37146,7 @@
         <v>1499</v>
       </c>
       <c r="B546" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C546" s="36">
         <v>3</v>
@@ -37185,7 +37175,7 @@
         <v>1500</v>
       </c>
       <c r="B547" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C547" s="36">
         <v>4</v>
@@ -37214,7 +37204,7 @@
         <v>1501</v>
       </c>
       <c r="B548" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C548" s="36">
         <v>5</v>
@@ -37243,7 +37233,7 @@
         <v>1502</v>
       </c>
       <c r="B549" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C549" s="36">
         <v>6</v>
@@ -37272,7 +37262,7 @@
         <v>1503</v>
       </c>
       <c r="B550" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C550" s="36">
         <v>7</v>
@@ -37301,7 +37291,7 @@
         <v>1504</v>
       </c>
       <c r="B551" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C551" s="36">
         <v>8</v>
@@ -37330,7 +37320,7 @@
         <v>1505</v>
       </c>
       <c r="B552" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C552" s="36">
         <v>9</v>
@@ -37359,7 +37349,7 @@
         <v>1506</v>
       </c>
       <c r="B553" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C553" s="36">
         <v>10</v>
@@ -37388,7 +37378,7 @@
         <v>1507</v>
       </c>
       <c r="B554" s="73" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C554" s="36">
         <v>11</v>
@@ -37707,7 +37697,7 @@
         <v>1277</v>
       </c>
       <c r="B565" s="84" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="C565" s="73" t="s">
         <v>2234</v>
@@ -37733,7 +37723,7 @@
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
-        <v>3100</v>
+        <v>3097</v>
       </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
@@ -38896,7 +38886,7 @@
     </row>
     <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="29" t="s">
-        <v>2892</v>
+        <v>2889</v>
       </c>
       <c r="B603" s="73" t="s">
         <v>1289</v>
@@ -38929,7 +38919,7 @@
     </row>
     <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="29" t="s">
-        <v>2893</v>
+        <v>2890</v>
       </c>
       <c r="B604" s="73" t="s">
         <v>1289</v>
@@ -38962,7 +38952,7 @@
     </row>
     <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="29" t="s">
-        <v>2894</v>
+        <v>2891</v>
       </c>
       <c r="B605" s="73" t="s">
         <v>1289</v>
@@ -38995,7 +38985,7 @@
     </row>
     <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="29" t="s">
-        <v>2895</v>
+        <v>2892</v>
       </c>
       <c r="B606" s="73" t="s">
         <v>1289</v>
@@ -39028,7 +39018,7 @@
     </row>
     <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="29" t="s">
-        <v>2896</v>
+        <v>2893</v>
       </c>
       <c r="B607" s="73" t="s">
         <v>1289</v>
@@ -39059,7 +39049,7 @@
     </row>
     <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="29" t="s">
-        <v>2897</v>
+        <v>2894</v>
       </c>
       <c r="B608" s="73" t="s">
         <v>1289</v>
@@ -39090,7 +39080,7 @@
     </row>
     <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="29" t="s">
-        <v>2898</v>
+        <v>2895</v>
       </c>
       <c r="B609" s="73" t="s">
         <v>1289</v>
@@ -39121,7 +39111,7 @@
     </row>
     <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="29" t="s">
-        <v>2899</v>
+        <v>2896</v>
       </c>
       <c r="B610" s="73" t="s">
         <v>1289</v>
@@ -39152,7 +39142,7 @@
     </row>
     <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="29" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="B611" s="73" t="s">
         <v>1289</v>
@@ -39183,7 +39173,7 @@
     </row>
     <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="29" t="s">
-        <v>2901</v>
+        <v>2898</v>
       </c>
       <c r="B612" s="73" t="s">
         <v>1289</v>
@@ -39214,7 +39204,7 @@
     </row>
     <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="29" t="s">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="B613" s="73" t="s">
         <v>1289</v>
@@ -39245,7 +39235,7 @@
     </row>
     <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="29" t="s">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="B614" s="73" t="s">
         <v>1289</v>
@@ -39276,7 +39266,7 @@
     </row>
     <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="29" t="s">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="B615" s="73" t="s">
         <v>1289</v>
@@ -39307,7 +39297,7 @@
     </row>
     <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="29" t="s">
-        <v>2905</v>
+        <v>2902</v>
       </c>
       <c r="B616" s="73" t="s">
         <v>1289</v>
@@ -39338,7 +39328,7 @@
     </row>
     <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="29" t="s">
-        <v>2906</v>
+        <v>2903</v>
       </c>
       <c r="B617" s="73" t="s">
         <v>1289</v>
@@ -39371,7 +39361,7 @@
     </row>
     <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="29" t="s">
-        <v>2907</v>
+        <v>2904</v>
       </c>
       <c r="B618" s="73" t="s">
         <v>1289</v>
@@ -39404,7 +39394,7 @@
     </row>
     <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="29" t="s">
-        <v>2908</v>
+        <v>2905</v>
       </c>
       <c r="B619" s="82" t="s">
         <v>1278</v>
@@ -39435,7 +39425,7 @@
     </row>
     <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="29" t="s">
-        <v>2909</v>
+        <v>2906</v>
       </c>
       <c r="B620" s="82" t="s">
         <v>1278</v>
@@ -39466,7 +39456,7 @@
     </row>
     <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="29" t="s">
-        <v>2910</v>
+        <v>2907</v>
       </c>
       <c r="B621" s="82" t="s">
         <v>1278</v>
@@ -39497,7 +39487,7 @@
     </row>
     <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="29" t="s">
-        <v>2911</v>
+        <v>2908</v>
       </c>
       <c r="B622" s="82" t="s">
         <v>1278</v>
@@ -39530,7 +39520,7 @@
     </row>
     <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="29" t="s">
-        <v>2912</v>
+        <v>2909</v>
       </c>
       <c r="B623" s="83" t="s">
         <v>1283</v>
@@ -39563,7 +39553,7 @@
     </row>
     <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="29" t="s">
-        <v>2913</v>
+        <v>2910</v>
       </c>
       <c r="B624" s="83" t="s">
         <v>1283</v>
@@ -39594,7 +39584,7 @@
     </row>
     <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="29" t="s">
-        <v>2914</v>
+        <v>2911</v>
       </c>
       <c r="B625" s="83" t="s">
         <v>1283</v>
@@ -39625,7 +39615,7 @@
     </row>
     <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="29" t="s">
-        <v>2915</v>
+        <v>2912</v>
       </c>
       <c r="B626" s="83" t="s">
         <v>1283</v>
@@ -39722,7 +39712,7 @@
     </row>
     <row r="629" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A629" s="29" t="s">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="B629" s="82" t="s">
         <v>1337</v>
@@ -39749,7 +39739,7 @@
     </row>
     <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
-        <v>2917</v>
+        <v>2914</v>
       </c>
       <c r="B630" s="83" t="s">
         <v>1337</v>
@@ -40826,10 +40816,10 @@
     </row>
     <row r="661" spans="1:13" s="131" customFormat="1" ht="82" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="128" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
       <c r="B661" s="83" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C661" s="128" t="s">
         <v>2401</v>
@@ -40847,13 +40837,13 @@
         <v>1478</v>
       </c>
       <c r="H661" s="56" t="s">
-        <v>3107</v>
+        <v>3104</v>
       </c>
       <c r="I661" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J661" s="130" t="s">
-        <v>3139</v>
+        <v>3136</v>
       </c>
       <c r="K661" s="128" t="s">
         <v>465</v>
@@ -40863,13 +40853,13 @@
     </row>
     <row r="662" spans="1:13" s="131" customFormat="1" ht="66" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="128" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
       <c r="B662" s="83" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="C662" s="128" t="s">
-        <v>3111</v>
+        <v>3108</v>
       </c>
       <c r="D662" s="84" t="s">
         <v>1629</v>
@@ -40884,13 +40874,13 @@
         <v>1478</v>
       </c>
       <c r="H662" s="56" t="s">
-        <v>3108</v>
+        <v>3105</v>
       </c>
       <c r="I662" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J662" s="130" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="K662" s="128" t="s">
         <v>989</v>
@@ -40900,7 +40890,7 @@
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
-        <v>3088</v>
+        <v>3085</v>
       </c>
       <c r="B663" s="84" t="s">
         <v>1852</v>
@@ -40927,7 +40917,7 @@
         <v>60</v>
       </c>
       <c r="J663" s="29" t="s">
-        <v>3110</v>
+        <v>3107</v>
       </c>
       <c r="K663" s="29"/>
       <c r="L663" s="31"/>
@@ -42037,7 +42027,7 @@
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
-        <v>2918</v>
+        <v>2915</v>
       </c>
       <c r="B698" s="85" t="s">
         <v>1370</v>
@@ -42066,7 +42056,7 @@
     </row>
     <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
-        <v>2919</v>
+        <v>2916</v>
       </c>
       <c r="B699" s="85" t="s">
         <v>1370</v>
@@ -42095,7 +42085,7 @@
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
-        <v>2920</v>
+        <v>2917</v>
       </c>
       <c r="B700" s="85" t="s">
         <v>1370</v>
@@ -42124,7 +42114,7 @@
     </row>
     <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
-        <v>2921</v>
+        <v>2918</v>
       </c>
       <c r="B701" s="85" t="s">
         <v>1370</v>
@@ -42153,7 +42143,7 @@
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
-        <v>2922</v>
+        <v>2919</v>
       </c>
       <c r="B702" s="85" t="s">
         <v>1370</v>
@@ -42182,7 +42172,7 @@
     </row>
     <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="B703" s="85" t="s">
         <v>1370</v>
@@ -42211,7 +42201,7 @@
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
-        <v>2924</v>
+        <v>2921</v>
       </c>
       <c r="B704" s="85" t="s">
         <v>1370</v>
@@ -42240,7 +42230,7 @@
     </row>
     <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
-        <v>2925</v>
+        <v>2922</v>
       </c>
       <c r="B705" s="85" t="s">
         <v>1370</v>
@@ -42269,7 +42259,7 @@
     </row>
     <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
-        <v>2926</v>
+        <v>2923</v>
       </c>
       <c r="B706" s="85" t="s">
         <v>1370</v>
@@ -42298,7 +42288,7 @@
     </row>
     <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
-        <v>2927</v>
+        <v>2924</v>
       </c>
       <c r="B707" s="85" t="s">
         <v>1370</v>
@@ -42327,7 +42317,7 @@
     </row>
     <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
-        <v>2928</v>
+        <v>2925</v>
       </c>
       <c r="B708" s="85" t="s">
         <v>1370</v>
@@ -42356,7 +42346,7 @@
     </row>
     <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
-        <v>2929</v>
+        <v>2926</v>
       </c>
       <c r="B709" s="85" t="s">
         <v>1370</v>
@@ -42385,7 +42375,7 @@
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
-        <v>2930</v>
+        <v>2927</v>
       </c>
       <c r="B710" s="85" t="s">
         <v>1370</v>
@@ -42414,7 +42404,7 @@
     </row>
     <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
-        <v>2931</v>
+        <v>2928</v>
       </c>
       <c r="B711" s="85" t="s">
         <v>1370</v>
@@ -42443,7 +42433,7 @@
     </row>
     <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
-        <v>2932</v>
+        <v>2929</v>
       </c>
       <c r="B712" s="85" t="s">
         <v>1370</v>
@@ -42472,7 +42462,7 @@
     </row>
     <row r="713" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A713" s="29" t="s">
-        <v>2933</v>
+        <v>2930</v>
       </c>
       <c r="B713" s="85" t="s">
         <v>1370</v>
@@ -42501,7 +42491,7 @@
     </row>
     <row r="714" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A714" s="29" t="s">
-        <v>2934</v>
+        <v>2931</v>
       </c>
       <c r="B714" s="85" t="s">
         <v>1371</v>
@@ -42530,7 +42520,7 @@
     </row>
     <row r="715" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A715" s="29" t="s">
-        <v>2935</v>
+        <v>2932</v>
       </c>
       <c r="B715" s="85" t="s">
         <v>1371</v>
@@ -42559,7 +42549,7 @@
     </row>
     <row r="716" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A716" s="29" t="s">
-        <v>2936</v>
+        <v>2933</v>
       </c>
       <c r="B716" s="85" t="s">
         <v>1371</v>
@@ -42588,7 +42578,7 @@
     </row>
     <row r="717" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A717" s="29" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
       <c r="B717" s="85" t="s">
         <v>1371</v>
@@ -42617,7 +42607,7 @@
     </row>
     <row r="718" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A718" s="29" t="s">
-        <v>2938</v>
+        <v>2935</v>
       </c>
       <c r="B718" s="85" t="s">
         <v>1371</v>
@@ -42646,7 +42636,7 @@
     </row>
     <row r="719" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2939</v>
+        <v>2936</v>
       </c>
       <c r="B719" s="85" t="s">
         <v>1371</v>
@@ -42675,7 +42665,7 @@
     </row>
     <row r="720" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A720" s="29" t="s">
-        <v>2940</v>
+        <v>2937</v>
       </c>
       <c r="B720" s="85" t="s">
         <v>1371</v>
@@ -42704,7 +42694,7 @@
     </row>
     <row r="721" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
       <c r="B721" s="85" t="s">
         <v>1371</v>
@@ -45366,7 +45356,7 @@
     </row>
     <row r="801" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
-        <v>2942</v>
+        <v>2939</v>
       </c>
       <c r="B801" s="83" t="s">
         <v>1530</v>
@@ -45397,7 +45387,7 @@
     </row>
     <row r="802" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
-        <v>2943</v>
+        <v>2940</v>
       </c>
       <c r="B802" s="83" t="s">
         <v>1530</v>
@@ -45428,7 +45418,7 @@
     </row>
     <row r="803" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
-        <v>2944</v>
+        <v>2941</v>
       </c>
       <c r="B803" s="83" t="s">
         <v>1530</v>
@@ -45459,7 +45449,7 @@
     </row>
     <row r="804" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
-        <v>2945</v>
+        <v>2942</v>
       </c>
       <c r="B804" s="83" t="s">
         <v>1530</v>
@@ -45490,7 +45480,7 @@
     </row>
     <row r="805" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
-        <v>2946</v>
+        <v>2943</v>
       </c>
       <c r="B805" s="83" t="s">
         <v>1530</v>
@@ -45521,7 +45511,7 @@
     </row>
     <row r="806" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A806" s="29" t="s">
-        <v>2947</v>
+        <v>2944</v>
       </c>
       <c r="B806" s="85" t="s">
         <v>1485</v>
@@ -45550,7 +45540,7 @@
     </row>
     <row r="807" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A807" s="29" t="s">
-        <v>2948</v>
+        <v>2945</v>
       </c>
       <c r="B807" s="85" t="s">
         <v>1485</v>
@@ -45579,7 +45569,7 @@
     </row>
     <row r="808" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
-        <v>2949</v>
+        <v>2946</v>
       </c>
       <c r="B808" s="85" t="s">
         <v>1486</v>
@@ -45608,7 +45598,7 @@
     </row>
     <row r="809" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
-        <v>2950</v>
+        <v>2947</v>
       </c>
       <c r="B809" s="85" t="s">
         <v>1486</v>
@@ -45637,7 +45627,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2951</v>
+        <v>2948</v>
       </c>
       <c r="B810" s="85" t="s">
         <v>1489</v>
@@ -45666,7 +45656,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
@@ -45683,19 +45673,19 @@
     </row>
     <row r="812" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
-        <v>2952</v>
+        <v>2949</v>
       </c>
       <c r="B812" s="83" t="s">
         <v>1675</v>
       </c>
       <c r="C812" s="83" t="s">
-        <v>3000</v>
+        <v>2997</v>
       </c>
       <c r="D812" s="85" t="s">
         <v>1672</v>
       </c>
       <c r="E812" s="83" t="s">
-        <v>3001</v>
+        <v>2998</v>
       </c>
       <c r="F812" s="31" t="s">
         <v>231</v>
@@ -45706,7 +45696,7 @@
       <c r="H812" s="29"/>
       <c r="I812" s="29"/>
       <c r="J812" s="29" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="K812" s="29"/>
       <c r="L812" s="31"/>
@@ -45714,7 +45704,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
-        <v>3089</v>
+        <v>3086</v>
       </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
@@ -45826,7 +45816,7 @@
     </row>
     <row r="817" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
-        <v>2953</v>
+        <v>2950</v>
       </c>
       <c r="B817" s="96" t="s">
         <v>1674</v>
@@ -45857,7 +45847,7 @@
     </row>
     <row r="818" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
-        <v>2954</v>
+        <v>2951</v>
       </c>
       <c r="B818" s="83" t="s">
         <v>1675</v>
@@ -45888,7 +45878,7 @@
     </row>
     <row r="819" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A819" s="29" t="s">
-        <v>2955</v>
+        <v>2952</v>
       </c>
       <c r="B819" s="83" t="s">
         <v>1675</v>
@@ -46043,7 +46033,7 @@
     </row>
     <row r="824" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
-        <v>2956</v>
+        <v>2953</v>
       </c>
       <c r="B824" s="83" t="s">
         <v>1573</v>
@@ -46074,7 +46064,7 @@
     </row>
     <row r="825" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
-        <v>2957</v>
+        <v>2954</v>
       </c>
       <c r="B825" s="83" t="s">
         <v>1574</v>
@@ -46105,7 +46095,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2958</v>
+        <v>2955</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1577</v>
@@ -46136,7 +46126,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1578</v>
@@ -46167,7 +46157,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1579</v>
@@ -46196,7 +46186,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>2961</v>
+        <v>2958</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1579</v>
@@ -47220,7 +47210,7 @@
       <c r="D860" s="83"/>
       <c r="E860" s="83"/>
       <c r="F860" s="31" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="G860" s="31" t="s">
         <v>52</v>
@@ -47694,7 +47684,7 @@
         <v>96</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -47910,7 +47900,7 @@
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A881" s="29" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
@@ -50672,10 +50662,10 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A965" s="29" t="s">
-        <v>3023</v>
+        <v>3020</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3022</v>
+        <v>3019</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>335</v>
@@ -50701,10 +50691,10 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>3024</v>
+        <v>3021</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3022</v>
+        <v>3019</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>336</v>
@@ -50730,10 +50720,10 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A967" s="29" t="s">
-        <v>3025</v>
+        <v>3022</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3021</v>
+        <v>3018</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>335</v>
@@ -50759,10 +50749,10 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3021</v>
+        <v>3018</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>336</v>
@@ -50788,7 +50778,7 @@
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A969" s="29" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
@@ -50805,7 +50795,7 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A970" s="29" t="s">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>
@@ -50825,7 +50815,7 @@
         <v>1529</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3018</v>
+        <v>3015</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>760</v>
@@ -50855,10 +50845,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3019</v>
+        <v>3016</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>760</v>
@@ -50894,7 +50884,7 @@
         <v>1342</v>
       </c>
       <c r="D973" s="15" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="F973" t="s">
         <v>1550</v>
@@ -55944,7 +55934,7 @@
         <v>1528</v>
       </c>
       <c r="D1126" s="29" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="E1126" s="82" t="s">
         <v>2182</v>
@@ -55982,7 +55972,7 @@
         <v>1342</v>
       </c>
       <c r="E1127" s="83" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="F1127" s="31" t="s">
         <v>1651</v>
@@ -56003,44 +55993,24 @@
     </row>
     <row r="1128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1128" s="29" t="s">
-        <v>2557</v>
-      </c>
-      <c r="B1128" s="100" t="s">
-        <v>1674</v>
-      </c>
-      <c r="C1128" s="83" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D1128" s="85" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1128" s="83" t="s">
-        <v>2182</v>
-      </c>
-      <c r="F1128" s="31" t="s">
-        <v>1651</v>
-      </c>
-      <c r="G1128" s="31" t="s">
-        <v>1478</v>
-      </c>
-      <c r="H1128" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1128" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1128" s="29" t="s">
-        <v>2555</v>
-      </c>
-      <c r="K1128" s="29" t="s">
-        <v>2556</v>
-      </c>
+        <v>3209</v>
+      </c>
+      <c r="B1128" s="100"/>
+      <c r="C1128" s="83"/>
+      <c r="D1128" s="85"/>
+      <c r="E1128" s="83"/>
+      <c r="F1128" s="31"/>
+      <c r="G1128" s="31"/>
+      <c r="H1128" s="29"/>
+      <c r="I1128" s="119"/>
+      <c r="J1128" s="29"/>
+      <c r="K1128" s="29"/>
       <c r="L1128" s="31"/>
       <c r="M1128" s="29"/>
     </row>
     <row r="1129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1129" s="29" t="s">
-        <v>2558</v>
+        <v>2555</v>
       </c>
       <c r="B1129" s="100" t="s">
         <v>1675</v>
@@ -56075,7 +56045,7 @@
     </row>
     <row r="1130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1130" s="29" t="s">
-        <v>2559</v>
+        <v>2556</v>
       </c>
       <c r="B1130" s="100" t="s">
         <v>1675</v>
@@ -56110,13 +56080,13 @@
     </row>
     <row r="1131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1131" s="29" t="s">
-        <v>2560</v>
+        <v>2557</v>
       </c>
       <c r="B1131" s="100" t="s">
         <v>1675</v>
       </c>
       <c r="C1131" s="83" t="s">
-        <v>2564</v>
+        <v>2561</v>
       </c>
       <c r="D1131" s="85" t="s">
         <v>332</v>
@@ -56145,7 +56115,7 @@
     </row>
     <row r="1132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1132" s="29" t="s">
-        <v>2561</v>
+        <v>2558</v>
       </c>
       <c r="B1132" s="100" t="s">
         <v>1675</v>
@@ -56180,7 +56150,7 @@
     </row>
     <row r="1133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1133" s="29" t="s">
-        <v>2562</v>
+        <v>2559</v>
       </c>
       <c r="B1133" s="100" t="s">
         <v>1675</v>
@@ -56215,7 +56185,7 @@
     </row>
     <row r="1134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1134" s="29" t="s">
-        <v>2563</v>
+        <v>2560</v>
       </c>
       <c r="B1134" s="100" t="s">
         <v>1675</v>
@@ -56250,7 +56220,7 @@
     </row>
     <row r="1135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1135" s="29" t="s">
-        <v>2567</v>
+        <v>2564</v>
       </c>
       <c r="B1135" s="100" t="s">
         <v>2033</v>
@@ -56275,7 +56245,7 @@
         <v>96</v>
       </c>
       <c r="J1135" s="29" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="K1135" s="29"/>
       <c r="L1135" s="31"/>
@@ -56283,7 +56253,7 @@
     </row>
     <row r="1136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1136" s="29" t="s">
-        <v>2568</v>
+        <v>2565</v>
       </c>
       <c r="B1136" s="100" t="s">
         <v>55</v>
@@ -56308,7 +56278,7 @@
         <v>96</v>
       </c>
       <c r="J1136" s="29" t="s">
-        <v>2566</v>
+        <v>2563</v>
       </c>
       <c r="K1136" s="29"/>
       <c r="L1136" s="31"/>
@@ -56316,7 +56286,7 @@
     </row>
     <row r="1137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1137" s="29" t="s">
-        <v>2570</v>
+        <v>2567</v>
       </c>
       <c r="B1137" s="31" t="s">
         <v>2473</v>
@@ -56349,7 +56319,7 @@
     </row>
     <row r="1138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1138" s="29" t="s">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="B1138" s="31" t="s">
         <v>2473</v>
@@ -56382,7 +56352,7 @@
     </row>
     <row r="1139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1139" s="29" t="s">
-        <v>2572</v>
+        <v>2569</v>
       </c>
       <c r="B1139" s="31" t="s">
         <v>2473</v>
@@ -56415,7 +56385,7 @@
     </row>
     <row r="1140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1140" s="29" t="s">
-        <v>2573</v>
+        <v>2570</v>
       </c>
       <c r="B1140" s="31" t="s">
         <v>2473</v>
@@ -56448,7 +56418,7 @@
     </row>
     <row r="1141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1141" s="29" t="s">
-        <v>2574</v>
+        <v>2571</v>
       </c>
       <c r="B1141" s="31" t="s">
         <v>2473</v>
@@ -56481,7 +56451,7 @@
     </row>
     <row r="1142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1142" s="29" t="s">
-        <v>2575</v>
+        <v>2572</v>
       </c>
       <c r="B1142" s="31" t="s">
         <v>2473</v>
@@ -56514,7 +56484,7 @@
     </row>
     <row r="1143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1143" s="29" t="s">
-        <v>2576</v>
+        <v>2573</v>
       </c>
       <c r="B1143" s="31" t="s">
         <v>2473</v>
@@ -56547,7 +56517,7 @@
     </row>
     <row r="1144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1144" s="29" t="s">
-        <v>2577</v>
+        <v>2574</v>
       </c>
       <c r="B1144" s="31" t="s">
         <v>2473</v>
@@ -56580,7 +56550,7 @@
     </row>
     <row r="1145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1145" s="29" t="s">
-        <v>2578</v>
+        <v>2575</v>
       </c>
       <c r="B1145" s="31" t="s">
         <v>2473</v>
@@ -56613,7 +56583,7 @@
     </row>
     <row r="1146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1146" s="29" t="s">
-        <v>2579</v>
+        <v>2576</v>
       </c>
       <c r="B1146" s="31" t="s">
         <v>2473</v>
@@ -56646,7 +56616,7 @@
     </row>
     <row r="1147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1147" s="29" t="s">
-        <v>2580</v>
+        <v>2577</v>
       </c>
       <c r="B1147" s="31" t="s">
         <v>2473</v>
@@ -56679,7 +56649,7 @@
     </row>
     <row r="1148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1148" s="29" t="s">
-        <v>2581</v>
+        <v>2578</v>
       </c>
       <c r="B1148" s="31" t="s">
         <v>2473</v>
@@ -56712,7 +56682,7 @@
     </row>
     <row r="1149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1149" s="29" t="s">
-        <v>2582</v>
+        <v>2579</v>
       </c>
       <c r="B1149" s="31" t="s">
         <v>2473</v>
@@ -56745,7 +56715,7 @@
     </row>
     <row r="1150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1150" s="29" t="s">
-        <v>2583</v>
+        <v>2580</v>
       </c>
       <c r="B1150" s="31" t="s">
         <v>2473</v>
@@ -56778,7 +56748,7 @@
     </row>
     <row r="1151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1151" s="29" t="s">
-        <v>2584</v>
+        <v>2581</v>
       </c>
       <c r="B1151" s="31" t="s">
         <v>2473</v>
@@ -56811,7 +56781,7 @@
     </row>
     <row r="1152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1152" s="29" t="s">
-        <v>2585</v>
+        <v>2582</v>
       </c>
       <c r="B1152" s="31" t="s">
         <v>2473</v>
@@ -56844,7 +56814,7 @@
     </row>
     <row r="1153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1153" s="29" t="s">
-        <v>2586</v>
+        <v>2583</v>
       </c>
       <c r="B1153" s="31" t="s">
         <v>2473</v>
@@ -56877,7 +56847,7 @@
     </row>
     <row r="1154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1154" s="29" t="s">
-        <v>2587</v>
+        <v>2584</v>
       </c>
       <c r="B1154" s="31" t="s">
         <v>2473</v>
@@ -56910,7 +56880,7 @@
     </row>
     <row r="1155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1155" s="29" t="s">
-        <v>2588</v>
+        <v>2585</v>
       </c>
       <c r="B1155" s="31" t="s">
         <v>2473</v>
@@ -56943,7 +56913,7 @@
     </row>
     <row r="1156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1156" s="29" t="s">
-        <v>2589</v>
+        <v>2586</v>
       </c>
       <c r="B1156" s="31" t="s">
         <v>2473</v>
@@ -56976,7 +56946,7 @@
     </row>
     <row r="1157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1157" s="29" t="s">
-        <v>2590</v>
+        <v>2587</v>
       </c>
       <c r="B1157" s="31" t="s">
         <v>2473</v>
@@ -57009,7 +56979,7 @@
     </row>
     <row r="1158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1158" s="29" t="s">
-        <v>2591</v>
+        <v>2588</v>
       </c>
       <c r="B1158" s="31" t="s">
         <v>2473</v>
@@ -57042,7 +57012,7 @@
     </row>
     <row r="1159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1159" s="29" t="s">
-        <v>2592</v>
+        <v>2589</v>
       </c>
       <c r="B1159" s="31" t="s">
         <v>2473</v>
@@ -57075,7 +57045,7 @@
     </row>
     <row r="1160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1160" s="29" t="s">
-        <v>2593</v>
+        <v>2590</v>
       </c>
       <c r="B1160" s="31" t="s">
         <v>2473</v>
@@ -57108,7 +57078,7 @@
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1161" s="29" t="s">
-        <v>3177</v>
+        <v>3174</v>
       </c>
       <c r="B1161" s="85" t="s">
         <v>1674</v>
@@ -57117,7 +57087,7 @@
         <v>1247</v>
       </c>
       <c r="D1161" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1161" s="83" t="s">
         <v>2286</v>
@@ -57135,15 +57105,15 @@
         <v>60</v>
       </c>
       <c r="J1161" s="29" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="K1161" s="29"/>
-      <c r="L1161" s="134"/>
+      <c r="L1161" s="31"/>
       <c r="M1161" s="29"/>
     </row>
     <row r="1162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1162" s="29" t="s">
-        <v>3178</v>
+        <v>3175</v>
       </c>
       <c r="B1162" s="85" t="s">
         <v>1674</v>
@@ -57152,7 +57122,7 @@
         <v>1249</v>
       </c>
       <c r="D1162" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1162" s="83" t="s">
         <v>2287</v>
@@ -57170,15 +57140,15 @@
         <v>60</v>
       </c>
       <c r="J1162" s="29" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="K1162" s="29"/>
-      <c r="L1162" s="134"/>
+      <c r="L1162" s="31"/>
       <c r="M1162" s="29"/>
     </row>
     <row r="1163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1163" s="29" t="s">
-        <v>3179</v>
+        <v>3176</v>
       </c>
       <c r="B1163" s="85" t="s">
         <v>1674</v>
@@ -57187,7 +57157,7 @@
         <v>1223</v>
       </c>
       <c r="D1163" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1163" s="83" t="s">
         <v>2288</v>
@@ -57205,15 +57175,15 @@
         <v>60</v>
       </c>
       <c r="J1163" s="29" t="s">
-        <v>2599</v>
+        <v>2596</v>
       </c>
       <c r="K1163" s="29"/>
-      <c r="L1163" s="134"/>
+      <c r="L1163" s="31"/>
       <c r="M1163" s="29"/>
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1164" s="29" t="s">
-        <v>3180</v>
+        <v>3177</v>
       </c>
       <c r="B1164" s="85" t="s">
         <v>1674</v>
@@ -57222,7 +57192,7 @@
         <v>1225</v>
       </c>
       <c r="D1164" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1164" s="83" t="s">
         <v>2289</v>
@@ -57240,15 +57210,15 @@
         <v>60</v>
       </c>
       <c r="J1164" s="29" t="s">
-        <v>2600</v>
+        <v>2597</v>
       </c>
       <c r="K1164" s="29"/>
-      <c r="L1164" s="134"/>
+      <c r="L1164" s="31"/>
       <c r="M1164" s="29"/>
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1165" s="29" t="s">
-        <v>3181</v>
+        <v>3178</v>
       </c>
       <c r="B1165" s="85" t="s">
         <v>1674</v>
@@ -57257,7 +57227,7 @@
         <v>1227</v>
       </c>
       <c r="D1165" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1165" s="83" t="s">
         <v>2285</v>
@@ -57275,15 +57245,15 @@
         <v>60</v>
       </c>
       <c r="J1165" s="29" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="K1165" s="29"/>
-      <c r="L1165" s="134"/>
+      <c r="L1165" s="31"/>
       <c r="M1165" s="29"/>
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1166" s="29" t="s">
-        <v>3182</v>
+        <v>3179</v>
       </c>
       <c r="B1166" s="85" t="s">
         <v>1674</v>
@@ -57292,7 +57262,7 @@
         <v>1229</v>
       </c>
       <c r="D1166" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1166" s="83" t="s">
         <v>2386</v>
@@ -57310,15 +57280,15 @@
         <v>60</v>
       </c>
       <c r="J1166" s="29" t="s">
-        <v>2601</v>
+        <v>2598</v>
       </c>
       <c r="K1166" s="29"/>
-      <c r="L1166" s="134"/>
+      <c r="L1166" s="31"/>
       <c r="M1166" s="29"/>
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1167" s="29" t="s">
-        <v>3183</v>
+        <v>3180</v>
       </c>
       <c r="B1167" s="85" t="s">
         <v>1674</v>
@@ -57327,7 +57297,7 @@
         <v>1231</v>
       </c>
       <c r="D1167" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1167" s="83" t="s">
         <v>2282</v>
@@ -57345,15 +57315,15 @@
         <v>60</v>
       </c>
       <c r="J1167" s="29" t="s">
-        <v>2602</v>
+        <v>2599</v>
       </c>
       <c r="K1167" s="29"/>
-      <c r="L1167" s="134"/>
+      <c r="L1167" s="31"/>
       <c r="M1167" s="29"/>
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1168" s="29" t="s">
-        <v>3184</v>
+        <v>3181</v>
       </c>
       <c r="B1168" s="85" t="s">
         <v>1674</v>
@@ -57362,7 +57332,7 @@
         <v>1256</v>
       </c>
       <c r="D1168" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1168" s="83" t="s">
         <v>2283</v>
@@ -57380,15 +57350,15 @@
         <v>60</v>
       </c>
       <c r="J1168" s="29" t="s">
-        <v>2603</v>
+        <v>2600</v>
       </c>
       <c r="K1168" s="29"/>
-      <c r="L1168" s="134"/>
+      <c r="L1168" s="31"/>
       <c r="M1168" s="29"/>
     </row>
     <row r="1169" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="29" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="B1169" s="85" t="s">
         <v>1674</v>
@@ -57397,7 +57367,7 @@
         <v>1258</v>
       </c>
       <c r="D1169" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1169" s="83" t="s">
         <v>2284</v>
@@ -57415,15 +57385,15 @@
         <v>60</v>
       </c>
       <c r="J1169" s="29" t="s">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="K1169" s="29"/>
-      <c r="L1169" s="134"/>
+      <c r="L1169" s="31"/>
       <c r="M1169" s="29"/>
     </row>
     <row r="1170" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="29" t="s">
-        <v>3186</v>
+        <v>3183</v>
       </c>
       <c r="B1170" s="85" t="s">
         <v>1674</v>
@@ -57432,7 +57402,7 @@
         <v>1260</v>
       </c>
       <c r="D1170" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1170" s="83" t="s">
         <v>2387</v>
@@ -57450,15 +57420,15 @@
         <v>60</v>
       </c>
       <c r="J1170" s="29" t="s">
-        <v>2605</v>
+        <v>2602</v>
       </c>
       <c r="K1170" s="29"/>
-      <c r="L1170" s="134"/>
+      <c r="L1170" s="31"/>
       <c r="M1170" s="29"/>
     </row>
     <row r="1171" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="29" t="s">
-        <v>3187</v>
+        <v>3184</v>
       </c>
       <c r="B1171" s="85" t="s">
         <v>1674</v>
@@ -57467,7 +57437,7 @@
         <v>1262</v>
       </c>
       <c r="D1171" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1171" s="83" t="s">
         <v>1847</v>
@@ -57485,15 +57455,15 @@
         <v>60</v>
       </c>
       <c r="J1171" s="29" t="s">
-        <v>2606</v>
+        <v>2603</v>
       </c>
       <c r="K1171" s="29"/>
-      <c r="L1171" s="134"/>
+      <c r="L1171" s="31"/>
       <c r="M1171" s="29"/>
     </row>
     <row r="1172" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="29" t="s">
-        <v>3188</v>
+        <v>3185</v>
       </c>
       <c r="B1172" s="85" t="s">
         <v>1674</v>
@@ -57502,7 +57472,7 @@
         <v>1264</v>
       </c>
       <c r="D1172" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1172" s="83" t="s">
         <v>2267</v>
@@ -57520,15 +57490,15 @@
         <v>60</v>
       </c>
       <c r="J1172" s="29" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="K1172" s="29"/>
-      <c r="L1172" s="134"/>
+      <c r="L1172" s="31"/>
       <c r="M1172" s="29"/>
     </row>
     <row r="1173" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="29" t="s">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="B1173" s="85" t="s">
         <v>1674</v>
@@ -57537,7 +57507,7 @@
         <v>1291</v>
       </c>
       <c r="D1173" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1173" s="83" t="s">
         <v>1854</v>
@@ -57555,15 +57525,15 @@
         <v>60</v>
       </c>
       <c r="J1173" s="29" t="s">
-        <v>2608</v>
+        <v>2605</v>
       </c>
       <c r="K1173" s="29"/>
-      <c r="L1173" s="134"/>
+      <c r="L1173" s="31"/>
       <c r="M1173" s="29"/>
     </row>
     <row r="1174" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>3190</v>
+        <v>3187</v>
       </c>
       <c r="B1174" s="85" t="s">
         <v>1674</v>
@@ -57572,7 +57542,7 @@
         <v>1293</v>
       </c>
       <c r="D1174" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1174" s="83" t="s">
         <v>1855</v>
@@ -57590,15 +57560,15 @@
         <v>60</v>
       </c>
       <c r="J1174" s="29" t="s">
-        <v>2607</v>
+        <v>2604</v>
       </c>
       <c r="K1174" s="29"/>
-      <c r="L1174" s="134"/>
+      <c r="L1174" s="31"/>
       <c r="M1174" s="29"/>
     </row>
     <row r="1175" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="29" t="s">
-        <v>3191</v>
+        <v>3188</v>
       </c>
       <c r="B1175" s="85" t="s">
         <v>1674</v>
@@ -57607,7 +57577,7 @@
         <v>1295</v>
       </c>
       <c r="D1175" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1175" s="83" t="s">
         <v>2264</v>
@@ -57625,15 +57595,15 @@
         <v>60</v>
       </c>
       <c r="J1175" s="29" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="K1175" s="29"/>
-      <c r="L1175" s="134"/>
+      <c r="L1175" s="31"/>
       <c r="M1175" s="29"/>
     </row>
     <row r="1176" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>3192</v>
+        <v>3189</v>
       </c>
       <c r="B1176" s="85" t="s">
         <v>1674</v>
@@ -57642,7 +57612,7 @@
         <v>1297</v>
       </c>
       <c r="D1176" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1176" s="83" t="s">
         <v>2263</v>
@@ -57660,15 +57630,15 @@
         <v>60</v>
       </c>
       <c r="J1176" s="29" t="s">
-        <v>2609</v>
+        <v>2606</v>
       </c>
       <c r="K1176" s="29"/>
-      <c r="L1176" s="134"/>
+      <c r="L1176" s="31"/>
       <c r="M1176" s="29"/>
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
       <c r="B1177" s="85" t="s">
         <v>1674</v>
@@ -57677,7 +57647,7 @@
         <v>1299</v>
       </c>
       <c r="D1177" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1177" s="83" t="s">
         <v>1860</v>
@@ -57695,24 +57665,24 @@
         <v>60</v>
       </c>
       <c r="J1177" s="29" t="s">
-        <v>2610</v>
+        <v>2607</v>
       </c>
       <c r="K1177" s="29"/>
-      <c r="L1177" s="134"/>
+      <c r="L1177" s="31"/>
       <c r="M1177" s="29"/>
     </row>
     <row r="1178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1178" s="29" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="B1178" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1178" s="83" t="s">
         <v>2395</v>
       </c>
       <c r="D1178" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1178" s="83" t="s">
         <v>1857</v>
@@ -57730,7 +57700,7 @@
         <v>60</v>
       </c>
       <c r="J1178" s="29" t="s">
-        <v>2611</v>
+        <v>2608</v>
       </c>
       <c r="K1178" s="29"/>
       <c r="L1178" s="31"/>
@@ -57738,16 +57708,16 @@
     </row>
     <row r="1179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1179" s="29" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="B1179" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1179" s="83" t="s">
         <v>2396</v>
       </c>
       <c r="D1179" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1179" s="83" t="s">
         <v>2395</v>
@@ -57765,7 +57735,7 @@
         <v>60</v>
       </c>
       <c r="J1179" s="29" t="s">
-        <v>2612</v>
+        <v>2609</v>
       </c>
       <c r="K1179" s="29"/>
       <c r="L1179" s="31"/>
@@ -57773,16 +57743,16 @@
     </row>
     <row r="1180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1180" s="29" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="B1180" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1180" s="83" t="s">
         <v>2397</v>
       </c>
       <c r="D1180" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1180" s="83" t="s">
         <v>2396</v>
@@ -57800,7 +57770,7 @@
         <v>60</v>
       </c>
       <c r="J1180" s="29" t="s">
-        <v>2613</v>
+        <v>2610</v>
       </c>
       <c r="K1180" s="29"/>
       <c r="L1180" s="31"/>
@@ -57808,16 +57778,16 @@
     </row>
     <row r="1181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1181" s="29" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="B1181" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1181" s="83" t="s">
         <v>2398</v>
       </c>
       <c r="D1181" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1181" s="83" t="s">
         <v>2397</v>
@@ -57835,7 +57805,7 @@
         <v>60</v>
       </c>
       <c r="J1181" s="29" t="s">
-        <v>2614</v>
+        <v>2611</v>
       </c>
       <c r="K1181" s="29"/>
       <c r="L1181" s="31"/>
@@ -57843,10 +57813,10 @@
     </row>
     <row r="1182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1182" s="29" t="s">
-        <v>2615</v>
+        <v>2612</v>
       </c>
       <c r="B1182" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1182" s="83" t="s">
         <v>2392</v>
@@ -57868,10 +57838,10 @@
     </row>
     <row r="1183" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="29" t="s">
-        <v>2616</v>
+        <v>2613</v>
       </c>
       <c r="B1183" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="C1183" s="83" t="s">
         <v>2393</v>
@@ -57893,10 +57863,10 @@
     </row>
     <row r="1184" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="29" t="s">
-        <v>2617</v>
+        <v>2614</v>
       </c>
       <c r="B1184" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1184" s="83" t="s">
         <v>2398</v>
@@ -57921,17 +57891,17 @@
       </c>
       <c r="J1184" s="29"/>
       <c r="K1184" s="29" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="L1184" s="31"/>
       <c r="M1184" s="29"/>
     </row>
     <row r="1185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1185" s="29" t="s">
-        <v>2618</v>
+        <v>2615</v>
       </c>
       <c r="B1185" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1185" s="83" t="s">
         <v>2399</v>
@@ -57956,17 +57926,17 @@
       </c>
       <c r="J1185" s="29"/>
       <c r="K1185" s="29" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="L1185" s="31"/>
       <c r="M1185" s="29"/>
     </row>
     <row r="1186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1186" s="29" t="s">
-        <v>2619</v>
+        <v>2616</v>
       </c>
       <c r="B1186" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1186" s="83" t="s">
         <v>2400</v>
@@ -57991,17 +57961,17 @@
       </c>
       <c r="J1186" s="29"/>
       <c r="K1186" s="29" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="L1186" s="31"/>
       <c r="M1186" s="29"/>
     </row>
     <row r="1187" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1187" s="29" t="s">
-        <v>2620</v>
+        <v>2617</v>
       </c>
       <c r="B1187" s="85" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1187" s="83" t="s">
         <v>2401</v>
@@ -58026,26 +57996,26 @@
       </c>
       <c r="J1187" s="29"/>
       <c r="K1187" s="29" t="s">
-        <v>2621</v>
+        <v>2618</v>
       </c>
       <c r="L1187" s="31"/>
       <c r="M1187" s="29"/>
     </row>
     <row r="1188" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="29" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B1188" s="80" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C1188" s="83" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D1188" s="85" t="s">
         <v>2624</v>
       </c>
-      <c r="B1188" s="80" t="s">
+      <c r="E1188" s="83" t="s">
         <v>2625</v>
-      </c>
-      <c r="C1188" s="83" t="s">
-        <v>2626</v>
-      </c>
-      <c r="D1188" s="85" t="s">
-        <v>2627</v>
-      </c>
-      <c r="E1188" s="83" t="s">
-        <v>2628</v>
       </c>
       <c r="F1188" s="31"/>
       <c r="G1188" s="31" t="s">
@@ -58064,10 +58034,10 @@
     </row>
     <row r="1189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1189" s="29" t="s">
-        <v>2630</v>
+        <v>2627</v>
       </c>
       <c r="B1189" s="85" t="s">
-        <v>2627</v>
+        <v>2624</v>
       </c>
       <c r="C1189" s="83" t="s">
         <v>2182</v>
@@ -58076,7 +58046,7 @@
         <v>1674</v>
       </c>
       <c r="E1189" s="83" t="s">
-        <v>2629</v>
+        <v>2626</v>
       </c>
       <c r="F1189" s="31"/>
       <c r="G1189" s="31" t="s">
@@ -58095,16 +58065,16 @@
     </row>
     <row r="1190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1190" s="29" t="s">
-        <v>2633</v>
+        <v>2630</v>
       </c>
       <c r="B1190" s="100" t="s">
         <v>1674</v>
       </c>
       <c r="C1190" s="83" t="s">
-        <v>2632</v>
+        <v>2629</v>
       </c>
       <c r="D1190" s="85" t="s">
-        <v>2631</v>
+        <v>2628</v>
       </c>
       <c r="E1190" s="83" t="s">
         <v>2182</v>
@@ -58128,16 +58098,16 @@
     </row>
     <row r="1191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1191" s="29" t="s">
-        <v>2636</v>
+        <v>2633</v>
       </c>
       <c r="B1191" s="100" t="s">
         <v>1674</v>
       </c>
       <c r="C1191" s="83" t="s">
-        <v>2634</v>
+        <v>2631</v>
       </c>
       <c r="D1191" s="85" t="s">
-        <v>2635</v>
+        <v>2632</v>
       </c>
       <c r="E1191" s="83" t="s">
         <v>1478</v>
@@ -58161,7 +58131,7 @@
     </row>
     <row r="1192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1192" s="29" t="s">
-        <v>2637</v>
+        <v>2634</v>
       </c>
       <c r="B1192" s="100"/>
       <c r="C1192" s="83"/>
@@ -58190,7 +58160,7 @@
     </row>
     <row r="1193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1193" s="29" t="s">
-        <v>2638</v>
+        <v>2635</v>
       </c>
       <c r="B1193" s="100"/>
       <c r="C1193" s="83"/>
@@ -58203,7 +58173,7 @@
         <v>30</v>
       </c>
       <c r="H1193" s="29" t="s">
-        <v>2639</v>
+        <v>2636</v>
       </c>
       <c r="I1193" s="119" t="s">
         <v>96</v>
@@ -58219,7 +58189,7 @@
     </row>
     <row r="1194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1194" s="29" t="s">
-        <v>2641</v>
+        <v>2638</v>
       </c>
       <c r="B1194" s="100"/>
       <c r="C1194" s="83"/>
@@ -58248,7 +58218,7 @@
     </row>
     <row r="1195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1195" s="29" t="s">
-        <v>2642</v>
+        <v>2639</v>
       </c>
       <c r="B1195" s="100"/>
       <c r="C1195" s="83"/>
@@ -58277,16 +58247,16 @@
     </row>
     <row r="1196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1196" s="29" t="s">
-        <v>2644</v>
+        <v>2641</v>
       </c>
       <c r="B1196" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1196" s="83" t="s">
         <v>2264</v>
       </c>
       <c r="D1196" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1196" s="83" t="s">
         <v>2294</v>
@@ -58310,16 +58280,16 @@
     </row>
     <row r="1197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1197" s="29" t="s">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="B1197" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1197" s="83" t="s">
         <v>2263</v>
       </c>
       <c r="D1197" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1197" s="83" t="s">
         <v>2383</v>
@@ -58343,16 +58313,16 @@
     </row>
     <row r="1198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1198" s="29" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="B1198" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1198" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1198" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1198" s="83" t="s">
         <v>1857</v>
@@ -58376,16 +58346,16 @@
     </row>
     <row r="1199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1199" s="29" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="B1199" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1199" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1199" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1199" s="83" t="s">
         <v>2395</v>
@@ -58409,16 +58379,16 @@
     </row>
     <row r="1200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1200" s="29" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="B1200" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1200" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1200" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1200" s="83" t="s">
         <v>2396</v>
@@ -58442,16 +58412,16 @@
     </row>
     <row r="1201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1201" s="29" t="s">
-        <v>2649</v>
+        <v>2646</v>
       </c>
       <c r="B1201" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1201" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1201" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1201" s="83" t="s">
         <v>2397</v>
@@ -58475,16 +58445,16 @@
     </row>
     <row r="1202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1202" s="29" t="s">
-        <v>2650</v>
+        <v>2647</v>
       </c>
       <c r="B1202" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1202" s="83" t="s">
         <v>2391</v>
       </c>
       <c r="D1202" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1202" s="83" t="s">
         <v>2398</v>
@@ -58508,16 +58478,16 @@
     </row>
     <row r="1203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1203" s="29" t="s">
-        <v>2651</v>
+        <v>2648</v>
       </c>
       <c r="B1203" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1203" s="83" t="s">
         <v>2392</v>
       </c>
       <c r="D1203" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1203" s="83" t="s">
         <v>2399</v>
@@ -58541,16 +58511,16 @@
     </row>
     <row r="1204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1204" s="29" t="s">
-        <v>2652</v>
+        <v>2649</v>
       </c>
       <c r="B1204" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1204" s="83" t="s">
         <v>2393</v>
       </c>
       <c r="D1204" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1204" s="83" t="s">
         <v>2400</v>
@@ -58574,16 +58544,16 @@
     </row>
     <row r="1205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1205" s="29" t="s">
-        <v>2653</v>
+        <v>2650</v>
       </c>
       <c r="B1205" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1205" s="83" t="s">
         <v>2394</v>
       </c>
       <c r="D1205" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1205" s="83" t="s">
         <v>2401</v>
@@ -58607,16 +58577,16 @@
     </row>
     <row r="1206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1206" s="29" t="s">
-        <v>2654</v>
+        <v>2651</v>
       </c>
       <c r="B1206" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1206" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1206" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1206" s="83" t="s">
         <v>2391</v>
@@ -58640,16 +58610,16 @@
     </row>
     <row r="1207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1207" s="29" t="s">
-        <v>2655</v>
+        <v>2652</v>
       </c>
       <c r="B1207" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1207" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1207" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1207" s="83" t="s">
         <v>2392</v>
@@ -58673,16 +58643,16 @@
     </row>
     <row r="1208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1208" s="29" t="s">
-        <v>2656</v>
+        <v>2653</v>
       </c>
       <c r="B1208" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1208" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1208" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1208" s="83" t="s">
         <v>2393</v>
@@ -58706,16 +58676,16 @@
     </row>
     <row r="1209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1209" s="29" t="s">
-        <v>2657</v>
+        <v>2654</v>
       </c>
       <c r="B1209" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="C1209" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1209" s="100" t="s">
-        <v>2643</v>
+        <v>2640</v>
       </c>
       <c r="E1209" s="83" t="s">
         <v>2394</v>
@@ -58739,7 +58709,7 @@
     </row>
     <row r="1210" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="29" t="s">
-        <v>2778</v>
+        <v>2775</v>
       </c>
       <c r="B1210" s="100"/>
       <c r="C1210" s="83"/>
@@ -58761,32 +58731,32 @@
         <v>439</v>
       </c>
       <c r="K1210" s="29" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
       <c r="L1210" s="31"/>
       <c r="M1210" s="29"/>
     </row>
     <row r="1211" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1211" s="29" t="s">
-        <v>2782</v>
+        <v>2779</v>
       </c>
       <c r="B1211" s="112" t="s">
-        <v>2798</v>
+        <v>2795</v>
       </c>
       <c r="C1211" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1211" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1211" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1211" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1211" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1211" s="29">
         <v>0</v>
@@ -58803,25 +58773,25 @@
     </row>
     <row r="1212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1212" s="29" t="s">
-        <v>2783</v>
+        <v>2780</v>
       </c>
       <c r="B1212" s="100" t="s">
-        <v>2799</v>
+        <v>2796</v>
       </c>
       <c r="C1212" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1212" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1212" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1212" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1212" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1212" s="29">
         <v>0</v>
@@ -58838,25 +58808,25 @@
     </row>
     <row r="1213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1213" s="29" t="s">
-        <v>2784</v>
+        <v>2781</v>
       </c>
       <c r="B1213" s="100" t="s">
-        <v>2800</v>
+        <v>2797</v>
       </c>
       <c r="C1213" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1213" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1213" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1213" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1213" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1213" s="29">
         <v>0</v>
@@ -58873,25 +58843,25 @@
     </row>
     <row r="1214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1214" s="29" t="s">
-        <v>2785</v>
+        <v>2782</v>
       </c>
       <c r="B1214" s="100" t="s">
-        <v>2801</v>
+        <v>2798</v>
       </c>
       <c r="C1214" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1214" s="100" t="s">
         <v>328</v>
       </c>
       <c r="E1214" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1214" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1214" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1214" s="29">
         <v>0</v>
@@ -58908,25 +58878,25 @@
     </row>
     <row r="1215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1215" s="29" t="s">
-        <v>2786</v>
+        <v>2783</v>
       </c>
       <c r="B1215" s="100" t="s">
-        <v>2802</v>
+        <v>2799</v>
       </c>
       <c r="C1215" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1215" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1215" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1215" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1215" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1215" s="29">
         <v>0</v>
@@ -58943,25 +58913,25 @@
     </row>
     <row r="1216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1216" s="29" t="s">
-        <v>2787</v>
+        <v>2784</v>
       </c>
       <c r="B1216" s="100" t="s">
-        <v>2803</v>
+        <v>2800</v>
       </c>
       <c r="C1216" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1216" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1216" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1216" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1216" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1216" s="29">
         <v>0</v>
@@ -58978,25 +58948,25 @@
     </row>
     <row r="1217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1217" s="29" t="s">
-        <v>2788</v>
+        <v>2785</v>
       </c>
       <c r="B1217" s="100" t="s">
-        <v>2804</v>
+        <v>2801</v>
       </c>
       <c r="C1217" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1217" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1217" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1217" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1217" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1217" s="29">
         <v>0</v>
@@ -59013,25 +58983,25 @@
     </row>
     <row r="1218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1218" s="29" t="s">
-        <v>2789</v>
+        <v>2786</v>
       </c>
       <c r="B1218" s="100" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="C1218" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1218" s="100" t="s">
         <v>332</v>
       </c>
       <c r="E1218" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1218" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1218" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1218" s="29">
         <v>0</v>
@@ -59048,25 +59018,25 @@
     </row>
     <row r="1219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1219" s="29" t="s">
-        <v>2790</v>
+        <v>2787</v>
       </c>
       <c r="B1219" s="100" t="s">
-        <v>2806</v>
+        <v>2803</v>
       </c>
       <c r="C1219" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1219" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1219" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1219" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1219" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1219" s="29">
         <v>0</v>
@@ -59083,25 +59053,25 @@
     </row>
     <row r="1220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1220" s="29" t="s">
-        <v>2791</v>
+        <v>2788</v>
       </c>
       <c r="B1220" s="100" t="s">
-        <v>2807</v>
+        <v>2804</v>
       </c>
       <c r="C1220" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1220" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1220" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1220" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1220" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1220" s="29">
         <v>0</v>
@@ -59118,25 +59088,25 @@
     </row>
     <row r="1221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1221" s="29" t="s">
-        <v>2792</v>
+        <v>2789</v>
       </c>
       <c r="B1221" s="83" t="s">
         <v>2189</v>
       </c>
       <c r="C1221" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1221" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1221" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1221" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1221" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1221" s="29">
         <v>0</v>
@@ -59153,25 +59123,25 @@
     </row>
     <row r="1222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1222" s="29" t="s">
-        <v>2793</v>
+        <v>2790</v>
       </c>
       <c r="B1222" s="83" t="s">
-        <v>3029</v>
+        <v>3026</v>
       </c>
       <c r="C1222" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1222" s="100" t="s">
         <v>333</v>
       </c>
       <c r="E1222" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1222" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1222" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1222" s="29">
         <v>0</v>
@@ -59188,25 +59158,25 @@
     </row>
     <row r="1223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1223" s="29" t="s">
-        <v>2794</v>
+        <v>2791</v>
       </c>
       <c r="B1223" s="100" t="s">
-        <v>2810</v>
+        <v>2807</v>
       </c>
       <c r="C1223" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1223" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1223" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1223" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1223" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1223" s="29">
         <v>0</v>
@@ -59223,25 +59193,25 @@
     </row>
     <row r="1224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1224" s="29" t="s">
-        <v>2795</v>
+        <v>2792</v>
       </c>
       <c r="B1224" s="100" t="s">
-        <v>2808</v>
+        <v>2805</v>
       </c>
       <c r="C1224" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1224" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1224" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1224" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1224" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1224" s="29">
         <v>0</v>
@@ -59258,25 +59228,25 @@
     </row>
     <row r="1225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1225" s="29" t="s">
-        <v>2796</v>
+        <v>2793</v>
       </c>
       <c r="B1225" s="126" t="s">
-        <v>2809</v>
+        <v>2806</v>
       </c>
       <c r="C1225" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1225" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1225" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1225" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1225" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1225" s="29">
         <v>0</v>
@@ -59293,25 +59263,25 @@
     </row>
     <row r="1226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1226" s="29" t="s">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="B1226" s="125" t="s">
-        <v>2811</v>
+        <v>2808</v>
       </c>
       <c r="C1226" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1226" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1226" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1226" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1226" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1226" s="29">
         <v>0</v>
@@ -59328,25 +59298,25 @@
     </row>
     <row r="1227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1227" s="29" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
       <c r="B1227" s="100" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="C1227" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1227" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1227" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1227" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1227" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1227" s="29">
         <v>0</v>
@@ -59355,7 +59325,7 @@
         <v>60</v>
       </c>
       <c r="J1227" s="29" t="s">
-        <v>2815</v>
+        <v>2812</v>
       </c>
       <c r="K1227" s="29"/>
       <c r="L1227" s="31"/>
@@ -59363,25 +59333,25 @@
     </row>
     <row r="1228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1228" s="29" t="s">
-        <v>2814</v>
+        <v>2811</v>
       </c>
       <c r="B1228" s="100" t="s">
-        <v>2818</v>
+        <v>2815</v>
       </c>
       <c r="C1228" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="D1228" s="100" t="s">
         <v>334</v>
       </c>
       <c r="E1228" s="83" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="F1228" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1228" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1228" s="29">
         <v>0</v>
@@ -59390,7 +59360,7 @@
         <v>60</v>
       </c>
       <c r="J1228" s="29" t="s">
-        <v>2816</v>
+        <v>2813</v>
       </c>
       <c r="K1228" s="29"/>
       <c r="L1228" s="31"/>
@@ -59398,25 +59368,25 @@
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1229" s="29" t="s">
-        <v>2977</v>
+        <v>2974</v>
       </c>
       <c r="B1229" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1229" s="83" t="s">
-        <v>2973</v>
+        <v>2970</v>
       </c>
       <c r="D1229" s="85" t="s">
-        <v>2963</v>
+        <v>2960</v>
       </c>
       <c r="E1229" s="83" t="s">
-        <v>2973</v>
+        <v>2970</v>
       </c>
       <c r="F1229" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1229" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1229" s="29">
         <v>0</v>
@@ -59425,35 +59395,35 @@
         <v>60</v>
       </c>
       <c r="J1229" s="29" t="s">
-        <v>2987</v>
+        <v>2984</v>
       </c>
       <c r="K1229" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1229" s="31"/>
       <c r="M1229" s="29"/>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1230" s="29" t="s">
-        <v>2978</v>
+        <v>2975</v>
       </c>
       <c r="B1230" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1230" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="D1230" s="85" t="s">
-        <v>2964</v>
+        <v>2961</v>
       </c>
       <c r="E1230" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1230" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1230" s="29">
         <v>0</v>
@@ -59462,35 +59432,35 @@
         <v>60</v>
       </c>
       <c r="J1230" s="29" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="K1230" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1230" s="31"/>
       <c r="M1230" s="29"/>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1231" s="29" t="s">
-        <v>2979</v>
+        <v>2976</v>
       </c>
       <c r="B1231" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1231" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="D1231" s="85" t="s">
-        <v>2965</v>
+        <v>2962</v>
       </c>
       <c r="E1231" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="F1231" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1231" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1231" s="29">
         <v>0</v>
@@ -59499,35 +59469,35 @@
         <v>60</v>
       </c>
       <c r="J1231" s="29" t="s">
-        <v>2989</v>
+        <v>2986</v>
       </c>
       <c r="K1231" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1231" s="31"/>
       <c r="M1231" s="29"/>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1232" s="29" t="s">
-        <v>2980</v>
+        <v>2977</v>
       </c>
       <c r="B1232" s="100" t="s">
         <v>1485</v>
       </c>
       <c r="C1232" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="D1232" s="85" t="s">
-        <v>2966</v>
+        <v>2963</v>
       </c>
       <c r="E1232" s="83" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1232" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1232" s="29">
         <v>0</v>
@@ -59536,35 +59506,35 @@
         <v>60</v>
       </c>
       <c r="J1232" s="29" t="s">
-        <v>2990</v>
+        <v>2987</v>
       </c>
       <c r="K1232" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1232" s="31"/>
       <c r="M1232" s="29"/>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1233" s="29" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="B1233" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1233" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="D1233" s="85" t="s">
-        <v>2967</v>
+        <v>2964</v>
       </c>
       <c r="E1233" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="F1233" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1233" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1233" s="29">
         <v>0</v>
@@ -59573,35 +59543,35 @@
         <v>60</v>
       </c>
       <c r="J1233" s="29" t="s">
-        <v>2991</v>
+        <v>2988</v>
       </c>
       <c r="K1233" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1233" s="31"/>
       <c r="M1233" s="29"/>
     </row>
     <row r="1234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1234" s="29" t="s">
-        <v>2982</v>
+        <v>2979</v>
       </c>
       <c r="B1234" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1234" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="D1234" s="85" t="s">
-        <v>2968</v>
+        <v>2965</v>
       </c>
       <c r="E1234" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="F1234" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1234" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1234" s="29">
         <v>0</v>
@@ -59610,35 +59580,35 @@
         <v>60</v>
       </c>
       <c r="J1234" s="29" t="s">
-        <v>2992</v>
+        <v>2989</v>
       </c>
       <c r="K1234" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1234" s="31"/>
       <c r="M1234" s="29"/>
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1235" s="29" t="s">
-        <v>2983</v>
+        <v>2980</v>
       </c>
       <c r="B1235" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1235" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="D1235" s="85" t="s">
-        <v>2969</v>
+        <v>2966</v>
       </c>
       <c r="E1235" s="83" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="F1235" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1235" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1235" s="29">
         <v>0</v>
@@ -59647,35 +59617,35 @@
         <v>60</v>
       </c>
       <c r="J1235" s="29" t="s">
-        <v>2993</v>
+        <v>2990</v>
       </c>
       <c r="K1235" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1235" s="31"/>
       <c r="M1235" s="29"/>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1236" s="29" t="s">
-        <v>2984</v>
+        <v>2981</v>
       </c>
       <c r="B1236" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1236" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="D1236" s="85" t="s">
-        <v>2970</v>
+        <v>2967</v>
       </c>
       <c r="E1236" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="F1236" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1236" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1236" s="29">
         <v>0</v>
@@ -59684,35 +59654,35 @@
         <v>60</v>
       </c>
       <c r="J1236" s="29" t="s">
+        <v>2991</v>
+      </c>
+      <c r="K1236" s="29" t="s">
         <v>2994</v>
-      </c>
-      <c r="K1236" s="29" t="s">
-        <v>2997</v>
       </c>
       <c r="L1236" s="31"/>
       <c r="M1236" s="29"/>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1237" s="29" t="s">
-        <v>2985</v>
+        <v>2982</v>
       </c>
       <c r="B1237" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1237" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="D1237" s="85" t="s">
-        <v>2971</v>
+        <v>2968</v>
       </c>
       <c r="E1237" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1237" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1237" s="29">
         <v>0</v>
@@ -59721,35 +59691,35 @@
         <v>60</v>
       </c>
       <c r="J1237" s="29" t="s">
-        <v>2995</v>
+        <v>2992</v>
       </c>
       <c r="K1237" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1237" s="31"/>
       <c r="M1237" s="29"/>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1238" s="29" t="s">
-        <v>2986</v>
+        <v>2983</v>
       </c>
       <c r="B1238" s="100" t="s">
         <v>1486</v>
       </c>
       <c r="C1238" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="D1238" s="85" t="s">
-        <v>2972</v>
+        <v>2969</v>
       </c>
       <c r="E1238" s="83" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="F1238" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1238" s="31" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="H1238" s="29">
         <v>0</v>
@@ -59758,20 +59728,20 @@
         <v>60</v>
       </c>
       <c r="J1238" s="29" t="s">
-        <v>2996</v>
+        <v>2993</v>
       </c>
       <c r="K1238" s="29" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="L1238" s="31"/>
       <c r="M1238" s="29"/>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1239" s="29" t="s">
-        <v>3003</v>
+        <v>3000</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>760</v>
@@ -59789,13 +59759,13 @@
         <v>1482</v>
       </c>
       <c r="H1239" s="29" t="s">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="I1239" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1239" s="29" t="s">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
@@ -59803,7 +59773,7 @@
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1240" s="29" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="B1240" s="100" t="s">
         <v>1050</v>
@@ -59824,13 +59794,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>3010</v>
+        <v>3007</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59838,7 +59808,7 @@
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1241" s="29" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="B1241" s="29" t="s">
         <v>1629</v>
@@ -59865,7 +59835,7 @@
         <v>96</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59873,7 +59843,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>3009</v>
+        <v>3006</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1672</v>
@@ -59904,16 +59874,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>3012</v>
+        <v>3009</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>52</v>
@@ -59926,10 +59896,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
-        <v>3016</v>
+        <v>3013</v>
       </c>
       <c r="J1243" s="29" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59937,16 +59907,16 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3015</v>
+        <v>3012</v>
       </c>
       <c r="B1244" s="29" t="s">
         <v>1629</v>
       </c>
       <c r="C1244" s="83" t="s">
-        <v>3046</v>
+        <v>3043</v>
       </c>
       <c r="D1244" s="100" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="E1244" s="83" t="s">
         <v>2182</v>
@@ -59959,10 +59929,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
-        <v>3016</v>
+        <v>3013</v>
       </c>
       <c r="J1244" s="29" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>
@@ -59970,10 +59940,10 @@
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1245" s="29" t="s">
-        <v>3033</v>
+        <v>3030</v>
       </c>
       <c r="B1245" s="100" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="C1245" s="83" t="s">
         <v>213</v>
@@ -59989,7 +59959,7 @@
       <c r="H1245" s="29"/>
       <c r="I1245" s="119"/>
       <c r="J1245" s="29" t="s">
-        <v>3035</v>
+        <v>3032</v>
       </c>
       <c r="K1245" s="29"/>
       <c r="L1245" s="31"/>
@@ -59997,7 +59967,7 @@
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1246" s="29" t="s">
-        <v>3034</v>
+        <v>3031</v>
       </c>
       <c r="B1246" s="100"/>
       <c r="C1246" s="83"/>
@@ -60016,16 +59986,16 @@
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1247" s="29" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="B1247" s="100" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="C1247" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1247" s="85" t="s">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="E1247" s="83" t="s">
         <v>52</v>
@@ -60037,13 +60007,13 @@
         <v>52</v>
       </c>
       <c r="H1247" s="29" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="I1247" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1247" s="29" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="K1247" s="29"/>
       <c r="L1247" s="31" t="s">
@@ -60053,16 +60023,16 @@
     </row>
     <row r="1248" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1248" s="29" t="s">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="B1248" s="100" t="s">
-        <v>3044</v>
+        <v>3041</v>
       </c>
       <c r="C1248" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1248" s="85" t="s">
-        <v>3042</v>
+        <v>3039</v>
       </c>
       <c r="E1248" s="83" t="s">
         <v>52</v>
@@ -60074,13 +60044,13 @@
         <v>52</v>
       </c>
       <c r="H1248" s="29" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="I1248" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1248" s="29" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
       <c r="K1248" s="29"/>
       <c r="L1248" s="31" t="s">
@@ -60090,7 +60060,7 @@
     </row>
     <row r="1249" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="29" t="s">
-        <v>3043</v>
+        <v>3040</v>
       </c>
       <c r="B1249" s="127" t="s">
         <v>1626</v>
@@ -60099,7 +60069,7 @@
         <v>2285</v>
       </c>
       <c r="D1249" s="85" t="s">
-        <v>3044</v>
+        <v>3041</v>
       </c>
       <c r="E1249" s="83" t="s">
         <v>2182</v>
@@ -60111,13 +60081,13 @@
         <v>1478</v>
       </c>
       <c r="H1249" s="29" t="s">
-        <v>3045</v>
+        <v>3042</v>
       </c>
       <c r="I1249" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1249" s="29" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
       <c r="K1249" s="29"/>
       <c r="L1249" s="31"/>
@@ -60125,7 +60095,7 @@
     </row>
     <row r="1250" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="29" t="s">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="B1250" s="85" t="s">
         <v>53</v>
@@ -60134,16 +60104,16 @@
         <v>2277</v>
       </c>
       <c r="D1250" s="100" t="s">
-        <v>3042</v>
+        <v>3039</v>
       </c>
       <c r="E1250" s="86" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="F1250" s="31" t="s">
         <v>1550</v>
       </c>
       <c r="G1250" s="31" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="H1250" s="29">
         <v>0</v>
@@ -60152,7 +60122,7 @@
         <v>60</v>
       </c>
       <c r="J1250" s="29" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="K1250" s="29"/>
       <c r="L1250" s="31"/>
@@ -60160,7 +60130,7 @@
     </row>
     <row r="1251" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="29" t="s">
-        <v>3051</v>
+        <v>3048</v>
       </c>
       <c r="B1251" s="80" t="s">
         <v>1672</v>
@@ -60185,7 +60155,7 @@
         <v>60</v>
       </c>
       <c r="J1251" s="29" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
       <c r="K1251" s="29"/>
       <c r="L1251" s="31"/>
@@ -60193,7 +60163,7 @@
     </row>
     <row r="1252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1252" s="29" t="s">
-        <v>3052</v>
+        <v>3049</v>
       </c>
       <c r="B1252" s="100" t="s">
         <v>2224</v>
@@ -60205,7 +60175,7 @@
         <v>968</v>
       </c>
       <c r="E1252" s="83" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="F1252" s="31" t="s">
         <v>1550</v>
@@ -60220,7 +60190,7 @@
         <v>60</v>
       </c>
       <c r="J1252" s="29" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="K1252" s="29"/>
       <c r="L1252" s="31"/>
@@ -60228,13 +60198,13 @@
     </row>
     <row r="1253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1253" s="29" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="B1253" s="100" t="s">
         <v>968</v>
       </c>
       <c r="C1253" s="83" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="D1253" s="85" t="s">
         <v>1164</v>
@@ -60255,7 +60225,7 @@
         <v>60</v>
       </c>
       <c r="J1253" s="29" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="K1253" s="29"/>
       <c r="L1253" s="31"/>
@@ -60263,7 +60233,7 @@
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1254" s="29" t="s">
-        <v>3096</v>
+        <v>3093</v>
       </c>
       <c r="B1254" s="29" t="s">
         <v>1629</v>
@@ -60290,7 +60260,7 @@
         <v>96</v>
       </c>
       <c r="J1254" s="29" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="K1254" s="29"/>
       <c r="L1254" s="31"/>
@@ -60298,7 +60268,7 @@
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1255" s="29" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
       <c r="B1255" s="100" t="s">
         <v>1672</v>
@@ -60323,7 +60293,7 @@
         <v>60</v>
       </c>
       <c r="J1255" s="29" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="K1255" s="29"/>
       <c r="L1255" s="31"/>
@@ -60331,16 +60301,16 @@
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1256" s="29" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
       <c r="B1256" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1256" s="83" t="s">
         <v>2286</v>
       </c>
       <c r="D1256" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1256" s="83" t="s">
         <v>2380</v>
@@ -60364,16 +60334,16 @@
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1257" s="29" t="s">
-        <v>3113</v>
+        <v>3110</v>
       </c>
       <c r="B1257" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1257" s="83" t="s">
         <v>2287</v>
       </c>
       <c r="D1257" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1257" s="83" t="s">
         <v>2381</v>
@@ -60397,16 +60367,16 @@
     </row>
     <row r="1258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1258" s="29" t="s">
-        <v>3114</v>
+        <v>3111</v>
       </c>
       <c r="B1258" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1258" s="83" t="s">
         <v>2288</v>
       </c>
       <c r="D1258" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1258" s="83" t="s">
         <v>2382</v>
@@ -60430,16 +60400,16 @@
     </row>
     <row r="1259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1259" s="29" t="s">
-        <v>3115</v>
+        <v>3112</v>
       </c>
       <c r="B1259" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1259" s="83" t="s">
         <v>2289</v>
       </c>
       <c r="D1259" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1259" s="83" t="s">
         <v>1853</v>
@@ -60463,16 +60433,16 @@
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1260" s="29" t="s">
-        <v>3116</v>
+        <v>3113</v>
       </c>
       <c r="B1260" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1260" s="83" t="s">
         <v>2285</v>
       </c>
       <c r="D1260" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1260" s="83" t="s">
         <v>2290</v>
@@ -60496,16 +60466,16 @@
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1261" s="29" t="s">
-        <v>3117</v>
+        <v>3114</v>
       </c>
       <c r="B1261" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1261" s="83" t="s">
         <v>2386</v>
       </c>
       <c r="D1261" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1261" s="83" t="s">
         <v>2034</v>
@@ -60529,16 +60499,16 @@
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1262" s="29" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
       <c r="B1262" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1262" s="83" t="s">
         <v>2282</v>
       </c>
       <c r="D1262" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1262" s="83" t="s">
         <v>2291</v>
@@ -60562,16 +60532,16 @@
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1263" s="29" t="s">
-        <v>3119</v>
+        <v>3116</v>
       </c>
       <c r="B1263" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1263" s="83" t="s">
         <v>2283</v>
       </c>
       <c r="D1263" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1263" s="83" t="s">
         <v>2292</v>
@@ -60595,16 +60565,16 @@
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1264" s="29" t="s">
-        <v>3120</v>
+        <v>3117</v>
       </c>
       <c r="B1264" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1264" s="83" t="s">
         <v>2284</v>
       </c>
       <c r="D1264" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1264" s="83" t="s">
         <v>2265</v>
@@ -60628,16 +60598,16 @@
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1265" s="29" t="s">
-        <v>3121</v>
+        <v>3118</v>
       </c>
       <c r="B1265" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1265" s="83" t="s">
         <v>2387</v>
       </c>
       <c r="D1265" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1265" s="83" t="s">
         <v>2293</v>
@@ -60661,16 +60631,16 @@
     </row>
     <row r="1266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1266" s="29" t="s">
-        <v>3122</v>
+        <v>3119</v>
       </c>
       <c r="B1266" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1266" s="83" t="s">
         <v>1847</v>
       </c>
       <c r="D1266" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1266" s="83" t="s">
         <v>1849</v>
@@ -60694,16 +60664,16 @@
     </row>
     <row r="1267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1267" s="29" t="s">
-        <v>3123</v>
+        <v>3120</v>
       </c>
       <c r="B1267" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1267" s="83" t="s">
         <v>2267</v>
       </c>
       <c r="D1267" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1267" s="83" t="s">
         <v>1968</v>
@@ -60727,16 +60697,16 @@
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1268" s="29" t="s">
-        <v>3124</v>
+        <v>3121</v>
       </c>
       <c r="B1268" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1268" s="83" t="s">
         <v>1854</v>
       </c>
       <c r="D1268" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1268" s="83" t="s">
         <v>1851</v>
@@ -60760,16 +60730,16 @@
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1269" s="29" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="B1269" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1269" s="83" t="s">
         <v>1855</v>
       </c>
       <c r="D1269" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1269" s="83" t="s">
         <v>1850</v>
@@ -60793,16 +60763,16 @@
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1270" s="29" t="s">
-        <v>3126</v>
+        <v>3123</v>
       </c>
       <c r="B1270" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1270" s="83" t="s">
         <v>2264</v>
       </c>
       <c r="D1270" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1270" s="83" t="s">
         <v>2294</v>
@@ -60826,16 +60796,16 @@
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1271" s="29" t="s">
-        <v>3127</v>
+        <v>3124</v>
       </c>
       <c r="B1271" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1271" s="83" t="s">
         <v>2263</v>
       </c>
       <c r="D1271" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1271" s="83" t="s">
         <v>2383</v>
@@ -60859,16 +60829,16 @@
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1272" s="29" t="s">
-        <v>3128</v>
+        <v>3125</v>
       </c>
       <c r="B1272" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1272" s="83" t="s">
         <v>1860</v>
       </c>
       <c r="D1272" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1272" s="83" t="s">
         <v>1857</v>
@@ -60892,16 +60862,16 @@
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1273" s="29" t="s">
-        <v>3129</v>
+        <v>3126</v>
       </c>
       <c r="B1273" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1273" s="83" t="s">
         <v>2388</v>
       </c>
       <c r="D1273" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1273" s="83" t="s">
         <v>2395</v>
@@ -60925,16 +60895,16 @@
     </row>
     <row r="1274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1274" s="29" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="B1274" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1274" s="83" t="s">
         <v>2389</v>
       </c>
       <c r="D1274" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1274" s="83" t="s">
         <v>2396</v>
@@ -60958,16 +60928,16 @@
     </row>
     <row r="1275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1275" s="29" t="s">
-        <v>3131</v>
+        <v>3128</v>
       </c>
       <c r="B1275" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1275" s="83" t="s">
         <v>2390</v>
       </c>
       <c r="D1275" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1275" s="83" t="s">
         <v>2397</v>
@@ -60991,16 +60961,16 @@
     </row>
     <row r="1276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1276" s="29" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
       <c r="B1276" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1276" s="83" t="s">
         <v>2391</v>
       </c>
       <c r="D1276" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1276" s="83" t="s">
         <v>2398</v>
@@ -61024,16 +60994,16 @@
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1277" s="29" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="B1277" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1277" s="83" t="s">
         <v>2392</v>
       </c>
       <c r="D1277" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1277" s="83" t="s">
         <v>2399</v>
@@ -61057,16 +61027,16 @@
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1278" s="29" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B1278" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1278" s="83" t="s">
         <v>2393</v>
       </c>
       <c r="D1278" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1278" s="83" t="s">
         <v>2400</v>
@@ -61090,16 +61060,16 @@
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1279" s="29" t="s">
-        <v>3135</v>
+        <v>3132</v>
       </c>
       <c r="B1279" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C1279" s="83" t="s">
         <v>2394</v>
       </c>
       <c r="D1279" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1279" s="83" t="s">
         <v>2401</v>
@@ -61123,7 +61093,7 @@
     </row>
     <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1280" s="128" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
       <c r="B1280" s="100" t="s">
         <v>242</v>
@@ -61132,7 +61102,7 @@
         <v>1263</v>
       </c>
       <c r="D1280" s="100" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="E1280" s="83" t="s">
         <v>2394</v>
@@ -61144,13 +61114,13 @@
         <v>1478</v>
       </c>
       <c r="H1280" s="128" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="I1280" s="129" t="s">
         <v>60</v>
       </c>
       <c r="J1280" s="130" t="s">
-        <v>3137</v>
+        <v>3134</v>
       </c>
       <c r="K1280" s="128"/>
       <c r="L1280" s="83"/>
@@ -61158,7 +61128,7 @@
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1281" s="29" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="B1281" s="85" t="s">
         <v>1674</v>
@@ -61167,7 +61137,7 @@
         <v>1246</v>
       </c>
       <c r="D1281" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1281" s="83" t="s">
         <v>2286</v>
@@ -61191,7 +61161,7 @@
     </row>
     <row r="1282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1282" s="29" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="B1282" s="85" t="s">
         <v>1674</v>
@@ -61200,7 +61170,7 @@
         <v>1248</v>
       </c>
       <c r="D1282" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1282" s="83" t="s">
         <v>2287</v>
@@ -61224,7 +61194,7 @@
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1283" s="29" t="s">
-        <v>3154</v>
+        <v>3151</v>
       </c>
       <c r="B1283" s="85" t="s">
         <v>1674</v>
@@ -61233,7 +61203,7 @@
         <v>1222</v>
       </c>
       <c r="D1283" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1283" s="83" t="s">
         <v>2288</v>
@@ -61257,7 +61227,7 @@
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1284" s="29" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="B1284" s="85" t="s">
         <v>1674</v>
@@ -61266,7 +61236,7 @@
         <v>1224</v>
       </c>
       <c r="D1284" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1284" s="83" t="s">
         <v>2289</v>
@@ -61290,7 +61260,7 @@
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1285" s="29" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="B1285" s="85" t="s">
         <v>1674</v>
@@ -61299,7 +61269,7 @@
         <v>1226</v>
       </c>
       <c r="D1285" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1285" s="83" t="s">
         <v>2285</v>
@@ -61323,7 +61293,7 @@
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1286" s="29" t="s">
-        <v>3157</v>
+        <v>3154</v>
       </c>
       <c r="B1286" s="85" t="s">
         <v>1674</v>
@@ -61332,7 +61302,7 @@
         <v>1228</v>
       </c>
       <c r="D1286" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1286" s="83" t="s">
         <v>2386</v>
@@ -61356,7 +61326,7 @@
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1287" s="29" t="s">
-        <v>3158</v>
+        <v>3155</v>
       </c>
       <c r="B1287" s="85" t="s">
         <v>1674</v>
@@ -61365,7 +61335,7 @@
         <v>1230</v>
       </c>
       <c r="D1287" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1287" s="83" t="s">
         <v>2282</v>
@@ -61389,7 +61359,7 @@
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1288" s="29" t="s">
-        <v>3159</v>
+        <v>3156</v>
       </c>
       <c r="B1288" s="85" t="s">
         <v>1674</v>
@@ -61398,7 +61368,7 @@
         <v>1232</v>
       </c>
       <c r="D1288" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="E1288" s="83" t="s">
         <v>2283</v>
@@ -61422,10 +61392,10 @@
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1289" s="29" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="B1289" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1289" s="83" t="s">
         <v>2284</v>
@@ -61445,10 +61415,10 @@
     </row>
     <row r="1290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1290" s="29" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="B1290" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1290" s="83" t="s">
         <v>2387</v>
@@ -61468,10 +61438,10 @@
     </row>
     <row r="1291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1291" s="29" t="s">
-        <v>3162</v>
+        <v>3159</v>
       </c>
       <c r="B1291" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1291" s="83" t="s">
         <v>1847</v>
@@ -61491,10 +61461,10 @@
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1292" s="29" t="s">
-        <v>3163</v>
+        <v>3160</v>
       </c>
       <c r="B1292" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1292" s="83" t="s">
         <v>2267</v>
@@ -61514,10 +61484,10 @@
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1293" s="29" t="s">
-        <v>3164</v>
+        <v>3161</v>
       </c>
       <c r="B1293" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1293" s="83" t="s">
         <v>1854</v>
@@ -61537,10 +61507,10 @@
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1294" s="29" t="s">
-        <v>3165</v>
+        <v>3162</v>
       </c>
       <c r="B1294" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1294" s="83" t="s">
         <v>1855</v>
@@ -61560,10 +61530,10 @@
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1295" s="29" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="B1295" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1295" s="83" t="s">
         <v>2264</v>
@@ -61583,10 +61553,10 @@
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1296" s="29" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="B1296" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1296" s="83" t="s">
         <v>2263</v>
@@ -61606,10 +61576,10 @@
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1297" s="29" t="s">
-        <v>3168</v>
+        <v>3165</v>
       </c>
       <c r="B1297" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1297" s="83" t="s">
         <v>1860</v>
@@ -61629,10 +61599,10 @@
     </row>
     <row r="1298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1298" s="29" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="B1298" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1298" s="83" t="s">
         <v>2388</v>
@@ -61652,10 +61622,10 @@
     </row>
     <row r="1299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1299" s="29" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="B1299" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1299" s="83" t="s">
         <v>2389</v>
@@ -61675,10 +61645,10 @@
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1300" s="29" t="s">
-        <v>3171</v>
+        <v>3168</v>
       </c>
       <c r="B1300" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1300" s="83" t="s">
         <v>2390</v>
@@ -61698,10 +61668,10 @@
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1301" s="29" t="s">
-        <v>3172</v>
+        <v>3169</v>
       </c>
       <c r="B1301" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1301" s="83" t="s">
         <v>2391</v>
@@ -61721,10 +61691,10 @@
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1302" s="29" t="s">
-        <v>3173</v>
+        <v>3170</v>
       </c>
       <c r="B1302" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1302" s="83" t="s">
         <v>2392</v>
@@ -61744,10 +61714,10 @@
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1303" s="29" t="s">
-        <v>3174</v>
+        <v>3171</v>
       </c>
       <c r="B1303" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1303" s="83" t="s">
         <v>2393</v>
@@ -61767,10 +61737,10 @@
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1304" s="29" t="s">
-        <v>3175</v>
+        <v>3172</v>
       </c>
       <c r="B1304" s="100" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="C1304" s="83" t="s">
         <v>2394</v>
@@ -61790,7 +61760,7 @@
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1305" s="29" t="s">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="B1305" s="85" t="s">
         <v>1674</v>
@@ -61799,7 +61769,7 @@
         <v>1301</v>
       </c>
       <c r="D1305" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1305" s="83" t="s">
         <v>2388</v>
@@ -61818,12 +61788,12 @@
       </c>
       <c r="J1305" s="29"/>
       <c r="K1305" s="29"/>
-      <c r="L1305" s="134"/>
+      <c r="L1305" s="31"/>
       <c r="M1305" s="29"/>
     </row>
     <row r="1306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1306" s="29" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="B1306" s="85" t="s">
         <v>1674</v>
@@ -61832,7 +61802,7 @@
         <v>1303</v>
       </c>
       <c r="D1306" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1306" s="83" t="s">
         <v>2389</v>
@@ -61851,12 +61821,12 @@
       </c>
       <c r="J1306" s="29"/>
       <c r="K1306" s="29"/>
-      <c r="L1306" s="134"/>
+      <c r="L1306" s="31"/>
       <c r="M1306" s="29"/>
     </row>
     <row r="1307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1307" s="29" t="s">
-        <v>3150</v>
+        <v>3147</v>
       </c>
       <c r="B1307" s="85" t="s">
         <v>1674</v>
@@ -61865,7 +61835,7 @@
         <v>1305</v>
       </c>
       <c r="D1307" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1307" s="83" t="s">
         <v>2390</v>
@@ -61884,12 +61854,12 @@
       </c>
       <c r="J1307" s="29"/>
       <c r="K1307" s="29"/>
-      <c r="L1307" s="134"/>
+      <c r="L1307" s="31"/>
       <c r="M1307" s="29"/>
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1308" s="29" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="B1308" s="85" t="s">
         <v>1674</v>
@@ -61898,7 +61868,7 @@
         <v>1280</v>
       </c>
       <c r="D1308" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1308" s="83" t="s">
         <v>2391</v>
@@ -61917,17 +61887,17 @@
       </c>
       <c r="J1308" s="29"/>
       <c r="K1308" s="29"/>
-      <c r="L1308" s="134"/>
+      <c r="L1308" s="31"/>
       <c r="M1308" s="29"/>
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1309" s="29" t="s">
-        <v>3176</v>
+        <v>3173</v>
       </c>
       <c r="B1309" s="125"/>
-      <c r="C1309" s="133"/>
+      <c r="C1309" s="83"/>
       <c r="D1309" s="100" t="s">
-        <v>2598</v>
+        <v>2595</v>
       </c>
       <c r="E1309" s="83" t="s">
         <v>2394</v>
@@ -61947,19 +61917,19 @@
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1310" s="29" t="s">
-        <v>3197</v>
+        <v>3194</v>
       </c>
       <c r="B1310" s="100" t="s">
         <v>1342</v>
       </c>
       <c r="C1310" s="83" t="s">
+        <v>3192</v>
+      </c>
+      <c r="D1310" s="85" t="s">
         <v>3195</v>
       </c>
-      <c r="D1310" s="85" t="s">
-        <v>3198</v>
-      </c>
       <c r="E1310" s="83" t="s">
-        <v>3199</v>
+        <v>3196</v>
       </c>
       <c r="F1310" s="31"/>
       <c r="G1310" s="31"/>
@@ -61972,19 +61942,19 @@
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1311" s="29" t="s">
-        <v>3202</v>
+        <v>3199</v>
       </c>
       <c r="B1311" s="100" t="s">
         <v>1342</v>
       </c>
       <c r="C1311" s="83" t="s">
+        <v>3193</v>
+      </c>
+      <c r="D1311" s="85" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E1311" s="83" t="s">
         <v>3196</v>
-      </c>
-      <c r="D1311" s="85" t="s">
-        <v>3201</v>
-      </c>
-      <c r="E1311" s="83" t="s">
-        <v>3199</v>
       </c>
       <c r="F1311" s="31"/>
       <c r="G1311" s="31"/>
@@ -61997,19 +61967,19 @@
     </row>
     <row r="1312" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="29" t="s">
-        <v>3203</v>
+        <v>3200</v>
       </c>
       <c r="B1312" s="85" t="s">
-        <v>3198</v>
+        <v>3195</v>
       </c>
       <c r="C1312" s="83" t="s">
-        <v>3199</v>
+        <v>3196</v>
       </c>
       <c r="D1312" s="85" t="s">
-        <v>3200</v>
+        <v>3197</v>
       </c>
       <c r="E1312" s="83" t="s">
-        <v>3199</v>
+        <v>3196</v>
       </c>
       <c r="F1312" s="31"/>
       <c r="G1312" s="31"/>
@@ -62022,13 +61992,13 @@
     </row>
     <row r="1313" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="29" t="s">
-        <v>3204</v>
+        <v>3201</v>
       </c>
       <c r="B1313" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C1313" s="82" t="s">
-        <v>3205</v>
+        <v>3202</v>
       </c>
       <c r="D1313" s="100" t="s">
         <v>1050</v>
@@ -62049,19 +62019,19 @@
         <v>96</v>
       </c>
       <c r="J1313" s="29" t="s">
-        <v>3206</v>
+        <v>3203</v>
       </c>
       <c r="K1313" s="29"/>
       <c r="L1313" s="31" t="s">
-        <v>3207</v>
+        <v>3204</v>
       </c>
       <c r="M1313" s="29" t="s">
-        <v>3208</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="1314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1314" s="29" t="s">
-        <v>3209</v>
+        <v>3206</v>
       </c>
       <c r="B1314" s="100" t="s">
         <v>1050</v>
@@ -62079,7 +62049,7 @@
         <v>1550</v>
       </c>
       <c r="G1314" s="31" t="s">
-        <v>3210</v>
+        <v>3207</v>
       </c>
       <c r="H1314" s="29">
         <v>0</v>
@@ -62088,10 +62058,10 @@
         <v>503</v>
       </c>
       <c r="J1314" s="29" t="s">
-        <v>3206</v>
+        <v>3203</v>
       </c>
       <c r="K1314" s="29" t="s">
-        <v>3211</v>
+        <v>3208</v>
       </c>
       <c r="L1314" s="31"/>
       <c r="M1314" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644CC564-F402-A34A-A0DC-4E1965B1DF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE3FB06-C1B8-664C-912D-97F86E26744A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10951" uniqueCount="3256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10951" uniqueCount="3255">
   <si>
     <t>Tag</t>
   </si>
@@ -9803,9 +9803,6 @@
   </si>
   <si>
     <t>jump1334</t>
-  </si>
-  <si>
-    <t>2405-2501-F03</t>
   </si>
   <si>
     <t>NSCU-A001 to NSCU-A003 link</t>
@@ -23608,7 +23605,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="23"/>
@@ -62661,7 +62658,7 @@
         <v>96</v>
       </c>
       <c r="J1331" s="29" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="K1331" s="29"/>
       <c r="L1331" s="136"/>
@@ -62692,7 +62689,7 @@
         <v>96</v>
       </c>
       <c r="J1332" s="29" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="K1332" s="29"/>
       <c r="L1332" s="136"/>
@@ -62723,7 +62720,7 @@
         <v>96</v>
       </c>
       <c r="J1333" s="29" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="K1333" s="29"/>
       <c r="L1333" s="136"/>
@@ -62740,7 +62737,7 @@
         <v>1228</v>
       </c>
       <c r="D1334" s="133" t="s">
-        <v>3253</v>
+        <v>3093</v>
       </c>
       <c r="E1334" s="134" t="s">
         <v>2281</v>
@@ -62754,7 +62751,7 @@
         <v>96</v>
       </c>
       <c r="J1334" s="29" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="K1334" s="29"/>
       <c r="L1334" s="136"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADC30C-4F0F-0C40-98C4-5617DF585A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1365B779-EE7C-E948-AE3C-768EF60DA627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10957" uniqueCount="3256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10996" uniqueCount="3269">
   <si>
     <t>Tag</t>
   </si>
@@ -8540,12 +8540,6 @@
   </si>
   <si>
     <t>a359</t>
-  </si>
-  <si>
-    <t>a375</t>
-  </si>
-  <si>
-    <t>a376</t>
   </si>
   <si>
     <t>a379</t>
@@ -9812,6 +9806,51 @@
   </si>
   <si>
     <t>black</t>
+  </si>
+  <si>
+    <t>I think this is wrong</t>
+  </si>
+  <si>
+    <t>AP2-4</t>
+  </si>
+  <si>
+    <t>AP2-3</t>
+  </si>
+  <si>
+    <t>notag1336</t>
+  </si>
+  <si>
+    <t>unk1336</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>s_camera</t>
+  </si>
+  <si>
+    <t>n_camera</t>
+  </si>
+  <si>
+    <t>unk1337</t>
+  </si>
+  <si>
+    <t>unk1338</t>
+  </si>
+  <si>
+    <t>notag1339</t>
+  </si>
+  <si>
+    <t>notag1340</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>14?</t>
+  </si>
+  <si>
+    <t>need to confirm</t>
   </si>
 </sst>
 </file>
@@ -9926,7 +9965,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9984,6 +10023,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBA4EFF"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -10238,7 +10283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10511,6 +10556,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20020,7 +20075,7 @@
         <v>725</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>19</v>
@@ -20057,7 +20112,7 @@
         <v>725</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>19</v>
@@ -20094,7 +20149,7 @@
         <v>725</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>19</v>
@@ -20115,7 +20170,7 @@
         <v>60</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>3051</v>
+        <v>3049</v>
       </c>
       <c r="K4" s="19" t="s">
         <v>274</v>
@@ -20131,7 +20186,7 @@
         <v>725</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>19</v>
@@ -20152,7 +20207,7 @@
         <v>60</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="K5" s="23" t="s">
         <v>276</v>
@@ -20168,7 +20223,7 @@
         <v>725</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>19</v>
@@ -20189,7 +20244,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="K6" s="19" t="s">
         <v>277</v>
@@ -20205,7 +20260,7 @@
         <v>725</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>3048</v>
+        <v>3046</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>19</v>
@@ -20226,7 +20281,7 @@
         <v>60</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>279</v>
@@ -20271,7 +20326,7 @@
         <v>725</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="D9" s="103" t="s">
         <v>19</v>
@@ -20292,7 +20347,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>281</v>
@@ -20339,7 +20394,7 @@
         <v>725</v>
       </c>
       <c r="E11" s="104" t="s">
-        <v>3050</v>
+        <v>3048</v>
       </c>
       <c r="F11" s="102" t="s">
         <v>1542</v>
@@ -20354,7 +20409,7 @@
         <v>60</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="K11" s="23" t="s">
         <v>282</v>
@@ -20364,10 +20419,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="C12" s="91" t="s">
         <v>52</v>
@@ -20385,7 +20440,7 @@
         <v>52</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>497</v>
@@ -20399,7 +20454,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>263</v>
@@ -20417,14 +20472,14 @@
         <v>176</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="H13" s="23"/>
       <c r="I13" s="23" t="s">
         <v>497</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -20432,7 +20487,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>263</v>
@@ -20450,7 +20505,7 @@
         <v>176</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="H14" s="23"/>
       <c r="I14" s="23" t="s">
@@ -20465,7 +20520,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>263</v>
@@ -20483,14 +20538,14 @@
         <v>176</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="H15" s="29"/>
       <c r="I15" s="23" t="s">
         <v>497</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="K15" s="23"/>
       <c r="L15" s="23"/>
@@ -20498,7 +20553,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>263</v>
@@ -20516,7 +20571,7 @@
         <v>176</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="23" t="s">
@@ -20531,32 +20586,32 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>53</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>2246</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="F17" s="23" t="s">
         <v>1542</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="H17" s="29"/>
       <c r="I17" s="119" t="s">
         <v>60</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
@@ -21021,7 +21076,7 @@
         <v>147</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>193</v>
@@ -21039,7 +21094,7 @@
         <v>96</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="K34" s="19" t="s">
         <v>113</v>
@@ -22762,7 +22817,7 @@
         <v>60</v>
       </c>
       <c r="J89" s="23" t="s">
-        <v>2948</v>
+        <v>2946</v>
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23"/>
@@ -23071,7 +23126,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="B101" s="22" t="s">
         <v>53</v>
@@ -23300,7 +23355,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="B108" s="22" t="s">
         <v>223</v>
@@ -23309,7 +23364,7 @@
         <v>133</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
       <c r="E108" s="23" t="s">
         <v>133</v>
@@ -23551,23 +23606,23 @@
       <c r="M115" s="20"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="28" t="s">
         <v>2812</v>
       </c>
-      <c r="B116" s="22" t="s">
+      <c r="B116" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="27" t="s">
         <v>265</v>
       </c>
-      <c r="D116" s="22" t="s">
+      <c r="D116" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="E116" s="23" t="s">
+      <c r="E116" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23" t="s">
+      <c r="F116" s="27"/>
+      <c r="G116" s="27" t="s">
         <v>1470</v>
       </c>
       <c r="H116" s="23"/>
@@ -23575,7 +23630,9 @@
       <c r="J116" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="K116" s="23"/>
+      <c r="K116" s="23" t="s">
+        <v>3254</v>
+      </c>
       <c r="L116" s="23"/>
       <c r="M116" s="24"/>
     </row>
@@ -23608,7 +23665,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="23"/>
@@ -23625,27 +23682,27 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="23"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
       <c r="F119" s="23" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
       <c r="G119" s="23" t="s">
         <v>52</v>
       </c>
       <c r="H119" s="23" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
       <c r="I119" s="23"/>
       <c r="J119" s="23" t="s">
         <v>433</v>
       </c>
       <c r="K119" s="23" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="L119" s="19"/>
       <c r="M119" s="20"/>
@@ -27189,14 +27246,14 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="29" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
       <c r="B225" s="31" t="s">
         <v>53</v>
       </c>
       <c r="C225" s="29"/>
       <c r="D225" s="31" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="E225" s="29">
         <v>5343</v>
@@ -27205,7 +27262,7 @@
         <v>1542</v>
       </c>
       <c r="G225" s="31" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="H225" s="29">
         <v>0</v>
@@ -27214,7 +27271,7 @@
         <v>497</v>
       </c>
       <c r="J225" s="29" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="K225" s="29"/>
       <c r="L225" s="31"/>
@@ -28325,7 +28382,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="29" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="B263" s="31" t="s">
         <v>223</v>
@@ -29056,7 +29113,7 @@
         <v>618</v>
       </c>
       <c r="B289" s="31" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="C289" s="29" t="s">
         <v>147</v>
@@ -29080,10 +29137,10 @@
         <v>96</v>
       </c>
       <c r="J289" s="29" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="K289" s="29" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="L289" s="31"/>
       <c r="M289" s="29"/>
@@ -30035,10 +30092,10 @@
         <v>96</v>
       </c>
       <c r="J320" s="29" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="K320" s="29" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="L320" s="31"/>
       <c r="M320" s="29"/>
@@ -30395,7 +30452,7 @@
       </c>
       <c r="J331" s="29"/>
       <c r="K331" s="35" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="L331" s="32"/>
       <c r="M331" s="35"/>
@@ -31685,16 +31742,16 @@
         <v>855</v>
       </c>
       <c r="B374" s="31" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="C374" s="29" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="D374" s="31" t="s">
         <v>856</v>
       </c>
       <c r="E374" s="29" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="F374" s="31" t="s">
         <v>306</v>
@@ -31707,7 +31764,7 @@
         <v>96</v>
       </c>
       <c r="J374" s="29" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="K374" s="29" t="s">
         <v>857</v>
@@ -31717,7 +31774,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
-        <v>2833</v>
+        <v>3255</v>
       </c>
       <c r="B375" s="31" t="s">
         <v>260</v>
@@ -31748,7 +31805,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
-        <v>2834</v>
+        <v>3256</v>
       </c>
       <c r="B376" s="31" t="s">
         <v>260</v>
@@ -31779,7 +31836,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="B377" s="31" t="s">
         <v>262</v>
@@ -31804,7 +31861,7 @@
         <v>60</v>
       </c>
       <c r="J377" s="29" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="K377" s="29"/>
       <c r="L377" s="31"/>
@@ -31812,7 +31869,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="B378" s="31" t="s">
         <v>262</v>
@@ -31837,7 +31894,7 @@
         <v>60</v>
       </c>
       <c r="J378" s="29" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="K378" s="29"/>
       <c r="L378" s="31"/>
@@ -31845,7 +31902,7 @@
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="29" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="B379" s="31" t="s">
         <v>242</v>
@@ -31876,7 +31933,7 @@
     </row>
     <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="29" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
       <c r="B380" s="31" t="s">
         <v>258</v>
@@ -32265,7 +32322,7 @@
     </row>
     <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="29" t="s">
-        <v>2837</v>
+        <v>2835</v>
       </c>
       <c r="B393" s="31" t="s">
         <v>890</v>
@@ -32292,7 +32349,7 @@
     </row>
     <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="29" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
       <c r="B394" s="31" t="s">
         <v>891</v>
@@ -32319,7 +32376,7 @@
     </row>
     <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="29" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="B395" s="29" t="s">
         <v>892</v>
@@ -32342,7 +32399,7 @@
     </row>
     <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="29" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="B396" s="29" t="s">
         <v>894</v>
@@ -32365,7 +32422,7 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="29" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="B397" s="29" t="s">
         <v>892</v>
@@ -32388,7 +32445,7 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="29" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="B398" s="31" t="s">
         <v>896</v>
@@ -32411,7 +32468,7 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="29" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="B399" s="31" t="s">
         <v>897</v>
@@ -32434,7 +32491,7 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="29" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="B400" s="31" t="s">
         <v>898</v>
@@ -32457,7 +32514,7 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="29" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="B401" s="31" t="s">
         <v>899</v>
@@ -32480,7 +32537,7 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="29" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="B402" s="31" t="s">
         <v>900</v>
@@ -32503,7 +32560,7 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="29" t="s">
-        <v>2847</v>
+        <v>2845</v>
       </c>
       <c r="B403" s="31" t="s">
         <v>901</v>
@@ -32526,7 +32583,7 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="29" t="s">
-        <v>2848</v>
+        <v>2846</v>
       </c>
       <c r="B404" s="31" t="s">
         <v>902</v>
@@ -32549,7 +32606,7 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="29" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
       <c r="B405" s="31" t="s">
         <v>903</v>
@@ -32572,7 +32629,7 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="29" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
       <c r="B406" s="31" t="s">
         <v>889</v>
@@ -32721,7 +32778,7 @@
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="29" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="B411" s="31" t="s">
         <v>258</v>
@@ -32746,7 +32803,7 @@
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="29" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
       <c r="B412" s="31" t="s">
         <v>258</v>
@@ -32771,7 +32828,7 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="29" t="s">
-        <v>2853</v>
+        <v>2851</v>
       </c>
       <c r="B413" s="31" t="s">
         <v>258</v>
@@ -32796,7 +32853,7 @@
     </row>
     <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="29" t="s">
-        <v>2854</v>
+        <v>2852</v>
       </c>
       <c r="B414" s="31" t="s">
         <v>258</v>
@@ -33550,7 +33607,7 @@
     </row>
     <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="29" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
       <c r="B438" s="31" t="s">
         <v>974</v>
@@ -33585,7 +33642,7 @@
     </row>
     <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="29" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="B439" s="31" t="s">
         <v>974</v>
@@ -33620,7 +33677,7 @@
     </row>
     <row r="440" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A440" s="29" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="B440" s="31" t="s">
         <v>974</v>
@@ -33655,7 +33712,7 @@
     </row>
     <row r="441" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A441" s="29" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
       <c r="B441" s="87" t="s">
         <v>1047</v>
@@ -33688,7 +33745,7 @@
     </row>
     <row r="442" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A442" s="29" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="B442" s="87" t="s">
         <v>1450</v>
@@ -33716,14 +33773,14 @@
         <v>1048</v>
       </c>
       <c r="K442" s="29" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="L442" s="31"/>
       <c r="M442" s="29"/>
     </row>
     <row r="443" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A443" s="29" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="B443" s="29" t="s">
         <v>1596</v>
@@ -33752,7 +33809,7 @@
     </row>
     <row r="444" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A444" s="29" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="B444" s="87" t="s">
         <v>1603</v>
@@ -33785,7 +33842,7 @@
     </row>
     <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="29" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
       <c r="B445" t="s">
         <v>1598</v>
@@ -33816,7 +33873,7 @@
     </row>
     <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="29" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
       <c r="B446" t="s">
         <v>1599</v>
@@ -33847,7 +33904,7 @@
     </row>
     <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="29" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
       <c r="B447" t="s">
         <v>1600</v>
@@ -33878,7 +33935,7 @@
     </row>
     <row r="448" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A448" s="29" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="B448" t="s">
         <v>1601</v>
@@ -33909,7 +33966,7 @@
     </row>
     <row r="449" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" s="29" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="B449" s="87" t="s">
         <v>1602</v>
@@ -33942,7 +33999,7 @@
     </row>
     <row r="450" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A450" s="29" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="B450" s="87" t="s">
         <v>1448</v>
@@ -33973,7 +34030,7 @@
     </row>
     <row r="451" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A451" s="29" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="B451" s="87" t="s">
         <v>1449</v>
@@ -34004,7 +34061,7 @@
     </row>
     <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="29" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="B452" s="31" t="s">
         <v>1236</v>
@@ -34698,7 +34755,7 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="34" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="B472" s="29" t="s">
         <v>19</v>
@@ -34764,7 +34821,7 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="34" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="B474" s="29" t="s">
         <v>19</v>
@@ -34828,7 +34885,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="29" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="B476" s="29"/>
       <c r="C476" s="36"/>
@@ -35347,7 +35404,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="29" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="B491" s="32"/>
       <c r="C491" s="53" t="s">
@@ -35596,7 +35653,7 @@
     </row>
     <row r="498" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A498" s="34" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
       <c r="B498" s="59" t="s">
         <v>1103</v>
@@ -35938,7 +35995,7 @@
     </row>
     <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="34" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="B508" s="32"/>
       <c r="C508" s="53"/>
@@ -35965,7 +36022,7 @@
     </row>
     <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="24" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="B509" s="22"/>
       <c r="C509" s="25"/>
@@ -37110,7 +37167,7 @@
     </row>
     <row r="542" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A542" s="29" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="B542" s="59" t="s">
         <v>1666</v>
@@ -37139,7 +37196,7 @@
     </row>
     <row r="543" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A543" s="29" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
       <c r="B543" s="59" t="s">
         <v>1666</v>
@@ -37168,7 +37225,7 @@
     </row>
     <row r="544" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A544" s="29" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="B544" s="59" t="s">
         <v>1666</v>
@@ -37806,7 +37863,7 @@
     </row>
     <row r="566" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A566" s="29" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="B566" s="95"/>
       <c r="C566" s="73"/>
@@ -38969,7 +39026,7 @@
     </row>
     <row r="603" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A603" s="29" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="B603" s="73" t="s">
         <v>1281</v>
@@ -39002,7 +39059,7 @@
     </row>
     <row r="604" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A604" s="29" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="B604" s="73" t="s">
         <v>1281</v>
@@ -39035,7 +39092,7 @@
     </row>
     <row r="605" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A605" s="29" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="B605" s="73" t="s">
         <v>1281</v>
@@ -39068,7 +39125,7 @@
     </row>
     <row r="606" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="29" t="s">
-        <v>2881</v>
+        <v>2879</v>
       </c>
       <c r="B606" s="73" t="s">
         <v>1281</v>
@@ -39101,7 +39158,7 @@
     </row>
     <row r="607" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A607" s="29" t="s">
-        <v>2882</v>
+        <v>2880</v>
       </c>
       <c r="B607" s="73" t="s">
         <v>1281</v>
@@ -39132,7 +39189,7 @@
     </row>
     <row r="608" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A608" s="29" t="s">
-        <v>2883</v>
+        <v>2881</v>
       </c>
       <c r="B608" s="73" t="s">
         <v>1281</v>
@@ -39163,7 +39220,7 @@
     </row>
     <row r="609" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A609" s="29" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
       <c r="B609" s="73" t="s">
         <v>1281</v>
@@ -39194,7 +39251,7 @@
     </row>
     <row r="610" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A610" s="29" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
       <c r="B610" s="73" t="s">
         <v>1281</v>
@@ -39225,7 +39282,7 @@
     </row>
     <row r="611" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A611" s="29" t="s">
-        <v>2886</v>
+        <v>2884</v>
       </c>
       <c r="B611" s="73" t="s">
         <v>1281</v>
@@ -39256,7 +39313,7 @@
     </row>
     <row r="612" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A612" s="29" t="s">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="B612" s="73" t="s">
         <v>1281</v>
@@ -39287,7 +39344,7 @@
     </row>
     <row r="613" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A613" s="29" t="s">
-        <v>2888</v>
+        <v>2886</v>
       </c>
       <c r="B613" s="73" t="s">
         <v>1281</v>
@@ -39318,7 +39375,7 @@
     </row>
     <row r="614" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A614" s="29" t="s">
-        <v>2889</v>
+        <v>2887</v>
       </c>
       <c r="B614" s="73" t="s">
         <v>1281</v>
@@ -39349,7 +39406,7 @@
     </row>
     <row r="615" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A615" s="29" t="s">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="B615" s="73" t="s">
         <v>1281</v>
@@ -39380,7 +39437,7 @@
     </row>
     <row r="616" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A616" s="29" t="s">
-        <v>2891</v>
+        <v>2889</v>
       </c>
       <c r="B616" s="73" t="s">
         <v>1281</v>
@@ -39411,7 +39468,7 @@
     </row>
     <row r="617" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A617" s="29" t="s">
-        <v>2892</v>
+        <v>2890</v>
       </c>
       <c r="B617" s="73" t="s">
         <v>1281</v>
@@ -39444,7 +39501,7 @@
     </row>
     <row r="618" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A618" s="29" t="s">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="B618" s="73" t="s">
         <v>1281</v>
@@ -39477,7 +39534,7 @@
     </row>
     <row r="619" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A619" s="29" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="B619" s="82" t="s">
         <v>1270</v>
@@ -39508,7 +39565,7 @@
     </row>
     <row r="620" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A620" s="29" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="B620" s="82" t="s">
         <v>1270</v>
@@ -39539,7 +39596,7 @@
     </row>
     <row r="621" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A621" s="29" t="s">
-        <v>2896</v>
+        <v>2894</v>
       </c>
       <c r="B621" s="82" t="s">
         <v>1270</v>
@@ -39570,7 +39627,7 @@
     </row>
     <row r="622" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A622" s="29" t="s">
-        <v>2897</v>
+        <v>2895</v>
       </c>
       <c r="B622" s="82" t="s">
         <v>1270</v>
@@ -39603,7 +39660,7 @@
     </row>
     <row r="623" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A623" s="29" t="s">
-        <v>2898</v>
+        <v>2896</v>
       </c>
       <c r="B623" s="83" t="s">
         <v>1275</v>
@@ -39636,7 +39693,7 @@
     </row>
     <row r="624" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A624" s="29" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="B624" s="83" t="s">
         <v>1275</v>
@@ -39667,7 +39724,7 @@
     </row>
     <row r="625" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A625" s="29" t="s">
-        <v>2900</v>
+        <v>2898</v>
       </c>
       <c r="B625" s="83" t="s">
         <v>1275</v>
@@ -39698,7 +39755,7 @@
     </row>
     <row r="626" spans="1:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A626" s="29" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="B626" s="83" t="s">
         <v>1275</v>
@@ -39795,7 +39852,7 @@
     </row>
     <row r="629" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A629" s="29" t="s">
-        <v>2902</v>
+        <v>2900</v>
       </c>
       <c r="B629" s="82" t="s">
         <v>1329</v>
@@ -39822,7 +39879,7 @@
     </row>
     <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="29" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="B630" s="83" t="s">
         <v>1329</v>
@@ -40899,10 +40956,10 @@
     </row>
     <row r="661" spans="1:13" s="131" customFormat="1" ht="82" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A661" s="128" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="B661" s="83" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C661" s="128" t="s">
         <v>2393</v>
@@ -40920,13 +40977,13 @@
         <v>1470</v>
       </c>
       <c r="H661" s="56" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="I661" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J661" s="130" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="K661" s="128" t="s">
         <v>459</v>
@@ -40936,13 +40993,13 @@
     </row>
     <row r="662" spans="1:13" s="131" customFormat="1" ht="66" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A662" s="128" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="B662" s="83" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="C662" s="128" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="D662" s="84" t="s">
         <v>1621</v>
@@ -40957,13 +41014,13 @@
         <v>1470</v>
       </c>
       <c r="H662" s="56" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="I662" s="56" t="s">
         <v>96</v>
       </c>
       <c r="J662" s="130" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="K662" s="128" t="s">
         <v>981</v>
@@ -40973,7 +41030,7 @@
     </row>
     <row r="663" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A663" s="29" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="B663" s="84" t="s">
         <v>1844</v>
@@ -41000,7 +41057,7 @@
         <v>60</v>
       </c>
       <c r="J663" s="29" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="K663" s="29"/>
       <c r="L663" s="31"/>
@@ -42110,7 +42167,7 @@
     </row>
     <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="29" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="B698" s="85" t="s">
         <v>1362</v>
@@ -42139,7 +42196,7 @@
     </row>
     <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="29" t="s">
-        <v>2905</v>
+        <v>2903</v>
       </c>
       <c r="B699" s="85" t="s">
         <v>1362</v>
@@ -42168,7 +42225,7 @@
     </row>
     <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="29" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="B700" s="85" t="s">
         <v>1362</v>
@@ -42197,7 +42254,7 @@
     </row>
     <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="29" t="s">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="B701" s="85" t="s">
         <v>1362</v>
@@ -42226,7 +42283,7 @@
     </row>
     <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="29" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="B702" s="85" t="s">
         <v>1362</v>
@@ -42255,7 +42312,7 @@
     </row>
     <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="29" t="s">
-        <v>2909</v>
+        <v>2907</v>
       </c>
       <c r="B703" s="85" t="s">
         <v>1362</v>
@@ -42284,7 +42341,7 @@
     </row>
     <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="29" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="B704" s="85" t="s">
         <v>1362</v>
@@ -42313,7 +42370,7 @@
     </row>
     <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="29" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="B705" s="85" t="s">
         <v>1362</v>
@@ -42342,7 +42399,7 @@
     </row>
     <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="29" t="s">
-        <v>2912</v>
+        <v>2910</v>
       </c>
       <c r="B706" s="85" t="s">
         <v>1362</v>
@@ -42371,7 +42428,7 @@
     </row>
     <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="29" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="B707" s="85" t="s">
         <v>1362</v>
@@ -42400,7 +42457,7 @@
     </row>
     <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="29" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="B708" s="85" t="s">
         <v>1362</v>
@@ -42429,7 +42486,7 @@
     </row>
     <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="29" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="B709" s="85" t="s">
         <v>1362</v>
@@ -42458,7 +42515,7 @@
     </row>
     <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="29" t="s">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="B710" s="85" t="s">
         <v>1362</v>
@@ -42487,7 +42544,7 @@
     </row>
     <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="29" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="B711" s="85" t="s">
         <v>1362</v>
@@ -42516,7 +42573,7 @@
     </row>
     <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="29" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="B712" s="85" t="s">
         <v>1362</v>
@@ -42545,7 +42602,7 @@
     </row>
     <row r="713" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A713" s="29" t="s">
-        <v>2919</v>
+        <v>2917</v>
       </c>
       <c r="B713" s="85" t="s">
         <v>1362</v>
@@ -42574,7 +42631,7 @@
     </row>
     <row r="714" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A714" s="29" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="B714" s="85" t="s">
         <v>1363</v>
@@ -42603,7 +42660,7 @@
     </row>
     <row r="715" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A715" s="29" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="B715" s="85" t="s">
         <v>1363</v>
@@ -42632,7 +42689,7 @@
     </row>
     <row r="716" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A716" s="29" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="B716" s="85" t="s">
         <v>1363</v>
@@ -42661,7 +42718,7 @@
     </row>
     <row r="717" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A717" s="29" t="s">
-        <v>2923</v>
+        <v>2921</v>
       </c>
       <c r="B717" s="85" t="s">
         <v>1363</v>
@@ -42690,7 +42747,7 @@
     </row>
     <row r="718" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A718" s="29" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="B718" s="85" t="s">
         <v>1363</v>
@@ -42719,7 +42776,7 @@
     </row>
     <row r="719" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A719" s="29" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="B719" s="85" t="s">
         <v>1363</v>
@@ -42748,7 +42805,7 @@
     </row>
     <row r="720" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A720" s="29" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="B720" s="85" t="s">
         <v>1363</v>
@@ -42777,7 +42834,7 @@
     </row>
     <row r="721" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A721" s="29" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="B721" s="85" t="s">
         <v>1363</v>
@@ -45439,7 +45496,7 @@
     </row>
     <row r="801" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A801" s="29" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="B801" s="83" t="s">
         <v>1522</v>
@@ -45470,7 +45527,7 @@
     </row>
     <row r="802" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A802" s="29" t="s">
-        <v>2929</v>
+        <v>2927</v>
       </c>
       <c r="B802" s="83" t="s">
         <v>1522</v>
@@ -45501,7 +45558,7 @@
     </row>
     <row r="803" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A803" s="29" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="B803" s="83" t="s">
         <v>1522</v>
@@ -45532,7 +45589,7 @@
     </row>
     <row r="804" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A804" s="29" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="B804" s="83" t="s">
         <v>1522</v>
@@ -45563,7 +45620,7 @@
     </row>
     <row r="805" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A805" s="29" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="B805" s="83" t="s">
         <v>1522</v>
@@ -45594,7 +45651,7 @@
     </row>
     <row r="806" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A806" s="29" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="B806" s="85" t="s">
         <v>1477</v>
@@ -45623,7 +45680,7 @@
     </row>
     <row r="807" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A807" s="29" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="B807" s="85" t="s">
         <v>1477</v>
@@ -45652,7 +45709,7 @@
     </row>
     <row r="808" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A808" s="29" t="s">
-        <v>2935</v>
+        <v>2933</v>
       </c>
       <c r="B808" s="85" t="s">
         <v>1478</v>
@@ -45681,7 +45738,7 @@
     </row>
     <row r="809" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A809" s="29" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="B809" s="85" t="s">
         <v>1478</v>
@@ -45710,7 +45767,7 @@
     </row>
     <row r="810" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A810" s="29" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="B810" s="85" t="s">
         <v>1481</v>
@@ -45739,7 +45796,7 @@
     </row>
     <row r="811" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A811" s="29" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="B811" s="83"/>
       <c r="C811" s="83"/>
@@ -45756,19 +45813,19 @@
     </row>
     <row r="812" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A812" s="29" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="B812" s="83" t="s">
         <v>1667</v>
       </c>
       <c r="C812" s="83" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="D812" s="85" t="s">
         <v>1664</v>
       </c>
       <c r="E812" s="83" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="F812" s="31" t="s">
         <v>231</v>
@@ -45779,7 +45836,7 @@
       <c r="H812" s="29"/>
       <c r="I812" s="29"/>
       <c r="J812" s="29" t="s">
-        <v>2988</v>
+        <v>2986</v>
       </c>
       <c r="K812" s="29"/>
       <c r="L812" s="31"/>
@@ -45787,7 +45844,7 @@
     </row>
     <row r="813" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A813" s="29" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
       <c r="B813" s="83"/>
       <c r="C813" s="83"/>
@@ -45899,7 +45956,7 @@
     </row>
     <row r="817" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A817" s="29" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="B817" s="96" t="s">
         <v>1666</v>
@@ -45930,7 +45987,7 @@
     </row>
     <row r="818" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A818" s="29" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="B818" s="83" t="s">
         <v>1667</v>
@@ -45961,7 +46018,7 @@
     </row>
     <row r="819" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A819" s="29" t="s">
-        <v>2941</v>
+        <v>2939</v>
       </c>
       <c r="B819" s="83" t="s">
         <v>1667</v>
@@ -46116,7 +46173,7 @@
     </row>
     <row r="824" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A824" s="29" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="B824" s="83" t="s">
         <v>1565</v>
@@ -46147,7 +46204,7 @@
     </row>
     <row r="825" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A825" s="29" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="B825" s="83" t="s">
         <v>1566</v>
@@ -46178,7 +46235,7 @@
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A826" s="29" t="s">
-        <v>2944</v>
+        <v>2942</v>
       </c>
       <c r="B826" s="83" t="s">
         <v>1569</v>
@@ -46209,7 +46266,7 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A827" s="29" t="s">
-        <v>2945</v>
+        <v>2943</v>
       </c>
       <c r="B827" s="83" t="s">
         <v>1570</v>
@@ -46240,7 +46297,7 @@
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A828" s="29" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="B828" s="83" t="s">
         <v>1571</v>
@@ -46269,7 +46326,7 @@
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A829" s="29" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="B829" s="83" t="s">
         <v>1571</v>
@@ -47293,7 +47350,7 @@
       <c r="D860" s="83"/>
       <c r="E860" s="83"/>
       <c r="F860" s="31" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="G860" s="31" t="s">
         <v>52</v>
@@ -47767,7 +47824,7 @@
         <v>96</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -47983,7 +48040,7 @@
     </row>
     <row r="881" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A881" s="29" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="B881" s="83"/>
       <c r="C881" s="83"/>
@@ -50745,10 +50802,10 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A965" s="29" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="B965" s="100" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="C965" s="83" t="s">
         <v>329</v>
@@ -50774,10 +50831,10 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A966" s="29" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="B966" s="100" t="s">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="C966" s="83" t="s">
         <v>330</v>
@@ -50803,10 +50860,10 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A967" s="29" t="s">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="B967" s="100" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="C967" s="83" t="s">
         <v>329</v>
@@ -50832,10 +50889,10 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A968" s="29" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="B968" s="100" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="C968" s="83" t="s">
         <v>330</v>
@@ -50861,7 +50918,7 @@
     </row>
     <row r="969" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A969" s="29" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B969" s="100"/>
       <c r="C969" s="83"/>
@@ -50878,7 +50935,7 @@
     </row>
     <row r="970" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A970" s="29" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="B970" s="112"/>
       <c r="C970" s="120"/>
@@ -50898,7 +50955,7 @@
         <v>1521</v>
       </c>
       <c r="B971" s="100" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="C971" s="121" t="s">
         <v>752</v>
@@ -50928,10 +50985,10 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A972" s="29" t="s">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="B972" s="100" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="C972" s="122" t="s">
         <v>752</v>
@@ -50967,7 +51024,7 @@
         <v>1334</v>
       </c>
       <c r="D973" s="15" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="F973" t="s">
         <v>1542</v>
@@ -56017,7 +56074,7 @@
         <v>1520</v>
       </c>
       <c r="D1126" s="29" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="E1126" s="82" t="s">
         <v>2174</v>
@@ -56055,7 +56112,7 @@
         <v>1334</v>
       </c>
       <c r="E1127" s="83" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="F1127" s="31" t="s">
         <v>1643</v>
@@ -56076,7 +56133,7 @@
     </row>
     <row r="1128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1128" s="29" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="B1128" s="100"/>
       <c r="C1128" s="83"/>
@@ -57161,7 +57218,7 @@
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1161" s="29" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="B1161" s="85" t="s">
         <v>1666</v>
@@ -57188,7 +57245,7 @@
         <v>60</v>
       </c>
       <c r="J1161" s="29" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="K1161" s="29"/>
       <c r="L1161" s="31"/>
@@ -57196,7 +57253,7 @@
     </row>
     <row r="1162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1162" s="29" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="B1162" s="85" t="s">
         <v>1666</v>
@@ -57223,7 +57280,7 @@
         <v>60</v>
       </c>
       <c r="J1162" s="29" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="K1162" s="29"/>
       <c r="L1162" s="31"/>
@@ -57231,7 +57288,7 @@
     </row>
     <row r="1163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1163" s="29" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="B1163" s="85" t="s">
         <v>1666</v>
@@ -57266,7 +57323,7 @@
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1164" s="29" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="B1164" s="85" t="s">
         <v>1666</v>
@@ -57301,7 +57358,7 @@
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1165" s="29" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="B1165" s="85" t="s">
         <v>1666</v>
@@ -57328,7 +57385,7 @@
         <v>60</v>
       </c>
       <c r="J1165" s="29" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="K1165" s="29"/>
       <c r="L1165" s="31"/>
@@ -57336,7 +57393,7 @@
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1166" s="29" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="B1166" s="85" t="s">
         <v>1666</v>
@@ -57371,7 +57428,7 @@
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1167" s="29" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="B1167" s="85" t="s">
         <v>1666</v>
@@ -57406,7 +57463,7 @@
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1168" s="29" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="B1168" s="85" t="s">
         <v>1666</v>
@@ -57441,7 +57498,7 @@
     </row>
     <row r="1169" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="29" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="B1169" s="85" t="s">
         <v>1666</v>
@@ -57476,7 +57533,7 @@
     </row>
     <row r="1170" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="29" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="B1170" s="85" t="s">
         <v>1666</v>
@@ -57511,7 +57568,7 @@
     </row>
     <row r="1171" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="29" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="B1171" s="85" t="s">
         <v>1666</v>
@@ -57546,7 +57603,7 @@
     </row>
     <row r="1172" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="29" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="B1172" s="85" t="s">
         <v>1666</v>
@@ -57573,7 +57630,7 @@
         <v>60</v>
       </c>
       <c r="J1172" s="29" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="K1172" s="29"/>
       <c r="L1172" s="31"/>
@@ -57581,7 +57638,7 @@
     </row>
     <row r="1173" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="29" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="B1173" s="85" t="s">
         <v>1666</v>
@@ -57616,7 +57673,7 @@
     </row>
     <row r="1174" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="B1174" s="85" t="s">
         <v>1666</v>
@@ -57651,7 +57708,7 @@
     </row>
     <row r="1175" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="29" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="B1175" s="85" t="s">
         <v>1666</v>
@@ -57678,7 +57735,7 @@
         <v>60</v>
       </c>
       <c r="J1175" s="29" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="K1175" s="29"/>
       <c r="L1175" s="31"/>
@@ -57686,7 +57743,7 @@
     </row>
     <row r="1176" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="B1176" s="85" t="s">
         <v>1666</v>
@@ -57721,7 +57778,7 @@
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="B1177" s="85" t="s">
         <v>1666</v>
@@ -58804,7 +58861,7 @@
         <v>223</v>
       </c>
       <c r="E1210" s="83" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="F1210" s="31" t="s">
         <v>231</v>
@@ -58819,7 +58876,7 @@
         <v>96</v>
       </c>
       <c r="J1210" s="29" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="K1210" s="29" t="s">
         <v>2768</v>
@@ -59217,7 +59274,7 @@
         <v>2782</v>
       </c>
       <c r="B1222" s="83" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="C1222" s="83" t="s">
         <v>2770</v>
@@ -59459,19 +59516,19 @@
     </row>
     <row r="1229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1229" s="29" t="s">
-        <v>2963</v>
+        <v>2961</v>
       </c>
       <c r="B1229" s="100" t="s">
         <v>1477</v>
       </c>
       <c r="C1229" s="83" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="D1229" s="85" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="E1229" s="83" t="s">
-        <v>2959</v>
+        <v>2957</v>
       </c>
       <c r="F1229" s="31" t="s">
         <v>1542</v>
@@ -59486,29 +59543,29 @@
         <v>60</v>
       </c>
       <c r="J1229" s="29" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="K1229" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1229" s="31"/>
       <c r="M1229" s="29"/>
     </row>
     <row r="1230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1230" s="29" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="B1230" s="100" t="s">
         <v>1477</v>
       </c>
       <c r="C1230" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="D1230" s="85" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="E1230" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="F1230" s="31" t="s">
         <v>1542</v>
@@ -59523,29 +59580,29 @@
         <v>60</v>
       </c>
       <c r="J1230" s="29" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="K1230" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1230" s="31"/>
       <c r="M1230" s="29"/>
     </row>
     <row r="1231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1231" s="29" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="B1231" s="100" t="s">
         <v>1477</v>
       </c>
       <c r="C1231" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="D1231" s="85" t="s">
-        <v>2951</v>
+        <v>2949</v>
       </c>
       <c r="E1231" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="F1231" s="31" t="s">
         <v>1542</v>
@@ -59560,29 +59617,29 @@
         <v>60</v>
       </c>
       <c r="J1231" s="29" t="s">
-        <v>2975</v>
+        <v>2973</v>
       </c>
       <c r="K1231" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1231" s="31"/>
       <c r="M1231" s="29"/>
     </row>
     <row r="1232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1232" s="29" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="B1232" s="100" t="s">
         <v>1477</v>
       </c>
       <c r="C1232" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="D1232" s="85" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="E1232" s="83" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="F1232" s="31" t="s">
         <v>1542</v>
@@ -59597,29 +59654,29 @@
         <v>60</v>
       </c>
       <c r="J1232" s="29" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="K1232" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1232" s="31"/>
       <c r="M1232" s="29"/>
     </row>
     <row r="1233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1233" s="29" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="B1233" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1233" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="D1233" s="85" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="E1233" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="F1233" s="31" t="s">
         <v>1542</v>
@@ -59634,29 +59691,29 @@
         <v>60</v>
       </c>
       <c r="J1233" s="29" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="K1233" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1233" s="31"/>
       <c r="M1233" s="29"/>
     </row>
     <row r="1234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1234" s="29" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="B1234" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1234" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="D1234" s="85" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="E1234" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="F1234" s="31" t="s">
         <v>1542</v>
@@ -59671,29 +59728,29 @@
         <v>60</v>
       </c>
       <c r="J1234" s="29" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="K1234" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1234" s="31"/>
       <c r="M1234" s="29"/>
     </row>
     <row r="1235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1235" s="29" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="B1235" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1235" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="D1235" s="85" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="E1235" s="83" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="F1235" s="31" t="s">
         <v>1542</v>
@@ -59708,29 +59765,29 @@
         <v>60</v>
       </c>
       <c r="J1235" s="29" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="K1235" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1235" s="31"/>
       <c r="M1235" s="29"/>
     </row>
     <row r="1236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1236" s="29" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="B1236" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1236" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="D1236" s="85" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="E1236" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="F1236" s="31" t="s">
         <v>1542</v>
@@ -59745,29 +59802,29 @@
         <v>60</v>
       </c>
       <c r="J1236" s="29" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="K1236" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1236" s="31"/>
       <c r="M1236" s="29"/>
     </row>
     <row r="1237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1237" s="29" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="B1237" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1237" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="D1237" s="85" t="s">
-        <v>2957</v>
+        <v>2955</v>
       </c>
       <c r="E1237" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="F1237" s="31" t="s">
         <v>1542</v>
@@ -59782,29 +59839,29 @@
         <v>60</v>
       </c>
       <c r="J1237" s="29" t="s">
+        <v>2979</v>
+      </c>
+      <c r="K1237" s="29" t="s">
         <v>2981</v>
-      </c>
-      <c r="K1237" s="29" t="s">
-        <v>2983</v>
       </c>
       <c r="L1237" s="31"/>
       <c r="M1237" s="29"/>
     </row>
     <row r="1238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1238" s="29" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="B1238" s="100" t="s">
         <v>1478</v>
       </c>
       <c r="C1238" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="D1238" s="85" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="E1238" s="83" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="F1238" s="31" t="s">
         <v>1542</v>
@@ -59819,20 +59876,20 @@
         <v>60</v>
       </c>
       <c r="J1238" s="29" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="K1238" s="29" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L1238" s="31"/>
       <c r="M1238" s="29"/>
     </row>
     <row r="1239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1239" s="29" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="B1239" s="100" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="C1239" s="83" t="s">
         <v>752</v>
@@ -59850,13 +59907,13 @@
         <v>1474</v>
       </c>
       <c r="H1239" s="29" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="I1239" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1239" s="29" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="K1239" s="29"/>
       <c r="L1239" s="31"/>
@@ -59864,7 +59921,7 @@
     </row>
     <row r="1240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1240" s="29" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="B1240" s="100" t="s">
         <v>1042</v>
@@ -59885,13 +59942,13 @@
         <v>27</v>
       </c>
       <c r="H1240" s="29" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="I1240" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1240" s="29" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="K1240" s="29"/>
       <c r="L1240" s="31"/>
@@ -59899,7 +59956,7 @@
     </row>
     <row r="1241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1241" s="29" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="B1241" s="29" t="s">
         <v>1621</v>
@@ -59926,7 +59983,7 @@
         <v>96</v>
       </c>
       <c r="J1241" s="29" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="K1241" s="29"/>
       <c r="L1241" s="31"/>
@@ -59934,7 +59991,7 @@
     </row>
     <row r="1242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1242" s="29" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="B1242" s="100" t="s">
         <v>1664</v>
@@ -59965,16 +60022,16 @@
     </row>
     <row r="1243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1243" s="29" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="B1243" s="100" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="C1243" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1243" s="85" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E1243" s="83" t="s">
         <v>52</v>
@@ -59987,10 +60044,10 @@
       </c>
       <c r="H1243" s="29"/>
       <c r="I1243" s="119" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="J1243" s="29" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="K1243" s="29"/>
       <c r="L1243" s="31"/>
@@ -59998,16 +60055,16 @@
     </row>
     <row r="1244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1244" s="29" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="B1244" s="29" t="s">
         <v>1621</v>
       </c>
       <c r="C1244" s="83" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="D1244" s="100" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E1244" s="83" t="s">
         <v>2174</v>
@@ -60020,10 +60077,10 @@
       </c>
       <c r="H1244" s="29"/>
       <c r="I1244" s="119" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="J1244" s="29" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="K1244" s="29"/>
       <c r="L1244" s="31"/>
@@ -60031,10 +60088,10 @@
     </row>
     <row r="1245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1245" s="29" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="B1245" s="100" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="C1245" s="83" t="s">
         <v>213</v>
@@ -60050,7 +60107,7 @@
       <c r="H1245" s="29"/>
       <c r="I1245" s="119"/>
       <c r="J1245" s="29" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="K1245" s="29"/>
       <c r="L1245" s="31"/>
@@ -60058,7 +60115,7 @@
     </row>
     <row r="1246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1246" s="29" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="B1246" s="100"/>
       <c r="C1246" s="83"/>
@@ -60077,16 +60134,16 @@
     </row>
     <row r="1247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1247" s="29" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="B1247" s="100" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="C1247" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1247" s="85" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="E1247" s="83" t="s">
         <v>52</v>
@@ -60098,13 +60155,13 @@
         <v>52</v>
       </c>
       <c r="H1247" s="29" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="I1247" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1247" s="29" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="K1247" s="29"/>
       <c r="L1247" s="31" t="s">
@@ -60114,16 +60171,16 @@
     </row>
     <row r="1248" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1248" s="29" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="B1248" s="100" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="C1248" s="83" t="s">
         <v>52</v>
       </c>
       <c r="D1248" s="85" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E1248" s="83" t="s">
         <v>52</v>
@@ -60135,13 +60192,13 @@
         <v>52</v>
       </c>
       <c r="H1248" s="29" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="I1248" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1248" s="29" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="K1248" s="29"/>
       <c r="L1248" s="31" t="s">
@@ -60151,7 +60208,7 @@
     </row>
     <row r="1249" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="29" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="B1249" s="127" t="s">
         <v>1618</v>
@@ -60160,7 +60217,7 @@
         <v>2277</v>
       </c>
       <c r="D1249" s="85" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="E1249" s="83" t="s">
         <v>2174</v>
@@ -60172,13 +60229,13 @@
         <v>1470</v>
       </c>
       <c r="H1249" s="29" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="I1249" s="119" t="s">
         <v>96</v>
       </c>
       <c r="J1249" s="29" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="K1249" s="29"/>
       <c r="L1249" s="31"/>
@@ -60186,7 +60243,7 @@
     </row>
     <row r="1250" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="29" t="s">
-        <v>3033</v>
+        <v>3031</v>
       </c>
       <c r="B1250" s="85" t="s">
         <v>53</v>
@@ -60195,16 +60252,16 @@
         <v>2269</v>
       </c>
       <c r="D1250" s="100" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E1250" s="86" t="s">
-        <v>3036</v>
+        <v>3034</v>
       </c>
       <c r="F1250" s="31" t="s">
         <v>1542</v>
       </c>
       <c r="G1250" s="31" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="H1250" s="29">
         <v>0</v>
@@ -60213,7 +60270,7 @@
         <v>60</v>
       </c>
       <c r="J1250" s="29" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="K1250" s="29"/>
       <c r="L1250" s="31"/>
@@ -60221,7 +60278,7 @@
     </row>
     <row r="1251" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="29" t="s">
-        <v>3037</v>
+        <v>3035</v>
       </c>
       <c r="B1251" s="80" t="s">
         <v>1664</v>
@@ -60246,7 +60303,7 @@
         <v>60</v>
       </c>
       <c r="J1251" s="29" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="K1251" s="29"/>
       <c r="L1251" s="31"/>
@@ -60254,7 +60311,7 @@
     </row>
     <row r="1252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1252" s="29" t="s">
-        <v>3038</v>
+        <v>3036</v>
       </c>
       <c r="B1252" s="100" t="s">
         <v>2216</v>
@@ -60266,7 +60323,7 @@
         <v>960</v>
       </c>
       <c r="E1252" s="83" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="F1252" s="31" t="s">
         <v>1542</v>
@@ -60281,7 +60338,7 @@
         <v>60</v>
       </c>
       <c r="J1252" s="29" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="K1252" s="29"/>
       <c r="L1252" s="31"/>
@@ -60289,13 +60346,13 @@
     </row>
     <row r="1253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1253" s="29" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
       <c r="B1253" s="100" t="s">
         <v>960</v>
       </c>
       <c r="C1253" s="83" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="D1253" s="85" t="s">
         <v>1156</v>
@@ -60316,7 +60373,7 @@
         <v>60</v>
       </c>
       <c r="J1253" s="29" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="K1253" s="29"/>
       <c r="L1253" s="31"/>
@@ -60324,7 +60381,7 @@
     </row>
     <row r="1254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1254" s="29" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
       <c r="B1254" s="29" t="s">
         <v>1621</v>
@@ -60351,7 +60408,7 @@
         <v>96</v>
       </c>
       <c r="J1254" s="29" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="K1254" s="29"/>
       <c r="L1254" s="31"/>
@@ -60359,7 +60416,7 @@
     </row>
     <row r="1255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1255" s="29" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
       <c r="B1255" s="100" t="s">
         <v>1664</v>
@@ -60384,7 +60441,7 @@
         <v>60</v>
       </c>
       <c r="J1255" s="29" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="K1255" s="29"/>
       <c r="L1255" s="31"/>
@@ -60392,16 +60449,16 @@
     </row>
     <row r="1256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1256" s="29" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B1256" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1256" s="83" t="s">
         <v>2278</v>
       </c>
       <c r="D1256" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1256" s="83" t="s">
         <v>2372</v>
@@ -60425,16 +60482,16 @@
     </row>
     <row r="1257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1257" s="29" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="B1257" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1257" s="83" t="s">
         <v>2279</v>
       </c>
       <c r="D1257" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1257" s="83" t="s">
         <v>2373</v>
@@ -60458,16 +60515,16 @@
     </row>
     <row r="1258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1258" s="29" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="B1258" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1258" s="83" t="s">
         <v>2280</v>
       </c>
       <c r="D1258" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1258" s="83" t="s">
         <v>2374</v>
@@ -60491,16 +60548,16 @@
     </row>
     <row r="1259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1259" s="29" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="B1259" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1259" s="83" t="s">
         <v>2281</v>
       </c>
       <c r="D1259" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1259" s="83" t="s">
         <v>1845</v>
@@ -60524,16 +60581,16 @@
     </row>
     <row r="1260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1260" s="29" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="B1260" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1260" s="83" t="s">
         <v>2277</v>
       </c>
       <c r="D1260" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1260" s="83" t="s">
         <v>2282</v>
@@ -60557,16 +60614,16 @@
     </row>
     <row r="1261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1261" s="29" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="B1261" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1261" s="83" t="s">
         <v>2378</v>
       </c>
       <c r="D1261" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1261" s="83" t="s">
         <v>2026</v>
@@ -60590,16 +60647,16 @@
     </row>
     <row r="1262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1262" s="29" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="B1262" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1262" s="83" t="s">
         <v>2274</v>
       </c>
       <c r="D1262" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1262" s="83" t="s">
         <v>2283</v>
@@ -60623,16 +60680,16 @@
     </row>
     <row r="1263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1263" s="29" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="B1263" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1263" s="83" t="s">
         <v>2275</v>
       </c>
       <c r="D1263" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1263" s="83" t="s">
         <v>2284</v>
@@ -60656,16 +60713,16 @@
     </row>
     <row r="1264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1264" s="29" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="B1264" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1264" s="83" t="s">
         <v>2276</v>
       </c>
       <c r="D1264" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1264" s="83" t="s">
         <v>2257</v>
@@ -60689,16 +60746,16 @@
     </row>
     <row r="1265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1265" s="29" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="B1265" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1265" s="83" t="s">
         <v>2379</v>
       </c>
       <c r="D1265" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1265" s="83" t="s">
         <v>2285</v>
@@ -60722,16 +60779,16 @@
     </row>
     <row r="1266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1266" s="29" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="B1266" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1266" s="83" t="s">
         <v>1839</v>
       </c>
       <c r="D1266" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1266" s="83" t="s">
         <v>1841</v>
@@ -60755,16 +60812,16 @@
     </row>
     <row r="1267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1267" s="29" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B1267" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1267" s="83" t="s">
         <v>2259</v>
       </c>
       <c r="D1267" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1267" s="83" t="s">
         <v>1960</v>
@@ -60788,16 +60845,16 @@
     </row>
     <row r="1268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1268" s="29" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="B1268" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1268" s="83" t="s">
         <v>1846</v>
       </c>
       <c r="D1268" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1268" s="83" t="s">
         <v>1843</v>
@@ -60821,16 +60878,16 @@
     </row>
     <row r="1269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1269" s="29" t="s">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="B1269" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1269" s="83" t="s">
         <v>1847</v>
       </c>
       <c r="D1269" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1269" s="83" t="s">
         <v>1842</v>
@@ -60854,16 +60911,16 @@
     </row>
     <row r="1270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1270" s="29" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="B1270" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1270" s="83" t="s">
         <v>2256</v>
       </c>
       <c r="D1270" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1270" s="83" t="s">
         <v>2286</v>
@@ -60887,16 +60944,16 @@
     </row>
     <row r="1271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1271" s="29" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="B1271" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1271" s="83" t="s">
         <v>2255</v>
       </c>
       <c r="D1271" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1271" s="83" t="s">
         <v>2375</v>
@@ -60920,16 +60977,16 @@
     </row>
     <row r="1272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1272" s="29" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="B1272" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1272" s="83" t="s">
         <v>1852</v>
       </c>
       <c r="D1272" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1272" s="83" t="s">
         <v>1849</v>
@@ -60953,16 +61010,16 @@
     </row>
     <row r="1273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1273" s="29" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="B1273" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1273" s="83" t="s">
         <v>2380</v>
       </c>
       <c r="D1273" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1273" s="83" t="s">
         <v>2387</v>
@@ -60986,16 +61043,16 @@
     </row>
     <row r="1274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1274" s="29" t="s">
-        <v>3111</v>
+        <v>3109</v>
       </c>
       <c r="B1274" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1274" s="83" t="s">
         <v>2381</v>
       </c>
       <c r="D1274" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1274" s="83" t="s">
         <v>2388</v>
@@ -61019,16 +61076,16 @@
     </row>
     <row r="1275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1275" s="29" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="B1275" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1275" s="83" t="s">
         <v>2382</v>
       </c>
       <c r="D1275" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1275" s="83" t="s">
         <v>2389</v>
@@ -61052,16 +61109,16 @@
     </row>
     <row r="1276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1276" s="29" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="B1276" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1276" s="83" t="s">
         <v>2383</v>
       </c>
       <c r="D1276" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1276" s="83" t="s">
         <v>2390</v>
@@ -61085,16 +61142,16 @@
     </row>
     <row r="1277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1277" s="29" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="B1277" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1277" s="83" t="s">
         <v>2384</v>
       </c>
       <c r="D1277" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1277" s="83" t="s">
         <v>2391</v>
@@ -61118,16 +61175,16 @@
     </row>
     <row r="1278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1278" s="29" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="B1278" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1278" s="83" t="s">
         <v>2385</v>
       </c>
       <c r="D1278" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1278" s="83" t="s">
         <v>2392</v>
@@ -61151,16 +61208,16 @@
     </row>
     <row r="1279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1279" s="29" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="B1279" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1279" s="83" t="s">
         <v>2386</v>
       </c>
       <c r="D1279" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1279" s="83" t="s">
         <v>2393</v>
@@ -61184,7 +61241,7 @@
     </row>
     <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1280" s="128" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="B1280" s="100" t="s">
         <v>242</v>
@@ -61193,7 +61250,7 @@
         <v>1255</v>
       </c>
       <c r="D1280" s="100" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1280" s="83" t="s">
         <v>2386</v>
@@ -61205,13 +61262,13 @@
         <v>1470</v>
       </c>
       <c r="H1280" s="128" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="I1280" s="129" t="s">
         <v>60</v>
       </c>
       <c r="J1280" s="130" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="K1280" s="128"/>
       <c r="L1280" s="83"/>
@@ -61219,7 +61276,7 @@
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1281" s="29" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="B1281" s="85" t="s">
         <v>1666</v>
@@ -61228,7 +61285,7 @@
         <v>1238</v>
       </c>
       <c r="D1281" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1281" s="83" t="s">
         <v>2278</v>
@@ -61252,7 +61309,7 @@
     </row>
     <row r="1282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1282" s="29" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="B1282" s="85" t="s">
         <v>1666</v>
@@ -61261,7 +61318,7 @@
         <v>1240</v>
       </c>
       <c r="D1282" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1282" s="83" t="s">
         <v>2279</v>
@@ -61285,7 +61342,7 @@
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1283" s="29" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="B1283" s="85" t="s">
         <v>1666</v>
@@ -61294,7 +61351,7 @@
         <v>1214</v>
       </c>
       <c r="D1283" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1283" s="83" t="s">
         <v>2280</v>
@@ -61318,7 +61375,7 @@
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1284" s="29" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B1284" s="85" t="s">
         <v>1666</v>
@@ -61327,7 +61384,7 @@
         <v>1216</v>
       </c>
       <c r="D1284" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1284" s="83" t="s">
         <v>2281</v>
@@ -61351,7 +61408,7 @@
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1285" s="29" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="B1285" s="85" t="s">
         <v>1666</v>
@@ -61360,7 +61417,7 @@
         <v>1218</v>
       </c>
       <c r="D1285" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1285" s="83" t="s">
         <v>2277</v>
@@ -61384,7 +61441,7 @@
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1286" s="29" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="B1286" s="85" t="s">
         <v>1666</v>
@@ -61393,7 +61450,7 @@
         <v>1220</v>
       </c>
       <c r="D1286" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1286" s="83" t="s">
         <v>2378</v>
@@ -61417,7 +61474,7 @@
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1287" s="29" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="B1287" s="85" t="s">
         <v>1666</v>
@@ -61426,7 +61483,7 @@
         <v>1222</v>
       </c>
       <c r="D1287" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1287" s="83" t="s">
         <v>2274</v>
@@ -61450,7 +61507,7 @@
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1288" s="29" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="B1288" s="85" t="s">
         <v>1666</v>
@@ -61459,7 +61516,7 @@
         <v>1224</v>
       </c>
       <c r="D1288" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="E1288" s="83" t="s">
         <v>2275</v>
@@ -61483,10 +61540,10 @@
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1289" s="29" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="B1289" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1289" s="83" t="s">
         <v>2276</v>
@@ -61506,10 +61563,10 @@
     </row>
     <row r="1290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1290" s="29" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B1290" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1290" s="83" t="s">
         <v>2379</v>
@@ -61529,10 +61586,10 @@
     </row>
     <row r="1291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1291" s="29" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="B1291" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1291" s="83" t="s">
         <v>1839</v>
@@ -61552,10 +61609,10 @@
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1292" s="29" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B1292" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1292" s="83" t="s">
         <v>2259</v>
@@ -61575,10 +61632,10 @@
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1293" s="29" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B1293" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1293" s="83" t="s">
         <v>1846</v>
@@ -61598,10 +61655,10 @@
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1294" s="29" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="B1294" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1294" s="83" t="s">
         <v>1847</v>
@@ -61621,10 +61678,10 @@
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1295" s="29" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="B1295" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1295" s="83" t="s">
         <v>2256</v>
@@ -61644,10 +61701,10 @@
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1296" s="29" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="B1296" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1296" s="83" t="s">
         <v>2255</v>
@@ -61667,10 +61724,10 @@
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1297" s="29" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B1297" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1297" s="83" t="s">
         <v>1852</v>
@@ -61690,10 +61747,10 @@
     </row>
     <row r="1298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1298" s="29" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="B1298" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1298" s="83" t="s">
         <v>2380</v>
@@ -61713,10 +61770,10 @@
     </row>
     <row r="1299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1299" s="29" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="B1299" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1299" s="83" t="s">
         <v>2381</v>
@@ -61736,10 +61793,10 @@
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1300" s="29" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="B1300" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1300" s="83" t="s">
         <v>2382</v>
@@ -61759,10 +61816,10 @@
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1301" s="29" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="B1301" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1301" s="83" t="s">
         <v>2383</v>
@@ -61782,10 +61839,10 @@
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1302" s="29" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="B1302" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1302" s="83" t="s">
         <v>2384</v>
@@ -61805,10 +61862,10 @@
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1303" s="29" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="B1303" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1303" s="83" t="s">
         <v>2385</v>
@@ -61828,10 +61885,10 @@
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1304" s="29" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="B1304" s="100" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="C1304" s="83" t="s">
         <v>2386</v>
@@ -61851,7 +61908,7 @@
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1305" s="29" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="B1305" s="85" t="s">
         <v>1666</v>
@@ -61884,7 +61941,7 @@
     </row>
     <row r="1306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1306" s="29" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="B1306" s="85" t="s">
         <v>1666</v>
@@ -61917,7 +61974,7 @@
     </row>
     <row r="1307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1307" s="29" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="B1307" s="85" t="s">
         <v>1666</v>
@@ -61950,7 +62007,7 @@
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1308" s="29" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="B1308" s="85" t="s">
         <v>1666</v>
@@ -61983,7 +62040,7 @@
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1309" s="29" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="B1309" s="125"/>
       <c r="C1309" s="83"/>
@@ -62008,19 +62065,19 @@
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1310" s="29" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B1310" s="100" t="s">
         <v>1334</v>
       </c>
       <c r="C1310" s="83" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="D1310" s="85" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="E1310" s="83" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="F1310" s="31"/>
       <c r="G1310" s="31"/>
@@ -62033,19 +62090,19 @@
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1311" s="29" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="B1311" s="100" t="s">
         <v>1334</v>
       </c>
       <c r="C1311" s="83" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="D1311" s="85" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="E1311" s="83" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="F1311" s="31"/>
       <c r="G1311" s="31"/>
@@ -62058,19 +62115,19 @@
     </row>
     <row r="1312" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="29" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="B1312" s="85" t="s">
+        <v>3177</v>
+      </c>
+      <c r="C1312" s="83" t="s">
+        <v>3178</v>
+      </c>
+      <c r="D1312" s="85" t="s">
         <v>3179</v>
       </c>
-      <c r="C1312" s="83" t="s">
-        <v>3180</v>
-      </c>
-      <c r="D1312" s="85" t="s">
-        <v>3181</v>
-      </c>
       <c r="E1312" s="83" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="F1312" s="31"/>
       <c r="G1312" s="31"/>
@@ -62083,13 +62140,13 @@
     </row>
     <row r="1313" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="29" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B1313" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C1313" s="82" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="D1313" s="100" t="s">
         <v>1042</v>
@@ -62110,19 +62167,19 @@
         <v>96</v>
       </c>
       <c r="J1313" s="29" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="K1313" s="29"/>
       <c r="L1313" s="31" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="M1313" s="29" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="1314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1314" s="29" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="B1314" s="100" t="s">
         <v>1042</v>
@@ -62140,7 +62197,7 @@
         <v>1542</v>
       </c>
       <c r="G1314" s="31" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="H1314" s="29">
         <v>0</v>
@@ -62149,29 +62206,29 @@
         <v>497</v>
       </c>
       <c r="J1314" s="29" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="K1314" s="29" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="L1314" s="31"/>
       <c r="M1314" s="29"/>
     </row>
     <row r="1315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1315" s="29" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B1315" s="100" t="s">
+        <v>3194</v>
+      </c>
+      <c r="C1315" s="83" t="s">
         <v>3195</v>
-      </c>
-      <c r="B1315" s="100" t="s">
-        <v>3196</v>
-      </c>
-      <c r="C1315" s="83" t="s">
-        <v>3197</v>
       </c>
       <c r="D1315" s="85" t="s">
         <v>223</v>
       </c>
       <c r="E1315" s="83" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="F1315" s="31" t="s">
         <v>52</v>
@@ -62186,7 +62243,7 @@
         <v>96</v>
       </c>
       <c r="J1315" s="29" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="K1315" s="29"/>
       <c r="L1315" s="31"/>
@@ -62194,19 +62251,19 @@
     </row>
     <row r="1316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1316" s="29" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="B1316" s="100" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="C1316" s="83" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="D1316" s="85" t="s">
         <v>223</v>
       </c>
       <c r="E1316" s="83" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="F1316" s="31" t="s">
         <v>52</v>
@@ -62221,7 +62278,7 @@
         <v>96</v>
       </c>
       <c r="J1316" s="29" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="K1316" s="29"/>
       <c r="L1316" s="31"/>
@@ -62229,7 +62286,7 @@
     </row>
     <row r="1317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1317" s="29" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="B1317" s="100" t="s">
         <v>263</v>
@@ -62254,7 +62311,7 @@
         <v>96</v>
       </c>
       <c r="J1317" s="29" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="K1317" s="29"/>
       <c r="L1317" s="31"/>
@@ -62262,7 +62319,7 @@
     </row>
     <row r="1318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1318" s="29" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="B1318" s="100" t="s">
         <v>263</v>
@@ -62271,7 +62328,7 @@
         <v>1222</v>
       </c>
       <c r="D1318" s="85" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="E1318" s="83" t="s">
         <v>2174</v>
@@ -62288,14 +62345,14 @@
       </c>
       <c r="J1318" s="29"/>
       <c r="K1318" s="29" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="L1318" s="31"/>
       <c r="M1318" s="29"/>
     </row>
     <row r="1319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1319" s="29" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="B1319" s="100" t="s">
         <v>263</v>
@@ -62309,10 +62366,10 @@
       <c r="G1319" s="31"/>
       <c r="H1319" s="29"/>
       <c r="I1319" s="119" t="s">
-        <v>3002</v>
+        <v>3000</v>
       </c>
       <c r="J1319" s="29" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="K1319" s="29"/>
       <c r="L1319" s="31"/>
@@ -62320,7 +62377,7 @@
     </row>
     <row r="1320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1320" s="29" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="B1320" s="100" t="s">
         <v>263</v>
@@ -62345,7 +62402,7 @@
         <v>96</v>
       </c>
       <c r="J1320" s="29" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="K1320" s="29" t="s">
         <v>459</v>
@@ -62355,7 +62412,7 @@
     </row>
     <row r="1321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1321" s="29" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="B1321" s="100" t="s">
         <v>433</v>
@@ -62384,7 +62441,7 @@
     </row>
     <row r="1322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1322" s="142" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B1322" s="83" t="s">
         <v>433</v>
@@ -62403,14 +62460,14 @@
         <v>433</v>
       </c>
       <c r="K1322" s="29" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="L1322" s="136"/>
       <c r="M1322" s="29"/>
     </row>
     <row r="1323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1323" s="29" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="B1323" s="133" t="s">
         <v>263</v>
@@ -62433,29 +62490,29 @@
         <v>96</v>
       </c>
       <c r="J1323" s="29" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="K1323" s="29" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="L1323" s="136"/>
       <c r="M1323" s="29"/>
     </row>
     <row r="1324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1324" s="29" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="B1324" s="133" t="s">
         <v>262</v>
       </c>
       <c r="C1324" s="134" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="D1324" s="135" t="s">
         <v>263</v>
       </c>
       <c r="E1324" s="134" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="F1324" s="136"/>
       <c r="G1324" s="136"/>
@@ -62470,7 +62527,7 @@
     </row>
     <row r="1325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1325" s="29" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="B1325" s="133" t="s">
         <v>262</v>
@@ -62479,10 +62536,10 @@
         <v>2553</v>
       </c>
       <c r="D1325" s="135" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="E1325" s="134" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="F1325" s="136"/>
       <c r="G1325" s="136"/>
@@ -62493,7 +62550,7 @@
         <v>96</v>
       </c>
       <c r="J1325" s="29" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="K1325" s="29"/>
       <c r="L1325" s="136"/>
@@ -62501,7 +62558,7 @@
     </row>
     <row r="1326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1326" s="29" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="B1326" s="133"/>
       <c r="C1326" s="134"/>
@@ -62518,7 +62575,7 @@
     </row>
     <row r="1327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1327" s="29" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="B1327" s="133" t="s">
         <v>262</v>
@@ -62527,7 +62584,7 @@
         <v>1520</v>
       </c>
       <c r="D1327" s="135" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="E1327" s="134"/>
       <c r="F1327" s="136"/>
@@ -62537,7 +62594,7 @@
         <v>60</v>
       </c>
       <c r="J1327" s="29" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="K1327" s="29"/>
       <c r="L1327" s="136"/>
@@ -62545,7 +62602,7 @@
     </row>
     <row r="1328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1328" s="29" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="B1328" s="133" t="s">
         <v>262</v>
@@ -62554,7 +62611,7 @@
         <v>1219</v>
       </c>
       <c r="D1328" s="135" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="E1328" s="134"/>
       <c r="F1328" s="136"/>
@@ -62570,10 +62627,10 @@
     </row>
     <row r="1329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1329" s="31" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="B1329" s="133" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="C1329" s="134" t="s">
         <v>1134</v>
@@ -62582,7 +62639,7 @@
         <v>855</v>
       </c>
       <c r="E1329" s="134" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="F1329" s="136" t="s">
         <v>231</v>
@@ -62594,14 +62651,14 @@
       </c>
       <c r="J1329" s="29"/>
       <c r="K1329" s="29" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="L1329" s="136"/>
       <c r="M1329" s="29"/>
     </row>
     <row r="1330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1330" s="29" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="B1330" s="133" t="s">
         <v>262</v>
@@ -62620,29 +62677,29 @@
         <v>96</v>
       </c>
       <c r="J1330" s="29" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="K1330" s="29" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="L1330" s="136"/>
       <c r="M1330" s="29"/>
     </row>
     <row r="1331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1331" s="29" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="B1331" s="29" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="C1331" s="134" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="D1331" s="133" t="s">
         <v>262</v>
       </c>
       <c r="E1331" s="134" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="F1331" s="136"/>
       <c r="G1331" s="136" t="s">
@@ -62655,7 +62712,7 @@
         <v>96</v>
       </c>
       <c r="J1331" s="29" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="K1331" s="29"/>
       <c r="L1331" s="136"/>
@@ -62663,19 +62720,19 @@
     </row>
     <row r="1332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1332" s="29" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="B1332" s="135" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="C1332" s="134" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="D1332" s="133" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="E1332" s="134" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="F1332" s="136"/>
       <c r="G1332" s="136" t="s">
@@ -62686,7 +62743,7 @@
         <v>96</v>
       </c>
       <c r="J1332" s="29" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="K1332" s="29"/>
       <c r="L1332" s="136"/>
@@ -62694,19 +62751,19 @@
     </row>
     <row r="1333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1333" s="29" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="B1333" s="135" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="C1333" s="134" t="s">
         <v>2374</v>
       </c>
       <c r="D1333" s="29" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="E1333" s="134" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="F1333" s="136"/>
       <c r="G1333" s="136" t="s">
@@ -62717,7 +62774,7 @@
         <v>96</v>
       </c>
       <c r="J1333" s="29" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="K1333" s="29"/>
       <c r="L1333" s="136"/>
@@ -62725,7 +62782,7 @@
     </row>
     <row r="1334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1334" s="29" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B1334" s="135" t="s">
         <v>242</v>
@@ -62734,7 +62791,7 @@
         <v>1227</v>
       </c>
       <c r="D1334" s="133" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="E1334" s="134" t="s">
         <v>2280</v>
@@ -62748,7 +62805,7 @@
         <v>96</v>
       </c>
       <c r="J1334" s="29" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="K1334" s="29"/>
       <c r="L1334" s="136"/>
@@ -62756,7 +62813,7 @@
     </row>
     <row r="1335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1335" s="29" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="B1335" s="133" t="s">
         <v>1667</v>
@@ -62765,7 +62822,7 @@
         <v>1255</v>
       </c>
       <c r="D1335" s="85" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="E1335" s="83" t="s">
         <v>2174</v>
@@ -62781,84 +62838,160 @@
         <v>96</v>
       </c>
       <c r="J1335" s="29" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="K1335" s="29"/>
       <c r="L1335" s="136"/>
       <c r="M1335" s="29"/>
     </row>
     <row r="1336" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1336" s="29"/>
-      <c r="B1336" s="133"/>
-      <c r="C1336" s="134"/>
-      <c r="D1336" s="85"/>
+      <c r="A1336" s="29" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B1336" s="133" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1336" s="134" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D1336" s="85" t="s">
+        <v>3258</v>
+      </c>
       <c r="E1336" s="83"/>
       <c r="F1336" s="136"/>
-      <c r="G1336" s="136"/>
+      <c r="G1336" s="136" t="s">
+        <v>1470</v>
+      </c>
       <c r="H1336" s="137"/>
-      <c r="I1336" s="119"/>
-      <c r="J1336" s="29"/>
+      <c r="I1336" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1336" s="29" t="s">
+        <v>3259</v>
+      </c>
       <c r="K1336" s="29"/>
       <c r="L1336" s="136"/>
       <c r="M1336" s="29"/>
     </row>
     <row r="1337" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1337" s="29"/>
-      <c r="B1337" s="133"/>
-      <c r="C1337" s="134"/>
-      <c r="D1337" s="135"/>
+      <c r="A1337" s="29" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B1337" s="133" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1337" s="134" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D1337" s="85" t="s">
+        <v>3262</v>
+      </c>
       <c r="E1337" s="134"/>
       <c r="F1337" s="136"/>
-      <c r="G1337" s="136"/>
+      <c r="G1337" s="136" t="s">
+        <v>1470</v>
+      </c>
       <c r="H1337" s="137"/>
-      <c r="I1337" s="119"/>
-      <c r="J1337" s="29"/>
+      <c r="I1337" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1337" s="29" t="s">
+        <v>457</v>
+      </c>
       <c r="K1337" s="29"/>
       <c r="L1337" s="136"/>
       <c r="M1337" s="29"/>
     </row>
     <row r="1338" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1338" s="29"/>
-      <c r="B1338" s="133"/>
-      <c r="C1338" s="134"/>
-      <c r="D1338" s="135"/>
+      <c r="A1338" s="29" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B1338" s="133" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1338" s="134" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D1338" s="85" t="s">
+        <v>3263</v>
+      </c>
       <c r="E1338" s="134"/>
       <c r="F1338" s="136"/>
-      <c r="G1338" s="136"/>
+      <c r="G1338" s="136" t="s">
+        <v>1470</v>
+      </c>
       <c r="H1338" s="137"/>
-      <c r="I1338" s="119"/>
-      <c r="J1338" s="29"/>
+      <c r="I1338" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1338" s="29" t="s">
+        <v>457</v>
+      </c>
       <c r="K1338" s="29"/>
       <c r="L1338" s="136"/>
       <c r="M1338" s="29"/>
     </row>
     <row r="1339" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1339" s="29"/>
-      <c r="B1339" s="133"/>
-      <c r="C1339" s="134"/>
-      <c r="D1339" s="135"/>
-      <c r="E1339" s="134"/>
+      <c r="A1339" s="29" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B1339" s="133" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1339" s="134" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D1339" s="135" t="s">
+        <v>2616</v>
+      </c>
+      <c r="E1339" s="134" t="s">
+        <v>2617</v>
+      </c>
       <c r="F1339" s="136"/>
-      <c r="G1339" s="136"/>
+      <c r="G1339" s="136" t="s">
+        <v>1470</v>
+      </c>
       <c r="H1339" s="137"/>
-      <c r="I1339" s="119"/>
-      <c r="J1339" s="29"/>
+      <c r="I1339" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1339" s="29" t="s">
+        <v>3266</v>
+      </c>
       <c r="K1339" s="29"/>
       <c r="L1339" s="136"/>
       <c r="M1339" s="29"/>
     </row>
     <row r="1340" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1340" s="29"/>
-      <c r="B1340" s="133"/>
-      <c r="C1340" s="134"/>
-      <c r="D1340" s="135"/>
-      <c r="E1340" s="134"/>
-      <c r="F1340" s="136"/>
-      <c r="G1340" s="136"/>
-      <c r="H1340" s="137"/>
-      <c r="I1340" s="119"/>
-      <c r="J1340" s="29"/>
-      <c r="K1340" s="29"/>
+      <c r="A1340" s="45" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B1340" s="144" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1340" s="145" t="s">
+        <v>3267</v>
+      </c>
+      <c r="D1340" s="146" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1340" s="145" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F1340" s="41"/>
+      <c r="G1340" s="41" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H1340" s="45"/>
+      <c r="I1340" s="147" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1340" s="45" t="s">
+        <v>3266</v>
+      </c>
+      <c r="K1340" s="45" t="s">
+        <v>3268</v>
+      </c>
       <c r="L1340" s="136"/>
       <c r="M1340" s="29"/>
     </row>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5F728E-E679-B544-8E4D-133C9F010BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4550386-5D6C-4344-A919-D06B6624349A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="3" r:id="rId3"/>
-    <pivotCache cacheId="5" r:id="rId4"/>
+    <pivotCache cacheId="19" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11013" uniqueCount="3276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11437" uniqueCount="3375">
   <si>
     <t>Tag</t>
   </si>
@@ -9341,9 +9341,6 @@
   </si>
   <si>
     <t>pt1279</t>
-  </si>
-  <si>
-    <t>notag1280</t>
   </si>
   <si>
     <t>uplink to switch in 2602-1800.
@@ -9856,9 +9853,6 @@
     <t>blank112</t>
   </si>
   <si>
-    <t>cable</t>
-  </si>
-  <si>
     <t>Electrical room - rogers ingress</t>
   </si>
   <si>
@@ -9872,6 +9866,309 @@
   </si>
   <si>
     <t>MHPR-G002</t>
+  </si>
+  <si>
+    <t>south_lot</t>
+  </si>
+  <si>
+    <t>security camera</t>
+  </si>
+  <si>
+    <t>notag1047</t>
+  </si>
+  <si>
+    <t>10-BaseT</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>PDU</t>
+  </si>
+  <si>
+    <t>AANU-G001</t>
+  </si>
+  <si>
+    <t>notag1348</t>
+  </si>
+  <si>
+    <t>notag1349</t>
+  </si>
+  <si>
+    <t>2606-2305</t>
+  </si>
+  <si>
+    <t>2606-2306</t>
+  </si>
+  <si>
+    <t>prayer room</t>
+  </si>
+  <si>
+    <t>2606-2399</t>
+  </si>
+  <si>
+    <t>pt1350</t>
+  </si>
+  <si>
+    <t>pt1351</t>
+  </si>
+  <si>
+    <t>pt1352</t>
+  </si>
+  <si>
+    <t>pt1353</t>
+  </si>
+  <si>
+    <t>pt1354</t>
+  </si>
+  <si>
+    <t>pt1355</t>
+  </si>
+  <si>
+    <t>pt1356</t>
+  </si>
+  <si>
+    <t>pt1357</t>
+  </si>
+  <si>
+    <t>pt1358</t>
+  </si>
+  <si>
+    <t>pt1359</t>
+  </si>
+  <si>
+    <t>pt1360</t>
+  </si>
+  <si>
+    <t>pt1361</t>
+  </si>
+  <si>
+    <t>pt1362</t>
+  </si>
+  <si>
+    <t>pt1363</t>
+  </si>
+  <si>
+    <t>pt1364</t>
+  </si>
+  <si>
+    <t>pt1365</t>
+  </si>
+  <si>
+    <t>pt1366</t>
+  </si>
+  <si>
+    <t>pt1367</t>
+  </si>
+  <si>
+    <t>pt1368</t>
+  </si>
+  <si>
+    <t>pt1369</t>
+  </si>
+  <si>
+    <t>pt1370</t>
+  </si>
+  <si>
+    <t>pt1371</t>
+  </si>
+  <si>
+    <t>pt1372</t>
+  </si>
+  <si>
+    <t>pt1373</t>
+  </si>
+  <si>
+    <t>Switch A002 in Electrical Room</t>
+  </si>
+  <si>
+    <t>2606-2307</t>
+  </si>
+  <si>
+    <t>bookkeepper</t>
+  </si>
+  <si>
+    <t>2606-2308</t>
+  </si>
+  <si>
+    <t>2606-2309</t>
+  </si>
+  <si>
+    <t>cat5</t>
+  </si>
+  <si>
+    <t>2606-2310</t>
+  </si>
+  <si>
+    <t>Gb1</t>
+  </si>
+  <si>
+    <t>CSWU1</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>DOCSIS</t>
+  </si>
+  <si>
+    <t>jp01</t>
+  </si>
+  <si>
+    <t>jp02</t>
+  </si>
+  <si>
+    <t>jp03</t>
+  </si>
+  <si>
+    <t>jp04</t>
+  </si>
+  <si>
+    <t>jp05</t>
+  </si>
+  <si>
+    <t>jp06</t>
+  </si>
+  <si>
+    <t>jp07</t>
+  </si>
+  <si>
+    <t>jp08</t>
+  </si>
+  <si>
+    <t>jp09</t>
+  </si>
+  <si>
+    <t>jp11</t>
+  </si>
+  <si>
+    <t>jp12</t>
+  </si>
+  <si>
+    <t>jp13</t>
+  </si>
+  <si>
+    <t>jp14</t>
+  </si>
+  <si>
+    <t>jp15</t>
+  </si>
+  <si>
+    <t>jp16</t>
+  </si>
+  <si>
+    <t>drop01</t>
+  </si>
+  <si>
+    <t>drop02</t>
+  </si>
+  <si>
+    <t>drop03</t>
+  </si>
+  <si>
+    <t>drop04</t>
+  </si>
+  <si>
+    <t>drop05</t>
+  </si>
+  <si>
+    <t>drop06</t>
+  </si>
+  <si>
+    <t>drop07</t>
+  </si>
+  <si>
+    <t>drop08</t>
+  </si>
+  <si>
+    <t>drop09</t>
+  </si>
+  <si>
+    <t>drop11</t>
+  </si>
+  <si>
+    <t>drop12</t>
+  </si>
+  <si>
+    <t>drop13</t>
+  </si>
+  <si>
+    <t>drop14</t>
+  </si>
+  <si>
+    <t>drop15</t>
+  </si>
+  <si>
+    <t>drop16</t>
+  </si>
+  <si>
+    <t>drop17</t>
+  </si>
+  <si>
+    <t>unk1387</t>
+  </si>
+  <si>
+    <t>unk1395</t>
+  </si>
+  <si>
+    <t>unk1396</t>
+  </si>
+  <si>
+    <t>unk1397</t>
+  </si>
+  <si>
+    <t>unk1398</t>
+  </si>
+  <si>
+    <t>unk1399</t>
+  </si>
+  <si>
+    <t>unk1400</t>
+  </si>
+  <si>
+    <t>unk1401</t>
+  </si>
+  <si>
+    <t>room 135</t>
+  </si>
+  <si>
+    <t>room 134</t>
+  </si>
+  <si>
+    <t>Room 133</t>
+  </si>
+  <si>
+    <t>Room 132</t>
+  </si>
+  <si>
+    <t>Room 120</t>
+  </si>
+  <si>
+    <t>Room 128</t>
+  </si>
+  <si>
+    <t>Room 122</t>
+  </si>
+  <si>
+    <t>Room 121</t>
+  </si>
+  <si>
+    <t>Room 125</t>
+  </si>
+  <si>
+    <t>Room 126</t>
+  </si>
+  <si>
+    <t>Room 124</t>
+  </si>
+  <si>
+    <t>Room 131</t>
+  </si>
+  <si>
+    <t>usage unkown</t>
+  </si>
+  <si>
+    <t>unk1394</t>
   </si>
 </sst>
 </file>
@@ -9881,7 +10178,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Yes&quot;;&quot;Yes&quot;;&quot;No&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -9984,6 +10281,13 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -10304,7 +10608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10571,8 +10875,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10589,6 +10891,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11020,7 +11323,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Terry Doner" refreshedDate="46030.710642245373" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="442" xr:uid="{966EC718-ADB8-7746-9366-54097C9D57FA}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:M1369" sheet="Cables"/>
+    <worksheetSource ref="A1:M1414" sheet="Cables"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="Tag" numFmtId="0">
@@ -19394,7 +19697,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{10F736CA-5D69-4D44-A803-D4241D124F38}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B56" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -19714,8 +20017,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1370" totalsRowCount="1" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
-  <autoFilter ref="A1:M1369" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}" name="Table1" displayName="Table1" ref="A1:M1415" totalsRowCount="1" headerRowDxfId="19" dataDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="A1:M1414" xr:uid="{BD7E3698-8860-904B-8BDB-00EF1039C49C}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4D442337-BE86-B24A-84A4-338FB80A6A49}" name="Tag" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{74A36D7B-C989-3B4B-B1E5-AB1FA4C2DD45}" name="SrcTag" dataDxfId="10" totalsRowDxfId="0"/>
@@ -20032,7 +20335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B91ADC-4569-1C4E-B002-1ED2E647C959}">
-  <dimension ref="A1:W1370"/>
+  <dimension ref="A1:W1415"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" customWidth="1"/>
@@ -20477,7 +20780,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>256</v>
@@ -20510,7 +20813,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>256</v>
@@ -20543,7 +20846,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>256</v>
@@ -20576,7 +20879,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>256</v>
@@ -23419,8 +23722,12 @@
       <c r="C109" s="23">
         <v>24</v>
       </c>
-      <c r="D109" s="22"/>
-      <c r="E109" s="23"/>
+      <c r="D109" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E109" s="23" t="s">
+        <v>2268</v>
+      </c>
       <c r="F109" s="23" t="s">
         <v>226</v>
       </c>
@@ -23433,7 +23740,9 @@
       <c r="I109" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="J109" s="23"/>
+      <c r="J109" s="23" t="s">
+        <v>3285</v>
+      </c>
       <c r="K109" s="23"/>
       <c r="L109" s="19"/>
       <c r="M109" s="20"/>
@@ -23502,7 +23811,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="B112" s="22"/>
       <c r="C112" s="23"/>
@@ -23519,7 +23828,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="B113" s="22"/>
       <c r="C113" s="23"/>
@@ -23536,7 +23845,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="B114" s="22"/>
       <c r="C114" s="23"/>
@@ -23582,24 +23891,24 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="28" t="s">
-        <v>3253</v>
-      </c>
-      <c r="B116" s="148"/>
-      <c r="C116" s="149"/>
-      <c r="D116" s="148"/>
-      <c r="E116" s="149"/>
-      <c r="F116" s="149"/>
-      <c r="G116" s="149"/>
-      <c r="H116" s="149"/>
-      <c r="I116" s="149"/>
-      <c r="J116" s="149"/>
-      <c r="K116" s="149"/>
+        <v>3252</v>
+      </c>
+      <c r="B116" s="146"/>
+      <c r="C116" s="147"/>
+      <c r="D116" s="146"/>
+      <c r="E116" s="147"/>
+      <c r="F116" s="147"/>
+      <c r="G116" s="147"/>
+      <c r="H116" s="147"/>
+      <c r="I116" s="147"/>
+      <c r="J116" s="147"/>
+      <c r="K116" s="147"/>
       <c r="L116" s="23"/>
       <c r="M116" s="24"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="B117" s="22"/>
       <c r="C117" s="23"/>
@@ -23616,7 +23925,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="23"/>
@@ -28333,7 +28642,7 @@
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="29" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="B263" s="31" t="s">
         <v>223</v>
@@ -28792,22 +29101,32 @@
         <v>591</v>
       </c>
       <c r="B279" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="C279" s="29"/>
-      <c r="D279" s="31"/>
-      <c r="E279" s="29"/>
+        <v>240</v>
+      </c>
+      <c r="C279" s="29">
+        <v>17</v>
+      </c>
+      <c r="D279" s="31" t="s">
+        <v>3274</v>
+      </c>
+      <c r="E279" s="29" t="s">
+        <v>2162</v>
+      </c>
       <c r="F279" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="G279" s="31"/>
+      <c r="G279" s="31" t="s">
+        <v>1458</v>
+      </c>
       <c r="H279" s="29" t="s">
         <v>590</v>
       </c>
       <c r="I279" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="J279" s="29"/>
+      <c r="J279" s="29" t="s">
+        <v>3275</v>
+      </c>
       <c r="K279" s="29"/>
       <c r="L279" s="31"/>
       <c r="M279" s="29"/>
@@ -30043,10 +30362,10 @@
         <v>96</v>
       </c>
       <c r="J320" s="29" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="K320" s="29" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="L320" s="31"/>
       <c r="M320" s="29"/>
@@ -31693,16 +32012,16 @@
         <v>843</v>
       </c>
       <c r="B374" s="31" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C374" s="29" t="s">
         <v>3218</v>
-      </c>
-      <c r="C374" s="29" t="s">
-        <v>3219</v>
       </c>
       <c r="D374" s="31" t="s">
         <v>844</v>
       </c>
       <c r="E374" s="29" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="F374" s="31" t="s">
         <v>296</v>
@@ -31715,7 +32034,7 @@
         <v>96</v>
       </c>
       <c r="J374" s="29" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="K374" s="29" t="s">
         <v>845</v>
@@ -31725,7 +32044,7 @@
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="29" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="B375" s="31" t="s">
         <v>254</v>
@@ -31756,7 +32075,7 @@
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="29" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="B376" s="31" t="s">
         <v>254</v>
@@ -31787,7 +32106,7 @@
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="29" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="B377" s="31" t="s">
         <v>255</v>
@@ -31812,7 +32131,7 @@
         <v>60</v>
       </c>
       <c r="J377" s="29" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="K377" s="29"/>
       <c r="L377" s="31"/>
@@ -31820,7 +32139,7 @@
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="29" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="B378" s="31" t="s">
         <v>255</v>
@@ -31845,7 +32164,7 @@
         <v>60</v>
       </c>
       <c r="J378" s="29" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="K378" s="29"/>
       <c r="L378" s="31"/>
@@ -40934,7 +41253,7 @@
         <v>96</v>
       </c>
       <c r="J661" s="130" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="K661" s="128" t="s">
         <v>449</v>
@@ -40947,7 +41266,7 @@
         <v>3070</v>
       </c>
       <c r="B662" s="83" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="C662" s="128" t="s">
         <v>3075</v>
@@ -40971,7 +41290,7 @@
         <v>96</v>
       </c>
       <c r="J662" s="130" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="K662" s="128" t="s">
         <v>969</v>
@@ -47775,7 +48094,7 @@
         <v>96</v>
       </c>
       <c r="J874" s="29" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="K874" s="29"/>
       <c r="L874" s="31"/>
@@ -56063,7 +56382,7 @@
         <v>1322</v>
       </c>
       <c r="E1127" s="83" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="F1127" s="31" t="s">
         <v>1631</v>
@@ -56084,7 +56403,7 @@
     </row>
     <row r="1128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1128" s="29" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B1128" s="100"/>
       <c r="C1128" s="83"/>
@@ -57169,7 +57488,7 @@
     </row>
     <row r="1161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1161" s="29" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="B1161" s="85" t="s">
         <v>1654</v>
@@ -57196,7 +57515,7 @@
         <v>60</v>
       </c>
       <c r="J1161" s="29" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="K1161" s="29"/>
       <c r="L1161" s="31"/>
@@ -57204,7 +57523,7 @@
     </row>
     <row r="1162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1162" s="29" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="B1162" s="85" t="s">
         <v>1654</v>
@@ -57231,7 +57550,7 @@
         <v>60</v>
       </c>
       <c r="J1162" s="29" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="K1162" s="29"/>
       <c r="L1162" s="31"/>
@@ -57239,7 +57558,7 @@
     </row>
     <row r="1163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1163" s="29" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="B1163" s="85" t="s">
         <v>1654</v>
@@ -57274,7 +57593,7 @@
     </row>
     <row r="1164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1164" s="29" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="B1164" s="85" t="s">
         <v>1654</v>
@@ -57309,7 +57628,7 @@
     </row>
     <row r="1165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1165" s="29" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="B1165" s="85" t="s">
         <v>1654</v>
@@ -57336,7 +57655,7 @@
         <v>60</v>
       </c>
       <c r="J1165" s="29" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="K1165" s="29"/>
       <c r="L1165" s="31"/>
@@ -57344,7 +57663,7 @@
     </row>
     <row r="1166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1166" s="29" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B1166" s="85" t="s">
         <v>1654</v>
@@ -57379,7 +57698,7 @@
     </row>
     <row r="1167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1167" s="29" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B1167" s="85" t="s">
         <v>1654</v>
@@ -57414,7 +57733,7 @@
     </row>
     <row r="1168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1168" s="29" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="B1168" s="85" t="s">
         <v>1654</v>
@@ -57449,7 +57768,7 @@
     </row>
     <row r="1169" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1169" s="29" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="B1169" s="85" t="s">
         <v>1654</v>
@@ -57484,7 +57803,7 @@
     </row>
     <row r="1170" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="29" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="B1170" s="85" t="s">
         <v>1654</v>
@@ -57519,7 +57838,7 @@
     </row>
     <row r="1171" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1171" s="29" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B1171" s="85" t="s">
         <v>1654</v>
@@ -57554,7 +57873,7 @@
     </row>
     <row r="1172" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="29" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="B1172" s="85" t="s">
         <v>1654</v>
@@ -57581,7 +57900,7 @@
         <v>60</v>
       </c>
       <c r="J1172" s="29" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="K1172" s="29"/>
       <c r="L1172" s="31"/>
@@ -57589,7 +57908,7 @@
     </row>
     <row r="1173" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1173" s="29" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B1173" s="85" t="s">
         <v>1654</v>
@@ -57624,7 +57943,7 @@
     </row>
     <row r="1174" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="29" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="B1174" s="85" t="s">
         <v>1654</v>
@@ -57659,7 +57978,7 @@
     </row>
     <row r="1175" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1175" s="29" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B1175" s="85" t="s">
         <v>1654</v>
@@ -57686,7 +58005,7 @@
         <v>60</v>
       </c>
       <c r="J1175" s="29" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="K1175" s="29"/>
       <c r="L1175" s="31"/>
@@ -57694,7 +58013,7 @@
     </row>
     <row r="1176" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="29" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B1176" s="85" t="s">
         <v>1654</v>
@@ -57729,7 +58048,7 @@
     </row>
     <row r="1177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1177" s="29" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="B1177" s="85" t="s">
         <v>1654</v>
@@ -58812,7 +59131,7 @@
         <v>223</v>
       </c>
       <c r="E1210" s="83" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="F1210" s="31" t="s">
         <v>231</v>
@@ -58827,7 +59146,7 @@
         <v>96</v>
       </c>
       <c r="J1210" s="29" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="K1210" s="29" t="s">
         <v>2756</v>
@@ -61192,13 +61511,13 @@
     </row>
     <row r="1280" spans="1:13" s="131" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A1280" s="128" t="s">
-        <v>3100</v>
+        <v>3283</v>
       </c>
       <c r="B1280" s="100" t="s">
         <v>240</v>
       </c>
       <c r="C1280" s="83" t="s">
-        <v>1243</v>
+        <v>1209</v>
       </c>
       <c r="D1280" s="100" t="s">
         <v>3073</v>
@@ -61219,7 +61538,7 @@
         <v>60</v>
       </c>
       <c r="J1280" s="130" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="K1280" s="128"/>
       <c r="L1280" s="83"/>
@@ -61227,7 +61546,7 @@
     </row>
     <row r="1281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1281" s="29" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B1281" s="85" t="s">
         <v>1654</v>
@@ -61236,7 +61555,7 @@
         <v>1226</v>
       </c>
       <c r="D1281" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1281" s="83" t="s">
         <v>2266</v>
@@ -61260,7 +61579,7 @@
     </row>
     <row r="1282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1282" s="29" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B1282" s="85" t="s">
         <v>1654</v>
@@ -61269,7 +61588,7 @@
         <v>1228</v>
       </c>
       <c r="D1282" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1282" s="83" t="s">
         <v>2267</v>
@@ -61293,7 +61612,7 @@
     </row>
     <row r="1283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1283" s="29" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="B1283" s="85" t="s">
         <v>1654</v>
@@ -61302,7 +61621,7 @@
         <v>1202</v>
       </c>
       <c r="D1283" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1283" s="83" t="s">
         <v>2268</v>
@@ -61326,7 +61645,7 @@
     </row>
     <row r="1284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1284" s="29" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B1284" s="85" t="s">
         <v>1654</v>
@@ -61335,7 +61654,7 @@
         <v>1204</v>
       </c>
       <c r="D1284" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1284" s="83" t="s">
         <v>2269</v>
@@ -61359,7 +61678,7 @@
     </row>
     <row r="1285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1285" s="29" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="B1285" s="85" t="s">
         <v>1654</v>
@@ -61368,7 +61687,7 @@
         <v>1206</v>
       </c>
       <c r="D1285" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1285" s="83" t="s">
         <v>2265</v>
@@ -61392,7 +61711,7 @@
     </row>
     <row r="1286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1286" s="29" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B1286" s="85" t="s">
         <v>1654</v>
@@ -61401,7 +61720,7 @@
         <v>1208</v>
       </c>
       <c r="D1286" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1286" s="83" t="s">
         <v>2366</v>
@@ -61425,7 +61744,7 @@
     </row>
     <row r="1287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1287" s="29" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="B1287" s="85" t="s">
         <v>1654</v>
@@ -61434,7 +61753,7 @@
         <v>1210</v>
       </c>
       <c r="D1287" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1287" s="83" t="s">
         <v>2262</v>
@@ -61458,7 +61777,7 @@
     </row>
     <row r="1288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1288" s="29" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B1288" s="85" t="s">
         <v>1654</v>
@@ -61467,7 +61786,7 @@
         <v>1212</v>
       </c>
       <c r="D1288" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E1288" s="83" t="s">
         <v>2263</v>
@@ -61491,10 +61810,10 @@
     </row>
     <row r="1289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1289" s="29" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="B1289" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1289" s="83" t="s">
         <v>2264</v>
@@ -61514,10 +61833,10 @@
     </row>
     <row r="1290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1290" s="29" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B1290" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1290" s="83" t="s">
         <v>2367</v>
@@ -61537,10 +61856,10 @@
     </row>
     <row r="1291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1291" s="29" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="B1291" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1291" s="83" t="s">
         <v>1827</v>
@@ -61560,10 +61879,10 @@
     </row>
     <row r="1292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1292" s="29" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="B1292" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1292" s="83" t="s">
         <v>2247</v>
@@ -61583,10 +61902,10 @@
     </row>
     <row r="1293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1293" s="29" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="B1293" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1293" s="83" t="s">
         <v>1834</v>
@@ -61606,10 +61925,10 @@
     </row>
     <row r="1294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1294" s="29" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="B1294" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1294" s="83" t="s">
         <v>1835</v>
@@ -61629,10 +61948,10 @@
     </row>
     <row r="1295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1295" s="29" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="B1295" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1295" s="83" t="s">
         <v>2244</v>
@@ -61652,10 +61971,10 @@
     </row>
     <row r="1296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1296" s="29" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="B1296" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1296" s="83" t="s">
         <v>2243</v>
@@ -61675,10 +61994,10 @@
     </row>
     <row r="1297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1297" s="29" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="B1297" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1297" s="83" t="s">
         <v>1840</v>
@@ -61698,10 +62017,10 @@
     </row>
     <row r="1298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1298" s="29" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="B1298" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1298" s="83" t="s">
         <v>2368</v>
@@ -61721,10 +62040,10 @@
     </row>
     <row r="1299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1299" s="29" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="B1299" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1299" s="83" t="s">
         <v>2369</v>
@@ -61744,10 +62063,10 @@
     </row>
     <row r="1300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1300" s="29" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="B1300" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1300" s="83" t="s">
         <v>2370</v>
@@ -61767,10 +62086,10 @@
     </row>
     <row r="1301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1301" s="29" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="B1301" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1301" s="83" t="s">
         <v>2371</v>
@@ -61790,10 +62109,10 @@
     </row>
     <row r="1302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1302" s="29" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="B1302" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1302" s="83" t="s">
         <v>2372</v>
@@ -61813,10 +62132,10 @@
     </row>
     <row r="1303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1303" s="29" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B1303" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1303" s="83" t="s">
         <v>2373</v>
@@ -61836,10 +62155,10 @@
     </row>
     <row r="1304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1304" s="29" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="B1304" s="100" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="C1304" s="83" t="s">
         <v>2374</v>
@@ -61859,7 +62178,7 @@
     </row>
     <row r="1305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1305" s="29" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="B1305" s="85" t="s">
         <v>1654</v>
@@ -61892,7 +62211,7 @@
     </row>
     <row r="1306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1306" s="29" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B1306" s="85" t="s">
         <v>1654</v>
@@ -61925,7 +62244,7 @@
     </row>
     <row r="1307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1307" s="29" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B1307" s="85" t="s">
         <v>1654</v>
@@ -61958,7 +62277,7 @@
     </row>
     <row r="1308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1308" s="29" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B1308" s="85" t="s">
         <v>1654</v>
@@ -61991,7 +62310,7 @@
     </row>
     <row r="1309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1309" s="29" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="B1309" s="125"/>
       <c r="C1309" s="83"/>
@@ -62016,19 +62335,19 @@
     </row>
     <row r="1310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1310" s="29" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="B1310" s="100" t="s">
         <v>1322</v>
       </c>
       <c r="C1310" s="83" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D1310" s="85" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E1310" s="83" t="s">
         <v>3162</v>
-      </c>
-      <c r="E1310" s="83" t="s">
-        <v>3163</v>
       </c>
       <c r="F1310" s="31"/>
       <c r="G1310" s="31"/>
@@ -62041,19 +62360,19 @@
     </row>
     <row r="1311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1311" s="29" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="B1311" s="100" t="s">
         <v>1322</v>
       </c>
       <c r="C1311" s="83" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="D1311" s="85" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="E1311" s="83" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="F1311" s="31"/>
       <c r="G1311" s="31"/>
@@ -62066,19 +62385,19 @@
     </row>
     <row r="1312" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="29" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="B1312" s="85" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1312" s="83" t="s">
         <v>3162</v>
       </c>
-      <c r="C1312" s="83" t="s">
+      <c r="D1312" s="85" t="s">
         <v>3163</v>
       </c>
-      <c r="D1312" s="85" t="s">
-        <v>3164</v>
-      </c>
       <c r="E1312" s="83" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="F1312" s="31"/>
       <c r="G1312" s="31"/>
@@ -62091,13 +62410,13 @@
     </row>
     <row r="1313" spans="1:13" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="29" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="B1313" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C1313" s="82" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="D1313" s="100" t="s">
         <v>1030</v>
@@ -62118,19 +62437,19 @@
         <v>96</v>
       </c>
       <c r="J1313" s="29" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="K1313" s="29"/>
       <c r="L1313" s="31" t="s">
+        <v>3170</v>
+      </c>
+      <c r="M1313" s="29" t="s">
         <v>3171</v>
-      </c>
-      <c r="M1313" s="29" t="s">
-        <v>3172</v>
       </c>
     </row>
     <row r="1314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1314" s="29" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="B1314" s="100" t="s">
         <v>1030</v>
@@ -62148,7 +62467,7 @@
         <v>1530</v>
       </c>
       <c r="G1314" s="31" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="H1314" s="29">
         <v>0</v>
@@ -62157,29 +62476,29 @@
         <v>487</v>
       </c>
       <c r="J1314" s="29" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="K1314" s="29" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="L1314" s="31"/>
       <c r="M1314" s="29"/>
     </row>
     <row r="1315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1315" s="29" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B1315" s="100" t="s">
         <v>3178</v>
       </c>
-      <c r="B1315" s="100" t="s">
+      <c r="C1315" s="83" t="s">
         <v>3179</v>
-      </c>
-      <c r="C1315" s="83" t="s">
-        <v>3180</v>
       </c>
       <c r="D1315" s="85" t="s">
         <v>223</v>
       </c>
       <c r="E1315" s="83" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="F1315" s="31" t="s">
         <v>52</v>
@@ -62194,7 +62513,7 @@
         <v>96</v>
       </c>
       <c r="J1315" s="29" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="K1315" s="29"/>
       <c r="L1315" s="31"/>
@@ -62202,19 +62521,19 @@
     </row>
     <row r="1316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1316" s="29" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B1316" s="100" t="s">
         <v>3183</v>
       </c>
-      <c r="B1316" s="100" t="s">
-        <v>3184</v>
-      </c>
       <c r="C1316" s="83" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="D1316" s="85" t="s">
         <v>223</v>
       </c>
       <c r="E1316" s="83" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="F1316" s="31" t="s">
         <v>52</v>
@@ -62229,7 +62548,7 @@
         <v>96</v>
       </c>
       <c r="J1316" s="29" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="K1316" s="29"/>
       <c r="L1316" s="31"/>
@@ -62237,7 +62556,7 @@
     </row>
     <row r="1317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1317" s="29" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="B1317" s="100" t="s">
         <v>256</v>
@@ -62262,7 +62581,7 @@
         <v>96</v>
       </c>
       <c r="J1317" s="29" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="K1317" s="29"/>
       <c r="L1317" s="31"/>
@@ -62270,7 +62589,7 @@
     </row>
     <row r="1318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1318" s="29" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B1318" s="100" t="s">
         <v>256</v>
@@ -62279,7 +62598,7 @@
         <v>1210</v>
       </c>
       <c r="D1318" s="85" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="E1318" s="83" t="s">
         <v>2162</v>
@@ -62296,14 +62615,14 @@
       </c>
       <c r="J1318" s="29"/>
       <c r="K1318" s="29" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="L1318" s="31"/>
       <c r="M1318" s="29"/>
     </row>
     <row r="1319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1319" s="29" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="B1319" s="100" t="s">
         <v>256</v>
@@ -62320,7 +62639,7 @@
         <v>2985</v>
       </c>
       <c r="J1319" s="29" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="K1319" s="29"/>
       <c r="L1319" s="31"/>
@@ -62328,7 +62647,7 @@
     </row>
     <row r="1320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1320" s="29" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="B1320" s="100" t="s">
         <v>256</v>
@@ -62353,7 +62672,7 @@
         <v>96</v>
       </c>
       <c r="J1320" s="29" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="K1320" s="29" t="s">
         <v>449</v>
@@ -62363,7 +62682,7 @@
     </row>
     <row r="1321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1321" s="29" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B1321" s="100" t="s">
         <v>423</v>
@@ -62391,34 +62710,34 @@
       <c r="M1321" s="29"/>
     </row>
     <row r="1322" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1322" s="142" t="s">
-        <v>3200</v>
+      <c r="A1322" s="140" t="s">
+        <v>3199</v>
       </c>
       <c r="B1322" s="83" t="s">
         <v>423</v>
       </c>
-      <c r="C1322" s="143"/>
-      <c r="E1322" s="142"/>
-      <c r="F1322" s="142"/>
-      <c r="G1322" s="142"/>
-      <c r="H1322" s="142" t="s">
+      <c r="C1322" s="141"/>
+      <c r="E1322" s="140"/>
+      <c r="F1322" s="140"/>
+      <c r="G1322" s="140"/>
+      <c r="H1322" s="140" t="s">
         <v>278</v>
       </c>
-      <c r="I1322" s="142" t="s">
+      <c r="I1322" s="140" t="s">
         <v>96</v>
       </c>
-      <c r="J1322" s="142" t="s">
+      <c r="J1322" s="140" t="s">
         <v>423</v>
       </c>
       <c r="K1322" s="29" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="L1322" s="136"/>
       <c r="M1322" s="29"/>
     </row>
     <row r="1323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1323" s="29" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="B1323" s="133" t="s">
         <v>256</v>
@@ -62441,29 +62760,29 @@
         <v>96</v>
       </c>
       <c r="J1323" s="29" t="s">
+        <v>3202</v>
+      </c>
+      <c r="K1323" s="29" t="s">
         <v>3203</v>
-      </c>
-      <c r="K1323" s="29" t="s">
-        <v>3204</v>
       </c>
       <c r="L1323" s="136"/>
       <c r="M1323" s="29"/>
     </row>
     <row r="1324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1324" s="29" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B1324" s="133" t="s">
         <v>255</v>
       </c>
       <c r="C1324" s="134" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="D1324" s="135" t="s">
         <v>256</v>
       </c>
       <c r="E1324" s="134" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="F1324" s="136"/>
       <c r="G1324" s="136"/>
@@ -62478,7 +62797,7 @@
     </row>
     <row r="1325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1325" s="29" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="B1325" s="133" t="s">
         <v>255</v>
@@ -62487,10 +62806,10 @@
         <v>2541</v>
       </c>
       <c r="D1325" s="135" t="s">
+        <v>3209</v>
+      </c>
+      <c r="E1325" s="134" t="s">
         <v>3210</v>
-      </c>
-      <c r="E1325" s="134" t="s">
-        <v>3211</v>
       </c>
       <c r="F1325" s="136"/>
       <c r="G1325" s="136"/>
@@ -62501,7 +62820,7 @@
         <v>96</v>
       </c>
       <c r="J1325" s="29" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="K1325" s="29"/>
       <c r="L1325" s="136"/>
@@ -62509,7 +62828,7 @@
     </row>
     <row r="1326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1326" s="29" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="B1326" s="133"/>
       <c r="C1326" s="134"/>
@@ -62526,7 +62845,7 @@
     </row>
     <row r="1327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1327" s="29" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="B1327" s="133" t="s">
         <v>255</v>
@@ -62535,7 +62854,7 @@
         <v>1508</v>
       </c>
       <c r="D1327" s="135" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="E1327" s="134"/>
       <c r="F1327" s="136"/>
@@ -62545,7 +62864,7 @@
         <v>60</v>
       </c>
       <c r="J1327" s="29" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="K1327" s="29"/>
       <c r="L1327" s="136"/>
@@ -62553,7 +62872,7 @@
     </row>
     <row r="1328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1328" s="29" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="B1328" s="133" t="s">
         <v>255</v>
@@ -62562,7 +62881,7 @@
         <v>1207</v>
       </c>
       <c r="D1328" s="135" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="E1328" s="134"/>
       <c r="F1328" s="136"/>
@@ -62578,10 +62897,10 @@
     </row>
     <row r="1329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1329" s="31" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="B1329" s="133" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="C1329" s="134" t="s">
         <v>1122</v>
@@ -62590,7 +62909,7 @@
         <v>843</v>
       </c>
       <c r="E1329" s="134" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="F1329" s="136" t="s">
         <v>231</v>
@@ -62602,14 +62921,14 @@
       </c>
       <c r="J1329" s="29"/>
       <c r="K1329" s="29" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="L1329" s="136"/>
       <c r="M1329" s="29"/>
     </row>
     <row r="1330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1330" s="29" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="B1330" s="133" t="s">
         <v>255</v>
@@ -62628,29 +62947,29 @@
         <v>96</v>
       </c>
       <c r="J1330" s="29" t="s">
+        <v>3221</v>
+      </c>
+      <c r="K1330" s="29" t="s">
         <v>3222</v>
-      </c>
-      <c r="K1330" s="29" t="s">
-        <v>3223</v>
       </c>
       <c r="L1330" s="136"/>
       <c r="M1330" s="29"/>
     </row>
     <row r="1331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1331" s="29" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B1331" s="29" t="s">
         <v>3225</v>
       </c>
-      <c r="B1331" s="29" t="s">
-        <v>3226</v>
-      </c>
       <c r="C1331" s="134" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="D1331" s="133" t="s">
         <v>255</v>
       </c>
       <c r="E1331" s="134" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="F1331" s="136"/>
       <c r="G1331" s="136" t="s">
@@ -62663,7 +62982,7 @@
         <v>96</v>
       </c>
       <c r="J1331" s="29" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="K1331" s="29"/>
       <c r="L1331" s="136"/>
@@ -62671,19 +62990,19 @@
     </row>
     <row r="1332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1332" s="29" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B1332" s="135" t="s">
         <v>3226</v>
       </c>
-      <c r="B1332" s="135" t="s">
-        <v>3227</v>
-      </c>
       <c r="C1332" s="134" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="D1332" s="133" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E1332" s="134" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="F1332" s="136"/>
       <c r="G1332" s="136" t="s">
@@ -62694,7 +63013,7 @@
         <v>96</v>
       </c>
       <c r="J1332" s="29" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="K1332" s="29"/>
       <c r="L1332" s="136"/>
@@ -62702,7 +63021,7 @@
     </row>
     <row r="1333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1333" s="29" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="B1333" s="135" t="s">
         <v>3073</v>
@@ -62711,10 +63030,10 @@
         <v>2362</v>
       </c>
       <c r="D1333" s="29" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="E1333" s="134" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="F1333" s="136"/>
       <c r="G1333" s="136" t="s">
@@ -62725,7 +63044,7 @@
         <v>96</v>
       </c>
       <c r="J1333" s="29" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="K1333" s="29"/>
       <c r="L1333" s="136"/>
@@ -62733,7 +63052,7 @@
     </row>
     <row r="1334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1334" s="29" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="B1334" s="135" t="s">
         <v>240</v>
@@ -62756,7 +63075,7 @@
         <v>96</v>
       </c>
       <c r="J1334" s="29" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="K1334" s="29"/>
       <c r="L1334" s="136"/>
@@ -62764,7 +63083,7 @@
     </row>
     <row r="1335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1335" s="29" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="B1335" s="133" t="s">
         <v>1655</v>
@@ -62789,7 +63108,7 @@
         <v>96</v>
       </c>
       <c r="J1335" s="29" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="K1335" s="29"/>
       <c r="L1335" s="136"/>
@@ -62797,7 +63116,7 @@
     </row>
     <row r="1336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1336" s="29" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="B1336" s="133" t="s">
         <v>254</v>
@@ -62806,7 +63125,7 @@
         <v>1216</v>
       </c>
       <c r="D1336" s="85" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="E1336" s="83"/>
       <c r="F1336" s="136"/>
@@ -62818,7 +63137,7 @@
         <v>60</v>
       </c>
       <c r="J1336" s="29" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="K1336" s="29"/>
       <c r="L1336" s="136"/>
@@ -62826,7 +63145,7 @@
     </row>
     <row r="1337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1337" s="29" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="B1337" s="133" t="s">
         <v>254</v>
@@ -62835,7 +63154,7 @@
         <v>1508</v>
       </c>
       <c r="D1337" s="85" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="E1337" s="134"/>
       <c r="F1337" s="136"/>
@@ -62855,7 +63174,7 @@
     </row>
     <row r="1338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1338" s="29" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="B1338" s="133" t="s">
         <v>254</v>
@@ -62864,7 +63183,7 @@
         <v>1207</v>
       </c>
       <c r="D1338" s="85" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="E1338" s="134"/>
       <c r="F1338" s="136"/>
@@ -62884,7 +63203,7 @@
     </row>
     <row r="1339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1339" s="29" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="B1339" s="133" t="s">
         <v>254</v>
@@ -62907,7 +63226,7 @@
         <v>60</v>
       </c>
       <c r="J1339" s="29" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="K1339" s="29"/>
       <c r="L1339" s="136"/>
@@ -62915,58 +63234,58 @@
     </row>
     <row r="1340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1340" s="45" t="s">
-        <v>3249</v>
-      </c>
-      <c r="B1340" s="144" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B1340" s="142" t="s">
         <v>256</v>
       </c>
-      <c r="C1340" s="145" t="s">
-        <v>3251</v>
-      </c>
-      <c r="D1340" s="146" t="s">
+      <c r="C1340" s="143" t="s">
+        <v>3250</v>
+      </c>
+      <c r="D1340" s="144" t="s">
         <v>254</v>
       </c>
-      <c r="E1340" s="145" t="s">
-        <v>3207</v>
+      <c r="E1340" s="143" t="s">
+        <v>3206</v>
       </c>
       <c r="F1340" s="41"/>
       <c r="G1340" s="41" t="s">
         <v>1458</v>
       </c>
       <c r="H1340" s="45"/>
-      <c r="I1340" s="147" t="s">
+      <c r="I1340" s="145" t="s">
         <v>60</v>
       </c>
       <c r="J1340" s="45" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="K1340" s="45" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="L1340" s="136"/>
       <c r="M1340" s="29"/>
     </row>
     <row r="1341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1341" s="29" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B1341" s="133" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C1341" s="134" t="s">
+        <v>3257</v>
+      </c>
+      <c r="D1341" s="135" t="s">
         <v>3256</v>
       </c>
-      <c r="B1341" s="133" t="s">
-        <v>3272</v>
-      </c>
-      <c r="C1341" s="134" t="s">
-        <v>3258</v>
-      </c>
-      <c r="D1341" s="135" t="s">
+      <c r="E1341" s="134" t="s">
         <v>3257</v>
-      </c>
-      <c r="E1341" s="134" t="s">
-        <v>3258</v>
       </c>
       <c r="F1341" s="136" t="s">
         <v>894</v>
       </c>
       <c r="G1341" s="136" t="s">
-        <v>3270</v>
+        <v>3321</v>
       </c>
       <c r="H1341" s="137"/>
       <c r="I1341" s="119" t="s">
@@ -62974,23 +63293,23 @@
       </c>
       <c r="J1341" s="29"/>
       <c r="K1341" s="29" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
       <c r="L1341" s="136"/>
       <c r="M1341" s="29"/>
     </row>
     <row r="1342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1342" s="29" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="B1342" s="135" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="C1342" s="134" t="s">
         <v>708</v>
       </c>
       <c r="D1342" s="135" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="E1342" s="134" t="s">
         <v>449</v>
@@ -63014,22 +63333,22 @@
     </row>
     <row r="1343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1343" s="29" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="B1343" s="135" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
       <c r="C1343" s="134" t="s">
         <v>2541</v>
       </c>
       <c r="D1343" s="135" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="E1343" s="134" t="s">
         <v>444</v>
       </c>
       <c r="F1343" s="136" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="G1343" s="136" t="s">
         <v>1458</v>
@@ -63047,16 +63366,16 @@
     </row>
     <row r="1344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1344" s="29" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B1344" s="135" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C1344" s="134" t="s">
         <v>3263</v>
       </c>
-      <c r="B1344" s="135" t="s">
-        <v>3261</v>
-      </c>
-      <c r="C1344" s="134" t="s">
+      <c r="D1344" s="135" t="s">
         <v>3264</v>
-      </c>
-      <c r="D1344" s="135" t="s">
-        <v>3265</v>
       </c>
       <c r="E1344" s="134" t="s">
         <v>444</v>
@@ -63080,13 +63399,13 @@
     </row>
     <row r="1345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1345" s="29" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="B1345" s="135" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="C1345" s="134" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="D1345" s="135" t="s">
         <v>3073</v>
@@ -63115,7 +63434,7 @@
     </row>
     <row r="1346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1346" s="29" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
       <c r="B1346" s="135" t="s">
         <v>3073</v>
@@ -63127,7 +63446,7 @@
         <v>240</v>
       </c>
       <c r="E1346" s="134" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
       <c r="F1346" s="136"/>
       <c r="G1346" s="136" t="s">
@@ -63143,28 +63462,62 @@
       <c r="M1346" s="29"/>
     </row>
     <row r="1347" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1347" s="29"/>
-      <c r="B1347" s="133"/>
-      <c r="C1347" s="134"/>
-      <c r="D1347" s="135"/>
-      <c r="E1347" s="134"/>
-      <c r="F1347" s="136"/>
-      <c r="G1347" s="136"/>
+      <c r="A1347" s="29" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B1347" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1347" s="134" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D1347" s="148" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E1347" s="134" t="s">
+        <v>3277</v>
+      </c>
+      <c r="F1347" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1347" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1347" s="137"/>
-      <c r="I1347" s="119"/>
-      <c r="J1347" s="29"/>
-      <c r="K1347" s="29"/>
+      <c r="I1347" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1347" s="29" t="s">
+        <v>3279</v>
+      </c>
+      <c r="K1347" s="29" t="s">
+        <v>3278</v>
+      </c>
       <c r="L1347" s="136"/>
       <c r="M1347" s="29"/>
     </row>
     <row r="1348" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1348" s="29"/>
-      <c r="B1348" s="133"/>
-      <c r="C1348" s="134"/>
-      <c r="D1348" s="135"/>
-      <c r="E1348" s="134"/>
-      <c r="F1348" s="136"/>
-      <c r="G1348" s="136"/>
+      <c r="A1348" s="29" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B1348" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1348" s="134" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D1348" s="135" t="s">
+        <v>3280</v>
+      </c>
+      <c r="E1348" s="134" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1348" s="136" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1348" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1348" s="137"/>
       <c r="I1348" s="119"/>
       <c r="J1348" s="29"/>
@@ -63173,11 +63526,21 @@
       <c r="M1348" s="29"/>
     </row>
     <row r="1349" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1349" s="29"/>
-      <c r="B1349" s="133"/>
-      <c r="C1349" s="134"/>
-      <c r="D1349" s="135"/>
-      <c r="E1349" s="134"/>
+      <c r="A1349" s="29" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1349" s="133" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1349" s="134" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D1349" s="135" t="s">
+        <v>443</v>
+      </c>
+      <c r="E1349" s="134" t="s">
+        <v>2162</v>
+      </c>
       <c r="F1349" s="136"/>
       <c r="G1349" s="136"/>
       <c r="H1349" s="137"/>
@@ -63188,307 +63551,1772 @@
       <c r="M1349" s="29"/>
     </row>
     <row r="1350" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1350" s="29"/>
-      <c r="B1350" s="133"/>
-      <c r="C1350" s="134"/>
-      <c r="D1350" s="135"/>
-      <c r="E1350" s="134"/>
-      <c r="F1350" s="136"/>
-      <c r="G1350" s="136"/>
+      <c r="A1350" s="29" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B1350" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1350" s="134" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D1350" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1350" s="134" t="s">
+        <v>2360</v>
+      </c>
+      <c r="F1350" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1350" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1350" s="137"/>
-      <c r="I1350" s="119"/>
+      <c r="I1350" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1350" s="29"/>
       <c r="K1350" s="29"/>
       <c r="L1350" s="136"/>
       <c r="M1350" s="29"/>
     </row>
     <row r="1351" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1351" s="29"/>
-      <c r="B1351" s="133"/>
-      <c r="C1351" s="134"/>
-      <c r="D1351" s="135"/>
-      <c r="E1351" s="134"/>
-      <c r="F1351" s="136"/>
-      <c r="G1351" s="136"/>
+      <c r="A1351" s="29" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B1351" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1351" s="134" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D1351" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1351" s="134" t="s">
+        <v>2361</v>
+      </c>
+      <c r="F1351" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1351" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1351" s="137"/>
-      <c r="I1351" s="119"/>
+      <c r="I1351" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1351" s="29"/>
       <c r="K1351" s="29"/>
       <c r="L1351" s="136"/>
       <c r="M1351" s="29"/>
     </row>
     <row r="1352" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1352" s="29"/>
-      <c r="B1352" s="133"/>
-      <c r="C1352" s="134"/>
-      <c r="D1352" s="135"/>
-      <c r="E1352" s="134"/>
-      <c r="F1352" s="136"/>
-      <c r="G1352" s="136"/>
+      <c r="A1352" s="29" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B1352" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1352" s="134" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D1352" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1352" s="134" t="s">
+        <v>2362</v>
+      </c>
+      <c r="F1352" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1352" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1352" s="137"/>
-      <c r="I1352" s="119"/>
+      <c r="I1352" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1352" s="29"/>
       <c r="K1352" s="29"/>
       <c r="L1352" s="136"/>
       <c r="M1352" s="29"/>
     </row>
     <row r="1353" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1353" s="29"/>
-      <c r="B1353" s="133"/>
-      <c r="C1353" s="134"/>
-      <c r="D1353" s="135"/>
-      <c r="E1353" s="134"/>
-      <c r="F1353" s="136"/>
-      <c r="G1353" s="136"/>
+      <c r="A1353" s="29" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B1353" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1353" s="134" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D1353" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1353" s="134" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F1353" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1353" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1353" s="137"/>
-      <c r="I1353" s="119"/>
+      <c r="I1353" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1353" s="29"/>
       <c r="K1353" s="29"/>
       <c r="L1353" s="136"/>
       <c r="M1353" s="29"/>
     </row>
     <row r="1354" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1354" s="29"/>
-      <c r="B1354" s="133"/>
-      <c r="C1354" s="134"/>
-      <c r="D1354" s="135"/>
-      <c r="E1354" s="134"/>
-      <c r="F1354" s="136"/>
-      <c r="G1354" s="136"/>
+      <c r="A1354" s="29" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B1354" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1354" s="134" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D1354" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1354" s="134" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F1354" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1354" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1354" s="137"/>
-      <c r="I1354" s="119"/>
+      <c r="I1354" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1354" s="29"/>
       <c r="K1354" s="29"/>
       <c r="L1354" s="136"/>
       <c r="M1354" s="29"/>
     </row>
     <row r="1355" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1355" s="29"/>
-      <c r="B1355" s="133"/>
-      <c r="C1355" s="134"/>
-      <c r="D1355" s="135"/>
-      <c r="E1355" s="134"/>
-      <c r="F1355" s="136"/>
-      <c r="G1355" s="136"/>
+      <c r="A1355" s="29" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B1355" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1355" s="134" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D1355" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1355" s="134" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F1355" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1355" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1355" s="137"/>
-      <c r="I1355" s="119"/>
+      <c r="I1355" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1355" s="29"/>
       <c r="K1355" s="29"/>
       <c r="L1355" s="136"/>
       <c r="M1355" s="29"/>
     </row>
     <row r="1356" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1356" s="29"/>
-      <c r="B1356" s="133"/>
-      <c r="C1356" s="134"/>
-      <c r="D1356" s="135"/>
-      <c r="E1356" s="134"/>
-      <c r="F1356" s="136"/>
-      <c r="G1356" s="136"/>
+      <c r="A1356" s="29" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B1356" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1356" s="134" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D1356" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1356" s="134" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F1356" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1356" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1356" s="137"/>
-      <c r="I1356" s="119"/>
+      <c r="I1356" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1356" s="29"/>
       <c r="K1356" s="29"/>
       <c r="L1356" s="136"/>
       <c r="M1356" s="29"/>
     </row>
     <row r="1357" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1357" s="29"/>
-      <c r="B1357" s="133"/>
-      <c r="C1357" s="134"/>
-      <c r="D1357" s="135"/>
-      <c r="E1357" s="134"/>
-      <c r="F1357" s="136"/>
-      <c r="G1357" s="136"/>
+      <c r="A1357" s="29" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B1357" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1357" s="134" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D1357" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1357" s="134" t="s">
+        <v>2272</v>
+      </c>
+      <c r="F1357" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1357" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1357" s="137"/>
-      <c r="I1357" s="119"/>
+      <c r="I1357" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1357" s="29"/>
       <c r="K1357" s="29"/>
       <c r="L1357" s="136"/>
       <c r="M1357" s="29"/>
     </row>
     <row r="1358" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1358" s="29"/>
-      <c r="B1358" s="133"/>
-      <c r="C1358" s="134"/>
-      <c r="D1358" s="135"/>
-      <c r="E1358" s="134"/>
-      <c r="F1358" s="136"/>
-      <c r="G1358" s="136"/>
+      <c r="A1358" s="29" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B1358" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1358" s="134" t="s">
+        <v>2264</v>
+      </c>
+      <c r="D1358" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1358" s="134" t="s">
+        <v>2245</v>
+      </c>
+      <c r="F1358" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1358" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1358" s="137"/>
-      <c r="I1358" s="119"/>
+      <c r="I1358" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1358" s="29"/>
       <c r="K1358" s="29"/>
       <c r="L1358" s="136"/>
       <c r="M1358" s="29"/>
     </row>
     <row r="1359" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1359" s="29"/>
-      <c r="B1359" s="133"/>
-      <c r="C1359" s="134"/>
-      <c r="D1359" s="135"/>
-      <c r="E1359" s="134"/>
-      <c r="F1359" s="136"/>
-      <c r="G1359" s="136"/>
+      <c r="A1359" s="29" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B1359" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1359" s="134" t="s">
+        <v>2367</v>
+      </c>
+      <c r="D1359" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1359" s="134" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F1359" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1359" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1359" s="137"/>
-      <c r="I1359" s="119"/>
+      <c r="I1359" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1359" s="29"/>
       <c r="K1359" s="29"/>
       <c r="L1359" s="136"/>
       <c r="M1359" s="29"/>
     </row>
     <row r="1360" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1360" s="29"/>
-      <c r="B1360" s="133"/>
-      <c r="C1360" s="134"/>
-      <c r="D1360" s="135"/>
-      <c r="E1360" s="134"/>
-      <c r="F1360" s="136"/>
-      <c r="G1360" s="136"/>
+      <c r="A1360" s="29" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B1360" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1360" s="134" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D1360" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1360" s="134" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F1360" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1360" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1360" s="137"/>
-      <c r="I1360" s="119"/>
+      <c r="I1360" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1360" s="29"/>
       <c r="K1360" s="29"/>
       <c r="L1360" s="136"/>
       <c r="M1360" s="29"/>
     </row>
     <row r="1361" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1361" s="29"/>
-      <c r="B1361" s="133"/>
-      <c r="C1361" s="134"/>
-      <c r="D1361" s="135"/>
-      <c r="E1361" s="134"/>
-      <c r="F1361" s="136"/>
-      <c r="G1361" s="136"/>
+      <c r="A1361" s="29" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B1361" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1361" s="134" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D1361" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1361" s="134" t="s">
+        <v>1948</v>
+      </c>
+      <c r="F1361" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1361" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1361" s="137"/>
-      <c r="I1361" s="119"/>
+      <c r="I1361" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1361" s="29"/>
       <c r="K1361" s="29"/>
       <c r="L1361" s="136"/>
       <c r="M1361" s="29"/>
     </row>
     <row r="1362" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1362" s="29"/>
-      <c r="B1362" s="133"/>
-      <c r="C1362" s="134"/>
-      <c r="D1362" s="135"/>
-      <c r="E1362" s="134"/>
-      <c r="F1362" s="136"/>
-      <c r="G1362" s="136"/>
+      <c r="A1362" s="29" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B1362" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1362" s="134" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D1362" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1362" s="134" t="s">
+        <v>1831</v>
+      </c>
+      <c r="F1362" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1362" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1362" s="137"/>
-      <c r="I1362" s="119"/>
+      <c r="I1362" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1362" s="29"/>
       <c r="K1362" s="29"/>
       <c r="L1362" s="136"/>
       <c r="M1362" s="29"/>
     </row>
     <row r="1363" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1363" s="29"/>
-      <c r="B1363" s="133"/>
-      <c r="C1363" s="134"/>
-      <c r="D1363" s="135"/>
-      <c r="E1363" s="134"/>
-      <c r="F1363" s="136"/>
-      <c r="G1363" s="136"/>
+      <c r="A1363" s="29" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1363" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1363" s="134" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D1363" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1363" s="134" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F1363" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1363" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1363" s="137"/>
-      <c r="I1363" s="119"/>
+      <c r="I1363" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1363" s="29"/>
       <c r="K1363" s="29"/>
       <c r="L1363" s="136"/>
       <c r="M1363" s="29"/>
     </row>
     <row r="1364" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1364" s="29"/>
-      <c r="B1364" s="133"/>
-      <c r="C1364" s="134"/>
-      <c r="D1364" s="135"/>
-      <c r="E1364" s="134"/>
-      <c r="F1364" s="136"/>
-      <c r="G1364" s="136"/>
+      <c r="A1364" s="29" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B1364" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1364" s="134" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D1364" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1364" s="134" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F1364" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1364" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1364" s="137"/>
-      <c r="I1364" s="119"/>
+      <c r="I1364" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1364" s="29"/>
       <c r="K1364" s="29"/>
       <c r="L1364" s="136"/>
       <c r="M1364" s="29"/>
     </row>
     <row r="1365" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1365" s="29"/>
-      <c r="B1365" s="133"/>
-      <c r="C1365" s="134"/>
-      <c r="D1365" s="135"/>
-      <c r="E1365" s="134"/>
-      <c r="F1365" s="136"/>
-      <c r="G1365" s="136"/>
+      <c r="A1365" s="29" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1365" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1365" s="134" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D1365" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1365" s="134" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F1365" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1365" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1365" s="137"/>
-      <c r="I1365" s="119"/>
+      <c r="I1365" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1365" s="29"/>
       <c r="K1365" s="29"/>
       <c r="L1365" s="136"/>
       <c r="M1365" s="29"/>
     </row>
     <row r="1366" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1366" s="29"/>
-      <c r="B1366" s="133"/>
-      <c r="C1366" s="134"/>
-      <c r="D1366" s="135"/>
-      <c r="E1366" s="134"/>
-      <c r="F1366" s="136"/>
-      <c r="G1366" s="136"/>
+      <c r="A1366" s="29" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B1366" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1366" s="134" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D1366" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1366" s="134" t="s">
+        <v>1837</v>
+      </c>
+      <c r="F1366" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1366" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1366" s="137"/>
-      <c r="I1366" s="119"/>
+      <c r="I1366" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1366" s="29"/>
       <c r="K1366" s="29"/>
       <c r="L1366" s="136"/>
       <c r="M1366" s="29"/>
     </row>
     <row r="1367" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1367" s="29"/>
-      <c r="B1367" s="133"/>
-      <c r="C1367" s="134"/>
-      <c r="D1367" s="135"/>
-      <c r="E1367" s="134"/>
-      <c r="F1367" s="136"/>
-      <c r="G1367" s="136"/>
+      <c r="A1367" s="29" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B1367" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1367" s="134" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1367" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1367" s="134" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F1367" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1367" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1367" s="137"/>
-      <c r="I1367" s="119"/>
+      <c r="I1367" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1367" s="29"/>
       <c r="K1367" s="29"/>
       <c r="L1367" s="136"/>
       <c r="M1367" s="29"/>
     </row>
     <row r="1368" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1368" s="29"/>
-      <c r="B1368" s="133"/>
-      <c r="C1368" s="134"/>
-      <c r="D1368" s="135"/>
-      <c r="E1368" s="134"/>
-      <c r="F1368" s="136"/>
-      <c r="G1368" s="136"/>
+      <c r="A1368" s="29" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B1368" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1368" s="134" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D1368" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1368" s="134" t="s">
+        <v>2376</v>
+      </c>
+      <c r="F1368" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1368" s="136" t="s">
+        <v>1458</v>
+      </c>
       <c r="H1368" s="137"/>
-      <c r="I1368" s="119"/>
+      <c r="I1368" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1368" s="29"/>
       <c r="K1368" s="29"/>
       <c r="L1368" s="136"/>
       <c r="M1368" s="29"/>
     </row>
     <row r="1369" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1369" s="138"/>
-      <c r="B1369" s="133"/>
-      <c r="C1369" s="134"/>
-      <c r="D1369" s="135"/>
-      <c r="E1369" s="134"/>
-      <c r="F1369" s="139"/>
-      <c r="G1369" s="139"/>
-      <c r="H1369" s="140"/>
-      <c r="I1369" s="141"/>
+      <c r="A1369" s="29" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B1369" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1369" s="134" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D1369" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1369" s="134" t="s">
+        <v>2377</v>
+      </c>
+      <c r="F1369" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1369" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1369" s="137"/>
+      <c r="I1369" s="119" t="s">
+        <v>60</v>
+      </c>
       <c r="J1369" s="138"/>
       <c r="K1369" s="138"/>
       <c r="L1369" s="139"/>
       <c r="M1369" s="138"/>
     </row>
     <row r="1370" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="L1370" s="3"/>
+      <c r="A1370" s="29" t="s">
+        <v>3307</v>
+      </c>
+      <c r="B1370" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1370" s="134" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D1370" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1370" s="134" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F1370" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1370" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1370" s="137"/>
+      <c r="I1370" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1370" s="29"/>
+      <c r="K1370" s="29"/>
+      <c r="L1370" s="136"/>
+      <c r="M1370" s="29"/>
+    </row>
+    <row r="1371" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1371" s="29" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B1371" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1371" s="134" t="s">
+        <v>2372</v>
+      </c>
+      <c r="D1371" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1371" s="134" t="s">
+        <v>2379</v>
+      </c>
+      <c r="F1371" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1371" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1371" s="137"/>
+      <c r="I1371" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1371" s="29"/>
+      <c r="K1371" s="29"/>
+      <c r="L1371" s="136"/>
+      <c r="M1371" s="29"/>
+    </row>
+    <row r="1372" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1372" s="29" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B1372" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1372" s="134" t="s">
+        <v>2373</v>
+      </c>
+      <c r="D1372" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1372" s="134" t="s">
+        <v>2380</v>
+      </c>
+      <c r="F1372" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1372" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1372" s="137"/>
+      <c r="I1372" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1372" s="29"/>
+      <c r="K1372" s="29"/>
+      <c r="L1372" s="136"/>
+      <c r="M1372" s="29"/>
+    </row>
+    <row r="1373" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1373" s="29" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B1373" s="22" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1373" s="134" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D1373" s="89" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1373" s="134" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1373" s="136" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1373" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1373" s="137"/>
+      <c r="I1373" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1373" s="29"/>
+      <c r="K1373" s="29"/>
+      <c r="L1373" s="136"/>
+      <c r="M1373" s="29"/>
+    </row>
+    <row r="1374" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1374" s="29" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B1374" s="85" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1374" s="83" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1374" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1374" s="83" t="s">
+        <v>2266</v>
+      </c>
+      <c r="F1374" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1374" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1374" s="137"/>
+      <c r="I1374" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1374" s="29" t="s">
+        <v>3313</v>
+      </c>
+      <c r="K1374" s="29"/>
+      <c r="L1374" s="136"/>
+      <c r="M1374" s="29"/>
+    </row>
+    <row r="1375" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1375" s="29" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B1375" s="85" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1375" s="83" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D1375" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1375" s="83" t="s">
+        <v>2243</v>
+      </c>
+      <c r="F1375" s="136" t="s">
+        <v>231</v>
+      </c>
+      <c r="G1375" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1375" s="137"/>
+      <c r="I1375" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1375" s="29"/>
+      <c r="K1375" s="29"/>
+      <c r="L1375" s="136"/>
+      <c r="M1375" s="29"/>
+    </row>
+    <row r="1376" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1376" s="29" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B1376" s="85" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1376" s="83" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D1376" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1376" s="83" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F1376" s="136" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G1376" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1376" s="137"/>
+      <c r="I1376" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1376" s="29" t="s">
+        <v>3311</v>
+      </c>
+      <c r="K1376" s="29"/>
+      <c r="L1376" s="136"/>
+      <c r="M1376" s="29"/>
+    </row>
+    <row r="1377" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1377" s="29" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B1377" s="85" t="s">
+        <v>3073</v>
+      </c>
+      <c r="C1377" s="83" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D1377" s="85" t="s">
+        <v>3319</v>
+      </c>
+      <c r="E1377" s="83" t="s">
+        <v>3318</v>
+      </c>
+      <c r="F1377" s="136" t="s">
+        <v>3316</v>
+      </c>
+      <c r="G1377" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1377" s="137"/>
+      <c r="I1377" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1377" s="29" t="s">
+        <v>3320</v>
+      </c>
+      <c r="K1377" s="29"/>
+      <c r="L1377" s="136"/>
+      <c r="M1377" s="29"/>
+    </row>
+    <row r="1378" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1378" s="29" t="s">
+        <v>3337</v>
+      </c>
+      <c r="B1378" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1378" s="83" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D1378" s="85" t="s">
+        <v>3322</v>
+      </c>
+      <c r="E1378" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1378" s="136"/>
+      <c r="G1378" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1378" s="137"/>
+      <c r="I1378" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1378" s="29" t="s">
+        <v>3361</v>
+      </c>
+      <c r="K1378" s="29"/>
+      <c r="L1378" s="136"/>
+      <c r="M1378" s="29"/>
+    </row>
+    <row r="1379" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1379" s="29" t="s">
+        <v>3338</v>
+      </c>
+      <c r="B1379" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1379" s="83" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D1379" s="85" t="s">
+        <v>3323</v>
+      </c>
+      <c r="E1379" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1379" s="136"/>
+      <c r="G1379" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1379" s="137"/>
+      <c r="I1379" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1379" s="29" t="s">
+        <v>3362</v>
+      </c>
+      <c r="K1379" s="29"/>
+      <c r="L1379" s="136"/>
+      <c r="M1379" s="29"/>
+    </row>
+    <row r="1380" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1380" s="29" t="s">
+        <v>3339</v>
+      </c>
+      <c r="B1380" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1380" s="83" t="s">
+        <v>2362</v>
+      </c>
+      <c r="D1380" s="85" t="s">
+        <v>3324</v>
+      </c>
+      <c r="E1380" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1380" s="136"/>
+      <c r="G1380" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1380" s="137"/>
+      <c r="I1380" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1380" s="29" t="s">
+        <v>3363</v>
+      </c>
+      <c r="K1380" s="29"/>
+      <c r="L1380" s="136"/>
+      <c r="M1380" s="29"/>
+    </row>
+    <row r="1381" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1381" s="29" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B1381" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1381" s="83" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D1381" s="85" t="s">
+        <v>3325</v>
+      </c>
+      <c r="E1381" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1381" s="136"/>
+      <c r="G1381" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1381" s="137"/>
+      <c r="I1381" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1381" s="29" t="s">
+        <v>3364</v>
+      </c>
+      <c r="K1381" s="29"/>
+      <c r="L1381" s="136"/>
+      <c r="M1381" s="29"/>
+    </row>
+    <row r="1382" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1382" s="29" t="s">
+        <v>3341</v>
+      </c>
+      <c r="B1382" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1382" s="83" t="s">
+        <v>2270</v>
+      </c>
+      <c r="D1382" s="85" t="s">
+        <v>3326</v>
+      </c>
+      <c r="E1382" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1382" s="136"/>
+      <c r="G1382" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1382" s="137"/>
+      <c r="I1382" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1382" s="29" t="s">
+        <v>3365</v>
+      </c>
+      <c r="K1382" s="29"/>
+      <c r="L1382" s="136"/>
+      <c r="M1382" s="29"/>
+    </row>
+    <row r="1383" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1383" s="29" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B1383" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1383" s="83" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D1383" s="85" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E1383" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1383" s="136"/>
+      <c r="G1383" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1383" s="137"/>
+      <c r="I1383" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1383" s="29" t="s">
+        <v>3366</v>
+      </c>
+      <c r="K1383" s="29"/>
+      <c r="L1383" s="136"/>
+      <c r="M1383" s="29"/>
+    </row>
+    <row r="1384" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1384" s="29" t="s">
+        <v>3343</v>
+      </c>
+      <c r="B1384" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1384" s="83" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D1384" s="85" t="s">
+        <v>3328</v>
+      </c>
+      <c r="E1384" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1384" s="136"/>
+      <c r="G1384" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1384" s="137"/>
+      <c r="I1384" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1384" s="29" t="s">
+        <v>3367</v>
+      </c>
+      <c r="K1384" s="29"/>
+      <c r="L1384" s="136"/>
+      <c r="M1384" s="29"/>
+    </row>
+    <row r="1385" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1385" s="29" t="s">
+        <v>3344</v>
+      </c>
+      <c r="B1385" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1385" s="83" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D1385" s="85" t="s">
+        <v>3329</v>
+      </c>
+      <c r="E1385" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1385" s="136"/>
+      <c r="G1385" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1385" s="137"/>
+      <c r="I1385" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1385" s="29" t="s">
+        <v>3368</v>
+      </c>
+      <c r="K1385" s="29"/>
+      <c r="L1385" s="136"/>
+      <c r="M1385" s="29"/>
+    </row>
+    <row r="1386" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1386" s="29" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B1386" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1386" s="83" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D1386" s="85" t="s">
+        <v>3330</v>
+      </c>
+      <c r="E1386" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1386" s="136"/>
+      <c r="G1386" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1386" s="137"/>
+      <c r="I1386" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1386" s="29" t="s">
+        <v>3369</v>
+      </c>
+      <c r="K1386" s="29"/>
+      <c r="L1386" s="136"/>
+      <c r="M1386" s="29"/>
+    </row>
+    <row r="1387" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1387" s="29" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B1387" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1387" s="83" t="s">
+        <v>2273</v>
+      </c>
+      <c r="D1387" s="85"/>
+      <c r="E1387" s="83"/>
+      <c r="F1387" s="136"/>
+      <c r="G1387" s="136"/>
+      <c r="H1387" s="137"/>
+      <c r="I1387" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1387" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1387" s="29"/>
+      <c r="L1387" s="136"/>
+      <c r="M1387" s="29"/>
+    </row>
+    <row r="1388" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1388" s="29" t="s">
+        <v>3346</v>
+      </c>
+      <c r="B1388" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1388" s="83" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D1388" s="85" t="s">
+        <v>3331</v>
+      </c>
+      <c r="E1388" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1388" s="136"/>
+      <c r="G1388" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1388" s="137"/>
+      <c r="I1388" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1388" s="29" t="s">
+        <v>3370</v>
+      </c>
+      <c r="K1388" s="29"/>
+      <c r="L1388" s="136"/>
+      <c r="M1388" s="29"/>
+    </row>
+    <row r="1389" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1389" s="29" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B1389" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1389" s="83" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D1389" s="85" t="s">
+        <v>3332</v>
+      </c>
+      <c r="E1389" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1389" s="136"/>
+      <c r="G1389" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1389" s="137"/>
+      <c r="I1389" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1389" s="29" t="s">
+        <v>3371</v>
+      </c>
+      <c r="K1389" s="29"/>
+      <c r="L1389" s="136"/>
+      <c r="M1389" s="29"/>
+    </row>
+    <row r="1390" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1390" s="29" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B1390" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1390" s="83" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D1390" s="85" t="s">
+        <v>3333</v>
+      </c>
+      <c r="E1390" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1390" s="136"/>
+      <c r="G1390" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1390" s="137"/>
+      <c r="I1390" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1390" s="29" t="s">
+        <v>3371</v>
+      </c>
+      <c r="K1390" s="29"/>
+      <c r="L1390" s="136"/>
+      <c r="M1390" s="29"/>
+    </row>
+    <row r="1391" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1391" s="29" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B1391" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1391" s="83" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D1391" s="85" t="s">
+        <v>3334</v>
+      </c>
+      <c r="E1391" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1391" s="136"/>
+      <c r="G1391" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1391" s="137"/>
+      <c r="I1391" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1391" s="29" t="s">
+        <v>3371</v>
+      </c>
+      <c r="K1391" s="29"/>
+      <c r="L1391" s="136"/>
+      <c r="M1391" s="29"/>
+    </row>
+    <row r="1392" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1392" s="29" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B1392" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1392" s="83" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D1392" s="85" t="s">
+        <v>3335</v>
+      </c>
+      <c r="E1392" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1392" s="136"/>
+      <c r="G1392" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1392" s="137"/>
+      <c r="I1392" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1392" s="29" t="s">
+        <v>3371</v>
+      </c>
+      <c r="K1392" s="29"/>
+      <c r="L1392" s="136"/>
+      <c r="M1392" s="29"/>
+    </row>
+    <row r="1393" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1393" s="29" t="s">
+        <v>3351</v>
+      </c>
+      <c r="B1393" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1393" s="83" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D1393" s="85" t="s">
+        <v>3336</v>
+      </c>
+      <c r="E1393" s="83" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F1393" s="136"/>
+      <c r="G1393" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1393" s="137"/>
+      <c r="I1393" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1393" s="29" t="s">
+        <v>3372</v>
+      </c>
+      <c r="K1393" s="29"/>
+      <c r="L1393" s="136"/>
+      <c r="M1393" s="29"/>
+    </row>
+    <row r="1394" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1394" s="29" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B1394" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1394" s="83" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D1394" s="85" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1394" s="83" t="s">
+        <v>3374</v>
+      </c>
+      <c r="F1394" s="136"/>
+      <c r="G1394" s="136" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H1394" s="137"/>
+      <c r="I1394" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1394" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1394" s="29"/>
+      <c r="L1394" s="136"/>
+      <c r="M1394" s="29"/>
+    </row>
+    <row r="1395" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1395" s="29" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B1395" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1395" s="83" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1395" s="85"/>
+      <c r="E1395" s="83"/>
+      <c r="F1395" s="136"/>
+      <c r="G1395" s="136"/>
+      <c r="H1395" s="137"/>
+      <c r="I1395" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1395" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1395" s="29"/>
+      <c r="L1395" s="136"/>
+      <c r="M1395" s="29"/>
+    </row>
+    <row r="1396" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1396" s="29" t="s">
+        <v>3355</v>
+      </c>
+      <c r="B1396" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1396" s="83" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D1396" s="85"/>
+      <c r="E1396" s="83"/>
+      <c r="F1396" s="136"/>
+      <c r="G1396" s="136"/>
+      <c r="H1396" s="137"/>
+      <c r="I1396" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1396" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1396" s="29"/>
+      <c r="L1396" s="136"/>
+      <c r="M1396" s="29"/>
+    </row>
+    <row r="1397" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1397" s="29" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B1397" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1397" s="83" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D1397" s="85"/>
+      <c r="E1397" s="83"/>
+      <c r="F1397" s="136"/>
+      <c r="G1397" s="136"/>
+      <c r="H1397" s="137"/>
+      <c r="I1397" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1397" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1397" s="29"/>
+      <c r="L1397" s="136"/>
+      <c r="M1397" s="29"/>
+    </row>
+    <row r="1398" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1398" s="29" t="s">
+        <v>3357</v>
+      </c>
+      <c r="B1398" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1398" s="83" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D1398" s="85"/>
+      <c r="E1398" s="83"/>
+      <c r="F1398" s="136"/>
+      <c r="G1398" s="136"/>
+      <c r="H1398" s="137"/>
+      <c r="I1398" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1398" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1398" s="29"/>
+      <c r="L1398" s="136"/>
+      <c r="M1398" s="29"/>
+    </row>
+    <row r="1399" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1399" s="29" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B1399" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1399" s="83" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D1399" s="85"/>
+      <c r="E1399" s="83"/>
+      <c r="F1399" s="136"/>
+      <c r="G1399" s="136"/>
+      <c r="H1399" s="137"/>
+      <c r="I1399" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1399" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1399" s="29"/>
+      <c r="L1399" s="136"/>
+      <c r="M1399" s="29"/>
+    </row>
+    <row r="1400" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1400" s="29" t="s">
+        <v>3359</v>
+      </c>
+      <c r="B1400" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1400" s="83" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D1400" s="85"/>
+      <c r="E1400" s="83"/>
+      <c r="F1400" s="136"/>
+      <c r="G1400" s="136"/>
+      <c r="H1400" s="137"/>
+      <c r="I1400" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1400" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1400" s="29"/>
+      <c r="L1400" s="136"/>
+      <c r="M1400" s="29"/>
+    </row>
+    <row r="1401" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1401" s="29" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B1401" s="100" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1401" s="83" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D1401" s="85"/>
+      <c r="E1401" s="83"/>
+      <c r="F1401" s="136"/>
+      <c r="G1401" s="136"/>
+      <c r="H1401" s="137"/>
+      <c r="I1401" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1401" s="29" t="s">
+        <v>3373</v>
+      </c>
+      <c r="K1401" s="29"/>
+      <c r="L1401" s="136"/>
+      <c r="M1401" s="29"/>
+    </row>
+    <row r="1402" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1402" s="29"/>
+      <c r="B1402" s="100"/>
+      <c r="C1402" s="83"/>
+      <c r="D1402" s="85"/>
+      <c r="E1402" s="83"/>
+      <c r="F1402" s="136"/>
+      <c r="G1402" s="136"/>
+      <c r="H1402" s="137"/>
+      <c r="I1402" s="119"/>
+      <c r="J1402" s="29"/>
+      <c r="K1402" s="29"/>
+      <c r="L1402" s="136"/>
+      <c r="M1402" s="29"/>
+    </row>
+    <row r="1403" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1403" s="29"/>
+      <c r="B1403" s="100"/>
+      <c r="C1403" s="83"/>
+      <c r="D1403" s="85"/>
+      <c r="E1403" s="83"/>
+      <c r="F1403" s="136"/>
+      <c r="G1403" s="136"/>
+      <c r="H1403" s="137"/>
+      <c r="I1403" s="119"/>
+      <c r="J1403" s="29"/>
+      <c r="K1403" s="29"/>
+      <c r="L1403" s="136"/>
+      <c r="M1403" s="29"/>
+    </row>
+    <row r="1404" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1404" s="29"/>
+      <c r="B1404" s="100"/>
+      <c r="C1404" s="83"/>
+      <c r="D1404" s="85"/>
+      <c r="E1404" s="83"/>
+      <c r="F1404" s="136"/>
+      <c r="G1404" s="136"/>
+      <c r="H1404" s="137"/>
+      <c r="I1404" s="119"/>
+      <c r="J1404" s="29"/>
+      <c r="K1404" s="29"/>
+      <c r="L1404" s="136"/>
+      <c r="M1404" s="29"/>
+    </row>
+    <row r="1405" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1405" s="29"/>
+      <c r="B1405" s="100"/>
+      <c r="C1405" s="83"/>
+      <c r="D1405" s="85"/>
+      <c r="E1405" s="83"/>
+      <c r="F1405" s="136"/>
+      <c r="G1405" s="136"/>
+      <c r="H1405" s="137"/>
+      <c r="I1405" s="119"/>
+      <c r="J1405" s="29"/>
+      <c r="K1405" s="29"/>
+      <c r="L1405" s="136"/>
+      <c r="M1405" s="29"/>
+    </row>
+    <row r="1406" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1406" s="29"/>
+      <c r="B1406" s="100"/>
+      <c r="C1406" s="83"/>
+      <c r="D1406" s="85"/>
+      <c r="E1406" s="83"/>
+      <c r="F1406" s="136"/>
+      <c r="G1406" s="136"/>
+      <c r="H1406" s="137"/>
+      <c r="I1406" s="119"/>
+      <c r="J1406" s="29"/>
+      <c r="K1406" s="29"/>
+      <c r="L1406" s="136"/>
+      <c r="M1406" s="29"/>
+    </row>
+    <row r="1407" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1407" s="29"/>
+      <c r="B1407" s="100"/>
+      <c r="C1407" s="83"/>
+      <c r="D1407" s="85"/>
+      <c r="E1407" s="83"/>
+      <c r="F1407" s="136"/>
+      <c r="G1407" s="136"/>
+      <c r="H1407" s="137"/>
+      <c r="I1407" s="119"/>
+      <c r="J1407" s="29"/>
+      <c r="K1407" s="29"/>
+      <c r="L1407" s="136"/>
+      <c r="M1407" s="29"/>
+    </row>
+    <row r="1408" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1408" s="29"/>
+      <c r="B1408" s="100"/>
+      <c r="C1408" s="83"/>
+      <c r="D1408" s="85"/>
+      <c r="E1408" s="83"/>
+      <c r="F1408" s="136"/>
+      <c r="G1408" s="136"/>
+      <c r="H1408" s="137"/>
+      <c r="I1408" s="119"/>
+      <c r="J1408" s="29"/>
+      <c r="K1408" s="29"/>
+      <c r="L1408" s="136"/>
+      <c r="M1408" s="29"/>
+    </row>
+    <row r="1409" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1409" s="29"/>
+      <c r="B1409" s="100"/>
+      <c r="C1409" s="83"/>
+      <c r="D1409" s="85"/>
+      <c r="E1409" s="83"/>
+      <c r="F1409" s="136"/>
+      <c r="G1409" s="136"/>
+      <c r="H1409" s="137"/>
+      <c r="I1409" s="119"/>
+      <c r="J1409" s="29"/>
+      <c r="K1409" s="29"/>
+      <c r="L1409" s="136"/>
+      <c r="M1409" s="29"/>
+    </row>
+    <row r="1410" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1410" s="29"/>
+      <c r="B1410" s="100"/>
+      <c r="C1410" s="83"/>
+      <c r="D1410" s="85"/>
+      <c r="E1410" s="83"/>
+      <c r="F1410" s="136"/>
+      <c r="G1410" s="136"/>
+      <c r="H1410" s="137"/>
+      <c r="I1410" s="119"/>
+      <c r="J1410" s="29"/>
+      <c r="K1410" s="29"/>
+      <c r="L1410" s="136"/>
+      <c r="M1410" s="29"/>
+    </row>
+    <row r="1411" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1411" s="29"/>
+      <c r="B1411" s="100"/>
+      <c r="C1411" s="83"/>
+      <c r="D1411" s="85"/>
+      <c r="E1411" s="83"/>
+      <c r="F1411" s="136"/>
+      <c r="G1411" s="136"/>
+      <c r="H1411" s="137"/>
+      <c r="I1411" s="119"/>
+      <c r="J1411" s="29"/>
+      <c r="K1411" s="29"/>
+      <c r="L1411" s="136"/>
+      <c r="M1411" s="29"/>
+    </row>
+    <row r="1412" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1412" s="29"/>
+      <c r="B1412" s="100"/>
+      <c r="C1412" s="83"/>
+      <c r="D1412" s="85"/>
+      <c r="E1412" s="83"/>
+      <c r="F1412" s="136"/>
+      <c r="G1412" s="136"/>
+      <c r="H1412" s="137"/>
+      <c r="I1412" s="119"/>
+      <c r="J1412" s="29"/>
+      <c r="K1412" s="29"/>
+      <c r="L1412" s="136"/>
+      <c r="M1412" s="29"/>
+    </row>
+    <row r="1413" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1413" s="29"/>
+      <c r="B1413" s="100"/>
+      <c r="C1413" s="83"/>
+      <c r="D1413" s="85"/>
+      <c r="E1413" s="83"/>
+      <c r="F1413" s="136"/>
+      <c r="G1413" s="136"/>
+      <c r="H1413" s="137"/>
+      <c r="I1413" s="119"/>
+      <c r="J1413" s="29"/>
+      <c r="K1413" s="29"/>
+      <c r="L1413" s="136"/>
+      <c r="M1413" s="29"/>
+    </row>
+    <row r="1414" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1414" s="29"/>
+      <c r="B1414" s="100"/>
+      <c r="C1414" s="83"/>
+      <c r="D1414" s="85"/>
+      <c r="E1414" s="83"/>
+      <c r="F1414" s="136"/>
+      <c r="G1414" s="136"/>
+      <c r="H1414" s="137"/>
+      <c r="I1414" s="119"/>
+      <c r="J1414" s="29"/>
+      <c r="K1414" s="29"/>
+      <c r="L1414" s="136"/>
+      <c r="M1414" s="29"/>
+    </row>
+    <row r="1415" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L1415" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D0F113-2FB3-A843-92AA-3EBEB9065D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7496C55C-2F9D-8C41-83FC-0C6127F97750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11450" uniqueCount="3373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11456" uniqueCount="3373">
   <si>
     <t>Tag</t>
   </si>
@@ -23843,8 +23843,12 @@
       <c r="G112" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H112" s="23"/>
-      <c r="I112" s="23"/>
+      <c r="H112" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I112" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="J112" s="29"/>
       <c r="K112" s="23"/>
       <c r="L112" s="23"/>
@@ -23866,10 +23870,18 @@
       <c r="E113" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="F113" s="23"/>
-      <c r="G113" s="22"/>
-      <c r="H113" s="23"/>
-      <c r="I113" s="23"/>
+      <c r="F113" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G113" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H113" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I113" s="23" t="s">
+        <v>96</v>
+      </c>
       <c r="J113" s="23"/>
       <c r="K113" s="23"/>
       <c r="L113" s="19"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2D2D56-4487-DB47-A4D9-F688FE78D3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5936473-6982-8F46-90C8-6E0110B20075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -10171,7 +10171,7 @@
     <t>2308-1104-int</t>
   </si>
   <si>
-    <t>2606-2810-1</t>
+    <t>2606-2810</t>
   </si>
 </sst>
 </file>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5E6497-65FD-B94F-BC9D-5792B5415208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE392FE4-4E2F-E346-BADB-D99B5DE1D71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11452" uniqueCount="3374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11454" uniqueCount="3375">
   <si>
     <t>Tag</t>
   </si>
@@ -10166,6 +10166,9 @@
   </si>
   <si>
     <t>i875</t>
+  </si>
+  <si>
+    <t>blank1402</t>
   </si>
 </sst>
 </file>
@@ -65148,7 +65151,9 @@
       <c r="M1401" s="29"/>
     </row>
     <row r="1402" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1402" s="29"/>
+      <c r="A1402" s="29" t="s">
+        <v>3374</v>
+      </c>
       <c r="B1402" s="100"/>
       <c r="C1402" s="83"/>
       <c r="D1402" s="85"/>
@@ -65157,7 +65162,9 @@
       <c r="G1402" s="136"/>
       <c r="H1402" s="137"/>
       <c r="I1402" s="119"/>
-      <c r="J1402" s="29"/>
+      <c r="J1402" s="29" t="s">
+        <v>418</v>
+      </c>
       <c r="K1402" s="29"/>
       <c r="L1402" s="136"/>
       <c r="M1402" s="29"/>

--- a/cables.xlsx
+++ b/cables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donert/Documents/UACTech/uacdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE392FE4-4E2F-E346-BADB-D99B5DE1D71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1437D667-1511-684A-B0A9-18D619F1DBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="1520" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
+    <workbookView xWindow="1820" yWindow="760" windowWidth="26600" windowHeight="18020" xr2:uid="{288904EE-D384-EA4C-9B98-052B972FB267}"/>
   </bookViews>
   <sheets>
     <sheet name="Cables" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
-    <pivotCache cacheId="19" r:id="rId4"/>
+    <pivotCache cacheId="20" r:id="rId3"/>
+    <pivotCache cacheId="21" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11454" uniqueCount="3375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11454" uniqueCount="3374">
   <si>
     <t>Tag</t>
   </si>
@@ -10160,9 +10160,6 @@
   </si>
   <si>
     <t>2308-1104-int</t>
-  </si>
-  <si>
-    <t>2606-2810</t>
   </si>
   <si>
     <t>i875</t>
@@ -10608,7 +10605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -10862,35 +10859,13 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -10898,22 +10873,43 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
+        <sz val="11"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+   